--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R50a8b21eff784068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R9e35382064264bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R3c81870c173245d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R2ed5d66aaea448e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R074365b27a95444c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rc24a5773a9dc41a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4b0177e8540648c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R7c0fd581062f46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rabb7a57e16af4669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R5868b1daef764190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R929cd4c3a95e4539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rbb156853c393496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R2df0b55a782b4e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R72d3b112f49e4239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R5ef886061503449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R79489a36fe6741de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -483,25 +483,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>8740.668</x:v>
+        <x:v>8489.476</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>8559.285</x:v>
+        <x:v>8261.398</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>181.4</x:v>
+        <x:v>228.1</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>19644.1</x:v>
+        <x:v>20134.1</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>165.1</x:v>
+        <x:v>166.4</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -512,25 +512,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8860.416</x:v>
+        <x:v>8663.665</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>8636.15</x:v>
+        <x:v>8457.576</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>224.3</x:v>
+        <x:v>206.1</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>19815.1</x:v>
+        <x:v>20273.4</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>166.5</x:v>
+        <x:v>167.5</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -541,25 +541,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>4073.88</x:v>
+        <x:v>4028.514</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>4027.255</x:v>
+        <x:v>3971.713</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>46.6</x:v>
+        <x:v>56.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>5612.6</x:v>
+        <x:v>5724.1</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.2</x:v>
+        <x:v>47.3</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -570,25 +570,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>8475</x:v>
+        <x:v>8274.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>8337.8</x:v>
+        <x:v>8068.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>137.2</x:v>
+        <x:v>205.4</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>21247.8</x:v>
+        <x:v>21660</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>178.6</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -599,25 +599,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8650</x:v>
+        <x:v>8478.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>8442</x:v>
+        <x:v>8281</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>208</x:v>
+        <x:v>197.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>22628.8</x:v>
+        <x:v>23034.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>190.2</x:v>
+        <x:v>190.4</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -628,25 +628,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4810.4</x:v>
+        <x:v>4752.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4728</x:v>
+        <x:v>4671.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>82.4</x:v>
+        <x:v>81.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>8573.8</x:v>
+        <x:v>8735.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -657,25 +657,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2912</x:v>
+        <x:v>2908.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2873.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>38.4</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>4836.4</x:v>
+        <x:v>4920</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.6</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -689,7 +689,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -4094,34 +4094,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>8694.805</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>8432.897</x:v>
+      </x:c>
+      <x:c r="F154" s="26" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>261.9</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>8489.476</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>8261.398</x:v>
+      </x:c>
+      <x:c r="F155" s="26" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>228.1</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>195.3</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>215.2</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7431,34 +7479,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>8823.05</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>8570.892</x:v>
+      </x:c>
+      <x:c r="F154" s="26" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>252.2</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>8663.665</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>8457.576</x:v>
+      </x:c>
+      <x:c r="F155" s="26" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>206.1</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>680.9</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>1139.2</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>227.8</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10768,34 +10864,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>4060.069</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>4005.414</x:v>
+      </x:c>
+      <x:c r="F154" s="26" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>54.7</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>4028.514</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>3971.713</x:v>
+      </x:c>
+      <x:c r="F155" s="26" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>56.8</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>176.9</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>288.4</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>57.7</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14105,34 +14249,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>8419.8</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>8213</x:v>
+      </x:c>
+      <x:c r="F154" s="26" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>206.8</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>8274.2</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>8068.8</x:v>
+      </x:c>
+      <x:c r="F155" s="26" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>205.4</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>498.2</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>910.4</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>166.1</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>182.1</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -17442,34 +17634,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>8584.2</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>8376</x:v>
+      </x:c>
+      <x:c r="F154" s="26" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>208.2</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>8478.8</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>8281</x:v>
+      </x:c>
+      <x:c r="F155" s="26" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>197.8</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>646.8</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>1052.8</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>215.6</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>210.6</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20779,34 +21019,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>4781.2</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>4701</x:v>
+      </x:c>
+      <x:c r="F154" s="24" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>80.2</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>4752.6</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>4671.4</x:v>
+      </x:c>
+      <x:c r="F155" s="24" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>81.2</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>436.4</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>91.7</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>87.3</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -24116,34 +24404,82 @@
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="33" t="str">
+      <x:c r="A154" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="23" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="24" t="n">
+        <x:v>2915</x:v>
+      </x:c>
+      <x:c r="E154" s="24" t="n">
+        <x:v>2877.4</x:v>
+      </x:c>
+      <x:c r="F154" s="24" t="n">
+        <x:f>ROUND(D154-E154,1)</x:f>
+        <x:v>37.6</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="23" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="24" t="n">
+        <x:v>2908.4</x:v>
+      </x:c>
+      <x:c r="E155" s="24" t="n">
+        <x:v>2862.4</x:v>
+      </x:c>
+      <x:c r="F155" s="24" t="n">
+        <x:f>ROUND(D155-E155,1)</x:f>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="33" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B154" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C154" s="32"/>
-      <x:c r="D154" s="32"/>
-      <x:c r="E154" s="32"/>
-      <x:c r="F154" s="34" t="n">
-        <x:f>ROUND(SUM(F151:F153),1)</x:f>
-        <x:v>159.2</x:v>
-      </x:c>
-      <x:c r="G154" s="32"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
+      <x:c r="B156" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C156" s="32"/>
+      <x:c r="D156" s="32"/>
+      <x:c r="E156" s="32"/>
+      <x:c r="F156" s="34" t="n">
+        <x:f>ROUND(SUM(F151:F155),1)</x:f>
+        <x:v>242.8</x:v>
+      </x:c>
+      <x:c r="G156" s="32"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="33" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B155" s="32"/>
-      <x:c r="C155" s="32"/>
-      <x:c r="D155" s="32"/>
-      <x:c r="E155" s="32"/>
-      <x:c r="F155" s="36" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(F151:F153),0),1)</x:f>
-        <x:v>53.1</x:v>
-      </x:c>
-      <x:c r="G155" s="32"/>
+      <x:c r="B157" s="32"/>
+      <x:c r="C157" s="32"/>
+      <x:c r="D157" s="32"/>
+      <x:c r="E157" s="32"/>
+      <x:c r="F157" s="36" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(F151:F155),0),1)</x:f>
+        <x:v>48.6</x:v>
+      </x:c>
+      <x:c r="G157" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R76c879b03e734238"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R925be213e87a469f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R3e0acb723ba64bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R47100fa0c4194121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R740ee4fc44fa4122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Ra2edc753f16f429f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Ra973b8625b43491a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rcc315af2530340a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R428509857a6b4527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re57a2ad2bd1b4fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R23abfd971ea24e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R9f2668ea5e994d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Re582d1f3fbb94019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R529d0f7e58f943c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R86f0ed9783174dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R952fc92eaae54a6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,25 +493,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>8489.476</x:v>
+        <x:v>8328.965</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>8261.398</x:v>
+        <x:v>8117.861</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>228.1</x:v>
+        <x:v>211.1</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>20134.1</x:v>
+        <x:v>20345.2</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>166.4</x:v>
+        <x:v>166.8</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -522,25 +522,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8663.665</x:v>
+        <x:v>8571.525</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>8457.576</x:v>
+        <x:v>8343.923</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>206.1</x:v>
+        <x:v>227.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>20273.4</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>167.5</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -551,22 +551,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>4028.514</x:v>
+        <x:v>4016.026</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3971.713</x:v>
+        <x:v>3967.913</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>56.8</x:v>
+        <x:v>48.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>5724.1</x:v>
+        <x:v>5772.2</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>47.3</x:v>
@@ -580,25 +580,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>8274.2</x:v>
+        <x:v>8149.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>8068.8</x:v>
+        <x:v>7965</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>205.4</x:v>
+        <x:v>184.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>21660</x:v>
+        <x:v>21844.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>179</x:v>
+        <x:v>179.1</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -609,25 +609,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8478.8</x:v>
+        <x:v>8376</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>8281</x:v>
+        <x:v>8203.6</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>197.8</x:v>
+        <x:v>172.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>23034.8</x:v>
+        <x:v>23207.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>190.4</x:v>
+        <x:v>190.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -638,25 +638,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4752.6</x:v>
+        <x:v>4747.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4671.4</x:v>
+        <x:v>4666</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>81.2</x:v>
+        <x:v>81.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>8735.2</x:v>
+        <x:v>8816.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.2</x:v>
+        <x:v>72.3</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -667,22 +667,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2908.4</x:v>
+        <x:v>2911</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2866.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>46</x:v>
+        <x:v>44.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>4920</x:v>
+        <x:v>4964.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>40.7</x:v>
@@ -699,7 +699,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -5364,40 +5364,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>1076</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>8315.962</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>8328.965</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>8117.861</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>8117.861</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.02215699142017813</x:v>
+      </x:c>
+      <x:c r="I156" s="27" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>211.1</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>215.2</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>1287.1</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>214.5</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9967,40 +10000,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>1139.2</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>8539.016</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>8571.525</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>8343.923</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>8390.019</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.013958508079116805</x:v>
+      </x:c>
+      <x:c r="I156" s="27" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>227.6</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>1366.8</x:v>
+      </x:c>
+      <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
         <x:v>227.8</x:v>
       </x:c>
-      <x:c r="J157" s="35"/>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14570,40 +14636,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>288.4</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>3996.807</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>4016.026</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>3967.913</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>3970.88</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.004850591506515234</x:v>
+      </x:c>
+      <x:c r="I156" s="24" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>48.1</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>57.7</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>336.5</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>56.1</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -19173,40 +19272,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>910.4</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>8140.2</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>8149.8</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>7965</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>7974</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.017399447949526747</x:v>
+      </x:c>
+      <x:c r="I156" s="24" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>184.8</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>182.1</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>1095.2</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>182.5</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -23776,40 +23908,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>1052.8</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>8376</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>8376</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>8203.6</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>8255.2</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.008098430778843091</x:v>
+      </x:c>
+      <x:c r="I156" s="27" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>172.4</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>210.6</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>1225.2</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>204.2</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -28379,40 +28544,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>436.4</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>4728</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>4747.6</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>4666</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>4668</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.007526470213037317</x:v>
+      </x:c>
+      <x:c r="I156" s="24" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>81.6</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>87.3</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>86.3</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32982,40 +33180,73 @@
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="36" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B156" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C156" s="35"/>
-      <x:c r="D156" s="35"/>
-      <x:c r="E156" s="35"/>
-      <x:c r="F156" s="35"/>
-      <x:c r="G156" s="35"/>
-      <x:c r="H156" s="35"/>
-      <x:c r="I156" s="37" t="n">
-        <x:f>ROUND(SUM(I151:I155),1)</x:f>
-        <x:v>242.8</x:v>
-      </x:c>
-      <x:c r="J156" s="35"/>
+      <x:c r="A156" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="23" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="24" t="n">
+        <x:v>2877.4</x:v>
+      </x:c>
+      <x:c r="E156" s="24" t="n">
+        <x:v>2911</x:v>
+      </x:c>
+      <x:c r="F156" s="24" t="n">
+        <x:v>2866.2</x:v>
+      </x:c>
+      <x:c r="G156" s="24" t="n">
+        <x:v>2868</x:v>
+      </x:c>
+      <x:c r="H156" s="25" t="n">
+        <x:v>-0.0009057339928933983</x:v>
+      </x:c>
+      <x:c r="I156" s="24" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>44.8</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B157" s="35"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C157" s="35"/>
       <x:c r="D157" s="35"/>
       <x:c r="E157" s="35"/>
       <x:c r="F157" s="35"/>
       <x:c r="G157" s="35"/>
       <x:c r="H157" s="35"/>
-      <x:c r="I157" s="39" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I151:I155),0),1)</x:f>
-        <x:v>48.6</x:v>
+      <x:c r="I157" s="37" t="n">
+        <x:f>ROUND(SUM(I151:I156),1)</x:f>
+        <x:v>287.6</x:v>
       </x:c>
       <x:c r="J157" s="35"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="36" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B158" s="35"/>
+      <x:c r="C158" s="35"/>
+      <x:c r="D158" s="35"/>
+      <x:c r="E158" s="35"/>
+      <x:c r="F158" s="35"/>
+      <x:c r="G158" s="35"/>
+      <x:c r="H158" s="35"/>
+      <x:c r="I158" s="39" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I151:I156),0),1)</x:f>
+        <x:v>47.9</x:v>
+      </x:c>
+      <x:c r="J158" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R428509857a6b4527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re57a2ad2bd1b4fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R23abfd971ea24e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R9f2668ea5e994d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Re582d1f3fbb94019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R529d0f7e58f943c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R86f0ed9783174dc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R952fc92eaae54a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6533aed68dd246ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R7bf3e5c015bd4d7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8e992f62f35c4a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rb8515c959fb94a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rda7d208b900f4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R31ad5425031f4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Rf5e0c8cbe40049d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R896fd459e8b843ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -699,7 +699,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6533aed68dd246ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R7bf3e5c015bd4d7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8e992f62f35c4a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rb8515c959fb94a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rda7d208b900f4d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R31ad5425031f4b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Rf5e0c8cbe40049d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R896fd459e8b843ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R2f31c8829fda446e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Rb2306be80fb1436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Ra58a7e1f4bc148de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R734fb67b1d7a43c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rd1f2363e0e324916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rb868944928a041ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R33032eeb92484c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R56246a3a1a184d6d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -699,7 +699,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rdab634c70c5d4353"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R3baa6502aa824f9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R6bebaa6043f24818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rfe25275d0ae54c04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rc00d6e029afb4701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R2f0128f016b04e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R7b70833213904f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R880670efc3d947ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4ee502befd8e4b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re4fdbc376ad54f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R66a6112174c94e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R7d214485518546e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rcfbab595b6a94beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rb519e8d2d05647e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Ra692667c59d24f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Ree364ef90ee44819"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>8312.621</x:v>
+        <x:v>8438.194</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7978.806</x:v>
+        <x:v>8198.308</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>333.8</x:v>
+        <x:v>239.9</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>20679</x:v>
+        <x:v>20918.9</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>168.1</x:v>
+        <x:v>168.7</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8659.65</x:v>
+        <x:v>8783.249</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>8281.953</x:v>
+        <x:v>8503.245</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>377.7</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>20878.7</x:v>
+        <x:v>21158.7</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>169.7</x:v>
+        <x:v>170.6</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>4040.539</x:v>
+        <x:v>4074.828</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3938.878</x:v>
+        <x:v>3995.807</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>101.7</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>5873.9</x:v>
+        <x:v>5952.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>8149.8</x:v>
+        <x:v>8244.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7965</x:v>
+        <x:v>8016</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>184.8</x:v>
+        <x:v>228.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>21844.8</x:v>
+        <x:v>22345.6</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>179.1</x:v>
+        <x:v>180.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8509.2</x:v>
+        <x:v>8618</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>8173</x:v>
+        <x:v>8330</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>336.2</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>23543.4</x:v>
+        <x:v>23831.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>191.4</x:v>
+        <x:v>192.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4747.6</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4666</x:v>
+        <x:v>4703.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>81.6</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>8816.8</x:v>
+        <x:v>9074.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.3</x:v>
+        <x:v>73.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2956.2</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2875</x:v>
+        <x:v>2908.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>81.2</x:v>
+        <x:v>75.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5046</x:v>
+        <x:v>5121.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>41.3</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -5860,30 +5860,48 @@
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B158" s="37" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J157),1)</x:f>
-        <x:v>1620.9</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>8312.492</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>8438.194</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>8198.308</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>8198.308</x:v>
+      </x:c>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-101.8</x:v>
+      </x:c>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.012261211552615503</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>239.9</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B159" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C159" s="37"/>
       <x:c r="D159" s="37"/>
       <x:c r="E159" s="37"/>
@@ -5891,11 +5909,29 @@
       <x:c r="G159" s="37"/>
       <x:c r="H159" s="37"/>
       <x:c r="I159" s="37"/>
-      <x:c r="J159" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J157),0),1)</x:f>
-        <x:v>231.6</x:v>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>1860.8</x:v>
       </x:c>
       <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>232.6</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10941,30 +10977,48 @@
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B158" s="37" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J157),1)</x:f>
-        <x:v>1744.5</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>8672.363</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>8783.249</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>8503.245</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>8503.971</x:v>
+      </x:c>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-148.8</x:v>
+      </x:c>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.01719862051382992</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B159" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C159" s="37"/>
       <x:c r="D159" s="37"/>
       <x:c r="E159" s="37"/>
@@ -10972,11 +11026,29 @@
       <x:c r="G159" s="37"/>
       <x:c r="H159" s="37"/>
       <x:c r="I159" s="37"/>
-      <x:c r="J159" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J157),0),1)</x:f>
-        <x:v>249.2</x:v>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>2024.5</x:v>
       </x:c>
       <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>253.1</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16022,30 +16094,48 @@
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B158" s="37" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J157),1)</x:f>
-        <x:v>438.2</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>4031.537</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>4074.828</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>3995.807</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>3996.162</x:v>
+      </x:c>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-40.4</x:v>
+      </x:c>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.010014893766715938</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B159" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C159" s="37"/>
       <x:c r="D159" s="37"/>
       <x:c r="E159" s="37"/>
@@ -16053,11 +16143,29 @@
       <x:c r="G159" s="37"/>
       <x:c r="H159" s="37"/>
       <x:c r="I159" s="37"/>
-      <x:c r="J159" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J157),0),1)</x:f>
-        <x:v>62.6</x:v>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>517.2</x:v>
       </x:c>
       <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>64.7</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20823,42 +20931,110 @@
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="38" t="str">
+      <x:c r="A157" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B157" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C157" s="23" t="str">
+        <x:v>7月9日</x:v>
+      </x:c>
+      <x:c r="D157" s="24" t="n">
+        <x:v>8034.8</x:v>
+      </x:c>
+      <x:c r="E157" s="24" t="n">
+        <x:v>8140.2</x:v>
+      </x:c>
+      <x:c r="F157" s="24" t="n">
+        <x:v>7868.2</x:v>
+      </x:c>
+      <x:c r="G157" s="24" t="n">
+        <x:v>8127.4</x:v>
+      </x:c>
+      <x:c r="H157" s="24"/>
+      <x:c r="I157" s="25" t="n">
+        <x:v>0.019237521946325442</x:v>
+      </x:c>
+      <x:c r="J157" s="29" t="n">
+        <x:f>ROUND(E157-F157,1)</x:f>
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="K157" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>8140.2</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>8244.8</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>8016</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>8019.4</x:v>
+      </x:c>
+      <x:c r="H158" s="24"/>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.013288382508551355</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>228.8</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B157" s="37" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C157" s="37"/>
-      <x:c r="D157" s="37"/>
-      <x:c r="E157" s="37"/>
-      <x:c r="F157" s="37"/>
-      <x:c r="G157" s="37"/>
-      <x:c r="H157" s="37"/>
-      <x:c r="I157" s="37"/>
-      <x:c r="J157" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J156),1)</x:f>
-        <x:v>1095.2</x:v>
-      </x:c>
-      <x:c r="K157" s="37"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="38" t="str">
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C159" s="37"/>
+      <x:c r="D159" s="37"/>
+      <x:c r="E159" s="37"/>
+      <x:c r="F159" s="37"/>
+      <x:c r="G159" s="37"/>
+      <x:c r="H159" s="37"/>
+      <x:c r="I159" s="37"/>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>1596</x:v>
+      </x:c>
+      <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B158" s="37"/>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J156),0),1)</x:f>
-        <x:v>182.5</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>199.5</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -25645,9 +25821,7 @@
       <x:c r="G157" s="24" t="n">
         <x:v>8502.4</x:v>
       </x:c>
-      <x:c r="H157" s="27" t="n">
-        <x:v>247.2</x:v>
-      </x:c>
+      <x:c r="H157" s="24"/>
       <x:c r="I157" s="25" t="n">
         <x:v>0.029944762089349597</x:v>
       </x:c>
@@ -25660,30 +25834,46 @@
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B158" s="37" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J157),1)</x:f>
-        <x:v>1561.4</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>8522</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>8618</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>8330</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>8333</x:v>
+      </x:c>
+      <x:c r="H158" s="24"/>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.019923786225065854</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B159" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C159" s="37"/>
       <x:c r="D159" s="37"/>
       <x:c r="E159" s="37"/>
@@ -25691,11 +25881,29 @@
       <x:c r="G159" s="37"/>
       <x:c r="H159" s="37"/>
       <x:c r="I159" s="37"/>
-      <x:c r="J159" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J157),0),1)</x:f>
-        <x:v>223.1</x:v>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>1849.4</x:v>
       </x:c>
       <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>231.2</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -30461,42 +30669,110 @@
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="38" t="str">
+      <x:c r="A157" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B157" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C157" s="23" t="str">
+        <x:v>7月9日</x:v>
+      </x:c>
+      <x:c r="D157" s="24" t="n">
+        <x:v>4690</x:v>
+      </x:c>
+      <x:c r="E157" s="24" t="n">
+        <x:v>4804</x:v>
+      </x:c>
+      <x:c r="F157" s="24" t="n">
+        <x:v>4665.2</x:v>
+      </x:c>
+      <x:c r="G157" s="24" t="n">
+        <x:v>4780.8</x:v>
+      </x:c>
+      <x:c r="H157" s="24"/>
+      <x:c r="I157" s="25" t="n">
+        <x:v>0.02416452442159378</x:v>
+      </x:c>
+      <x:c r="J157" s="29" t="n">
+        <x:f>ROUND(E157-F157,1)</x:f>
+        <x:v>138.8</x:v>
+      </x:c>
+      <x:c r="K157" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>4790.2</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>4822.2</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>4703.6</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="H158" s="24"/>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.015938755020080242</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>118.6</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B157" s="37" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C157" s="37"/>
-      <x:c r="D157" s="37"/>
-      <x:c r="E157" s="37"/>
-      <x:c r="F157" s="37"/>
-      <x:c r="G157" s="37"/>
-      <x:c r="H157" s="37"/>
-      <x:c r="I157" s="37"/>
-      <x:c r="J157" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J156),1)</x:f>
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="K157" s="37"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="38" t="str">
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C159" s="37"/>
+      <x:c r="D159" s="37"/>
+      <x:c r="E159" s="37"/>
+      <x:c r="F159" s="37"/>
+      <x:c r="G159" s="37"/>
+      <x:c r="H159" s="37"/>
+      <x:c r="I159" s="37"/>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>775.4</x:v>
+      </x:c>
+      <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B158" s="37"/>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J156),0),1)</x:f>
-        <x:v>86.3</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>96.9</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35283,9 +35559,7 @@
       <x:c r="G157" s="24" t="n">
         <x:v>2939.8</x:v>
       </x:c>
-      <x:c r="H157" s="24" t="n">
-        <x:v>71.8</x:v>
-      </x:c>
+      <x:c r="H157" s="24"/>
       <x:c r="I157" s="25" t="n">
         <x:v>0.025034867503486824</x:v>
       </x:c>
@@ -35298,30 +35572,46 @@
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B158" s="37" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C158" s="37"/>
-      <x:c r="D158" s="37"/>
-      <x:c r="E158" s="37"/>
-      <x:c r="F158" s="37"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="37"/>
-      <x:c r="I158" s="37"/>
-      <x:c r="J158" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J157),1)</x:f>
-        <x:v>368.8</x:v>
-      </x:c>
-      <x:c r="K158" s="37"/>
+      <x:c r="A158" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="23" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="23" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="24" t="n">
+        <x:v>2945.2</x:v>
+      </x:c>
+      <x:c r="E158" s="24" t="n">
+        <x:v>2983.8</x:v>
+      </x:c>
+      <x:c r="F158" s="24" t="n">
+        <x:v>2908.2</x:v>
+      </x:c>
+      <x:c r="G158" s="24" t="n">
+        <x:v>2910.2</x:v>
+      </x:c>
+      <x:c r="H158" s="24"/>
+      <x:c r="I158" s="25" t="n">
+        <x:v>-0.010068712157289772</x:v>
+      </x:c>
+      <x:c r="J158" s="29" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>75.6</x:v>
+      </x:c>
+      <x:c r="K158" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B159" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B159" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C159" s="37"/>
       <x:c r="D159" s="37"/>
       <x:c r="E159" s="37"/>
@@ -35329,11 +35619,29 @@
       <x:c r="G159" s="37"/>
       <x:c r="H159" s="37"/>
       <x:c r="I159" s="37"/>
-      <x:c r="J159" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J157),0),1)</x:f>
-        <x:v>52.7</x:v>
+      <x:c r="J159" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J158),1)</x:f>
+        <x:v>444.4</x:v>
       </x:c>
       <x:c r="K159" s="37"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B160" s="37"/>
+      <x:c r="C160" s="37"/>
+      <x:c r="D160" s="37"/>
+      <x:c r="E160" s="37"/>
+      <x:c r="F160" s="37"/>
+      <x:c r="G160" s="37"/>
+      <x:c r="H160" s="37"/>
+      <x:c r="I160" s="37"/>
+      <x:c r="J160" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
+        <x:v>55.6</x:v>
+      </x:c>
+      <x:c r="K160" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4ee502befd8e4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re4fdbc376ad54f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R66a6112174c94e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R7d214485518546e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rcfbab595b6a94beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rb519e8d2d05647e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Ra692667c59d24f3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Ree364ef90ee44819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rfe850cab131c4fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R0652ba25a2ef4517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Rd67aef5e6e9445ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R3074479a89ab42d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R45ace03b30db415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Refb4e4b2748f4706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4e30ae77457542f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R171767c7cb9e48ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>8438.194</x:v>
+        <x:v>7836.39</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>8198.308</x:v>
+        <x:v>7591.421</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>239.9</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>20918.9</x:v>
+        <x:v>22038.4</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>168.7</x:v>
+        <x:v>172.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8783.249</x:v>
+        <x:v>8148.042</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>8503.245</x:v>
+        <x:v>7907.097</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>280</x:v>
+        <x:v>240.9</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>21158.7</x:v>
+        <x:v>22259.5</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>170.6</x:v>
+        <x:v>173.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>4074.828</x:v>
+        <x:v>3940.451</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3995.807</x:v>
+        <x:v>3867.601</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>79</x:v>
+        <x:v>72.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>5952.9</x:v>
+        <x:v>6243.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48</x:v>
+        <x:v>48.8</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>8244.8</x:v>
+        <x:v>7750.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>8016</x:v>
+        <x:v>7511</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>228.8</x:v>
+        <x:v>239.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>22345.6</x:v>
+        <x:v>23378.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>180.2</x:v>
+        <x:v>182.6</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8618</x:v>
+        <x:v>8054.4</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>8330</x:v>
+        <x:v>7823</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>288</x:v>
+        <x:v>231.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>23831.4</x:v>
+        <x:v>24888.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.2</x:v>
+        <x:v>194.4</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4712.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4703.6</x:v>
+        <x:v>4618</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>118.6</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9074.2</x:v>
+        <x:v>9432.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.2</x:v>
+        <x:v>73.7</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2911.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2908.2</x:v>
+        <x:v>2853.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>75.6</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5121.6</x:v>
+        <x:v>5326.2</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.3</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -5896,42 +5896,186 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>8124.363</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>8171.504</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>7769.292</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>7787.853</x:v>
+      </x:c>
+      <x:c r="H159" s="27" t="n">
+        <x:v>-410.5</x:v>
+      </x:c>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.050065818459126055</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>402.2</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>7799.813</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>7934.103</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>7657.671</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>7925.123</x:v>
+      </x:c>
+      <x:c r="H160" s="24" t="n">
+        <x:v>137.3</x:v>
+      </x:c>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.017626167314662933</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>276.4</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>7959.374</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>7979.077</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>7783.219</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>7817.831</x:v>
+      </x:c>
+      <x:c r="H161" s="24" t="n">
+        <x:v>-107.3</x:v>
+      </x:c>
+      <x:c r="I161" s="25" t="n">
+        <x:v>-0.01353821259304111</x:v>
+      </x:c>
+      <x:c r="J161" s="29" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>195.9</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>7713.135</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>7836.39</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>7591.421</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>7631.762</x:v>
+      </x:c>
+      <x:c r="H162" s="27" t="n">
+        <x:v>-186.1</x:v>
+      </x:c>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.02380059123815803</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>1860.8</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>2980.3</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>232.6</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>248.4</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11013,42 +11157,186 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>8409.143</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>8457.692</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>8106.269</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>8138.144</x:v>
+      </x:c>
+      <x:c r="H159" s="27" t="n">
+        <x:v>-365.8</x:v>
+      </x:c>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.04301837341637216</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>351.4</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>8135.046</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>8275.96</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>7955.308</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>8275.939</x:v>
+      </x:c>
+      <x:c r="H160" s="24" t="n">
+        <x:v>137.8</x:v>
+      </x:c>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.016931993339021734</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>320.7</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>8294.142</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>8305.272</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>8117.459</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>8147.579</x:v>
+      </x:c>
+      <x:c r="H161" s="24" t="n">
+        <x:v>-128.4</x:v>
+      </x:c>
+      <x:c r="I161" s="25" t="n">
+        <x:v>-0.015510022488082642</x:v>
+      </x:c>
+      <x:c r="J161" s="29" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>187.8</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>8006.449</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>8148.042</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>7907.097</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>7955.664</x:v>
+      </x:c>
+      <x:c r="H162" s="27" t="n">
+        <x:v>-191.9</x:v>
+      </x:c>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.02355484985171663</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>240.9</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>2024.5</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>3125.3</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>253.1</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>260.4</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16130,42 +16418,186 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>3966.023</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>3983.054</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>3900.668</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>3913.794</x:v>
+      </x:c>
+      <x:c r="H159" s="24" t="n">
+        <x:v>-82.4</x:v>
+      </x:c>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.020611777000031473</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>82.4</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>3909.274</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>3967.126</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>3869.304</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>3967.126</x:v>
+      </x:c>
+      <x:c r="H160" s="24" t="n">
+        <x:v>53.3</x:v>
+      </x:c>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.01362667529256778</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>97.8</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>3963.727</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>3981.672</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>3943.695</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>3955.578</x:v>
+      </x:c>
+      <x:c r="H161" s="24" t="n">
+        <x:v>-11.5</x:v>
+      </x:c>
+      <x:c r="I161" s="25" t="n">
+        <x:v>-0.002910923424161549</x:v>
+      </x:c>
+      <x:c r="J161" s="24" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>3912.381</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>3940.451</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>3867.601</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>3882.413</x:v>
+      </x:c>
+      <x:c r="H162" s="24" t="n">
+        <x:v>-73.2</x:v>
+      </x:c>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.01849666470993616</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>72.8</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>517.2</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>808.2</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>64.7</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>67.4</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20999,42 +21431,178 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>7995</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>8029.8</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>7651</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>7684.4</x:v>
+      </x:c>
+      <x:c r="H159" s="24"/>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.04177369878045745</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>378.8</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>7720</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>7810.6</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>7580</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>7788</x:v>
+      </x:c>
+      <x:c r="H160" s="24"/>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.013481859351413217</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>230.6</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>7838</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>7846</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>7661.4</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>7723.2</x:v>
+      </x:c>
+      <x:c r="H161" s="24"/>
+      <x:c r="I161" s="25" t="n">
+        <x:v>-0.008320493066255819</x:v>
+      </x:c>
+      <x:c r="J161" s="24" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>184.6</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>7648.6</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>7750.2</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>7511</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>7552.6</x:v>
+      </x:c>
+      <x:c r="H162" s="24"/>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.022089289413714464</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>239.2</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>1596</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>2629.2</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>199.5</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>219.1</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -25868,42 +26436,178 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>8303</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>8328</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>7995.8</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>8021.6</x:v>
+      </x:c>
+      <x:c r="H159" s="24"/>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.037369494779791124</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>332.2</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>8043.2</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>8166</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>7881</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>8117</x:v>
+      </x:c>
+      <x:c r="H160" s="24"/>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.011892889199162315</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>8160</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>8192.2</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>7983.8</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>8046.4</x:v>
+      </x:c>
+      <x:c r="H161" s="24"/>
+      <x:c r="I161" s="25" t="n">
+        <x:v>-0.008697794751755583</x:v>
+      </x:c>
+      <x:c r="J161" s="29" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>208.4</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>7955.4</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>8054.4</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>7823</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>7869.6</x:v>
+      </x:c>
+      <x:c r="H162" s="24"/>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.021972559156890004</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>231.4</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>1849.4</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>2906.4</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>231.2</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>242.2</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -30737,42 +31441,178 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>4691</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>4705</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>4610.2</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>4634.6</x:v>
+      </x:c>
+      <x:c r="H159" s="24"/>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.014879054542362824</x:v>
+      </x:c>
+      <x:c r="J159" s="29" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>94.8</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>4640</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>4713.2</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>4593</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>4690</x:v>
+      </x:c>
+      <x:c r="H160" s="24"/>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.011953566650843683</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>120.2</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>4706</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>4739.4</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>4690.6</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>4717.4</x:v>
+      </x:c>
+      <x:c r="H161" s="24"/>
+      <x:c r="I161" s="25" t="n">
+        <x:v>0.005842217484008483</x:v>
+      </x:c>
+      <x:c r="J161" s="24" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>48.8</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>4677</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>4712.6</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>4618</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>4645.6</x:v>
+      </x:c>
+      <x:c r="H162" s="24"/>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.015220248441938256</x:v>
+      </x:c>
+      <x:c r="J162" s="29" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>94.6</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>775.4</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>1133.8</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>96.9</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>94.5</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35606,42 +36446,178 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="38" t="str">
+      <x:c r="A159" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="24" t="n">
+        <x:v>2895.8</x:v>
+      </x:c>
+      <x:c r="E159" s="24" t="n">
+        <x:v>2908.6</x:v>
+      </x:c>
+      <x:c r="F159" s="24" t="n">
+        <x:v>2858</x:v>
+      </x:c>
+      <x:c r="G159" s="24" t="n">
+        <x:v>2872.6</x:v>
+      </x:c>
+      <x:c r="H159" s="24"/>
+      <x:c r="I159" s="25" t="n">
+        <x:v>-0.012920074221702937</x:v>
+      </x:c>
+      <x:c r="J159" s="24" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>50.6</x:v>
+      </x:c>
+      <x:c r="K159" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="23" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="24" t="n">
+        <x:v>2872</x:v>
+      </x:c>
+      <x:c r="E160" s="24" t="n">
+        <x:v>2894</x:v>
+      </x:c>
+      <x:c r="F160" s="24" t="n">
+        <x:v>2831.4</x:v>
+      </x:c>
+      <x:c r="G160" s="24" t="n">
+        <x:v>2891.2</x:v>
+      </x:c>
+      <x:c r="H160" s="24"/>
+      <x:c r="I160" s="25" t="n">
+        <x:v>0.006474970410081493</x:v>
+      </x:c>
+      <x:c r="J160" s="29" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>62.6</x:v>
+      </x:c>
+      <x:c r="K160" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="23" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="24" t="n">
+        <x:v>2900</x:v>
+      </x:c>
+      <x:c r="E161" s="24" t="n">
+        <x:v>2924</x:v>
+      </x:c>
+      <x:c r="F161" s="24" t="n">
+        <x:v>2891</x:v>
+      </x:c>
+      <x:c r="G161" s="24" t="n">
+        <x:v>2914</x:v>
+      </x:c>
+      <x:c r="H161" s="24"/>
+      <x:c r="I161" s="25" t="n">
+        <x:v>0.007885998893193191</x:v>
+      </x:c>
+      <x:c r="J161" s="24" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K161" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="24" t="n">
+        <x:v>2889</x:v>
+      </x:c>
+      <x:c r="E162" s="24" t="n">
+        <x:v>2911.8</x:v>
+      </x:c>
+      <x:c r="F162" s="24" t="n">
+        <x:v>2853.4</x:v>
+      </x:c>
+      <x:c r="G162" s="24" t="n">
+        <x:v>2867.8</x:v>
+      </x:c>
+      <x:c r="H162" s="24"/>
+      <x:c r="I162" s="25" t="n">
+        <x:v>-0.015854495538778268</x:v>
+      </x:c>
+      <x:c r="J162" s="24" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>58.4</x:v>
+      </x:c>
+      <x:c r="K162" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B159" s="37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C159" s="37"/>
-      <x:c r="D159" s="37"/>
-      <x:c r="E159" s="37"/>
-      <x:c r="F159" s="37"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="37"/>
-      <x:c r="I159" s="37"/>
-      <x:c r="J159" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J158),1)</x:f>
-        <x:v>444.4</x:v>
-      </x:c>
-      <x:c r="K159" s="37"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="38" t="str">
+      <x:c r="B163" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C163" s="37"/>
+      <x:c r="D163" s="37"/>
+      <x:c r="E163" s="37"/>
+      <x:c r="F163" s="37"/>
+      <x:c r="G163" s="37"/>
+      <x:c r="H163" s="37"/>
+      <x:c r="I163" s="37"/>
+      <x:c r="J163" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J162),1)</x:f>
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="K163" s="37"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="38" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B160" s="37"/>
-      <x:c r="C160" s="37"/>
-      <x:c r="D160" s="37"/>
-      <x:c r="E160" s="37"/>
-      <x:c r="F160" s="37"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="37"/>
-      <x:c r="I160" s="37"/>
-      <x:c r="J160" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J158),0),1)</x:f>
-        <x:v>55.6</x:v>
-      </x:c>
-      <x:c r="K160" s="37"/>
+      <x:c r="B164" s="37"/>
+      <x:c r="C164" s="37"/>
+      <x:c r="D164" s="37"/>
+      <x:c r="E164" s="37"/>
+      <x:c r="F164" s="37"/>
+      <x:c r="G164" s="37"/>
+      <x:c r="H164" s="37"/>
+      <x:c r="I164" s="37"/>
+      <x:c r="J164" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
+        <x:v>54.1</x:v>
+      </x:c>
+      <x:c r="K164" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rfe850cab131c4fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R0652ba25a2ef4517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Rd67aef5e6e9445ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R3074479a89ab42d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R45ace03b30db415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Refb4e4b2748f4706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4e30ae77457542f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R171767c7cb9e48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf056ecd3e30b4e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R8fe51632a4444471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R36a98e053d5542ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf2135713d60c4f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R9d880b69855c4ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R7d94fba92f4547f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R7535b600b4434768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re1c7a7207f984472"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16708,7 +16708,9 @@
       <x:c r="G5" s="24" t="n">
         <x:v>7639</x:v>
       </x:c>
-      <x:c r="H5" s="24"/>
+      <x:c r="H5" s="27" t="n">
+        <x:v>202.8</x:v>
+      </x:c>
       <x:c r="I5" s="25" t="n">
         <x:v>0.02727199376025391</x:v>
       </x:c>
@@ -16742,7 +16744,9 @@
       <x:c r="G6" s="24" t="n">
         <x:v>7762.4</x:v>
       </x:c>
-      <x:c r="H6" s="24"/>
+      <x:c r="H6" s="24" t="n">
+        <x:v>123.4</x:v>
+      </x:c>
       <x:c r="I6" s="25" t="n">
         <x:v>0.016153946851682033</x:v>
       </x:c>
@@ -16776,7 +16780,9 @@
       <x:c r="G7" s="24" t="n">
         <x:v>7760.2</x:v>
       </x:c>
-      <x:c r="H7" s="24"/>
+      <x:c r="H7" s="24" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
       <x:c r="I7" s="25" t="n">
         <x:v>-0.00028341749974236663</x:v>
       </x:c>
@@ -16810,7 +16816,9 @@
       <x:c r="G8" s="24" t="n">
         <x:v>7820.6</x:v>
       </x:c>
-      <x:c r="H8" s="24"/>
+      <x:c r="H8" s="24" t="n">
+        <x:v>60.4</x:v>
+      </x:c>
       <x:c r="I8" s="25" t="n">
         <x:v>0.007783304554006332</x:v>
       </x:c>
@@ -16844,7 +16852,9 @@
       <x:c r="G9" s="24" t="n">
         <x:v>8048.4</x:v>
       </x:c>
-      <x:c r="H9" s="24"/>
+      <x:c r="H9" s="27" t="n">
+        <x:v>227.8</x:v>
+      </x:c>
       <x:c r="I9" s="25" t="n">
         <x:v>0.029128199882361816</x:v>
       </x:c>
@@ -16878,7 +16888,9 @@
       <x:c r="G10" s="24" t="n">
         <x:v>8311.4</x:v>
       </x:c>
-      <x:c r="H10" s="24"/>
+      <x:c r="H10" s="27" t="n">
+        <x:v>263</x:v>
+      </x:c>
       <x:c r="I10" s="25" t="n">
         <x:v>0.03267730232095811</x:v>
       </x:c>
@@ -16912,7 +16924,9 @@
       <x:c r="G11" s="24" t="n">
         <x:v>8160.4</x:v>
       </x:c>
-      <x:c r="H11" s="24"/>
+      <x:c r="H11" s="27" t="n">
+        <x:v>-151</x:v>
+      </x:c>
       <x:c r="I11" s="25" t="n">
         <x:v>-0.01816781769617637</x:v>
       </x:c>
@@ -16946,7 +16960,9 @@
       <x:c r="G12" s="24" t="n">
         <x:v>8156</x:v>
       </x:c>
-      <x:c r="H12" s="24"/>
+      <x:c r="H12" s="24" t="n">
+        <x:v>-4.4</x:v>
+      </x:c>
       <x:c r="I12" s="25" t="n">
         <x:v>-0.0005391892554286182</x:v>
       </x:c>
@@ -16980,7 +16996,9 @@
       <x:c r="G13" s="24" t="n">
         <x:v>8195.4</x:v>
       </x:c>
-      <x:c r="H13" s="24"/>
+      <x:c r="H13" s="24" t="n">
+        <x:v>39.4</x:v>
+      </x:c>
       <x:c r="I13" s="25" t="n">
         <x:v>0.004830799411476239</x:v>
       </x:c>
@@ -17014,7 +17032,9 @@
       <x:c r="G14" s="34" t="n">
         <x:v>8179.2</x:v>
       </x:c>
-      <x:c r="H14" s="34"/>
+      <x:c r="H14" s="34" t="n">
+        <x:v>-16.2</x:v>
+      </x:c>
       <x:c r="I14" s="35" t="n">
         <x:v>-0.0019767186470458498</x:v>
       </x:c>
@@ -17048,7 +17068,9 @@
       <x:c r="G15" s="24" t="n">
         <x:v>8186.6</x:v>
       </x:c>
-      <x:c r="H15" s="24"/>
+      <x:c r="H15" s="24" t="n">
+        <x:v>7.4</x:v>
+      </x:c>
       <x:c r="I15" s="25" t="n">
         <x:v>0.0009047339593115655</x:v>
       </x:c>
@@ -17082,7 +17104,9 @@
       <x:c r="G16" s="24" t="n">
         <x:v>8120.8</x:v>
       </x:c>
-      <x:c r="H16" s="24"/>
+      <x:c r="H16" s="24" t="n">
+        <x:v>-65.8</x:v>
+      </x:c>
       <x:c r="I16" s="25" t="n">
         <x:v>-0.008037524735543422</x:v>
       </x:c>
@@ -17116,7 +17140,9 @@
       <x:c r="G17" s="24" t="n">
         <x:v>8231</x:v>
       </x:c>
-      <x:c r="H17" s="24"/>
+      <x:c r="H17" s="24" t="n">
+        <x:v>110.2</x:v>
+      </x:c>
       <x:c r="I17" s="25" t="n">
         <x:v>0.013570091616589508</x:v>
       </x:c>
@@ -17150,7 +17176,9 @@
       <x:c r="G18" s="24" t="n">
         <x:v>8292.6</x:v>
       </x:c>
-      <x:c r="H18" s="24"/>
+      <x:c r="H18" s="24" t="n">
+        <x:v>61.6</x:v>
+      </x:c>
       <x:c r="I18" s="25" t="n">
         <x:v>0.007483902320495783</x:v>
       </x:c>
@@ -17184,7 +17212,9 @@
       <x:c r="G19" s="24" t="n">
         <x:v>8516.6</x:v>
       </x:c>
-      <x:c r="H19" s="24"/>
+      <x:c r="H19" s="27" t="n">
+        <x:v>224</x:v>
+      </x:c>
       <x:c r="I19" s="25" t="n">
         <x:v>0.027012034826230602</x:v>
       </x:c>
@@ -17218,7 +17248,9 @@
       <x:c r="G20" s="24" t="n">
         <x:v>8289.2</x:v>
       </x:c>
-      <x:c r="H20" s="24"/>
+      <x:c r="H20" s="27" t="n">
+        <x:v>-227.4</x:v>
+      </x:c>
       <x:c r="I20" s="25" t="n">
         <x:v>-0.02670079609233722</x:v>
       </x:c>
@@ -17252,7 +17284,9 @@
       <x:c r="G21" s="24" t="n">
         <x:v>8357.2</x:v>
       </x:c>
-      <x:c r="H21" s="24"/>
+      <x:c r="H21" s="24" t="n">
+        <x:v>68</x:v>
+      </x:c>
       <x:c r="I21" s="25" t="n">
         <x:v>0.008203445447087843</x:v>
       </x:c>
@@ -17286,7 +17320,9 @@
       <x:c r="G22" s="24" t="n">
         <x:v>8377.8</x:v>
       </x:c>
-      <x:c r="H22" s="24"/>
+      <x:c r="H22" s="24" t="n">
+        <x:v>20.6</x:v>
+      </x:c>
       <x:c r="I22" s="25" t="n">
         <x:v>0.0024649404106635853</x:v>
       </x:c>
@@ -17320,7 +17356,9 @@
       <x:c r="G23" s="24" t="n">
         <x:v>8329</x:v>
       </x:c>
-      <x:c r="H23" s="24"/>
+      <x:c r="H23" s="24" t="n">
+        <x:v>-48.8</x:v>
+      </x:c>
       <x:c r="I23" s="25" t="n">
         <x:v>-0.0058249182362910545</x:v>
       </x:c>
@@ -17354,7 +17392,9 @@
       <x:c r="G24" s="24" t="n">
         <x:v>8260.6</x:v>
       </x:c>
-      <x:c r="H24" s="24"/>
+      <x:c r="H24" s="24" t="n">
+        <x:v>-68.4</x:v>
+      </x:c>
       <x:c r="I24" s="25" t="n">
         <x:v>-0.008212270380597908</x:v>
       </x:c>
@@ -17476,7 +17516,9 @@
       <x:c r="G30" s="24" t="n">
         <x:v>7871.8</x:v>
       </x:c>
-      <x:c r="H30" s="24"/>
+      <x:c r="H30" s="27" t="n">
+        <x:v>-388.8</x:v>
+      </x:c>
       <x:c r="I30" s="25" t="n">
         <x:v>-0.04706679902186284</x:v>
       </x:c>
@@ -17510,7 +17552,9 @@
       <x:c r="G31" s="24" t="n">
         <x:v>8183</x:v>
       </x:c>
-      <x:c r="H31" s="24"/>
+      <x:c r="H31" s="27" t="n">
+        <x:v>311.2</x:v>
+      </x:c>
       <x:c r="I31" s="25" t="n">
         <x:v>0.03953352473386018</x:v>
       </x:c>
@@ -17544,7 +17588,9 @@
       <x:c r="G32" s="24" t="n">
         <x:v>8203.4</x:v>
       </x:c>
-      <x:c r="H32" s="24"/>
+      <x:c r="H32" s="24" t="n">
+        <x:v>20.4</x:v>
+      </x:c>
       <x:c r="I32" s="25" t="n">
         <x:v>0.002492973237198992</x:v>
       </x:c>
@@ -17578,7 +17624,9 @@
       <x:c r="G33" s="24" t="n">
         <x:v>8039.8</x:v>
       </x:c>
-      <x:c r="H33" s="24"/>
+      <x:c r="H33" s="27" t="n">
+        <x:v>-163.6</x:v>
+      </x:c>
       <x:c r="I33" s="25" t="n">
         <x:v>-0.019942950483945565</x:v>
       </x:c>
@@ -17612,7 +17660,9 @@
       <x:c r="G34" s="24" t="n">
         <x:v>7990.8</x:v>
       </x:c>
-      <x:c r="H34" s="24"/>
+      <x:c r="H34" s="24" t="n">
+        <x:v>-49</x:v>
+      </x:c>
       <x:c r="I34" s="25" t="n">
         <x:v>-0.006094678972113687</x:v>
       </x:c>
@@ -17646,7 +17696,9 @@
       <x:c r="G35" s="24" t="n">
         <x:v>8232.6</x:v>
       </x:c>
-      <x:c r="H35" s="24"/>
+      <x:c r="H35" s="27" t="n">
+        <x:v>241.8</x:v>
+      </x:c>
       <x:c r="I35" s="25" t="n">
         <x:v>0.03025979876858398</x:v>
       </x:c>
@@ -17680,7 +17732,9 @@
       <x:c r="G36" s="24" t="n">
         <x:v>8229</x:v>
       </x:c>
-      <x:c r="H36" s="24"/>
+      <x:c r="H36" s="24" t="n">
+        <x:v>-3.6</x:v>
+      </x:c>
       <x:c r="I36" s="25" t="n">
         <x:v>-0.0004372859121055672</x:v>
       </x:c>
@@ -17714,7 +17768,9 @@
       <x:c r="G37" s="24" t="n">
         <x:v>8241</x:v>
       </x:c>
-      <x:c r="H37" s="24"/>
+      <x:c r="H37" s="24" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="I37" s="25" t="n">
         <x:v>0.0014582573824279965</x:v>
       </x:c>
@@ -17748,7 +17804,9 @@
       <x:c r="G38" s="24" t="n">
         <x:v>8338</x:v>
       </x:c>
-      <x:c r="H38" s="24"/>
+      <x:c r="H38" s="24" t="n">
+        <x:v>97</x:v>
+      </x:c>
       <x:c r="I38" s="25" t="n">
         <x:v>0.011770416211624779</x:v>
       </x:c>
@@ -17782,7 +17840,9 @@
       <x:c r="G39" s="24" t="n">
         <x:v>8189</x:v>
       </x:c>
-      <x:c r="H39" s="24"/>
+      <x:c r="H39" s="24" t="n">
+        <x:v>-149</x:v>
+      </x:c>
       <x:c r="I39" s="25" t="n">
         <x:v>-0.01786999280402979</x:v>
       </x:c>
@@ -17816,7 +17876,9 @@
       <x:c r="G40" s="34" t="n">
         <x:v>8271</x:v>
       </x:c>
-      <x:c r="H40" s="34"/>
+      <x:c r="H40" s="34" t="n">
+        <x:v>82</x:v>
+      </x:c>
       <x:c r="I40" s="35" t="n">
         <x:v>0.010013432653559695</x:v>
       </x:c>
@@ -17850,7 +17912,9 @@
       <x:c r="G41" s="24" t="n">
         <x:v>8405.6</x:v>
       </x:c>
-      <x:c r="H41" s="24"/>
+      <x:c r="H41" s="24" t="n">
+        <x:v>134.6</x:v>
+      </x:c>
       <x:c r="I41" s="25" t="n">
         <x:v>0.016273727481562084</x:v>
       </x:c>
@@ -17884,7 +17948,9 @@
       <x:c r="G42" s="24" t="n">
         <x:v>8443.4</x:v>
       </x:c>
-      <x:c r="H42" s="24"/>
+      <x:c r="H42" s="24" t="n">
+        <x:v>37.8</x:v>
+      </x:c>
       <x:c r="I42" s="25" t="n">
         <x:v>0.004497001998667427</x:v>
       </x:c>
@@ -17918,7 +17984,9 @@
       <x:c r="G43" s="24" t="n">
         <x:v>8531.4</x:v>
       </x:c>
-      <x:c r="H43" s="24"/>
+      <x:c r="H43" s="24" t="n">
+        <x:v>88</x:v>
+      </x:c>
       <x:c r="I43" s="25" t="n">
         <x:v>0.010422341710685235</x:v>
       </x:c>
@@ -18040,7 +18108,9 @@
       <x:c r="G49" s="24" t="n">
         <x:v>8423.8</x:v>
       </x:c>
-      <x:c r="H49" s="24"/>
+      <x:c r="H49" s="24" t="n">
+        <x:v>-107.6</x:v>
+      </x:c>
       <x:c r="I49" s="25" t="n">
         <x:v>-0.012612232458916517</x:v>
       </x:c>
@@ -18074,7 +18144,9 @@
       <x:c r="G50" s="24" t="n">
         <x:v>8129.4</x:v>
       </x:c>
-      <x:c r="H50" s="24"/>
+      <x:c r="H50" s="27" t="n">
+        <x:v>-294.4</x:v>
+      </x:c>
       <x:c r="I50" s="25" t="n">
         <x:v>-0.034948598019895916</x:v>
       </x:c>
@@ -18108,7 +18180,9 @@
       <x:c r="G51" s="24" t="n">
         <x:v>8064.2</x:v>
       </x:c>
-      <x:c r="H51" s="24"/>
+      <x:c r="H51" s="24" t="n">
+        <x:v>-65.2</x:v>
+      </x:c>
       <x:c r="I51" s="25" t="n">
         <x:v>-0.00802027209880185</x:v>
       </x:c>
@@ -18142,7 +18216,9 @@
       <x:c r="G52" s="24" t="n">
         <x:v>8130</x:v>
       </x:c>
-      <x:c r="H52" s="24"/>
+      <x:c r="H52" s="24" t="n">
+        <x:v>65.8</x:v>
+      </x:c>
       <x:c r="I52" s="25" t="n">
         <x:v>0.00815951985317831</x:v>
       </x:c>
@@ -18176,7 +18252,9 @@
       <x:c r="G53" s="24" t="n">
         <x:v>8211.8</x:v>
       </x:c>
-      <x:c r="H53" s="24"/>
+      <x:c r="H53" s="24" t="n">
+        <x:v>81.8</x:v>
+      </x:c>
       <x:c r="I53" s="25" t="n">
         <x:v>0.010061500615005992</x:v>
       </x:c>
@@ -18210,7 +18288,9 @@
       <x:c r="G54" s="24" t="n">
         <x:v>8191</x:v>
       </x:c>
-      <x:c r="H54" s="24"/>
+      <x:c r="H54" s="24" t="n">
+        <x:v>-20.8</x:v>
+      </x:c>
       <x:c r="I54" s="25" t="n">
         <x:v>-0.0025329404028348046</x:v>
       </x:c>
@@ -18244,7 +18324,9 @@
       <x:c r="G55" s="24" t="n">
         <x:v>8313.6</x:v>
       </x:c>
-      <x:c r="H55" s="24"/>
+      <x:c r="H55" s="24" t="n">
+        <x:v>122.6</x:v>
+      </x:c>
       <x:c r="I55" s="25" t="n">
         <x:v>0.01496764741789769</x:v>
       </x:c>
@@ -18278,7 +18360,9 @@
       <x:c r="G56" s="24" t="n">
         <x:v>8313</x:v>
       </x:c>
-      <x:c r="H56" s="24"/>
+      <x:c r="H56" s="24" t="n">
+        <x:v>-0.6</x:v>
+      </x:c>
       <x:c r="I56" s="25" t="n">
         <x:v>-0.00007217090069289167</x:v>
       </x:c>
@@ -18312,7 +18396,9 @@
       <x:c r="G57" s="24" t="n">
         <x:v>8277.2</x:v>
       </x:c>
-      <x:c r="H57" s="24"/>
+      <x:c r="H57" s="24" t="n">
+        <x:v>-35.8</x:v>
+      </x:c>
       <x:c r="I57" s="25" t="n">
         <x:v>-0.004306507879225263</x:v>
       </x:c>
@@ -18346,9 +18432,11 @@
       <x:c r="G58" s="24" t="n">
         <x:v>8187</x:v>
       </x:c>
-      <x:c r="H58" s="24"/>
+      <x:c r="H58" s="24" t="n">
+        <x:v>-90.2</x:v>
+      </x:c>
       <x:c r="I58" s="25" t="n">
-        <x:v>-0.039385299376600846</x:v>
+        <x:v>-0.010897404919538056</x:v>
       </x:c>
       <x:c r="J58" s="24" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
@@ -18380,9 +18468,11 @@
       <x:c r="G59" s="24" t="n">
         <x:v>8187</x:v>
       </x:c>
-      <x:c r="H59" s="24"/>
+      <x:c r="H59" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I59" s="25" t="n">
-        <x:v>0.00020122748767481546</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J59" s="24" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
@@ -18414,9 +18504,11 @@
       <x:c r="G60" s="24" t="n">
         <x:v>8014</x:v>
       </x:c>
-      <x:c r="H60" s="24"/>
+      <x:c r="H60" s="27" t="n">
+        <x:v>-173</x:v>
+      </x:c>
       <x:c r="I60" s="25" t="n">
-        <x:v>-0.022885021627602864</x:v>
+        <x:v>-0.02113106143886645</x:v>
       </x:c>
       <x:c r="J60" s="29" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
@@ -18448,9 +18540,11 @@
       <x:c r="G61" s="24" t="n">
         <x:v>8080.4</x:v>
       </x:c>
-      <x:c r="H61" s="24"/>
+      <x:c r="H61" s="24" t="n">
+        <x:v>66.4</x:v>
+      </x:c>
       <x:c r="I61" s="25" t="n">
-        <x:v>0.009497091676532676</x:v>
+        <x:v>0.008285500374344945</x:v>
       </x:c>
       <x:c r="J61" s="24" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -18482,9 +18576,11 @@
       <x:c r="G62" s="24" t="n">
         <x:v>7923.8</x:v>
       </x:c>
-      <x:c r="H62" s="24"/>
+      <x:c r="H62" s="27" t="n">
+        <x:v>-156.6</x:v>
+      </x:c>
       <x:c r="I62" s="25" t="n">
-        <x:v>-0.02085511052188771</x:v>
+        <x:v>-0.019380228701549318</x:v>
       </x:c>
       <x:c r="J62" s="24" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -18516,9 +18612,11 @@
       <x:c r="G63" s="34" t="n">
         <x:v>7876.2</x:v>
       </x:c>
-      <x:c r="H63" s="34"/>
+      <x:c r="H63" s="34" t="n">
+        <x:v>-47.6</x:v>
+      </x:c>
       <x:c r="I63" s="35" t="n">
-        <x:v>-0.01575315714099723</x:v>
+        <x:v>-0.006007218758676491</x:v>
       </x:c>
       <x:c r="J63" s="34" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -18550,9 +18648,11 @@
       <x:c r="G64" s="24" t="n">
         <x:v>7190</x:v>
       </x:c>
-      <x:c r="H64" s="24"/>
+      <x:c r="H64" s="27" t="n">
+        <x:v>-686.2</x:v>
+      </x:c>
       <x:c r="I64" s="25" t="n">
-        <x:v>-0.04894179894179895</x:v>
+        <x:v>-0.08712323201543892</x:v>
       </x:c>
       <x:c r="J64" s="29" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -18584,7 +18684,9 @@
       <x:c r="G65" s="24" t="n">
         <x:v>7387.2</x:v>
       </x:c>
-      <x:c r="H65" s="24"/>
+      <x:c r="H65" s="27" t="n">
+        <x:v>197.2</x:v>
+      </x:c>
       <x:c r="I65" s="25" t="n">
         <x:v>0.02742698191933246</x:v>
       </x:c>
@@ -18618,7 +18720,9 @@
       <x:c r="G66" s="24" t="n">
         <x:v>7477.4</x:v>
       </x:c>
-      <x:c r="H66" s="24"/>
+      <x:c r="H66" s="24" t="n">
+        <x:v>90.2</x:v>
+      </x:c>
       <x:c r="I66" s="25" t="n">
         <x:v>0.012210309724929536</x:v>
       </x:c>
@@ -18652,7 +18756,9 @@
       <x:c r="G67" s="24" t="n">
         <x:v>7375.6</x:v>
       </x:c>
-      <x:c r="H67" s="24"/>
+      <x:c r="H67" s="24" t="n">
+        <x:v>-101.8</x:v>
+      </x:c>
       <x:c r="I67" s="25" t="n">
         <x:v>-0.013614357931901355</x:v>
       </x:c>
@@ -18686,7 +18792,9 @@
       <x:c r="G68" s="24" t="n">
         <x:v>7523.8</x:v>
       </x:c>
-      <x:c r="H68" s="24"/>
+      <x:c r="H68" s="24" t="n">
+        <x:v>148.2</x:v>
+      </x:c>
       <x:c r="I68" s="25" t="n">
         <x:v>0.02009328054666737</x:v>
       </x:c>
@@ -18720,7 +18828,9 @@
       <x:c r="G69" s="24" t="n">
         <x:v>7509.4</x:v>
       </x:c>
-      <x:c r="H69" s="24"/>
+      <x:c r="H69" s="24" t="n">
+        <x:v>-14.4</x:v>
+      </x:c>
       <x:c r="I69" s="25" t="n">
         <x:v>-0.0019139264733246675</x:v>
       </x:c>
@@ -18754,7 +18864,9 @@
       <x:c r="G70" s="24" t="n">
         <x:v>7379.4</x:v>
       </x:c>
-      <x:c r="H70" s="24"/>
+      <x:c r="H70" s="24" t="n">
+        <x:v>-130</x:v>
+      </x:c>
       <x:c r="I70" s="25" t="n">
         <x:v>-0.017311636082776305</x:v>
       </x:c>
@@ -18876,7 +18988,9 @@
       <x:c r="G76" s="24" t="n">
         <x:v>7518.6</x:v>
       </x:c>
-      <x:c r="H76" s="24"/>
+      <x:c r="H76" s="24" t="n">
+        <x:v>139.2</x:v>
+      </x:c>
       <x:c r="I76" s="25" t="n">
         <x:v>0.018863322221318812</x:v>
       </x:c>
@@ -18910,7 +19024,9 @@
       <x:c r="G77" s="24" t="n">
         <x:v>7371.6</x:v>
       </x:c>
-      <x:c r="H77" s="24"/>
+      <x:c r="H77" s="24" t="n">
+        <x:v>-147</x:v>
+      </x:c>
       <x:c r="I77" s="25" t="n">
         <x:v>-0.019551512249620928</x:v>
       </x:c>
@@ -18944,7 +19060,9 @@
       <x:c r="G78" s="24" t="n">
         <x:v>7309.4</x:v>
       </x:c>
-      <x:c r="H78" s="24"/>
+      <x:c r="H78" s="24" t="n">
+        <x:v>-62.2</x:v>
+      </x:c>
       <x:c r="I78" s="25" t="n">
         <x:v>-0.008437788268489954</x:v>
       </x:c>
@@ -18978,7 +19096,9 @@
       <x:c r="G79" s="24" t="n">
         <x:v>7376.6</x:v>
       </x:c>
-      <x:c r="H79" s="24"/>
+      <x:c r="H79" s="24" t="n">
+        <x:v>67.2</x:v>
+      </x:c>
       <x:c r="I79" s="25" t="n">
         <x:v>0.009193641064930258</x:v>
       </x:c>
@@ -19012,7 +19132,9 @@
       <x:c r="G80" s="24" t="n">
         <x:v>7778</x:v>
       </x:c>
-      <x:c r="H80" s="24"/>
+      <x:c r="H80" s="27" t="n">
+        <x:v>401.4</x:v>
+      </x:c>
       <x:c r="I80" s="25" t="n">
         <x:v>0.05441531328796456</x:v>
       </x:c>
@@ -19046,7 +19168,9 @@
       <x:c r="G81" s="24" t="n">
         <x:v>7709.4</x:v>
       </x:c>
-      <x:c r="H81" s="24"/>
+      <x:c r="H81" s="24" t="n">
+        <x:v>-68.6</x:v>
+      </x:c>
       <x:c r="I81" s="25" t="n">
         <x:v>-0.008819748007199868</x:v>
       </x:c>
@@ -19080,7 +19204,9 @@
       <x:c r="G82" s="24" t="n">
         <x:v>7785.8</x:v>
       </x:c>
-      <x:c r="H82" s="24"/>
+      <x:c r="H82" s="24" t="n">
+        <x:v>76.4</x:v>
+      </x:c>
       <x:c r="I82" s="25" t="n">
         <x:v>0.009909980024385812</x:v>
       </x:c>
@@ -19114,7 +19240,9 @@
       <x:c r="G83" s="24" t="n">
         <x:v>7795.6</x:v>
       </x:c>
-      <x:c r="H83" s="24"/>
+      <x:c r="H83" s="24" t="n">
+        <x:v>9.8</x:v>
+      </x:c>
       <x:c r="I83" s="25" t="n">
         <x:v>0.0012587017390635058</x:v>
       </x:c>
@@ -19148,7 +19276,9 @@
       <x:c r="G84" s="24" t="n">
         <x:v>7913</x:v>
       </x:c>
-      <x:c r="H84" s="24"/>
+      <x:c r="H84" s="24" t="n">
+        <x:v>117.4</x:v>
+      </x:c>
       <x:c r="I84" s="25" t="n">
         <x:v>0.015059777310277633</x:v>
       </x:c>
@@ -19182,7 +19312,9 @@
       <x:c r="G85" s="24" t="n">
         <x:v>7904.6</x:v>
       </x:c>
-      <x:c r="H85" s="24"/>
+      <x:c r="H85" s="24" t="n">
+        <x:v>-8.4</x:v>
+      </x:c>
       <x:c r="I85" s="25" t="n">
         <x:v>-0.001061544294199357</x:v>
       </x:c>
@@ -19216,7 +19348,9 @@
       <x:c r="G86" s="24" t="n">
         <x:v>8052.2</x:v>
       </x:c>
-      <x:c r="H86" s="24"/>
+      <x:c r="H86" s="24" t="n">
+        <x:v>147.6</x:v>
+      </x:c>
       <x:c r="I86" s="25" t="n">
         <x:v>0.018672671608936486</x:v>
       </x:c>
@@ -19250,7 +19384,9 @@
       <x:c r="G87" s="34" t="n">
         <x:v>8132</x:v>
       </x:c>
-      <x:c r="H87" s="34"/>
+      <x:c r="H87" s="34" t="n">
+        <x:v>79.8</x:v>
+      </x:c>
       <x:c r="I87" s="35" t="n">
         <x:v>0.009910335063709308</x:v>
       </x:c>
@@ -19284,7 +19420,9 @@
       <x:c r="G88" s="24" t="n">
         <x:v>8159.2</x:v>
       </x:c>
-      <x:c r="H88" s="24"/>
+      <x:c r="H88" s="24" t="n">
+        <x:v>27.2</x:v>
+      </x:c>
       <x:c r="I88" s="25" t="n">
         <x:v>0.003344810624692496</x:v>
       </x:c>
@@ -19318,7 +19456,9 @@
       <x:c r="G89" s="24" t="n">
         <x:v>8170</x:v>
       </x:c>
-      <x:c r="H89" s="24"/>
+      <x:c r="H89" s="24" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
       <x:c r="I89" s="25" t="n">
         <x:v>0.0013236591822727295</x:v>
       </x:c>
@@ -19352,7 +19492,9 @@
       <x:c r="G90" s="24" t="n">
         <x:v>8322.8</x:v>
       </x:c>
-      <x:c r="H90" s="24"/>
+      <x:c r="H90" s="27" t="n">
+        <x:v>152.8</x:v>
+      </x:c>
       <x:c r="I90" s="25" t="n">
         <x:v>0.01870257037943679</x:v>
       </x:c>
@@ -19386,7 +19528,9 @@
       <x:c r="G91" s="24" t="n">
         <x:v>8219.2</x:v>
       </x:c>
-      <x:c r="H91" s="24"/>
+      <x:c r="H91" s="24" t="n">
+        <x:v>-103.6</x:v>
+      </x:c>
       <x:c r="I91" s="25" t="n">
         <x:v>-0.012447733935694538</x:v>
       </x:c>
@@ -19420,7 +19564,9 @@
       <x:c r="G92" s="24" t="n">
         <x:v>8163</x:v>
       </x:c>
-      <x:c r="H92" s="24"/>
+      <x:c r="H92" s="24" t="n">
+        <x:v>-56.2</x:v>
+      </x:c>
       <x:c r="I92" s="25" t="n">
         <x:v>-0.006837648432937549</x:v>
       </x:c>
@@ -19454,7 +19600,9 @@
       <x:c r="G93" s="24" t="n">
         <x:v>8199.2</x:v>
       </x:c>
-      <x:c r="H93" s="24"/>
+      <x:c r="H93" s="24" t="n">
+        <x:v>36.2</x:v>
+      </x:c>
       <x:c r="I93" s="25" t="n">
         <x:v>0.004434644125934195</x:v>
       </x:c>
@@ -19488,7 +19636,9 @@
       <x:c r="G94" s="24" t="n">
         <x:v>8103.6</x:v>
       </x:c>
-      <x:c r="H94" s="24"/>
+      <x:c r="H94" s="24" t="n">
+        <x:v>-95.6</x:v>
+      </x:c>
       <x:c r="I94" s="25" t="n">
         <x:v>-0.011659674114547824</x:v>
       </x:c>
@@ -19522,7 +19672,9 @@
       <x:c r="G95" s="24" t="n">
         <x:v>8246</x:v>
       </x:c>
-      <x:c r="H95" s="24"/>
+      <x:c r="H95" s="24" t="n">
+        <x:v>142.4</x:v>
+      </x:c>
       <x:c r="I95" s="25" t="n">
         <x:v>0.01757243694160615</x:v>
       </x:c>
@@ -19556,7 +19708,9 @@
       <x:c r="G96" s="24" t="n">
         <x:v>8279.2</x:v>
       </x:c>
-      <x:c r="H96" s="24"/>
+      <x:c r="H96" s="24" t="n">
+        <x:v>33.2</x:v>
+      </x:c>
       <x:c r="I96" s="25" t="n">
         <x:v>0.00402619451855446</x:v>
       </x:c>
@@ -19678,7 +19832,9 @@
       <x:c r="G102" s="24" t="n">
         <x:v>8461.6</x:v>
       </x:c>
-      <x:c r="H102" s="24"/>
+      <x:c r="H102" s="27" t="n">
+        <x:v>182.4</x:v>
+      </x:c>
       <x:c r="I102" s="25" t="n">
         <x:v>0.02203111411730596</x:v>
       </x:c>
@@ -19712,7 +19868,9 @@
       <x:c r="G103" s="24" t="n">
         <x:v>8627.6</x:v>
       </x:c>
-      <x:c r="H103" s="24"/>
+      <x:c r="H103" s="27" t="n">
+        <x:v>166</x:v>
+      </x:c>
       <x:c r="I103" s="25" t="n">
         <x:v>0.019618039141533483</x:v>
       </x:c>
@@ -19746,7 +19904,9 @@
       <x:c r="G104" s="24" t="n">
         <x:v>8642.2</x:v>
       </x:c>
-      <x:c r="H104" s="24"/>
+      <x:c r="H104" s="24" t="n">
+        <x:v>14.6</x:v>
+      </x:c>
       <x:c r="I104" s="25" t="n">
         <x:v>0.0016922434976123224</x:v>
       </x:c>
@@ -19780,7 +19940,9 @@
       <x:c r="G105" s="24" t="n">
         <x:v>8723</x:v>
       </x:c>
-      <x:c r="H105" s="24"/>
+      <x:c r="H105" s="24" t="n">
+        <x:v>80.8</x:v>
+      </x:c>
       <x:c r="I105" s="25" t="n">
         <x:v>0.009349471199463055</x:v>
       </x:c>
@@ -19814,7 +19976,9 @@
       <x:c r="G106" s="24" t="n">
         <x:v>8701.8</x:v>
       </x:c>
-      <x:c r="H106" s="24"/>
+      <x:c r="H106" s="24" t="n">
+        <x:v>-21.2</x:v>
+      </x:c>
       <x:c r="I106" s="25" t="n">
         <x:v>-0.002430356528717259</x:v>
       </x:c>
@@ -19848,7 +20012,9 @@
       <x:c r="G107" s="24" t="n">
         <x:v>8870.6</x:v>
       </x:c>
-      <x:c r="H107" s="24"/>
+      <x:c r="H107" s="27" t="n">
+        <x:v>168.8</x:v>
+      </x:c>
       <x:c r="I107" s="25" t="n">
         <x:v>0.019398285412213667</x:v>
       </x:c>
@@ -19882,7 +20048,9 @@
       <x:c r="G108" s="24" t="n">
         <x:v>8689.8</x:v>
       </x:c>
-      <x:c r="H108" s="24"/>
+      <x:c r="H108" s="27" t="n">
+        <x:v>-180.8</x:v>
+      </x:c>
       <x:c r="I108" s="25" t="n">
         <x:v>-0.020381935832976428</x:v>
       </x:c>
@@ -19916,7 +20084,9 @@
       <x:c r="G109" s="34" t="n">
         <x:v>8582.6</x:v>
       </x:c>
-      <x:c r="H109" s="34"/>
+      <x:c r="H109" s="34" t="n">
+        <x:v>-107.2</x:v>
+      </x:c>
       <x:c r="I109" s="35" t="n">
         <x:v>-0.012336302331468985</x:v>
       </x:c>
@@ -19950,7 +20120,9 @@
       <x:c r="G110" s="24" t="n">
         <x:v>8632.6</x:v>
       </x:c>
-      <x:c r="H110" s="24"/>
+      <x:c r="H110" s="24" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="I110" s="25" t="n">
         <x:v>0.005825740451611328</x:v>
       </x:c>
@@ -19984,7 +20156,9 @@
       <x:c r="G111" s="24" t="n">
         <x:v>8718.6</x:v>
       </x:c>
-      <x:c r="H111" s="24"/>
+      <x:c r="H111" s="24" t="n">
+        <x:v>86</x:v>
+      </x:c>
       <x:c r="I111" s="25" t="n">
         <x:v>0.009962236174501315</x:v>
       </x:c>
@@ -20018,7 +20192,9 @@
       <x:c r="G112" s="24" t="n">
         <x:v>8705</x:v>
       </x:c>
-      <x:c r="H112" s="24"/>
+      <x:c r="H112" s="24" t="n">
+        <x:v>-13.6</x:v>
+      </x:c>
       <x:c r="I112" s="25" t="n">
         <x:v>-0.0015598834675292217</x:v>
       </x:c>
@@ -20052,7 +20228,9 @@
       <x:c r="G113" s="24" t="n">
         <x:v>8438.2</x:v>
       </x:c>
-      <x:c r="H113" s="24"/>
+      <x:c r="H113" s="27" t="n">
+        <x:v>-266.8</x:v>
+      </x:c>
       <x:c r="I113" s="25" t="n">
         <x:v>-0.030649052268810983</x:v>
       </x:c>
@@ -20086,7 +20264,9 @@
       <x:c r="G114" s="24" t="n">
         <x:v>8589.8</x:v>
       </x:c>
-      <x:c r="H114" s="24"/>
+      <x:c r="H114" s="27" t="n">
+        <x:v>151.6</x:v>
+      </x:c>
       <x:c r="I114" s="25" t="n">
         <x:v>0.01796591690170879</x:v>
       </x:c>
@@ -20120,7 +20300,9 @@
       <x:c r="G115" s="24" t="n">
         <x:v>8661.4</x:v>
       </x:c>
-      <x:c r="H115" s="24"/>
+      <x:c r="H115" s="24" t="n">
+        <x:v>71.6</x:v>
+      </x:c>
       <x:c r="I115" s="25" t="n">
         <x:v>0.008335467647675232</x:v>
       </x:c>
@@ -20154,7 +20336,9 @@
       <x:c r="G116" s="24" t="n">
         <x:v>8596</x:v>
       </x:c>
-      <x:c r="H116" s="24"/>
+      <x:c r="H116" s="24" t="n">
+        <x:v>-65.4</x:v>
+      </x:c>
       <x:c r="I116" s="25" t="n">
         <x:v>-0.007550742374211938</x:v>
       </x:c>
@@ -20188,7 +20372,9 @@
       <x:c r="G117" s="24" t="n">
         <x:v>8441.2</x:v>
       </x:c>
-      <x:c r="H117" s="24"/>
+      <x:c r="H117" s="27" t="n">
+        <x:v>-154.8</x:v>
+      </x:c>
       <x:c r="I117" s="25" t="n">
         <x:v>-0.01800837598883198</x:v>
       </x:c>
@@ -20222,7 +20408,9 @@
       <x:c r="G118" s="24" t="n">
         <x:v>8524.4</x:v>
       </x:c>
-      <x:c r="H118" s="24"/>
+      <x:c r="H118" s="24" t="n">
+        <x:v>83.2</x:v>
+      </x:c>
       <x:c r="I118" s="25" t="n">
         <x:v>0.009856418518693788</x:v>
       </x:c>
@@ -20256,7 +20444,9 @@
       <x:c r="G119" s="24" t="n">
         <x:v>8344.8</x:v>
       </x:c>
-      <x:c r="H119" s="24"/>
+      <x:c r="H119" s="27" t="n">
+        <x:v>-179.6</x:v>
+      </x:c>
       <x:c r="I119" s="25" t="n">
         <x:v>-0.021068931537703617</x:v>
       </x:c>
@@ -20378,7 +20568,9 @@
       <x:c r="G125" s="24" t="n">
         <x:v>8305.8</x:v>
       </x:c>
-      <x:c r="H125" s="24"/>
+      <x:c r="H125" s="24" t="n">
+        <x:v>-39</x:v>
+      </x:c>
       <x:c r="I125" s="25" t="n">
         <x:v>-0.004673569168823666</x:v>
       </x:c>
@@ -20412,7 +20604,9 @@
       <x:c r="G126" s="24" t="n">
         <x:v>8324.6</x:v>
       </x:c>
-      <x:c r="H126" s="24"/>
+      <x:c r="H126" s="24" t="n">
+        <x:v>18.8</x:v>
+      </x:c>
       <x:c r="I126" s="25" t="n">
         <x:v>0.002263478533073515</x:v>
       </x:c>
@@ -20446,7 +20640,9 @@
       <x:c r="G127" s="24" t="n">
         <x:v>8368.4</x:v>
       </x:c>
-      <x:c r="H127" s="24"/>
+      <x:c r="H127" s="24" t="n">
+        <x:v>43.8</x:v>
+      </x:c>
       <x:c r="I127" s="25" t="n">
         <x:v>0.0052615140667418014</x:v>
       </x:c>
@@ -20480,7 +20676,9 @@
       <x:c r="G128" s="24" t="n">
         <x:v>8354.8</x:v>
       </x:c>
-      <x:c r="H128" s="24"/>
+      <x:c r="H128" s="24" t="n">
+        <x:v>-13.6</x:v>
+      </x:c>
       <x:c r="I128" s="25" t="n">
         <x:v>-0.0016251613211606397</x:v>
       </x:c>
@@ -20514,7 +20712,9 @@
       <x:c r="G129" s="24" t="n">
         <x:v>8291.8</x:v>
       </x:c>
-      <x:c r="H129" s="24"/>
+      <x:c r="H129" s="24" t="n">
+        <x:v>-63</x:v>
+      </x:c>
       <x:c r="I129" s="25" t="n">
         <x:v>-0.007540575477569811</x:v>
       </x:c>
@@ -20548,7 +20748,9 @@
       <x:c r="G130" s="24" t="n">
         <x:v>8072.8</x:v>
       </x:c>
-      <x:c r="H130" s="24"/>
+      <x:c r="H130" s="27" t="n">
+        <x:v>-219</x:v>
+      </x:c>
       <x:c r="I130" s="25" t="n">
         <x:v>-0.026411635591789384</x:v>
       </x:c>
@@ -20582,7 +20784,9 @@
       <x:c r="G131" s="24" t="n">
         <x:v>8233.4</x:v>
       </x:c>
-      <x:c r="H131" s="24"/>
+      <x:c r="H131" s="27" t="n">
+        <x:v>160.6</x:v>
+      </x:c>
       <x:c r="I131" s="25" t="n">
         <x:v>0.019893964919234897</x:v>
       </x:c>
@@ -20616,7 +20820,9 @@
       <x:c r="G132" s="24" t="n">
         <x:v>8162.2</x:v>
       </x:c>
-      <x:c r="H132" s="24"/>
+      <x:c r="H132" s="24" t="n">
+        <x:v>-71.2</x:v>
+      </x:c>
       <x:c r="I132" s="25" t="n">
         <x:v>-0.008647703257463446</x:v>
       </x:c>
@@ -20650,7 +20856,9 @@
       <x:c r="G133" s="24" t="n">
         <x:v>8126.4</x:v>
       </x:c>
-      <x:c r="H133" s="24"/>
+      <x:c r="H133" s="24" t="n">
+        <x:v>-35.8</x:v>
+      </x:c>
       <x:c r="I133" s="25" t="n">
         <x:v>-0.004386072382445927</x:v>
       </x:c>
@@ -20684,7 +20892,9 @@
       <x:c r="G134" s="24" t="n">
         <x:v>8196.8</x:v>
       </x:c>
-      <x:c r="H134" s="24"/>
+      <x:c r="H134" s="24" t="n">
+        <x:v>70.4</x:v>
+      </x:c>
       <x:c r="I134" s="25" t="n">
         <x:v>0.008663122661941358</x:v>
       </x:c>
@@ -20718,9 +20928,11 @@
       <x:c r="G135" s="24" t="n">
         <x:v>8475.2</x:v>
       </x:c>
-      <x:c r="H135" s="24"/>
+      <x:c r="H135" s="27" t="n">
+        <x:v>278.4</x:v>
+      </x:c>
       <x:c r="I135" s="25" t="n">
-        <x:v>0.00583154401717767</x:v>
+        <x:v>0.03396447394105029</x:v>
       </x:c>
       <x:c r="J135" s="29" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
@@ -20752,9 +20964,11 @@
       <x:c r="G136" s="24" t="n">
         <x:v>8602.4</x:v>
       </x:c>
-      <x:c r="H136" s="24"/>
+      <x:c r="H136" s="24" t="n">
+        <x:v>127.2</x:v>
+      </x:c>
       <x:c r="I136" s="25" t="n">
-        <x:v>0.012662833854886868</x:v>
+        <x:v>0.01500849537474025</x:v>
       </x:c>
       <x:c r="J136" s="29" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -20786,9 +21000,11 @@
       <x:c r="G137" s="24" t="n">
         <x:v>8695</x:v>
       </x:c>
-      <x:c r="H137" s="24"/>
+      <x:c r="H137" s="24" t="n">
+        <x:v>92.6</x:v>
+      </x:c>
       <x:c r="I137" s="25" t="n">
-        <x:v>0.01149838303988493</x:v>
+        <x:v>0.010764437831302986</x:v>
       </x:c>
       <x:c r="J137" s="24" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -20820,9 +21036,11 @@
       <x:c r="G138" s="24" t="n">
         <x:v>8766</x:v>
       </x:c>
-      <x:c r="H138" s="24"/>
+      <x:c r="H138" s="24" t="n">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="I138" s="25" t="n">
-        <x:v>0.007696862048549358</x:v>
+        <x:v>0.0081656124209315</x:v>
       </x:c>
       <x:c r="J138" s="24" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -20854,9 +21072,11 @@
       <x:c r="G139" s="34" t="n">
         <x:v>8524.2</x:v>
       </x:c>
-      <x:c r="H139" s="34"/>
+      <x:c r="H139" s="27" t="n">
+        <x:v>-241.8</x:v>
+      </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.001668625146886038</x:v>
+        <x:v>-0.02758384668035585</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -20888,7 +21108,9 @@
       <x:c r="G140" s="24" t="n">
         <x:v>8403</x:v>
       </x:c>
-      <x:c r="H140" s="24"/>
+      <x:c r="H140" s="24" t="n">
+        <x:v>-121.2</x:v>
+      </x:c>
       <x:c r="I140" s="25" t="n">
         <x:v>-0.014218343070317552</x:v>
       </x:c>
@@ -20922,7 +21144,9 @@
       <x:c r="G141" s="24" t="n">
         <x:v>8472.4</x:v>
       </x:c>
-      <x:c r="H141" s="24"/>
+      <x:c r="H141" s="24" t="n">
+        <x:v>69.4</x:v>
+      </x:c>
       <x:c r="I141" s="25" t="n">
         <x:v>0.008258955135070689</x:v>
       </x:c>
@@ -20956,7 +21180,9 @@
       <x:c r="G142" s="24" t="n">
         <x:v>8523.8</x:v>
       </x:c>
-      <x:c r="H142" s="24"/>
+      <x:c r="H142" s="24" t="n">
+        <x:v>51.4</x:v>
+      </x:c>
       <x:c r="I142" s="25" t="n">
         <x:v>0.0060667579434399155</x:v>
       </x:c>
@@ -20990,7 +21216,9 @@
       <x:c r="G143" s="24" t="n">
         <x:v>8319.2</x:v>
       </x:c>
-      <x:c r="H143" s="24"/>
+      <x:c r="H143" s="27" t="n">
+        <x:v>-204.6</x:v>
+      </x:c>
       <x:c r="I143" s="25" t="n">
         <x:v>-0.024003378774724693</x:v>
       </x:c>
@@ -21024,7 +21252,9 @@
       <x:c r="G144" s="24" t="n">
         <x:v>8308.6</x:v>
       </x:c>
-      <x:c r="H144" s="24"/>
+      <x:c r="H144" s="24" t="n">
+        <x:v>-10.6</x:v>
+      </x:c>
       <x:c r="I144" s="25" t="n">
         <x:v>-0.001274160977017047</x:v>
       </x:c>
@@ -21058,7 +21288,9 @@
       <x:c r="G145" s="24" t="n">
         <x:v>8504.2</x:v>
       </x:c>
-      <x:c r="H145" s="24"/>
+      <x:c r="H145" s="27" t="n">
+        <x:v>195.6</x:v>
+      </x:c>
       <x:c r="I145" s="25" t="n">
         <x:v>0.02354187227691784</x:v>
       </x:c>
@@ -21180,7 +21412,9 @@
       <x:c r="G151" s="24" t="n">
         <x:v>8517.6</x:v>
       </x:c>
-      <x:c r="H151" s="24"/>
+      <x:c r="H151" s="24" t="n">
+        <x:v>13.4</x:v>
+      </x:c>
       <x:c r="I151" s="25" t="n">
         <x:v>0.00157569201100638</x:v>
       </x:c>
@@ -21214,7 +21448,9 @@
       <x:c r="G152" s="24" t="n">
         <x:v>8370.2</x:v>
       </x:c>
-      <x:c r="H152" s="24"/>
+      <x:c r="H152" s="24" t="n">
+        <x:v>-147.4</x:v>
+      </x:c>
       <x:c r="I152" s="25" t="n">
         <x:v>-0.017305344228421116</x:v>
       </x:c>
@@ -21248,7 +21484,9 @@
       <x:c r="G153" s="24" t="n">
         <x:v>8373</x:v>
       </x:c>
-      <x:c r="H153" s="24"/>
+      <x:c r="H153" s="24" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
       <x:c r="I153" s="25" t="n">
         <x:v>0.00033452008315215664</x:v>
       </x:c>
@@ -21282,7 +21520,9 @@
       <x:c r="G154" s="24" t="n">
         <x:v>8265</x:v>
       </x:c>
-      <x:c r="H154" s="24"/>
+      <x:c r="H154" s="24" t="n">
+        <x:v>-108</x:v>
+      </x:c>
       <x:c r="I154" s="25" t="n">
         <x:v>-0.012898602651379432</x:v>
       </x:c>
@@ -21316,7 +21556,9 @@
       <x:c r="G155" s="24" t="n">
         <x:v>8115.2</x:v>
       </x:c>
-      <x:c r="H155" s="24"/>
+      <x:c r="H155" s="24" t="n">
+        <x:v>-149.8</x:v>
+      </x:c>
       <x:c r="I155" s="25" t="n">
         <x:v>-0.018124621899576532</x:v>
       </x:c>
@@ -21350,7 +21592,9 @@
       <x:c r="G156" s="24" t="n">
         <x:v>7974</x:v>
       </x:c>
-      <x:c r="H156" s="24"/>
+      <x:c r="H156" s="24" t="n">
+        <x:v>-141.2</x:v>
+      </x:c>
       <x:c r="I156" s="25" t="n">
         <x:v>-0.017399447949526747</x:v>
       </x:c>
@@ -21384,7 +21628,9 @@
       <x:c r="G157" s="24" t="n">
         <x:v>8127.4</x:v>
       </x:c>
-      <x:c r="H157" s="24"/>
+      <x:c r="H157" s="27" t="n">
+        <x:v>153.4</x:v>
+      </x:c>
       <x:c r="I157" s="25" t="n">
         <x:v>0.019237521946325442</x:v>
       </x:c>
@@ -21418,7 +21664,9 @@
       <x:c r="G158" s="24" t="n">
         <x:v>8019.4</x:v>
       </x:c>
-      <x:c r="H158" s="24"/>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-108</x:v>
+      </x:c>
       <x:c r="I158" s="25" t="n">
         <x:v>-0.013288382508551355</x:v>
       </x:c>
@@ -21452,7 +21700,9 @@
       <x:c r="G159" s="24" t="n">
         <x:v>7684.4</x:v>
       </x:c>
-      <x:c r="H159" s="24"/>
+      <x:c r="H159" s="27" t="n">
+        <x:v>-335</x:v>
+      </x:c>
       <x:c r="I159" s="25" t="n">
         <x:v>-0.04177369878045745</x:v>
       </x:c>
@@ -21486,7 +21736,9 @@
       <x:c r="G160" s="24" t="n">
         <x:v>7788</x:v>
       </x:c>
-      <x:c r="H160" s="24"/>
+      <x:c r="H160" s="24" t="n">
+        <x:v>103.6</x:v>
+      </x:c>
       <x:c r="I160" s="25" t="n">
         <x:v>0.013481859351413217</x:v>
       </x:c>
@@ -21520,7 +21772,9 @@
       <x:c r="G161" s="24" t="n">
         <x:v>7723.2</x:v>
       </x:c>
-      <x:c r="H161" s="24"/>
+      <x:c r="H161" s="24" t="n">
+        <x:v>-64.8</x:v>
+      </x:c>
       <x:c r="I161" s="25" t="n">
         <x:v>-0.008320493066255819</x:v>
       </x:c>
@@ -21554,7 +21808,9 @@
       <x:c r="G162" s="24" t="n">
         <x:v>7552.6</x:v>
       </x:c>
-      <x:c r="H162" s="24"/>
+      <x:c r="H162" s="27" t="n">
+        <x:v>-170.6</x:v>
+      </x:c>
       <x:c r="I162" s="25" t="n">
         <x:v>-0.022089289413714464</x:v>
       </x:c>
@@ -21713,7 +21969,9 @@
       <x:c r="G5" s="24" t="n">
         <x:v>7596</x:v>
       </x:c>
-      <x:c r="H5" s="24"/>
+      <x:c r="H5" s="27" t="n">
+        <x:v>233.2</x:v>
+      </x:c>
       <x:c r="I5" s="25" t="n">
         <x:v>0.031672733199326286</x:v>
       </x:c>
@@ -21747,7 +22005,9 @@
       <x:c r="G6" s="24" t="n">
         <x:v>7786.4</x:v>
       </x:c>
-      <x:c r="H6" s="24"/>
+      <x:c r="H6" s="27" t="n">
+        <x:v>190.4</x:v>
+      </x:c>
       <x:c r="I6" s="25" t="n">
         <x:v>0.02506582411795688</x:v>
       </x:c>
@@ -21781,7 +22041,9 @@
       <x:c r="G7" s="24" t="n">
         <x:v>7802.6</x:v>
       </x:c>
-      <x:c r="H7" s="24"/>
+      <x:c r="H7" s="24" t="n">
+        <x:v>16.2</x:v>
+      </x:c>
       <x:c r="I7" s="25" t="n">
         <x:v>0.0020805507037913173</x:v>
       </x:c>
@@ -21815,7 +22077,9 @@
       <x:c r="G8" s="24" t="n">
         <x:v>7814.4</x:v>
       </x:c>
-      <x:c r="H8" s="24"/>
+      <x:c r="H8" s="24" t="n">
+        <x:v>11.8</x:v>
+      </x:c>
       <x:c r="I8" s="25" t="n">
         <x:v>0.0015123164073513884</x:v>
       </x:c>
@@ -21849,7 +22113,9 @@
       <x:c r="G9" s="24" t="n">
         <x:v>8037.8</x:v>
       </x:c>
-      <x:c r="H9" s="24"/>
+      <x:c r="H9" s="27" t="n">
+        <x:v>223.4</x:v>
+      </x:c>
       <x:c r="I9" s="25" t="n">
         <x:v>0.028588247338247497</x:v>
       </x:c>
@@ -21883,7 +22149,9 @@
       <x:c r="G10" s="24" t="n">
         <x:v>8236.6</x:v>
       </x:c>
-      <x:c r="H10" s="24"/>
+      <x:c r="H10" s="27" t="n">
+        <x:v>198.8</x:v>
+      </x:c>
       <x:c r="I10" s="25" t="n">
         <x:v>0.024733135932717865</x:v>
       </x:c>
@@ -21917,7 +22185,9 @@
       <x:c r="G11" s="24" t="n">
         <x:v>8131.2</x:v>
       </x:c>
-      <x:c r="H11" s="24"/>
+      <x:c r="H11" s="24" t="n">
+        <x:v>-105.4</x:v>
+      </x:c>
       <x:c r="I11" s="25" t="n">
         <x:v>-0.012796542262584087</x:v>
       </x:c>
@@ -21951,7 +22221,9 @@
       <x:c r="G12" s="24" t="n">
         <x:v>8197.8</x:v>
       </x:c>
-      <x:c r="H12" s="24"/>
+      <x:c r="H12" s="24" t="n">
+        <x:v>66.6</x:v>
+      </x:c>
       <x:c r="I12" s="25" t="n">
         <x:v>0.008190672963400258</x:v>
       </x:c>
@@ -21985,7 +22257,9 @@
       <x:c r="G13" s="24" t="n">
         <x:v>8206.8</x:v>
       </x:c>
-      <x:c r="H13" s="24"/>
+      <x:c r="H13" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="I13" s="25" t="n">
         <x:v>0.001097855522213198</x:v>
       </x:c>
@@ -22019,7 +22293,9 @@
       <x:c r="G14" s="34" t="n">
         <x:v>8210.4</x:v>
       </x:c>
-      <x:c r="H14" s="34"/>
+      <x:c r="H14" s="34" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
       <x:c r="I14" s="35" t="n">
         <x:v>0.0004386606228981016</x:v>
       </x:c>
@@ -22053,7 +22329,9 @@
       <x:c r="G15" s="24" t="n">
         <x:v>8266</x:v>
       </x:c>
-      <x:c r="H15" s="24"/>
+      <x:c r="H15" s="24" t="n">
+        <x:v>55.6</x:v>
+      </x:c>
       <x:c r="I15" s="25" t="n">
         <x:v>0.006771899054857311</x:v>
       </x:c>
@@ -22087,7 +22365,9 @@
       <x:c r="G16" s="24" t="n">
         <x:v>8248.8</x:v>
       </x:c>
-      <x:c r="H16" s="24"/>
+      <x:c r="H16" s="24" t="n">
+        <x:v>-17.2</x:v>
+      </x:c>
       <x:c r="I16" s="25" t="n">
         <x:v>-0.002080812968787926</x:v>
       </x:c>
@@ -22121,7 +22401,9 @@
       <x:c r="G17" s="24" t="n">
         <x:v>8371</x:v>
       </x:c>
-      <x:c r="H17" s="24"/>
+      <x:c r="H17" s="24" t="n">
+        <x:v>122.2</x:v>
+      </x:c>
       <x:c r="I17" s="25" t="n">
         <x:v>0.014814276015905348</x:v>
       </x:c>
@@ -22155,7 +22437,9 @@
       <x:c r="G18" s="24" t="n">
         <x:v>8400</x:v>
       </x:c>
-      <x:c r="H18" s="24"/>
+      <x:c r="H18" s="24" t="n">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="I18" s="25" t="n">
         <x:v>0.0034643411778760846</x:v>
       </x:c>
@@ -22189,7 +22473,9 @@
       <x:c r="G19" s="24" t="n">
         <x:v>8658.2</x:v>
       </x:c>
-      <x:c r="H19" s="24"/>
+      <x:c r="H19" s="27" t="n">
+        <x:v>258.2</x:v>
+      </x:c>
       <x:c r="I19" s="25" t="n">
         <x:v>0.030738095238095342</x:v>
       </x:c>
@@ -22223,7 +22509,9 @@
       <x:c r="G20" s="24" t="n">
         <x:v>8470</x:v>
       </x:c>
-      <x:c r="H20" s="24"/>
+      <x:c r="H20" s="27" t="n">
+        <x:v>-188.2</x:v>
+      </x:c>
       <x:c r="I20" s="25" t="n">
         <x:v>-0.0217366196207065</x:v>
       </x:c>
@@ -22257,7 +22545,9 @@
       <x:c r="G21" s="24" t="n">
         <x:v>8547.6</x:v>
       </x:c>
-      <x:c r="H21" s="24"/>
+      <x:c r="H21" s="24" t="n">
+        <x:v>77.6</x:v>
+      </x:c>
       <x:c r="I21" s="25" t="n">
         <x:v>0.009161747343565674</x:v>
       </x:c>
@@ -22291,7 +22581,9 @@
       <x:c r="G22" s="24" t="n">
         <x:v>8622</x:v>
       </x:c>
-      <x:c r="H22" s="24"/>
+      <x:c r="H22" s="24" t="n">
+        <x:v>74.4</x:v>
+      </x:c>
       <x:c r="I22" s="25" t="n">
         <x:v>0.00870419766952124</x:v>
       </x:c>
@@ -22325,7 +22617,9 @@
       <x:c r="G23" s="24" t="n">
         <x:v>8517.6</x:v>
       </x:c>
-      <x:c r="H23" s="24"/>
+      <x:c r="H23" s="24" t="n">
+        <x:v>-104.4</x:v>
+      </x:c>
       <x:c r="I23" s="25" t="n">
         <x:v>-0.012108559498956062</x:v>
       </x:c>
@@ -22359,7 +22653,9 @@
       <x:c r="G24" s="24" t="n">
         <x:v>8362.4</x:v>
       </x:c>
-      <x:c r="H24" s="24"/>
+      <x:c r="H24" s="27" t="n">
+        <x:v>-155.2</x:v>
+      </x:c>
       <x:c r="I24" s="25" t="n">
         <x:v>-0.01822109514417214</x:v>
       </x:c>
@@ -22481,7 +22777,9 @@
       <x:c r="G30" s="24" t="n">
         <x:v>7903.2</x:v>
       </x:c>
-      <x:c r="H30" s="24"/>
+      <x:c r="H30" s="27" t="n">
+        <x:v>-459.2</x:v>
+      </x:c>
       <x:c r="I30" s="25" t="n">
         <x:v>-0.0549124653209605</x:v>
       </x:c>
@@ -22515,7 +22813,9 @@
       <x:c r="G31" s="24" t="n">
         <x:v>8282</x:v>
       </x:c>
-      <x:c r="H31" s="24"/>
+      <x:c r="H31" s="27" t="n">
+        <x:v>378.8</x:v>
+      </x:c>
       <x:c r="I31" s="25" t="n">
         <x:v>0.0479299524243344</x:v>
       </x:c>
@@ -22549,7 +22849,9 @@
       <x:c r="G32" s="24" t="n">
         <x:v>8313.6</x:v>
       </x:c>
-      <x:c r="H32" s="24"/>
+      <x:c r="H32" s="24" t="n">
+        <x:v>31.6</x:v>
+      </x:c>
       <x:c r="I32" s="25" t="n">
         <x:v>0.0038155035015696726</x:v>
       </x:c>
@@ -22583,7 +22885,9 @@
       <x:c r="G33" s="24" t="n">
         <x:v>8120.2</x:v>
       </x:c>
-      <x:c r="H33" s="24"/>
+      <x:c r="H33" s="27" t="n">
+        <x:v>-193.4</x:v>
+      </x:c>
       <x:c r="I33" s="25" t="n">
         <x:v>-0.023263086989992354</x:v>
       </x:c>
@@ -22617,7 +22921,9 @@
       <x:c r="G34" s="24" t="n">
         <x:v>8117.4</x:v>
       </x:c>
-      <x:c r="H34" s="24"/>
+      <x:c r="H34" s="24" t="n">
+        <x:v>-2.8</x:v>
+      </x:c>
       <x:c r="I34" s="25" t="n">
         <x:v>-0.0003448190931257811</x:v>
       </x:c>
@@ -22651,7 +22957,9 @@
       <x:c r="G35" s="24" t="n">
         <x:v>8311.6</x:v>
       </x:c>
-      <x:c r="H35" s="24"/>
+      <x:c r="H35" s="27" t="n">
+        <x:v>194.2</x:v>
+      </x:c>
       <x:c r="I35" s="25" t="n">
         <x:v>0.023923916524995814</x:v>
       </x:c>
@@ -22685,7 +22993,9 @@
       <x:c r="G36" s="24" t="n">
         <x:v>8290.8</x:v>
       </x:c>
-      <x:c r="H36" s="24"/>
+      <x:c r="H36" s="24" t="n">
+        <x:v>-20.8</x:v>
+      </x:c>
       <x:c r="I36" s="25" t="n">
         <x:v>-0.002502526589345133</x:v>
       </x:c>
@@ -22719,7 +23029,9 @@
       <x:c r="G37" s="24" t="n">
         <x:v>8336.4</x:v>
       </x:c>
-      <x:c r="H37" s="24"/>
+      <x:c r="H37" s="24" t="n">
+        <x:v>45.6</x:v>
+      </x:c>
       <x:c r="I37" s="25" t="n">
         <x:v>0.005500072369373221</x:v>
       </x:c>
@@ -22753,7 +23065,9 @@
       <x:c r="G38" s="24" t="n">
         <x:v>8448.8</x:v>
       </x:c>
-      <x:c r="H38" s="24"/>
+      <x:c r="H38" s="24" t="n">
+        <x:v>112.4</x:v>
+      </x:c>
       <x:c r="I38" s="25" t="n">
         <x:v>0.01348303824192687</x:v>
       </x:c>
@@ -22787,7 +23101,9 @@
       <x:c r="G39" s="24" t="n">
         <x:v>8274.8</x:v>
       </x:c>
-      <x:c r="H39" s="24"/>
+      <x:c r="H39" s="27" t="n">
+        <x:v>-174</x:v>
+      </x:c>
       <x:c r="I39" s="25" t="n">
         <x:v>-0.020594640659028496</x:v>
       </x:c>
@@ -22821,7 +23137,9 @@
       <x:c r="G40" s="34" t="n">
         <x:v>8371.6</x:v>
       </x:c>
-      <x:c r="H40" s="34"/>
+      <x:c r="H40" s="34" t="n">
+        <x:v>96.8</x:v>
+      </x:c>
       <x:c r="I40" s="35" t="n">
         <x:v>0.011698167931551318</x:v>
       </x:c>
@@ -22855,7 +23173,9 @@
       <x:c r="G41" s="24" t="n">
         <x:v>8529</x:v>
       </x:c>
-      <x:c r="H41" s="24"/>
+      <x:c r="H41" s="27" t="n">
+        <x:v>157.4</x:v>
+      </x:c>
       <x:c r="I41" s="25" t="n">
         <x:v>0.01880166276458506</x:v>
       </x:c>
@@ -22889,7 +23209,9 @@
       <x:c r="G42" s="24" t="n">
         <x:v>8537.4</x:v>
       </x:c>
-      <x:c r="H42" s="24"/>
+      <x:c r="H42" s="24" t="n">
+        <x:v>8.4</x:v>
+      </x:c>
       <x:c r="I42" s="25" t="n">
         <x:v>0.0009848751319028182</x:v>
       </x:c>
@@ -22923,7 +23245,9 @@
       <x:c r="G43" s="24" t="n">
         <x:v>8645.4</x:v>
       </x:c>
-      <x:c r="H43" s="24"/>
+      <x:c r="H43" s="24" t="n">
+        <x:v>108</x:v>
+      </x:c>
       <x:c r="I43" s="25" t="n">
         <x:v>0.012650221378874171</x:v>
       </x:c>
@@ -23045,7 +23369,9 @@
       <x:c r="G49" s="24" t="n">
         <x:v>8627</x:v>
       </x:c>
-      <x:c r="H49" s="24"/>
+      <x:c r="H49" s="24" t="n">
+        <x:v>-18.4</x:v>
+      </x:c>
       <x:c r="I49" s="25" t="n">
         <x:v>-0.0021282994424780544</x:v>
       </x:c>
@@ -23079,7 +23405,9 @@
       <x:c r="G50" s="24" t="n">
         <x:v>8266.2</x:v>
       </x:c>
-      <x:c r="H50" s="24"/>
+      <x:c r="H50" s="27" t="n">
+        <x:v>-360.8</x:v>
+      </x:c>
       <x:c r="I50" s="25" t="n">
         <x:v>-0.04182218615973099</x:v>
       </x:c>
@@ -23113,7 +23441,9 @@
       <x:c r="G51" s="24" t="n">
         <x:v>8219.4</x:v>
       </x:c>
-      <x:c r="H51" s="24"/>
+      <x:c r="H51" s="24" t="n">
+        <x:v>-46.8</x:v>
+      </x:c>
       <x:c r="I51" s="25" t="n">
         <x:v>-0.00566160992959297</x:v>
       </x:c>
@@ -23147,7 +23477,9 @@
       <x:c r="G52" s="24" t="n">
         <x:v>8255.6</x:v>
       </x:c>
-      <x:c r="H52" s="24"/>
+      <x:c r="H52" s="24" t="n">
+        <x:v>36.2</x:v>
+      </x:c>
       <x:c r="I52" s="25" t="n">
         <x:v>0.004404214419544195</x:v>
       </x:c>
@@ -23181,7 +23513,9 @@
       <x:c r="G53" s="24" t="n">
         <x:v>8322.6</x:v>
       </x:c>
-      <x:c r="H53" s="24"/>
+      <x:c r="H53" s="24" t="n">
+        <x:v>67</x:v>
+      </x:c>
       <x:c r="I53" s="25" t="n">
         <x:v>0.008115703280197728</x:v>
       </x:c>
@@ -23215,7 +23549,9 @@
       <x:c r="G54" s="24" t="n">
         <x:v>8267</x:v>
       </x:c>
-      <x:c r="H54" s="24"/>
+      <x:c r="H54" s="24" t="n">
+        <x:v>-55.6</x:v>
+      </x:c>
       <x:c r="I54" s="25" t="n">
         <x:v>-0.006680604618748975</x:v>
       </x:c>
@@ -23249,7 +23585,9 @@
       <x:c r="G55" s="24" t="n">
         <x:v>8393.6</x:v>
       </x:c>
-      <x:c r="H55" s="24"/>
+      <x:c r="H55" s="24" t="n">
+        <x:v>126.6</x:v>
+      </x:c>
       <x:c r="I55" s="25" t="n">
         <x:v>0.015313898633119605</x:v>
       </x:c>
@@ -23283,9 +23621,11 @@
       <x:c r="G56" s="24" t="n">
         <x:v>8360</x:v>
       </x:c>
-      <x:c r="H56" s="24"/>
+      <x:c r="H56" s="24" t="n">
+        <x:v>-33.6</x:v>
+      </x:c>
       <x:c r="I56" s="25" t="n">
-        <x:v>-0.023136675562333342</x:v>
+        <x:v>-0.004003049942813641</x:v>
       </x:c>
       <x:c r="J56" s="24" t="n">
         <x:f>ROUND(E56-F56,1)</x:f>
@@ -23317,9 +23657,11 @@
       <x:c r="G57" s="24" t="n">
         <x:v>8301</x:v>
       </x:c>
-      <x:c r="H57" s="24"/>
+      <x:c r="H57" s="24" t="n">
+        <x:v>-59</x:v>
+      </x:c>
       <x:c r="I57" s="25" t="n">
-        <x:v>-0.008805522355294304</x:v>
+        <x:v>-0.00705741626794254</x:v>
       </x:c>
       <x:c r="J57" s="29" t="n">
         <x:f>ROUND(E57-F57,1)</x:f>
@@ -23351,9 +23693,11 @@
       <x:c r="G58" s="24" t="n">
         <x:v>8213.8</x:v>
       </x:c>
-      <x:c r="H58" s="24"/>
+      <x:c r="H58" s="24" t="n">
+        <x:v>-87.2</x:v>
+      </x:c>
       <x:c r="I58" s="25" t="n">
-        <x:v>-0.01186140368146471</x:v>
+        <x:v>-0.01050475846283594</x:v>
       </x:c>
       <x:c r="J58" s="29" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
@@ -23385,9 +23729,11 @@
       <x:c r="G59" s="24" t="n">
         <x:v>8178.4</x:v>
       </x:c>
-      <x:c r="H59" s="24"/>
+      <x:c r="H59" s="24" t="n">
+        <x:v>-35.4</x:v>
+      </x:c>
       <x:c r="I59" s="25" t="n">
-        <x:v>-0.0034118643223589595</x:v>
+        <x:v>-0.004309820058925218</x:v>
       </x:c>
       <x:c r="J59" s="29" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
@@ -23419,9 +23765,11 @@
       <x:c r="G60" s="24" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="H60" s="24"/>
+      <x:c r="H60" s="27" t="n">
+        <x:v>-178.4</x:v>
+      </x:c>
       <x:c r="I60" s="25" t="n">
-        <x:v>-0.024189719369267948</x:v>
+        <x:v>-0.021813557664090766</x:v>
       </x:c>
       <x:c r="J60" s="29" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
@@ -23453,9 +23801,11 @@
       <x:c r="G61" s="24" t="n">
         <x:v>8086</x:v>
       </x:c>
-      <x:c r="H61" s="24"/>
+      <x:c r="H61" s="24" t="n">
+        <x:v>86</x:v>
+      </x:c>
       <x:c r="I61" s="25" t="n">
-        <x:v>0.009552101206176777</x:v>
+        <x:v>0.010750000000000037</x:v>
       </x:c>
       <x:c r="J61" s="24" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -23487,9 +23837,11 @@
       <x:c r="G62" s="24" t="n">
         <x:v>7886.4</x:v>
       </x:c>
-      <x:c r="H62" s="24"/>
+      <x:c r="H62" s="27" t="n">
+        <x:v>-199.6</x:v>
+      </x:c>
       <x:c r="I62" s="25" t="n">
-        <x:v>-0.027066105220435288</x:v>
+        <x:v>-0.024684640118723733</x:v>
       </x:c>
       <x:c r="J62" s="29" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -23521,9 +23873,11 @@
       <x:c r="G63" s="34" t="n">
         <x:v>7844.4</x:v>
       </x:c>
-      <x:c r="H63" s="34"/>
+      <x:c r="H63" s="34" t="n">
+        <x:v>-42</x:v>
+      </x:c>
       <x:c r="I63" s="35" t="n">
-        <x:v>-0.014548298787641856</x:v>
+        <x:v>-0.00532562385879487</x:v>
       </x:c>
       <x:c r="J63" s="34" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -23555,9 +23909,11 @@
       <x:c r="G64" s="24" t="n">
         <x:v>7235</x:v>
       </x:c>
-      <x:c r="H64" s="24"/>
+      <x:c r="H64" s="27" t="n">
+        <x:v>-609.4</x:v>
+      </x:c>
       <x:c r="I64" s="25" t="n">
-        <x:v>-0.042913458740111654</x:v>
+        <x:v>-0.07768599255519859</x:v>
       </x:c>
       <x:c r="J64" s="29" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -23589,7 +23945,9 @@
       <x:c r="G65" s="24" t="n">
         <x:v>7409.6</x:v>
       </x:c>
-      <x:c r="H65" s="24"/>
+      <x:c r="H65" s="27" t="n">
+        <x:v>174.6</x:v>
+      </x:c>
       <x:c r="I65" s="25" t="n">
         <x:v>0.024132688320663398</x:v>
       </x:c>
@@ -23623,7 +23981,9 @@
       <x:c r="G66" s="24" t="n">
         <x:v>7530</x:v>
       </x:c>
-      <x:c r="H66" s="24"/>
+      <x:c r="H66" s="24" t="n">
+        <x:v>120.4</x:v>
+      </x:c>
       <x:c r="I66" s="25" t="n">
         <x:v>0.01624919023968907</x:v>
       </x:c>
@@ -23657,7 +24017,9 @@
       <x:c r="G67" s="24" t="n">
         <x:v>7413.8</x:v>
       </x:c>
-      <x:c r="H67" s="24"/>
+      <x:c r="H67" s="24" t="n">
+        <x:v>-116.2</x:v>
+      </x:c>
       <x:c r="I67" s="25" t="n">
         <x:v>-0.015431606905710438</x:v>
       </x:c>
@@ -23691,7 +24053,9 @@
       <x:c r="G68" s="24" t="n">
         <x:v>7559.2</x:v>
       </x:c>
-      <x:c r="H68" s="24"/>
+      <x:c r="H68" s="24" t="n">
+        <x:v>145.4</x:v>
+      </x:c>
       <x:c r="I68" s="25" t="n">
         <x:v>0.01961207477946525</x:v>
       </x:c>
@@ -23725,7 +24089,9 @@
       <x:c r="G69" s="24" t="n">
         <x:v>7560.6</x:v>
       </x:c>
-      <x:c r="H69" s="24"/>
+      <x:c r="H69" s="24" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
       <x:c r="I69" s="25" t="n">
         <x:v>0.00018520478357508807</x:v>
       </x:c>
@@ -23759,7 +24125,9 @@
       <x:c r="G70" s="24" t="n">
         <x:v>7425</x:v>
       </x:c>
-      <x:c r="H70" s="24"/>
+      <x:c r="H70" s="24" t="n">
+        <x:v>-135.6</x:v>
+      </x:c>
       <x:c r="I70" s="25" t="n">
         <x:v>-0.017935084517101907</x:v>
       </x:c>
@@ -23881,7 +24249,9 @@
       <x:c r="G76" s="24" t="n">
         <x:v>7565.8</x:v>
       </x:c>
-      <x:c r="H76" s="24"/>
+      <x:c r="H76" s="24" t="n">
+        <x:v>140.8</x:v>
+      </x:c>
       <x:c r="I76" s="25" t="n">
         <x:v>0.01896296296296307</x:v>
       </x:c>
@@ -23915,7 +24285,9 @@
       <x:c r="G77" s="24" t="n">
         <x:v>7409.6</x:v>
       </x:c>
-      <x:c r="H77" s="24"/>
+      <x:c r="H77" s="27" t="n">
+        <x:v>-156.2</x:v>
+      </x:c>
       <x:c r="I77" s="25" t="n">
         <x:v>-0.020645536493166583</x:v>
       </x:c>
@@ -23949,7 +24321,9 @@
       <x:c r="G78" s="24" t="n">
         <x:v>7352</x:v>
       </x:c>
-      <x:c r="H78" s="24"/>
+      <x:c r="H78" s="24" t="n">
+        <x:v>-57.6</x:v>
+      </x:c>
       <x:c r="I78" s="25" t="n">
         <x:v>-0.007773698985100497</x:v>
       </x:c>
@@ -23983,7 +24357,9 @@
       <x:c r="G79" s="24" t="n">
         <x:v>7388.8</x:v>
       </x:c>
-      <x:c r="H79" s="24"/>
+      <x:c r="H79" s="24" t="n">
+        <x:v>36.8</x:v>
+      </x:c>
       <x:c r="I79" s="25" t="n">
         <x:v>0.005005440696409069</x:v>
       </x:c>
@@ -24017,7 +24393,9 @@
       <x:c r="G80" s="24" t="n">
         <x:v>7831.8</x:v>
       </x:c>
-      <x:c r="H80" s="24"/>
+      <x:c r="H80" s="27" t="n">
+        <x:v>443</x:v>
+      </x:c>
       <x:c r="I80" s="25" t="n">
         <x:v>0.059955608488523104</x:v>
       </x:c>
@@ -24051,7 +24429,9 @@
       <x:c r="G81" s="24" t="n">
         <x:v>7748.8</x:v>
       </x:c>
-      <x:c r="H81" s="24"/>
+      <x:c r="H81" s="24" t="n">
+        <x:v>-83</x:v>
+      </x:c>
       <x:c r="I81" s="25" t="n">
         <x:v>-0.010597819147577847</x:v>
       </x:c>
@@ -24085,7 +24465,9 @@
       <x:c r="G82" s="24" t="n">
         <x:v>7828.6</x:v>
       </x:c>
-      <x:c r="H82" s="24"/>
+      <x:c r="H82" s="24" t="n">
+        <x:v>79.8</x:v>
+      </x:c>
       <x:c r="I82" s="25" t="n">
         <x:v>0.010298368779682043</x:v>
       </x:c>
@@ -24119,7 +24501,9 @@
       <x:c r="G83" s="24" t="n">
         <x:v>7808.8</x:v>
       </x:c>
-      <x:c r="H83" s="24"/>
+      <x:c r="H83" s="24" t="n">
+        <x:v>-19.8</x:v>
+      </x:c>
       <x:c r="I83" s="25" t="n">
         <x:v>-0.0025291878496793707</x:v>
       </x:c>
@@ -24153,7 +24537,9 @@
       <x:c r="G84" s="24" t="n">
         <x:v>7938.4</x:v>
       </x:c>
-      <x:c r="H84" s="24"/>
+      <x:c r="H84" s="24" t="n">
+        <x:v>129.6</x:v>
+      </x:c>
       <x:c r="I84" s="25" t="n">
         <x:v>0.016596660178260336</x:v>
       </x:c>
@@ -24187,7 +24573,9 @@
       <x:c r="G85" s="24" t="n">
         <x:v>7904</x:v>
       </x:c>
-      <x:c r="H85" s="24"/>
+      <x:c r="H85" s="24" t="n">
+        <x:v>-34.4</x:v>
+      </x:c>
       <x:c r="I85" s="25" t="n">
         <x:v>-0.004333366925324933</x:v>
       </x:c>
@@ -24221,7 +24609,9 @@
       <x:c r="G86" s="24" t="n">
         <x:v>8065</x:v>
       </x:c>
-      <x:c r="H86" s="24"/>
+      <x:c r="H86" s="27" t="n">
+        <x:v>161</x:v>
+      </x:c>
       <x:c r="I86" s="25" t="n">
         <x:v>0.020369433198380582</x:v>
       </x:c>
@@ -24255,7 +24645,9 @@
       <x:c r="G87" s="34" t="n">
         <x:v>8098.8</x:v>
       </x:c>
-      <x:c r="H87" s="34"/>
+      <x:c r="H87" s="34" t="n">
+        <x:v>33.8</x:v>
+      </x:c>
       <x:c r="I87" s="35" t="n">
         <x:v>0.004190948543087547</x:v>
       </x:c>
@@ -24289,7 +24681,9 @@
       <x:c r="G88" s="24" t="n">
         <x:v>8146.2</x:v>
       </x:c>
-      <x:c r="H88" s="24"/>
+      <x:c r="H88" s="24" t="n">
+        <x:v>47.4</x:v>
+      </x:c>
       <x:c r="I88" s="25" t="n">
         <x:v>0.005852718921321554</x:v>
       </x:c>
@@ -24323,7 +24717,9 @@
       <x:c r="G89" s="24" t="n">
         <x:v>8124.4</x:v>
       </x:c>
-      <x:c r="H89" s="24"/>
+      <x:c r="H89" s="24" t="n">
+        <x:v>-21.8</x:v>
+      </x:c>
       <x:c r="I89" s="25" t="n">
         <x:v>-0.0026760943752915933</x:v>
       </x:c>
@@ -24357,7 +24753,9 @@
       <x:c r="G90" s="24" t="n">
         <x:v>8264.2</x:v>
       </x:c>
-      <x:c r="H90" s="24"/>
+      <x:c r="H90" s="24" t="n">
+        <x:v>139.8</x:v>
+      </x:c>
       <x:c r="I90" s="25" t="n">
         <x:v>0.017207424548274508</x:v>
       </x:c>
@@ -24391,7 +24789,9 @@
       <x:c r="G91" s="24" t="n">
         <x:v>8177</x:v>
       </x:c>
-      <x:c r="H91" s="24"/>
+      <x:c r="H91" s="24" t="n">
+        <x:v>-87.2</x:v>
+      </x:c>
       <x:c r="I91" s="25" t="n">
         <x:v>-0.010551535538830259</x:v>
       </x:c>
@@ -24425,7 +24825,9 @@
       <x:c r="G92" s="24" t="n">
         <x:v>8132.8</x:v>
       </x:c>
-      <x:c r="H92" s="24"/>
+      <x:c r="H92" s="24" t="n">
+        <x:v>-44.2</x:v>
+      </x:c>
       <x:c r="I92" s="25" t="n">
         <x:v>-0.00540540540540535</x:v>
       </x:c>
@@ -24459,7 +24861,9 @@
       <x:c r="G93" s="24" t="n">
         <x:v>8186.4</x:v>
       </x:c>
-      <x:c r="H93" s="24"/>
+      <x:c r="H93" s="24" t="n">
+        <x:v>53.6</x:v>
+      </x:c>
       <x:c r="I93" s="25" t="n">
         <x:v>0.006590596104662616</x:v>
       </x:c>
@@ -24493,7 +24897,9 @@
       <x:c r="G94" s="24" t="n">
         <x:v>8094.6</x:v>
       </x:c>
-      <x:c r="H94" s="24"/>
+      <x:c r="H94" s="24" t="n">
+        <x:v>-91.8</x:v>
+      </x:c>
       <x:c r="I94" s="25" t="n">
         <x:v>-0.0112137203166226</x:v>
       </x:c>
@@ -24527,7 +24933,9 @@
       <x:c r="G95" s="24" t="n">
         <x:v>8270</x:v>
       </x:c>
-      <x:c r="H95" s="24"/>
+      <x:c r="H95" s="27" t="n">
+        <x:v>175.4</x:v>
+      </x:c>
       <x:c r="I95" s="25" t="n">
         <x:v>0.021668766832209085</x:v>
       </x:c>
@@ -24561,7 +24969,9 @@
       <x:c r="G96" s="24" t="n">
         <x:v>8270</x:v>
       </x:c>
-      <x:c r="H96" s="24"/>
+      <x:c r="H96" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I96" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -24683,7 +25093,9 @@
       <x:c r="G102" s="24" t="n">
         <x:v>8497.6</x:v>
       </x:c>
-      <x:c r="H102" s="24"/>
+      <x:c r="H102" s="27" t="n">
+        <x:v>227.6</x:v>
+      </x:c>
       <x:c r="I102" s="25" t="n">
         <x:v>0.027521160822249202</x:v>
       </x:c>
@@ -24717,7 +25129,9 @@
       <x:c r="G103" s="24" t="n">
         <x:v>8624.8</x:v>
       </x:c>
-      <x:c r="H103" s="24"/>
+      <x:c r="H103" s="24" t="n">
+        <x:v>127.2</x:v>
+      </x:c>
       <x:c r="I103" s="25" t="n">
         <x:v>0.014968932404443525</x:v>
       </x:c>
@@ -24751,7 +25165,9 @@
       <x:c r="G104" s="24" t="n">
         <x:v>8620.8</x:v>
       </x:c>
-      <x:c r="H104" s="24"/>
+      <x:c r="H104" s="24" t="n">
+        <x:v>-4</x:v>
+      </x:c>
       <x:c r="I104" s="25" t="n">
         <x:v>-0.0004637788702346324</x:v>
       </x:c>
@@ -24785,7 +25201,9 @@
       <x:c r="G105" s="24" t="n">
         <x:v>8738.6</x:v>
       </x:c>
-      <x:c r="H105" s="24"/>
+      <x:c r="H105" s="24" t="n">
+        <x:v>117.8</x:v>
+      </x:c>
       <x:c r="I105" s="25" t="n">
         <x:v>0.013664625092798977</x:v>
       </x:c>
@@ -24819,7 +25237,9 @@
       <x:c r="G106" s="24" t="n">
         <x:v>8695.4</x:v>
       </x:c>
-      <x:c r="H106" s="24"/>
+      <x:c r="H106" s="24" t="n">
+        <x:v>-43.2</x:v>
+      </x:c>
       <x:c r="I106" s="25" t="n">
         <x:v>-0.004943583640400151</x:v>
       </x:c>
@@ -24853,7 +25273,9 @@
       <x:c r="G107" s="24" t="n">
         <x:v>8850.2</x:v>
       </x:c>
-      <x:c r="H107" s="24"/>
+      <x:c r="H107" s="27" t="n">
+        <x:v>154.8</x:v>
+      </x:c>
       <x:c r="I107" s="25" t="n">
         <x:v>0.017802516272972024</x:v>
       </x:c>
@@ -24887,7 +25309,9 @@
       <x:c r="G108" s="24" t="n">
         <x:v>8608</x:v>
       </x:c>
-      <x:c r="H108" s="24"/>
+      <x:c r="H108" s="27" t="n">
+        <x:v>-242.2</x:v>
+      </x:c>
       <x:c r="I108" s="25" t="n">
         <x:v>-0.027366613183882893</x:v>
       </x:c>
@@ -24921,7 +25345,9 @@
       <x:c r="G109" s="34" t="n">
         <x:v>8448.8</x:v>
       </x:c>
-      <x:c r="H109" s="34"/>
+      <x:c r="H109" s="27" t="n">
+        <x:v>-159.2</x:v>
+      </x:c>
       <x:c r="I109" s="35" t="n">
         <x:v>-0.018494423791821646</x:v>
       </x:c>
@@ -24955,7 +25381,9 @@
       <x:c r="G110" s="24" t="n">
         <x:v>8479.2</x:v>
       </x:c>
-      <x:c r="H110" s="24"/>
+      <x:c r="H110" s="24" t="n">
+        <x:v>30.4</x:v>
+      </x:c>
       <x:c r="I110" s="25" t="n">
         <x:v>0.0035981441151407</x:v>
       </x:c>
@@ -24989,7 +25417,9 @@
       <x:c r="G111" s="24" t="n">
         <x:v>8535.2</x:v>
       </x:c>
-      <x:c r="H111" s="24"/>
+      <x:c r="H111" s="24" t="n">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="I111" s="25" t="n">
         <x:v>0.006604396641192611</x:v>
       </x:c>
@@ -25023,7 +25453,9 @@
       <x:c r="G112" s="24" t="n">
         <x:v>8573.8</x:v>
       </x:c>
-      <x:c r="H112" s="24"/>
+      <x:c r="H112" s="24" t="n">
+        <x:v>38.6</x:v>
+      </x:c>
       <x:c r="I112" s="25" t="n">
         <x:v>0.004522448214453023</x:v>
       </x:c>
@@ -25057,7 +25489,9 @@
       <x:c r="G113" s="24" t="n">
         <x:v>8326.8</x:v>
       </x:c>
-      <x:c r="H113" s="24"/>
+      <x:c r="H113" s="27" t="n">
+        <x:v>-247</x:v>
+      </x:c>
       <x:c r="I113" s="25" t="n">
         <x:v>-0.02880869626070126</x:v>
       </x:c>
@@ -25091,7 +25525,9 @@
       <x:c r="G114" s="24" t="n">
         <x:v>8469.2</x:v>
       </x:c>
-      <x:c r="H114" s="24"/>
+      <x:c r="H114" s="24" t="n">
+        <x:v>142.4</x:v>
+      </x:c>
       <x:c r="I114" s="25" t="n">
         <x:v>0.01710140750348299</x:v>
       </x:c>
@@ -25125,7 +25561,9 @@
       <x:c r="G115" s="24" t="n">
         <x:v>8582.8</x:v>
       </x:c>
-      <x:c r="H115" s="24"/>
+      <x:c r="H115" s="24" t="n">
+        <x:v>113.6</x:v>
+      </x:c>
       <x:c r="I115" s="25" t="n">
         <x:v>0.013413309403485396</x:v>
       </x:c>
@@ -25159,7 +25597,9 @@
       <x:c r="G116" s="24" t="n">
         <x:v>8565</x:v>
       </x:c>
-      <x:c r="H116" s="24"/>
+      <x:c r="H116" s="24" t="n">
+        <x:v>-17.8</x:v>
+      </x:c>
       <x:c r="I116" s="25" t="n">
         <x:v>-0.0020739152724051912</x:v>
       </x:c>
@@ -25193,7 +25633,9 @@
       <x:c r="G117" s="24" t="n">
         <x:v>8415.8</x:v>
       </x:c>
-      <x:c r="H117" s="24"/>
+      <x:c r="H117" s="24" t="n">
+        <x:v>-149.2</x:v>
+      </x:c>
       <x:c r="I117" s="25" t="n">
         <x:v>-0.017419731465265653</x:v>
       </x:c>
@@ -25227,7 +25669,9 @@
       <x:c r="G118" s="24" t="n">
         <x:v>8458</x:v>
       </x:c>
-      <x:c r="H118" s="24"/>
+      <x:c r="H118" s="24" t="n">
+        <x:v>42.2</x:v>
+      </x:c>
       <x:c r="I118" s="25" t="n">
         <x:v>0.005014377718101759</x:v>
       </x:c>
@@ -25261,7 +25705,9 @@
       <x:c r="G119" s="24" t="n">
         <x:v>8274.6</x:v>
       </x:c>
-      <x:c r="H119" s="24"/>
+      <x:c r="H119" s="27" t="n">
+        <x:v>-183.4</x:v>
+      </x:c>
       <x:c r="I119" s="25" t="n">
         <x:v>-0.02168361314731615</x:v>
       </x:c>
@@ -25383,7 +25829,9 @@
       <x:c r="G125" s="24" t="n">
         <x:v>8225.2</x:v>
       </x:c>
-      <x:c r="H125" s="24"/>
+      <x:c r="H125" s="24" t="n">
+        <x:v>-49.4</x:v>
+      </x:c>
       <x:c r="I125" s="25" t="n">
         <x:v>-0.005970077103424898</x:v>
       </x:c>
@@ -25417,7 +25865,9 @@
       <x:c r="G126" s="24" t="n">
         <x:v>8260.4</x:v>
       </x:c>
-      <x:c r="H126" s="24"/>
+      <x:c r="H126" s="24" t="n">
+        <x:v>35.2</x:v>
+      </x:c>
       <x:c r="I126" s="25" t="n">
         <x:v>0.004279531196809572</x:v>
       </x:c>
@@ -25451,7 +25901,9 @@
       <x:c r="G127" s="24" t="n">
         <x:v>8314.2</x:v>
       </x:c>
-      <x:c r="H127" s="24"/>
+      <x:c r="H127" s="24" t="n">
+        <x:v>53.8</x:v>
+      </x:c>
       <x:c r="I127" s="25" t="n">
         <x:v>0.006513001791681017</x:v>
       </x:c>
@@ -25485,7 +25937,9 @@
       <x:c r="G128" s="24" t="n">
         <x:v>8300.2</x:v>
       </x:c>
-      <x:c r="H128" s="24"/>
+      <x:c r="H128" s="24" t="n">
+        <x:v>-14</x:v>
+      </x:c>
       <x:c r="I128" s="25" t="n">
         <x:v>-0.0016838661566958013</x:v>
       </x:c>
@@ -25519,7 +25973,9 @@
       <x:c r="G129" s="24" t="n">
         <x:v>8190.6</x:v>
       </x:c>
-      <x:c r="H129" s="24"/>
+      <x:c r="H129" s="24" t="n">
+        <x:v>-109.6</x:v>
+      </x:c>
       <x:c r="I129" s="25" t="n">
         <x:v>-0.013204501096359178</x:v>
       </x:c>
@@ -25553,7 +26009,9 @@
       <x:c r="G130" s="24" t="n">
         <x:v>7935</x:v>
       </x:c>
-      <x:c r="H130" s="24"/>
+      <x:c r="H130" s="27" t="n">
+        <x:v>-255.6</x:v>
+      </x:c>
       <x:c r="I130" s="25" t="n">
         <x:v>-0.031206505017947417</x:v>
       </x:c>
@@ -25587,7 +26045,9 @@
       <x:c r="G131" s="24" t="n">
         <x:v>8112.4</x:v>
       </x:c>
-      <x:c r="H131" s="24"/>
+      <x:c r="H131" s="27" t="n">
+        <x:v>177.4</x:v>
+      </x:c>
       <x:c r="I131" s="25" t="n">
         <x:v>0.022356647763075</x:v>
       </x:c>
@@ -25621,7 +26081,9 @@
       <x:c r="G132" s="24" t="n">
         <x:v>8024.2</x:v>
       </x:c>
-      <x:c r="H132" s="24"/>
+      <x:c r="H132" s="24" t="n">
+        <x:v>-88.2</x:v>
+      </x:c>
       <x:c r="I132" s="25" t="n">
         <x:v>-0.010872244958335386</x:v>
       </x:c>
@@ -25655,7 +26117,9 @@
       <x:c r="G133" s="24" t="n">
         <x:v>7990.8</x:v>
       </x:c>
-      <x:c r="H133" s="24"/>
+      <x:c r="H133" s="24" t="n">
+        <x:v>-33.4</x:v>
+      </x:c>
       <x:c r="I133" s="25" t="n">
         <x:v>-0.0041624087136411525</x:v>
       </x:c>
@@ -25689,7 +26153,9 @@
       <x:c r="G134" s="24" t="n">
         <x:v>8117.2</x:v>
       </x:c>
-      <x:c r="H134" s="24"/>
+      <x:c r="H134" s="24" t="n">
+        <x:v>126.4</x:v>
+      </x:c>
       <x:c r="I134" s="25" t="n">
         <x:v>0.015818190919557384</x:v>
       </x:c>
@@ -25723,9 +26189,11 @@
       <x:c r="G135" s="24" t="n">
         <x:v>8384.8</x:v>
       </x:c>
-      <x:c r="H135" s="24"/>
+      <x:c r="H135" s="27" t="n">
+        <x:v>267.6</x:v>
+      </x:c>
       <x:c r="I135" s="25" t="n">
-        <x:v>0.011013650027102972</x:v>
+        <x:v>0.03296703296703285</x:v>
       </x:c>
       <x:c r="J135" s="29" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
@@ -25757,9 +26225,11 @@
       <x:c r="G136" s="24" t="n">
         <x:v>8475.8</x:v>
       </x:c>
-      <x:c r="H136" s="24"/>
+      <x:c r="H136" s="24" t="n">
+        <x:v>91</x:v>
+      </x:c>
       <x:c r="I136" s="25" t="n">
-        <x:v>0.008700314381107743</x:v>
+        <x:v>0.010852972044652187</x:v>
       </x:c>
       <x:c r="J136" s="29" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -25791,9 +26261,11 @@
       <x:c r="G137" s="24" t="n">
         <x:v>8613.2</x:v>
       </x:c>
-      <x:c r="H137" s="24"/>
+      <x:c r="H137" s="24" t="n">
+        <x:v>137.4</x:v>
+      </x:c>
       <x:c r="I137" s="25" t="n">
-        <x:v>0.018241121043730324</x:v>
+        <x:v>0.01621085915193854</x:v>
       </x:c>
       <x:c r="J137" s="29" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -25825,9 +26297,11 @@
       <x:c r="G138" s="24" t="n">
         <x:v>8682.8</x:v>
       </x:c>
-      <x:c r="H138" s="24"/>
+      <x:c r="H138" s="24" t="n">
+        <x:v>69.6</x:v>
+      </x:c>
       <x:c r="I138" s="25" t="n">
-        <x:v>0.010487602325305545</x:v>
+        <x:v>0.008080620443040809</x:v>
       </x:c>
       <x:c r="J138" s="24" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -25859,9 +26333,11 @@
       <x:c r="G139" s="34" t="n">
         <x:v>8650</x:v>
       </x:c>
-      <x:c r="H139" s="34"/>
+      <x:c r="H139" s="34" t="n">
+        <x:v>-32.8</x:v>
+      </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.015568131119825246</x:v>
+        <x:v>-0.003777583268070095</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -25893,7 +26369,9 @@
       <x:c r="G140" s="24" t="n">
         <x:v>8455</x:v>
       </x:c>
-      <x:c r="H140" s="24"/>
+      <x:c r="H140" s="27" t="n">
+        <x:v>-195</x:v>
+      </x:c>
       <x:c r="I140" s="25" t="n">
         <x:v>-0.02254335260115603</x:v>
       </x:c>
@@ -25927,7 +26405,9 @@
       <x:c r="G141" s="24" t="n">
         <x:v>8595</x:v>
       </x:c>
-      <x:c r="H141" s="24"/>
+      <x:c r="H141" s="24" t="n">
+        <x:v>140</x:v>
+      </x:c>
       <x:c r="I141" s="25" t="n">
         <x:v>0.016558249556475557</x:v>
       </x:c>
@@ -25961,7 +26441,9 @@
       <x:c r="G142" s="24" t="n">
         <x:v>8699.4</x:v>
       </x:c>
-      <x:c r="H142" s="24"/>
+      <x:c r="H142" s="24" t="n">
+        <x:v>104.4</x:v>
+      </x:c>
       <x:c r="I142" s="25" t="n">
         <x:v>0.012146596858638725</x:v>
       </x:c>
@@ -25995,7 +26477,9 @@
       <x:c r="G143" s="24" t="n">
         <x:v>8447</x:v>
       </x:c>
-      <x:c r="H143" s="24"/>
+      <x:c r="H143" s="27" t="n">
+        <x:v>-252.4</x:v>
+      </x:c>
       <x:c r="I143" s="25" t="n">
         <x:v>-0.029013495183575877</x:v>
       </x:c>
@@ -26029,7 +26513,9 @@
       <x:c r="G144" s="24" t="n">
         <x:v>8537.6</x:v>
       </x:c>
-      <x:c r="H144" s="24"/>
+      <x:c r="H144" s="24" t="n">
+        <x:v>90.6</x:v>
+      </x:c>
       <x:c r="I144" s="25" t="n">
         <x:v>0.010725701432461321</x:v>
       </x:c>
@@ -26063,7 +26549,9 @@
       <x:c r="G145" s="24" t="n">
         <x:v>8783</x:v>
       </x:c>
-      <x:c r="H145" s="24"/>
+      <x:c r="H145" s="27" t="n">
+        <x:v>245.4</x:v>
+      </x:c>
       <x:c r="I145" s="25" t="n">
         <x:v>0.028743440779610108</x:v>
       </x:c>
@@ -26185,7 +26673,9 @@
       <x:c r="G151" s="24" t="n">
         <x:v>8713</x:v>
       </x:c>
-      <x:c r="H151" s="24"/>
+      <x:c r="H151" s="24" t="n">
+        <x:v>-70</x:v>
+      </x:c>
       <x:c r="I151" s="25" t="n">
         <x:v>-0.007969941933280156</x:v>
       </x:c>
@@ -26219,7 +26709,9 @@
       <x:c r="G152" s="24" t="n">
         <x:v>8488</x:v>
       </x:c>
-      <x:c r="H152" s="24"/>
+      <x:c r="H152" s="27" t="n">
+        <x:v>-225</x:v>
+      </x:c>
       <x:c r="I152" s="25" t="n">
         <x:v>-0.025823482153104593</x:v>
       </x:c>
@@ -26253,7 +26745,9 @@
       <x:c r="G153" s="24" t="n">
         <x:v>8538</x:v>
       </x:c>
-      <x:c r="H153" s="24"/>
+      <x:c r="H153" s="24" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="I153" s="25" t="n">
         <x:v>0.005890669180018904</x:v>
       </x:c>
@@ -26287,7 +26781,9 @@
       <x:c r="G154" s="24" t="n">
         <x:v>8467</x:v>
       </x:c>
-      <x:c r="H154" s="24"/>
+      <x:c r="H154" s="24" t="n">
+        <x:v>-71</x:v>
+      </x:c>
       <x:c r="I154" s="25" t="n">
         <x:v>-0.008315764816116178</x:v>
       </x:c>
@@ -26321,7 +26817,9 @@
       <x:c r="G155" s="24" t="n">
         <x:v>8322.6</x:v>
       </x:c>
-      <x:c r="H155" s="24"/>
+      <x:c r="H155" s="24" t="n">
+        <x:v>-144.4</x:v>
+      </x:c>
       <x:c r="I155" s="25" t="n">
         <x:v>-0.01705444667532774</x:v>
       </x:c>
@@ -26355,7 +26853,9 @@
       <x:c r="G156" s="24" t="n">
         <x:v>8255.2</x:v>
       </x:c>
-      <x:c r="H156" s="24"/>
+      <x:c r="H156" s="24" t="n">
+        <x:v>-67.4</x:v>
+      </x:c>
       <x:c r="I156" s="25" t="n">
         <x:v>-0.008098430778843091</x:v>
       </x:c>
@@ -26389,7 +26889,9 @@
       <x:c r="G157" s="24" t="n">
         <x:v>8502.4</x:v>
       </x:c>
-      <x:c r="H157" s="24"/>
+      <x:c r="H157" s="27" t="n">
+        <x:v>247.2</x:v>
+      </x:c>
       <x:c r="I157" s="25" t="n">
         <x:v>0.029944762089349597</x:v>
       </x:c>
@@ -26423,7 +26925,9 @@
       <x:c r="G158" s="24" t="n">
         <x:v>8333</x:v>
       </x:c>
-      <x:c r="H158" s="24"/>
+      <x:c r="H158" s="27" t="n">
+        <x:v>-169.4</x:v>
+      </x:c>
       <x:c r="I158" s="25" t="n">
         <x:v>-0.019923786225065854</x:v>
       </x:c>
@@ -26457,7 +26961,9 @@
       <x:c r="G159" s="24" t="n">
         <x:v>8021.6</x:v>
       </x:c>
-      <x:c r="H159" s="24"/>
+      <x:c r="H159" s="27" t="n">
+        <x:v>-311.4</x:v>
+      </x:c>
       <x:c r="I159" s="25" t="n">
         <x:v>-0.037369494779791124</x:v>
       </x:c>
@@ -26491,7 +26997,9 @@
       <x:c r="G160" s="24" t="n">
         <x:v>8117</x:v>
       </x:c>
-      <x:c r="H160" s="24"/>
+      <x:c r="H160" s="24" t="n">
+        <x:v>95.4</x:v>
+      </x:c>
       <x:c r="I160" s="25" t="n">
         <x:v>0.011892889199162315</x:v>
       </x:c>
@@ -26525,7 +27033,9 @@
       <x:c r="G161" s="24" t="n">
         <x:v>8046.4</x:v>
       </x:c>
-      <x:c r="H161" s="24"/>
+      <x:c r="H161" s="24" t="n">
+        <x:v>-70.6</x:v>
+      </x:c>
       <x:c r="I161" s="25" t="n">
         <x:v>-0.008697794751755583</x:v>
       </x:c>
@@ -26559,7 +27069,9 @@
       <x:c r="G162" s="24" t="n">
         <x:v>7869.6</x:v>
       </x:c>
-      <x:c r="H162" s="24"/>
+      <x:c r="H162" s="27" t="n">
+        <x:v>-176.8</x:v>
+      </x:c>
       <x:c r="I162" s="25" t="n">
         <x:v>-0.021972559156890004</x:v>
       </x:c>
@@ -26718,7 +27230,9 @@
       <x:c r="G5" s="24" t="n">
         <x:v>4697</x:v>
       </x:c>
-      <x:c r="H5" s="24"/>
+      <x:c r="H5" s="24" t="n">
+        <x:v>97.2</x:v>
+      </x:c>
       <x:c r="I5" s="25" t="n">
         <x:v>0.021131353537110265</x:v>
       </x:c>
@@ -26752,7 +27266,9 @@
       <x:c r="G6" s="24" t="n">
         <x:v>4778</x:v>
       </x:c>
-      <x:c r="H6" s="24"/>
+      <x:c r="H6" s="24" t="n">
+        <x:v>81</x:v>
+      </x:c>
       <x:c r="I6" s="25" t="n">
         <x:v>0.017245050031935216</x:v>
       </x:c>
@@ -26786,7 +27302,9 @@
       <x:c r="G7" s="24" t="n">
         <x:v>4753</x:v>
       </x:c>
-      <x:c r="H7" s="24"/>
+      <x:c r="H7" s="24" t="n">
+        <x:v>-25</x:v>
+      </x:c>
       <x:c r="I7" s="25" t="n">
         <x:v>-0.005232314776056901</x:v>
       </x:c>
@@ -26820,7 +27338,9 @@
       <x:c r="G8" s="24" t="n">
         <x:v>4718.4</x:v>
       </x:c>
-      <x:c r="H8" s="24"/>
+      <x:c r="H8" s="24" t="n">
+        <x:v>-34.6</x:v>
+      </x:c>
       <x:c r="I8" s="25" t="n">
         <x:v>-0.007279612876078367</x:v>
       </x:c>
@@ -26854,7 +27374,9 @@
       <x:c r="G9" s="24" t="n">
         <x:v>4743.8</x:v>
       </x:c>
-      <x:c r="H9" s="24"/>
+      <x:c r="H9" s="24" t="n">
+        <x:v>25.4</x:v>
+      </x:c>
       <x:c r="I9" s="25" t="n">
         <x:v>0.005383180739233717</x:v>
       </x:c>
@@ -26888,7 +27410,9 @@
       <x:c r="G10" s="24" t="n">
         <x:v>4774</x:v>
       </x:c>
-      <x:c r="H10" s="24"/>
+      <x:c r="H10" s="24" t="n">
+        <x:v>30.2</x:v>
+      </x:c>
       <x:c r="I10" s="25" t="n">
         <x:v>0.006366204308781986</x:v>
       </x:c>
@@ -26922,7 +27446,9 @@
       <x:c r="G11" s="24" t="n">
         <x:v>4758.6</x:v>
       </x:c>
-      <x:c r="H11" s="24"/>
+      <x:c r="H11" s="24" t="n">
+        <x:v>-15.4</x:v>
+      </x:c>
       <x:c r="I11" s="25" t="n">
         <x:v>-0.003225806451612856</x:v>
       </x:c>
@@ -26956,7 +27482,9 @@
       <x:c r="G12" s="24" t="n">
         <x:v>4740</x:v>
       </x:c>
-      <x:c r="H12" s="24"/>
+      <x:c r="H12" s="24" t="n">
+        <x:v>-18.6</x:v>
+      </x:c>
       <x:c r="I12" s="25" t="n">
         <x:v>-0.003908712646576773</x:v>
       </x:c>
@@ -26990,7 +27518,9 @@
       <x:c r="G13" s="24" t="n">
         <x:v>4746.6</x:v>
       </x:c>
-      <x:c r="H13" s="24"/>
+      <x:c r="H13" s="24" t="n">
+        <x:v>6.6</x:v>
+      </x:c>
       <x:c r="I13" s="25" t="n">
         <x:v>0.001392405063291191</x:v>
       </x:c>
@@ -27024,7 +27554,9 @@
       <x:c r="G14" s="34" t="n">
         <x:v>4723.2</x:v>
       </x:c>
-      <x:c r="H14" s="34"/>
+      <x:c r="H14" s="34" t="n">
+        <x:v>-23.4</x:v>
+      </x:c>
       <x:c r="I14" s="35" t="n">
         <x:v>-0.004929844520288329</x:v>
       </x:c>
@@ -27058,7 +27590,9 @@
       <x:c r="G15" s="24" t="n">
         <x:v>4728.6</x:v>
       </x:c>
-      <x:c r="H15" s="24"/>
+      <x:c r="H15" s="24" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
       <x:c r="I15" s="25" t="n">
         <x:v>0.0011432926829268997</x:v>
       </x:c>
@@ -27092,7 +27626,9 @@
       <x:c r="G16" s="24" t="n">
         <x:v>4708.6</x:v>
       </x:c>
-      <x:c r="H16" s="24"/>
+      <x:c r="H16" s="24" t="n">
+        <x:v>-20</x:v>
+      </x:c>
       <x:c r="I16" s="25" t="n">
         <x:v>-0.004229581694370377</x:v>
       </x:c>
@@ -27126,7 +27662,9 @@
       <x:c r="G17" s="24" t="n">
         <x:v>4722.8</x:v>
       </x:c>
-      <x:c r="H17" s="24"/>
+      <x:c r="H17" s="24" t="n">
+        <x:v>14.2</x:v>
+      </x:c>
       <x:c r="I17" s="25" t="n">
         <x:v>0.003015758399524282</x:v>
       </x:c>
@@ -27160,7 +27698,9 @@
       <x:c r="G18" s="24" t="n">
         <x:v>4719.4</x:v>
       </x:c>
-      <x:c r="H18" s="24"/>
+      <x:c r="H18" s="24" t="n">
+        <x:v>-3.4</x:v>
+      </x:c>
       <x:c r="I18" s="25" t="n">
         <x:v>-0.0007199119166597656</x:v>
       </x:c>
@@ -27194,7 +27734,9 @@
       <x:c r="G19" s="24" t="n">
         <x:v>4709.2</x:v>
       </x:c>
-      <x:c r="H19" s="24"/>
+      <x:c r="H19" s="24" t="n">
+        <x:v>-10.2</x:v>
+      </x:c>
       <x:c r="I19" s="25" t="n">
         <x:v>-0.002161291689621536</x:v>
       </x:c>
@@ -27228,7 +27770,9 @@
       <x:c r="G20" s="24" t="n">
         <x:v>4719.4</x:v>
       </x:c>
-      <x:c r="H20" s="24"/>
+      <x:c r="H20" s="24" t="n">
+        <x:v>10.2</x:v>
+      </x:c>
       <x:c r="I20" s="25" t="n">
         <x:v>0.0021659729890426416</x:v>
       </x:c>
@@ -27262,7 +27806,9 @@
       <x:c r="G21" s="24" t="n">
         <x:v>4718.2</x:v>
       </x:c>
-      <x:c r="H21" s="24"/>
+      <x:c r="H21" s="24" t="n">
+        <x:v>-1.2</x:v>
+      </x:c>
       <x:c r="I21" s="25" t="n">
         <x:v>-0.00025426961054364483</x:v>
       </x:c>
@@ -27296,7 +27842,9 @@
       <x:c r="G22" s="24" t="n">
         <x:v>4732.8</x:v>
       </x:c>
-      <x:c r="H22" s="24"/>
+      <x:c r="H22" s="24" t="n">
+        <x:v>14.6</x:v>
+      </x:c>
       <x:c r="I22" s="25" t="n">
         <x:v>0.003094400406934872</x:v>
       </x:c>
@@ -27330,7 +27878,9 @@
       <x:c r="G23" s="24" t="n">
         <x:v>4784</x:v>
       </x:c>
-      <x:c r="H23" s="24"/>
+      <x:c r="H23" s="24" t="n">
+        <x:v>51.2</x:v>
+      </x:c>
       <x:c r="I23" s="25" t="n">
         <x:v>0.010818120351588911</x:v>
       </x:c>
@@ -27364,7 +27914,9 @@
       <x:c r="G24" s="24" t="n">
         <x:v>4711</x:v>
       </x:c>
-      <x:c r="H24" s="24"/>
+      <x:c r="H24" s="24" t="n">
+        <x:v>-73</x:v>
+      </x:c>
       <x:c r="I24" s="25" t="n">
         <x:v>-0.01525919732441472</x:v>
       </x:c>
@@ -27486,7 +28038,9 @@
       <x:c r="G30" s="24" t="n">
         <x:v>4577.4</x:v>
       </x:c>
-      <x:c r="H30" s="24"/>
+      <x:c r="H30" s="24" t="n">
+        <x:v>-133.6</x:v>
+      </x:c>
       <x:c r="I30" s="25" t="n">
         <x:v>-0.028359159414137247</x:v>
       </x:c>
@@ -27520,7 +28074,9 @@
       <x:c r="G31" s="24" t="n">
         <x:v>4653</x:v>
       </x:c>
-      <x:c r="H31" s="24"/>
+      <x:c r="H31" s="24" t="n">
+        <x:v>75.6</x:v>
+      </x:c>
       <x:c r="I31" s="25" t="n">
         <x:v>0.016515926071569043</x:v>
       </x:c>
@@ -27554,7 +28110,9 @@
       <x:c r="G32" s="24" t="n">
         <x:v>4693.6</x:v>
       </x:c>
-      <x:c r="H32" s="24"/>
+      <x:c r="H32" s="24" t="n">
+        <x:v>40.6</x:v>
+      </x:c>
       <x:c r="I32" s="25" t="n">
         <x:v>0.008725553406404574</x:v>
       </x:c>
@@ -27588,7 +28146,9 @@
       <x:c r="G33" s="24" t="n">
         <x:v>4665.2</x:v>
       </x:c>
-      <x:c r="H33" s="24"/>
+      <x:c r="H33" s="24" t="n">
+        <x:v>-28.4</x:v>
+      </x:c>
       <x:c r="I33" s="25" t="n">
         <x:v>-0.006050792568604191</x:v>
       </x:c>
@@ -27622,7 +28182,9 @@
       <x:c r="G34" s="24" t="n">
         <x:v>4637.6</x:v>
       </x:c>
-      <x:c r="H34" s="24"/>
+      <x:c r="H34" s="24" t="n">
+        <x:v>-27.6</x:v>
+      </x:c>
       <x:c r="I34" s="25" t="n">
         <x:v>-0.005916145074166046</x:v>
       </x:c>
@@ -27656,7 +28218,9 @@
       <x:c r="G35" s="24" t="n">
         <x:v>4721.2</x:v>
       </x:c>
-      <x:c r="H35" s="24"/>
+      <x:c r="H35" s="24" t="n">
+        <x:v>83.6</x:v>
+      </x:c>
       <x:c r="I35" s="25" t="n">
         <x:v>0.01802656546489545</x:v>
       </x:c>
@@ -27690,7 +28254,9 @@
       <x:c r="G36" s="24" t="n">
         <x:v>4724</x:v>
       </x:c>
-      <x:c r="H36" s="24"/>
+      <x:c r="H36" s="24" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
       <x:c r="I36" s="25" t="n">
         <x:v>0.000593069558586734</x:v>
       </x:c>
@@ -27724,7 +28290,9 @@
       <x:c r="G37" s="24" t="n">
         <x:v>4714.8</x:v>
       </x:c>
-      <x:c r="H37" s="24"/>
+      <x:c r="H37" s="24" t="n">
+        <x:v>-9.2</x:v>
+      </x:c>
       <x:c r="I37" s="25" t="n">
         <x:v>-0.0019475021168501305</x:v>
       </x:c>
@@ -27758,7 +28326,9 @@
       <x:c r="G38" s="24" t="n">
         <x:v>4716.8</x:v>
       </x:c>
-      <x:c r="H38" s="24"/>
+      <x:c r="H38" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I38" s="25" t="n">
         <x:v>0.0004241961482989165</x:v>
       </x:c>
@@ -27792,7 +28362,9 @@
       <x:c r="G39" s="24" t="n">
         <x:v>4627</x:v>
       </x:c>
-      <x:c r="H39" s="24"/>
+      <x:c r="H39" s="24" t="n">
+        <x:v>-89.8</x:v>
+      </x:c>
       <x:c r="I39" s="25" t="n">
         <x:v>-0.019038331071913217</x:v>
       </x:c>
@@ -27826,7 +28398,9 @@
       <x:c r="G40" s="34" t="n">
         <x:v>4683.4</x:v>
       </x:c>
-      <x:c r="H40" s="34"/>
+      <x:c r="H40" s="34" t="n">
+        <x:v>56.4</x:v>
+      </x:c>
       <x:c r="I40" s="35" t="n">
         <x:v>0.012189323535768182</x:v>
       </x:c>
@@ -27860,7 +28434,9 @@
       <x:c r="G41" s="24" t="n">
         <x:v>4731.4</x:v>
       </x:c>
-      <x:c r="H41" s="24"/>
+      <x:c r="H41" s="24" t="n">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="I41" s="25" t="n">
         <x:v>0.010248964427552743</x:v>
       </x:c>
@@ -27894,7 +28470,9 @@
       <x:c r="G42" s="24" t="n">
         <x:v>4712.2</x:v>
       </x:c>
-      <x:c r="H42" s="24"/>
+      <x:c r="H42" s="24" t="n">
+        <x:v>-19.2</x:v>
+      </x:c>
       <x:c r="I42" s="25" t="n">
         <x:v>-0.004057995519296531</x:v>
       </x:c>
@@ -27928,7 +28506,9 @@
       <x:c r="G43" s="24" t="n">
         <x:v>4713.8</x:v>
       </x:c>
-      <x:c r="H43" s="24"/>
+      <x:c r="H43" s="24" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
       <x:c r="I43" s="25" t="n">
         <x:v>0.00033954416196269044</x:v>
       </x:c>
@@ -28050,7 +28630,9 @@
       <x:c r="G49" s="24" t="n">
         <x:v>4711.2</x:v>
       </x:c>
-      <x:c r="H49" s="24"/>
+      <x:c r="H49" s="24" t="n">
+        <x:v>-2.6</x:v>
+      </x:c>
       <x:c r="I49" s="25" t="n">
         <x:v>-0.0005515719801434393</x:v>
       </x:c>
@@ -28084,7 +28666,9 @@
       <x:c r="G50" s="24" t="n">
         <x:v>4651.4</x:v>
       </x:c>
-      <x:c r="H50" s="24"/>
+      <x:c r="H50" s="24" t="n">
+        <x:v>-59.8</x:v>
+      </x:c>
       <x:c r="I50" s="25" t="n">
         <x:v>-0.012693156732891842</x:v>
       </x:c>
@@ -28118,7 +28702,9 @@
       <x:c r="G51" s="24" t="n">
         <x:v>4591</x:v>
       </x:c>
-      <x:c r="H51" s="24"/>
+      <x:c r="H51" s="24" t="n">
+        <x:v>-60.4</x:v>
+      </x:c>
       <x:c r="I51" s="25" t="n">
         <x:v>-0.012985337747774772</x:v>
       </x:c>
@@ -28152,7 +28738,9 @@
       <x:c r="G52" s="24" t="n">
         <x:v>4629</x:v>
       </x:c>
-      <x:c r="H52" s="24"/>
+      <x:c r="H52" s="24" t="n">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="I52" s="25" t="n">
         <x:v>0.008277063820518515</x:v>
       </x:c>
@@ -28186,7 +28774,9 @@
       <x:c r="G53" s="24" t="n">
         <x:v>4646</x:v>
       </x:c>
-      <x:c r="H53" s="24"/>
+      <x:c r="H53" s="24" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="I53" s="25" t="n">
         <x:v>0.003672499459926648</x:v>
       </x:c>
@@ -28220,7 +28810,9 @@
       <x:c r="G54" s="24" t="n">
         <x:v>4599.2</x:v>
       </x:c>
-      <x:c r="H54" s="24"/>
+      <x:c r="H54" s="24" t="n">
+        <x:v>-46.8</x:v>
+      </x:c>
       <x:c r="I54" s="25" t="n">
         <x:v>-0.010073181231166628</x:v>
       </x:c>
@@ -28254,7 +28846,9 @@
       <x:c r="G55" s="24" t="n">
         <x:v>4664</x:v>
       </x:c>
-      <x:c r="H55" s="24"/>
+      <x:c r="H55" s="24" t="n">
+        <x:v>64.8</x:v>
+      </x:c>
       <x:c r="I55" s="25" t="n">
         <x:v>0.014089406853365904</x:v>
       </x:c>
@@ -28288,7 +28882,9 @@
       <x:c r="G56" s="24" t="n">
         <x:v>4687</x:v>
       </x:c>
-      <x:c r="H56" s="24"/>
+      <x:c r="H56" s="24" t="n">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="I56" s="25" t="n">
         <x:v>0.004931389365351535</x:v>
       </x:c>
@@ -28322,7 +28918,9 @@
       <x:c r="G57" s="24" t="n">
         <x:v>4658.4</x:v>
       </x:c>
-      <x:c r="H57" s="24"/>
+      <x:c r="H57" s="24" t="n">
+        <x:v>-28.6</x:v>
+      </x:c>
       <x:c r="I57" s="25" t="n">
         <x:v>-0.006101984211649314</x:v>
       </x:c>
@@ -28356,9 +28954,11 @@
       <x:c r="G58" s="24" t="n">
         <x:v>4658</x:v>
       </x:c>
-      <x:c r="H58" s="24"/>
+      <x:c r="H58" s="24" t="n">
+        <x:v>-0.4</x:v>
+      </x:c>
       <x:c r="I58" s="25" t="n">
-        <x:v>-0.016057015284217657</x:v>
+        <x:v>-0.00008586639189411827</x:v>
       </x:c>
       <x:c r="J58" s="24" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
@@ -28390,9 +28990,11 @@
       <x:c r="G59" s="24" t="n">
         <x:v>4662.8</x:v>
       </x:c>
-      <x:c r="H59" s="24"/>
+      <x:c r="H59" s="24" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
       <x:c r="I59" s="25" t="n">
-        <x:v>0.0011781132734094424</x:v>
+        <x:v>0.0010304851867755094</x:v>
       </x:c>
       <x:c r="J59" s="24" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
@@ -28424,9 +29026,11 @@
       <x:c r="G60" s="24" t="n">
         <x:v>4628.8</x:v>
       </x:c>
-      <x:c r="H60" s="24"/>
+      <x:c r="H60" s="24" t="n">
+        <x:v>-34</x:v>
+      </x:c>
       <x:c r="I60" s="25" t="n">
-        <x:v>-0.0067988668555239995</x:v>
+        <x:v>-0.007291756026421847</x:v>
       </x:c>
       <x:c r="J60" s="29" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
@@ -28458,9 +29062,11 @@
       <x:c r="G61" s="24" t="n">
         <x:v>4651.4</x:v>
       </x:c>
-      <x:c r="H61" s="24"/>
+      <x:c r="H61" s="24" t="n">
+        <x:v>22.6</x:v>
+      </x:c>
       <x:c r="I61" s="25" t="n">
-        <x:v>0.0025889683619291226</x:v>
+        <x:v>0.004882474939509107</x:v>
       </x:c>
       <x:c r="J61" s="24" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -28492,9 +29098,11 @@
       <x:c r="G62" s="24" t="n">
         <x:v>4586.6</x:v>
       </x:c>
-      <x:c r="H62" s="24"/>
+      <x:c r="H62" s="24" t="n">
+        <x:v>-64.8</x:v>
+      </x:c>
       <x:c r="I62" s="25" t="n">
-        <x:v>-0.014749649859944092</x:v>
+        <x:v>-0.013931289504235167</x:v>
       </x:c>
       <x:c r="J62" s="24" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -28526,9 +29134,11 @@
       <x:c r="G63" s="34" t="n">
         <x:v>4596.8</x:v>
       </x:c>
-      <x:c r="H63" s="34"/>
+      <x:c r="H63" s="34" t="n">
+        <x:v>10.2</x:v>
+      </x:c>
       <x:c r="I63" s="35" t="n">
-        <x:v>-0.0035093954066901523</x:v>
+        <x:v>0.002223869532987255</x:v>
       </x:c>
       <x:c r="J63" s="34" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -28560,9 +29170,11 @@
       <x:c r="G64" s="24" t="n">
         <x:v>4344.4</x:v>
       </x:c>
-      <x:c r="H64" s="24"/>
+      <x:c r="H64" s="27" t="n">
+        <x:v>-252.4</x:v>
+      </x:c>
       <x:c r="I64" s="25" t="n">
-        <x:v>-0.03165121255349501</x:v>
+        <x:v>-0.05490776192133673</x:v>
       </x:c>
       <x:c r="J64" s="29" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -28594,7 +29206,9 @@
       <x:c r="G65" s="24" t="n">
         <x:v>4388.4</x:v>
       </x:c>
-      <x:c r="H65" s="24"/>
+      <x:c r="H65" s="24" t="n">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="I65" s="25" t="n">
         <x:v>0.01012798084890898</x:v>
       </x:c>
@@ -28628,7 +29242,9 @@
       <x:c r="G66" s="24" t="n">
         <x:v>4450</x:v>
       </x:c>
-      <x:c r="H66" s="24"/>
+      <x:c r="H66" s="24" t="n">
+        <x:v>61.6</x:v>
+      </x:c>
       <x:c r="I66" s="25" t="n">
         <x:v>0.014037006653905726</x:v>
       </x:c>
@@ -28662,7 +29278,9 @@
       <x:c r="G67" s="24" t="n">
         <x:v>4396</x:v>
       </x:c>
-      <x:c r="H67" s="24"/>
+      <x:c r="H67" s="24" t="n">
+        <x:v>-54</x:v>
+      </x:c>
       <x:c r="I67" s="25" t="n">
         <x:v>-0.012134831460674178</x:v>
       </x:c>
@@ -28696,7 +29314,9 @@
       <x:c r="G68" s="24" t="n">
         <x:v>4427.4</x:v>
       </x:c>
-      <x:c r="H68" s="24"/>
+      <x:c r="H68" s="24" t="n">
+        <x:v>31.4</x:v>
+      </x:c>
       <x:c r="I68" s="25" t="n">
         <x:v>0.0071428571428571175</x:v>
       </x:c>
@@ -28730,7 +29350,9 @@
       <x:c r="G69" s="24" t="n">
         <x:v>4414</x:v>
       </x:c>
-      <x:c r="H69" s="24"/>
+      <x:c r="H69" s="24" t="n">
+        <x:v>-13.4</x:v>
+      </x:c>
       <x:c r="I69" s="25" t="n">
         <x:v>-0.003026607037990625</x:v>
       </x:c>
@@ -28764,7 +29386,9 @@
       <x:c r="G70" s="24" t="n">
         <x:v>4375.8</x:v>
       </x:c>
-      <x:c r="H70" s="24"/>
+      <x:c r="H70" s="24" t="n">
+        <x:v>-38.2</x:v>
+      </x:c>
       <x:c r="I70" s="25" t="n">
         <x:v>-0.008654281830539179</x:v>
       </x:c>
@@ -28886,7 +29510,9 @@
       <x:c r="G76" s="24" t="n">
         <x:v>4448.2</x:v>
       </x:c>
-      <x:c r="H76" s="24"/>
+      <x:c r="H76" s="24" t="n">
+        <x:v>72.4</x:v>
+      </x:c>
       <x:c r="I76" s="25" t="n">
         <x:v>0.016545545957310503</x:v>
       </x:c>
@@ -28920,7 +29546,9 @@
       <x:c r="G77" s="24" t="n">
         <x:v>4390.2</x:v>
       </x:c>
-      <x:c r="H77" s="24"/>
+      <x:c r="H77" s="24" t="n">
+        <x:v>-58</x:v>
+      </x:c>
       <x:c r="I77" s="25" t="n">
         <x:v>-0.013038982060159188</x:v>
       </x:c>
@@ -28954,7 +29582,9 @@
       <x:c r="G78" s="24" t="n">
         <x:v>4362.2</x:v>
       </x:c>
-      <x:c r="H78" s="24"/>
+      <x:c r="H78" s="24" t="n">
+        <x:v>-28</x:v>
+      </x:c>
       <x:c r="I78" s="25" t="n">
         <x:v>-0.006377841556193364</x:v>
       </x:c>
@@ -28988,7 +29618,9 @@
       <x:c r="G79" s="24" t="n">
         <x:v>4360</x:v>
       </x:c>
-      <x:c r="H79" s="24"/>
+      <x:c r="H79" s="24" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
       <x:c r="I79" s="25" t="n">
         <x:v>-0.0005043326761725586</x:v>
       </x:c>
@@ -29022,7 +29654,9 @@
       <x:c r="G80" s="24" t="n">
         <x:v>4539.6</x:v>
       </x:c>
-      <x:c r="H80" s="24"/>
+      <x:c r="H80" s="27" t="n">
+        <x:v>179.6</x:v>
+      </x:c>
       <x:c r="I80" s="25" t="n">
         <x:v>0.04119266055045889</x:v>
       </x:c>
@@ -29056,7 +29690,9 @@
       <x:c r="G81" s="24" t="n">
         <x:v>4500</x:v>
       </x:c>
-      <x:c r="H81" s="24"/>
+      <x:c r="H81" s="24" t="n">
+        <x:v>-39.6</x:v>
+      </x:c>
       <x:c r="I81" s="25" t="n">
         <x:v>-0.008723235527359319</x:v>
       </x:c>
@@ -29090,7 +29726,9 @@
       <x:c r="G82" s="24" t="n">
         <x:v>4562</x:v>
       </x:c>
-      <x:c r="H82" s="24"/>
+      <x:c r="H82" s="24" t="n">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="I82" s="25" t="n">
         <x:v>0.013777777777777889</x:v>
       </x:c>
@@ -29124,7 +29762,9 @@
       <x:c r="G83" s="24" t="n">
         <x:v>4570.6</x:v>
       </x:c>
-      <x:c r="H83" s="24"/>
+      <x:c r="H83" s="24" t="n">
+        <x:v>8.6</x:v>
+      </x:c>
       <x:c r="I83" s="25" t="n">
         <x:v>0.0018851380973257115</x:v>
       </x:c>
@@ -29158,7 +29798,9 @@
       <x:c r="G84" s="24" t="n">
         <x:v>4639.6</x:v>
       </x:c>
-      <x:c r="H84" s="24"/>
+      <x:c r="H84" s="24" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="I84" s="25" t="n">
         <x:v>0.015096486238130646</x:v>
       </x:c>
@@ -29192,7 +29834,9 @@
       <x:c r="G85" s="24" t="n">
         <x:v>4625.2</x:v>
       </x:c>
-      <x:c r="H85" s="24"/>
+      <x:c r="H85" s="24" t="n">
+        <x:v>-14.4</x:v>
+      </x:c>
       <x:c r="I85" s="25" t="n">
         <x:v>-0.003103715837572296</x:v>
       </x:c>
@@ -29226,7 +29870,9 @@
       <x:c r="G86" s="24" t="n">
         <x:v>4677.8</x:v>
       </x:c>
-      <x:c r="H86" s="24"/>
+      <x:c r="H86" s="24" t="n">
+        <x:v>52.6</x:v>
+      </x:c>
       <x:c r="I86" s="25" t="n">
         <x:v>0.01137248119000267</x:v>
       </x:c>
@@ -29260,7 +29906,9 @@
       <x:c r="G87" s="34" t="n">
         <x:v>4667</x:v>
       </x:c>
-      <x:c r="H87" s="34"/>
+      <x:c r="H87" s="34" t="n">
+        <x:v>-10.8</x:v>
+      </x:c>
       <x:c r="I87" s="35" t="n">
         <x:v>-0.0023087776305100727</x:v>
       </x:c>
@@ -29294,7 +29942,9 @@
       <x:c r="G88" s="24" t="n">
         <x:v>4696.6</x:v>
       </x:c>
-      <x:c r="H88" s="24"/>
+      <x:c r="H88" s="24" t="n">
+        <x:v>29.6</x:v>
+      </x:c>
       <x:c r="I88" s="25" t="n">
         <x:v>0.006342404113991895</x:v>
       </x:c>
@@ -29328,7 +29978,9 @@
       <x:c r="G89" s="24" t="n">
         <x:v>4707.8</x:v>
       </x:c>
-      <x:c r="H89" s="24"/>
+      <x:c r="H89" s="24" t="n">
+        <x:v>11.2</x:v>
+      </x:c>
       <x:c r="I89" s="25" t="n">
         <x:v>0.00238470382830136</x:v>
       </x:c>
@@ -29362,7 +30014,9 @@
       <x:c r="G90" s="24" t="n">
         <x:v>4744.8</x:v>
       </x:c>
-      <x:c r="H90" s="24"/>
+      <x:c r="H90" s="24" t="n">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="I90" s="25" t="n">
         <x:v>0.007859297336335391</x:v>
       </x:c>
@@ -29396,7 +30050,9 @@
       <x:c r="G91" s="24" t="n">
         <x:v>4724.4</x:v>
       </x:c>
-      <x:c r="H91" s="24"/>
+      <x:c r="H91" s="24" t="n">
+        <x:v>-20.4</x:v>
+      </x:c>
       <x:c r="I91" s="25" t="n">
         <x:v>-0.0042994436014164306</x:v>
       </x:c>
@@ -29430,7 +30086,9 @@
       <x:c r="G92" s="24" t="n">
         <x:v>4713.6</x:v>
       </x:c>
-      <x:c r="H92" s="24"/>
+      <x:c r="H92" s="24" t="n">
+        <x:v>-10.8</x:v>
+      </x:c>
       <x:c r="I92" s="25" t="n">
         <x:v>-0.002286004572009004</x:v>
       </x:c>
@@ -29464,7 +30122,9 @@
       <x:c r="G93" s="24" t="n">
         <x:v>4715.6</x:v>
       </x:c>
-      <x:c r="H93" s="24"/>
+      <x:c r="H93" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I93" s="25" t="n">
         <x:v>0.0004243041412084203</x:v>
       </x:c>
@@ -29498,7 +30158,9 @@
       <x:c r="G94" s="24" t="n">
         <x:v>4702.4</x:v>
       </x:c>
-      <x:c r="H94" s="24"/>
+      <x:c r="H94" s="24" t="n">
+        <x:v>-13.2</x:v>
+      </x:c>
       <x:c r="I94" s="25" t="n">
         <x:v>-0.0027992196115024237</x:v>
       </x:c>
@@ -29532,7 +30194,9 @@
       <x:c r="G95" s="24" t="n">
         <x:v>4766</x:v>
       </x:c>
-      <x:c r="H95" s="24"/>
+      <x:c r="H95" s="24" t="n">
+        <x:v>63.6</x:v>
+      </x:c>
       <x:c r="I95" s="25" t="n">
         <x:v>0.013525008506294789</x:v>
       </x:c>
@@ -29566,7 +30230,9 @@
       <x:c r="G96" s="24" t="n">
         <x:v>4763.4</x:v>
       </x:c>
-      <x:c r="H96" s="24"/>
+      <x:c r="H96" s="24" t="n">
+        <x:v>-2.6</x:v>
+      </x:c>
       <x:c r="I96" s="25" t="n">
         <x:v>-0.0005455308434746398</x:v>
       </x:c>
@@ -29688,7 +30354,9 @@
       <x:c r="G102" s="24" t="n">
         <x:v>4839.4</x:v>
       </x:c>
-      <x:c r="H102" s="24"/>
+      <x:c r="H102" s="24" t="n">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="I102" s="25" t="n">
         <x:v>0.0159549901330982</x:v>
       </x:c>
@@ -29722,7 +30390,9 @@
       <x:c r="G103" s="24" t="n">
         <x:v>4862.4</x:v>
       </x:c>
-      <x:c r="H103" s="24"/>
+      <x:c r="H103" s="24" t="n">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="I103" s="25" t="n">
         <x:v>0.004752655287845631</x:v>
       </x:c>
@@ -29756,7 +30426,9 @@
       <x:c r="G104" s="24" t="n">
         <x:v>4836.8</x:v>
       </x:c>
-      <x:c r="H104" s="24"/>
+      <x:c r="H104" s="24" t="n">
+        <x:v>-25.6</x:v>
+      </x:c>
       <x:c r="I104" s="25" t="n">
         <x:v>-0.005264889766370406</x:v>
       </x:c>
@@ -29790,7 +30462,9 @@
       <x:c r="G105" s="24" t="n">
         <x:v>4912.6</x:v>
       </x:c>
-      <x:c r="H105" s="24"/>
+      <x:c r="H105" s="24" t="n">
+        <x:v>75.8</x:v>
+      </x:c>
       <x:c r="I105" s="25" t="n">
         <x:v>0.01567151835924574</x:v>
       </x:c>
@@ -29824,7 +30498,9 @@
       <x:c r="G106" s="24" t="n">
         <x:v>4911.6</x:v>
       </x:c>
-      <x:c r="H106" s="24"/>
+      <x:c r="H106" s="24" t="n">
+        <x:v>-1</x:v>
+      </x:c>
       <x:c r="I106" s="25" t="n">
         <x:v>-0.00020355819728856694</x:v>
       </x:c>
@@ -29858,7 +30534,9 @@
       <x:c r="G107" s="24" t="n">
         <x:v>4968.8</x:v>
       </x:c>
-      <x:c r="H107" s="24"/>
+      <x:c r="H107" s="24" t="n">
+        <x:v>57.2</x:v>
+      </x:c>
       <x:c r="I107" s="25" t="n">
         <x:v>0.011645899503216928</x:v>
       </x:c>
@@ -29892,7 +30570,9 @@
       <x:c r="G108" s="24" t="n">
         <x:v>4884.4</x:v>
       </x:c>
-      <x:c r="H108" s="24"/>
+      <x:c r="H108" s="24" t="n">
+        <x:v>-84.4</x:v>
+      </x:c>
       <x:c r="I108" s="25" t="n">
         <x:v>-0.016985992593785304</x:v>
       </x:c>
@@ -29926,7 +30606,9 @@
       <x:c r="G109" s="34" t="n">
         <x:v>4824</x:v>
       </x:c>
-      <x:c r="H109" s="34"/>
+      <x:c r="H109" s="34" t="n">
+        <x:v>-60.4</x:v>
+      </x:c>
       <x:c r="I109" s="35" t="n">
         <x:v>-0.012365899598722363</x:v>
       </x:c>
@@ -29960,7 +30642,9 @@
       <x:c r="G110" s="24" t="n">
         <x:v>4802</x:v>
       </x:c>
-      <x:c r="H110" s="24"/>
+      <x:c r="H110" s="24" t="n">
+        <x:v>-22</x:v>
+      </x:c>
       <x:c r="I110" s="25" t="n">
         <x:v>-0.004560530679933672</x:v>
       </x:c>
@@ -29994,7 +30678,9 @@
       <x:c r="G111" s="24" t="n">
         <x:v>4813.2</x:v>
       </x:c>
-      <x:c r="H111" s="24"/>
+      <x:c r="H111" s="24" t="n">
+        <x:v>11.2</x:v>
+      </x:c>
       <x:c r="I111" s="25" t="n">
         <x:v>0.0023323615160348865</x:v>
       </x:c>
@@ -30028,7 +30714,9 @@
       <x:c r="G112" s="24" t="n">
         <x:v>4806.6</x:v>
       </x:c>
-      <x:c r="H112" s="24"/>
+      <x:c r="H112" s="24" t="n">
+        <x:v>-6.6</x:v>
+      </x:c>
       <x:c r="I112" s="25" t="n">
         <x:v>-0.0013712291199201587</x:v>
       </x:c>
@@ -30062,7 +30750,9 @@
       <x:c r="G113" s="24" t="n">
         <x:v>4743</x:v>
       </x:c>
-      <x:c r="H113" s="24"/>
+      <x:c r="H113" s="24" t="n">
+        <x:v>-63.6</x:v>
+      </x:c>
       <x:c r="I113" s="25" t="n">
         <x:v>-0.013231806266383761</x:v>
       </x:c>
@@ -30096,7 +30786,9 @@
       <x:c r="G114" s="24" t="n">
         <x:v>4788.2</x:v>
       </x:c>
-      <x:c r="H114" s="24"/>
+      <x:c r="H114" s="24" t="n">
+        <x:v>45.2</x:v>
+      </x:c>
       <x:c r="I114" s="25" t="n">
         <x:v>0.009529833438751911</x:v>
       </x:c>
@@ -30130,7 +30822,9 @@
       <x:c r="G115" s="24" t="n">
         <x:v>4852.6</x:v>
       </x:c>
-      <x:c r="H115" s="24"/>
+      <x:c r="H115" s="24" t="n">
+        <x:v>64.4</x:v>
+      </x:c>
       <x:c r="I115" s="25" t="n">
         <x:v>0.01344973058769483</x:v>
       </x:c>
@@ -30164,7 +30858,9 @@
       <x:c r="G116" s="24" t="n">
         <x:v>4899.2</x:v>
       </x:c>
-      <x:c r="H116" s="24"/>
+      <x:c r="H116" s="24" t="n">
+        <x:v>46.6</x:v>
+      </x:c>
       <x:c r="I116" s="25" t="n">
         <x:v>0.009603099369410062</x:v>
       </x:c>
@@ -30198,7 +30894,9 @@
       <x:c r="G117" s="24" t="n">
         <x:v>4857.2</x:v>
       </x:c>
-      <x:c r="H117" s="24"/>
+      <x:c r="H117" s="24" t="n">
+        <x:v>-42</x:v>
+      </x:c>
       <x:c r="I117" s="25" t="n">
         <x:v>-0.00857282821685168</x:v>
       </x:c>
@@ -30232,7 +30930,9 @@
       <x:c r="G118" s="24" t="n">
         <x:v>4856</x:v>
       </x:c>
-      <x:c r="H118" s="24"/>
+      <x:c r="H118" s="24" t="n">
+        <x:v>-1.2</x:v>
+      </x:c>
       <x:c r="I118" s="25" t="n">
         <x:v>-0.0002470559169891473</x:v>
       </x:c>
@@ -30266,7 +30966,9 @@
       <x:c r="G119" s="24" t="n">
         <x:v>4847.8</x:v>
       </x:c>
-      <x:c r="H119" s="24"/>
+      <x:c r="H119" s="24" t="n">
+        <x:v>-8.2</x:v>
+      </x:c>
       <x:c r="I119" s="25" t="n">
         <x:v>-0.001688632619439856</x:v>
       </x:c>
@@ -30388,7 +31090,9 @@
       <x:c r="G125" s="24" t="n">
         <x:v>4811</x:v>
       </x:c>
-      <x:c r="H125" s="24"/>
+      <x:c r="H125" s="24" t="n">
+        <x:v>-36.8</x:v>
+      </x:c>
       <x:c r="I125" s="25" t="n">
         <x:v>-0.007591072238953833</x:v>
       </x:c>
@@ -30422,7 +31126,9 @@
       <x:c r="G126" s="24" t="n">
         <x:v>4878.6</x:v>
       </x:c>
-      <x:c r="H126" s="24"/>
+      <x:c r="H126" s="24" t="n">
+        <x:v>67.6</x:v>
+      </x:c>
       <x:c r="I126" s="25" t="n">
         <x:v>0.014051132820619427</x:v>
       </x:c>
@@ -30456,7 +31162,9 @@
       <x:c r="G127" s="24" t="n">
         <x:v>4913.8</x:v>
       </x:c>
-      <x:c r="H127" s="24"/>
+      <x:c r="H127" s="24" t="n">
+        <x:v>35.2</x:v>
+      </x:c>
       <x:c r="I127" s="25" t="n">
         <x:v>0.007215184684130627</x:v>
       </x:c>
@@ -30490,7 +31198,9 @@
       <x:c r="G128" s="24" t="n">
         <x:v>4871</x:v>
       </x:c>
-      <x:c r="H128" s="24"/>
+      <x:c r="H128" s="24" t="n">
+        <x:v>-42.8</x:v>
+      </x:c>
       <x:c r="I128" s="25" t="n">
         <x:v>-0.008710163213806021</x:v>
       </x:c>
@@ -30524,7 +31234,9 @@
       <x:c r="G129" s="24" t="n">
         <x:v>4776.8</x:v>
       </x:c>
-      <x:c r="H129" s="24"/>
+      <x:c r="H129" s="24" t="n">
+        <x:v>-94.2</x:v>
+      </x:c>
       <x:c r="I129" s="25" t="n">
         <x:v>-0.01933894477520015</x:v>
       </x:c>
@@ -30558,7 +31270,9 @@
       <x:c r="G130" s="24" t="n">
         <x:v>4682.6</x:v>
       </x:c>
-      <x:c r="H130" s="24"/>
+      <x:c r="H130" s="24" t="n">
+        <x:v>-94.2</x:v>
+      </x:c>
       <x:c r="I130" s="25" t="n">
         <x:v>-0.019720314855133148</x:v>
       </x:c>
@@ -30592,7 +31306,9 @@
       <x:c r="G131" s="24" t="n">
         <x:v>4743.6</x:v>
       </x:c>
-      <x:c r="H131" s="24"/>
+      <x:c r="H131" s="24" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="I131" s="25" t="n">
         <x:v>0.013026950839277296</x:v>
       </x:c>
@@ -30626,7 +31342,9 @@
       <x:c r="G132" s="24" t="n">
         <x:v>4721.4</x:v>
       </x:c>
-      <x:c r="H132" s="24"/>
+      <x:c r="H132" s="24" t="n">
+        <x:v>-22.2</x:v>
+      </x:c>
       <x:c r="I132" s="25" t="n">
         <x:v>-0.004679989881103075</x:v>
       </x:c>
@@ -30660,9 +31378,11 @@
       <x:c r="G133" s="24" t="n">
         <x:v>4693.4</x:v>
       </x:c>
-      <x:c r="H133" s="24"/>
+      <x:c r="H133" s="24" t="n">
+        <x:v>-28</x:v>
+      </x:c>
       <x:c r="I133" s="25" t="n">
-        <x:v>-0.02744948532215008</x:v>
+        <x:v>-0.0059304443597237855</x:v>
       </x:c>
       <x:c r="J133" s="24" t="n">
         <x:f>ROUND(E133-F133,1)</x:f>
@@ -30694,9 +31414,11 @@
       <x:c r="G134" s="24" t="n">
         <x:v>4769.8</x:v>
       </x:c>
-      <x:c r="H134" s="24"/>
+      <x:c r="H134" s="24" t="n">
+        <x:v>76.4</x:v>
+      </x:c>
       <x:c r="I134" s="25" t="n">
-        <x:v>0.0174223616011151</x:v>
+        <x:v>0.016278177866791754</x:v>
       </x:c>
       <x:c r="J134" s="24" t="n">
         <x:f>ROUND(E134-F134,1)</x:f>
@@ -30728,9 +31450,11 @@
       <x:c r="G135" s="24" t="n">
         <x:v>4880</x:v>
       </x:c>
-      <x:c r="H135" s="24"/>
+      <x:c r="H135" s="24" t="n">
+        <x:v>110.2</x:v>
+      </x:c>
       <x:c r="I135" s="25" t="n">
-        <x:v>0.024144869215291687</x:v>
+        <x:v>0.02310369407522317</x:v>
       </x:c>
       <x:c r="J135" s="24" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
@@ -30762,9 +31486,11 @@
       <x:c r="G136" s="24" t="n">
         <x:v>4875.2</x:v>
       </x:c>
-      <x:c r="H136" s="24"/>
+      <x:c r="H136" s="24" t="n">
+        <x:v>-4.8</x:v>
+      </x:c>
       <x:c r="I136" s="25" t="n">
-        <x:v>-0.0036784684195126927</x:v>
+        <x:v>-0.0009836065573770592</x:v>
       </x:c>
       <x:c r="J136" s="24" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -30796,9 +31522,11 @@
       <x:c r="G137" s="24" t="n">
         <x:v>4928</x:v>
       </x:c>
-      <x:c r="H137" s="24"/>
+      <x:c r="H137" s="24" t="n">
+        <x:v>52.8</x:v>
+      </x:c>
       <x:c r="I137" s="25" t="n">
-        <x:v>0.011747430249632984</x:v>
+        <x:v>0.010830324909747224</x:v>
       </x:c>
       <x:c r="J137" s="24" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -30830,9 +31558,11 @@
       <x:c r="G138" s="24" t="n">
         <x:v>4960.6</x:v>
       </x:c>
-      <x:c r="H138" s="24"/>
+      <x:c r="H138" s="24" t="n">
+        <x:v>32.6</x:v>
+      </x:c>
       <x:c r="I138" s="25" t="n">
-        <x:v>0.008252125233257246</x:v>
+        <x:v>0.006615259740259782</x:v>
       </x:c>
       <x:c r="J138" s="24" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -30864,9 +31594,11 @@
       <x:c r="G139" s="34" t="n">
         <x:v>4983.8</x:v>
       </x:c>
-      <x:c r="H139" s="34"/>
+      <x:c r="H139" s="34" t="n">
+        <x:v>23.2</x:v>
+      </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.024882783581475776</x:v>
+        <x:v>0.004676853606418563</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -30898,7 +31630,9 @@
       <x:c r="G140" s="24" t="n">
         <x:v>4812.4</x:v>
       </x:c>
-      <x:c r="H140" s="24"/>
+      <x:c r="H140" s="27" t="n">
+        <x:v>-171.4</x:v>
+      </x:c>
       <x:c r="I140" s="25" t="n">
         <x:v>-0.03439142822745711</x:v>
       </x:c>
@@ -30932,7 +31666,9 @@
       <x:c r="G141" s="24" t="n">
         <x:v>4830.8</x:v>
       </x:c>
-      <x:c r="H141" s="24"/>
+      <x:c r="H141" s="24" t="n">
+        <x:v>18.4</x:v>
+      </x:c>
       <x:c r="I141" s="25" t="n">
         <x:v>0.003823456071814668</x:v>
       </x:c>
@@ -30966,7 +31702,9 @@
       <x:c r="G142" s="24" t="n">
         <x:v>4907</x:v>
       </x:c>
-      <x:c r="H142" s="24"/>
+      <x:c r="H142" s="24" t="n">
+        <x:v>76.2</x:v>
+      </x:c>
       <x:c r="I142" s="25" t="n">
         <x:v>0.01577378488035097</x:v>
       </x:c>
@@ -31000,7 +31738,9 @@
       <x:c r="G143" s="24" t="n">
         <x:v>4748.2</x:v>
       </x:c>
-      <x:c r="H143" s="24"/>
+      <x:c r="H143" s="27" t="n">
+        <x:v>-158.8</x:v>
+      </x:c>
       <x:c r="I143" s="25" t="n">
         <x:v>-0.032361931933971966</x:v>
       </x:c>
@@ -31034,7 +31774,9 @@
       <x:c r="G144" s="24" t="n">
         <x:v>4796.4</x:v>
       </x:c>
-      <x:c r="H144" s="24"/>
+      <x:c r="H144" s="24" t="n">
+        <x:v>48.2</x:v>
+      </x:c>
       <x:c r="I144" s="25" t="n">
         <x:v>0.01015121519733797</x:v>
       </x:c>
@@ -31068,7 +31810,9 @@
       <x:c r="G145" s="24" t="n">
         <x:v>4855.8</x:v>
       </x:c>
-      <x:c r="H145" s="24"/>
+      <x:c r="H145" s="24" t="n">
+        <x:v>59.4</x:v>
+      </x:c>
       <x:c r="I145" s="25" t="n">
         <x:v>0.01238428821616222</x:v>
       </x:c>
@@ -31190,7 +31934,9 @@
       <x:c r="G151" s="24" t="n">
         <x:v>4831.2</x:v>
       </x:c>
-      <x:c r="H151" s="24"/>
+      <x:c r="H151" s="24" t="n">
+        <x:v>-24.6</x:v>
+      </x:c>
       <x:c r="I151" s="25" t="n">
         <x:v>-0.0050661065118003945</x:v>
       </x:c>
@@ -31224,7 +31970,9 @@
       <x:c r="G152" s="24" t="n">
         <x:v>4719.4</x:v>
       </x:c>
-      <x:c r="H152" s="24"/>
+      <x:c r="H152" s="24" t="n">
+        <x:v>-111.8</x:v>
+      </x:c>
       <x:c r="I152" s="25" t="n">
         <x:v>-0.02314124855108468</x:v>
       </x:c>
@@ -31258,7 +32006,9 @@
       <x:c r="G153" s="24" t="n">
         <x:v>4752.2</x:v>
       </x:c>
-      <x:c r="H153" s="24"/>
+      <x:c r="H153" s="24" t="n">
+        <x:v>32.8</x:v>
+      </x:c>
       <x:c r="I153" s="25" t="n">
         <x:v>0.006950036021528216</x:v>
       </x:c>
@@ -31292,7 +32042,9 @@
       <x:c r="G154" s="24" t="n">
         <x:v>4753.2</x:v>
       </x:c>
-      <x:c r="H154" s="24"/>
+      <x:c r="H154" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I154" s="25" t="n">
         <x:v>0.00021042885400435196</x:v>
       </x:c>
@@ -31326,7 +32078,9 @@
       <x:c r="G155" s="24" t="n">
         <x:v>4703.4</x:v>
       </x:c>
-      <x:c r="H155" s="24"/>
+      <x:c r="H155" s="24" t="n">
+        <x:v>-49.8</x:v>
+      </x:c>
       <x:c r="I155" s="25" t="n">
         <x:v>-0.01047715223428436</x:v>
       </x:c>
@@ -31360,7 +32114,9 @@
       <x:c r="G156" s="24" t="n">
         <x:v>4668</x:v>
       </x:c>
-      <x:c r="H156" s="24"/>
+      <x:c r="H156" s="24" t="n">
+        <x:v>-35.4</x:v>
+      </x:c>
       <x:c r="I156" s="25" t="n">
         <x:v>-0.007526470213037317</x:v>
       </x:c>
@@ -31394,7 +32150,9 @@
       <x:c r="G157" s="24" t="n">
         <x:v>4780.8</x:v>
       </x:c>
-      <x:c r="H157" s="24"/>
+      <x:c r="H157" s="24" t="n">
+        <x:v>112.8</x:v>
+      </x:c>
       <x:c r="I157" s="25" t="n">
         <x:v>0.02416452442159378</x:v>
       </x:c>
@@ -31428,7 +32186,9 @@
       <x:c r="G158" s="24" t="n">
         <x:v>4704.6</x:v>
       </x:c>
-      <x:c r="H158" s="24"/>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-76.2</x:v>
+      </x:c>
       <x:c r="I158" s="25" t="n">
         <x:v>-0.015938755020080242</x:v>
       </x:c>
@@ -31462,7 +32222,9 @@
       <x:c r="G159" s="24" t="n">
         <x:v>4634.6</x:v>
       </x:c>
-      <x:c r="H159" s="24"/>
+      <x:c r="H159" s="24" t="n">
+        <x:v>-70</x:v>
+      </x:c>
       <x:c r="I159" s="25" t="n">
         <x:v>-0.014879054542362824</x:v>
       </x:c>
@@ -31496,7 +32258,9 @@
       <x:c r="G160" s="24" t="n">
         <x:v>4690</x:v>
       </x:c>
-      <x:c r="H160" s="24"/>
+      <x:c r="H160" s="24" t="n">
+        <x:v>55.4</x:v>
+      </x:c>
       <x:c r="I160" s="25" t="n">
         <x:v>0.011953566650843683</x:v>
       </x:c>
@@ -31530,7 +32294,9 @@
       <x:c r="G161" s="24" t="n">
         <x:v>4717.4</x:v>
       </x:c>
-      <x:c r="H161" s="24"/>
+      <x:c r="H161" s="24" t="n">
+        <x:v>27.4</x:v>
+      </x:c>
       <x:c r="I161" s="25" t="n">
         <x:v>0.005842217484008483</x:v>
       </x:c>
@@ -31564,7 +32330,9 @@
       <x:c r="G162" s="24" t="n">
         <x:v>4645.6</x:v>
       </x:c>
-      <x:c r="H162" s="24"/>
+      <x:c r="H162" s="24" t="n">
+        <x:v>-71.8</x:v>
+      </x:c>
       <x:c r="I162" s="25" t="n">
         <x:v>-0.015220248441938256</x:v>
       </x:c>
@@ -31723,7 +32491,9 @@
       <x:c r="G5" s="24" t="n">
         <x:v>3098.8</x:v>
       </x:c>
-      <x:c r="H5" s="24"/>
+      <x:c r="H5" s="24" t="n">
+        <x:v>73.8</x:v>
+      </x:c>
       <x:c r="I5" s="25" t="n">
         <x:v>0.024396694214876113</x:v>
       </x:c>
@@ -31757,7 +32527,9 @@
       <x:c r="G6" s="24" t="n">
         <x:v>3161.8</x:v>
       </x:c>
-      <x:c r="H6" s="24"/>
+      <x:c r="H6" s="24" t="n">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="I6" s="25" t="n">
         <x:v>0.02033045049696658</x:v>
       </x:c>
@@ -31791,7 +32563,9 @@
       <x:c r="G7" s="24" t="n">
         <x:v>3143.8</x:v>
       </x:c>
-      <x:c r="H7" s="24"/>
+      <x:c r="H7" s="24" t="n">
+        <x:v>-18</x:v>
+      </x:c>
       <x:c r="I7" s="25" t="n">
         <x:v>-0.005692959706496303</x:v>
       </x:c>
@@ -31825,7 +32599,9 @@
       <x:c r="G8" s="24" t="n">
         <x:v>3122.4</x:v>
       </x:c>
-      <x:c r="H8" s="24"/>
+      <x:c r="H8" s="24" t="n">
+        <x:v>-21.4</x:v>
+      </x:c>
       <x:c r="I8" s="25" t="n">
         <x:v>-0.006807048794452597</x:v>
       </x:c>
@@ -31859,7 +32635,9 @@
       <x:c r="G9" s="24" t="n">
         <x:v>3134.8</x:v>
       </x:c>
-      <x:c r="H9" s="24"/>
+      <x:c r="H9" s="24" t="n">
+        <x:v>12.4</x:v>
+      </x:c>
       <x:c r="I9" s="25" t="n">
         <x:v>0.003971304125031994</x:v>
       </x:c>
@@ -31893,7 +32671,9 @@
       <x:c r="G10" s="24" t="n">
         <x:v>3140.2</x:v>
       </x:c>
-      <x:c r="H10" s="24"/>
+      <x:c r="H10" s="24" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
       <x:c r="I10" s="25" t="n">
         <x:v>0.0017225979328823193</x:v>
       </x:c>
@@ -31927,7 +32707,9 @@
       <x:c r="G11" s="24" t="n">
         <x:v>3137.6</x:v>
       </x:c>
-      <x:c r="H11" s="24"/>
+      <x:c r="H11" s="24" t="n">
+        <x:v>-2.6</x:v>
+      </x:c>
       <x:c r="I11" s="25" t="n">
         <x:v>-0.0008279727405897663</x:v>
       </x:c>
@@ -31961,7 +32743,9 @@
       <x:c r="G12" s="24" t="n">
         <x:v>3114</x:v>
       </x:c>
-      <x:c r="H12" s="24"/>
+      <x:c r="H12" s="24" t="n">
+        <x:v>-23.6</x:v>
+      </x:c>
       <x:c r="I12" s="25" t="n">
         <x:v>-0.0075216726160122205</x:v>
       </x:c>
@@ -31995,7 +32779,9 @@
       <x:c r="G13" s="24" t="n">
         <x:v>3108</x:v>
       </x:c>
-      <x:c r="H13" s="24"/>
+      <x:c r="H13" s="24" t="n">
+        <x:v>-6</x:v>
+      </x:c>
       <x:c r="I13" s="25" t="n">
         <x:v>-0.0019267822736031004</x:v>
       </x:c>
@@ -32029,7 +32815,9 @@
       <x:c r="G14" s="34" t="n">
         <x:v>3084.4</x:v>
       </x:c>
-      <x:c r="H14" s="34"/>
+      <x:c r="H14" s="34" t="n">
+        <x:v>-23.6</x:v>
+      </x:c>
       <x:c r="I14" s="35" t="n">
         <x:v>-0.007593307593307563</x:v>
       </x:c>
@@ -32063,7 +32851,9 @@
       <x:c r="G15" s="24" t="n">
         <x:v>3077.6</x:v>
       </x:c>
-      <x:c r="H15" s="24"/>
+      <x:c r="H15" s="24" t="n">
+        <x:v>-6.8</x:v>
+      </x:c>
       <x:c r="I15" s="25" t="n">
         <x:v>-0.0022046427181948713</x:v>
       </x:c>
@@ -32097,7 +32887,9 @@
       <x:c r="G16" s="24" t="n">
         <x:v>3075.4</x:v>
       </x:c>
-      <x:c r="H16" s="24"/>
+      <x:c r="H16" s="24" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
       <x:c r="I16" s="25" t="n">
         <x:v>-0.0007148427345983199</x:v>
       </x:c>
@@ -32131,7 +32923,9 @@
       <x:c r="G17" s="24" t="n">
         <x:v>3073.6</x:v>
       </x:c>
-      <x:c r="H17" s="24"/>
+      <x:c r="H17" s="24" t="n">
+        <x:v>-1.8</x:v>
+      </x:c>
       <x:c r="I17" s="25" t="n">
         <x:v>-0.0005852897184106531</x:v>
       </x:c>
@@ -32165,7 +32959,9 @@
       <x:c r="G18" s="24" t="n">
         <x:v>3061.2</x:v>
       </x:c>
-      <x:c r="H18" s="24"/>
+      <x:c r="H18" s="24" t="n">
+        <x:v>-12.4</x:v>
+      </x:c>
       <x:c r="I18" s="25" t="n">
         <x:v>-0.0040343571056741245</x:v>
       </x:c>
@@ -32199,7 +32995,9 @@
       <x:c r="G19" s="24" t="n">
         <x:v>3037.8</x:v>
       </x:c>
-      <x:c r="H19" s="24"/>
+      <x:c r="H19" s="24" t="n">
+        <x:v>-23.4</x:v>
+      </x:c>
       <x:c r="I19" s="25" t="n">
         <x:v>-0.007644061152489057</x:v>
       </x:c>
@@ -32233,7 +33031,9 @@
       <x:c r="G20" s="24" t="n">
         <x:v>3058.2</x:v>
       </x:c>
-      <x:c r="H20" s="24"/>
+      <x:c r="H20" s="24" t="n">
+        <x:v>20.4</x:v>
+      </x:c>
       <x:c r="I20" s="25" t="n">
         <x:v>0.006715386134702683</x:v>
       </x:c>
@@ -32267,7 +33067,9 @@
       <x:c r="G21" s="24" t="n">
         <x:v>3064</x:v>
       </x:c>
-      <x:c r="H21" s="24"/>
+      <x:c r="H21" s="24" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
       <x:c r="I21" s="25" t="n">
         <x:v>0.0018965404486299686</x:v>
       </x:c>
@@ -32301,7 +33103,9 @@
       <x:c r="G22" s="24" t="n">
         <x:v>3069.8</x:v>
       </x:c>
-      <x:c r="H22" s="24"/>
+      <x:c r="H22" s="24" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
       <x:c r="I22" s="25" t="n">
         <x:v>0.001892950391644943</x:v>
       </x:c>
@@ -32335,7 +33139,9 @@
       <x:c r="G23" s="24" t="n">
         <x:v>3130.4</x:v>
       </x:c>
-      <x:c r="H23" s="24"/>
+      <x:c r="H23" s="24" t="n">
+        <x:v>60.6</x:v>
+      </x:c>
       <x:c r="I23" s="25" t="n">
         <x:v>0.019740699719851484</x:v>
       </x:c>
@@ -32369,7 +33175,9 @@
       <x:c r="G24" s="24" t="n">
         <x:v>3074</x:v>
       </x:c>
-      <x:c r="H24" s="24"/>
+      <x:c r="H24" s="24" t="n">
+        <x:v>-56.4</x:v>
+      </x:c>
       <x:c r="I24" s="25" t="n">
         <x:v>-0.01801686685407622</x:v>
       </x:c>
@@ -32491,7 +33299,9 @@
       <x:c r="G30" s="24" t="n">
         <x:v>3004.2</x:v>
       </x:c>
-      <x:c r="H30" s="24"/>
+      <x:c r="H30" s="24" t="n">
+        <x:v>-69.8</x:v>
+      </x:c>
       <x:c r="I30" s="25" t="n">
         <x:v>-0.022706571242680607</x:v>
       </x:c>
@@ -32525,7 +33335,9 @@
       <x:c r="G31" s="24" t="n">
         <x:v>3033</x:v>
       </x:c>
-      <x:c r="H31" s="24"/>
+      <x:c r="H31" s="24" t="n">
+        <x:v>28.8</x:v>
+      </x:c>
       <x:c r="I31" s="25" t="n">
         <x:v>0.009586578789694489</x:v>
       </x:c>
@@ -32559,7 +33371,9 @@
       <x:c r="G32" s="24" t="n">
         <x:v>3071.8</x:v>
       </x:c>
-      <x:c r="H32" s="24"/>
+      <x:c r="H32" s="24" t="n">
+        <x:v>38.8</x:v>
+      </x:c>
       <x:c r="I32" s="25" t="n">
         <x:v>0.012792614573030159</x:v>
       </x:c>
@@ -32593,7 +33407,9 @@
       <x:c r="G33" s="24" t="n">
         <x:v>3061.4</x:v>
       </x:c>
-      <x:c r="H33" s="24"/>
+      <x:c r="H33" s="24" t="n">
+        <x:v>-10.4</x:v>
+      </x:c>
       <x:c r="I33" s="25" t="n">
         <x:v>-0.0033856370857477947</x:v>
       </x:c>
@@ -32627,7 +33443,9 @@
       <x:c r="G34" s="24" t="n">
         <x:v>3036.2</x:v>
       </x:c>
-      <x:c r="H34" s="24"/>
+      <x:c r="H34" s="24" t="n">
+        <x:v>-25.2</x:v>
+      </x:c>
       <x:c r="I34" s="25" t="n">
         <x:v>-0.008231528059058024</x:v>
       </x:c>
@@ -32661,7 +33479,9 @@
       <x:c r="G35" s="24" t="n">
         <x:v>3084</x:v>
       </x:c>
-      <x:c r="H35" s="24"/>
+      <x:c r="H35" s="24" t="n">
+        <x:v>47.8</x:v>
+      </x:c>
       <x:c r="I35" s="25" t="n">
         <x:v>0.015743363414794764</x:v>
       </x:c>
@@ -32695,7 +33515,9 @@
       <x:c r="G36" s="24" t="n">
         <x:v>3093.6</x:v>
       </x:c>
-      <x:c r="H36" s="24"/>
+      <x:c r="H36" s="24" t="n">
+        <x:v>9.6</x:v>
+      </x:c>
       <x:c r="I36" s="25" t="n">
         <x:v>0.003112840466926059</x:v>
       </x:c>
@@ -32729,7 +33551,9 @@
       <x:c r="G37" s="24" t="n">
         <x:v>3091.4</x:v>
       </x:c>
-      <x:c r="H37" s="24"/>
+      <x:c r="H37" s="24" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
       <x:c r="I37" s="25" t="n">
         <x:v>-0.0007111455908972442</x:v>
       </x:c>
@@ -32763,7 +33587,9 @@
       <x:c r="G38" s="24" t="n">
         <x:v>3083</x:v>
       </x:c>
-      <x:c r="H38" s="24"/>
+      <x:c r="H38" s="24" t="n">
+        <x:v>-8.4</x:v>
+      </x:c>
       <x:c r="I38" s="25" t="n">
         <x:v>-0.002717215501067516</x:v>
       </x:c>
@@ -32797,7 +33623,9 @@
       <x:c r="G39" s="24" t="n">
         <x:v>3020</x:v>
       </x:c>
-      <x:c r="H39" s="24"/>
+      <x:c r="H39" s="24" t="n">
+        <x:v>-63</x:v>
+      </x:c>
       <x:c r="I39" s="25" t="n">
         <x:v>-0.02043464158287378</x:v>
       </x:c>
@@ -32831,7 +33659,9 @@
       <x:c r="G40" s="34" t="n">
         <x:v>3037.4</x:v>
       </x:c>
-      <x:c r="H40" s="34"/>
+      <x:c r="H40" s="34" t="n">
+        <x:v>17.4</x:v>
+      </x:c>
       <x:c r="I40" s="35" t="n">
         <x:v>0.005761589403973533</x:v>
       </x:c>
@@ -32865,7 +33695,9 @@
       <x:c r="G41" s="24" t="n">
         <x:v>3058.2</x:v>
       </x:c>
-      <x:c r="H41" s="24"/>
+      <x:c r="H41" s="24" t="n">
+        <x:v>20.8</x:v>
+      </x:c>
       <x:c r="I41" s="25" t="n">
         <x:v>0.006847962072825453</x:v>
       </x:c>
@@ -32899,7 +33731,9 @@
       <x:c r="G42" s="24" t="n">
         <x:v>3034.6</x:v>
       </x:c>
-      <x:c r="H42" s="24"/>
+      <x:c r="H42" s="24" t="n">
+        <x:v>-23.6</x:v>
+      </x:c>
       <x:c r="I42" s="25" t="n">
         <x:v>-0.007716957687528558</x:v>
       </x:c>
@@ -32933,7 +33767,9 @@
       <x:c r="G43" s="24" t="n">
         <x:v>3045.4</x:v>
       </x:c>
-      <x:c r="H43" s="24"/>
+      <x:c r="H43" s="24" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
       <x:c r="I43" s="25" t="n">
         <x:v>0.003558953404073195</x:v>
       </x:c>
@@ -33055,7 +33891,9 @@
       <x:c r="G49" s="24" t="n">
         <x:v>3045.8</x:v>
       </x:c>
-      <x:c r="H49" s="24"/>
+      <x:c r="H49" s="24" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
       <x:c r="I49" s="25" t="n">
         <x:v>0.00013134563604122462</x:v>
       </x:c>
@@ -33089,7 +33927,9 @@
       <x:c r="G50" s="24" t="n">
         <x:v>3019</x:v>
       </x:c>
-      <x:c r="H50" s="24"/>
+      <x:c r="H50" s="24" t="n">
+        <x:v>-26.8</x:v>
+      </x:c>
       <x:c r="I50" s="25" t="n">
         <x:v>-0.008799001904261639</x:v>
       </x:c>
@@ -33123,7 +33963,9 @@
       <x:c r="G51" s="24" t="n">
         <x:v>2972.2</x:v>
       </x:c>
-      <x:c r="H51" s="24"/>
+      <x:c r="H51" s="24" t="n">
+        <x:v>-46.8</x:v>
+      </x:c>
       <x:c r="I51" s="25" t="n">
         <x:v>-0.015501821795296467</x:v>
       </x:c>
@@ -33157,7 +33999,9 @@
       <x:c r="G52" s="24" t="n">
         <x:v>2987</x:v>
       </x:c>
-      <x:c r="H52" s="24"/>
+      <x:c r="H52" s="24" t="n">
+        <x:v>14.8</x:v>
+      </x:c>
       <x:c r="I52" s="25" t="n">
         <x:v>0.004979476482067202</x:v>
       </x:c>
@@ -33191,7 +34035,9 @@
       <x:c r="G53" s="24" t="n">
         <x:v>2990</x:v>
       </x:c>
-      <x:c r="H53" s="24"/>
+      <x:c r="H53" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I53" s="25" t="n">
         <x:v>0.001004352192835567</x:v>
       </x:c>
@@ -33225,7 +34071,9 @@
       <x:c r="G54" s="24" t="n">
         <x:v>2962.4</x:v>
       </x:c>
-      <x:c r="H54" s="24"/>
+      <x:c r="H54" s="24" t="n">
+        <x:v>-27.6</x:v>
+      </x:c>
       <x:c r="I54" s="25" t="n">
         <x:v>-0.009230769230769154</x:v>
       </x:c>
@@ -33259,7 +34107,9 @@
       <x:c r="G55" s="24" t="n">
         <x:v>2981.4</x:v>
       </x:c>
-      <x:c r="H55" s="24"/>
+      <x:c r="H55" s="24" t="n">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="I55" s="25" t="n">
         <x:v>0.006413718606535168</x:v>
       </x:c>
@@ -33293,7 +34143,9 @@
       <x:c r="G56" s="24" t="n">
         <x:v>2983.8</x:v>
       </x:c>
-      <x:c r="H56" s="24"/>
+      <x:c r="H56" s="24" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
       <x:c r="I56" s="25" t="n">
         <x:v>0.000804990943851891</x:v>
       </x:c>
@@ -33327,7 +34179,9 @@
       <x:c r="G57" s="24" t="n">
         <x:v>2966.4</x:v>
       </x:c>
-      <x:c r="H57" s="24"/>
+      <x:c r="H57" s="24" t="n">
+        <x:v>-17.4</x:v>
+      </x:c>
       <x:c r="I57" s="25" t="n">
         <x:v>-0.005831490046249832</x:v>
       </x:c>
@@ -33361,7 +34215,9 @@
       <x:c r="G58" s="24" t="n">
         <x:v>2957</x:v>
       </x:c>
-      <x:c r="H58" s="24"/>
+      <x:c r="H58" s="24" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
       <x:c r="I58" s="25" t="n">
         <x:v>-0.0031688241639697967</x:v>
       </x:c>
@@ -33395,7 +34251,9 @@
       <x:c r="G59" s="24" t="n">
         <x:v>2952</x:v>
       </x:c>
-      <x:c r="H59" s="24"/>
+      <x:c r="H59" s="24" t="n">
+        <x:v>-5</x:v>
+      </x:c>
       <x:c r="I59" s="25" t="n">
         <x:v>-0.001690902942171113</x:v>
       </x:c>
@@ -33429,7 +34287,9 @@
       <x:c r="G60" s="24" t="n">
         <x:v>2962</x:v>
       </x:c>
-      <x:c r="H60" s="24"/>
+      <x:c r="H60" s="24" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="I60" s="25" t="n">
         <x:v>0.003387533875338855</x:v>
       </x:c>
@@ -33463,9 +34323,11 @@
       <x:c r="G61" s="24" t="n">
         <x:v>2958.6</x:v>
       </x:c>
-      <x:c r="H61" s="24"/>
+      <x:c r="H61" s="24" t="n">
+        <x:v>-3.4</x:v>
+      </x:c>
       <x:c r="I61" s="25" t="n">
-        <x:v>-0.006684672518568635</x:v>
+        <x:v>-0.0011478730587440866</x:v>
       </x:c>
       <x:c r="J61" s="24" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -33497,9 +34359,11 @@
       <x:c r="G62" s="24" t="n">
         <x:v>2920.2</x:v>
       </x:c>
-      <x:c r="H62" s="24"/>
+      <x:c r="H62" s="24" t="n">
+        <x:v>-38.4</x:v>
+      </x:c>
       <x:c r="I62" s="25" t="n">
-        <x:v>-0.016450275304194073</x:v>
+        <x:v>-0.01297911174204014</x:v>
       </x:c>
       <x:c r="J62" s="24" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -33531,9 +34395,11 @@
       <x:c r="G63" s="34" t="n">
         <x:v>2898.4</x:v>
       </x:c>
-      <x:c r="H63" s="34"/>
+      <x:c r="H63" s="34" t="n">
+        <x:v>-21.8</x:v>
+      </x:c>
       <x:c r="I63" s="35" t="n">
-        <x:v>-0.009675858732462461</x:v>
+        <x:v>-0.007465242106704961</x:v>
       </x:c>
       <x:c r="J63" s="34" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -33565,9 +34431,11 @@
       <x:c r="G64" s="24" t="n">
         <x:v>2776</x:v>
       </x:c>
-      <x:c r="H64" s="24"/>
+      <x:c r="H64" s="24" t="n">
+        <x:v>-122.4</x:v>
+      </x:c>
       <x:c r="I64" s="25" t="n">
-        <x:v>-0.03133505478400456</x:v>
+        <x:v>-0.04223019597019051</x:v>
       </x:c>
       <x:c r="J64" s="29" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -33599,7 +34467,9 @@
       <x:c r="G65" s="24" t="n">
         <x:v>2810.6</x:v>
       </x:c>
-      <x:c r="H65" s="24"/>
+      <x:c r="H65" s="24" t="n">
+        <x:v>34.6</x:v>
+      </x:c>
       <x:c r="I65" s="25" t="n">
         <x:v>0.012463976945244815</x:v>
       </x:c>
@@ -33633,7 +34503,9 @@
       <x:c r="G66" s="24" t="n">
         <x:v>2830</x:v>
       </x:c>
-      <x:c r="H66" s="24"/>
+      <x:c r="H66" s="24" t="n">
+        <x:v>19.4</x:v>
+      </x:c>
       <x:c r="I66" s="25" t="n">
         <x:v>0.006902440759980033</x:v>
       </x:c>
@@ -33667,7 +34539,9 @@
       <x:c r="G67" s="24" t="n">
         <x:v>2804.8</x:v>
       </x:c>
-      <x:c r="H67" s="24"/>
+      <x:c r="H67" s="24" t="n">
+        <x:v>-25.2</x:v>
+      </x:c>
       <x:c r="I67" s="25" t="n">
         <x:v>-0.008904593639575853</x:v>
       </x:c>
@@ -33701,7 +34575,9 @@
       <x:c r="G68" s="24" t="n">
         <x:v>2814.4</x:v>
       </x:c>
-      <x:c r="H68" s="24"/>
+      <x:c r="H68" s="24" t="n">
+        <x:v>9.6</x:v>
+      </x:c>
       <x:c r="I68" s="25" t="n">
         <x:v>0.003422703936109439</x:v>
       </x:c>
@@ -33735,7 +34611,9 @@
       <x:c r="G69" s="24" t="n">
         <x:v>2812.4</x:v>
       </x:c>
-      <x:c r="H69" s="24"/>
+      <x:c r="H69" s="24" t="n">
+        <x:v>-2</x:v>
+      </x:c>
       <x:c r="I69" s="25" t="n">
         <x:v>-0.0007106310403638405</x:v>
       </x:c>
@@ -33769,7 +34647,9 @@
       <x:c r="G70" s="24" t="n">
         <x:v>2804</x:v>
       </x:c>
-      <x:c r="H70" s="24"/>
+      <x:c r="H70" s="24" t="n">
+        <x:v>-8.4</x:v>
+      </x:c>
       <x:c r="I70" s="25" t="n">
         <x:v>-0.0029867728630351698</x:v>
       </x:c>
@@ -33891,7 +34771,9 @@
       <x:c r="G76" s="24" t="n">
         <x:v>2853.8</x:v>
       </x:c>
-      <x:c r="H76" s="24"/>
+      <x:c r="H76" s="24" t="n">
+        <x:v>49.8</x:v>
+      </x:c>
       <x:c r="I76" s="25" t="n">
         <x:v>0.01776034236804569</x:v>
       </x:c>
@@ -33925,7 +34807,9 @@
       <x:c r="G77" s="24" t="n">
         <x:v>2827.6</x:v>
       </x:c>
-      <x:c r="H77" s="24"/>
+      <x:c r="H77" s="24" t="n">
+        <x:v>-26.2</x:v>
+      </x:c>
       <x:c r="I77" s="25" t="n">
         <x:v>-0.009180741467517128</x:v>
       </x:c>
@@ -33959,7 +34843,9 @@
       <x:c r="G78" s="24" t="n">
         <x:v>2804.4</x:v>
       </x:c>
-      <x:c r="H78" s="24"/>
+      <x:c r="H78" s="24" t="n">
+        <x:v>-23.2</x:v>
+      </x:c>
       <x:c r="I78" s="25" t="n">
         <x:v>-0.00820483802518035</x:v>
       </x:c>
@@ -33993,7 +34879,9 @@
       <x:c r="G79" s="24" t="n">
         <x:v>2798.4</x:v>
       </x:c>
-      <x:c r="H79" s="24"/>
+      <x:c r="H79" s="24" t="n">
+        <x:v>-6</x:v>
+      </x:c>
       <x:c r="I79" s="25" t="n">
         <x:v>-0.0021394950791613354</x:v>
       </x:c>
@@ -34027,7 +34915,9 @@
       <x:c r="G80" s="24" t="n">
         <x:v>2886</x:v>
       </x:c>
-      <x:c r="H80" s="24"/>
+      <x:c r="H80" s="24" t="n">
+        <x:v>87.6</x:v>
+      </x:c>
       <x:c r="I80" s="25" t="n">
         <x:v>0.03130360205831906</x:v>
       </x:c>
@@ -34061,7 +34951,9 @@
       <x:c r="G81" s="24" t="n">
         <x:v>2860.6</x:v>
       </x:c>
-      <x:c r="H81" s="24"/>
+      <x:c r="H81" s="24" t="n">
+        <x:v>-25.4</x:v>
+      </x:c>
       <x:c r="I81" s="25" t="n">
         <x:v>-0.008801108801108848</x:v>
       </x:c>
@@ -34095,7 +34987,9 @@
       <x:c r="G82" s="24" t="n">
         <x:v>2873.2</x:v>
       </x:c>
-      <x:c r="H82" s="24"/>
+      <x:c r="H82" s="24" t="n">
+        <x:v>12.6</x:v>
+      </x:c>
       <x:c r="I82" s="25" t="n">
         <x:v>0.004404670348877815</x:v>
       </x:c>
@@ -34129,7 +35023,9 @@
       <x:c r="G83" s="24" t="n">
         <x:v>2873</x:v>
       </x:c>
-      <x:c r="H83" s="24"/>
+      <x:c r="H83" s="24" t="n">
+        <x:v>-0.2</x:v>
+      </x:c>
       <x:c r="I83" s="25" t="n">
         <x:v>-0.0000696087985521121</x:v>
       </x:c>
@@ -34163,7 +35059,9 @@
       <x:c r="G84" s="24" t="n">
         <x:v>2898.4</x:v>
       </x:c>
-      <x:c r="H84" s="24"/>
+      <x:c r="H84" s="24" t="n">
+        <x:v>25.4</x:v>
+      </x:c>
       <x:c r="I84" s="25" t="n">
         <x:v>0.00884093282283338</x:v>
       </x:c>
@@ -34197,7 +35095,9 @@
       <x:c r="G85" s="24" t="n">
         <x:v>2907.6</x:v>
       </x:c>
-      <x:c r="H85" s="24"/>
+      <x:c r="H85" s="24" t="n">
+        <x:v>9.2</x:v>
+      </x:c>
       <x:c r="I85" s="25" t="n">
         <x:v>0.003174165056582856</x:v>
       </x:c>
@@ -34231,7 +35131,9 @@
       <x:c r="G86" s="24" t="n">
         <x:v>2920</x:v>
       </x:c>
-      <x:c r="H86" s="24"/>
+      <x:c r="H86" s="24" t="n">
+        <x:v>12.4</x:v>
+      </x:c>
       <x:c r="I86" s="25" t="n">
         <x:v>0.004264685651396372</x:v>
       </x:c>
@@ -34265,7 +35167,9 @@
       <x:c r="G87" s="34" t="n">
         <x:v>2888</x:v>
       </x:c>
-      <x:c r="H87" s="34"/>
+      <x:c r="H87" s="34" t="n">
+        <x:v>-32</x:v>
+      </x:c>
       <x:c r="I87" s="35" t="n">
         <x:v>-0.010958904109588996</x:v>
       </x:c>
@@ -34299,7 +35203,9 @@
       <x:c r="G88" s="24" t="n">
         <x:v>2918</x:v>
       </x:c>
-      <x:c r="H88" s="24"/>
+      <x:c r="H88" s="24" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="I88" s="25" t="n">
         <x:v>0.010387811634348987</x:v>
       </x:c>
@@ -34333,7 +35239,9 @@
       <x:c r="G89" s="24" t="n">
         <x:v>2916.6</x:v>
       </x:c>
-      <x:c r="H89" s="24"/>
+      <x:c r="H89" s="24" t="n">
+        <x:v>-1.4</x:v>
+      </x:c>
       <x:c r="I89" s="25" t="n">
         <x:v>-0.00047978067169296423</x:v>
       </x:c>
@@ -34367,7 +35275,9 @@
       <x:c r="G90" s="24" t="n">
         <x:v>2917.8</x:v>
       </x:c>
-      <x:c r="H90" s="24"/>
+      <x:c r="H90" s="24" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
       <x:c r="I90" s="25" t="n">
         <x:v>0.0004114379757251818</x:v>
       </x:c>
@@ -34401,7 +35311,9 @@
       <x:c r="G91" s="24" t="n">
         <x:v>2911.2</x:v>
       </x:c>
-      <x:c r="H91" s="24"/>
+      <x:c r="H91" s="24" t="n">
+        <x:v>-6.6</x:v>
+      </x:c>
       <x:c r="I91" s="25" t="n">
         <x:v>-0.0022619782027556434</x:v>
       </x:c>
@@ -34435,7 +35347,9 @@
       <x:c r="G92" s="24" t="n">
         <x:v>2929</x:v>
       </x:c>
-      <x:c r="H92" s="24"/>
+      <x:c r="H92" s="24" t="n">
+        <x:v>17.8</x:v>
+      </x:c>
       <x:c r="I92" s="25" t="n">
         <x:v>0.00611431712008792</x:v>
       </x:c>
@@ -34469,7 +35383,9 @@
       <x:c r="G93" s="24" t="n">
         <x:v>2922.4</x:v>
       </x:c>
-      <x:c r="H93" s="24"/>
+      <x:c r="H93" s="24" t="n">
+        <x:v>-6.6</x:v>
+      </x:c>
       <x:c r="I93" s="25" t="n">
         <x:v>-0.002253328781153918</x:v>
       </x:c>
@@ -34503,7 +35419,9 @@
       <x:c r="G94" s="24" t="n">
         <x:v>2930.2</x:v>
       </x:c>
-      <x:c r="H94" s="24"/>
+      <x:c r="H94" s="24" t="n">
+        <x:v>7.8</x:v>
+      </x:c>
       <x:c r="I94" s="25" t="n">
         <x:v>0.002669039145907437</x:v>
       </x:c>
@@ -34537,7 +35455,9 @@
       <x:c r="G95" s="24" t="n">
         <x:v>2947</x:v>
       </x:c>
-      <x:c r="H95" s="24"/>
+      <x:c r="H95" s="24" t="n">
+        <x:v>16.8</x:v>
+      </x:c>
       <x:c r="I95" s="25" t="n">
         <x:v>0.005733397037744892</x:v>
       </x:c>
@@ -34571,7 +35491,9 @@
       <x:c r="G96" s="24" t="n">
         <x:v>2968.8</x:v>
       </x:c>
-      <x:c r="H96" s="24"/>
+      <x:c r="H96" s="24" t="n">
+        <x:v>21.8</x:v>
+      </x:c>
       <x:c r="I96" s="25" t="n">
         <x:v>0.0073973532405837705</x:v>
       </x:c>
@@ -34693,7 +35615,9 @@
       <x:c r="G102" s="24" t="n">
         <x:v>3007.6</x:v>
       </x:c>
-      <x:c r="H102" s="24"/>
+      <x:c r="H102" s="24" t="n">
+        <x:v>38.8</x:v>
+      </x:c>
       <x:c r="I102" s="25" t="n">
         <x:v>0.013069253570466177</x:v>
       </x:c>
@@ -34727,7 +35651,9 @@
       <x:c r="G103" s="24" t="n">
         <x:v>3012</x:v>
       </x:c>
-      <x:c r="H103" s="24"/>
+      <x:c r="H103" s="24" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
       <x:c r="I103" s="25" t="n">
         <x:v>0.0014629605000664458</x:v>
       </x:c>
@@ -34761,7 +35687,9 @@
       <x:c r="G104" s="24" t="n">
         <x:v>2981.6</x:v>
       </x:c>
-      <x:c r="H104" s="24"/>
+      <x:c r="H104" s="24" t="n">
+        <x:v>-30.4</x:v>
+      </x:c>
       <x:c r="I104" s="25" t="n">
         <x:v>-0.010092961487383811</x:v>
       </x:c>
@@ -34795,7 +35723,9 @@
       <x:c r="G105" s="24" t="n">
         <x:v>3022.8</x:v>
       </x:c>
-      <x:c r="H105" s="24"/>
+      <x:c r="H105" s="24" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
       <x:c r="I105" s="25" t="n">
         <x:v>0.013818084250067253</x:v>
       </x:c>
@@ -34829,7 +35759,9 @@
       <x:c r="G106" s="24" t="n">
         <x:v>3029.2</x:v>
       </x:c>
-      <x:c r="H106" s="24"/>
+      <x:c r="H106" s="24" t="n">
+        <x:v>6.4</x:v>
+      </x:c>
       <x:c r="I106" s="25" t="n">
         <x:v>0.0021172422919146783</x:v>
       </x:c>
@@ -34863,7 +35795,9 @@
       <x:c r="G107" s="24" t="n">
         <x:v>3033</x:v>
       </x:c>
-      <x:c r="H107" s="24"/>
+      <x:c r="H107" s="24" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
       <x:c r="I107" s="25" t="n">
         <x:v>0.0012544566222105757</x:v>
       </x:c>
@@ -34897,7 +35831,9 @@
       <x:c r="G108" s="24" t="n">
         <x:v>2984.6</x:v>
       </x:c>
-      <x:c r="H108" s="24"/>
+      <x:c r="H108" s="24" t="n">
+        <x:v>-48.4</x:v>
+      </x:c>
       <x:c r="I108" s="25" t="n">
         <x:v>-0.01595779756017146</x:v>
       </x:c>
@@ -34931,7 +35867,9 @@
       <x:c r="G109" s="34" t="n">
         <x:v>2945</x:v>
       </x:c>
-      <x:c r="H109" s="34"/>
+      <x:c r="H109" s="34" t="n">
+        <x:v>-39.6</x:v>
+      </x:c>
       <x:c r="I109" s="35" t="n">
         <x:v>-0.013268109629431035</x:v>
       </x:c>
@@ -34965,7 +35903,9 @@
       <x:c r="G110" s="24" t="n">
         <x:v>2922.4</x:v>
       </x:c>
-      <x:c r="H110" s="24"/>
+      <x:c r="H110" s="24" t="n">
+        <x:v>-22.6</x:v>
+      </x:c>
       <x:c r="I110" s="25" t="n">
         <x:v>-0.007674023769100091</x:v>
       </x:c>
@@ -34999,7 +35939,9 @@
       <x:c r="G111" s="24" t="n">
         <x:v>2931.4</x:v>
       </x:c>
-      <x:c r="H111" s="24"/>
+      <x:c r="H111" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="I111" s="25" t="n">
         <x:v>0.0030796605529701537</x:v>
       </x:c>
@@ -35033,7 +35975,9 @@
       <x:c r="G112" s="24" t="n">
         <x:v>2934.8</x:v>
       </x:c>
-      <x:c r="H112" s="24"/>
+      <x:c r="H112" s="24" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
       <x:c r="I112" s="25" t="n">
         <x:v>0.0011598553592140348</x:v>
       </x:c>
@@ -35067,7 +36011,9 @@
       <x:c r="G113" s="24" t="n">
         <x:v>2903.8</x:v>
       </x:c>
-      <x:c r="H113" s="24"/>
+      <x:c r="H113" s="24" t="n">
+        <x:v>-31</x:v>
+      </x:c>
       <x:c r="I113" s="25" t="n">
         <x:v>-0.010562900367997785</x:v>
       </x:c>
@@ -35101,7 +36047,9 @@
       <x:c r="G114" s="24" t="n">
         <x:v>2899.2</x:v>
       </x:c>
-      <x:c r="H114" s="24"/>
+      <x:c r="H114" s="24" t="n">
+        <x:v>-4.6</x:v>
+      </x:c>
       <x:c r="I114" s="25" t="n">
         <x:v>-0.0015841311385083046</x:v>
       </x:c>
@@ -35135,7 +36083,9 @@
       <x:c r="G115" s="24" t="n">
         <x:v>2943.2</x:v>
       </x:c>
-      <x:c r="H115" s="24"/>
+      <x:c r="H115" s="24" t="n">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="I115" s="25" t="n">
         <x:v>0.015176600441501042</x:v>
       </x:c>
@@ -35169,7 +36119,9 @@
       <x:c r="G116" s="24" t="n">
         <x:v>2955.6</x:v>
       </x:c>
-      <x:c r="H116" s="24"/>
+      <x:c r="H116" s="24" t="n">
+        <x:v>12.4</x:v>
+      </x:c>
       <x:c r="I116" s="25" t="n">
         <x:v>0.00421310138624631</x:v>
       </x:c>
@@ -35203,7 +36155,9 @@
       <x:c r="G117" s="24" t="n">
         <x:v>2910.8</x:v>
       </x:c>
-      <x:c r="H117" s="24"/>
+      <x:c r="H117" s="24" t="n">
+        <x:v>-44.8</x:v>
+      </x:c>
       <x:c r="I117" s="25" t="n">
         <x:v>-0.015157666802002923</x:v>
       </x:c>
@@ -35237,7 +36191,9 @@
       <x:c r="G118" s="24" t="n">
         <x:v>2890.4</x:v>
       </x:c>
-      <x:c r="H118" s="24"/>
+      <x:c r="H118" s="24" t="n">
+        <x:v>-20.4</x:v>
+      </x:c>
       <x:c r="I118" s="25" t="n">
         <x:v>-0.00700838257523706</x:v>
       </x:c>
@@ -35271,7 +36227,9 @@
       <x:c r="G119" s="24" t="n">
         <x:v>2900.6</x:v>
       </x:c>
-      <x:c r="H119" s="24"/>
+      <x:c r="H119" s="24" t="n">
+        <x:v>10.2</x:v>
+      </x:c>
       <x:c r="I119" s="25" t="n">
         <x:v>0.003528923332410727</x:v>
       </x:c>
@@ -35393,7 +36351,9 @@
       <x:c r="G125" s="24" t="n">
         <x:v>2880.2</x:v>
       </x:c>
-      <x:c r="H125" s="24"/>
+      <x:c r="H125" s="24" t="n">
+        <x:v>-20.4</x:v>
+      </x:c>
       <x:c r="I125" s="25" t="n">
         <x:v>-0.007033027649451906</x:v>
       </x:c>
@@ -35427,7 +36387,9 @@
       <x:c r="G126" s="24" t="n">
         <x:v>2902.8</x:v>
       </x:c>
-      <x:c r="H126" s="24"/>
+      <x:c r="H126" s="24" t="n">
+        <x:v>22.6</x:v>
+      </x:c>
       <x:c r="I126" s="25" t="n">
         <x:v>0.007846677314075512</x:v>
       </x:c>
@@ -35461,7 +36423,9 @@
       <x:c r="G127" s="24" t="n">
         <x:v>2907.8</x:v>
       </x:c>
-      <x:c r="H127" s="24"/>
+      <x:c r="H127" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="I127" s="25" t="n">
         <x:v>0.0017224748518671618</x:v>
       </x:c>
@@ -35495,7 +36459,9 @@
       <x:c r="G128" s="24" t="n">
         <x:v>2871.8</x:v>
       </x:c>
-      <x:c r="H128" s="24"/>
+      <x:c r="H128" s="24" t="n">
+        <x:v>-36</x:v>
+      </x:c>
       <x:c r="I128" s="25" t="n">
         <x:v>-0.012380493844143303</x:v>
       </x:c>
@@ -35529,7 +36495,9 @@
       <x:c r="G129" s="24" t="n">
         <x:v>2844</x:v>
       </x:c>
-      <x:c r="H129" s="24"/>
+      <x:c r="H129" s="24" t="n">
+        <x:v>-27.8</x:v>
+      </x:c>
       <x:c r="I129" s="25" t="n">
         <x:v>-0.009680339856536047</x:v>
       </x:c>
@@ -35563,7 +36531,9 @@
       <x:c r="G130" s="24" t="n">
         <x:v>2813</x:v>
       </x:c>
-      <x:c r="H130" s="24"/>
+      <x:c r="H130" s="24" t="n">
+        <x:v>-31</x:v>
+      </x:c>
       <x:c r="I130" s="25" t="n">
         <x:v>-0.010900140646976086</x:v>
       </x:c>
@@ -35597,7 +36567,9 @@
       <x:c r="G131" s="24" t="n">
         <x:v>2817.2</x:v>
       </x:c>
-      <x:c r="H131" s="24"/>
+      <x:c r="H131" s="24" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
       <x:c r="I131" s="25" t="n">
         <x:v>0.0014930678990401347</x:v>
       </x:c>
@@ -35631,7 +36603,9 @@
       <x:c r="G132" s="24" t="n">
         <x:v>2833.8</x:v>
       </x:c>
-      <x:c r="H132" s="24"/>
+      <x:c r="H132" s="24" t="n">
+        <x:v>16.6</x:v>
+      </x:c>
       <x:c r="I132" s="25" t="n">
         <x:v>0.005892375408206751</x:v>
       </x:c>
@@ -35665,7 +36639,9 @@
       <x:c r="G133" s="24" t="n">
         <x:v>2835.8</x:v>
       </x:c>
-      <x:c r="H133" s="24"/>
+      <x:c r="H133" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I133" s="25" t="n">
         <x:v>0.0007057661091114387</x:v>
       </x:c>
@@ -35699,7 +36675,9 @@
       <x:c r="G134" s="24" t="n">
         <x:v>2897.2</x:v>
       </x:c>
-      <x:c r="H134" s="24"/>
+      <x:c r="H134" s="24" t="n">
+        <x:v>61.4</x:v>
+      </x:c>
       <x:c r="I134" s="25" t="n">
         <x:v>0.021651738486494043</x:v>
       </x:c>
@@ -35733,7 +36711,9 @@
       <x:c r="G135" s="24" t="n">
         <x:v>2938.6</x:v>
       </x:c>
-      <x:c r="H135" s="24"/>
+      <x:c r="H135" s="24" t="n">
+        <x:v>41.4</x:v>
+      </x:c>
       <x:c r="I135" s="25" t="n">
         <x:v>0.014289658981085251</x:v>
       </x:c>
@@ -35767,9 +36747,11 @@
       <x:c r="G136" s="24" t="n">
         <x:v>2911</x:v>
       </x:c>
-      <x:c r="H136" s="24"/>
+      <x:c r="H136" s="24" t="n">
+        <x:v>-27.6</x:v>
+      </x:c>
       <x:c r="I136" s="25" t="n">
-        <x:v>-0.02266385353569722</x:v>
+        <x:v>-0.00939222759137004</x:v>
       </x:c>
       <x:c r="J136" s="24" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -35801,9 +36783,11 @@
       <x:c r="G137" s="24" t="n">
         <x:v>2935</x:v>
       </x:c>
-      <x:c r="H137" s="24"/>
+      <x:c r="H137" s="24" t="n">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="I137" s="25" t="n">
-        <x:v>0.007799442896935904</x:v>
+        <x:v>0.008244589488148435</x:v>
       </x:c>
       <x:c r="J137" s="24" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -35835,9 +36819,11 @@
       <x:c r="G138" s="24" t="n">
         <x:v>2941</x:v>
       </x:c>
-      <x:c r="H138" s="24"/>
+      <x:c r="H138" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="I138" s="25" t="n">
-        <x:v>0.001865671641791078</x:v>
+        <x:v>0.002044293015332155</x:v>
       </x:c>
       <x:c r="J138" s="24" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -35869,9 +36855,11 @@
       <x:c r="G139" s="34" t="n">
         <x:v>2978</x:v>
       </x:c>
-      <x:c r="H139" s="34"/>
+      <x:c r="H139" s="34" t="n">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.026967377060486797</x:v>
+        <x:v>0.012580754845290754</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -35903,7 +36891,9 @@
       <x:c r="G140" s="24" t="n">
         <x:v>2884.6</x:v>
       </x:c>
-      <x:c r="H140" s="24"/>
+      <x:c r="H140" s="24" t="n">
+        <x:v>-93.4</x:v>
+      </x:c>
       <x:c r="I140" s="25" t="n">
         <x:v>-0.03136333109469447</x:v>
       </x:c>
@@ -35937,7 +36927,9 @@
       <x:c r="G141" s="24" t="n">
         <x:v>2896.2</x:v>
       </x:c>
-      <x:c r="H141" s="24"/>
+      <x:c r="H141" s="24" t="n">
+        <x:v>11.6</x:v>
+      </x:c>
       <x:c r="I141" s="25" t="n">
         <x:v>0.004021354780558761</x:v>
       </x:c>
@@ -35971,7 +36963,9 @@
       <x:c r="G142" s="24" t="n">
         <x:v>2924.8</x:v>
       </x:c>
-      <x:c r="H142" s="24"/>
+      <x:c r="H142" s="24" t="n">
+        <x:v>28.6</x:v>
+      </x:c>
       <x:c r="I142" s="25" t="n">
         <x:v>0.009875008632000748</x:v>
       </x:c>
@@ -36005,7 +36999,9 @@
       <x:c r="G143" s="24" t="n">
         <x:v>2859</x:v>
       </x:c>
-      <x:c r="H143" s="24"/>
+      <x:c r="H143" s="24" t="n">
+        <x:v>-65.8</x:v>
+      </x:c>
       <x:c r="I143" s="25" t="n">
         <x:v>-0.02249726477024072</x:v>
       </x:c>
@@ -36039,7 +37035,9 @@
       <x:c r="G144" s="24" t="n">
         <x:v>2928</x:v>
       </x:c>
-      <x:c r="H144" s="24"/>
+      <x:c r="H144" s="24" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="I144" s="25" t="n">
         <x:v>0.02413431269674704</x:v>
       </x:c>
@@ -36073,7 +37071,9 @@
       <x:c r="G145" s="24" t="n">
         <x:v>2938</x:v>
       </x:c>
-      <x:c r="H145" s="24"/>
+      <x:c r="H145" s="24" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="I145" s="25" t="n">
         <x:v>0.003415300546448119</x:v>
       </x:c>
@@ -36195,7 +37195,9 @@
       <x:c r="G151" s="24" t="n">
         <x:v>2934.6</x:v>
       </x:c>
-      <x:c r="H151" s="24"/>
+      <x:c r="H151" s="24" t="n">
+        <x:v>-3.4</x:v>
+      </x:c>
       <x:c r="I151" s="25" t="n">
         <x:v>-0.0011572498298162426</x:v>
       </x:c>
@@ -36229,7 +37231,9 @@
       <x:c r="G152" s="24" t="n">
         <x:v>2871</x:v>
       </x:c>
-      <x:c r="H152" s="24"/>
+      <x:c r="H152" s="24" t="n">
+        <x:v>-63.6</x:v>
+      </x:c>
       <x:c r="I152" s="25" t="n">
         <x:v>-0.02167245961970965</x:v>
       </x:c>
@@ -36263,7 +37267,9 @@
       <x:c r="G153" s="24" t="n">
         <x:v>2886.6</x:v>
       </x:c>
-      <x:c r="H153" s="24"/>
+      <x:c r="H153" s="24" t="n">
+        <x:v>15.6</x:v>
+      </x:c>
       <x:c r="I153" s="25" t="n">
         <x:v>0.005433646812957216</x:v>
       </x:c>
@@ -36297,7 +37303,9 @@
       <x:c r="G154" s="24" t="n">
         <x:v>2905.2</x:v>
       </x:c>
-      <x:c r="H154" s="24"/>
+      <x:c r="H154" s="24" t="n">
+        <x:v>18.6</x:v>
+      </x:c>
       <x:c r="I154" s="25" t="n">
         <x:v>0.00644356682602365</x:v>
       </x:c>
@@ -36331,7 +37339,9 @@
       <x:c r="G155" s="24" t="n">
         <x:v>2870.6</x:v>
       </x:c>
-      <x:c r="H155" s="24"/>
+      <x:c r="H155" s="24" t="n">
+        <x:v>-34.6</x:v>
+      </x:c>
       <x:c r="I155" s="25" t="n">
         <x:v>-0.01190967919592456</x:v>
       </x:c>
@@ -36365,7 +37375,9 @@
       <x:c r="G156" s="24" t="n">
         <x:v>2868</x:v>
       </x:c>
-      <x:c r="H156" s="24"/>
+      <x:c r="H156" s="24" t="n">
+        <x:v>-2.6</x:v>
+      </x:c>
       <x:c r="I156" s="25" t="n">
         <x:v>-0.0009057339928933983</x:v>
       </x:c>
@@ -36399,7 +37411,9 @@
       <x:c r="G157" s="24" t="n">
         <x:v>2939.8</x:v>
       </x:c>
-      <x:c r="H157" s="24"/>
+      <x:c r="H157" s="24" t="n">
+        <x:v>71.8</x:v>
+      </x:c>
       <x:c r="I157" s="25" t="n">
         <x:v>0.025034867503486824</x:v>
       </x:c>
@@ -36433,7 +37447,9 @@
       <x:c r="G158" s="24" t="n">
         <x:v>2910.2</x:v>
       </x:c>
-      <x:c r="H158" s="24"/>
+      <x:c r="H158" s="24" t="n">
+        <x:v>-29.6</x:v>
+      </x:c>
       <x:c r="I158" s="25" t="n">
         <x:v>-0.010068712157289772</x:v>
       </x:c>
@@ -36467,7 +37483,9 @@
       <x:c r="G159" s="24" t="n">
         <x:v>2872.6</x:v>
       </x:c>
-      <x:c r="H159" s="24"/>
+      <x:c r="H159" s="24" t="n">
+        <x:v>-37.6</x:v>
+      </x:c>
       <x:c r="I159" s="25" t="n">
         <x:v>-0.012920074221702937</x:v>
       </x:c>
@@ -36501,7 +37519,9 @@
       <x:c r="G160" s="24" t="n">
         <x:v>2891.2</x:v>
       </x:c>
-      <x:c r="H160" s="24"/>
+      <x:c r="H160" s="24" t="n">
+        <x:v>18.6</x:v>
+      </x:c>
       <x:c r="I160" s="25" t="n">
         <x:v>0.006474970410081493</x:v>
       </x:c>
@@ -36535,7 +37555,9 @@
       <x:c r="G161" s="24" t="n">
         <x:v>2914</x:v>
       </x:c>
-      <x:c r="H161" s="24"/>
+      <x:c r="H161" s="24" t="n">
+        <x:v>22.8</x:v>
+      </x:c>
       <x:c r="I161" s="25" t="n">
         <x:v>0.007885998893193191</x:v>
       </x:c>
@@ -36569,7 +37591,9 @@
       <x:c r="G162" s="24" t="n">
         <x:v>2867.8</x:v>
       </x:c>
-      <x:c r="H162" s="24"/>
+      <x:c r="H162" s="24" t="n">
+        <x:v>-46.2</x:v>
+      </x:c>
       <x:c r="I162" s="25" t="n">
         <x:v>-0.015854495538778268</x:v>
       </x:c>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf056ecd3e30b4e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R8fe51632a4444471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R36a98e053d5542ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf2135713d60c4f5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R9d880b69855c4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R7d94fba92f4547f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R7535b600b4434768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re1c7a7207f984472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rff185eb19b5a4e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re86ad8ffb9e74926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R87eafa3cf8914c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R188477d335404f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R6ad97c13fbd949dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rbd7f3d1a2cef4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4e38c9e4fccf447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R0357539c298e472c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rff185eb19b5a4e62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Re86ad8ffb9e74926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R87eafa3cf8914c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R188477d335404f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R6ad97c13fbd949dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rbd7f3d1a2cef4760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4e38c9e4fccf447e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R0357539c298e472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3f1bd54b26d444a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R4bbe3b5359a2493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8c3b548ad8ac4727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R1aeed9eed2ee4b3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rf3567544ed8c4ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R7a3b29e4d0544fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R2bd64dc709234c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re496a8066b804526"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3f1bd54b26d444a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R4bbe3b5359a2493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8c3b548ad8ac4727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R1aeed9eed2ee4b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rf3567544ed8c4ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R7a3b29e4d0544fb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R2bd64dc709234c20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re496a8066b804526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7d8e300044c3474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R81e45023cf654954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R696709bad88b447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R20a2c28f3b9a4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R594b7c2a8afd482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Ra894b411801841ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R2bd093c1386d487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R588d5fc3e3284aa4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -615,7 +615,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>23378.8</x:v>
+        <x:v>23369.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
         <x:v>182.6</x:v>
@@ -644,10 +644,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>24888.4</x:v>
+        <x:v>24814.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>194.4</x:v>
+        <x:v>193.9</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -673,10 +673,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9432.6</x:v>
+        <x:v>9389</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.7</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -702,10 +702,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5326.2</x:v>
+        <x:v>5305.2</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.6</x:v>
+        <x:v>41.4</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -21061,29 +21061,29 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="34" t="n">
-        <x:v>8546</x:v>
+        <x:v>8790</x:v>
       </x:c>
       <x:c r="E139" s="34" t="n">
-        <x:v>8558</x:v>
+        <x:v>8802.4</x:v>
       </x:c>
       <x:c r="F139" s="34" t="n">
-        <x:v>8367</x:v>
+        <x:v>8620.4</x:v>
       </x:c>
       <x:c r="G139" s="34" t="n">
-        <x:v>8524.2</x:v>
-      </x:c>
-      <x:c r="H139" s="27" t="n">
-        <x:v>-241.8</x:v>
+        <x:v>8774.2</x:v>
+      </x:c>
+      <x:c r="H139" s="34" t="n">
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>-0.02758384668035585</x:v>
-      </x:c>
-      <x:c r="J139" s="29" t="n">
+        <x:v>0.0009354323522701158</x:v>
+      </x:c>
+      <x:c r="J139" s="34" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
-        <x:v>191</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="K139" s="33" t="str">
-        <x:v>IM2609</x:v>
+        <x:v>IM2606</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -21108,11 +21108,11 @@
       <x:c r="G140" s="24" t="n">
         <x:v>8403</x:v>
       </x:c>
-      <x:c r="H140" s="24" t="n">
-        <x:v>-121.2</x:v>
+      <x:c r="H140" s="27" t="n">
+        <x:v>-371.2</x:v>
       </x:c>
       <x:c r="I140" s="25" t="n">
-        <x:v>-0.014218343070317552</x:v>
+        <x:v>-0.042305851245697745</x:v>
       </x:c>
       <x:c r="J140" s="29" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -21318,7 +21318,7 @@
       <x:c r="I146" s="37"/>
       <x:c r="J146" s="39" t="n">
         <x:f>ROUND(SUM(J125:J145),1)</x:f>
-        <x:v>3857.2</x:v>
+        <x:v>3848.2</x:v>
       </x:c>
       <x:c r="K146" s="37"/>
     </x:row>
@@ -21336,7 +21336,7 @@
       <x:c r="I147" s="37"/>
       <x:c r="J147" s="41" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
-        <x:v>183.7</x:v>
+        <x:v>183.2</x:v>
       </x:c>
       <x:c r="K147" s="37"/>
     </x:row>
@@ -26322,29 +26322,29 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="34" t="n">
-        <x:v>8536</x:v>
+        <x:v>8692.8</x:v>
       </x:c>
       <x:c r="E139" s="34" t="n">
-        <x:v>8677</x:v>
+        <x:v>8778.8</x:v>
       </x:c>
       <x:c r="F139" s="34" t="n">
-        <x:v>8432</x:v>
+        <x:v>8607.4</x:v>
       </x:c>
       <x:c r="G139" s="34" t="n">
-        <x:v>8650</x:v>
+        <x:v>8778.2</x:v>
       </x:c>
       <x:c r="H139" s="34" t="n">
-        <x:v>-32.8</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>-0.003777583268070095</x:v>
+        <x:v>0.010987239139448324</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
-        <x:v>245</x:v>
+        <x:v>171.4</x:v>
       </x:c>
       <x:c r="K139" s="33" t="str">
-        <x:v>IC2609</x:v>
+        <x:v>IC2606</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -26370,10 +26370,10 @@
         <x:v>8455</x:v>
       </x:c>
       <x:c r="H140" s="27" t="n">
-        <x:v>-195</x:v>
+        <x:v>-323.2</x:v>
       </x:c>
       <x:c r="I140" s="25" t="n">
-        <x:v>-0.02254335260115603</x:v>
+        <x:v>-0.03681848214896</x:v>
       </x:c>
       <x:c r="J140" s="29" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -26579,7 +26579,7 @@
       <x:c r="I146" s="37"/>
       <x:c r="J146" s="39" t="n">
         <x:f>ROUND(SUM(J125:J145),1)</x:f>
-        <x:v>4219.8</x:v>
+        <x:v>4146.2</x:v>
       </x:c>
       <x:c r="K146" s="37"/>
     </x:row>
@@ -26597,7 +26597,7 @@
       <x:c r="I147" s="37"/>
       <x:c r="J147" s="41" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
-        <x:v>200.9</x:v>
+        <x:v>197.4</x:v>
       </x:c>
       <x:c r="K147" s="37"/>
     </x:row>
@@ -31583,29 +31583,29 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="34" t="n">
-        <x:v>4852.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="E139" s="34" t="n">
-        <x:v>4987.4</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="F139" s="34" t="n">
-        <x:v>4838.8</x:v>
+        <x:v>4925.2</x:v>
       </x:c>
       <x:c r="G139" s="34" t="n">
-        <x:v>4983.8</x:v>
+        <x:v>5029.2</x:v>
       </x:c>
       <x:c r="H139" s="34" t="n">
-        <x:v>23.2</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.004676853606418563</x:v>
+        <x:v>0.013828972301737519</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
-        <x:v>148.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="K139" s="33" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -31631,10 +31631,10 @@
         <x:v>4812.4</x:v>
       </x:c>
       <x:c r="H140" s="27" t="n">
-        <x:v>-171.4</x:v>
+        <x:v>-216.8</x:v>
       </x:c>
       <x:c r="I140" s="25" t="n">
-        <x:v>-0.03439142822745711</x:v>
+        <x:v>-0.04310824783265732</x:v>
       </x:c>
       <x:c r="J140" s="29" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -31840,7 +31840,7 @@
       <x:c r="I146" s="37"/>
       <x:c r="J146" s="39" t="n">
         <x:f>ROUND(SUM(J125:J145),1)</x:f>
-        <x:v>1929</x:v>
+        <x:v>1885.4</x:v>
       </x:c>
       <x:c r="K146" s="37"/>
     </x:row>
@@ -31858,7 +31858,7 @@
       <x:c r="I147" s="37"/>
       <x:c r="J147" s="41" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
-        <x:v>91.9</x:v>
+        <x:v>89.8</x:v>
       </x:c>
       <x:c r="K147" s="37"/>
     </x:row>
@@ -36844,29 +36844,29 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="34" t="n">
-        <x:v>2896</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="E139" s="34" t="n">
-        <x:v>2982.2</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="F139" s="34" t="n">
-        <x:v>2883.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="G139" s="34" t="n">
-        <x:v>2978</x:v>
+        <x:v>2995.6</x:v>
       </x:c>
       <x:c r="H139" s="34" t="n">
-        <x:v>37</x:v>
+        <x:v>54.6</x:v>
       </x:c>
       <x:c r="I139" s="35" t="n">
-        <x:v>0.012580754845290754</x:v>
+        <x:v>0.018565113906834352</x:v>
       </x:c>
       <x:c r="J139" s="29" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="K139" s="33" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -36892,10 +36892,10 @@
         <x:v>2884.6</x:v>
       </x:c>
       <x:c r="H140" s="24" t="n">
-        <x:v>-93.4</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="I140" s="25" t="n">
-        <x:v>-0.03136333109469447</x:v>
+        <x:v>-0.037054346374682856</x:v>
       </x:c>
       <x:c r="J140" s="29" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -37101,7 +37101,7 @@
       <x:c r="I146" s="37"/>
       <x:c r="J146" s="39" t="n">
         <x:f>ROUND(SUM(J125:J145),1)</x:f>
-        <x:v>991.4</x:v>
+        <x:v>970.4</x:v>
       </x:c>
       <x:c r="K146" s="37"/>
     </x:row>
@@ -37119,7 +37119,7 @@
       <x:c r="I147" s="37"/>
       <x:c r="J147" s="41" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
-        <x:v>47.2</x:v>
+        <x:v>46.2</x:v>
       </x:c>
       <x:c r="K147" s="37"/>
     </x:row>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7d8e300044c3474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R81e45023cf654954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R696709bad88b447a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R20a2c28f3b9a4a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R594b7c2a8afd482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Ra894b411801841ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R2bd093c1386d487f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R588d5fc3e3284aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re24f06ff4259474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Rb88720c8ff5a430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8225427e7dd44ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R73027c3422bf4e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Ra716694001c240aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Re01c782eba92462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R260ebaf24b4a4954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R849d27b3b20342c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re24f06ff4259474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Rb88720c8ff5a430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8225427e7dd44ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R73027c3422bf4e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Ra716694001c240aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Re01c782eba92462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R260ebaf24b4a4954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R849d27b3b20342c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R65e74a90e97143e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R5c9e4393bf57461b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R917eba7abeac4d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R68ffe3e78fe247cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R4e665cce3b5742dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R485fa77a4e704cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4bfb2f691336487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rf1167e1966de463b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R65e74a90e97143e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R5c9e4393bf57461b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R917eba7abeac4d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R68ffe3e78fe247cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R4e665cce3b5742dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R485fa77a4e704cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R4bfb2f691336487c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rf1167e1966de463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rfa055c8ad6f34995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R4a0a1260488446e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R0e932be338994314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf641dba5fd6f4069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Raca53dd463174c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R52881cbc85174a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R8be1dc98055f4e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rfc3690bc4e0a46ad"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rfa055c8ad6f34995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R4a0a1260488446e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R0e932be338994314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf641dba5fd6f4069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Raca53dd463174c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R52881cbc85174a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R8be1dc98055f4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rfc3690bc4e0a46ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4f640cc4fb8a4ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R1f83cb0295bc4502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R33829206d7d74f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R9d9d2a723a024263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rbad007c5de3946b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R2e5c4cd448184090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R36dad2f9a5a7478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R6407075f52194c27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7836.39</x:v>
+        <x:v>7605.613</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7591.421</x:v>
+        <x:v>7163.309</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>245</x:v>
+        <x:v>442.3</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>22038.4</x:v>
+        <x:v>22480.7</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>172.2</x:v>
+        <x:v>174.3</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8148.042</x:v>
+        <x:v>7908.739</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7907.097</x:v>
+        <x:v>7474.151</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>240.9</x:v>
+        <x:v>434.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>22259.5</x:v>
+        <x:v>22694.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.9</x:v>
+        <x:v>175.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3940.451</x:v>
+        <x:v>3869.215</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3867.601</x:v>
+        <x:v>3745.174</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>72.8</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>6243.9</x:v>
+        <x:v>6367.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.8</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7750.2</x:v>
+        <x:v>7534.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7511</x:v>
+        <x:v>7018.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>239.2</x:v>
+        <x:v>515.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>23369.8</x:v>
+        <x:v>23885.6</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>182.6</x:v>
+        <x:v>185.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4712.6</x:v>
+        <x:v>4633.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4618</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>94.6</x:v>
+        <x:v>192.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9389</x:v>
+        <x:v>9581.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.4</x:v>
+        <x:v>74.3</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6040,30 +6040,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>2980.3</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>7599.388</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>7605.613</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>7163.309</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>7167.996</x:v>
+      </x:c>
+      <x:c r="H163" s="27" t="n">
+        <x:v>-463.8</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.06076788034008396</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>442.3</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -6071,11 +6089,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>248.4</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>3422.6</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>263.3</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11301,30 +11337,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>3125.3</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>7900.097</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>7908.739</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>7474.151</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>7513.763</x:v>
+      </x:c>
+      <x:c r="H163" s="27" t="n">
+        <x:v>-441.9</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.05554545792783605</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>434.6</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -11332,11 +11386,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>260.4</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>3559.9</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>273.8</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16562,30 +16634,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>808.2</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>3865.317</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>3869.215</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>3745.174</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>3764.155</x:v>
+      </x:c>
+      <x:c r="H163" s="34" t="n">
+        <x:v>-118.3</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.030459922733619527</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -16593,11 +16683,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>67.4</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>932.2</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>71.7</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -21823,30 +21931,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>2629.2</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>7520</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>7534.6</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>7018.8</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>7065.2</x:v>
+      </x:c>
+      <x:c r="H163" s="27" t="n">
+        <x:v>-487.4</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.06453406773826242</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>515.8</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -21854,11 +21980,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>219.1</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>3145</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>241.9</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32345,30 +32489,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>1133.8</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>4615.8</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>4633.8</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>4441.4</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="H163" s="27" t="n">
+        <x:v>-171.8</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.036981229550542505</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>192.4</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -32376,11 +32538,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>94.5</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>1326.2</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4f640cc4fb8a4ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R1f83cb0295bc4502"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R33829206d7d74f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R9d9d2a723a024263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rbad007c5de3946b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R2e5c4cd448184090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R36dad2f9a5a7478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R6407075f52194c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R9a2429961a14493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R221b58d075904301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R9da707cf8e3d467a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rb48f6db8ff43401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R602768505bd24b47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R30e2c3fa536e466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Ra81581c160c54bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Ra69471f60d174290"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8054.4</x:v>
+        <x:v>7848.2</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7823</x:v>
+        <x:v>7362.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>231.4</x:v>
+        <x:v>485.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>24814.8</x:v>
+        <x:v>25300.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>193.9</x:v>
+        <x:v>196.1</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2911.8</x:v>
+        <x:v>2864.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2853.4</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>58.4</x:v>
+        <x:v>82.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5305.2</x:v>
+        <x:v>5387.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.4</x:v>
+        <x:v>41.8</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -27228,30 +27228,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>2906.4</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>7842</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>7848.2</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>7362.8</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>7389</x:v>
+      </x:c>
+      <x:c r="H163" s="27" t="n">
+        <x:v>-480.6</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.06107044830741082</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>485.4</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -27259,11 +27277,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>242.2</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>3391.8</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>260.9</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -37786,30 +37822,48 @@
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B163" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C163" s="37"/>
-      <x:c r="D163" s="37"/>
-      <x:c r="E163" s="37"/>
-      <x:c r="F163" s="37"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="37"/>
-      <x:c r="I163" s="37"/>
-      <x:c r="J163" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J162),1)</x:f>
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="K163" s="37"/>
+      <x:c r="A163" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="34" t="n">
+        <x:v>2855</x:v>
+      </x:c>
+      <x:c r="E163" s="34" t="n">
+        <x:v>2864.8</x:v>
+      </x:c>
+      <x:c r="F163" s="34" t="n">
+        <x:v>2782.6</x:v>
+      </x:c>
+      <x:c r="G163" s="34" t="n">
+        <x:v>2796.4</x:v>
+      </x:c>
+      <x:c r="H163" s="34" t="n">
+        <x:v>-71.4</x:v>
+      </x:c>
+      <x:c r="I163" s="35" t="n">
+        <x:v>-0.024897133691331397</x:v>
+      </x:c>
+      <x:c r="J163" s="29" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>82.2</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B164" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B164" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C164" s="37"/>
       <x:c r="D164" s="37"/>
       <x:c r="E164" s="37"/>
@@ -37817,11 +37871,29 @@
       <x:c r="G164" s="37"/>
       <x:c r="H164" s="37"/>
       <x:c r="I164" s="37"/>
-      <x:c r="J164" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J162),0),1)</x:f>
-        <x:v>54.1</x:v>
+      <x:c r="J164" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J163),1)</x:f>
+        <x:v>731.2</x:v>
       </x:c>
       <x:c r="K164" s="37"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B165" s="37"/>
+      <x:c r="C165" s="37"/>
+      <x:c r="D165" s="37"/>
+      <x:c r="E165" s="37"/>
+      <x:c r="F165" s="37"/>
+      <x:c r="G165" s="37"/>
+      <x:c r="H165" s="37"/>
+      <x:c r="I165" s="37"/>
+      <x:c r="J165" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
+        <x:v>56.2</x:v>
+      </x:c>
+      <x:c r="K165" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R9a2429961a14493a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R221b58d075904301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R9da707cf8e3d467a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rb48f6db8ff43401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R602768505bd24b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R30e2c3fa536e466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Ra81581c160c54bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Ra69471f60d174290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5ad15876a003463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R6e352e6131954932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Ra385c05ee6324697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf5c058a63c304c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R674728ba21ea48f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R2e937ad6b04c4b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R86d2fcec6ee54cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R2d3deb4cca0f43c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7605.613</x:v>
+        <x:v>7298.122</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7163.309</x:v>
+        <x:v>6824.145</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>442.3</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>22480.7</x:v>
+        <x:v>22954.7</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.3</x:v>
+        <x:v>176.6</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7908.739</x:v>
+        <x:v>7626.489</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7474.151</x:v>
+        <x:v>7253.518</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>434.6</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>22694.1</x:v>
+        <x:v>23067.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>175.9</x:v>
+        <x:v>177.4</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3869.215</x:v>
+        <x:v>3831.659</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3745.174</x:v>
+        <x:v>3741.11</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>124</x:v>
+        <x:v>90.5</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>6367.9</x:v>
+        <x:v>6458.4</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.4</x:v>
+        <x:v>49.7</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7534.6</x:v>
+        <x:v>7237</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7018.8</x:v>
+        <x:v>6652.2</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>515.8</x:v>
+        <x:v>584.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>23885.6</x:v>
+        <x:v>24470.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>185.2</x:v>
+        <x:v>188.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7848.2</x:v>
+        <x:v>7561.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7362.8</x:v>
+        <x:v>7092</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>485.4</x:v>
+        <x:v>469.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>25300.2</x:v>
+        <x:v>25770</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>196.1</x:v>
+        <x:v>198.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4633.8</x:v>
+        <x:v>4590</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>192.4</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9581.4</x:v>
+        <x:v>9706.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.3</x:v>
+        <x:v>74.7</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2864.8</x:v>
+        <x:v>2884.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>82.2</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5387.4</x:v>
+        <x:v>5452</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.8</x:v>
+        <x:v>41.9</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-17</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6076,30 +6076,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>3422.6</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>7256.267</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>7298.122</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>6824.145</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>6965.376</x:v>
+      </x:c>
+      <x:c r="H164" s="27" t="n">
+        <x:v>-202.6</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>-0.028267314881314065</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -6107,11 +6125,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>263.3</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>3896.6</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>278.3</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11373,30 +11409,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>3559.9</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>7597.769</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>7626.489</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>7253.518</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>7411.313</x:v>
+      </x:c>
+      <x:c r="H164" s="24" t="n">
+        <x:v>-102.4</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>-0.013634978904711215</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -11404,11 +11458,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>273.8</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>3932.9</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>280.9</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16670,30 +16742,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>932.2</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>3791.662</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>3831.659</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>3741.11</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>3796.281</x:v>
+      </x:c>
+      <x:c r="H164" s="24" t="n">
+        <x:v>32.1</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>0.008534717619226528</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>90.5</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -16701,11 +16791,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>71.7</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>1022.7</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>73.1</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -21967,30 +22075,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>3145</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>7165.2</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>7237</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>6652.2</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>6849.8</x:v>
+      </x:c>
+      <x:c r="H164" s="27" t="n">
+        <x:v>-215.4</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>-0.030487459661439065</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>584.8</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -21998,11 +22124,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>241.9</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>3729.8</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>266.4</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -27264,30 +27408,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>3391.8</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>7490</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>7561.8</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>7092</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>7302.2</x:v>
+      </x:c>
+      <x:c r="H164" s="24" t="n">
+        <x:v>-86.8</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>-0.011747191771552368</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>469.8</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -27295,11 +27457,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>260.9</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>3861.6</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>275.8</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32561,30 +32741,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>1326.2</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>4590</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>4465</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>4545.8</x:v>
+      </x:c>
+      <x:c r="H164" s="24" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>0.016093701104206604</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -32592,11 +32790,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>102</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>1451.2</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>103.7</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -37858,30 +38074,48 @@
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B164" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C164" s="37"/>
-      <x:c r="D164" s="37"/>
-      <x:c r="E164" s="37"/>
-      <x:c r="F164" s="37"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="37"/>
-      <x:c r="I164" s="37"/>
-      <x:c r="J164" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J163),1)</x:f>
-        <x:v>731.2</x:v>
-      </x:c>
-      <x:c r="K164" s="37"/>
+      <x:c r="A164" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="23" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="23" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="24" t="n">
+        <x:v>2820</x:v>
+      </x:c>
+      <x:c r="E164" s="24" t="n">
+        <x:v>2884.6</x:v>
+      </x:c>
+      <x:c r="F164" s="24" t="n">
+        <x:v>2820</x:v>
+      </x:c>
+      <x:c r="G164" s="24" t="n">
+        <x:v>2874</x:v>
+      </x:c>
+      <x:c r="H164" s="24" t="n">
+        <x:v>77.6</x:v>
+      </x:c>
+      <x:c r="I164" s="25" t="n">
+        <x:v>0.027749964239736746</x:v>
+      </x:c>
+      <x:c r="J164" s="29" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>64.6</x:v>
+      </x:c>
+      <x:c r="K164" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B165" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B165" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C165" s="37"/>
       <x:c r="D165" s="37"/>
       <x:c r="E165" s="37"/>
@@ -37889,11 +38123,29 @@
       <x:c r="G165" s="37"/>
       <x:c r="H165" s="37"/>
       <x:c r="I165" s="37"/>
-      <x:c r="J165" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J163),0),1)</x:f>
-        <x:v>56.2</x:v>
+      <x:c r="J165" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J164),1)</x:f>
+        <x:v>795.8</x:v>
       </x:c>
       <x:c r="K165" s="37"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B166" s="37"/>
+      <x:c r="C166" s="37"/>
+      <x:c r="D166" s="37"/>
+      <x:c r="E166" s="37"/>
+      <x:c r="F166" s="37"/>
+      <x:c r="G166" s="37"/>
+      <x:c r="H166" s="37"/>
+      <x:c r="I166" s="37"/>
+      <x:c r="J166" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
+        <x:v>56.8</x:v>
+      </x:c>
+      <x:c r="K166" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5ad15876a003463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R6e352e6131954932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Ra385c05ee6324697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rf5c058a63c304c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R674728ba21ea48f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R2e937ad6b04c4b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R86d2fcec6ee54cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R2d3deb4cca0f43c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re5cdcff448254e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R52c86837cca04706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R611737feed584a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R6d10f9a299714cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R969d91a342d14c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rf17b65d90fdc49b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R9fdb8338e477428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R7f26382d222b4397"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re5cdcff448254e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R52c86837cca04706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R611737feed584a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R6d10f9a299714cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R969d91a342d14c38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rf17b65d90fdc49b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R9fdb8338e477428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R7f26382d222b4397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0ce7b2c12e294836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R6c8f0e6122894292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8283cbebed974b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R745f681fd0de4aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R8f7a8758cfb541b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rf3ddedf796e8480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R53cd06f52fb243c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R4a41a83bba424f80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7298.122</x:v>
+        <x:v>7264.338</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>6824.145</x:v>
+        <x:v>6714.187</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>474</x:v>
+        <x:v>550.2</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>22954.7</x:v>
+        <x:v>23504.9</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>176.6</x:v>
+        <x:v>179.4</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7626.489</x:v>
+        <x:v>7802.755</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7253.518</x:v>
+        <x:v>7270.954</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>373</x:v>
+        <x:v>531.8</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>23067.1</x:v>
+        <x:v>23598.9</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>177.4</x:v>
+        <x:v>180.1</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3831.659</x:v>
+        <x:v>3864.6</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3741.11</x:v>
+        <x:v>3743.36</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>90.5</x:v>
+        <x:v>121.2</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>6458.4</x:v>
+        <x:v>6579.6</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.7</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7237</x:v>
+        <x:v>7175.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6652.2</x:v>
+        <x:v>6641.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>584.8</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>24470.4</x:v>
+        <x:v>25004.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>188.2</x:v>
+        <x:v>190.9</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7561.8</x:v>
+        <x:v>7700.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7092</x:v>
+        <x:v>7201.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>469.8</x:v>
+        <x:v>499.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>25770</x:v>
+        <x:v>26269.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>198.2</x:v>
+        <x:v>200.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4590</x:v>
+        <x:v>4673.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4465</x:v>
+        <x:v>4524.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>125</x:v>
+        <x:v>149.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9706.4</x:v>
+        <x:v>9855.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.7</x:v>
+        <x:v>75.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2884.6</x:v>
+        <x:v>2933</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2820</x:v>
+        <x:v>2875.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>64.6</x:v>
+        <x:v>57.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5452</x:v>
+        <x:v>5509.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.9</x:v>
+        <x:v>42.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6112,30 +6112,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>3896.6</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>6975.893</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>7264.338</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>6714.187</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>7259.863</x:v>
+      </x:c>
+      <x:c r="H165" s="27" t="n">
+        <x:v>294.5</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.042278693928367916</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>550.2</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -6143,11 +6161,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>278.3</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>4446.8</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>296.5</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11445,30 +11481,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>3932.9</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>7437.452</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>7802.755</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>7270.954</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>7800.609</x:v>
+      </x:c>
+      <x:c r="H165" s="27" t="n">
+        <x:v>389.3</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.052527264737031176</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>531.8</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -11476,11 +11530,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>280.9</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>4464.7</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>297.6</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16778,30 +16850,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>1022.7</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>3812.162</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>3864.6</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>3743.36</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>3864.367</x:v>
+      </x:c>
+      <x:c r="H165" s="24" t="n">
+        <x:v>68.1</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.01793492104509653</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>121.2</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -16809,11 +16899,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>73.1</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>1143.9</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>76.3</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -22111,30 +22219,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>3729.8</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>6920</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>7175.8</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>6641.8</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>7164.4</x:v>
+      </x:c>
+      <x:c r="H165" s="27" t="n">
+        <x:v>314.6</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.04592834827294223</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -22142,11 +22268,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>266.4</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>4263.8</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>284.3</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -27444,30 +27588,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>3861.6</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>7385</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>7700.6</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>7201.2</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>7685.8</x:v>
+      </x:c>
+      <x:c r="H165" s="27" t="n">
+        <x:v>383.6</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.052532113609597086</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>499.4</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -27475,11 +27637,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>275.8</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>4361</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>290.7</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32777,30 +32957,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>1451.2</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>4563.8</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>4673.8</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>4524.4</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>4662.4</x:v>
+      </x:c>
+      <x:c r="H165" s="24" t="n">
+        <x:v>116.6</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.02565005059615455</x:v>
+      </x:c>
+      <x:c r="J165" s="29" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>149.4</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -32808,11 +33006,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>103.7</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>1600.6</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>106.7</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -38110,30 +38326,48 @@
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B165" s="37" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C165" s="37"/>
-      <x:c r="D165" s="37"/>
-      <x:c r="E165" s="37"/>
-      <x:c r="F165" s="37"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="37"/>
-      <x:c r="I165" s="37"/>
-      <x:c r="J165" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J164),1)</x:f>
-        <x:v>795.8</x:v>
-      </x:c>
-      <x:c r="K165" s="37"/>
+      <x:c r="A165" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="23" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="23" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="24" t="n">
+        <x:v>2896</x:v>
+      </x:c>
+      <x:c r="E165" s="24" t="n">
+        <x:v>2933</x:v>
+      </x:c>
+      <x:c r="F165" s="24" t="n">
+        <x:v>2875.2</x:v>
+      </x:c>
+      <x:c r="G165" s="24" t="n">
+        <x:v>2923.6</x:v>
+      </x:c>
+      <x:c r="H165" s="24" t="n">
+        <x:v>49.6</x:v>
+      </x:c>
+      <x:c r="I165" s="25" t="n">
+        <x:v>0.017258176757132926</x:v>
+      </x:c>
+      <x:c r="J165" s="24" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>57.8</x:v>
+      </x:c>
+      <x:c r="K165" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B166" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B166" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C166" s="37"/>
       <x:c r="D166" s="37"/>
       <x:c r="E166" s="37"/>
@@ -38141,11 +38375,29 @@
       <x:c r="G166" s="37"/>
       <x:c r="H166" s="37"/>
       <x:c r="I166" s="37"/>
-      <x:c r="J166" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J164),0),1)</x:f>
-        <x:v>56.8</x:v>
+      <x:c r="J166" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J165),1)</x:f>
+        <x:v>853.6</x:v>
       </x:c>
       <x:c r="K166" s="37"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B167" s="37"/>
+      <x:c r="C167" s="37"/>
+      <x:c r="D167" s="37"/>
+      <x:c r="E167" s="37"/>
+      <x:c r="F167" s="37"/>
+      <x:c r="G167" s="37"/>
+      <x:c r="H167" s="37"/>
+      <x:c r="I167" s="37"/>
+      <x:c r="J167" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
+        <x:v>56.9</x:v>
+      </x:c>
+      <x:c r="K167" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0ce7b2c12e294836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R6c8f0e6122894292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R8283cbebed974b3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R745f681fd0de4aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R8f7a8758cfb541b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rf3ddedf796e8480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R53cd06f52fb243c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R4a41a83bba424f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R2e9f26dc86504946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Rc09582f6c7564852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R0eee4b19ab814ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R4201b1f83d8c403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Reda37498a2a3419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rabef3ee9c0a44b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R50a251651b4a4d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re21e668f6ab04180"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R2e9f26dc86504946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Rc09582f6c7564852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R0eee4b19ab814ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R4201b1f83d8c403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Reda37498a2a3419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rabef3ee9c0a44b53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R50a251651b4a4d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re21e668f6ab04180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R18fe0f356eb44e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R2d41416728ca4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R43fe62ae4c9d439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rfcd2b86069e14fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R470f928a7d9e4439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rfe43e0ff7636403a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R23c4bded53ad4ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R95a648f9d33b4974"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7264.338</x:v>
+        <x:v>7302.454</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>6714.187</x:v>
+        <x:v>7118.66</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>550.2</x:v>
+        <x:v>183.8</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>23504.9</x:v>
+        <x:v>23688.7</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.4</x:v>
+        <x:v>179.5</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7802.755</x:v>
+        <x:v>7889.446</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7270.954</x:v>
+        <x:v>7701.221</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>531.8</x:v>
+        <x:v>188.2</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>23598.9</x:v>
+        <x:v>23787.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.1</x:v>
+        <x:v>180.2</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,22 +571,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3864.6</x:v>
+        <x:v>3884.435</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3743.36</x:v>
+        <x:v>3839.665</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>121.2</x:v>
+        <x:v>44.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>6579.6</x:v>
+        <x:v>6624.4</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>50.2</x:v>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7175.8</x:v>
+        <x:v>7194.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6641.8</x:v>
+        <x:v>6985.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>534</x:v>
+        <x:v>208.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>25004.4</x:v>
+        <x:v>25213.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.9</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7700.6</x:v>
+        <x:v>7765.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7201.2</x:v>
+        <x:v>7583.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>499.4</x:v>
+        <x:v>181.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>26269.4</x:v>
+        <x:v>26451.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>200.5</x:v>
+        <x:v>200.4</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6148,30 +6148,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>4446.8</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>7196.863</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>7302.454</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>7118.66</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>7158.762</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>-101.1</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>-0.01392602036705104</x:v>
+      </x:c>
+      <x:c r="J166" s="29" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>183.8</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -6179,11 +6197,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>296.5</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>4630.6</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>289.4</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11517,30 +11553,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>4464.7</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>7741.906</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>7889.446</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>7701.221</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>7751.662</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>-48.9</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>-0.006274766495795392</x:v>
+      </x:c>
+      <x:c r="J166" s="29" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>188.2</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -11548,11 +11602,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>297.6</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>4652.9</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>290.8</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16886,30 +16958,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>1143.9</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>3839.665</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>3884.435</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>3839.665</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>3867.034</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>0.0006901518411681629</x:v>
+      </x:c>
+      <x:c r="J166" s="24" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>44.8</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -16917,11 +17007,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>76.3</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>1188.7</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>74.3</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -22255,30 +22363,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>4263.8</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>7148</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>7194.6</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>6985.8</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>7028.8</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>-135.6</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>-0.018926916420076934</x:v>
+      </x:c>
+      <x:c r="J166" s="29" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>208.8</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -22286,11 +22412,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>284.3</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>4472.6</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>279.5</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -27624,30 +27768,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>4361</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>7674.8</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>7765.6</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>7583.8</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>7611</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>-74.8</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>-0.009732233469515239</x:v>
+      </x:c>
+      <x:c r="J166" s="29" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>181.8</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -27655,11 +27817,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>290.7</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>4542.8</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>283.9</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R18fe0f356eb44e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R2d41416728ca4140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R43fe62ae4c9d439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rfcd2b86069e14fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R470f928a7d9e4439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rfe43e0ff7636403a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R23c4bded53ad4ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R95a648f9d33b4974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4db2ec7023f24fc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R57802ffead0a409f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R6083b0fc7abb435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rc8a417d0bb594ceb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rf7ce6d9953484f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R504fd7771ce94782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R61679556b2924348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R660fa40fca9747b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -658,22 +658,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4673.8</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4524.4</x:v>
+        <x:v>4634</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>149.4</x:v>
+        <x:v>73.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9855.8</x:v>
+        <x:v>9929.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>75.2</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2933</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2875.2</x:v>
+        <x:v>2906</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>57.8</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5509.8</x:v>
+        <x:v>5581.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.1</x:v>
+        <x:v>42.3</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -33173,30 +33173,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>1600.6</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>4652</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>4707.8</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>4634</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>4648</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>-14.4</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>-0.003088538091969739</x:v>
+      </x:c>
+      <x:c r="J166" s="24" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>73.8</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -33204,11 +33222,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>106.7</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>1674.4</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>104.7</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -38542,30 +38578,48 @@
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B166" s="37" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C166" s="37"/>
-      <x:c r="D166" s="37"/>
-      <x:c r="E166" s="37"/>
-      <x:c r="F166" s="37"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="37"/>
-      <x:c r="I166" s="37"/>
-      <x:c r="J166" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J165),1)</x:f>
-        <x:v>853.6</x:v>
-      </x:c>
-      <x:c r="K166" s="37"/>
+      <x:c r="A166" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="23" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="23" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="24" t="n">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="E166" s="24" t="n">
+        <x:v>2978</x:v>
+      </x:c>
+      <x:c r="F166" s="24" t="n">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="G166" s="24" t="n">
+        <x:v>2946.2</x:v>
+      </x:c>
+      <x:c r="H166" s="24" t="n">
+        <x:v>22.6</x:v>
+      </x:c>
+      <x:c r="I166" s="25" t="n">
+        <x:v>0.007730195649199523</x:v>
+      </x:c>
+      <x:c r="J166" s="29" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K166" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B167" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B167" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C167" s="37"/>
       <x:c r="D167" s="37"/>
       <x:c r="E167" s="37"/>
@@ -38573,11 +38627,29 @@
       <x:c r="G167" s="37"/>
       <x:c r="H167" s="37"/>
       <x:c r="I167" s="37"/>
-      <x:c r="J167" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J165),0),1)</x:f>
-        <x:v>56.9</x:v>
+      <x:c r="J167" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J166),1)</x:f>
+        <x:v>925.6</x:v>
       </x:c>
       <x:c r="K167" s="37"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B168" s="37"/>
+      <x:c r="C168" s="37"/>
+      <x:c r="D168" s="37"/>
+      <x:c r="E168" s="37"/>
+      <x:c r="F168" s="37"/>
+      <x:c r="G168" s="37"/>
+      <x:c r="H168" s="37"/>
+      <x:c r="I168" s="37"/>
+      <x:c r="J168" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
+        <x:v>57.9</x:v>
+      </x:c>
+      <x:c r="K168" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4db2ec7023f24fc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R57802ffead0a409f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R6083b0fc7abb435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rc8a417d0bb594ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="Rf7ce6d9953484f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="R504fd7771ce94782"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="R61679556b2924348"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="R660fa40fca9747b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra0bd1f0dfeea4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R73d1f475940f4614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R52285659c785480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R24cb3882f7964619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R3143dfcfee604770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rd0fa8a4c3a454b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Re9eeb3ae70b941ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re765a711fbb14fa5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -513,25 +513,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7302.454</x:v>
+        <x:v>7247.141</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7118.66</x:v>
+        <x:v>7113.498</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>183.8</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>23688.7</x:v>
+        <x:v>23822.3</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.5</x:v>
+        <x:v>179.1</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -542,25 +542,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7889.446</x:v>
+        <x:v>7795.35</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7701.221</x:v>
+        <x:v>7658.999</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>188.2</x:v>
+        <x:v>136.4</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>23787.1</x:v>
+        <x:v>23923.5</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.2</x:v>
+        <x:v>179.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -571,25 +571,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3884.435</x:v>
+        <x:v>3878.832</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3839.665</x:v>
+        <x:v>3851.706</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>44.8</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>6624.4</x:v>
+        <x:v>6651.5</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>50.2</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -719,7 +719,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6184,30 +6184,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>4630.6</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>7169.543</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>7247.141</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>7113.498</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>7195.5</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>36.7</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>0.0051318929166803695</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>133.6</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -6215,11 +6233,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>289.4</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>4764.2</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>280.2</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11589,30 +11625,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>4652.9</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>7750.852</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>7795.35</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>7658.999</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>7734.31</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>-17.4</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>-0.0022384876946388577</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>136.4</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -11620,11 +11674,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>290.8</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>4789.3</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>281.7</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16994,30 +17066,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>1188.7</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>3868.087</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>3878.832</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>3851.706</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>3876.777</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>9.7</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>0.0025195020266177703</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>27.1</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -17025,11 +17115,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>74.3</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>1215.8</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>71.5</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra0bd1f0dfeea4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="R73d1f475940f4614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="R52285659c785480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="R24cb3882f7964619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R3143dfcfee604770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Rd0fa8a4c3a454b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Re9eeb3ae70b941ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Re765a711fbb14fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1c1d92b8e64d4d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="2" r:id="Ra61e23724cfd4172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="3" r:id="Rc677b357c68b4cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="4" r:id="Rc41f4fc19bb3495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="5" r:id="R3b11653c7f694452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="6" r:id="Reaed2a3310954de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="7" r:id="Rb4c04a546a224b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="8" r:id="Rb7bd71e618424370"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -600,25 +600,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7194.6</x:v>
+        <x:v>7159.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6985.8</x:v>
+        <x:v>7000.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>208.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>25213.2</x:v>
+        <x:v>25372.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>191</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -629,25 +629,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7765.6</x:v>
+        <x:v>7693</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7583.8</x:v>
+        <x:v>7538</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>181.8</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>26451.2</x:v>
+        <x:v>26606.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>200.4</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -658,25 +658,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4682.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4634</x:v>
+        <x:v>4644</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>73.8</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>9929.6</x:v>
+        <x:v>9968.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.2</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -687,25 +687,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2978</x:v>
+        <x:v>2969.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2906</x:v>
+        <x:v>2938.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>72</x:v>
+        <x:v>30.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5581.8</x:v>
+        <x:v>5612.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.3</x:v>
+        <x:v>42.2</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -22507,30 +22507,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>4472.6</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>7061</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>7159.6</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>7000.6</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>7071.6</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>42.8</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>0.0060892328704758025</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -22538,11 +22556,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>279.5</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>4631.6</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>272.4</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -27912,30 +27948,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>4542.8</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>7675</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>7693</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>7538</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>7602.6</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>-8.4</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>-0.0011036657469452038</x:v>
+      </x:c>
+      <x:c r="J167" s="29" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -27943,11 +27997,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>283.9</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>4697.8</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>276.3</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -33317,30 +33389,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>1674.4</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>4670</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>4682.6</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>4644</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>4661.4</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>13.4</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>0.002882960413080893</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>38.6</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -33348,11 +33438,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>104.7</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>1713</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>100.8</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -38722,30 +38830,48 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="37" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C167" s="37"/>
-      <x:c r="D167" s="37"/>
-      <x:c r="E167" s="37"/>
-      <x:c r="F167" s="37"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="37"/>
-      <x:c r="I167" s="37"/>
-      <x:c r="J167" s="39" t="n">
-        <x:f>ROUND(SUM(J151:J166),1)</x:f>
-        <x:v>925.6</x:v>
-      </x:c>
-      <x:c r="K167" s="37"/>
+      <x:c r="A167" s="23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="23" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="24" t="n">
+        <x:v>2960</x:v>
+      </x:c>
+      <x:c r="E167" s="24" t="n">
+        <x:v>2969.6</x:v>
+      </x:c>
+      <x:c r="F167" s="24" t="n">
+        <x:v>2938.8</x:v>
+      </x:c>
+      <x:c r="G167" s="24" t="n">
+        <x:v>2948.8</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="I167" s="25" t="n">
+        <x:v>0.0008824927024642104</x:v>
+      </x:c>
+      <x:c r="J167" s="24" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>30.8</x:v>
+      </x:c>
+      <x:c r="K167" s="23" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="38" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="37"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C168" s="37"/>
       <x:c r="D168" s="37"/>
       <x:c r="E168" s="37"/>
@@ -38753,11 +38879,29 @@
       <x:c r="G168" s="37"/>
       <x:c r="H168" s="37"/>
       <x:c r="I168" s="37"/>
-      <x:c r="J168" s="41" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J151:J166),0),1)</x:f>
-        <x:v>57.9</x:v>
+      <x:c r="J168" s="39" t="n">
+        <x:f>ROUND(SUM(J151:J167),1)</x:f>
+        <x:v>956.4</x:v>
       </x:c>
       <x:c r="K168" s="37"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="38" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="37"/>
+      <x:c r="C169" s="37"/>
+      <x:c r="D169" s="37"/>
+      <x:c r="E169" s="37"/>
+      <x:c r="F169" s="37"/>
+      <x:c r="G169" s="37"/>
+      <x:c r="H169" s="37"/>
+      <x:c r="I169" s="37"/>
+      <x:c r="J169" s="41" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J167),0),1)</x:f>
+        <x:v>56.3</x:v>
+      </x:c>
+      <x:c r="K169" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb184a3527d0c400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R24408505fc6d4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R1913d3ea3efd4dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rafa2f9289cb24c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R38dfe0bdf3b0465b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra6afd9aaaf9a4c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rac837b4922784d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2cd8191f21694895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rc5865d43f8674fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3199b6950f2a4ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb16ad1f12d3a49c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R029473326a1946d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfc16f9f7d9404c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8e724223d5e7472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1a1a4818f4254187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R93ad701685144551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R47ece9aa86414d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R56e9983a7b2f4c2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -605,25 +605,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7205</x:v>
+        <x:v>7064.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6986</x:v>
+        <x:v>6976</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>219</x:v>
+        <x:v>88.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>26827.8</x:v>
+        <x:v>26916</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>193</x:v>
+        <x:v>192.3</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -5671,155 +5671,155 @@
       </x:c>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B139" s="30" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C139" s="30"/>
-      <x:c r="D139" s="30"/>
-      <x:c r="E139" s="30"/>
-      <x:c r="F139" s="30"/>
-      <x:c r="G139" s="30"/>
-      <x:c r="H139" s="30"/>
-      <x:c r="I139" s="32" t="n">
-        <x:f>ROUND(SUM(I110:I138),1)</x:f>
-        <x:v>12730</x:v>
-      </x:c>
-      <x:c r="J139" s="30"/>
-      <x:c r="K139" s="30"/>
+      <x:c r="A139" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B139" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="C139" s="23" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="D139" s="23" t="n">
+        <x:v>7064.2</x:v>
+      </x:c>
+      <x:c r="E139" s="23" t="n">
+        <x:v>6976</x:v>
+      </x:c>
+      <x:c r="F139" s="23" t="n">
+        <x:v>7023.4</x:v>
+      </x:c>
+      <x:c r="G139" s="23" t="n">
+        <x:f>ROUND(F139-F138,1)</x:f>
+        <x:v>35.6</x:v>
+      </x:c>
+      <x:c r="H139" s="24" t="n">
+        <x:f>IFERROR(F139/F138-1,"")</x:f>
+        <x:v>0.005094593434270989</x:v>
+      </x:c>
+      <x:c r="I139" s="23" t="n">
+        <x:f>ROUND(D139-E139,1)</x:f>
+        <x:v>88.2</x:v>
+      </x:c>
+      <x:c r="J139" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+      <x:c r="K139" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B140" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B140" s="30" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C140" s="30"/>
       <x:c r="D140" s="30"/>
       <x:c r="E140" s="30"/>
       <x:c r="F140" s="30"/>
       <x:c r="G140" s="30"/>
       <x:c r="H140" s="30"/>
-      <x:c r="I140" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I110:I138),0),1)</x:f>
-        <x:v>439</x:v>
+      <x:c r="I140" s="32" t="n">
+        <x:f>ROUND(SUM(I110:I139),1)</x:f>
+        <x:v>12818.2</x:v>
       </x:c>
       <x:c r="J140" s="30"/>
       <x:c r="K140" s="30"/>
     </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="17" t="str">
+    <x:row r="141">
+      <x:c r="A141" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B141" s="30"/>
+      <x:c r="C141" s="30"/>
+      <x:c r="D141" s="30"/>
+      <x:c r="E141" s="30"/>
+      <x:c r="F141" s="30"/>
+      <x:c r="G141" s="30"/>
+      <x:c r="H141" s="30"/>
+      <x:c r="I141" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I110:I139),0),1)</x:f>
+        <x:v>427.3</x:v>
+      </x:c>
+      <x:c r="J141" s="30"/>
+      <x:c r="K141" s="30"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="17" t="str">
         <x:v>IC主力</x:v>
       </x:c>
-      <x:c r="B142" s="17"/>
-      <x:c r="C142" s="17"/>
-      <x:c r="D142" s="17"/>
-      <x:c r="E142" s="17"/>
-      <x:c r="F142" s="17"/>
-      <x:c r="G142" s="17"/>
-      <x:c r="H142" s="17"/>
-      <x:c r="I142" s="17"/>
-      <x:c r="J142" s="17"/>
-      <x:c r="K142" s="17"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="20" t="str">
+      <x:c r="B143" s="17"/>
+      <x:c r="C143" s="17"/>
+      <x:c r="D143" s="17"/>
+      <x:c r="E143" s="17"/>
+      <x:c r="F143" s="17"/>
+      <x:c r="G143" s="17"/>
+      <x:c r="H143" s="17"/>
+      <x:c r="I143" s="17"/>
+      <x:c r="J143" s="17"/>
+      <x:c r="K143" s="17"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B143" s="20" t="str">
+      <x:c r="B144" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C143" s="20" t="str">
+      <x:c r="C144" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D143" s="20" t="str">
+      <x:c r="D144" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E143" s="20" t="str">
+      <x:c r="E144" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F143" s="20" t="str">
+      <x:c r="F144" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G143" s="20" t="str">
+      <x:c r="G144" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H143" s="20" t="str">
+      <x:c r="H144" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I143" s="20" t="str">
+      <x:c r="I144" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J143" s="20" t="str">
+      <x:c r="J144" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K143" s="20" t="str">
+      <x:c r="K144" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B144" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C144" s="23" t="n">
-        <x:v>7424.4</x:v>
-      </x:c>
-      <x:c r="D144" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="E144" s="23" t="n">
-        <x:v>7422</x:v>
-      </x:c>
-      <x:c r="F144" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="G144" s="23"/>
-      <x:c r="H144" s="24"/>
-      <x:c r="I144" s="26" t="n">
-        <x:f>ROUND(D144-E144,1)</x:f>
-        <x:v>615.8</x:v>
-      </x:c>
-      <x:c r="J144" s="22" t="str">
-        <x:v>IC2603</x:v>
-      </x:c>
-      <x:c r="K144" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B145" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C145" s="23" t="n">
-        <x:v>8099</x:v>
+        <x:v>7424.4</x:v>
       </x:c>
       <x:c r="D145" s="23" t="n">
-        <x:v>8388.6</x:v>
+        <x:v>8037.8</x:v>
       </x:c>
       <x:c r="E145" s="23" t="n">
-        <x:v>8044</x:v>
+        <x:v>7422</x:v>
       </x:c>
       <x:c r="F145" s="23" t="n">
-        <x:v>8210.4</x:v>
-      </x:c>
-      <x:c r="G145" s="28" t="n">
-        <x:f>ROUND(F145-F144,1)</x:f>
-        <x:v>172.6</x:v>
-      </x:c>
-      <x:c r="H145" s="24" t="n">
-        <x:f>IFERROR(F145/F144-1,"")</x:f>
-        <x:v>0.02147353753514647</x:v>
-      </x:c>
+        <x:v>8037.8</x:v>
+      </x:c>
+      <x:c r="G145" s="23"/>
+      <x:c r="H145" s="24"/>
       <x:c r="I145" s="26" t="n">
         <x:f>ROUND(D145-E145,1)</x:f>
-        <x:v>344.6</x:v>
+        <x:v>615.8</x:v>
       </x:c>
       <x:c r="J145" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -5830,34 +5830,34 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B146" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C146" s="23" t="n">
-        <x:v>8182.6</x:v>
+        <x:v>8099</x:v>
       </x:c>
       <x:c r="D146" s="23" t="n">
-        <x:v>8660</x:v>
+        <x:v>8388.6</x:v>
       </x:c>
       <x:c r="E146" s="23" t="n">
-        <x:v>8112</x:v>
+        <x:v>8044</x:v>
       </x:c>
       <x:c r="F146" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8210.4</x:v>
       </x:c>
       <x:c r="G146" s="28" t="n">
         <x:f>ROUND(F146-F145,1)</x:f>
-        <x:v>447.8</x:v>
+        <x:v>172.6</x:v>
       </x:c>
       <x:c r="H146" s="24" t="n">
         <x:f>IFERROR(F146/F145-1,"")</x:f>
-        <x:v>0.05454058267563111</x:v>
+        <x:v>0.02147353753514647</x:v>
       </x:c>
       <x:c r="I146" s="26" t="n">
         <x:f>ROUND(D146-E146,1)</x:f>
-        <x:v>548</x:v>
+        <x:v>344.6</x:v>
       </x:c>
       <x:c r="J146" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -5868,34 +5868,34 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B147" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C147" s="23" t="n">
-        <x:v>8695</x:v>
+        <x:v>8182.6</x:v>
       </x:c>
       <x:c r="D147" s="23" t="n">
-        <x:v>8728.2</x:v>
+        <x:v>8660</x:v>
       </x:c>
       <x:c r="E147" s="23" t="n">
-        <x:v>8135</x:v>
+        <x:v>8112</x:v>
       </x:c>
       <x:c r="F147" s="23" t="n">
-        <x:v>8362.4</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="G147" s="28" t="n">
         <x:f>ROUND(F147-F146,1)</x:f>
-        <x:v>-295.8</x:v>
+        <x:v>447.8</x:v>
       </x:c>
       <x:c r="H147" s="24" t="n">
         <x:f>IFERROR(F147/F146-1,"")</x:f>
-        <x:v>-0.03416414497239628</x:v>
+        <x:v>0.05454058267563111</x:v>
       </x:c>
       <x:c r="I147" s="26" t="n">
         <x:f>ROUND(D147-E147,1)</x:f>
-        <x:v>593.2</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J147" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -5906,34 +5906,34 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B148" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C148" s="23" t="n">
-        <x:v>8262.2</x:v>
+        <x:v>8695</x:v>
       </x:c>
       <x:c r="D148" s="23" t="n">
-        <x:v>8334.4</x:v>
+        <x:v>8728.2</x:v>
       </x:c>
       <x:c r="E148" s="23" t="n">
-        <x:v>7832</x:v>
+        <x:v>8135</x:v>
       </x:c>
       <x:c r="F148" s="23" t="n">
-        <x:v>8117.4</x:v>
+        <x:v>8362.4</x:v>
       </x:c>
       <x:c r="G148" s="28" t="n">
         <x:f>ROUND(F148-F147,1)</x:f>
-        <x:v>-245</x:v>
+        <x:v>-295.8</x:v>
       </x:c>
       <x:c r="H148" s="24" t="n">
         <x:f>IFERROR(F148/F147-1,"")</x:f>
-        <x:v>-0.029297809241366157</x:v>
+        <x:v>-0.03416414497239628</x:v>
       </x:c>
       <x:c r="I148" s="26" t="n">
         <x:f>ROUND(D148-E148,1)</x:f>
-        <x:v>502.4</x:v>
+        <x:v>593.2</x:v>
       </x:c>
       <x:c r="J148" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -5944,34 +5944,34 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B149" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C149" s="23" t="n">
-        <x:v>8260</x:v>
+        <x:v>8262.2</x:v>
       </x:c>
       <x:c r="D149" s="23" t="n">
-        <x:v>8458.8</x:v>
+        <x:v>8334.4</x:v>
       </x:c>
       <x:c r="E149" s="23" t="n">
-        <x:v>8220</x:v>
+        <x:v>7832</x:v>
       </x:c>
       <x:c r="F149" s="23" t="n">
-        <x:v>8274.8</x:v>
+        <x:v>8117.4</x:v>
       </x:c>
       <x:c r="G149" s="28" t="n">
         <x:f>ROUND(F149-F148,1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>-245</x:v>
       </x:c>
       <x:c r="H149" s="24" t="n">
         <x:f>IFERROR(F149/F148-1,"")</x:f>
-        <x:v>0.019390445216448615</x:v>
+        <x:v>-0.029297809241366157</x:v>
       </x:c>
       <x:c r="I149" s="26" t="n">
         <x:f>ROUND(D149-E149,1)</x:f>
-        <x:v>238.8</x:v>
+        <x:v>502.4</x:v>
       </x:c>
       <x:c r="J149" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -5982,110 +5982,110 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B150" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C150" s="23" t="n">
-        <x:v>8360</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="D150" s="23" t="n">
-        <x:v>8650</x:v>
+        <x:v>8458.8</x:v>
       </x:c>
       <x:c r="E150" s="23" t="n">
-        <x:v>8314</x:v>
+        <x:v>8220</x:v>
       </x:c>
       <x:c r="F150" s="23" t="n">
-        <x:v>8645.4</x:v>
+        <x:v>8274.8</x:v>
       </x:c>
       <x:c r="G150" s="28" t="n">
         <x:f>ROUND(F150-F149,1)</x:f>
-        <x:v>370.6</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="H150" s="24" t="n">
         <x:f>IFERROR(F150/F149-1,"")</x:f>
-        <x:v>0.04478658094455468</x:v>
+        <x:v>0.019390445216448615</x:v>
       </x:c>
       <x:c r="I150" s="26" t="n">
         <x:f>ROUND(D150-E150,1)</x:f>
-        <x:v>336</x:v>
+        <x:v>238.8</x:v>
       </x:c>
       <x:c r="J150" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K150" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B151" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C151" s="23" t="n">
-        <x:v>8600</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="D151" s="23" t="n">
-        <x:v>8686</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="E151" s="23" t="n">
-        <x:v>8180.6</x:v>
+        <x:v>8314</x:v>
       </x:c>
       <x:c r="F151" s="23" t="n">
-        <x:v>8322.6</x:v>
+        <x:v>8645.4</x:v>
       </x:c>
       <x:c r="G151" s="28" t="n">
         <x:f>ROUND(F151-F150,1)</x:f>
-        <x:v>-322.8</x:v>
+        <x:v>370.6</x:v>
       </x:c>
       <x:c r="H151" s="24" t="n">
         <x:f>IFERROR(F151/F150-1,"")</x:f>
-        <x:v>-0.03733777500173496</x:v>
+        <x:v>0.04478658094455468</x:v>
       </x:c>
       <x:c r="I151" s="26" t="n">
         <x:f>ROUND(D151-E151,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="J151" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K151" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B152" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C152" s="23" t="n">
-        <x:v>8201.8</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="D152" s="23" t="n">
-        <x:v>8434.4</x:v>
+        <x:v>8686</x:v>
       </x:c>
       <x:c r="E152" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>8180.6</x:v>
       </x:c>
       <x:c r="F152" s="23" t="n">
-        <x:v>8213.8</x:v>
-      </x:c>
-      <x:c r="G152" s="23" t="n">
+        <x:v>8322.6</x:v>
+      </x:c>
+      <x:c r="G152" s="28" t="n">
         <x:f>ROUND(F152-F151,1)</x:f>
-        <x:v>-108.8</x:v>
+        <x:v>-322.8</x:v>
       </x:c>
       <x:c r="H152" s="24" t="n">
         <x:f>IFERROR(F152/F151-1,"")</x:f>
-        <x:v>-0.013072837815106042</x:v>
+        <x:v>-0.03733777500173496</x:v>
       </x:c>
       <x:c r="I152" s="26" t="n">
         <x:f>ROUND(D152-E152,1)</x:f>
-        <x:v>724.4</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J152" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -6096,34 +6096,34 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B153" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C153" s="23" t="n">
-        <x:v>8225.2</x:v>
+        <x:v>8201.8</x:v>
       </x:c>
       <x:c r="D153" s="23" t="n">
-        <x:v>8229.6</x:v>
+        <x:v>8434.4</x:v>
       </x:c>
       <x:c r="E153" s="23" t="n">
-        <x:v>7827.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="F153" s="23" t="n">
-        <x:v>7844.4</x:v>
-      </x:c>
-      <x:c r="G153" s="28" t="n">
+        <x:v>8213.8</x:v>
+      </x:c>
+      <x:c r="G153" s="23" t="n">
         <x:f>ROUND(F153-F152,1)</x:f>
-        <x:v>-369.4</x:v>
+        <x:v>-108.8</x:v>
       </x:c>
       <x:c r="H153" s="24" t="n">
         <x:f>IFERROR(F153/F152-1,"")</x:f>
-        <x:v>-0.04497309406121397</x:v>
+        <x:v>-0.013072837815106042</x:v>
       </x:c>
       <x:c r="I153" s="26" t="n">
         <x:f>ROUND(D153-E153,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>724.4</x:v>
       </x:c>
       <x:c r="J153" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -6134,37 +6134,37 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B154" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C154" s="23" t="n">
-        <x:v>7460</x:v>
+        <x:v>8225.2</x:v>
       </x:c>
       <x:c r="D154" s="23" t="n">
-        <x:v>7652</x:v>
+        <x:v>8229.6</x:v>
       </x:c>
       <x:c r="E154" s="23" t="n">
-        <x:v>7171</x:v>
+        <x:v>7827.8</x:v>
       </x:c>
       <x:c r="F154" s="23" t="n">
-        <x:v>7559.2</x:v>
+        <x:v>7844.4</x:v>
       </x:c>
       <x:c r="G154" s="28" t="n">
         <x:f>ROUND(F154-F153,1)</x:f>
-        <x:v>-285.2</x:v>
+        <x:v>-369.4</x:v>
       </x:c>
       <x:c r="H154" s="24" t="n">
         <x:f>IFERROR(F154/F153-1,"")</x:f>
-        <x:v>-0.03635714649941357</x:v>
+        <x:v>-0.04497309406121397</x:v>
       </x:c>
       <x:c r="I154" s="26" t="n">
         <x:f>ROUND(D154-E154,1)</x:f>
-        <x:v>481</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J154" s="22" t="str">
-        <x:v>IC2606</x:v>
+        <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K154" s="22" t="n">
         <x:v>5</x:v>
@@ -6172,34 +6172,34 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B155" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C155" s="23" t="n">
-        <x:v>7470.8</x:v>
+        <x:v>7460</x:v>
       </x:c>
       <x:c r="D155" s="23" t="n">
-        <x:v>7619</x:v>
+        <x:v>7652</x:v>
       </x:c>
       <x:c r="E155" s="23" t="n">
-        <x:v>7325.2</x:v>
+        <x:v>7171</x:v>
       </x:c>
       <x:c r="F155" s="23" t="n">
-        <x:v>7352</x:v>
+        <x:v>7559.2</x:v>
       </x:c>
       <x:c r="G155" s="28" t="n">
         <x:f>ROUND(F155-F154,1)</x:f>
-        <x:v>-207.2</x:v>
+        <x:v>-285.2</x:v>
       </x:c>
       <x:c r="H155" s="24" t="n">
         <x:f>IFERROR(F155/F154-1,"")</x:f>
-        <x:v>-0.02741030796909727</x:v>
+        <x:v>-0.03635714649941357</x:v>
       </x:c>
       <x:c r="I155" s="26" t="n">
         <x:f>ROUND(D155-E155,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="J155" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6210,110 +6210,110 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B156" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C156" s="23" t="n">
-        <x:v>7380</x:v>
+        <x:v>7470.8</x:v>
       </x:c>
       <x:c r="D156" s="23" t="n">
-        <x:v>7945.4</x:v>
+        <x:v>7619</x:v>
       </x:c>
       <x:c r="E156" s="23" t="n">
-        <x:v>7355.6</x:v>
+        <x:v>7325.2</x:v>
       </x:c>
       <x:c r="F156" s="23" t="n">
-        <x:v>7828.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="G156" s="28" t="n">
         <x:f>ROUND(F156-F155,1)</x:f>
-        <x:v>476.6</x:v>
+        <x:v>-207.2</x:v>
       </x:c>
       <x:c r="H156" s="24" t="n">
         <x:f>IFERROR(F156/F155-1,"")</x:f>
-        <x:v>0.06482589771490765</x:v>
+        <x:v>-0.02741030796909727</x:v>
       </x:c>
       <x:c r="I156" s="26" t="n">
         <x:f>ROUND(D156-E156,1)</x:f>
-        <x:v>589.8</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J156" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K156" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B157" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C157" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>8119.6</x:v>
+        <x:v>7945.4</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7355.6</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>8098.8</x:v>
+        <x:v>7828.6</x:v>
       </x:c>
       <x:c r="G157" s="28" t="n">
         <x:f>ROUND(F157-F156,1)</x:f>
-        <x:v>270.2</x:v>
+        <x:v>476.6</x:v>
       </x:c>
       <x:c r="H157" s="24" t="n">
         <x:f>IFERROR(F157/F156-1,"")</x:f>
-        <x:v>0.034514472574917576</x:v>
+        <x:v>0.06482589771490765</x:v>
       </x:c>
       <x:c r="I157" s="26" t="n">
         <x:f>ROUND(D157-E157,1)</x:f>
-        <x:v>327.6</x:v>
+        <x:v>589.8</x:v>
       </x:c>
       <x:c r="J157" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K157" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B158" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C158" s="23" t="n">
-        <x:v>8076.4</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>8288.2</x:v>
+        <x:v>8119.6</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>8042</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>8132.8</x:v>
-      </x:c>
-      <x:c r="G158" s="23" t="n">
+        <x:v>8098.8</x:v>
+      </x:c>
+      <x:c r="G158" s="28" t="n">
         <x:f>ROUND(F158-F157,1)</x:f>
-        <x:v>34</x:v>
+        <x:v>270.2</x:v>
       </x:c>
       <x:c r="H158" s="24" t="n">
         <x:f>IFERROR(F158/F157-1,"")</x:f>
-        <x:v>0.004198152812762368</x:v>
+        <x:v>0.034514472574917576</x:v>
       </x:c>
       <x:c r="I158" s="26" t="n">
         <x:f>ROUND(D158-E158,1)</x:f>
-        <x:v>246.2</x:v>
+        <x:v>327.6</x:v>
       </x:c>
       <x:c r="J158" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6324,148 +6324,148 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
-        <x:v>8145.2</x:v>
+        <x:v>8076.4</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>8287.8</x:v>
+        <x:v>8288.2</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>8056.2</x:v>
+        <x:v>8042</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>8270</x:v>
+        <x:v>8132.8</x:v>
       </x:c>
       <x:c r="G159" s="23" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>137.2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>0.016869958685815423</x:v>
+        <x:v>0.004198152812762368</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
-        <x:v>231.6</x:v>
+        <x:v>246.2</x:v>
       </x:c>
       <x:c r="J159" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B160" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C160" s="23" t="n">
-        <x:v>8377.6</x:v>
+        <x:v>8145.2</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>8648</x:v>
+        <x:v>8287.8</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>8375.4</x:v>
+        <x:v>8056.2</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>8620.8</x:v>
-      </x:c>
-      <x:c r="G160" s="28" t="n">
+        <x:v>8270</x:v>
+      </x:c>
+      <x:c r="G160" s="23" t="n">
         <x:f>ROUND(F160-F159,1)</x:f>
-        <x:v>350.8</x:v>
+        <x:v>137.2</x:v>
       </x:c>
       <x:c r="H160" s="24" t="n">
         <x:f>IFERROR(F160/F159-1,"")</x:f>
-        <x:v>0.042418379685610574</x:v>
+        <x:v>0.016869958685815423</x:v>
       </x:c>
       <x:c r="I160" s="26" t="n">
         <x:f>ROUND(D160-E160,1)</x:f>
-        <x:v>272.6</x:v>
+        <x:v>231.6</x:v>
       </x:c>
       <x:c r="J160" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K160" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B161" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C161" s="23" t="n">
-        <x:v>8691</x:v>
+        <x:v>8377.6</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>8886.8</x:v>
+        <x:v>8648</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>8378.2</x:v>
+        <x:v>8375.4</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>8448.8</x:v>
+        <x:v>8620.8</x:v>
       </x:c>
       <x:c r="G161" s="28" t="n">
         <x:f>ROUND(F161-F160,1)</x:f>
-        <x:v>-172</x:v>
+        <x:v>350.8</x:v>
       </x:c>
       <x:c r="H161" s="24" t="n">
         <x:f>IFERROR(F161/F160-1,"")</x:f>
-        <x:v>-0.01995174461766891</x:v>
+        <x:v>0.042418379685610574</x:v>
       </x:c>
       <x:c r="I161" s="26" t="n">
         <x:f>ROUND(D161-E161,1)</x:f>
-        <x:v>508.6</x:v>
+        <x:v>272.6</x:v>
       </x:c>
       <x:c r="J161" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K161" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B162" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C162" s="23" t="n">
-        <x:v>8418.4</x:v>
+        <x:v>8691</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>8728</x:v>
+        <x:v>8886.8</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
-        <x:v>8310</x:v>
+        <x:v>8378.2</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>8469.2</x:v>
-      </x:c>
-      <x:c r="G162" s="23" t="n">
+        <x:v>8448.8</x:v>
+      </x:c>
+      <x:c r="G162" s="28" t="n">
         <x:f>ROUND(F162-F161,1)</x:f>
-        <x:v>20.4</x:v>
+        <x:v>-172</x:v>
       </x:c>
       <x:c r="H162" s="24" t="n">
         <x:f>IFERROR(F162/F161-1,"")</x:f>
-        <x:v>0.0024145440772656013</x:v>
+        <x:v>-0.01995174461766891</x:v>
       </x:c>
       <x:c r="I162" s="26" t="n">
         <x:f>ROUND(D162-E162,1)</x:f>
-        <x:v>418</x:v>
+        <x:v>508.6</x:v>
       </x:c>
       <x:c r="J162" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6476,34 +6476,34 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
-        <x:v>8543</x:v>
+        <x:v>8418.4</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8728</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
-        <x:v>8218.2</x:v>
+        <x:v>8310</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>8274.6</x:v>
-      </x:c>
-      <x:c r="G163" s="28" t="n">
+        <x:v>8469.2</x:v>
+      </x:c>
+      <x:c r="G163" s="23" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>-194.6</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>-0.022977376847872377</x:v>
+        <x:v>0.0024145440772656013</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>440</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6514,34 +6514,34 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B164" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C164" s="23" t="n">
-        <x:v>8298</x:v>
+        <x:v>8543</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>8425</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>8101.6</x:v>
+        <x:v>8218.2</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>8190.6</x:v>
-      </x:c>
-      <x:c r="G164" s="23" t="n">
+        <x:v>8274.6</x:v>
+      </x:c>
+      <x:c r="G164" s="28" t="n">
         <x:f>ROUND(F164-F163,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-194.6</x:v>
       </x:c>
       <x:c r="H164" s="24" t="n">
         <x:f>IFERROR(F164/F163-1,"")</x:f>
-        <x:v>-0.010151548111086983</x:v>
+        <x:v>-0.022977376847872377</x:v>
       </x:c>
       <x:c r="I164" s="26" t="n">
         <x:f>ROUND(D164-E164,1)</x:f>
-        <x:v>323.4</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="J164" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6552,34 +6552,34 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B165" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C165" s="23" t="n">
-        <x:v>8050</x:v>
+        <x:v>8298</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>8237.6</x:v>
+        <x:v>8425</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>7838</x:v>
+        <x:v>8101.6</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>8117.2</x:v>
+        <x:v>8190.6</x:v>
       </x:c>
       <x:c r="G165" s="23" t="n">
         <x:f>ROUND(F165-F164,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H165" s="24" t="n">
         <x:f>IFERROR(F165/F164-1,"")</x:f>
-        <x:v>-0.008961492442556174</x:v>
+        <x:v>-0.010151548111086983</x:v>
       </x:c>
       <x:c r="I165" s="26" t="n">
         <x:f>ROUND(D165-E165,1)</x:f>
-        <x:v>399.6</x:v>
+        <x:v>323.4</x:v>
       </x:c>
       <x:c r="J165" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -6590,113 +6590,113 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B166" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C166" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>8718</x:v>
+        <x:v>8237.6</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>7838</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
-        <x:v>8682.8</x:v>
-      </x:c>
-      <x:c r="G166" s="28" t="n">
+        <x:v>8117.2</x:v>
+      </x:c>
+      <x:c r="G166" s="23" t="n">
         <x:f>ROUND(F166-F165,1)</x:f>
-        <x:v>565.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H166" s="24" t="n">
         <x:f>IFERROR(F166/F165-1,"")</x:f>
-        <x:v>0.06967919972404268</x:v>
+        <x:v>-0.008961492442556174</x:v>
       </x:c>
       <x:c r="I166" s="26" t="n">
         <x:f>ROUND(D166-E166,1)</x:f>
-        <x:v>536.8</x:v>
+        <x:v>399.6</x:v>
       </x:c>
       <x:c r="J166" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K166" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
-        <x:v>8692.8</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>8778.8</x:v>
+        <x:v>8718</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>8377</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>8447</x:v>
+        <x:v>8682.8</x:v>
       </x:c>
       <x:c r="G167" s="28" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-235.8</x:v>
+        <x:v>565.6</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.027157138250333945</x:v>
+        <x:v>0.06967919972404268</x:v>
       </x:c>
       <x:c r="I167" s="26" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>536.8</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
-        <x:v>IC2606/IC2609</x:v>
+        <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K167" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B168" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C168" s="23" t="n">
-        <x:v>8463.8</x:v>
+        <x:v>8692.8</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>8873.8</x:v>
+        <x:v>8778.8</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>8350.4</x:v>
+        <x:v>8377</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>8538</x:v>
-      </x:c>
-      <x:c r="G168" s="23" t="n">
+        <x:v>8447</x:v>
+      </x:c>
+      <x:c r="G168" s="28" t="n">
         <x:f>ROUND(F168-F167,1)</x:f>
-        <x:v>91</x:v>
+        <x:v>-235.8</x:v>
       </x:c>
       <x:c r="H168" s="24" t="n">
         <x:f>IFERROR(F168/F167-1,"")</x:f>
-        <x:v>0.010773055522670827</x:v>
+        <x:v>-0.027157138250333945</x:v>
       </x:c>
       <x:c r="I168" s="26" t="n">
         <x:f>ROUND(D168-E168,1)</x:f>
-        <x:v>523.4</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J168" s="22" t="str">
-        <x:v>IC2609</x:v>
+        <x:v>IC2606/IC2609</x:v>
       </x:c>
       <x:c r="K168" s="22" t="n">
         <x:v>5</x:v>
@@ -6704,34 +6704,34 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B169" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C169" s="23" t="n">
-        <x:v>8574.4</x:v>
+        <x:v>8463.8</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>8618</x:v>
+        <x:v>8873.8</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>8173</x:v>
+        <x:v>8350.4</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>8333</x:v>
-      </x:c>
-      <x:c r="G169" s="28" t="n">
+        <x:v>8538</x:v>
+      </x:c>
+      <x:c r="G169" s="23" t="n">
         <x:f>ROUND(F169-F168,1)</x:f>
-        <x:v>-205</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H169" s="24" t="n">
         <x:f>IFERROR(F169/F168-1,"")</x:f>
-        <x:v>-0.024010306863434083</x:v>
+        <x:v>0.010773055522670827</x:v>
       </x:c>
       <x:c r="I169" s="26" t="n">
         <x:f>ROUND(D169-E169,1)</x:f>
-        <x:v>445</x:v>
+        <x:v>523.4</x:v>
       </x:c>
       <x:c r="J169" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -6742,34 +6742,34 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B170" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C170" s="23" t="n">
-        <x:v>8303</x:v>
+        <x:v>8574.4</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>8328</x:v>
+        <x:v>8618</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>7362.8</x:v>
+        <x:v>8173</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>7389</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="G170" s="28" t="n">
         <x:f>ROUND(F170-F169,1)</x:f>
-        <x:v>-944</x:v>
+        <x:v>-205</x:v>
       </x:c>
       <x:c r="H170" s="24" t="n">
         <x:f>IFERROR(F170/F169-1,"")</x:f>
-        <x:v>-0.11328453138125527</x:v>
+        <x:v>-0.024010306863434083</x:v>
       </x:c>
       <x:c r="I170" s="26" t="n">
         <x:f>ROUND(D170-E170,1)</x:f>
-        <x:v>965.2</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="J170" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -6780,34 +6780,34 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B171" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C171" s="23" t="n">
-        <x:v>7490</x:v>
+        <x:v>8303</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>7765.6</x:v>
+        <x:v>8328</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>7092</x:v>
+        <x:v>7362.8</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>7416</x:v>
-      </x:c>
-      <x:c r="G171" s="23" t="n">
+        <x:v>7389</x:v>
+      </x:c>
+      <x:c r="G171" s="28" t="n">
         <x:f>ROUND(F171-F170,1)</x:f>
-        <x:v>27</x:v>
+        <x:v>-944</x:v>
       </x:c>
       <x:c r="H171" s="24" t="n">
         <x:f>IFERROR(F171/F170-1,"")</x:f>
-        <x:v>0.0036540803897686658</x:v>
+        <x:v>-0.11328453138125527</x:v>
       </x:c>
       <x:c r="I171" s="26" t="n">
         <x:f>ROUND(D171-E171,1)</x:f>
-        <x:v>673.6</x:v>
+        <x:v>965.2</x:v>
       </x:c>
       <x:c r="J171" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -6818,34 +6818,34 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B172" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C172" s="23" t="n">
-        <x:v>7447</x:v>
+        <x:v>7490</x:v>
       </x:c>
       <x:c r="D172" s="23" t="n">
-        <x:v>7666.6</x:v>
+        <x:v>7765.6</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>7106</x:v>
+        <x:v>7092</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>7395</x:v>
+        <x:v>7416</x:v>
       </x:c>
       <x:c r="G172" s="23" t="n">
         <x:f>ROUND(F172-F171,1)</x:f>
-        <x:v>-21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H172" s="24" t="n">
         <x:f>IFERROR(F172/F171-1,"")</x:f>
-        <x:v>-0.0028317152103559673</x:v>
+        <x:v>0.0036540803897686658</x:v>
       </x:c>
       <x:c r="I172" s="26" t="n">
         <x:f>ROUND(D172-E172,1)</x:f>
-        <x:v>560.6</x:v>
+        <x:v>673.6</x:v>
       </x:c>
       <x:c r="J172" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -6856,192 +6856,192 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B173" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C173" s="23" t="n">
-        <x:v>7391</x:v>
+        <x:v>7447</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>7440</x:v>
+        <x:v>7666.6</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>7335</x:v>
+        <x:v>7106</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>7356</x:v>
+        <x:v>7395</x:v>
       </x:c>
       <x:c r="G173" s="23" t="n">
         <x:f>ROUND(F173-F172,1)</x:f>
-        <x:v>-39</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="H173" s="24" t="n">
         <x:f>IFERROR(F173/F172-1,"")</x:f>
-        <x:v>-0.005273833671399553</x:v>
-      </x:c>
-      <x:c r="I173" s="23" t="n">
+        <x:v>-0.0028317152103559673</x:v>
+      </x:c>
+      <x:c r="I173" s="26" t="n">
         <x:f>ROUND(D173-E173,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>560.6</x:v>
       </x:c>
       <x:c r="J173" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K173" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B174" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="C174" s="23" t="n">
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="D174" s="23" t="n">
+        <x:v>7440</x:v>
+      </x:c>
+      <x:c r="E174" s="23" t="n">
+        <x:v>7335</x:v>
+      </x:c>
+      <x:c r="F174" s="23" t="n">
+        <x:v>7356</x:v>
+      </x:c>
+      <x:c r="G174" s="23" t="n">
+        <x:f>ROUND(F174-F173,1)</x:f>
+        <x:v>-39</x:v>
+      </x:c>
+      <x:c r="H174" s="24" t="n">
+        <x:f>IFERROR(F174/F173-1,"")</x:f>
+        <x:v>-0.005273833671399553</x:v>
+      </x:c>
+      <x:c r="I174" s="23" t="n">
+        <x:f>ROUND(D174-E174,1)</x:f>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J174" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K174" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B174" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C174" s="30"/>
-      <x:c r="D174" s="30"/>
-      <x:c r="E174" s="30"/>
-      <x:c r="F174" s="30"/>
-      <x:c r="G174" s="30"/>
-      <x:c r="H174" s="30"/>
-      <x:c r="I174" s="32" t="n">
-        <x:f>ROUND(SUM(I144:I173),1)</x:f>
-        <x:v>13554</x:v>
-      </x:c>
-      <x:c r="J174" s="30"/>
-      <x:c r="K174" s="30"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B175" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B175" s="30" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C175" s="30"/>
       <x:c r="D175" s="30"/>
       <x:c r="E175" s="30"/>
       <x:c r="F175" s="30"/>
       <x:c r="G175" s="30"/>
       <x:c r="H175" s="30"/>
-      <x:c r="I175" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I144:I173),0),1)</x:f>
-        <x:v>451.8</x:v>
+      <x:c r="I175" s="32" t="n">
+        <x:f>ROUND(SUM(I145:I174),1)</x:f>
+        <x:v>13554</x:v>
       </x:c>
       <x:c r="J175" s="30"/>
       <x:c r="K175" s="30"/>
     </x:row>
-    <x:row r="177">
-      <x:c r="A177" s="17" t="str">
+    <x:row r="176">
+      <x:c r="A176" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B176" s="30"/>
+      <x:c r="C176" s="30"/>
+      <x:c r="D176" s="30"/>
+      <x:c r="E176" s="30"/>
+      <x:c r="F176" s="30"/>
+      <x:c r="G176" s="30"/>
+      <x:c r="H176" s="30"/>
+      <x:c r="I176" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I145:I174),0),1)</x:f>
+        <x:v>451.8</x:v>
+      </x:c>
+      <x:c r="J176" s="30"/>
+      <x:c r="K176" s="30"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B177" s="17"/>
-      <x:c r="C177" s="17"/>
-      <x:c r="D177" s="17"/>
-      <x:c r="E177" s="17"/>
-      <x:c r="F177" s="17"/>
-      <x:c r="G177" s="17"/>
-      <x:c r="H177" s="17"/>
-      <x:c r="I177" s="17"/>
-      <x:c r="J177" s="17"/>
-      <x:c r="K177" s="17"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178" s="20" t="str">
+      <x:c r="B178" s="17"/>
+      <x:c r="C178" s="17"/>
+      <x:c r="D178" s="17"/>
+      <x:c r="E178" s="17"/>
+      <x:c r="F178" s="17"/>
+      <x:c r="G178" s="17"/>
+      <x:c r="H178" s="17"/>
+      <x:c r="I178" s="17"/>
+      <x:c r="J178" s="17"/>
+      <x:c r="K178" s="17"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B178" s="20" t="str">
+      <x:c r="B179" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C178" s="20" t="str">
+      <x:c r="C179" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D178" s="20" t="str">
+      <x:c r="D179" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E178" s="20" t="str">
+      <x:c r="E179" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F178" s="20" t="str">
+      <x:c r="F179" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G178" s="20" t="str">
+      <x:c r="G179" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H178" s="20" t="str">
+      <x:c r="H179" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I178" s="20" t="str">
+      <x:c r="I179" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J178" s="20" t="str">
+      <x:c r="J179" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K178" s="20" t="str">
+      <x:c r="K179" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B179" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C179" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D179" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E179" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F179" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G179" s="23"/>
-      <x:c r="H179" s="24"/>
-      <x:c r="I179" s="26" t="n">
-        <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J179" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K179" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B180" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C180" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G180" s="23" t="n">
-        <x:f>ROUND(F180-F179,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H180" s="24" t="n">
-        <x:f>IFERROR(F180/F179-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G180" s="23"/>
+      <x:c r="H180" s="24"/>
       <x:c r="I180" s="26" t="n">
         <x:f>ROUND(D180-E180,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J180" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7052,34 +7052,34 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B181" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C181" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G181" s="23" t="n">
         <x:f>ROUND(F181-F180,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H181" s="24" t="n">
         <x:f>IFERROR(F181/F180-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I181" s="26" t="n">
         <x:f>ROUND(D181-E181,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J181" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7090,34 +7090,34 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B182" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C182" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G182" s="23" t="n">
         <x:f>ROUND(F182-F181,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H182" s="24" t="n">
         <x:f>IFERROR(F182/F181-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I182" s="26" t="n">
         <x:f>ROUND(D182-E182,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J182" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7128,34 +7128,34 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B183" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C183" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G183" s="23" t="n">
         <x:f>ROUND(F183-F182,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H183" s="24" t="n">
         <x:f>IFERROR(F183/F182-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I183" s="26" t="n">
         <x:f>ROUND(D183-E183,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J183" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7166,34 +7166,34 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D184" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G184" s="23" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7204,110 +7204,110 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B185" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C185" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G185" s="23" t="n">
         <x:f>ROUND(F185-F184,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H185" s="24" t="n">
         <x:f>IFERROR(F185/F184-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I185" s="26" t="n">
         <x:f>ROUND(D185-E185,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J185" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K185" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B186" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C186" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G186" s="23" t="n">
         <x:f>ROUND(F186-F185,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H186" s="24" t="n">
         <x:f>IFERROR(F186/F185-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I186" s="26" t="n">
         <x:f>ROUND(D186-E186,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J186" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K186" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B187" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C187" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
         <x:f>ROUND(F187-F186,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H187" s="24" t="n">
         <x:f>IFERROR(F187/F186-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I187" s="26" t="n">
         <x:f>ROUND(D187-E187,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J187" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7318,34 +7318,34 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B188" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C188" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G188" s="23" t="n">
         <x:f>ROUND(F188-F187,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H188" s="24" t="n">
         <x:f>IFERROR(F188/F187-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I188" s="26" t="n">
         <x:f>ROUND(D188-E188,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J188" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -7356,37 +7356,37 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B189" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C189" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G189" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G189" s="23" t="n">
         <x:f>ROUND(F189-F188,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H189" s="24" t="n">
         <x:f>IFERROR(F189/F188-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I189" s="26" t="n">
         <x:f>ROUND(D189-E189,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J189" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K189" s="22" t="n">
         <x:v>5</x:v>
@@ -7394,34 +7394,34 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B190" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C190" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G190" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G190" s="28" t="n">
         <x:f>ROUND(F190-F189,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H190" s="24" t="n">
         <x:f>IFERROR(F190/F189-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I190" s="26" t="n">
         <x:f>ROUND(D190-E190,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J190" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7432,110 +7432,110 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B191" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C191" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G191" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
         <x:f>ROUND(F191-F190,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H191" s="24" t="n">
         <x:f>IFERROR(F191/F190-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I191" s="26" t="n">
         <x:f>ROUND(D191-E191,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J191" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K191" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B192" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C192" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G192" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G192" s="28" t="n">
         <x:f>ROUND(F192-F191,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H192" s="24" t="n">
         <x:f>IFERROR(F192/F191-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I192" s="26" t="n">
         <x:f>ROUND(D192-E192,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J192" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K192" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B193" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C193" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D193" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E193" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F193" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G193" s="23" t="n">
         <x:f>ROUND(F193-F192,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H193" s="24" t="n">
         <x:f>IFERROR(F193/F192-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I193" s="26" t="n">
         <x:f>ROUND(D193-E193,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J193" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7546,148 +7546,148 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B194" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C194" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G194" s="23" t="n">
         <x:f>ROUND(F194-F193,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H194" s="24" t="n">
         <x:f>IFERROR(F194/F193-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I194" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I194" s="26" t="n">
         <x:f>ROUND(D194-E194,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J194" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K194" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B195" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C195" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G195" s="23" t="n">
         <x:f>ROUND(F195-F194,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H195" s="24" t="n">
         <x:f>IFERROR(F195/F194-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I195" s="23" t="n">
         <x:f>ROUND(D195-E195,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J195" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K195" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B196" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C196" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G196" s="23" t="n">
         <x:f>ROUND(F196-F195,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H196" s="24" t="n">
         <x:f>IFERROR(F196/F195-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I196" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I196" s="23" t="n">
         <x:f>ROUND(D196-E196,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J196" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K196" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B197" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C197" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G197" s="23" t="n">
         <x:f>ROUND(F197-F196,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H197" s="24" t="n">
         <x:f>IFERROR(F197/F196-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I197" s="26" t="n">
         <x:f>ROUND(D197-E197,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J197" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7698,34 +7698,34 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B198" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C198" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G198" s="23" t="n">
         <x:f>ROUND(F198-F197,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H198" s="24" t="n">
         <x:f>IFERROR(F198/F197-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I198" s="26" t="n">
         <x:f>ROUND(D198-E198,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J198" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7736,34 +7736,34 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7774,34 +7774,34 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B200" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C200" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D200" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E200" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F200" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G200" s="23" t="n">
         <x:f>ROUND(F200-F199,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H200" s="24" t="n">
         <x:f>IFERROR(F200/F199-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I200" s="26" t="n">
         <x:f>ROUND(D200-E200,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J200" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -7812,113 +7812,113 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B201" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C201" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D201" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E201" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F201" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G201" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G201" s="23" t="n">
         <x:f>ROUND(F201-F200,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H201" s="24" t="n">
         <x:f>IFERROR(F201/F200-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I201" s="26" t="n">
         <x:f>ROUND(D201-E201,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J201" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K201" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B202" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C202" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D202" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E202" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F202" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G202" s="28" t="n">
         <x:f>ROUND(F202-F201,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H202" s="24" t="n">
         <x:f>IFERROR(F202/F201-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I202" s="26" t="n">
         <x:f>ROUND(D202-E202,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J202" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K202" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B203" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C203" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D203" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E203" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F203" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G203" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G203" s="28" t="n">
         <x:f>ROUND(F203-F202,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H203" s="24" t="n">
         <x:f>IFERROR(F203/F202-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I203" s="26" t="n">
         <x:f>ROUND(D203-E203,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J203" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K203" s="22" t="n">
         <x:v>5</x:v>
@@ -7926,34 +7926,34 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -7964,34 +7964,34 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B205" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C205" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G205" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G205" s="23" t="n">
         <x:f>ROUND(F205-F204,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H205" s="24" t="n">
         <x:f>IFERROR(F205/F204-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I205" s="26" t="n">
         <x:f>ROUND(D205-E205,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J205" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -8002,34 +8002,34 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B206" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C206" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G206" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G206" s="28" t="n">
         <x:f>ROUND(F206-F205,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H206" s="24" t="n">
         <x:f>IFERROR(F206/F205-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I206" s="26" t="n">
         <x:f>ROUND(D206-E206,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J206" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -8040,34 +8040,34 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B207" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C207" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G207" s="23" t="n">
         <x:f>ROUND(F207-F206,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H207" s="24" t="n">
         <x:f>IFERROR(F207/F206-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I207" s="26" t="n">
         <x:f>ROUND(D207-E207,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J207" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -8078,192 +8078,192 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B208" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C208" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D208" s="23" t="n">
+        <x:v>4652.2</x:v>
+      </x:c>
+      <x:c r="E208" s="23" t="n">
+        <x:v>4420</x:v>
+      </x:c>
+      <x:c r="F208" s="23" t="n">
         <x:v>4538</x:v>
-      </x:c>
-      <x:c r="E208" s="23" t="n">
-        <x:v>4494.2</x:v>
-      </x:c>
-      <x:c r="F208" s="23" t="n">
-        <x:v>4512.2</x:v>
       </x:c>
       <x:c r="G208" s="23" t="n">
         <x:f>ROUND(F208-F207,1)</x:f>
-        <x:v>-25.8</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H208" s="24" t="n">
         <x:f>IFERROR(F208/F207-1,"")</x:f>
-        <x:v>-0.005685323931247321</x:v>
-      </x:c>
-      <x:c r="I208" s="23" t="n">
+        <x:v>-0.008780743523655543</x:v>
+      </x:c>
+      <x:c r="I208" s="26" t="n">
         <x:f>ROUND(D208-E208,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J208" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K208" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B209" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="C209" s="23" t="n">
+        <x:v>4526.4</x:v>
+      </x:c>
+      <x:c r="D209" s="23" t="n">
+        <x:v>4538</x:v>
+      </x:c>
+      <x:c r="E209" s="23" t="n">
+        <x:v>4494.2</x:v>
+      </x:c>
+      <x:c r="F209" s="23" t="n">
+        <x:v>4512.2</x:v>
+      </x:c>
+      <x:c r="G209" s="23" t="n">
+        <x:f>ROUND(F209-F208,1)</x:f>
+        <x:v>-25.8</x:v>
+      </x:c>
+      <x:c r="H209" s="24" t="n">
+        <x:f>IFERROR(F209/F208-1,"")</x:f>
+        <x:v>-0.005685323931247321</x:v>
+      </x:c>
+      <x:c r="I209" s="23" t="n">
+        <x:f>ROUND(D209-E209,1)</x:f>
+        <x:v>43.8</x:v>
+      </x:c>
+      <x:c r="J209" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K209" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B209" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C209" s="30"/>
-      <x:c r="D209" s="30"/>
-      <x:c r="E209" s="30"/>
-      <x:c r="F209" s="30"/>
-      <x:c r="G209" s="30"/>
-      <x:c r="H209" s="30"/>
-      <x:c r="I209" s="32" t="n">
-        <x:f>ROUND(SUM(I179:I208),1)</x:f>
-        <x:v>4849</x:v>
-      </x:c>
-      <x:c r="J209" s="30"/>
-      <x:c r="K209" s="30"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B210" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B210" s="30" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C210" s="30"/>
       <x:c r="D210" s="30"/>
       <x:c r="E210" s="30"/>
       <x:c r="F210" s="30"/>
       <x:c r="G210" s="30"/>
       <x:c r="H210" s="30"/>
-      <x:c r="I210" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I179:I208),0),1)</x:f>
-        <x:v>161.6</x:v>
+      <x:c r="I210" s="32" t="n">
+        <x:f>ROUND(SUM(I180:I209),1)</x:f>
+        <x:v>4849</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
     </x:row>
-    <x:row r="212">
-      <x:c r="A212" s="17" t="str">
+    <x:row r="211">
+      <x:c r="A211" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B211" s="30"/>
+      <x:c r="C211" s="30"/>
+      <x:c r="D211" s="30"/>
+      <x:c r="E211" s="30"/>
+      <x:c r="F211" s="30"/>
+      <x:c r="G211" s="30"/>
+      <x:c r="H211" s="30"/>
+      <x:c r="I211" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I180:I209),0),1)</x:f>
+        <x:v>161.6</x:v>
+      </x:c>
+      <x:c r="J211" s="30"/>
+      <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B212" s="17"/>
-      <x:c r="C212" s="17"/>
-      <x:c r="D212" s="17"/>
-      <x:c r="E212" s="17"/>
-      <x:c r="F212" s="17"/>
-      <x:c r="G212" s="17"/>
-      <x:c r="H212" s="17"/>
-      <x:c r="I212" s="17"/>
-      <x:c r="J212" s="17"/>
-      <x:c r="K212" s="17"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" s="20" t="str">
+      <x:c r="B213" s="17"/>
+      <x:c r="C213" s="17"/>
+      <x:c r="D213" s="17"/>
+      <x:c r="E213" s="17"/>
+      <x:c r="F213" s="17"/>
+      <x:c r="G213" s="17"/>
+      <x:c r="H213" s="17"/>
+      <x:c r="I213" s="17"/>
+      <x:c r="J213" s="17"/>
+      <x:c r="K213" s="17"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B213" s="20" t="str">
+      <x:c r="B214" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C213" s="20" t="str">
+      <x:c r="C214" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D213" s="20" t="str">
+      <x:c r="D214" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E213" s="20" t="str">
+      <x:c r="E214" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F213" s="20" t="str">
+      <x:c r="F214" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G213" s="20" t="str">
+      <x:c r="G214" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H213" s="20" t="str">
+      <x:c r="H214" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I213" s="20" t="str">
+      <x:c r="I214" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J213" s="20" t="str">
+      <x:c r="J214" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K213" s="20" t="str">
+      <x:c r="K214" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B214" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C214" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D214" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E214" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F214" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G214" s="23"/>
-      <x:c r="H214" s="24"/>
-      <x:c r="I214" s="26" t="n">
-        <x:f>ROUND(D214-E214,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J214" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K214" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G215" s="23" t="n">
-        <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H215" s="24" t="n">
-        <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G215" s="23"/>
+      <x:c r="H215" s="24"/>
       <x:c r="I215" s="26" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8274,34 +8274,34 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B216" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C216" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D216" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E216" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F216" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G216" s="23" t="n">
         <x:f>ROUND(F216-F215,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H216" s="24" t="n">
         <x:f>IFERROR(F216/F215-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I216" s="26" t="n">
         <x:f>ROUND(D216-E216,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J216" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8312,34 +8312,34 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B217" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C217" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D217" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E217" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F217" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G217" s="23" t="n">
         <x:f>ROUND(F217-F216,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H217" s="24" t="n">
         <x:f>IFERROR(F217/F216-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I217" s="26" t="n">
         <x:f>ROUND(D217-E217,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J217" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8350,34 +8350,34 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B218" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C218" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D218" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E218" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F218" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G218" s="23" t="n">
         <x:f>ROUND(F218-F217,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H218" s="24" t="n">
         <x:f>IFERROR(F218/F217-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I218" s="26" t="n">
         <x:f>ROUND(D218-E218,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J218" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8388,34 +8388,34 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D219" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G219" s="23" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8426,110 +8426,110 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B220" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C220" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D220" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E220" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F220" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G220" s="23" t="n">
         <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H220" s="24" t="n">
         <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I220" s="26" t="n">
         <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J220" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K220" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D221" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B222" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C222" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D222" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E222" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F222" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G222" s="23" t="n">
         <x:f>ROUND(F222-F221,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H222" s="24" t="n">
         <x:f>IFERROR(F222/F221-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I222" s="26" t="n">
         <x:f>ROUND(D222-E222,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J222" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8540,34 +8540,34 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B223" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C223" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D223" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E223" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F223" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G223" s="23" t="n">
         <x:f>ROUND(F223-F222,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H223" s="24" t="n">
         <x:f>IFERROR(F223/F222-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I223" s="26" t="n">
         <x:f>ROUND(D223-E223,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J223" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -8578,37 +8578,37 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D224" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K224" s="22" t="n">
         <x:v>5</x:v>
@@ -8616,34 +8616,34 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B225" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C225" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D225" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E225" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F225" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G225" s="23" t="n">
         <x:f>ROUND(F225-F224,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H225" s="24" t="n">
         <x:f>IFERROR(F225/F224-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I225" s="26" t="n">
         <x:f>ROUND(D225-E225,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J225" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -8654,110 +8654,110 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B226" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C226" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D226" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E226" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F226" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G226" s="23" t="n">
         <x:f>ROUND(F226-F225,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H226" s="24" t="n">
         <x:f>IFERROR(F226/F225-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I226" s="26" t="n">
         <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J226" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K226" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G227" s="23" t="n">
         <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H227" s="24" t="n">
         <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K227" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G228" s="23" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I228" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -8768,148 +8768,148 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I229" s="23" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K229" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I230" s="23" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K230" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I231" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I231" s="23" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K231" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -8920,34 +8920,34 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -8958,34 +8958,34 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -8996,34 +8996,34 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I235" s="26" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -9034,113 +9034,113 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I236" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K236" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I237" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I237" s="23" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K237" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K238" s="22" t="n">
         <x:v>5</x:v>
@@ -9148,34 +9148,34 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -9186,34 +9186,34 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G240" s="23" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I240" s="26" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -9224,34 +9224,34 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G241" s="23" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I241" s="26" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -9262,34 +9262,34 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G242" s="23" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I242" s="26" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -9300,79 +9300,117 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>2890</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>-31.8</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>-0.010996611107268905</x:v>
-      </x:c>
-      <x:c r="I243" s="23" t="n">
+        <x:v>-0.006254295532646004</x:v>
+      </x:c>
+      <x:c r="I243" s="26" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>44.2</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K243" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B244" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="C244" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D244" s="23" t="n">
+        <x:v>2890</x:v>
+      </x:c>
+      <x:c r="E244" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F244" s="23" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="G244" s="23" t="n">
+        <x:f>ROUND(F244-F243,1)</x:f>
+        <x:v>-31.8</x:v>
+      </x:c>
+      <x:c r="H244" s="24" t="n">
+        <x:f>IFERROR(F244/F243-1,"")</x:f>
+        <x:v>-0.010996611107268905</x:v>
+      </x:c>
+      <x:c r="I244" s="23" t="n">
+        <x:f>ROUND(D244-E244,1)</x:f>
+        <x:v>44.2</x:v>
+      </x:c>
+      <x:c r="J244" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K244" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A244" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B244" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C244" s="30"/>
-      <x:c r="D244" s="30"/>
-      <x:c r="E244" s="30"/>
-      <x:c r="F244" s="30"/>
-      <x:c r="G244" s="30"/>
-      <x:c r="H244" s="30"/>
-      <x:c r="I244" s="32" t="n">
-        <x:f>ROUND(SUM(I214:I243),1)</x:f>
-        <x:v>2777</x:v>
-      </x:c>
-      <x:c r="J244" s="30"/>
-      <x:c r="K244" s="30"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B245" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B245" s="30" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C245" s="30"/>
       <x:c r="D245" s="30"/>
       <x:c r="E245" s="30"/>
       <x:c r="F245" s="30"/>
       <x:c r="G245" s="30"/>
       <x:c r="H245" s="30"/>
-      <x:c r="I245" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I214:I243),0),1)</x:f>
-        <x:v>92.6</x:v>
+      <x:c r="I245" s="32" t="n">
+        <x:f>ROUND(SUM(I215:I244),1)</x:f>
+        <x:v>2777</x:v>
       </x:c>
       <x:c r="J245" s="30"/>
       <x:c r="K245" s="30"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B246" s="30"/>
+      <x:c r="C246" s="30"/>
+      <x:c r="D246" s="30"/>
+      <x:c r="E246" s="30"/>
+      <x:c r="F246" s="30"/>
+      <x:c r="G246" s="30"/>
+      <x:c r="H246" s="30"/>
+      <x:c r="I246" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I215:I244),0),1)</x:f>
+        <x:v>92.6</x:v>
+      </x:c>
+      <x:c r="J246" s="30"/>
+      <x:c r="K246" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9381,9 +9419,9 @@
     <x:mergeCell ref="A38:K38"/>
     <x:mergeCell ref="A73:K73"/>
     <x:mergeCell ref="A108:K108"/>
-    <x:mergeCell ref="A142:K142"/>
-    <x:mergeCell ref="A177:K177"/>
-    <x:mergeCell ref="A212:K212"/>
+    <x:mergeCell ref="A143:K143"/>
+    <x:mergeCell ref="A178:K178"/>
+    <x:mergeCell ref="A213:K213"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -32377,6 +32415,130 @@
       </x:c>
       <x:c r="K175" s="30"/>
     </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="17" t="str">
+        <x:v>8月</x:v>
+      </x:c>
+      <x:c r="B177" s="17"/>
+      <x:c r="C177" s="17"/>
+      <x:c r="D177" s="17"/>
+      <x:c r="E177" s="17"/>
+      <x:c r="F177" s="17"/>
+      <x:c r="G177" s="17"/>
+      <x:c r="H177" s="17"/>
+      <x:c r="I177" s="17"/>
+      <x:c r="J177" s="17"/>
+      <x:c r="K177" s="17"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B178" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C178" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D178" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E178" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F178" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G178" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H178" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I178" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J178" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K178" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B179" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C179" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="D179" s="23" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="E179" s="23" t="n">
+        <x:v>7064.2</x:v>
+      </x:c>
+      <x:c r="F179" s="23" t="n">
+        <x:v>6976</x:v>
+      </x:c>
+      <x:c r="G179" s="23" t="n">
+        <x:v>7023.4</x:v>
+      </x:c>
+      <x:c r="H179" s="23" t="n">
+        <x:v>35.6</x:v>
+      </x:c>
+      <x:c r="I179" s="24" t="n">
+        <x:v>0.005094593434270989</x:v>
+      </x:c>
+      <x:c r="J179" s="23" t="n">
+        <x:f>ROUND(E179-F179,1)</x:f>
+        <x:v>88.2</x:v>
+      </x:c>
+      <x:c r="K179" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B180" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C180" s="30"/>
+      <x:c r="D180" s="30"/>
+      <x:c r="E180" s="30"/>
+      <x:c r="F180" s="30"/>
+      <x:c r="G180" s="30"/>
+      <x:c r="H180" s="30"/>
+      <x:c r="I180" s="30"/>
+      <x:c r="J180" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J179),1)</x:f>
+        <x:v>88.2</x:v>
+      </x:c>
+      <x:c r="K180" s="30"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B181" s="30"/>
+      <x:c r="C181" s="30"/>
+      <x:c r="D181" s="30"/>
+      <x:c r="E181" s="30"/>
+      <x:c r="F181" s="30"/>
+      <x:c r="G181" s="30"/>
+      <x:c r="H181" s="30"/>
+      <x:c r="I181" s="30"/>
+      <x:c r="J181" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
+        <x:v>88.2</x:v>
+      </x:c>
+      <x:c r="K181" s="30"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -32387,6 +32549,7 @@
     <x:mergeCell ref="A100:K100"/>
     <x:mergeCell ref="A123:K123"/>
     <x:mergeCell ref="A149:K149"/>
+    <x:mergeCell ref="A177:K177"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3199b6950f2a4ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb16ad1f12d3a49c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R029473326a1946d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfc16f9f7d9404c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8e724223d5e7472a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1a1a4818f4254187"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R93ad701685144551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R47ece9aa86414d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R56e9983a7b2f4c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf07be08b0cbc437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rac0ee4987500450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rfe0d5609fc8442ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rb1d1859ac5b24345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R923a19595b3043b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2e58e7c6c9f64c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R5aee627235874270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R6f4f3b68726d46d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R53fe13bd321b4757"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -518,25 +518,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7118.1</x:v>
+        <x:v>7307.17</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7042.89</x:v>
+        <x:v>7102.46</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>75.2</x:v>
+        <x:v>204.7</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>25191.1</x:v>
+        <x:v>25395.8</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.9</x:v>
+        <x:v>180.1</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -547,25 +547,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7499.58</x:v>
+        <x:v>7645.48</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7397.94</x:v>
+        <x:v>7450.32</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>101.6</x:v>
+        <x:v>195.2</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>25397.6</x:v>
+        <x:v>25592.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>181.4</x:v>
+        <x:v>181.5</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -576,25 +576,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3827.64</x:v>
+        <x:v>3831.94</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3797.64</x:v>
+        <x:v>3799.52</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>30</x:v>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7005.3</x:v>
+        <x:v>7037.7</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>49.9</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -605,25 +605,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7064.2</x:v>
+        <x:v>7269.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6976</x:v>
+        <x:v>7057.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>88.2</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>26916</x:v>
+        <x:v>27128</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>192.3</x:v>
+        <x:v>192.4</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -634,22 +634,22 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7440</x:v>
+        <x:v>7599</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7335</x:v>
+        <x:v>7392.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>105</x:v>
+        <x:v>206.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>28277.6</x:v>
+        <x:v>28483.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:v>202</x:v>
@@ -663,25 +663,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4538</x:v>
+        <x:v>4580.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4524.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>43.8</x:v>
+        <x:v>56.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10603.4</x:v>
+        <x:v>10660</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.7</x:v>
+        <x:v>75.6</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -692,25 +692,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2890</x:v>
+        <x:v>2872</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2846.6</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>44.2</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5922</x:v>
+        <x:v>5947.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.3</x:v>
+        <x:v>42.2</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -724,7 +724,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -2009,37 +2009,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
         <x:v>7055.27</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7118.1</x:v>
+        <x:v>7307.17</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
         <x:v>7042.89</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7079.78</x:v>
-      </x:c>
-      <x:c r="G34" s="23" t="n">
+        <x:v>7279.19</x:v>
+      </x:c>
+      <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
-        <x:v>4.3</x:v>
+        <x:v>203.7</x:v>
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.0006034900664404486</x:v>
-      </x:c>
-      <x:c r="I34" s="23" t="n">
+        <x:v>0.028786617501777245</x:v>
+      </x:c>
+      <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
-        <x:v>75.2</x:v>
+        <x:v>264.3</x:v>
       </x:c>
       <x:c r="J34" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K34" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2057,7 +2057,7 @@
       <x:c r="H35" s="30"/>
       <x:c r="I35" s="32" t="n">
         <x:f>ROUND(SUM(I5:I34),1)</x:f>
-        <x:v>12144.4</x:v>
+        <x:v>12333.5</x:v>
       </x:c>
       <x:c r="J35" s="30"/>
       <x:c r="K35" s="30"/>
@@ -2075,7 +2075,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I34),0),1)</x:f>
-        <x:v>404.8</x:v>
+        <x:v>411.1</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -3231,37 +3231,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C69" s="23" t="n">
         <x:v>7457.12</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7499.58</x:v>
+        <x:v>7645.48</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
         <x:v>7397.94</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7414.52</x:v>
+        <x:v>7607.49</x:v>
       </x:c>
       <x:c r="G69" s="23" t="n">
         <x:f>ROUND(F69-F68,1)</x:f>
-        <x:v>-79.5</x:v>
+        <x:v>113.5</x:v>
       </x:c>
       <x:c r="H69" s="24" t="n">
         <x:f>IFERROR(F69/F68-1,"")</x:f>
-        <x:v>-0.010604497737520258</x:v>
-      </x:c>
-      <x:c r="I69" s="23" t="n">
+        <x:v>0.015145469903215858</x:v>
+      </x:c>
+      <x:c r="I69" s="26" t="n">
         <x:f>ROUND(D69-E69,1)</x:f>
-        <x:v>101.6</x:v>
+        <x:v>247.5</x:v>
       </x:c>
       <x:c r="J69" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K69" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -3279,7 +3279,7 @@
       <x:c r="H70" s="30"/>
       <x:c r="I70" s="32" t="n">
         <x:f>ROUND(SUM(I40:I69),1)</x:f>
-        <x:v>12396.7</x:v>
+        <x:v>12542.6</x:v>
       </x:c>
       <x:c r="J70" s="30"/>
       <x:c r="K70" s="30"/>
@@ -3297,7 +3297,7 @@
       <x:c r="H71" s="30"/>
       <x:c r="I71" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I40:I69),0),1)</x:f>
-        <x:v>413.2</x:v>
+        <x:v>418.1</x:v>
       </x:c>
       <x:c r="J71" s="30"/>
       <x:c r="K71" s="30"/>
@@ -4453,37 +4453,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B104" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C104" s="23" t="n">
         <x:v>3812.61</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>3827.64</x:v>
+        <x:v>3831.94</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
         <x:v>3797.64</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>3809.66</x:v>
+        <x:v>3822.28</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
         <x:f>ROUND(F104-F103,1)</x:f>
-        <x:v>-22.6</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H104" s="24" t="n">
         <x:f>IFERROR(F104/F103-1,"")</x:f>
-        <x:v>-0.005897303418870403</x:v>
+        <x:v>-0.0026042074389525105</x:v>
       </x:c>
       <x:c r="I104" s="23" t="n">
         <x:f>ROUND(D104-E104,1)</x:f>
-        <x:v>30</x:v>
+        <x:v>34.3</x:v>
       </x:c>
       <x:c r="J104" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K104" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -4501,7 +4501,7 @@
       <x:c r="H105" s="30"/>
       <x:c r="I105" s="32" t="n">
         <x:f>ROUND(SUM(I75:I104),1)</x:f>
-        <x:v>3265.9</x:v>
+        <x:v>3270.2</x:v>
       </x:c>
       <x:c r="J105" s="30"/>
       <x:c r="K105" s="30"/>
@@ -4519,7 +4519,7 @@
       <x:c r="H106" s="30"/>
       <x:c r="I106" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I75:I104),0),1)</x:f>
-        <x:v>108.9</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J106" s="30"/>
       <x:c r="K106" s="30"/>
@@ -5675,37 +5675,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B139" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C139" s="23" t="n">
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D139" s="23" t="n">
-        <x:v>7064.2</x:v>
+        <x:v>7269.8</x:v>
       </x:c>
       <x:c r="E139" s="23" t="n">
         <x:v>6976</x:v>
       </x:c>
       <x:c r="F139" s="23" t="n">
-        <x:v>7023.4</x:v>
-      </x:c>
-      <x:c r="G139" s="23" t="n">
+        <x:v>7211.4</x:v>
+      </x:c>
+      <x:c r="G139" s="28" t="n">
         <x:f>ROUND(F139-F138,1)</x:f>
-        <x:v>35.6</x:v>
+        <x:v>223.6</x:v>
       </x:c>
       <x:c r="H139" s="24" t="n">
         <x:f>IFERROR(F139/F138-1,"")</x:f>
-        <x:v>0.005094593434270989</x:v>
-      </x:c>
-      <x:c r="I139" s="23" t="n">
+        <x:v>0.03199862617705129</x:v>
+      </x:c>
+      <x:c r="I139" s="26" t="n">
         <x:f>ROUND(D139-E139,1)</x:f>
-        <x:v>88.2</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J139" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K139" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -5723,7 +5723,7 @@
       <x:c r="H140" s="30"/>
       <x:c r="I140" s="32" t="n">
         <x:f>ROUND(SUM(I110:I139),1)</x:f>
-        <x:v>12818.2</x:v>
+        <x:v>13023.8</x:v>
       </x:c>
       <x:c r="J140" s="30"/>
       <x:c r="K140" s="30"/>
@@ -5741,7 +5741,7 @@
       <x:c r="H141" s="30"/>
       <x:c r="I141" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I110:I139),0),1)</x:f>
-        <x:v>427.3</x:v>
+        <x:v>434.1</x:v>
       </x:c>
       <x:c r="J141" s="30"/>
       <x:c r="K141" s="30"/>
@@ -6897,37 +6897,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
         <x:v>7391</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>7440</x:v>
+        <x:v>7599</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
         <x:v>7335</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>7356</x:v>
+        <x:v>7529</x:v>
       </x:c>
       <x:c r="G174" s="23" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>-39</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>-0.005273833671399553</x:v>
-      </x:c>
-      <x:c r="I174" s="23" t="n">
+        <x:v>0.018120351588911454</x:v>
+      </x:c>
+      <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -6945,7 +6945,7 @@
       <x:c r="H175" s="30"/>
       <x:c r="I175" s="32" t="n">
         <x:f>ROUND(SUM(I145:I174),1)</x:f>
-        <x:v>13554</x:v>
+        <x:v>13713</x:v>
       </x:c>
       <x:c r="J175" s="30"/>
       <x:c r="K175" s="30"/>
@@ -6963,7 +6963,7 @@
       <x:c r="H176" s="30"/>
       <x:c r="I176" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I145:I174),0),1)</x:f>
-        <x:v>451.8</x:v>
+        <x:v>457.1</x:v>
       </x:c>
       <x:c r="J176" s="30"/>
       <x:c r="K176" s="30"/>
@@ -8119,37 +8119,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4580.8</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
         <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4512.2</x:v>
+        <x:v>4552.8</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-25.8</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.005685323931247321</x:v>
+        <x:v>0.003261348611723225</x:v>
       </x:c>
       <x:c r="I209" s="23" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>86.6</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -8167,7 +8167,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I180:I209),1)</x:f>
-        <x:v>4849</x:v>
+        <x:v>4891.8</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -8185,7 +8185,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I180:I209),0),1)</x:f>
-        <x:v>161.6</x:v>
+        <x:v>163.1</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -9341,7 +9341,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>8月3日</x:v>
+        <x:v>8月3日-8月4日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
         <x:v>2882.4</x:v>
@@ -9353,15 +9353,15 @@
         <x:v>2845.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2852.4</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>-31.8</x:v>
+        <x:v>-39.4</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>-0.010996611107268905</x:v>
+        <x:v>-0.01362473200082992</x:v>
       </x:c>
       <x:c r="I244" s="23" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
@@ -9371,7 +9371,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -15156,30 +15156,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>75.2</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>7128.49</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>7307.17</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>7102.46</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>7279.19</x:v>
+      </x:c>
+      <x:c r="H180" s="28" t="n">
+        <x:v>199.4</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.028166129456000055</x:v>
+      </x:c>
+      <x:c r="J180" s="26" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>204.7</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -15187,11 +15205,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>75.2</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>279.9</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20938,30 +20974,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>101.6</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>7467.08</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>7645.48</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>7450.32</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>7607.49</x:v>
+      </x:c>
+      <x:c r="H180" s="28" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.02602595987332945</x:v>
+      </x:c>
+      <x:c r="J180" s="26" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>195.2</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -20969,11 +21023,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>101.6</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>296.8</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>148.4</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -26720,30 +26792,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>3816.37</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>3831.94</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>3799.52</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>3822.28</x:v>
+      </x:c>
+      <x:c r="H180" s="23" t="n">
+        <x:v>12.6</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.0033126315734213208</x:v>
+      </x:c>
+      <x:c r="J180" s="23" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>32.4</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -26751,11 +26841,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>30</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>62.4</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>31.2</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32502,30 +32610,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>88.2</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>7073.2</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>7269.8</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>7057.8</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>7211.4</x:v>
+      </x:c>
+      <x:c r="H180" s="28" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.026767662385739133</x:v>
+      </x:c>
+      <x:c r="J180" s="26" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -32533,11 +32659,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>88.2</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>300.2</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>150.1</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -38284,30 +38428,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>7406</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>7599</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>7392.8</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>7529</x:v>
+      </x:c>
+      <x:c r="H180" s="28" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.023518216421968496</x:v>
+      </x:c>
+      <x:c r="J180" s="26" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>206.2</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -38315,11 +38477,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>105</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>311.2</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>155.6</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -44066,30 +44246,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>43.8</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>4538</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>4580.8</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>4524.2</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>4552.8</x:v>
+      </x:c>
+      <x:c r="H180" s="23" t="n">
+        <x:v>40.6</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.00899782811045613</x:v>
+      </x:c>
+      <x:c r="J180" s="23" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>56.6</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -44097,11 +44295,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>43.8</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>100.4</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>50.2</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -49848,30 +50064,48 @@
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B180" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C180" s="30"/>
-      <x:c r="D180" s="30"/>
-      <x:c r="E180" s="30"/>
-      <x:c r="F180" s="30"/>
-      <x:c r="G180" s="30"/>
-      <x:c r="H180" s="30"/>
-      <x:c r="I180" s="30"/>
-      <x:c r="J180" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J179),1)</x:f>
-        <x:v>44.2</x:v>
-      </x:c>
-      <x:c r="K180" s="30"/>
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>2872</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>2872</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>2846.6</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>2852.4</x:v>
+      </x:c>
+      <x:c r="H180" s="23" t="n">
+        <x:v>-7.6</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>-0.0026573426573426318</x:v>
+      </x:c>
+      <x:c r="J180" s="23" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>25.4</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B181" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B181" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C181" s="30"/>
       <x:c r="D181" s="30"/>
       <x:c r="E181" s="30"/>
@@ -49879,11 +50113,29 @@
       <x:c r="G181" s="30"/>
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="30"/>
-      <x:c r="J181" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J179),0),1)</x:f>
-        <x:v>44.2</x:v>
+      <x:c r="J181" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J180),1)</x:f>
+        <x:v>69.6</x:v>
       </x:c>
       <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B182" s="30"/>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
+        <x:v>34.8</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf07be08b0cbc437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rac0ee4987500450a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rfe0d5609fc8442ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rb1d1859ac5b24345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R923a19595b3043b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2e58e7c6c9f64c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R5aee627235874270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R6f4f3b68726d46d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R53fe13bd321b4757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R278638a03f5b4a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9d441619e7024973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb6f172fdb82f40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfc9cd13b17a44581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R295f6b12c1d34215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcd1a33a9cb20450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R70df2e5fe1834d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4142e6584cb94c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R72e5ed24bc9842f4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R278638a03f5b4a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9d441619e7024973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb6f172fdb82f40a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfc9cd13b17a44581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R295f6b12c1d34215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcd1a33a9cb20450c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R70df2e5fe1834d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4142e6584cb94c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R72e5ed24bc9842f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf2ce201e1ad0409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R8ab995b330734681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0237c693b94d446c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rce67ad61f2cf4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R5320b1bf95364917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R499dc64c1f0b4ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R23507040637b487d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ra3d8bec0f5fb4a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf9c40a04f72d493d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -518,25 +518,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7307.17</x:v>
+        <x:v>7523.5</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7102.46</x:v>
+        <x:v>7253.22</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>204.7</x:v>
+        <x:v>270.3</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>25395.8</x:v>
+        <x:v>25666.1</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.1</x:v>
+        <x:v>180.7</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -547,25 +547,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7645.48</x:v>
+        <x:v>7845.39</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7450.32</x:v>
+        <x:v>7567.96</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>195.2</x:v>
+        <x:v>277.4</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>25592.8</x:v>
+        <x:v>25870.2</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>181.5</x:v>
+        <x:v>182.2</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -576,25 +576,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3831.94</x:v>
+        <x:v>3884.4</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3799.52</x:v>
+        <x:v>3815.12</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>32.4</x:v>
+        <x:v>69.3</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7037.7</x:v>
+        <x:v>7107</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -605,25 +605,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7269.8</x:v>
+        <x:v>7466</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7057.8</x:v>
+        <x:v>7201.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>212</x:v>
+        <x:v>264.4</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>27128</x:v>
+        <x:v>27392.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>192.4</x:v>
+        <x:v>192.9</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -724,7 +724,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>数据源</x:v>
@@ -2009,37 +2009,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
         <x:v>7055.27</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7307.17</x:v>
+        <x:v>7523.5</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
         <x:v>7042.89</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7279.19</x:v>
+        <x:v>7493.05</x:v>
       </x:c>
       <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
-        <x:v>203.7</x:v>
+        <x:v>417.5</x:v>
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.028786617501777245</x:v>
+        <x:v>0.0590120005483703</x:v>
       </x:c>
       <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
-        <x:v>264.3</x:v>
+        <x:v>480.6</x:v>
       </x:c>
       <x:c r="J34" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K34" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2057,7 +2057,7 @@
       <x:c r="H35" s="30"/>
       <x:c r="I35" s="32" t="n">
         <x:f>ROUND(SUM(I5:I34),1)</x:f>
-        <x:v>12333.5</x:v>
+        <x:v>12549.8</x:v>
       </x:c>
       <x:c r="J35" s="30"/>
       <x:c r="K35" s="30"/>
@@ -2075,7 +2075,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I34),0),1)</x:f>
-        <x:v>411.1</x:v>
+        <x:v>418.3</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -3231,37 +3231,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C69" s="23" t="n">
         <x:v>7457.12</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7645.48</x:v>
+        <x:v>7845.39</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
         <x:v>7397.94</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7607.49</x:v>
-      </x:c>
-      <x:c r="G69" s="23" t="n">
+        <x:v>7809.21</x:v>
+      </x:c>
+      <x:c r="G69" s="28" t="n">
         <x:f>ROUND(F69-F68,1)</x:f>
-        <x:v>113.5</x:v>
+        <x:v>315.2</x:v>
       </x:c>
       <x:c r="H69" s="24" t="n">
         <x:f>IFERROR(F69/F68-1,"")</x:f>
-        <x:v>0.015145469903215858</x:v>
+        <x:v>0.04206303984926585</x:v>
       </x:c>
       <x:c r="I69" s="26" t="n">
         <x:f>ROUND(D69-E69,1)</x:f>
-        <x:v>247.5</x:v>
+        <x:v>447.5</x:v>
       </x:c>
       <x:c r="J69" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K69" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -3279,7 +3279,7 @@
       <x:c r="H70" s="30"/>
       <x:c r="I70" s="32" t="n">
         <x:f>ROUND(SUM(I40:I69),1)</x:f>
-        <x:v>12542.6</x:v>
+        <x:v>12742.6</x:v>
       </x:c>
       <x:c r="J70" s="30"/>
       <x:c r="K70" s="30"/>
@@ -3297,7 +3297,7 @@
       <x:c r="H71" s="30"/>
       <x:c r="I71" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I40:I69),0),1)</x:f>
-        <x:v>418.1</x:v>
+        <x:v>424.8</x:v>
       </x:c>
       <x:c r="J71" s="30"/>
       <x:c r="K71" s="30"/>
@@ -4453,37 +4453,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B104" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C104" s="23" t="n">
         <x:v>3812.61</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>3831.94</x:v>
+        <x:v>3884.4</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
         <x:v>3797.64</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>3822.28</x:v>
+        <x:v>3878.43</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
         <x:f>ROUND(F104-F103,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>46.2</x:v>
       </x:c>
       <x:c r="H104" s="24" t="n">
         <x:f>IFERROR(F104/F103-1,"")</x:f>
-        <x:v>-0.0026042074389525105</x:v>
-      </x:c>
-      <x:c r="I104" s="23" t="n">
+        <x:v>0.012047721188019445</x:v>
+      </x:c>
+      <x:c r="I104" s="26" t="n">
         <x:f>ROUND(D104-E104,1)</x:f>
-        <x:v>34.3</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="J104" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K104" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -4501,7 +4501,7 @@
       <x:c r="H105" s="30"/>
       <x:c r="I105" s="32" t="n">
         <x:f>ROUND(SUM(I75:I104),1)</x:f>
-        <x:v>3270.2</x:v>
+        <x:v>3322.7</x:v>
       </x:c>
       <x:c r="J105" s="30"/>
       <x:c r="K105" s="30"/>
@@ -4519,7 +4519,7 @@
       <x:c r="H106" s="30"/>
       <x:c r="I106" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I75:I104),0),1)</x:f>
-        <x:v>109</x:v>
+        <x:v>110.8</x:v>
       </x:c>
       <x:c r="J106" s="30"/>
       <x:c r="K106" s="30"/>
@@ -5675,37 +5675,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B139" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C139" s="23" t="n">
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D139" s="23" t="n">
-        <x:v>7269.8</x:v>
+        <x:v>7466</x:v>
       </x:c>
       <x:c r="E139" s="23" t="n">
         <x:v>6976</x:v>
       </x:c>
       <x:c r="F139" s="23" t="n">
-        <x:v>7211.4</x:v>
+        <x:v>7433.8</x:v>
       </x:c>
       <x:c r="G139" s="28" t="n">
         <x:f>ROUND(F139-F138,1)</x:f>
-        <x:v>223.6</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="H139" s="24" t="n">
         <x:f>IFERROR(F139/F138-1,"")</x:f>
-        <x:v>0.03199862617705129</x:v>
+        <x:v>0.06382552448553191</x:v>
       </x:c>
       <x:c r="I139" s="26" t="n">
         <x:f>ROUND(D139-E139,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="J139" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K139" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -5723,7 +5723,7 @@
       <x:c r="H140" s="30"/>
       <x:c r="I140" s="32" t="n">
         <x:f>ROUND(SUM(I110:I139),1)</x:f>
-        <x:v>13023.8</x:v>
+        <x:v>13220</x:v>
       </x:c>
       <x:c r="J140" s="30"/>
       <x:c r="K140" s="30"/>
@@ -5741,7 +5741,7 @@
       <x:c r="H141" s="30"/>
       <x:c r="I141" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I110:I139),0),1)</x:f>
-        <x:v>434.1</x:v>
+        <x:v>440.7</x:v>
       </x:c>
       <x:c r="J141" s="30"/>
       <x:c r="K141" s="30"/>
@@ -15192,30 +15192,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>279.9</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>7253.22</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>7523.5</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>7253.22</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>7493.05</x:v>
+      </x:c>
+      <x:c r="H181" s="28" t="n">
+        <x:v>213.9</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.02937964251517</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>270.3</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -15223,11 +15241,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>140</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>550.2</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>183.4</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -21010,30 +21046,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>296.8</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>7567.96</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>7845.39</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>7567.96</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>7809.21</x:v>
+      </x:c>
+      <x:c r="H181" s="28" t="n">
+        <x:v>201.7</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.026515973073904853</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>277.4</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -21041,11 +21095,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>148.4</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>574.2</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>191.4</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -26828,30 +26900,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>62.4</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>3815.12</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>3884.4</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>3815.12</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>3878.43</x:v>
+      </x:c>
+      <x:c r="H181" s="23" t="n">
+        <x:v>56.1</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.014690184915809423</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>69.3</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -26859,11 +26949,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>31.2</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>131.7</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>43.9</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32646,30 +32754,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>300.2</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>7206.4</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>7466</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>7201.6</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>7433.8</x:v>
+      </x:c>
+      <x:c r="H181" s="28" t="n">
+        <x:v>222.4</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.030840058795795544</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>264.4</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -32677,11 +32803,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>150.1</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>564.6</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>188.2</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf2ce201e1ad0409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R8ab995b330734681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0237c693b94d446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rce67ad61f2cf4b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R5320b1bf95364917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R499dc64c1f0b4ac4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R23507040637b487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ra3d8bec0f5fb4a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf9c40a04f72d493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R16dbcad5760d4405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Raa5d5c7cfbac485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd70388c38d534cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rd2c9616a7d234430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra0ba04e502e448df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R61a5684a293644fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R705721fc5cc4431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R83070ef59c9642c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re9e802a2ab3b4677"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -634,25 +634,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7599</x:v>
+        <x:v>7775.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7392.8</x:v>
+        <x:v>7501</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>206.2</x:v>
+        <x:v>274.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>28483.8</x:v>
+        <x:v>28758.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>202</x:v>
+        <x:v>202.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -663,25 +663,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4580.8</x:v>
+        <x:v>4641.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4524.2</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>56.6</x:v>
+        <x:v>121.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10660</x:v>
+        <x:v>10781.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.6</x:v>
+        <x:v>75.9</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -692,25 +692,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2872</x:v>
+        <x:v>2907.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2846.6</x:v>
+        <x:v>2855</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>25.4</x:v>
+        <x:v>52.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>5947.4</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.2</x:v>
+        <x:v>42.3</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -6897,37 +6897,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
         <x:v>7391</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>7599</x:v>
+        <x:v>7775.6</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
         <x:v>7335</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>7529</x:v>
-      </x:c>
-      <x:c r="G174" s="23" t="n">
+        <x:v>7744.4</x:v>
+      </x:c>
+      <x:c r="G174" s="28" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>134</x:v>
+        <x:v>349.4</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>0.018120351588911454</x:v>
+        <x:v>0.047248140635564484</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>264</x:v>
+        <x:v>440.6</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -6945,7 +6945,7 @@
       <x:c r="H175" s="30"/>
       <x:c r="I175" s="32" t="n">
         <x:f>ROUND(SUM(I145:I174),1)</x:f>
-        <x:v>13713</x:v>
+        <x:v>13889.6</x:v>
       </x:c>
       <x:c r="J175" s="30"/>
       <x:c r="K175" s="30"/>
@@ -6963,7 +6963,7 @@
       <x:c r="H176" s="30"/>
       <x:c r="I176" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I145:I174),0),1)</x:f>
-        <x:v>457.1</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="J176" s="30"/>
       <x:c r="K176" s="30"/>
@@ -8119,37 +8119,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4580.8</x:v>
+        <x:v>4641.2</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
         <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4552.8</x:v>
+        <x:v>4621</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>0.003261348611723225</x:v>
-      </x:c>
-      <x:c r="I209" s="23" t="n">
+        <x:v>0.018289995592772224</x:v>
+      </x:c>
+      <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>86.6</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -8167,7 +8167,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I180:I209),1)</x:f>
-        <x:v>4891.8</x:v>
+        <x:v>4952.2</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -8185,7 +8185,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I180:I209),0),1)</x:f>
-        <x:v>163.1</x:v>
+        <x:v>165.1</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -9341,37 +9341,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>8月3日-8月4日</x:v>
+        <x:v>8月3日-8月5日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
         <x:v>2882.4</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>2890</x:v>
+        <x:v>2907.6</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
         <x:v>2845.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2852.4</x:v>
+        <x:v>2893.4</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>-39.4</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>-0.01362473200082992</x:v>
-      </x:c>
-      <x:c r="I244" s="23" t="n">
+        <x:v>0.00055328860917081</x:v>
+      </x:c>
+      <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>44.2</x:v>
+        <x:v>61.8</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -9389,7 +9389,7 @@
       <x:c r="H245" s="30"/>
       <x:c r="I245" s="32" t="n">
         <x:f>ROUND(SUM(I215:I244),1)</x:f>
-        <x:v>2777</x:v>
+        <x:v>2794.6</x:v>
       </x:c>
       <x:c r="J245" s="30"/>
       <x:c r="K245" s="30"/>
@@ -9407,7 +9407,7 @@
       <x:c r="H246" s="30"/>
       <x:c r="I246" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I215:I244),0),1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
@@ -38608,30 +38608,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>311.2</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>7510.6</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>7775.6</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>7501</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>7744.4</x:v>
+      </x:c>
+      <x:c r="H181" s="28" t="n">
+        <x:v>215.4</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.02860937707530886</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>274.6</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -38639,11 +38657,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>155.6</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>585.8</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>195.3</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -44426,30 +44462,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>100.4</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>4520.6</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>4641.2</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>4520</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>4621</x:v>
+      </x:c>
+      <x:c r="H181" s="23" t="n">
+        <x:v>68.2</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.014979792655069435</x:v>
+      </x:c>
+      <x:c r="J181" s="26" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>121.2</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -44457,11 +44511,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>50.2</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>73.9</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -50244,30 +50316,48 @@
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B181" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="30"/>
-      <x:c r="D181" s="30"/>
-      <x:c r="E181" s="30"/>
-      <x:c r="F181" s="30"/>
-      <x:c r="G181" s="30"/>
-      <x:c r="H181" s="30"/>
-      <x:c r="I181" s="30"/>
-      <x:c r="J181" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J180),1)</x:f>
-        <x:v>69.6</x:v>
-      </x:c>
-      <x:c r="K181" s="30"/>
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>2858.8</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>2907.6</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>2855</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>2893.4</x:v>
+      </x:c>
+      <x:c r="H181" s="23" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.014373860608610345</x:v>
+      </x:c>
+      <x:c r="J181" s="23" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>52.6</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B182" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C182" s="30"/>
       <x:c r="D182" s="30"/>
       <x:c r="E182" s="30"/>
@@ -50275,11 +50365,29 @@
       <x:c r="G182" s="30"/>
       <x:c r="H182" s="30"/>
       <x:c r="I182" s="30"/>
-      <x:c r="J182" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J180),0),1)</x:f>
-        <x:v>34.8</x:v>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>122.2</x:v>
       </x:c>
       <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>40.7</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R16dbcad5760d4405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Raa5d5c7cfbac485a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd70388c38d534cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rd2c9616a7d234430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra0ba04e502e448df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R61a5684a293644fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R705721fc5cc4431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R83070ef59c9642c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re9e802a2ab3b4677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R94808877259a4d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1191204875974f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rccedb6b844b04239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5b279d49d7ce4fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re9fc810039e24de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2f8a12e6b9434460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re6a9ac296ec94ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R748f7826e3af47ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf251281633ca41e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R68df033dab174b6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -716,121 +717,6018 @@
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="14" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>碳酸锂2609</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="n">
+        <x:v>144300</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="n">
+        <x:v>138320</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="n">
+        <x:v>5980</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="n">
+        <x:v>1266600</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="n">
+        <x:v>8919.7</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
         <x:v>统计区间</x:v>
       </x:c>
-      <x:c r="B13" s="14" t="str">
+      <x:c r="B14" s="14" t="str">
         <x:v>2026-01-01</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="str">
+      <x:c r="C14" s="14" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="str">
+      <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="7" t="str">
-        <x:v>中证1000</x:v>
-      </x:c>
-      <x:c r="B14" s="7" t="str">
-        <x:v>sh000852</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>指数日线</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
-        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000852,day,,,80,qfq</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>中证500</x:v>
+        <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>sh000905</x:v>
+        <x:v>sh000852</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
         <x:v>指数日线</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000905,day,,,80,qfq</x:v>
+        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000852,day,,,80,qfq</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>上证指数</x:v>
+        <x:v>中证500</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>sh000001</x:v>
+        <x:v>sh000905</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
         <x:v>指数日线</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000001,day,,,80,qfq</x:v>
+        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000905,day,,,80,qfq</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>IM主力</x:v>
+        <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>IM0</x:v>
+        <x:v>sh000001</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
-        <x:v>用主连确定交易日，再按标的列的具体合约取日线</x:v>
+        <x:v>指数日线</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IM0</x:v>
+        <x:v>https://web.ifzq.gtimg.cn/appstock/app/fqkline/get?param=sh000001,day,,,80,qfq</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>IC主力</x:v>
+        <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>IC0</x:v>
+        <x:v>IM0</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
         <x:v>用主连确定交易日，再按标的列的具体合约取日线</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IC0</x:v>
+        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IM0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>IF主力</x:v>
+        <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>IF0</x:v>
+        <x:v>IC0</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
         <x:v>用主连确定交易日，再按标的列的具体合约取日线</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IF0</x:v>
+        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IC0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>IH主力</x:v>
+        <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>IH0</x:v>
+        <x:v>IF0</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
         <x:v>用主连确定交易日，再按标的列的具体合约取日线</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
+        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IF0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7" t="str">
+        <x:v>IH主力</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>IH0</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="str">
+        <x:v>用主连确定交易日，再按标的列的具体合约取日线</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
         <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=IH0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="7" t="str">
+        <x:v>碳酸锂2609</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="str">
+        <x:v>固定合约日线</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=LC2609</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>2026年统计 - 碳酸锂2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="17" t="str">
+        <x:v>1月</x:v>
+      </x:c>
+      <x:c r="B3" s="17"/>
+      <x:c r="C3" s="17"/>
+      <x:c r="D3" s="17"/>
+      <x:c r="E3" s="17"/>
+      <x:c r="F3" s="17"/>
+      <x:c r="G3" s="17"/>
+      <x:c r="H3" s="17"/>
+      <x:c r="I3" s="17"/>
+      <x:c r="J3" s="17"/>
+      <x:c r="K3" s="17"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G4" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>1月5日</x:v>
+      </x:c>
+      <x:c r="D5" s="23" t="n">
+        <x:v>126360</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="n">
+        <x:v>132400</x:v>
+      </x:c>
+      <x:c r="F5" s="23" t="n">
+        <x:v>125160</x:v>
+      </x:c>
+      <x:c r="G5" s="23" t="n">
+        <x:v>131940</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="n">
+        <x:v>7980</x:v>
+      </x:c>
+      <x:c r="I5" s="24" t="n">
+        <x:v>0.06437560503388196</x:v>
+      </x:c>
+      <x:c r="J5" s="26" t="n">
+        <x:f>ROUND(E5-F5,1)</x:f>
+        <x:v>7240</x:v>
+      </x:c>
+      <x:c r="K5" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="str">
+        <x:v>1月6日</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="n">
+        <x:v>133860</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="n">
+        <x:v>140020</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="n">
+        <x:v>133860</x:v>
+      </x:c>
+      <x:c r="G6" s="23" t="n">
+        <x:v>140020</x:v>
+      </x:c>
+      <x:c r="H6" s="28" t="n">
+        <x:v>8080</x:v>
+      </x:c>
+      <x:c r="I6" s="24" t="n">
+        <x:v>0.06123995755646505</x:v>
+      </x:c>
+      <x:c r="J6" s="26" t="n">
+        <x:f>ROUND(E6-F6,1)</x:f>
+        <x:v>6160</x:v>
+      </x:c>
+      <x:c r="K6" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="str">
+        <x:v>1月7日</x:v>
+      </x:c>
+      <x:c r="D7" s="23" t="n">
+        <x:v>144180</x:v>
+      </x:c>
+      <x:c r="E7" s="23" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="F7" s="23" t="n">
+        <x:v>140300</x:v>
+      </x:c>
+      <x:c r="G7" s="23" t="n">
+        <x:v>144380</x:v>
+      </x:c>
+      <x:c r="H7" s="28" t="n">
+        <x:v>4360</x:v>
+      </x:c>
+      <x:c r="I7" s="24" t="n">
+        <x:v>0.031138408798742967</x:v>
+      </x:c>
+      <x:c r="J7" s="26" t="n">
+        <x:f>ROUND(E7-F7,1)</x:f>
+        <x:v>8700</x:v>
+      </x:c>
+      <x:c r="K7" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C8" s="22" t="str">
+        <x:v>1月8日</x:v>
+      </x:c>
+      <x:c r="D8" s="23" t="n">
+        <x:v>143900</x:v>
+      </x:c>
+      <x:c r="E8" s="23" t="n">
+        <x:v>150760</x:v>
+      </x:c>
+      <x:c r="F8" s="23" t="n">
+        <x:v>139120</x:v>
+      </x:c>
+      <x:c r="G8" s="23" t="n">
+        <x:v>146940</x:v>
+      </x:c>
+      <x:c r="H8" s="28" t="n">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="I8" s="24" t="n">
+        <x:v>0.01773098767142267</x:v>
+      </x:c>
+      <x:c r="J8" s="26" t="n">
+        <x:f>ROUND(E8-F8,1)</x:f>
+        <x:v>11640</x:v>
+      </x:c>
+      <x:c r="K8" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>1月9日</x:v>
+      </x:c>
+      <x:c r="D9" s="23" t="n">
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="E9" s="23" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="F9" s="23" t="n">
+        <x:v>141500</x:v>
+      </x:c>
+      <x:c r="G9" s="23" t="n">
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="H9" s="28" t="n">
+        <x:v>-1560</x:v>
+      </x:c>
+      <x:c r="I9" s="24" t="n">
+        <x:v>-0.010616578195181692</x:v>
+      </x:c>
+      <x:c r="J9" s="26" t="n">
+        <x:f>ROUND(E9-F9,1)</x:f>
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>1月12日</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="n">
+        <x:v>153000</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="n">
+        <x:v>158420</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="n">
+        <x:v>153000</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="n">
+        <x:v>158420</x:v>
+      </x:c>
+      <x:c r="H10" s="28" t="n">
+        <x:v>13040</x:v>
+      </x:c>
+      <x:c r="I10" s="24" t="n">
+        <x:v>0.08969596918420697</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="n">
+        <x:f>ROUND(E10-F10,1)</x:f>
+        <x:v>5420</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>1月13日</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="n">
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="n">
+        <x:v>176120</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="n">
+        <x:v>163720</x:v>
+      </x:c>
+      <x:c r="G11" s="23" t="n">
+        <x:v>169200</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="n">
+        <x:v>10780</x:v>
+      </x:c>
+      <x:c r="I11" s="24" t="n">
+        <x:v>0.06804696376720121</x:v>
+      </x:c>
+      <x:c r="J11" s="26" t="n">
+        <x:f>ROUND(E11-F11,1)</x:f>
+        <x:v>12400</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>1月14日</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="n">
+        <x:v>168800</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="n">
+        <x:v>175220</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="n">
+        <x:v>156700</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="n">
+        <x:v>164000</x:v>
+      </x:c>
+      <x:c r="H12" s="28" t="n">
+        <x:v>-5200</x:v>
+      </x:c>
+      <x:c r="I12" s="24" t="n">
+        <x:v>-0.030732860520094607</x:v>
+      </x:c>
+      <x:c r="J12" s="26" t="n">
+        <x:f>ROUND(E12-F12,1)</x:f>
+        <x:v>18520</x:v>
+      </x:c>
+      <x:c r="K12" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="str">
+        <x:v>1月15日</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="n">
+        <x:v>166500</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="n">
+        <x:v>166900</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="n">
+        <x:v>157160</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="n">
+        <x:v>164880</x:v>
+      </x:c>
+      <x:c r="H13" s="28" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="I13" s="24" t="n">
+        <x:v>0.00536585365853659</x:v>
+      </x:c>
+      <x:c r="J13" s="26" t="n">
+        <x:f>ROUND(E13-F13,1)</x:f>
+        <x:v>9740</x:v>
+      </x:c>
+      <x:c r="K13" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="41" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C14" s="41" t="str">
+        <x:v>1月16日</x:v>
+      </x:c>
+      <x:c r="D14" s="42" t="n">
+        <x:v>165000</x:v>
+      </x:c>
+      <x:c r="E14" s="42" t="n">
+        <x:v>167500</x:v>
+      </x:c>
+      <x:c r="F14" s="42" t="n">
+        <x:v>147740</x:v>
+      </x:c>
+      <x:c r="G14" s="42" t="n">
+        <x:v>147740</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="n">
+        <x:v>-17140</x:v>
+      </x:c>
+      <x:c r="I14" s="43" t="n">
+        <x:v>-0.10395439107229498</x:v>
+      </x:c>
+      <x:c r="J14" s="26" t="n">
+        <x:f>ROUND(E14-F14,1)</x:f>
+        <x:v>19760</x:v>
+      </x:c>
+      <x:c r="K14" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="str">
+        <x:v>1月19日</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="n">
+        <x:v>150720</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="n">
+        <x:v>152800</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="n">
+        <x:v>143820</x:v>
+      </x:c>
+      <x:c r="G15" s="23" t="n">
+        <x:v>149300</x:v>
+      </x:c>
+      <x:c r="H15" s="28" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="I15" s="24" t="n">
+        <x:v>0.010559090293759343</x:v>
+      </x:c>
+      <x:c r="J15" s="26" t="n">
+        <x:f>ROUND(E15-F15,1)</x:f>
+        <x:v>8980</x:v>
+      </x:c>
+      <x:c r="K15" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>1月20日</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="n">
+        <x:v>152600</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="n">
+        <x:v>162560</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="n">
+        <x:v>151140</x:v>
+      </x:c>
+      <x:c r="G16" s="23" t="n">
+        <x:v>161900</x:v>
+      </x:c>
+      <x:c r="H16" s="28" t="n">
+        <x:v>12600</x:v>
+      </x:c>
+      <x:c r="I16" s="24" t="n">
+        <x:v>0.0843938379102478</x:v>
+      </x:c>
+      <x:c r="J16" s="26" t="n">
+        <x:f>ROUND(E16-F16,1)</x:f>
+        <x:v>11420</x:v>
+      </x:c>
+      <x:c r="K16" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="str">
+        <x:v>1月21日</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="n">
+        <x:v>162640</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="n">
+        <x:v>170600</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="G17" s="23" t="n">
+        <x:v>168320</x:v>
+      </x:c>
+      <x:c r="H17" s="28" t="n">
+        <x:v>6420</x:v>
+      </x:c>
+      <x:c r="I17" s="24" t="n">
+        <x:v>0.03965410747374931</x:v>
+      </x:c>
+      <x:c r="J17" s="26" t="n">
+        <x:f>ROUND(E17-F17,1)</x:f>
+        <x:v>10600</x:v>
+      </x:c>
+      <x:c r="K17" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>1月22日</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="n">
+        <x:v>168260</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="n">
+        <x:v>175520</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="n">
+        <x:v>165660</x:v>
+      </x:c>
+      <x:c r="G18" s="23" t="n">
+        <x:v>170120</x:v>
+      </x:c>
+      <x:c r="H18" s="28" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="I18" s="24" t="n">
+        <x:v>0.010693916349809873</x:v>
+      </x:c>
+      <x:c r="J18" s="26" t="n">
+        <x:f>ROUND(E18-F18,1)</x:f>
+        <x:v>9860</x:v>
+      </x:c>
+      <x:c r="K18" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="str">
+        <x:v>1月23日</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="n">
+        <x:v>173200</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="n">
+        <x:v>183780</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="n">
+        <x:v>173200</x:v>
+      </x:c>
+      <x:c r="G19" s="23" t="n">
+        <x:v>183380</x:v>
+      </x:c>
+      <x:c r="H19" s="28" t="n">
+        <x:v>13260</x:v>
+      </x:c>
+      <x:c r="I19" s="24" t="n">
+        <x:v>0.07794498001410766</x:v>
+      </x:c>
+      <x:c r="J19" s="26" t="n">
+        <x:f>ROUND(E19-F19,1)</x:f>
+        <x:v>10580</x:v>
+      </x:c>
+      <x:c r="K19" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B20" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="str">
+        <x:v>1月26日</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="n">
+        <x:v>187000</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="n">
+        <x:v>190600</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="n">
+        <x:v>165000</x:v>
+      </x:c>
+      <x:c r="G20" s="23" t="n">
+        <x:v>167000</x:v>
+      </x:c>
+      <x:c r="H20" s="28" t="n">
+        <x:v>-16380</x:v>
+      </x:c>
+      <x:c r="I20" s="24" t="n">
+        <x:v>-0.08932271785363721</x:v>
+      </x:c>
+      <x:c r="J20" s="26" t="n">
+        <x:f>ROUND(E20-F20,1)</x:f>
+        <x:v>25600</x:v>
+      </x:c>
+      <x:c r="K20" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
+        <x:v>1月27日</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="n">
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="n">
+        <x:v>180800</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="n">
+        <x:v>166140</x:v>
+      </x:c>
+      <x:c r="G21" s="23" t="n">
+        <x:v>180080</x:v>
+      </x:c>
+      <x:c r="H21" s="28" t="n">
+        <x:v>13080</x:v>
+      </x:c>
+      <x:c r="I21" s="24" t="n">
+        <x:v>0.07832335329341311</x:v>
+      </x:c>
+      <x:c r="J21" s="26" t="n">
+        <x:f>ROUND(E21-F21,1)</x:f>
+        <x:v>14660</x:v>
+      </x:c>
+      <x:c r="K21" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
+        <x:v>1月28日</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="n">
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="n">
+        <x:v>182880</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="n">
+        <x:v>165020</x:v>
+      </x:c>
+      <x:c r="G22" s="23" t="n">
+        <x:v>166800</x:v>
+      </x:c>
+      <x:c r="H22" s="28" t="n">
+        <x:v>-13280</x:v>
+      </x:c>
+      <x:c r="I22" s="24" t="n">
+        <x:v>-0.07374500222123503</x:v>
+      </x:c>
+      <x:c r="J22" s="26" t="n">
+        <x:f>ROUND(E22-F22,1)</x:f>
+        <x:v>17860</x:v>
+      </x:c>
+      <x:c r="K22" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
+        <x:v>1月29日</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="n">
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="n">
+        <x:v>174200</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="n">
+        <x:v>159400</x:v>
+      </x:c>
+      <x:c r="G23" s="23" t="n">
+        <x:v>166240</x:v>
+      </x:c>
+      <x:c r="H23" s="28" t="n">
+        <x:v>-560</x:v>
+      </x:c>
+      <x:c r="I23" s="24" t="n">
+        <x:v>-0.003357314148681012</x:v>
+      </x:c>
+      <x:c r="J23" s="26" t="n">
+        <x:f>ROUND(E23-F23,1)</x:f>
+        <x:v>14800</x:v>
+      </x:c>
+      <x:c r="K23" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>1月30日</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="n">
+        <x:v>164400</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="n">
+        <x:v>165660</x:v>
+      </x:c>
+      <x:c r="F24" s="23" t="n">
+        <x:v>148560</x:v>
+      </x:c>
+      <x:c r="G24" s="23" t="n">
+        <x:v>148560</x:v>
+      </x:c>
+      <x:c r="H24" s="28" t="n">
+        <x:v>-17680</x:v>
+      </x:c>
+      <x:c r="I24" s="24" t="n">
+        <x:v>-0.10635226179018287</x:v>
+      </x:c>
+      <x:c r="J24" s="26" t="n">
+        <x:f>ROUND(E24-F24,1)</x:f>
+        <x:v>17100</x:v>
+      </x:c>
+      <x:c r="K24" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B25" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C25" s="30"/>
+      <x:c r="D25" s="30"/>
+      <x:c r="E25" s="30"/>
+      <x:c r="F25" s="30"/>
+      <x:c r="G25" s="30"/>
+      <x:c r="H25" s="30"/>
+      <x:c r="I25" s="30"/>
+      <x:c r="J25" s="32" t="n">
+        <x:f>ROUND(SUM(J5:J24),1)</x:f>
+        <x:v>248540</x:v>
+      </x:c>
+      <x:c r="K25" s="30"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B26" s="30"/>
+      <x:c r="C26" s="30"/>
+      <x:c r="D26" s="30"/>
+      <x:c r="E26" s="30"/>
+      <x:c r="F26" s="30"/>
+      <x:c r="G26" s="30"/>
+      <x:c r="H26" s="30"/>
+      <x:c r="I26" s="30"/>
+      <x:c r="J26" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J5:J24),0),1)</x:f>
+        <x:v>12427</x:v>
+      </x:c>
+      <x:c r="K26" s="30"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="17" t="str">
+        <x:v>2月</x:v>
+      </x:c>
+      <x:c r="B28" s="17"/>
+      <x:c r="C28" s="17"/>
+      <x:c r="D28" s="17"/>
+      <x:c r="E28" s="17"/>
+      <x:c r="F28" s="17"/>
+      <x:c r="G28" s="17"/>
+      <x:c r="H28" s="17"/>
+      <x:c r="I28" s="17"/>
+      <x:c r="J28" s="17"/>
+      <x:c r="K28" s="17"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B29" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D29" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E29" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F29" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G29" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H29" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I29" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J29" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B30" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="str">
+        <x:v>2月2日</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="n">
+        <x:v>148040</x:v>
+      </x:c>
+      <x:c r="E30" s="23" t="n">
+        <x:v>153200</x:v>
+      </x:c>
+      <x:c r="F30" s="23" t="n">
+        <x:v>132500</x:v>
+      </x:c>
+      <x:c r="G30" s="23" t="n">
+        <x:v>132500</x:v>
+      </x:c>
+      <x:c r="H30" s="28" t="n">
+        <x:v>-16060</x:v>
+      </x:c>
+      <x:c r="I30" s="24" t="n">
+        <x:v>-0.10810446957458264</x:v>
+      </x:c>
+      <x:c r="J30" s="26" t="n">
+        <x:f>ROUND(E30-F30,1)</x:f>
+        <x:v>20700</x:v>
+      </x:c>
+      <x:c r="K30" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B31" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="str">
+        <x:v>2月3日</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="E31" s="23" t="n">
+        <x:v>152000</x:v>
+      </x:c>
+      <x:c r="F31" s="23" t="n">
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="G31" s="23" t="n">
+        <x:v>147500</x:v>
+      </x:c>
+      <x:c r="H31" s="28" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="I31" s="24" t="n">
+        <x:v>0.1132075471698113</x:v>
+      </x:c>
+      <x:c r="J31" s="26" t="n">
+        <x:f>ROUND(E31-F31,1)</x:f>
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="K31" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C32" s="22" t="str">
+        <x:v>2月4日</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="n">
+        <x:v>149200</x:v>
+      </x:c>
+      <x:c r="E32" s="23" t="n">
+        <x:v>152600</x:v>
+      </x:c>
+      <x:c r="F32" s="23" t="n">
+        <x:v>145720</x:v>
+      </x:c>
+      <x:c r="G32" s="23" t="n">
+        <x:v>147200</x:v>
+      </x:c>
+      <x:c r="H32" s="28" t="n">
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="I32" s="24" t="n">
+        <x:v>-0.0020338983050847137</x:v>
+      </x:c>
+      <x:c r="J32" s="26" t="n">
+        <x:f>ROUND(E32-F32,1)</x:f>
+        <x:v>6880</x:v>
+      </x:c>
+      <x:c r="K32" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B33" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C33" s="22" t="str">
+        <x:v>2月5日</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="E33" s="23" t="n">
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="F33" s="23" t="n">
+        <x:v>132360</x:v>
+      </x:c>
+      <x:c r="G33" s="23" t="n">
+        <x:v>132800</x:v>
+      </x:c>
+      <x:c r="H33" s="28" t="n">
+        <x:v>-14400</x:v>
+      </x:c>
+      <x:c r="I33" s="24" t="n">
+        <x:v>-0.09782608695652173</x:v>
+      </x:c>
+      <x:c r="J33" s="26" t="n">
+        <x:f>ROUND(E33-F33,1)</x:f>
+        <x:v>14640</x:v>
+      </x:c>
+      <x:c r="K33" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B34" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="str">
+        <x:v>2月6日</x:v>
+      </x:c>
+      <x:c r="D34" s="23" t="n">
+        <x:v>129780</x:v>
+      </x:c>
+      <x:c r="E34" s="23" t="n">
+        <x:v>139000</x:v>
+      </x:c>
+      <x:c r="F34" s="23" t="n">
+        <x:v>124480</x:v>
+      </x:c>
+      <x:c r="G34" s="23" t="n">
+        <x:v>133500</x:v>
+      </x:c>
+      <x:c r="H34" s="28" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="I34" s="24" t="n">
+        <x:v>0.005271084337349352</x:v>
+      </x:c>
+      <x:c r="J34" s="26" t="n">
+        <x:f>ROUND(E34-F34,1)</x:f>
+        <x:v>14520</x:v>
+      </x:c>
+      <x:c r="K34" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B35" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C35" s="22" t="str">
+        <x:v>2月9日</x:v>
+      </x:c>
+      <x:c r="D35" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="E35" s="23" t="n">
+        <x:v>139900</x:v>
+      </x:c>
+      <x:c r="F35" s="23" t="n">
+        <x:v>135100</x:v>
+      </x:c>
+      <x:c r="G35" s="23" t="n">
+        <x:v>137400</x:v>
+      </x:c>
+      <x:c r="H35" s="28" t="n">
+        <x:v>3900</x:v>
+      </x:c>
+      <x:c r="I35" s="24" t="n">
+        <x:v>0.02921348314606731</x:v>
+      </x:c>
+      <x:c r="J35" s="23" t="n">
+        <x:f>ROUND(E35-F35,1)</x:f>
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="K35" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B36" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C36" s="22" t="str">
+        <x:v>2月10日</x:v>
+      </x:c>
+      <x:c r="D36" s="23" t="n">
+        <x:v>136220</x:v>
+      </x:c>
+      <x:c r="E36" s="23" t="n">
+        <x:v>141220</x:v>
+      </x:c>
+      <x:c r="F36" s="23" t="n">
+        <x:v>133500</x:v>
+      </x:c>
+      <x:c r="G36" s="23" t="n">
+        <x:v>137560</x:v>
+      </x:c>
+      <x:c r="H36" s="28" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I36" s="24" t="n">
+        <x:v>0.001164483260553073</x:v>
+      </x:c>
+      <x:c r="J36" s="26" t="n">
+        <x:f>ROUND(E36-F36,1)</x:f>
+        <x:v>7720</x:v>
+      </x:c>
+      <x:c r="K36" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B37" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C37" s="22" t="str">
+        <x:v>2月11日</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="n">
+        <x:v>137880</x:v>
+      </x:c>
+      <x:c r="E37" s="23" t="n">
+        <x:v>150720</x:v>
+      </x:c>
+      <x:c r="F37" s="23" t="n">
+        <x:v>137880</x:v>
+      </x:c>
+      <x:c r="G37" s="23" t="n">
+        <x:v>150600</x:v>
+      </x:c>
+      <x:c r="H37" s="28" t="n">
+        <x:v>13040</x:v>
+      </x:c>
+      <x:c r="I37" s="24" t="n">
+        <x:v>0.09479499854608897</x:v>
+      </x:c>
+      <x:c r="J37" s="26" t="n">
+        <x:f>ROUND(E37-F37,1)</x:f>
+        <x:v>12840</x:v>
+      </x:c>
+      <x:c r="K37" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B38" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C38" s="22" t="str">
+        <x:v>2月12日</x:v>
+      </x:c>
+      <x:c r="D38" s="23" t="n">
+        <x:v>149200</x:v>
+      </x:c>
+      <x:c r="E38" s="23" t="n">
+        <x:v>152720</x:v>
+      </x:c>
+      <x:c r="F38" s="23" t="n">
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="G38" s="23" t="n">
+        <x:v>149380</x:v>
+      </x:c>
+      <x:c r="H38" s="28" t="n">
+        <x:v>-1220</x:v>
+      </x:c>
+      <x:c r="I38" s="24" t="n">
+        <x:v>-0.008100929614873853</x:v>
+      </x:c>
+      <x:c r="J38" s="23" t="n">
+        <x:f>ROUND(E38-F38,1)</x:f>
+        <x:v>5720</x:v>
+      </x:c>
+      <x:c r="K38" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B39" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C39" s="22" t="str">
+        <x:v>2月13日</x:v>
+      </x:c>
+      <x:c r="D39" s="23" t="n">
+        <x:v>143000</x:v>
+      </x:c>
+      <x:c r="E39" s="23" t="n">
+        <x:v>153700</x:v>
+      </x:c>
+      <x:c r="F39" s="23" t="n">
+        <x:v>142560</x:v>
+      </x:c>
+      <x:c r="G39" s="23" t="n">
+        <x:v>153500</x:v>
+      </x:c>
+      <x:c r="H39" s="28" t="n">
+        <x:v>4120</x:v>
+      </x:c>
+      <x:c r="I39" s="24" t="n">
+        <x:v>0.02758066675592441</x:v>
+      </x:c>
+      <x:c r="J39" s="26" t="n">
+        <x:f>ROUND(E39-F39,1)</x:f>
+        <x:v>11140</x:v>
+      </x:c>
+      <x:c r="K39" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="41" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B40" s="41" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C40" s="41" t="str">
+        <x:v>2月24日</x:v>
+      </x:c>
+      <x:c r="D40" s="42" t="n">
+        <x:v>158340</x:v>
+      </x:c>
+      <x:c r="E40" s="42" t="n">
+        <x:v>166800</x:v>
+      </x:c>
+      <x:c r="F40" s="42" t="n">
+        <x:v>158340</x:v>
+      </x:c>
+      <x:c r="G40" s="42" t="n">
+        <x:v>165920</x:v>
+      </x:c>
+      <x:c r="H40" s="28" t="n">
+        <x:v>12420</x:v>
+      </x:c>
+      <x:c r="I40" s="43" t="n">
+        <x:v>0.08091205211726393</x:v>
+      </x:c>
+      <x:c r="J40" s="26" t="n">
+        <x:f>ROUND(E40-F40,1)</x:f>
+        <x:v>8460</x:v>
+      </x:c>
+      <x:c r="K40" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B41" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C41" s="22" t="str">
+        <x:v>2月25日</x:v>
+      </x:c>
+      <x:c r="D41" s="23" t="n">
+        <x:v>165620</x:v>
+      </x:c>
+      <x:c r="E41" s="23" t="n">
+        <x:v>172320</x:v>
+      </x:c>
+      <x:c r="F41" s="23" t="n">
+        <x:v>165040</x:v>
+      </x:c>
+      <x:c r="G41" s="23" t="n">
+        <x:v>167200</x:v>
+      </x:c>
+      <x:c r="H41" s="28" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="I41" s="24" t="n">
+        <x:v>0.0077145612343298975</x:v>
+      </x:c>
+      <x:c r="J41" s="26" t="n">
+        <x:f>ROUND(E41-F41,1)</x:f>
+        <x:v>7280</x:v>
+      </x:c>
+      <x:c r="K41" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B42" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C42" s="22" t="str">
+        <x:v>2月26日</x:v>
+      </x:c>
+      <x:c r="D42" s="23" t="n">
+        <x:v>186000</x:v>
+      </x:c>
+      <x:c r="E42" s="23" t="n">
+        <x:v>186900</x:v>
+      </x:c>
+      <x:c r="F42" s="23" t="n">
+        <x:v>172000</x:v>
+      </x:c>
+      <x:c r="G42" s="23" t="n">
+        <x:v>175080</x:v>
+      </x:c>
+      <x:c r="H42" s="28" t="n">
+        <x:v>7880</x:v>
+      </x:c>
+      <x:c r="I42" s="24" t="n">
+        <x:v>0.04712918660287091</x:v>
+      </x:c>
+      <x:c r="J42" s="26" t="n">
+        <x:f>ROUND(E42-F42,1)</x:f>
+        <x:v>14900</x:v>
+      </x:c>
+      <x:c r="K42" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B43" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C43" s="22" t="str">
+        <x:v>2月27日</x:v>
+      </x:c>
+      <x:c r="D43" s="23" t="n">
+        <x:v>175220</x:v>
+      </x:c>
+      <x:c r="E43" s="23" t="n">
+        <x:v>177600</x:v>
+      </x:c>
+      <x:c r="F43" s="23" t="n">
+        <x:v>169160</x:v>
+      </x:c>
+      <x:c r="G43" s="23" t="n">
+        <x:v>177200</x:v>
+      </x:c>
+      <x:c r="H43" s="28" t="n">
+        <x:v>2120</x:v>
+      </x:c>
+      <x:c r="I43" s="24" t="n">
+        <x:v>0.01210875028558367</x:v>
+      </x:c>
+      <x:c r="J43" s="26" t="n">
+        <x:f>ROUND(E43-F43,1)</x:f>
+        <x:v>8440</x:v>
+      </x:c>
+      <x:c r="K43" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B44" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C44" s="30"/>
+      <x:c r="D44" s="30"/>
+      <x:c r="E44" s="30"/>
+      <x:c r="F44" s="30"/>
+      <x:c r="G44" s="30"/>
+      <x:c r="H44" s="30"/>
+      <x:c r="I44" s="30"/>
+      <x:c r="J44" s="32" t="n">
+        <x:f>ROUND(SUM(J30:J43),1)</x:f>
+        <x:v>153040</x:v>
+      </x:c>
+      <x:c r="K44" s="30"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B45" s="30"/>
+      <x:c r="C45" s="30"/>
+      <x:c r="D45" s="30"/>
+      <x:c r="E45" s="30"/>
+      <x:c r="F45" s="30"/>
+      <x:c r="G45" s="30"/>
+      <x:c r="H45" s="30"/>
+      <x:c r="I45" s="30"/>
+      <x:c r="J45" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J30:J43),0),1)</x:f>
+        <x:v>10931.4</x:v>
+      </x:c>
+      <x:c r="K45" s="30"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="17" t="str">
+        <x:v>3月</x:v>
+      </x:c>
+      <x:c r="B47" s="17"/>
+      <x:c r="C47" s="17"/>
+      <x:c r="D47" s="17"/>
+      <x:c r="E47" s="17"/>
+      <x:c r="F47" s="17"/>
+      <x:c r="G47" s="17"/>
+      <x:c r="H47" s="17"/>
+      <x:c r="I47" s="17"/>
+      <x:c r="J47" s="17"/>
+      <x:c r="K47" s="17"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B48" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D48" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E48" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F48" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G48" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H48" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I48" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J48" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K48" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B49" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C49" s="22" t="str">
+        <x:v>3月2日</x:v>
+      </x:c>
+      <x:c r="D49" s="23" t="n">
+        <x:v>180000</x:v>
+      </x:c>
+      <x:c r="E49" s="23" t="n">
+        <x:v>180060</x:v>
+      </x:c>
+      <x:c r="F49" s="23" t="n">
+        <x:v>170620</x:v>
+      </x:c>
+      <x:c r="G49" s="23" t="n">
+        <x:v>172780</x:v>
+      </x:c>
+      <x:c r="H49" s="28" t="n">
+        <x:v>-4420</x:v>
+      </x:c>
+      <x:c r="I49" s="24" t="n">
+        <x:v>-0.02494356659142216</x:v>
+      </x:c>
+      <x:c r="J49" s="26" t="n">
+        <x:f>ROUND(E49-F49,1)</x:f>
+        <x:v>9440</x:v>
+      </x:c>
+      <x:c r="K49" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B50" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C50" s="22" t="str">
+        <x:v>3月3日</x:v>
+      </x:c>
+      <x:c r="D50" s="23" t="n">
+        <x:v>170800</x:v>
+      </x:c>
+      <x:c r="E50" s="23" t="n">
+        <x:v>171340</x:v>
+      </x:c>
+      <x:c r="F50" s="23" t="n">
+        <x:v>151780</x:v>
+      </x:c>
+      <x:c r="G50" s="23" t="n">
+        <x:v>151780</x:v>
+      </x:c>
+      <x:c r="H50" s="28" t="n">
+        <x:v>-21000</x:v>
+      </x:c>
+      <x:c r="I50" s="24" t="n">
+        <x:v>-0.12154184512096311</x:v>
+      </x:c>
+      <x:c r="J50" s="26" t="n">
+        <x:f>ROUND(E50-F50,1)</x:f>
+        <x:v>19560</x:v>
+      </x:c>
+      <x:c r="K50" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B51" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="str">
+        <x:v>3月4日</x:v>
+      </x:c>
+      <x:c r="D51" s="23" t="n">
+        <x:v>151000</x:v>
+      </x:c>
+      <x:c r="E51" s="23" t="n">
+        <x:v>156000</x:v>
+      </x:c>
+      <x:c r="F51" s="23" t="n">
+        <x:v>146040</x:v>
+      </x:c>
+      <x:c r="G51" s="23" t="n">
+        <x:v>153740</x:v>
+      </x:c>
+      <x:c r="H51" s="28" t="n">
+        <x:v>1960</x:v>
+      </x:c>
+      <x:c r="I51" s="24" t="n">
+        <x:v>0.012913427329028782</x:v>
+      </x:c>
+      <x:c r="J51" s="26" t="n">
+        <x:f>ROUND(E51-F51,1)</x:f>
+        <x:v>9960</x:v>
+      </x:c>
+      <x:c r="K51" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B52" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C52" s="22" t="str">
+        <x:v>3月5日</x:v>
+      </x:c>
+      <x:c r="D52" s="23" t="n">
+        <x:v>155020</x:v>
+      </x:c>
+      <x:c r="E52" s="23" t="n">
+        <x:v>161600</x:v>
+      </x:c>
+      <x:c r="F52" s="23" t="n">
+        <x:v>149660</x:v>
+      </x:c>
+      <x:c r="G52" s="23" t="n">
+        <x:v>156300</x:v>
+      </x:c>
+      <x:c r="H52" s="28" t="n">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="I52" s="24" t="n">
+        <x:v>0.016651489527774066</x:v>
+      </x:c>
+      <x:c r="J52" s="26" t="n">
+        <x:f>ROUND(E52-F52,1)</x:f>
+        <x:v>11940</x:v>
+      </x:c>
+      <x:c r="K52" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B53" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C53" s="22" t="str">
+        <x:v>3月6日</x:v>
+      </x:c>
+      <x:c r="D53" s="23" t="n">
+        <x:v>155520</x:v>
+      </x:c>
+      <x:c r="E53" s="23" t="n">
+        <x:v>160820</x:v>
+      </x:c>
+      <x:c r="F53" s="23" t="n">
+        <x:v>151600</x:v>
+      </x:c>
+      <x:c r="G53" s="23" t="n">
+        <x:v>156700</x:v>
+      </x:c>
+      <x:c r="H53" s="28" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="I53" s="24" t="n">
+        <x:v>0.002559181062060212</x:v>
+      </x:c>
+      <x:c r="J53" s="26" t="n">
+        <x:f>ROUND(E53-F53,1)</x:f>
+        <x:v>9220</x:v>
+      </x:c>
+      <x:c r="K53" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B54" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C54" s="22" t="str">
+        <x:v>3月9日</x:v>
+      </x:c>
+      <x:c r="D54" s="23" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="E54" s="23" t="n">
+        <x:v>165600</x:v>
+      </x:c>
+      <x:c r="F54" s="23" t="n">
+        <x:v>142600</x:v>
+      </x:c>
+      <x:c r="G54" s="23" t="n">
+        <x:v>161500</x:v>
+      </x:c>
+      <x:c r="H54" s="28" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="I54" s="24" t="n">
+        <x:v>0.030631780472240022</x:v>
+      </x:c>
+      <x:c r="J54" s="26" t="n">
+        <x:f>ROUND(E54-F54,1)</x:f>
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="K54" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B55" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C55" s="22" t="str">
+        <x:v>3月10日</x:v>
+      </x:c>
+      <x:c r="D55" s="23" t="n">
+        <x:v>162000</x:v>
+      </x:c>
+      <x:c r="E55" s="23" t="n">
+        <x:v>166980</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="n">
+        <x:v>160020</x:v>
+      </x:c>
+      <x:c r="G55" s="23" t="n">
+        <x:v>163000</x:v>
+      </x:c>
+      <x:c r="H55" s="28" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="I55" s="24" t="n">
+        <x:v>0.009287925696594534</x:v>
+      </x:c>
+      <x:c r="J55" s="26" t="n">
+        <x:f>ROUND(E55-F55,1)</x:f>
+        <x:v>6960</x:v>
+      </x:c>
+      <x:c r="K55" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B56" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C56" s="22" t="str">
+        <x:v>3月11日</x:v>
+      </x:c>
+      <x:c r="D56" s="23" t="n">
+        <x:v>163000</x:v>
+      </x:c>
+      <x:c r="E56" s="23" t="n">
+        <x:v>167400</x:v>
+      </x:c>
+      <x:c r="F56" s="23" t="n">
+        <x:v>155200</x:v>
+      </x:c>
+      <x:c r="G56" s="23" t="n">
+        <x:v>155280</x:v>
+      </x:c>
+      <x:c r="H56" s="28" t="n">
+        <x:v>-7720</x:v>
+      </x:c>
+      <x:c r="I56" s="24" t="n">
+        <x:v>-0.04736196319018404</x:v>
+      </x:c>
+      <x:c r="J56" s="26" t="n">
+        <x:f>ROUND(E56-F56,1)</x:f>
+        <x:v>12200</x:v>
+      </x:c>
+      <x:c r="K56" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B57" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C57" s="22" t="str">
+        <x:v>3月12日</x:v>
+      </x:c>
+      <x:c r="D57" s="23" t="n">
+        <x:v>156000</x:v>
+      </x:c>
+      <x:c r="E57" s="23" t="n">
+        <x:v>159700</x:v>
+      </x:c>
+      <x:c r="F57" s="23" t="n">
+        <x:v>153100</x:v>
+      </x:c>
+      <x:c r="G57" s="23" t="n">
+        <x:v>157100</x:v>
+      </x:c>
+      <x:c r="H57" s="28" t="n">
+        <x:v>1820</x:v>
+      </x:c>
+      <x:c r="I57" s="24" t="n">
+        <x:v>0.011720762493560022</x:v>
+      </x:c>
+      <x:c r="J57" s="26" t="n">
+        <x:f>ROUND(E57-F57,1)</x:f>
+        <x:v>6600</x:v>
+      </x:c>
+      <x:c r="K57" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B58" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C58" s="22" t="str">
+        <x:v>3月13日</x:v>
+      </x:c>
+      <x:c r="D58" s="23" t="n">
+        <x:v>155000</x:v>
+      </x:c>
+      <x:c r="E58" s="23" t="n">
+        <x:v>162960</x:v>
+      </x:c>
+      <x:c r="F58" s="23" t="n">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="G58" s="23" t="n">
+        <x:v>152100</x:v>
+      </x:c>
+      <x:c r="H58" s="28" t="n">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="I58" s="24" t="n">
+        <x:v>-0.031826861871419476</x:v>
+      </x:c>
+      <x:c r="J58" s="26" t="n">
+        <x:f>ROUND(E58-F58,1)</x:f>
+        <x:v>12960</x:v>
+      </x:c>
+      <x:c r="K58" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B59" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C59" s="22" t="str">
+        <x:v>3月16日</x:v>
+      </x:c>
+      <x:c r="D59" s="23" t="n">
+        <x:v>150880</x:v>
+      </x:c>
+      <x:c r="E59" s="23" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="F59" s="23" t="n">
+        <x:v>149160</x:v>
+      </x:c>
+      <x:c r="G59" s="23" t="n">
+        <x:v>159560</x:v>
+      </x:c>
+      <x:c r="H59" s="28" t="n">
+        <x:v>7460</x:v>
+      </x:c>
+      <x:c r="I59" s="24" t="n">
+        <x:v>0.0490466798159106</x:v>
+      </x:c>
+      <x:c r="J59" s="26" t="n">
+        <x:f>ROUND(E59-F59,1)</x:f>
+        <x:v>10840</x:v>
+      </x:c>
+      <x:c r="K59" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B60" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C60" s="22" t="str">
+        <x:v>3月17日</x:v>
+      </x:c>
+      <x:c r="D60" s="23" t="n">
+        <x:v>159700</x:v>
+      </x:c>
+      <x:c r="E60" s="23" t="n">
+        <x:v>160800</x:v>
+      </x:c>
+      <x:c r="F60" s="23" t="n">
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="G60" s="23" t="n">
+        <x:v>155260</x:v>
+      </x:c>
+      <x:c r="H60" s="28" t="n">
+        <x:v>-4300</x:v>
+      </x:c>
+      <x:c r="I60" s="24" t="n">
+        <x:v>-0.026949110052644776</x:v>
+      </x:c>
+      <x:c r="J60" s="26" t="n">
+        <x:f>ROUND(E60-F60,1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="K60" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B61" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C61" s="22" t="str">
+        <x:v>3月18日</x:v>
+      </x:c>
+      <x:c r="D61" s="23" t="n">
+        <x:v>154400</x:v>
+      </x:c>
+      <x:c r="E61" s="23" t="n">
+        <x:v>156600</x:v>
+      </x:c>
+      <x:c r="F61" s="23" t="n">
+        <x:v>149560</x:v>
+      </x:c>
+      <x:c r="G61" s="23" t="n">
+        <x:v>150020</x:v>
+      </x:c>
+      <x:c r="H61" s="28" t="n">
+        <x:v>-5240</x:v>
+      </x:c>
+      <x:c r="I61" s="24" t="n">
+        <x:v>-0.033749838979775904</x:v>
+      </x:c>
+      <x:c r="J61" s="26" t="n">
+        <x:f>ROUND(E61-F61,1)</x:f>
+        <x:v>7040</x:v>
+      </x:c>
+      <x:c r="K61" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B62" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C62" s="22" t="str">
+        <x:v>3月19日</x:v>
+      </x:c>
+      <x:c r="D62" s="23" t="n">
+        <x:v>147840</x:v>
+      </x:c>
+      <x:c r="E62" s="23" t="n">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="F62" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="G62" s="23" t="n">
+        <x:v>142500</x:v>
+      </x:c>
+      <x:c r="H62" s="28" t="n">
+        <x:v>-7520</x:v>
+      </x:c>
+      <x:c r="I62" s="24" t="n">
+        <x:v>-0.05012664978002934</x:v>
+      </x:c>
+      <x:c r="J62" s="26" t="n">
+        <x:f>ROUND(E62-F62,1)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K62" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B63" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C63" s="41" t="str">
+        <x:v>3月20日</x:v>
+      </x:c>
+      <x:c r="D63" s="42" t="n">
+        <x:v>145500</x:v>
+      </x:c>
+      <x:c r="E63" s="42" t="n">
+        <x:v>150800</x:v>
+      </x:c>
+      <x:c r="F63" s="42" t="n">
+        <x:v>143300</x:v>
+      </x:c>
+      <x:c r="G63" s="42" t="n">
+        <x:v>143520</x:v>
+      </x:c>
+      <x:c r="H63" s="28" t="n">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="I63" s="43" t="n">
+        <x:v>0.00715789473684203</x:v>
+      </x:c>
+      <x:c r="J63" s="26" t="n">
+        <x:f>ROUND(E63-F63,1)</x:f>
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="K63" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B64" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="str">
+        <x:v>3月23日</x:v>
+      </x:c>
+      <x:c r="D64" s="23" t="n">
+        <x:v>141220</x:v>
+      </x:c>
+      <x:c r="E64" s="23" t="n">
+        <x:v>149300</x:v>
+      </x:c>
+      <x:c r="F64" s="23" t="n">
+        <x:v>140020</x:v>
+      </x:c>
+      <x:c r="G64" s="23" t="n">
+        <x:v>149040</x:v>
+      </x:c>
+      <x:c r="H64" s="28" t="n">
+        <x:v>5520</x:v>
+      </x:c>
+      <x:c r="I64" s="24" t="n">
+        <x:v>0.03846153846153855</x:v>
+      </x:c>
+      <x:c r="J64" s="26" t="n">
+        <x:f>ROUND(E64-F64,1)</x:f>
+        <x:v>9280</x:v>
+      </x:c>
+      <x:c r="K64" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B65" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="str">
+        <x:v>3月24日</x:v>
+      </x:c>
+      <x:c r="D65" s="23" t="n">
+        <x:v>151700</x:v>
+      </x:c>
+      <x:c r="E65" s="23" t="n">
+        <x:v>154660</x:v>
+      </x:c>
+      <x:c r="F65" s="23" t="n">
+        <x:v>150220</x:v>
+      </x:c>
+      <x:c r="G65" s="23" t="n">
+        <x:v>152900</x:v>
+      </x:c>
+      <x:c r="H65" s="28" t="n">
+        <x:v>3860</x:v>
+      </x:c>
+      <x:c r="I65" s="24" t="n">
+        <x:v>0.025899087493290285</x:v>
+      </x:c>
+      <x:c r="J65" s="23" t="n">
+        <x:f>ROUND(E65-F65,1)</x:f>
+        <x:v>4440</x:v>
+      </x:c>
+      <x:c r="K65" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B66" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="str">
+        <x:v>3月25日</x:v>
+      </x:c>
+      <x:c r="D66" s="23" t="n">
+        <x:v>156000</x:v>
+      </x:c>
+      <x:c r="E66" s="23" t="n">
+        <x:v>161500</x:v>
+      </x:c>
+      <x:c r="F66" s="23" t="n">
+        <x:v>154500</x:v>
+      </x:c>
+      <x:c r="G66" s="23" t="n">
+        <x:v>158960</x:v>
+      </x:c>
+      <x:c r="H66" s="28" t="n">
+        <x:v>6060</x:v>
+      </x:c>
+      <x:c r="I66" s="24" t="n">
+        <x:v>0.039633747547416665</x:v>
+      </x:c>
+      <x:c r="J66" s="26" t="n">
+        <x:f>ROUND(E66-F66,1)</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="K66" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B67" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="str">
+        <x:v>3月26日</x:v>
+      </x:c>
+      <x:c r="D67" s="23" t="n">
+        <x:v>158980</x:v>
+      </x:c>
+      <x:c r="E67" s="23" t="n">
+        <x:v>162860</x:v>
+      </x:c>
+      <x:c r="F67" s="23" t="n">
+        <x:v>155600</x:v>
+      </x:c>
+      <x:c r="G67" s="23" t="n">
+        <x:v>158040</x:v>
+      </x:c>
+      <x:c r="H67" s="28" t="n">
+        <x:v>-920</x:v>
+      </x:c>
+      <x:c r="I67" s="24" t="n">
+        <x:v>-0.00578761952692497</x:v>
+      </x:c>
+      <x:c r="J67" s="26" t="n">
+        <x:f>ROUND(E67-F67,1)</x:f>
+        <x:v>7260</x:v>
+      </x:c>
+      <x:c r="K67" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B68" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C68" s="22" t="str">
+        <x:v>3月27日</x:v>
+      </x:c>
+      <x:c r="D68" s="23" t="n">
+        <x:v>157660</x:v>
+      </x:c>
+      <x:c r="E68" s="23" t="n">
+        <x:v>172220</x:v>
+      </x:c>
+      <x:c r="F68" s="23" t="n">
+        <x:v>157000</x:v>
+      </x:c>
+      <x:c r="G68" s="23" t="n">
+        <x:v>169400</x:v>
+      </x:c>
+      <x:c r="H68" s="28" t="n">
+        <x:v>11360</x:v>
+      </x:c>
+      <x:c r="I68" s="24" t="n">
+        <x:v>0.07188053657301952</x:v>
+      </x:c>
+      <x:c r="J68" s="26" t="n">
+        <x:f>ROUND(E68-F68,1)</x:f>
+        <x:v>15220</x:v>
+      </x:c>
+      <x:c r="K68" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B69" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C69" s="22" t="str">
+        <x:v>3月30日</x:v>
+      </x:c>
+      <x:c r="D69" s="23" t="n">
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="E69" s="23" t="n">
+        <x:v>175000</x:v>
+      </x:c>
+      <x:c r="F69" s="23" t="n">
+        <x:v>169040</x:v>
+      </x:c>
+      <x:c r="G69" s="23" t="n">
+        <x:v>172860</x:v>
+      </x:c>
+      <x:c r="H69" s="28" t="n">
+        <x:v>3460</x:v>
+      </x:c>
+      <x:c r="I69" s="24" t="n">
+        <x:v>0.020425029515938498</x:v>
+      </x:c>
+      <x:c r="J69" s="23" t="n">
+        <x:f>ROUND(E69-F69,1)</x:f>
+        <x:v>5960</x:v>
+      </x:c>
+      <x:c r="K69" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="22" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B70" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C70" s="22" t="str">
+        <x:v>3月31日</x:v>
+      </x:c>
+      <x:c r="D70" s="23" t="n">
+        <x:v>170800</x:v>
+      </x:c>
+      <x:c r="E70" s="23" t="n">
+        <x:v>173380</x:v>
+      </x:c>
+      <x:c r="F70" s="23" t="n">
+        <x:v>157700</x:v>
+      </x:c>
+      <x:c r="G70" s="23" t="n">
+        <x:v>158040</x:v>
+      </x:c>
+      <x:c r="H70" s="28" t="n">
+        <x:v>-14820</x:v>
+      </x:c>
+      <x:c r="I70" s="24" t="n">
+        <x:v>-0.0857341200971885</x:v>
+      </x:c>
+      <x:c r="J70" s="26" t="n">
+        <x:f>ROUND(E70-F70,1)</x:f>
+        <x:v>15680</x:v>
+      </x:c>
+      <x:c r="K70" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B71" s="30" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C71" s="30"/>
+      <x:c r="D71" s="30"/>
+      <x:c r="E71" s="30"/>
+      <x:c r="F71" s="30"/>
+      <x:c r="G71" s="30"/>
+      <x:c r="H71" s="30"/>
+      <x:c r="I71" s="30"/>
+      <x:c r="J71" s="32" t="n">
+        <x:f>ROUND(SUM(J49:J70),1)</x:f>
+        <x:v>228860</x:v>
+      </x:c>
+      <x:c r="K71" s="30"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B72" s="30"/>
+      <x:c r="C72" s="30"/>
+      <x:c r="D72" s="30"/>
+      <x:c r="E72" s="30"/>
+      <x:c r="F72" s="30"/>
+      <x:c r="G72" s="30"/>
+      <x:c r="H72" s="30"/>
+      <x:c r="I72" s="30"/>
+      <x:c r="J72" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J49:J70),0),1)</x:f>
+        <x:v>10402.7</x:v>
+      </x:c>
+      <x:c r="K72" s="30"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="17" t="str">
+        <x:v>4月</x:v>
+      </x:c>
+      <x:c r="B74" s="17"/>
+      <x:c r="C74" s="17"/>
+      <x:c r="D74" s="17"/>
+      <x:c r="E74" s="17"/>
+      <x:c r="F74" s="17"/>
+      <x:c r="G74" s="17"/>
+      <x:c r="H74" s="17"/>
+      <x:c r="I74" s="17"/>
+      <x:c r="J74" s="17"/>
+      <x:c r="K74" s="17"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B75" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C75" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D75" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E75" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F75" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G75" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H75" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I75" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J75" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K75" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B76" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C76" s="22" t="str">
+        <x:v>4月1日</x:v>
+      </x:c>
+      <x:c r="D76" s="23" t="n">
+        <x:v>161000</x:v>
+      </x:c>
+      <x:c r="E76" s="23" t="n">
+        <x:v>164500</x:v>
+      </x:c>
+      <x:c r="F76" s="23" t="n">
+        <x:v>154560</x:v>
+      </x:c>
+      <x:c r="G76" s="23" t="n">
+        <x:v>159060</x:v>
+      </x:c>
+      <x:c r="H76" s="28" t="n">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="I76" s="24" t="n">
+        <x:v>0.006454062262718274</x:v>
+      </x:c>
+      <x:c r="J76" s="26" t="n">
+        <x:f>ROUND(E76-F76,1)</x:f>
+        <x:v>9940</x:v>
+      </x:c>
+      <x:c r="K76" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B77" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C77" s="22" t="str">
+        <x:v>4月2日</x:v>
+      </x:c>
+      <x:c r="D77" s="23" t="n">
+        <x:v>159800</x:v>
+      </x:c>
+      <x:c r="E77" s="23" t="n">
+        <x:v>163800</x:v>
+      </x:c>
+      <x:c r="F77" s="23" t="n">
+        <x:v>156000</x:v>
+      </x:c>
+      <x:c r="G77" s="23" t="n">
+        <x:v>160180</x:v>
+      </x:c>
+      <x:c r="H77" s="28" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="I77" s="24" t="n">
+        <x:v>0.007041368037218554</x:v>
+      </x:c>
+      <x:c r="J77" s="26" t="n">
+        <x:f>ROUND(E77-F77,1)</x:f>
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="K77" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B78" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C78" s="22" t="str">
+        <x:v>4月3日</x:v>
+      </x:c>
+      <x:c r="D78" s="23" t="n">
+        <x:v>161000</x:v>
+      </x:c>
+      <x:c r="E78" s="23" t="n">
+        <x:v>163120</x:v>
+      </x:c>
+      <x:c r="F78" s="23" t="n">
+        <x:v>157220</x:v>
+      </x:c>
+      <x:c r="G78" s="23" t="n">
+        <x:v>157860</x:v>
+      </x:c>
+      <x:c r="H78" s="28" t="n">
+        <x:v>-2320</x:v>
+      </x:c>
+      <x:c r="I78" s="24" t="n">
+        <x:v>-0.014483705830940163</x:v>
+      </x:c>
+      <x:c r="J78" s="23" t="n">
+        <x:f>ROUND(E78-F78,1)</x:f>
+        <x:v>5900</x:v>
+      </x:c>
+      <x:c r="K78" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B79" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C79" s="22" t="str">
+        <x:v>4月7日</x:v>
+      </x:c>
+      <x:c r="D79" s="23" t="n">
+        <x:v>158440</x:v>
+      </x:c>
+      <x:c r="E79" s="23" t="n">
+        <x:v>165500</x:v>
+      </x:c>
+      <x:c r="F79" s="23" t="n">
+        <x:v>156500</x:v>
+      </x:c>
+      <x:c r="G79" s="23" t="n">
+        <x:v>160860</x:v>
+      </x:c>
+      <x:c r="H79" s="28" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I79" s="24" t="n">
+        <x:v>0.01900418091980227</x:v>
+      </x:c>
+      <x:c r="J79" s="26" t="n">
+        <x:f>ROUND(E79-F79,1)</x:f>
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="K79" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B80" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C80" s="22" t="str">
+        <x:v>4月8日</x:v>
+      </x:c>
+      <x:c r="D80" s="23" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="E80" s="23" t="n">
+        <x:v>164700</x:v>
+      </x:c>
+      <x:c r="F80" s="23" t="n">
+        <x:v>157000</x:v>
+      </x:c>
+      <x:c r="G80" s="23" t="n">
+        <x:v>159620</x:v>
+      </x:c>
+      <x:c r="H80" s="28" t="n">
+        <x:v>-1240</x:v>
+      </x:c>
+      <x:c r="I80" s="24" t="n">
+        <x:v>-0.007708566455302712</x:v>
+      </x:c>
+      <x:c r="J80" s="26" t="n">
+        <x:f>ROUND(E80-F80,1)</x:f>
+        <x:v>7700</x:v>
+      </x:c>
+      <x:c r="K80" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B81" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C81" s="22" t="str">
+        <x:v>4月9日</x:v>
+      </x:c>
+      <x:c r="D81" s="23" t="n">
+        <x:v>159000</x:v>
+      </x:c>
+      <x:c r="E81" s="23" t="n">
+        <x:v>159740</x:v>
+      </x:c>
+      <x:c r="F81" s="23" t="n">
+        <x:v>152500</x:v>
+      </x:c>
+      <x:c r="G81" s="23" t="n">
+        <x:v>153560</x:v>
+      </x:c>
+      <x:c r="H81" s="28" t="n">
+        <x:v>-6060</x:v>
+      </x:c>
+      <x:c r="I81" s="24" t="n">
+        <x:v>-0.037965167272271616</x:v>
+      </x:c>
+      <x:c r="J81" s="26" t="n">
+        <x:f>ROUND(E81-F81,1)</x:f>
+        <x:v>7240</x:v>
+      </x:c>
+      <x:c r="K81" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B82" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C82" s="22" t="str">
+        <x:v>4月10日</x:v>
+      </x:c>
+      <x:c r="D82" s="23" t="n">
+        <x:v>156300</x:v>
+      </x:c>
+      <x:c r="E82" s="23" t="n">
+        <x:v>158900</x:v>
+      </x:c>
+      <x:c r="F82" s="23" t="n">
+        <x:v>153800</x:v>
+      </x:c>
+      <x:c r="G82" s="23" t="n">
+        <x:v>157600</x:v>
+      </x:c>
+      <x:c r="H82" s="28" t="n">
+        <x:v>4040</x:v>
+      </x:c>
+      <x:c r="I82" s="24" t="n">
+        <x:v>0.026308934618390234</x:v>
+      </x:c>
+      <x:c r="J82" s="23" t="n">
+        <x:f>ROUND(E82-F82,1)</x:f>
+        <x:v>5100</x:v>
+      </x:c>
+      <x:c r="K82" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B83" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C83" s="22" t="str">
+        <x:v>4月13日</x:v>
+      </x:c>
+      <x:c r="D83" s="23" t="n">
+        <x:v>155020</x:v>
+      </x:c>
+      <x:c r="E83" s="23" t="n">
+        <x:v>166600</x:v>
+      </x:c>
+      <x:c r="F83" s="23" t="n">
+        <x:v>154780</x:v>
+      </x:c>
+      <x:c r="G83" s="23" t="n">
+        <x:v>166500</x:v>
+      </x:c>
+      <x:c r="H83" s="28" t="n">
+        <x:v>8900</x:v>
+      </x:c>
+      <x:c r="I83" s="24" t="n">
+        <x:v>0.056472081218274184</x:v>
+      </x:c>
+      <x:c r="J83" s="26" t="n">
+        <x:f>ROUND(E83-F83,1)</x:f>
+        <x:v>11820</x:v>
+      </x:c>
+      <x:c r="K83" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B84" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C84" s="22" t="str">
+        <x:v>4月14日</x:v>
+      </x:c>
+      <x:c r="D84" s="23" t="n">
+        <x:v>167000</x:v>
+      </x:c>
+      <x:c r="E84" s="23" t="n">
+        <x:v>168400</x:v>
+      </x:c>
+      <x:c r="F84" s="23" t="n">
+        <x:v>164100</x:v>
+      </x:c>
+      <x:c r="G84" s="23" t="n">
+        <x:v>166840</x:v>
+      </x:c>
+      <x:c r="H84" s="28" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="I84" s="24" t="n">
+        <x:v>0.002042042042041947</x:v>
+      </x:c>
+      <x:c r="J84" s="23" t="n">
+        <x:f>ROUND(E84-F84,1)</x:f>
+        <x:v>4300</x:v>
+      </x:c>
+      <x:c r="K84" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B85" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C85" s="22" t="str">
+        <x:v>4月15日</x:v>
+      </x:c>
+      <x:c r="D85" s="23" t="n">
+        <x:v>168400</x:v>
+      </x:c>
+      <x:c r="E85" s="23" t="n">
+        <x:v>171980</x:v>
+      </x:c>
+      <x:c r="F85" s="23" t="n">
+        <x:v>165020</x:v>
+      </x:c>
+      <x:c r="G85" s="23" t="n">
+        <x:v>168660</x:v>
+      </x:c>
+      <x:c r="H85" s="28" t="n">
+        <x:v>1820</x:v>
+      </x:c>
+      <x:c r="I85" s="24" t="n">
+        <x:v>0.010908654998801337</x:v>
+      </x:c>
+      <x:c r="J85" s="26" t="n">
+        <x:f>ROUND(E85-F85,1)</x:f>
+        <x:v>6960</x:v>
+      </x:c>
+      <x:c r="K85" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B86" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C86" s="22" t="str">
+        <x:v>4月16日</x:v>
+      </x:c>
+      <x:c r="D86" s="23" t="n">
+        <x:v>170500</x:v>
+      </x:c>
+      <x:c r="E86" s="23" t="n">
+        <x:v>176200</x:v>
+      </x:c>
+      <x:c r="F86" s="23" t="n">
+        <x:v>169200</x:v>
+      </x:c>
+      <x:c r="G86" s="23" t="n">
+        <x:v>176000</x:v>
+      </x:c>
+      <x:c r="H86" s="28" t="n">
+        <x:v>7340</x:v>
+      </x:c>
+      <x:c r="I86" s="24" t="n">
+        <x:v>0.04351950669986948</x:v>
+      </x:c>
+      <x:c r="J86" s="26" t="n">
+        <x:f>ROUND(E86-F86,1)</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="K86" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="41" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B87" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C87" s="41" t="str">
+        <x:v>4月17日</x:v>
+      </x:c>
+      <x:c r="D87" s="42" t="n">
+        <x:v>177460</x:v>
+      </x:c>
+      <x:c r="E87" s="42" t="n">
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="F87" s="42" t="n">
+        <x:v>173680</x:v>
+      </x:c>
+      <x:c r="G87" s="42" t="n">
+        <x:v>177560</x:v>
+      </x:c>
+      <x:c r="H87" s="28" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="I87" s="43" t="n">
+        <x:v>0.008863636363636296</x:v>
+      </x:c>
+      <x:c r="J87" s="42" t="n">
+        <x:f>ROUND(E87-F87,1)</x:f>
+        <x:v>4320</x:v>
+      </x:c>
+      <x:c r="K87" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B88" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C88" s="22" t="str">
+        <x:v>4月20日</x:v>
+      </x:c>
+      <x:c r="D88" s="23" t="n">
+        <x:v>177000</x:v>
+      </x:c>
+      <x:c r="E88" s="23" t="n">
+        <x:v>181440</x:v>
+      </x:c>
+      <x:c r="F88" s="23" t="n">
+        <x:v>174800</x:v>
+      </x:c>
+      <x:c r="G88" s="23" t="n">
+        <x:v>180200</x:v>
+      </x:c>
+      <x:c r="H88" s="28" t="n">
+        <x:v>2640</x:v>
+      </x:c>
+      <x:c r="I88" s="24" t="n">
+        <x:v>0.014868213561612942</x:v>
+      </x:c>
+      <x:c r="J88" s="26" t="n">
+        <x:f>ROUND(E88-F88,1)</x:f>
+        <x:v>6640</x:v>
+      </x:c>
+      <x:c r="K88" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B89" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C89" s="22" t="str">
+        <x:v>4月21日</x:v>
+      </x:c>
+      <x:c r="D89" s="23" t="n">
+        <x:v>180900</x:v>
+      </x:c>
+      <x:c r="E89" s="23" t="n">
+        <x:v>180900</x:v>
+      </x:c>
+      <x:c r="F89" s="23" t="n">
+        <x:v>169500</x:v>
+      </x:c>
+      <x:c r="G89" s="23" t="n">
+        <x:v>174260</x:v>
+      </x:c>
+      <x:c r="H89" s="28" t="n">
+        <x:v>-5940</x:v>
+      </x:c>
+      <x:c r="I89" s="24" t="n">
+        <x:v>-0.03296337402885685</x:v>
+      </x:c>
+      <x:c r="J89" s="26" t="n">
+        <x:f>ROUND(E89-F89,1)</x:f>
+        <x:v>11400</x:v>
+      </x:c>
+      <x:c r="K89" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B90" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C90" s="22" t="str">
+        <x:v>4月22日</x:v>
+      </x:c>
+      <x:c r="D90" s="23" t="n">
+        <x:v>173660</x:v>
+      </x:c>
+      <x:c r="E90" s="23" t="n">
+        <x:v>176500</x:v>
+      </x:c>
+      <x:c r="F90" s="23" t="n">
+        <x:v>172020</x:v>
+      </x:c>
+      <x:c r="G90" s="23" t="n">
+        <x:v>175240</x:v>
+      </x:c>
+      <x:c r="H90" s="28" t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="I90" s="24" t="n">
+        <x:v>0.005623780557787228</x:v>
+      </x:c>
+      <x:c r="J90" s="23" t="n">
+        <x:f>ROUND(E90-F90,1)</x:f>
+        <x:v>4480</x:v>
+      </x:c>
+      <x:c r="K90" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B91" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C91" s="22" t="str">
+        <x:v>4月23日</x:v>
+      </x:c>
+      <x:c r="D91" s="23" t="n">
+        <x:v>175740</x:v>
+      </x:c>
+      <x:c r="E91" s="23" t="n">
+        <x:v>178900</x:v>
+      </x:c>
+      <x:c r="F91" s="23" t="n">
+        <x:v>172140</x:v>
+      </x:c>
+      <x:c r="G91" s="23" t="n">
+        <x:v>177960</x:v>
+      </x:c>
+      <x:c r="H91" s="28" t="n">
+        <x:v>2720</x:v>
+      </x:c>
+      <x:c r="I91" s="24" t="n">
+        <x:v>0.01552157041771296</x:v>
+      </x:c>
+      <x:c r="J91" s="26" t="n">
+        <x:f>ROUND(E91-F91,1)</x:f>
+        <x:v>6760</x:v>
+      </x:c>
+      <x:c r="K91" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B92" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C92" s="22" t="str">
+        <x:v>4月24日</x:v>
+      </x:c>
+      <x:c r="D92" s="23" t="n">
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="E92" s="23" t="n">
+        <x:v>179980</x:v>
+      </x:c>
+      <x:c r="F92" s="23" t="n">
+        <x:v>174500</x:v>
+      </x:c>
+      <x:c r="G92" s="23" t="n">
+        <x:v>177900</x:v>
+      </x:c>
+      <x:c r="H92" s="23" t="n">
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="I92" s="24" t="n">
+        <x:v>-0.0003371544167228846</x:v>
+      </x:c>
+      <x:c r="J92" s="23" t="n">
+        <x:f>ROUND(E92-F92,1)</x:f>
+        <x:v>5480</x:v>
+      </x:c>
+      <x:c r="K92" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B93" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C93" s="22" t="str">
+        <x:v>4月27日</x:v>
+      </x:c>
+      <x:c r="D93" s="23" t="n">
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="E93" s="23" t="n">
+        <x:v>184800</x:v>
+      </x:c>
+      <x:c r="F93" s="23" t="n">
+        <x:v>178500</x:v>
+      </x:c>
+      <x:c r="G93" s="23" t="n">
+        <x:v>180560</x:v>
+      </x:c>
+      <x:c r="H93" s="28" t="n">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="I93" s="24" t="n">
+        <x:v>0.014952220348510403</x:v>
+      </x:c>
+      <x:c r="J93" s="26" t="n">
+        <x:f>ROUND(E93-F93,1)</x:f>
+        <x:v>6300</x:v>
+      </x:c>
+      <x:c r="K93" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B94" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C94" s="22" t="str">
+        <x:v>4月28日</x:v>
+      </x:c>
+      <x:c r="D94" s="23" t="n">
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="E94" s="23" t="n">
+        <x:v>180500</x:v>
+      </x:c>
+      <x:c r="F94" s="23" t="n">
+        <x:v>173400</x:v>
+      </x:c>
+      <x:c r="G94" s="23" t="n">
+        <x:v>178620</x:v>
+      </x:c>
+      <x:c r="H94" s="28" t="n">
+        <x:v>-1940</x:v>
+      </x:c>
+      <x:c r="I94" s="24" t="n">
+        <x:v>-0.010744350908285294</x:v>
+      </x:c>
+      <x:c r="J94" s="26" t="n">
+        <x:f>ROUND(E94-F94,1)</x:f>
+        <x:v>7100</x:v>
+      </x:c>
+      <x:c r="K94" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B95" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C95" s="22" t="str">
+        <x:v>4月29日</x:v>
+      </x:c>
+      <x:c r="D95" s="23" t="n">
+        <x:v>178700</x:v>
+      </x:c>
+      <x:c r="E95" s="23" t="n">
+        <x:v>184440</x:v>
+      </x:c>
+      <x:c r="F95" s="23" t="n">
+        <x:v>175260</x:v>
+      </x:c>
+      <x:c r="G95" s="23" t="n">
+        <x:v>183880</x:v>
+      </x:c>
+      <x:c r="H95" s="28" t="n">
+        <x:v>5260</x:v>
+      </x:c>
+      <x:c r="I95" s="24" t="n">
+        <x:v>0.029447990146680203</x:v>
+      </x:c>
+      <x:c r="J95" s="26" t="n">
+        <x:f>ROUND(E95-F95,1)</x:f>
+        <x:v>9180</x:v>
+      </x:c>
+      <x:c r="K95" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B96" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C96" s="22" t="str">
+        <x:v>4月30日</x:v>
+      </x:c>
+      <x:c r="D96" s="23" t="n">
+        <x:v>184000</x:v>
+      </x:c>
+      <x:c r="E96" s="23" t="n">
+        <x:v>189500</x:v>
+      </x:c>
+      <x:c r="F96" s="23" t="n">
+        <x:v>182460</x:v>
+      </x:c>
+      <x:c r="G96" s="23" t="n">
+        <x:v>189080</x:v>
+      </x:c>
+      <x:c r="H96" s="28" t="n">
+        <x:v>5200</x:v>
+      </x:c>
+      <x:c r="I96" s="24" t="n">
+        <x:v>0.028279312595170802</x:v>
+      </x:c>
+      <x:c r="J96" s="26" t="n">
+        <x:f>ROUND(E96-F96,1)</x:f>
+        <x:v>7040</x:v>
+      </x:c>
+      <x:c r="K96" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B97" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C97" s="30"/>
+      <x:c r="D97" s="30"/>
+      <x:c r="E97" s="30"/>
+      <x:c r="F97" s="30"/>
+      <x:c r="G97" s="30"/>
+      <x:c r="H97" s="30"/>
+      <x:c r="I97" s="30"/>
+      <x:c r="J97" s="32" t="n">
+        <x:f>ROUND(SUM(J76:J96),1)</x:f>
+        <x:v>151460</x:v>
+      </x:c>
+      <x:c r="K97" s="30"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B98" s="30"/>
+      <x:c r="C98" s="30"/>
+      <x:c r="D98" s="30"/>
+      <x:c r="E98" s="30"/>
+      <x:c r="F98" s="30"/>
+      <x:c r="G98" s="30"/>
+      <x:c r="H98" s="30"/>
+      <x:c r="I98" s="30"/>
+      <x:c r="J98" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J76:J96),0),1)</x:f>
+        <x:v>7212.4</x:v>
+      </x:c>
+      <x:c r="K98" s="30"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="17" t="str">
+        <x:v>5月</x:v>
+      </x:c>
+      <x:c r="B100" s="17"/>
+      <x:c r="C100" s="17"/>
+      <x:c r="D100" s="17"/>
+      <x:c r="E100" s="17"/>
+      <x:c r="F100" s="17"/>
+      <x:c r="G100" s="17"/>
+      <x:c r="H100" s="17"/>
+      <x:c r="I100" s="17"/>
+      <x:c r="J100" s="17"/>
+      <x:c r="K100" s="17"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B101" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C101" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D101" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E101" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F101" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G101" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H101" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I101" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J101" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K101" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B102" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C102" s="22" t="str">
+        <x:v>5月6日</x:v>
+      </x:c>
+      <x:c r="D102" s="23" t="n">
+        <x:v>191500</x:v>
+      </x:c>
+      <x:c r="E102" s="23" t="n">
+        <x:v>199560</x:v>
+      </x:c>
+      <x:c r="F102" s="23" t="n">
+        <x:v>191040</x:v>
+      </x:c>
+      <x:c r="G102" s="23" t="n">
+        <x:v>199400</x:v>
+      </x:c>
+      <x:c r="H102" s="28" t="n">
+        <x:v>10320</x:v>
+      </x:c>
+      <x:c r="I102" s="24" t="n">
+        <x:v>0.05458007192722647</x:v>
+      </x:c>
+      <x:c r="J102" s="26" t="n">
+        <x:f>ROUND(E102-F102,1)</x:f>
+        <x:v>8520</x:v>
+      </x:c>
+      <x:c r="K102" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B103" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C103" s="22" t="str">
+        <x:v>5月7日</x:v>
+      </x:c>
+      <x:c r="D103" s="23" t="n">
+        <x:v>199000</x:v>
+      </x:c>
+      <x:c r="E103" s="23" t="n">
+        <x:v>200440</x:v>
+      </x:c>
+      <x:c r="F103" s="23" t="n">
+        <x:v>193400</x:v>
+      </x:c>
+      <x:c r="G103" s="23" t="n">
+        <x:v>199060</x:v>
+      </x:c>
+      <x:c r="H103" s="28" t="n">
+        <x:v>-340</x:v>
+      </x:c>
+      <x:c r="I103" s="24" t="n">
+        <x:v>-0.0017051153460381219</x:v>
+      </x:c>
+      <x:c r="J103" s="26" t="n">
+        <x:f>ROUND(E103-F103,1)</x:f>
+        <x:v>7040</x:v>
+      </x:c>
+      <x:c r="K103" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B104" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C104" s="22" t="str">
+        <x:v>5月8日</x:v>
+      </x:c>
+      <x:c r="D104" s="23" t="n">
+        <x:v>197120</x:v>
+      </x:c>
+      <x:c r="E104" s="23" t="n">
+        <x:v>201480</x:v>
+      </x:c>
+      <x:c r="F104" s="23" t="n">
+        <x:v>195100</x:v>
+      </x:c>
+      <x:c r="G104" s="23" t="n">
+        <x:v>196560</x:v>
+      </x:c>
+      <x:c r="H104" s="28" t="n">
+        <x:v>-2500</x:v>
+      </x:c>
+      <x:c r="I104" s="24" t="n">
+        <x:v>-0.012559027428915903</x:v>
+      </x:c>
+      <x:c r="J104" s="26" t="n">
+        <x:f>ROUND(E104-F104,1)</x:f>
+        <x:v>6380</x:v>
+      </x:c>
+      <x:c r="K104" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B105" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C105" s="22" t="str">
+        <x:v>5月11日</x:v>
+      </x:c>
+      <x:c r="D105" s="23" t="n">
+        <x:v>196560</x:v>
+      </x:c>
+      <x:c r="E105" s="23" t="n">
+        <x:v>205600</x:v>
+      </x:c>
+      <x:c r="F105" s="23" t="n">
+        <x:v>195200</x:v>
+      </x:c>
+      <x:c r="G105" s="23" t="n">
+        <x:v>205020</x:v>
+      </x:c>
+      <x:c r="H105" s="28" t="n">
+        <x:v>8460</x:v>
+      </x:c>
+      <x:c r="I105" s="24" t="n">
+        <x:v>0.04304029304029311</x:v>
+      </x:c>
+      <x:c r="J105" s="26" t="n">
+        <x:f>ROUND(E105-F105,1)</x:f>
+        <x:v>10400</x:v>
+      </x:c>
+      <x:c r="K105" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B106" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C106" s="22" t="str">
+        <x:v>5月12日</x:v>
+      </x:c>
+      <x:c r="D106" s="23" t="n">
+        <x:v>208000</x:v>
+      </x:c>
+      <x:c r="E106" s="23" t="n">
+        <x:v>208800</x:v>
+      </x:c>
+      <x:c r="F106" s="23" t="n">
+        <x:v>203300</x:v>
+      </x:c>
+      <x:c r="G106" s="23" t="n">
+        <x:v>205260</x:v>
+      </x:c>
+      <x:c r="H106" s="28" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="I106" s="24" t="n">
+        <x:v>0.0011706175007315522</x:v>
+      </x:c>
+      <x:c r="J106" s="23" t="n">
+        <x:f>ROUND(E106-F106,1)</x:f>
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="K106" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B107" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C107" s="22" t="str">
+        <x:v>5月13日</x:v>
+      </x:c>
+      <x:c r="D107" s="23" t="n">
+        <x:v>206520</x:v>
+      </x:c>
+      <x:c r="E107" s="23" t="n">
+        <x:v>209880</x:v>
+      </x:c>
+      <x:c r="F107" s="23" t="n">
+        <x:v>195000</x:v>
+      </x:c>
+      <x:c r="G107" s="23" t="n">
+        <x:v>201960</x:v>
+      </x:c>
+      <x:c r="H107" s="28" t="n">
+        <x:v>-3300</x:v>
+      </x:c>
+      <x:c r="I107" s="24" t="n">
+        <x:v>-0.01607717041800638</x:v>
+      </x:c>
+      <x:c r="J107" s="26" t="n">
+        <x:f>ROUND(E107-F107,1)</x:f>
+        <x:v>14880</x:v>
+      </x:c>
+      <x:c r="K107" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B108" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C108" s="22" t="str">
+        <x:v>5月14日</x:v>
+      </x:c>
+      <x:c r="D108" s="23" t="n">
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="E108" s="23" t="n">
+        <x:v>204400</x:v>
+      </x:c>
+      <x:c r="F108" s="23" t="n">
+        <x:v>190080</x:v>
+      </x:c>
+      <x:c r="G108" s="23" t="n">
+        <x:v>191760</x:v>
+      </x:c>
+      <x:c r="H108" s="28" t="n">
+        <x:v>-10200</x:v>
+      </x:c>
+      <x:c r="I108" s="24" t="n">
+        <x:v>-0.0505050505050505</x:v>
+      </x:c>
+      <x:c r="J108" s="26" t="n">
+        <x:f>ROUND(E108-F108,1)</x:f>
+        <x:v>14320</x:v>
+      </x:c>
+      <x:c r="K108" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="41" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B109" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C109" s="41" t="str">
+        <x:v>5月15日</x:v>
+      </x:c>
+      <x:c r="D109" s="42" t="n">
+        <x:v>190000</x:v>
+      </x:c>
+      <x:c r="E109" s="42" t="n">
+        <x:v>194900</x:v>
+      </x:c>
+      <x:c r="F109" s="42" t="n">
+        <x:v>186800</x:v>
+      </x:c>
+      <x:c r="G109" s="42" t="n">
+        <x:v>188800</x:v>
+      </x:c>
+      <x:c r="H109" s="28" t="n">
+        <x:v>-2960</x:v>
+      </x:c>
+      <x:c r="I109" s="43" t="n">
+        <x:v>-0.015435961618689986</x:v>
+      </x:c>
+      <x:c r="J109" s="26" t="n">
+        <x:f>ROUND(E109-F109,1)</x:f>
+        <x:v>8100</x:v>
+      </x:c>
+      <x:c r="K109" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B110" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C110" s="22" t="str">
+        <x:v>5月18日</x:v>
+      </x:c>
+      <x:c r="D110" s="23" t="n">
+        <x:v>189000</x:v>
+      </x:c>
+      <x:c r="E110" s="23" t="n">
+        <x:v>193900</x:v>
+      </x:c>
+      <x:c r="F110" s="23" t="n">
+        <x:v>187600</x:v>
+      </x:c>
+      <x:c r="G110" s="23" t="n">
+        <x:v>192180</x:v>
+      </x:c>
+      <x:c r="H110" s="28" t="n">
+        <x:v>3380</x:v>
+      </x:c>
+      <x:c r="I110" s="24" t="n">
+        <x:v>0.017902542372881358</x:v>
+      </x:c>
+      <x:c r="J110" s="26" t="n">
+        <x:f>ROUND(E110-F110,1)</x:f>
+        <x:v>6300</x:v>
+      </x:c>
+      <x:c r="K110" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B111" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C111" s="22" t="str">
+        <x:v>5月19日</x:v>
+      </x:c>
+      <x:c r="D111" s="23" t="n">
+        <x:v>190980</x:v>
+      </x:c>
+      <x:c r="E111" s="23" t="n">
+        <x:v>192120</x:v>
+      </x:c>
+      <x:c r="F111" s="23" t="n">
+        <x:v>182060</x:v>
+      </x:c>
+      <x:c r="G111" s="23" t="n">
+        <x:v>184400</x:v>
+      </x:c>
+      <x:c r="H111" s="28" t="n">
+        <x:v>-7780</x:v>
+      </x:c>
+      <x:c r="I111" s="24" t="n">
+        <x:v>-0.04048288063274019</x:v>
+      </x:c>
+      <x:c r="J111" s="26" t="n">
+        <x:f>ROUND(E111-F111,1)</x:f>
+        <x:v>10060</x:v>
+      </x:c>
+      <x:c r="K111" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B112" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C112" s="22" t="str">
+        <x:v>5月20日</x:v>
+      </x:c>
+      <x:c r="D112" s="23" t="n">
+        <x:v>182120</x:v>
+      </x:c>
+      <x:c r="E112" s="23" t="n">
+        <x:v>184800</x:v>
+      </x:c>
+      <x:c r="F112" s="23" t="n">
+        <x:v>175200</x:v>
+      </x:c>
+      <x:c r="G112" s="23" t="n">
+        <x:v>183100</x:v>
+      </x:c>
+      <x:c r="H112" s="28" t="n">
+        <x:v>-1300</x:v>
+      </x:c>
+      <x:c r="I112" s="24" t="n">
+        <x:v>-0.007049891540130138</x:v>
+      </x:c>
+      <x:c r="J112" s="26" t="n">
+        <x:f>ROUND(E112-F112,1)</x:f>
+        <x:v>9600</x:v>
+      </x:c>
+      <x:c r="K112" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B113" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C113" s="22" t="str">
+        <x:v>5月21日</x:v>
+      </x:c>
+      <x:c r="D113" s="23" t="n">
+        <x:v>184100</x:v>
+      </x:c>
+      <x:c r="E113" s="23" t="n">
+        <x:v>186200</x:v>
+      </x:c>
+      <x:c r="F113" s="23" t="n">
+        <x:v>177160</x:v>
+      </x:c>
+      <x:c r="G113" s="23" t="n">
+        <x:v>177600</x:v>
+      </x:c>
+      <x:c r="H113" s="28" t="n">
+        <x:v>-5500</x:v>
+      </x:c>
+      <x:c r="I113" s="24" t="n">
+        <x:v>-0.030038230475150196</x:v>
+      </x:c>
+      <x:c r="J113" s="26" t="n">
+        <x:f>ROUND(E113-F113,1)</x:f>
+        <x:v>9040</x:v>
+      </x:c>
+      <x:c r="K113" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B114" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C114" s="22" t="str">
+        <x:v>5月22日</x:v>
+      </x:c>
+      <x:c r="D114" s="23" t="n">
+        <x:v>178720</x:v>
+      </x:c>
+      <x:c r="E114" s="23" t="n">
+        <x:v>185300</x:v>
+      </x:c>
+      <x:c r="F114" s="23" t="n">
+        <x:v>176500</x:v>
+      </x:c>
+      <x:c r="G114" s="23" t="n">
+        <x:v>184460</x:v>
+      </x:c>
+      <x:c r="H114" s="28" t="n">
+        <x:v>6860</x:v>
+      </x:c>
+      <x:c r="I114" s="24" t="n">
+        <x:v>0.03862612612612604</x:v>
+      </x:c>
+      <x:c r="J114" s="26" t="n">
+        <x:f>ROUND(E114-F114,1)</x:f>
+        <x:v>8800</x:v>
+      </x:c>
+      <x:c r="K114" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B115" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C115" s="22" t="str">
+        <x:v>5月25日</x:v>
+      </x:c>
+      <x:c r="D115" s="23" t="n">
+        <x:v>185500</x:v>
+      </x:c>
+      <x:c r="E115" s="23" t="n">
+        <x:v>187900</x:v>
+      </x:c>
+      <x:c r="F115" s="23" t="n">
+        <x:v>179300</x:v>
+      </x:c>
+      <x:c r="G115" s="23" t="n">
+        <x:v>181200</x:v>
+      </x:c>
+      <x:c r="H115" s="28" t="n">
+        <x:v>-3260</x:v>
+      </x:c>
+      <x:c r="I115" s="24" t="n">
+        <x:v>-0.01767320828363872</x:v>
+      </x:c>
+      <x:c r="J115" s="26" t="n">
+        <x:f>ROUND(E115-F115,1)</x:f>
+        <x:v>8600</x:v>
+      </x:c>
+      <x:c r="K115" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B116" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C116" s="22" t="str">
+        <x:v>5月26日</x:v>
+      </x:c>
+      <x:c r="D116" s="23" t="n">
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="E116" s="23" t="n">
+        <x:v>182720</x:v>
+      </x:c>
+      <x:c r="F116" s="23" t="n">
+        <x:v>175260</x:v>
+      </x:c>
+      <x:c r="G116" s="23" t="n">
+        <x:v>175960</x:v>
+      </x:c>
+      <x:c r="H116" s="28" t="n">
+        <x:v>-5240</x:v>
+      </x:c>
+      <x:c r="I116" s="24" t="n">
+        <x:v>-0.02891832229580571</x:v>
+      </x:c>
+      <x:c r="J116" s="26" t="n">
+        <x:f>ROUND(E116-F116,1)</x:f>
+        <x:v>7460</x:v>
+      </x:c>
+      <x:c r="K116" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B117" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C117" s="22" t="str">
+        <x:v>5月27日</x:v>
+      </x:c>
+      <x:c r="D117" s="23" t="n">
+        <x:v>175000</x:v>
+      </x:c>
+      <x:c r="E117" s="23" t="n">
+        <x:v>178920</x:v>
+      </x:c>
+      <x:c r="F117" s="23" t="n">
+        <x:v>172080</x:v>
+      </x:c>
+      <x:c r="G117" s="23" t="n">
+        <x:v>173000</x:v>
+      </x:c>
+      <x:c r="H117" s="28" t="n">
+        <x:v>-2960</x:v>
+      </x:c>
+      <x:c r="I117" s="24" t="n">
+        <x:v>-0.01682200500113662</x:v>
+      </x:c>
+      <x:c r="J117" s="26" t="n">
+        <x:f>ROUND(E117-F117,1)</x:f>
+        <x:v>6840</x:v>
+      </x:c>
+      <x:c r="K117" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B118" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C118" s="22" t="str">
+        <x:v>5月28日</x:v>
+      </x:c>
+      <x:c r="D118" s="23" t="n">
+        <x:v>175000</x:v>
+      </x:c>
+      <x:c r="E118" s="23" t="n">
+        <x:v>180880</x:v>
+      </x:c>
+      <x:c r="F118" s="23" t="n">
+        <x:v>174000</x:v>
+      </x:c>
+      <x:c r="G118" s="23" t="n">
+        <x:v>178860</x:v>
+      </x:c>
+      <x:c r="H118" s="28" t="n">
+        <x:v>5860</x:v>
+      </x:c>
+      <x:c r="I118" s="24" t="n">
+        <x:v>0.03387283236994221</x:v>
+      </x:c>
+      <x:c r="J118" s="26" t="n">
+        <x:f>ROUND(E118-F118,1)</x:f>
+        <x:v>6880</x:v>
+      </x:c>
+      <x:c r="K118" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B119" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C119" s="22" t="str">
+        <x:v>5月29日</x:v>
+      </x:c>
+      <x:c r="D119" s="23" t="n">
+        <x:v>180000</x:v>
+      </x:c>
+      <x:c r="E119" s="23" t="n">
+        <x:v>182500</x:v>
+      </x:c>
+      <x:c r="F119" s="23" t="n">
+        <x:v>177760</x:v>
+      </x:c>
+      <x:c r="G119" s="23" t="n">
+        <x:v>179740</x:v>
+      </x:c>
+      <x:c r="H119" s="28" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="I119" s="24" t="n">
+        <x:v>0.004920049200491938</x:v>
+      </x:c>
+      <x:c r="J119" s="23" t="n">
+        <x:f>ROUND(E119-F119,1)</x:f>
+        <x:v>4740</x:v>
+      </x:c>
+      <x:c r="K119" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B120" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C120" s="30"/>
+      <x:c r="D120" s="30"/>
+      <x:c r="E120" s="30"/>
+      <x:c r="F120" s="30"/>
+      <x:c r="G120" s="30"/>
+      <x:c r="H120" s="30"/>
+      <x:c r="I120" s="30"/>
+      <x:c r="J120" s="32" t="n">
+        <x:f>ROUND(SUM(J102:J119),1)</x:f>
+        <x:v>153460</x:v>
+      </x:c>
+      <x:c r="K120" s="30"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B121" s="30"/>
+      <x:c r="C121" s="30"/>
+      <x:c r="D121" s="30"/>
+      <x:c r="E121" s="30"/>
+      <x:c r="F121" s="30"/>
+      <x:c r="G121" s="30"/>
+      <x:c r="H121" s="30"/>
+      <x:c r="I121" s="30"/>
+      <x:c r="J121" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J102:J119),0),1)</x:f>
+        <x:v>8525.6</x:v>
+      </x:c>
+      <x:c r="K121" s="30"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="17" t="str">
+        <x:v>6月</x:v>
+      </x:c>
+      <x:c r="B123" s="17"/>
+      <x:c r="C123" s="17"/>
+      <x:c r="D123" s="17"/>
+      <x:c r="E123" s="17"/>
+      <x:c r="F123" s="17"/>
+      <x:c r="G123" s="17"/>
+      <x:c r="H123" s="17"/>
+      <x:c r="I123" s="17"/>
+      <x:c r="J123" s="17"/>
+      <x:c r="K123" s="17"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B124" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C124" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D124" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E124" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F124" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G124" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H124" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I124" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J124" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K124" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B125" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C125" s="22" t="str">
+        <x:v>6月1日</x:v>
+      </x:c>
+      <x:c r="D125" s="23" t="n">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="E125" s="23" t="n">
+        <x:v>182100</x:v>
+      </x:c>
+      <x:c r="F125" s="23" t="n">
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="G125" s="23" t="n">
+        <x:v>178900</x:v>
+      </x:c>
+      <x:c r="H125" s="28" t="n">
+        <x:v>-840</x:v>
+      </x:c>
+      <x:c r="I125" s="24" t="n">
+        <x:v>-0.00467341715811731</x:v>
+      </x:c>
+      <x:c r="J125" s="23" t="n">
+        <x:f>ROUND(E125-F125,1)</x:f>
+        <x:v>4100</x:v>
+      </x:c>
+      <x:c r="K125" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B126" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C126" s="22" t="str">
+        <x:v>6月2日</x:v>
+      </x:c>
+      <x:c r="D126" s="23" t="n">
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="E126" s="23" t="n">
+        <x:v>179220</x:v>
+      </x:c>
+      <x:c r="F126" s="23" t="n">
+        <x:v>171100</x:v>
+      </x:c>
+      <x:c r="G126" s="23" t="n">
+        <x:v>172980</x:v>
+      </x:c>
+      <x:c r="H126" s="28" t="n">
+        <x:v>-5920</x:v>
+      </x:c>
+      <x:c r="I126" s="24" t="n">
+        <x:v>-0.03309111235327</x:v>
+      </x:c>
+      <x:c r="J126" s="26" t="n">
+        <x:f>ROUND(E126-F126,1)</x:f>
+        <x:v>8120</x:v>
+      </x:c>
+      <x:c r="K126" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B127" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C127" s="22" t="str">
+        <x:v>6月3日</x:v>
+      </x:c>
+      <x:c r="D127" s="23" t="n">
+        <x:v>173100</x:v>
+      </x:c>
+      <x:c r="E127" s="23" t="n">
+        <x:v>173100</x:v>
+      </x:c>
+      <x:c r="F127" s="23" t="n">
+        <x:v>166100</x:v>
+      </x:c>
+      <x:c r="G127" s="23" t="n">
+        <x:v>166760</x:v>
+      </x:c>
+      <x:c r="H127" s="28" t="n">
+        <x:v>-6220</x:v>
+      </x:c>
+      <x:c r="I127" s="24" t="n">
+        <x:v>-0.035957914209735264</x:v>
+      </x:c>
+      <x:c r="J127" s="26" t="n">
+        <x:f>ROUND(E127-F127,1)</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="K127" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B128" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C128" s="22" t="str">
+        <x:v>6月4日</x:v>
+      </x:c>
+      <x:c r="D128" s="23" t="n">
+        <x:v>165660</x:v>
+      </x:c>
+      <x:c r="E128" s="23" t="n">
+        <x:v>167580</x:v>
+      </x:c>
+      <x:c r="F128" s="23" t="n">
+        <x:v>157560</x:v>
+      </x:c>
+      <x:c r="G128" s="23" t="n">
+        <x:v>160740</x:v>
+      </x:c>
+      <x:c r="H128" s="28" t="n">
+        <x:v>-6020</x:v>
+      </x:c>
+      <x:c r="I128" s="24" t="n">
+        <x:v>-0.03609978412089232</x:v>
+      </x:c>
+      <x:c r="J128" s="26" t="n">
+        <x:f>ROUND(E128-F128,1)</x:f>
+        <x:v>10020</x:v>
+      </x:c>
+      <x:c r="K128" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B129" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C129" s="22" t="str">
+        <x:v>6月5日</x:v>
+      </x:c>
+      <x:c r="D129" s="23" t="n">
+        <x:v>160040</x:v>
+      </x:c>
+      <x:c r="E129" s="23" t="n">
+        <x:v>165580</x:v>
+      </x:c>
+      <x:c r="F129" s="23" t="n">
+        <x:v>157180</x:v>
+      </x:c>
+      <x:c r="G129" s="23" t="n">
+        <x:v>164360</x:v>
+      </x:c>
+      <x:c r="H129" s="28" t="n">
+        <x:v>3620</x:v>
+      </x:c>
+      <x:c r="I129" s="24" t="n">
+        <x:v>0.022520841109866963</x:v>
+      </x:c>
+      <x:c r="J129" s="26" t="n">
+        <x:f>ROUND(E129-F129,1)</x:f>
+        <x:v>8400</x:v>
+      </x:c>
+      <x:c r="K129" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B130" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C130" s="22" t="str">
+        <x:v>6月8日</x:v>
+      </x:c>
+      <x:c r="D130" s="23" t="n">
+        <x:v>161500</x:v>
+      </x:c>
+      <x:c r="E130" s="23" t="n">
+        <x:v>165800</x:v>
+      </x:c>
+      <x:c r="F130" s="23" t="n">
+        <x:v>160260</x:v>
+      </x:c>
+      <x:c r="G130" s="23" t="n">
+        <x:v>163340</x:v>
+      </x:c>
+      <x:c r="H130" s="28" t="n">
+        <x:v>-1020</x:v>
+      </x:c>
+      <x:c r="I130" s="24" t="n">
+        <x:v>-0.006205889510829898</x:v>
+      </x:c>
+      <x:c r="J130" s="23" t="n">
+        <x:f>ROUND(E130-F130,1)</x:f>
+        <x:v>5540</x:v>
+      </x:c>
+      <x:c r="K130" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B131" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C131" s="22" t="str">
+        <x:v>6月9日</x:v>
+      </x:c>
+      <x:c r="D131" s="23" t="n">
+        <x:v>163600</x:v>
+      </x:c>
+      <x:c r="E131" s="23" t="n">
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="F131" s="23" t="n">
+        <x:v>161600</x:v>
+      </x:c>
+      <x:c r="G131" s="23" t="n">
+        <x:v>168460</x:v>
+      </x:c>
+      <x:c r="H131" s="28" t="n">
+        <x:v>5120</x:v>
+      </x:c>
+      <x:c r="I131" s="24" t="n">
+        <x:v>0.031345659360842326</x:v>
+      </x:c>
+      <x:c r="J131" s="26" t="n">
+        <x:f>ROUND(E131-F131,1)</x:f>
+        <x:v>7400</x:v>
+      </x:c>
+      <x:c r="K131" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B132" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C132" s="22" t="str">
+        <x:v>6月10日</x:v>
+      </x:c>
+      <x:c r="D132" s="23" t="n">
+        <x:v>167980</x:v>
+      </x:c>
+      <x:c r="E132" s="23" t="n">
+        <x:v>169300</x:v>
+      </x:c>
+      <x:c r="F132" s="23" t="n">
+        <x:v>164800</x:v>
+      </x:c>
+      <x:c r="G132" s="23" t="n">
+        <x:v>167400</x:v>
+      </x:c>
+      <x:c r="H132" s="28" t="n">
+        <x:v>-1060</x:v>
+      </x:c>
+      <x:c r="I132" s="24" t="n">
+        <x:v>-0.006292294906802831</x:v>
+      </x:c>
+      <x:c r="J132" s="23" t="n">
+        <x:f>ROUND(E132-F132,1)</x:f>
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="K132" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B133" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C133" s="22" t="str">
+        <x:v>6月11日</x:v>
+      </x:c>
+      <x:c r="D133" s="23" t="n">
+        <x:v>166780</x:v>
+      </x:c>
+      <x:c r="E133" s="23" t="n">
+        <x:v>174960</x:v>
+      </x:c>
+      <x:c r="F133" s="23" t="n">
+        <x:v>166500</x:v>
+      </x:c>
+      <x:c r="G133" s="23" t="n">
+        <x:v>174600</x:v>
+      </x:c>
+      <x:c r="H133" s="28" t="n">
+        <x:v>7200</x:v>
+      </x:c>
+      <x:c r="I133" s="24" t="n">
+        <x:v>0.043010752688172005</x:v>
+      </x:c>
+      <x:c r="J133" s="26" t="n">
+        <x:f>ROUND(E133-F133,1)</x:f>
+        <x:v>8460</x:v>
+      </x:c>
+      <x:c r="K133" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B134" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C134" s="22" t="str">
+        <x:v>6月12日</x:v>
+      </x:c>
+      <x:c r="D134" s="23" t="n">
+        <x:v>176000</x:v>
+      </x:c>
+      <x:c r="E134" s="23" t="n">
+        <x:v>178740</x:v>
+      </x:c>
+      <x:c r="F134" s="23" t="n">
+        <x:v>174600</x:v>
+      </x:c>
+      <x:c r="G134" s="23" t="n">
+        <x:v>175300</x:v>
+      </x:c>
+      <x:c r="H134" s="28" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="I134" s="24" t="n">
+        <x:v>0.004009163802978222</x:v>
+      </x:c>
+      <x:c r="J134" s="23" t="n">
+        <x:f>ROUND(E134-F134,1)</x:f>
+        <x:v>4140</x:v>
+      </x:c>
+      <x:c r="K134" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B135" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C135" s="22" t="str">
+        <x:v>6月15日</x:v>
+      </x:c>
+      <x:c r="D135" s="23" t="n">
+        <x:v>177600</x:v>
+      </x:c>
+      <x:c r="E135" s="23" t="n">
+        <x:v>177920</x:v>
+      </x:c>
+      <x:c r="F135" s="23" t="n">
+        <x:v>172320</x:v>
+      </x:c>
+      <x:c r="G135" s="23" t="n">
+        <x:v>174440</x:v>
+      </x:c>
+      <x:c r="H135" s="28" t="n">
+        <x:v>-860</x:v>
+      </x:c>
+      <x:c r="I135" s="24" t="n">
+        <x:v>-0.00490587564175704</x:v>
+      </x:c>
+      <x:c r="J135" s="23" t="n">
+        <x:f>ROUND(E135-F135,1)</x:f>
+        <x:v>5600</x:v>
+      </x:c>
+      <x:c r="K135" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B136" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C136" s="22" t="str">
+        <x:v>6月16日</x:v>
+      </x:c>
+      <x:c r="D136" s="23" t="n">
+        <x:v>173800</x:v>
+      </x:c>
+      <x:c r="E136" s="23" t="n">
+        <x:v>174200</x:v>
+      </x:c>
+      <x:c r="F136" s="23" t="n">
+        <x:v>168420</x:v>
+      </x:c>
+      <x:c r="G136" s="23" t="n">
+        <x:v>169980</x:v>
+      </x:c>
+      <x:c r="H136" s="28" t="n">
+        <x:v>-4460</x:v>
+      </x:c>
+      <x:c r="I136" s="24" t="n">
+        <x:v>-0.025567530382939685</x:v>
+      </x:c>
+      <x:c r="J136" s="23" t="n">
+        <x:f>ROUND(E136-F136,1)</x:f>
+        <x:v>5780</x:v>
+      </x:c>
+      <x:c r="K136" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B137" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C137" s="22" t="str">
+        <x:v>6月17日</x:v>
+      </x:c>
+      <x:c r="D137" s="23" t="n">
+        <x:v>170100</x:v>
+      </x:c>
+      <x:c r="E137" s="23" t="n">
+        <x:v>173600</x:v>
+      </x:c>
+      <x:c r="F137" s="23" t="n">
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="G137" s="23" t="n">
+        <x:v>171300</x:v>
+      </x:c>
+      <x:c r="H137" s="28" t="n">
+        <x:v>1320</x:v>
+      </x:c>
+      <x:c r="I137" s="24" t="n">
+        <x:v>0.007765619484645159</x:v>
+      </x:c>
+      <x:c r="J137" s="23" t="n">
+        <x:f>ROUND(E137-F137,1)</x:f>
+        <x:v>4600</x:v>
+      </x:c>
+      <x:c r="K137" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B138" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C138" s="22" t="str">
+        <x:v>6月18日</x:v>
+      </x:c>
+      <x:c r="D138" s="23" t="n">
+        <x:v>172020</x:v>
+      </x:c>
+      <x:c r="E138" s="23" t="n">
+        <x:v>172500</x:v>
+      </x:c>
+      <x:c r="F138" s="23" t="n">
+        <x:v>160100</x:v>
+      </x:c>
+      <x:c r="G138" s="23" t="n">
+        <x:v>160500</x:v>
+      </x:c>
+      <x:c r="H138" s="28" t="n">
+        <x:v>-10800</x:v>
+      </x:c>
+      <x:c r="I138" s="24" t="n">
+        <x:v>-0.0630472854640981</x:v>
+      </x:c>
+      <x:c r="J138" s="26" t="n">
+        <x:f>ROUND(E138-F138,1)</x:f>
+        <x:v>12400</x:v>
+      </x:c>
+      <x:c r="K138" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B139" s="41" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C139" s="41" t="str">
+        <x:v>6月22日</x:v>
+      </x:c>
+      <x:c r="D139" s="42" t="n">
+        <x:v>157220</x:v>
+      </x:c>
+      <x:c r="E139" s="42" t="n">
+        <x:v>161800</x:v>
+      </x:c>
+      <x:c r="F139" s="42" t="n">
+        <x:v>150860</x:v>
+      </x:c>
+      <x:c r="G139" s="42" t="n">
+        <x:v>161740</x:v>
+      </x:c>
+      <x:c r="H139" s="28" t="n">
+        <x:v>1240</x:v>
+      </x:c>
+      <x:c r="I139" s="43" t="n">
+        <x:v>0.007725856697819333</x:v>
+      </x:c>
+      <x:c r="J139" s="26" t="n">
+        <x:f>ROUND(E139-F139,1)</x:f>
+        <x:v>10940</x:v>
+      </x:c>
+      <x:c r="K139" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B140" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C140" s="22" t="str">
+        <x:v>6月23日</x:v>
+      </x:c>
+      <x:c r="D140" s="23" t="n">
+        <x:v>158000</x:v>
+      </x:c>
+      <x:c r="E140" s="23" t="n">
+        <x:v>159460</x:v>
+      </x:c>
+      <x:c r="F140" s="23" t="n">
+        <x:v>153700</x:v>
+      </x:c>
+      <x:c r="G140" s="23" t="n">
+        <x:v>157220</x:v>
+      </x:c>
+      <x:c r="H140" s="28" t="n">
+        <x:v>-4520</x:v>
+      </x:c>
+      <x:c r="I140" s="24" t="n">
+        <x:v>-0.02794608631136397</x:v>
+      </x:c>
+      <x:c r="J140" s="23" t="n">
+        <x:f>ROUND(E140-F140,1)</x:f>
+        <x:v>5760</x:v>
+      </x:c>
+      <x:c r="K140" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B141" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C141" s="22" t="str">
+        <x:v>6月24日</x:v>
+      </x:c>
+      <x:c r="D141" s="23" t="n">
+        <x:v>156000</x:v>
+      </x:c>
+      <x:c r="E141" s="23" t="n">
+        <x:v>163940</x:v>
+      </x:c>
+      <x:c r="F141" s="23" t="n">
+        <x:v>154600</x:v>
+      </x:c>
+      <x:c r="G141" s="23" t="n">
+        <x:v>162740</x:v>
+      </x:c>
+      <x:c r="H141" s="28" t="n">
+        <x:v>5520</x:v>
+      </x:c>
+      <x:c r="I141" s="24" t="n">
+        <x:v>0.03511003689098069</x:v>
+      </x:c>
+      <x:c r="J141" s="26" t="n">
+        <x:f>ROUND(E141-F141,1)</x:f>
+        <x:v>9340</x:v>
+      </x:c>
+      <x:c r="K141" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B142" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C142" s="22" t="str">
+        <x:v>6月25日</x:v>
+      </x:c>
+      <x:c r="D142" s="23" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="E142" s="23" t="n">
+        <x:v>161200</x:v>
+      </x:c>
+      <x:c r="F142" s="23" t="n">
+        <x:v>150320</x:v>
+      </x:c>
+      <x:c r="G142" s="23" t="n">
+        <x:v>150840</x:v>
+      </x:c>
+      <x:c r="H142" s="28" t="n">
+        <x:v>-11900</x:v>
+      </x:c>
+      <x:c r="I142" s="24" t="n">
+        <x:v>-0.07312277252058497</x:v>
+      </x:c>
+      <x:c r="J142" s="26" t="n">
+        <x:f>ROUND(E142-F142,1)</x:f>
+        <x:v>10880</x:v>
+      </x:c>
+      <x:c r="K142" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B143" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C143" s="22" t="str">
+        <x:v>6月26日</x:v>
+      </x:c>
+      <x:c r="D143" s="23" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="E143" s="23" t="n">
+        <x:v>152880</x:v>
+      </x:c>
+      <x:c r="F143" s="23" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="G143" s="23" t="n">
+        <x:v>150220</x:v>
+      </x:c>
+      <x:c r="H143" s="28" t="n">
+        <x:v>-620</x:v>
+      </x:c>
+      <x:c r="I143" s="24" t="n">
+        <x:v>-0.004110315566162814</x:v>
+      </x:c>
+      <x:c r="J143" s="26" t="n">
+        <x:f>ROUND(E143-F143,1)</x:f>
+        <x:v>7880</x:v>
+      </x:c>
+      <x:c r="K143" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B144" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C144" s="22" t="str">
+        <x:v>6月29日</x:v>
+      </x:c>
+      <x:c r="D144" s="23" t="n">
+        <x:v>148000</x:v>
+      </x:c>
+      <x:c r="E144" s="23" t="n">
+        <x:v>154700</x:v>
+      </x:c>
+      <x:c r="F144" s="23" t="n">
+        <x:v>145300</x:v>
+      </x:c>
+      <x:c r="G144" s="23" t="n">
+        <x:v>153920</x:v>
+      </x:c>
+      <x:c r="H144" s="28" t="n">
+        <x:v>3700</x:v>
+      </x:c>
+      <x:c r="I144" s="24" t="n">
+        <x:v>0.024630541871921263</x:v>
+      </x:c>
+      <x:c r="J144" s="26" t="n">
+        <x:f>ROUND(E144-F144,1)</x:f>
+        <x:v>9400</x:v>
+      </x:c>
+      <x:c r="K144" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B145" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C145" s="22" t="str">
+        <x:v>6月30日</x:v>
+      </x:c>
+      <x:c r="D145" s="23" t="n">
+        <x:v>148020</x:v>
+      </x:c>
+      <x:c r="E145" s="23" t="n">
+        <x:v>163900</x:v>
+      </x:c>
+      <x:c r="F145" s="23" t="n">
+        <x:v>148020</x:v>
+      </x:c>
+      <x:c r="G145" s="23" t="n">
+        <x:v>163360</x:v>
+      </x:c>
+      <x:c r="H145" s="28" t="n">
+        <x:v>9440</x:v>
+      </x:c>
+      <x:c r="I145" s="24" t="n">
+        <x:v>0.06133056133056125</x:v>
+      </x:c>
+      <x:c r="J145" s="26" t="n">
+        <x:f>ROUND(E145-F145,1)</x:f>
+        <x:v>15880</x:v>
+      </x:c>
+      <x:c r="K145" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B146" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C146" s="30"/>
+      <x:c r="D146" s="30"/>
+      <x:c r="E146" s="30"/>
+      <x:c r="F146" s="30"/>
+      <x:c r="G146" s="30"/>
+      <x:c r="H146" s="30"/>
+      <x:c r="I146" s="30"/>
+      <x:c r="J146" s="32" t="n">
+        <x:f>ROUND(SUM(J125:J145),1)</x:f>
+        <x:v>166140</x:v>
+      </x:c>
+      <x:c r="K146" s="30"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B147" s="30"/>
+      <x:c r="C147" s="30"/>
+      <x:c r="D147" s="30"/>
+      <x:c r="E147" s="30"/>
+      <x:c r="F147" s="30"/>
+      <x:c r="G147" s="30"/>
+      <x:c r="H147" s="30"/>
+      <x:c r="I147" s="30"/>
+      <x:c r="J147" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
+        <x:v>7911.4</x:v>
+      </x:c>
+      <x:c r="K147" s="30"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="17" t="str">
+        <x:v>7月</x:v>
+      </x:c>
+      <x:c r="B149" s="17"/>
+      <x:c r="C149" s="17"/>
+      <x:c r="D149" s="17"/>
+      <x:c r="E149" s="17"/>
+      <x:c r="F149" s="17"/>
+      <x:c r="G149" s="17"/>
+      <x:c r="H149" s="17"/>
+      <x:c r="I149" s="17"/>
+      <x:c r="J149" s="17"/>
+      <x:c r="K149" s="17"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B150" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C150" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D150" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E150" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F150" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G150" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H150" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I150" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J150" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K150" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B151" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C151" s="22" t="str">
+        <x:v>7月1日</x:v>
+      </x:c>
+      <x:c r="D151" s="23" t="n">
+        <x:v>164000</x:v>
+      </x:c>
+      <x:c r="E151" s="23" t="n">
+        <x:v>166500</x:v>
+      </x:c>
+      <x:c r="F151" s="23" t="n">
+        <x:v>161500</x:v>
+      </x:c>
+      <x:c r="G151" s="23" t="n">
+        <x:v>164560</x:v>
+      </x:c>
+      <x:c r="H151" s="28" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="I151" s="24" t="n">
+        <x:v>0.007345739471106727</x:v>
+      </x:c>
+      <x:c r="J151" s="23" t="n">
+        <x:f>ROUND(E151-F151,1)</x:f>
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="K151" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B152" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C152" s="22" t="str">
+        <x:v>7月2日</x:v>
+      </x:c>
+      <x:c r="D152" s="23" t="n">
+        <x:v>163500</x:v>
+      </x:c>
+      <x:c r="E152" s="23" t="n">
+        <x:v>167800</x:v>
+      </x:c>
+      <x:c r="F152" s="23" t="n">
+        <x:v>162220</x:v>
+      </x:c>
+      <x:c r="G152" s="23" t="n">
+        <x:v>164040</x:v>
+      </x:c>
+      <x:c r="H152" s="28" t="n">
+        <x:v>-520</x:v>
+      </x:c>
+      <x:c r="I152" s="24" t="n">
+        <x:v>-0.003159941662615462</x:v>
+      </x:c>
+      <x:c r="J152" s="23" t="n">
+        <x:f>ROUND(E152-F152,1)</x:f>
+        <x:v>5580</x:v>
+      </x:c>
+      <x:c r="K152" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B153" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C153" s="22" t="str">
+        <x:v>7月3日</x:v>
+      </x:c>
+      <x:c r="D153" s="23" t="n">
+        <x:v>170600</x:v>
+      </x:c>
+      <x:c r="E153" s="23" t="n">
+        <x:v>172000</x:v>
+      </x:c>
+      <x:c r="F153" s="23" t="n">
+        <x:v>166300</x:v>
+      </x:c>
+      <x:c r="G153" s="23" t="n">
+        <x:v>168780</x:v>
+      </x:c>
+      <x:c r="H153" s="28" t="n">
+        <x:v>4740</x:v>
+      </x:c>
+      <x:c r="I153" s="24" t="n">
+        <x:v>0.028895391367959045</x:v>
+      </x:c>
+      <x:c r="J153" s="23" t="n">
+        <x:f>ROUND(E153-F153,1)</x:f>
+        <x:v>5700</x:v>
+      </x:c>
+      <x:c r="K153" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B154" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C154" s="22" t="str">
+        <x:v>7月6日</x:v>
+      </x:c>
+      <x:c r="D154" s="23" t="n">
+        <x:v>166980</x:v>
+      </x:c>
+      <x:c r="E154" s="23" t="n">
+        <x:v>168720</x:v>
+      </x:c>
+      <x:c r="F154" s="23" t="n">
+        <x:v>163280</x:v>
+      </x:c>
+      <x:c r="G154" s="23" t="n">
+        <x:v>164560</x:v>
+      </x:c>
+      <x:c r="H154" s="28" t="n">
+        <x:v>-4220</x:v>
+      </x:c>
+      <x:c r="I154" s="24" t="n">
+        <x:v>-0.02500296243630762</x:v>
+      </x:c>
+      <x:c r="J154" s="23" t="n">
+        <x:f>ROUND(E154-F154,1)</x:f>
+        <x:v>5440</x:v>
+      </x:c>
+      <x:c r="K154" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B155" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C155" s="22" t="str">
+        <x:v>7月7日</x:v>
+      </x:c>
+      <x:c r="D155" s="23" t="n">
+        <x:v>165000</x:v>
+      </x:c>
+      <x:c r="E155" s="23" t="n">
+        <x:v>166380</x:v>
+      </x:c>
+      <x:c r="F155" s="23" t="n">
+        <x:v>160660</x:v>
+      </x:c>
+      <x:c r="G155" s="23" t="n">
+        <x:v>163360</x:v>
+      </x:c>
+      <x:c r="H155" s="28" t="n">
+        <x:v>-1200</x:v>
+      </x:c>
+      <x:c r="I155" s="24" t="n">
+        <x:v>-0.007292173067574126</x:v>
+      </x:c>
+      <x:c r="J155" s="23" t="n">
+        <x:f>ROUND(E155-F155,1)</x:f>
+        <x:v>5720</x:v>
+      </x:c>
+      <x:c r="K155" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B156" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C156" s="22" t="str">
+        <x:v>7月8日</x:v>
+      </x:c>
+      <x:c r="D156" s="23" t="n">
+        <x:v>164220</x:v>
+      </x:c>
+      <x:c r="E156" s="23" t="n">
+        <x:v>165200</x:v>
+      </x:c>
+      <x:c r="F156" s="23" t="n">
+        <x:v>158400</x:v>
+      </x:c>
+      <x:c r="G156" s="23" t="n">
+        <x:v>158440</x:v>
+      </x:c>
+      <x:c r="H156" s="28" t="n">
+        <x:v>-4920</x:v>
+      </x:c>
+      <x:c r="I156" s="24" t="n">
+        <x:v>-0.030117531831537758</x:v>
+      </x:c>
+      <x:c r="J156" s="26" t="n">
+        <x:f>ROUND(E156-F156,1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="K156" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B157" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C157" s="22" t="str">
+        <x:v>7月9日</x:v>
+      </x:c>
+      <x:c r="D157" s="23" t="n">
+        <x:v>159600</x:v>
+      </x:c>
+      <x:c r="E157" s="23" t="n">
+        <x:v>159940</x:v>
+      </x:c>
+      <x:c r="F157" s="23" t="n">
+        <x:v>151020</x:v>
+      </x:c>
+      <x:c r="G157" s="23" t="n">
+        <x:v>153020</x:v>
+      </x:c>
+      <x:c r="H157" s="28" t="n">
+        <x:v>-5420</x:v>
+      </x:c>
+      <x:c r="I157" s="24" t="n">
+        <x:v>-0.03420853319868722</x:v>
+      </x:c>
+      <x:c r="J157" s="26" t="n">
+        <x:f>ROUND(E157-F157,1)</x:f>
+        <x:v>8920</x:v>
+      </x:c>
+      <x:c r="K157" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B158" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C158" s="22" t="str">
+        <x:v>7月10日</x:v>
+      </x:c>
+      <x:c r="D158" s="23" t="n">
+        <x:v>153000</x:v>
+      </x:c>
+      <x:c r="E158" s="23" t="n">
+        <x:v>153920</x:v>
+      </x:c>
+      <x:c r="F158" s="23" t="n">
+        <x:v>150260</x:v>
+      </x:c>
+      <x:c r="G158" s="23" t="n">
+        <x:v>151600</x:v>
+      </x:c>
+      <x:c r="H158" s="28" t="n">
+        <x:v>-1420</x:v>
+      </x:c>
+      <x:c r="I158" s="24" t="n">
+        <x:v>-0.009279832701607593</x:v>
+      </x:c>
+      <x:c r="J158" s="23" t="n">
+        <x:f>ROUND(E158-F158,1)</x:f>
+        <x:v>3660</x:v>
+      </x:c>
+      <x:c r="K158" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B159" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C159" s="22" t="str">
+        <x:v>7月13日</x:v>
+      </x:c>
+      <x:c r="D159" s="23" t="n">
+        <x:v>150500</x:v>
+      </x:c>
+      <x:c r="E159" s="23" t="n">
+        <x:v>153580</x:v>
+      </x:c>
+      <x:c r="F159" s="23" t="n">
+        <x:v>147840</x:v>
+      </x:c>
+      <x:c r="G159" s="23" t="n">
+        <x:v>152240</x:v>
+      </x:c>
+      <x:c r="H159" s="28" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="I159" s="24" t="n">
+        <x:v>0.004221635883905117</x:v>
+      </x:c>
+      <x:c r="J159" s="23" t="n">
+        <x:f>ROUND(E159-F159,1)</x:f>
+        <x:v>5740</x:v>
+      </x:c>
+      <x:c r="K159" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B160" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C160" s="22" t="str">
+        <x:v>7月14日</x:v>
+      </x:c>
+      <x:c r="D160" s="23" t="n">
+        <x:v>152000</x:v>
+      </x:c>
+      <x:c r="E160" s="23" t="n">
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="F160" s="23" t="n">
+        <x:v>150720</x:v>
+      </x:c>
+      <x:c r="G160" s="23" t="n">
+        <x:v>153180</x:v>
+      </x:c>
+      <x:c r="H160" s="28" t="n">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="I160" s="24" t="n">
+        <x:v>0.006174461376773577</x:v>
+      </x:c>
+      <x:c r="J160" s="23" t="n">
+        <x:f>ROUND(E160-F160,1)</x:f>
+        <x:v>3280</x:v>
+      </x:c>
+      <x:c r="K160" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B161" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C161" s="22" t="str">
+        <x:v>7月15日</x:v>
+      </x:c>
+      <x:c r="D161" s="23" t="n">
+        <x:v>153880</x:v>
+      </x:c>
+      <x:c r="E161" s="23" t="n">
+        <x:v>156500</x:v>
+      </x:c>
+      <x:c r="F161" s="23" t="n">
+        <x:v>147540</x:v>
+      </x:c>
+      <x:c r="G161" s="23" t="n">
+        <x:v>149240</x:v>
+      </x:c>
+      <x:c r="H161" s="28" t="n">
+        <x:v>-3940</x:v>
+      </x:c>
+      <x:c r="I161" s="24" t="n">
+        <x:v>-0.025721373547460513</x:v>
+      </x:c>
+      <x:c r="J161" s="26" t="n">
+        <x:f>ROUND(E161-F161,1)</x:f>
+        <x:v>8960</x:v>
+      </x:c>
+      <x:c r="K161" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B162" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C162" s="22" t="str">
+        <x:v>7月16日</x:v>
+      </x:c>
+      <x:c r="D162" s="23" t="n">
+        <x:v>148980</x:v>
+      </x:c>
+      <x:c r="E162" s="23" t="n">
+        <x:v>153340</x:v>
+      </x:c>
+      <x:c r="F162" s="23" t="n">
+        <x:v>145860</x:v>
+      </x:c>
+      <x:c r="G162" s="23" t="n">
+        <x:v>151660</x:v>
+      </x:c>
+      <x:c r="H162" s="28" t="n">
+        <x:v>2420</x:v>
+      </x:c>
+      <x:c r="I162" s="24" t="n">
+        <x:v>0.016215491825247952</x:v>
+      </x:c>
+      <x:c r="J162" s="26" t="n">
+        <x:f>ROUND(E162-F162,1)</x:f>
+        <x:v>7480</x:v>
+      </x:c>
+      <x:c r="K162" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="41" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B163" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C163" s="41" t="str">
+        <x:v>7月17日</x:v>
+      </x:c>
+      <x:c r="D163" s="42" t="n">
+        <x:v>153100</x:v>
+      </x:c>
+      <x:c r="E163" s="42" t="n">
+        <x:v>155300</x:v>
+      </x:c>
+      <x:c r="F163" s="42" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="G163" s="42" t="n">
+        <x:v>150140</x:v>
+      </x:c>
+      <x:c r="H163" s="28" t="n">
+        <x:v>-1520</x:v>
+      </x:c>
+      <x:c r="I163" s="43" t="n">
+        <x:v>-0.010022418567849134</x:v>
+      </x:c>
+      <x:c r="J163" s="26" t="n">
+        <x:f>ROUND(E163-F163,1)</x:f>
+        <x:v>6300</x:v>
+      </x:c>
+      <x:c r="K163" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B164" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C164" s="22" t="str">
+        <x:v>7月20日</x:v>
+      </x:c>
+      <x:c r="D164" s="23" t="n">
+        <x:v>151500</x:v>
+      </x:c>
+      <x:c r="E164" s="23" t="n">
+        <x:v>154800</x:v>
+      </x:c>
+      <x:c r="F164" s="23" t="n">
+        <x:v>141400</x:v>
+      </x:c>
+      <x:c r="G164" s="23" t="n">
+        <x:v>143900</x:v>
+      </x:c>
+      <x:c r="H164" s="28" t="n">
+        <x:v>-6240</x:v>
+      </x:c>
+      <x:c r="I164" s="24" t="n">
+        <x:v>-0.041561209537764765</x:v>
+      </x:c>
+      <x:c r="J164" s="26" t="n">
+        <x:f>ROUND(E164-F164,1)</x:f>
+        <x:v>13400</x:v>
+      </x:c>
+      <x:c r="K164" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B165" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C165" s="22" t="str">
+        <x:v>7月21日</x:v>
+      </x:c>
+      <x:c r="D165" s="23" t="n">
+        <x:v>143800</x:v>
+      </x:c>
+      <x:c r="E165" s="23" t="n">
+        <x:v>144300</x:v>
+      </x:c>
+      <x:c r="F165" s="23" t="n">
+        <x:v>136800</x:v>
+      </x:c>
+      <x:c r="G165" s="23" t="n">
+        <x:v>141620</x:v>
+      </x:c>
+      <x:c r="H165" s="28" t="n">
+        <x:v>-2280</x:v>
+      </x:c>
+      <x:c r="I165" s="24" t="n">
+        <x:v>-0.01584433634468385</x:v>
+      </x:c>
+      <x:c r="J165" s="26" t="n">
+        <x:f>ROUND(E165-F165,1)</x:f>
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="K165" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B166" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C166" s="22" t="str">
+        <x:v>7月22日</x:v>
+      </x:c>
+      <x:c r="D166" s="23" t="n">
+        <x:v>142980</x:v>
+      </x:c>
+      <x:c r="E166" s="23" t="n">
+        <x:v>145200</x:v>
+      </x:c>
+      <x:c r="F166" s="23" t="n">
+        <x:v>137220</x:v>
+      </x:c>
+      <x:c r="G166" s="23" t="n">
+        <x:v>143300</x:v>
+      </x:c>
+      <x:c r="H166" s="28" t="n">
+        <x:v>1680</x:v>
+      </x:c>
+      <x:c r="I166" s="24" t="n">
+        <x:v>0.011862731252648029</x:v>
+      </x:c>
+      <x:c r="J166" s="26" t="n">
+        <x:f>ROUND(E166-F166,1)</x:f>
+        <x:v>7980</x:v>
+      </x:c>
+      <x:c r="K166" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B167" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C167" s="22" t="str">
+        <x:v>7月23日</x:v>
+      </x:c>
+      <x:c r="D167" s="23" t="n">
+        <x:v>143380</x:v>
+      </x:c>
+      <x:c r="E167" s="23" t="n">
+        <x:v>148480</x:v>
+      </x:c>
+      <x:c r="F167" s="23" t="n">
+        <x:v>142240</x:v>
+      </x:c>
+      <x:c r="G167" s="23" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="H167" s="28" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="I167" s="24" t="n">
+        <x:v>0.011863224005582707</x:v>
+      </x:c>
+      <x:c r="J167" s="26" t="n">
+        <x:f>ROUND(E167-F167,1)</x:f>
+        <x:v>6240</x:v>
+      </x:c>
+      <x:c r="K167" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B168" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C168" s="22" t="str">
+        <x:v>7月24日</x:v>
+      </x:c>
+      <x:c r="D168" s="23" t="n">
+        <x:v>144200</x:v>
+      </x:c>
+      <x:c r="E168" s="23" t="n">
+        <x:v>145800</x:v>
+      </x:c>
+      <x:c r="F168" s="23" t="n">
+        <x:v>141320</x:v>
+      </x:c>
+      <x:c r="G168" s="23" t="n">
+        <x:v>144280</x:v>
+      </x:c>
+      <x:c r="H168" s="28" t="n">
+        <x:v>-720</x:v>
+      </x:c>
+      <x:c r="I168" s="24" t="n">
+        <x:v>-0.00496551724137928</x:v>
+      </x:c>
+      <x:c r="J168" s="23" t="n">
+        <x:f>ROUND(E168-F168,1)</x:f>
+        <x:v>4480</x:v>
+      </x:c>
+      <x:c r="K168" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B169" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C169" s="22" t="str">
+        <x:v>7月27日</x:v>
+      </x:c>
+      <x:c r="D169" s="23" t="n">
+        <x:v>145780</x:v>
+      </x:c>
+      <x:c r="E169" s="23" t="n">
+        <x:v>148220</x:v>
+      </x:c>
+      <x:c r="F169" s="23" t="n">
+        <x:v>143260</x:v>
+      </x:c>
+      <x:c r="G169" s="23" t="n">
+        <x:v>147220</x:v>
+      </x:c>
+      <x:c r="H169" s="28" t="n">
+        <x:v>2940</x:v>
+      </x:c>
+      <x:c r="I169" s="24" t="n">
+        <x:v>0.020377044635430996</x:v>
+      </x:c>
+      <x:c r="J169" s="23" t="n">
+        <x:f>ROUND(E169-F169,1)</x:f>
+        <x:v>4960</x:v>
+      </x:c>
+      <x:c r="K169" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B170" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C170" s="22" t="str">
+        <x:v>7月28日</x:v>
+      </x:c>
+      <x:c r="D170" s="23" t="n">
+        <x:v>146560</x:v>
+      </x:c>
+      <x:c r="E170" s="23" t="n">
+        <x:v>147680</x:v>
+      </x:c>
+      <x:c r="F170" s="23" t="n">
+        <x:v>142000</x:v>
+      </x:c>
+      <x:c r="G170" s="23" t="n">
+        <x:v>143480</x:v>
+      </x:c>
+      <x:c r="H170" s="28" t="n">
+        <x:v>-3740</x:v>
+      </x:c>
+      <x:c r="I170" s="24" t="n">
+        <x:v>-0.025404157043879882</x:v>
+      </x:c>
+      <x:c r="J170" s="23" t="n">
+        <x:f>ROUND(E170-F170,1)</x:f>
+        <x:v>5680</x:v>
+      </x:c>
+      <x:c r="K170" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B171" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C171" s="22" t="str">
+        <x:v>7月29日</x:v>
+      </x:c>
+      <x:c r="D171" s="23" t="n">
+        <x:v>143480</x:v>
+      </x:c>
+      <x:c r="E171" s="23" t="n">
+        <x:v>149400</x:v>
+      </x:c>
+      <x:c r="F171" s="23" t="n">
+        <x:v>142500</x:v>
+      </x:c>
+      <x:c r="G171" s="23" t="n">
+        <x:v>147900</x:v>
+      </x:c>
+      <x:c r="H171" s="28" t="n">
+        <x:v>4420</x:v>
+      </x:c>
+      <x:c r="I171" s="24" t="n">
+        <x:v>0.0308056872037914</x:v>
+      </x:c>
+      <x:c r="J171" s="26" t="n">
+        <x:f>ROUND(E171-F171,1)</x:f>
+        <x:v>6900</x:v>
+      </x:c>
+      <x:c r="K171" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="22" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B172" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C172" s="22" t="str">
+        <x:v>7月30日</x:v>
+      </x:c>
+      <x:c r="D172" s="23" t="n">
+        <x:v>147980</x:v>
+      </x:c>
+      <x:c r="E172" s="23" t="n">
+        <x:v>148080</x:v>
+      </x:c>
+      <x:c r="F172" s="23" t="n">
+        <x:v>140620</x:v>
+      </x:c>
+      <x:c r="G172" s="23" t="n">
+        <x:v>141060</x:v>
+      </x:c>
+      <x:c r="H172" s="28" t="n">
+        <x:v>-6840</x:v>
+      </x:c>
+      <x:c r="I172" s="24" t="n">
+        <x:v>-0.04624746450304262</x:v>
+      </x:c>
+      <x:c r="J172" s="26" t="n">
+        <x:f>ROUND(E172-F172,1)</x:f>
+        <x:v>7460</x:v>
+      </x:c>
+      <x:c r="K172" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="22" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B173" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C173" s="22" t="str">
+        <x:v>7月31日</x:v>
+      </x:c>
+      <x:c r="D173" s="23" t="n">
+        <x:v>143880</x:v>
+      </x:c>
+      <x:c r="E173" s="23" t="n">
+        <x:v>144400</x:v>
+      </x:c>
+      <x:c r="F173" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="G173" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="H173" s="28" t="n">
+        <x:v>-3300</x:v>
+      </x:c>
+      <x:c r="I173" s="24" t="n">
+        <x:v>-0.023394300297745585</x:v>
+      </x:c>
+      <x:c r="J173" s="26" t="n">
+        <x:f>ROUND(E173-F173,1)</x:f>
+        <x:v>6640</x:v>
+      </x:c>
+      <x:c r="K173" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B174" s="30" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C174" s="30"/>
+      <x:c r="D174" s="30"/>
+      <x:c r="E174" s="30"/>
+      <x:c r="F174" s="30"/>
+      <x:c r="G174" s="30"/>
+      <x:c r="H174" s="30"/>
+      <x:c r="I174" s="30"/>
+      <x:c r="J174" s="32" t="n">
+        <x:f>ROUND(SUM(J151:J173),1)</x:f>
+        <x:v>149820</x:v>
+      </x:c>
+      <x:c r="K174" s="30"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B175" s="30"/>
+      <x:c r="C175" s="30"/>
+      <x:c r="D175" s="30"/>
+      <x:c r="E175" s="30"/>
+      <x:c r="F175" s="30"/>
+      <x:c r="G175" s="30"/>
+      <x:c r="H175" s="30"/>
+      <x:c r="I175" s="30"/>
+      <x:c r="J175" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J151:J173),0),1)</x:f>
+        <x:v>6513.9</x:v>
+      </x:c>
+      <x:c r="K175" s="30"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="17" t="str">
+        <x:v>8月</x:v>
+      </x:c>
+      <x:c r="B177" s="17"/>
+      <x:c r="C177" s="17"/>
+      <x:c r="D177" s="17"/>
+      <x:c r="E177" s="17"/>
+      <x:c r="F177" s="17"/>
+      <x:c r="G177" s="17"/>
+      <x:c r="H177" s="17"/>
+      <x:c r="I177" s="17"/>
+      <x:c r="J177" s="17"/>
+      <x:c r="K177" s="17"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B178" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C178" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D178" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E178" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F178" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G178" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H178" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I178" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J178" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K178" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B179" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C179" s="22" t="str">
+        <x:v>8月3日</x:v>
+      </x:c>
+      <x:c r="D179" s="23" t="n">
+        <x:v>137500</x:v>
+      </x:c>
+      <x:c r="E179" s="23" t="n">
+        <x:v>140840</x:v>
+      </x:c>
+      <x:c r="F179" s="23" t="n">
+        <x:v>135560</x:v>
+      </x:c>
+      <x:c r="G179" s="23" t="n">
+        <x:v>138900</x:v>
+      </x:c>
+      <x:c r="H179" s="28" t="n">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="I179" s="24" t="n">
+        <x:v>0.008275261324041772</x:v>
+      </x:c>
+      <x:c r="J179" s="23" t="n">
+        <x:f>ROUND(E179-F179,1)</x:f>
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="K179" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B180" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C180" s="22" t="str">
+        <x:v>8月4日</x:v>
+      </x:c>
+      <x:c r="D180" s="23" t="n">
+        <x:v>138780</x:v>
+      </x:c>
+      <x:c r="E180" s="23" t="n">
+        <x:v>141360</x:v>
+      </x:c>
+      <x:c r="F180" s="23" t="n">
+        <x:v>137340</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
+        <x:v>139380</x:v>
+      </x:c>
+      <x:c r="H180" s="28" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="I180" s="24" t="n">
+        <x:v>0.003455723542116651</x:v>
+      </x:c>
+      <x:c r="J180" s="23" t="n">
+        <x:f>ROUND(E180-F180,1)</x:f>
+        <x:v>4020</x:v>
+      </x:c>
+      <x:c r="K180" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B181" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C181" s="22" t="str">
+        <x:v>8月5日</x:v>
+      </x:c>
+      <x:c r="D181" s="23" t="n">
+        <x:v>139720</x:v>
+      </x:c>
+      <x:c r="E181" s="23" t="n">
+        <x:v>144300</x:v>
+      </x:c>
+      <x:c r="F181" s="23" t="n">
+        <x:v>138320</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
+        <x:v>143220</x:v>
+      </x:c>
+      <x:c r="H181" s="28" t="n">
+        <x:v>3840</x:v>
+      </x:c>
+      <x:c r="I181" s="24" t="n">
+        <x:v>0.027550581145070918</x:v>
+      </x:c>
+      <x:c r="J181" s="23" t="n">
+        <x:f>ROUND(E181-F181,1)</x:f>
+        <x:v>5980</x:v>
+      </x:c>
+      <x:c r="K181" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B182" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C182" s="30"/>
+      <x:c r="D182" s="30"/>
+      <x:c r="E182" s="30"/>
+      <x:c r="F182" s="30"/>
+      <x:c r="G182" s="30"/>
+      <x:c r="H182" s="30"/>
+      <x:c r="I182" s="30"/>
+      <x:c r="J182" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J181),1)</x:f>
+        <x:v>15280</x:v>
+      </x:c>
+      <x:c r="K182" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B183" s="30"/>
+      <x:c r="C183" s="30"/>
+      <x:c r="D183" s="30"/>
+      <x:c r="E183" s="30"/>
+      <x:c r="F183" s="30"/>
+      <x:c r="G183" s="30"/>
+      <x:c r="H183" s="30"/>
+      <x:c r="I183" s="30"/>
+      <x:c r="J183" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
+        <x:v>5093.3</x:v>
+      </x:c>
+      <x:c r="K183" s="30"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A3:K3"/>
+    <x:mergeCell ref="A28:K28"/>
+    <x:mergeCell ref="A47:K47"/>
+    <x:mergeCell ref="A74:K74"/>
+    <x:mergeCell ref="A100:K100"/>
+    <x:mergeCell ref="A123:K123"/>
+    <x:mergeCell ref="A149:K149"/>
+    <x:mergeCell ref="A177:K177"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9412,6 +15310,1228 @@
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
     </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="17" t="str">
+        <x:v>碳酸锂2609</x:v>
+      </x:c>
+      <x:c r="B248" s="17"/>
+      <x:c r="C248" s="17"/>
+      <x:c r="D248" s="17"/>
+      <x:c r="E248" s="17"/>
+      <x:c r="F248" s="17"/>
+      <x:c r="G248" s="17"/>
+      <x:c r="H248" s="17"/>
+      <x:c r="I248" s="17"/>
+      <x:c r="J248" s="17"/>
+      <x:c r="K248" s="17"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B249" s="20" t="str">
+        <x:v>周期</x:v>
+      </x:c>
+      <x:c r="C249" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="D249" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="E249" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="F249" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="G249" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="H249" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="I249" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="J249" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+      <x:c r="K249" s="20" t="str">
+        <x:v>交易日</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B250" s="22" t="str">
+        <x:v>1月5日-1月9日</x:v>
+      </x:c>
+      <x:c r="C250" s="23" t="n">
+        <x:v>126360</x:v>
+      </x:c>
+      <x:c r="D250" s="23" t="n">
+        <x:v>150760</x:v>
+      </x:c>
+      <x:c r="E250" s="23" t="n">
+        <x:v>125160</x:v>
+      </x:c>
+      <x:c r="F250" s="23" t="n">
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="G250" s="23"/>
+      <x:c r="H250" s="24"/>
+      <x:c r="I250" s="26" t="n">
+        <x:f>ROUND(D250-E250,1)</x:f>
+        <x:v>25600</x:v>
+      </x:c>
+      <x:c r="J250" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K250" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B251" s="22" t="str">
+        <x:v>1月12日-1月16日</x:v>
+      </x:c>
+      <x:c r="C251" s="23" t="n">
+        <x:v>153000</x:v>
+      </x:c>
+      <x:c r="D251" s="23" t="n">
+        <x:v>176120</x:v>
+      </x:c>
+      <x:c r="E251" s="23" t="n">
+        <x:v>147740</x:v>
+      </x:c>
+      <x:c r="F251" s="23" t="n">
+        <x:v>147740</x:v>
+      </x:c>
+      <x:c r="G251" s="28" t="n">
+        <x:f>ROUND(F251-F250,1)</x:f>
+        <x:v>2360</x:v>
+      </x:c>
+      <x:c r="H251" s="24" t="n">
+        <x:f>IFERROR(F251/F250-1,"")</x:f>
+        <x:v>0.016233319576282934</x:v>
+      </x:c>
+      <x:c r="I251" s="26" t="n">
+        <x:f>ROUND(D251-E251,1)</x:f>
+        <x:v>28380</x:v>
+      </x:c>
+      <x:c r="J251" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K251" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B252" s="22" t="str">
+        <x:v>1月19日-1月23日</x:v>
+      </x:c>
+      <x:c r="C252" s="23" t="n">
+        <x:v>150720</x:v>
+      </x:c>
+      <x:c r="D252" s="23" t="n">
+        <x:v>183780</x:v>
+      </x:c>
+      <x:c r="E252" s="23" t="n">
+        <x:v>143820</x:v>
+      </x:c>
+      <x:c r="F252" s="23" t="n">
+        <x:v>183380</x:v>
+      </x:c>
+      <x:c r="G252" s="28" t="n">
+        <x:f>ROUND(F252-F251,1)</x:f>
+        <x:v>35640</x:v>
+      </x:c>
+      <x:c r="H252" s="24" t="n">
+        <x:f>IFERROR(F252/F251-1,"")</x:f>
+        <x:v>0.24123460132665486</x:v>
+      </x:c>
+      <x:c r="I252" s="26" t="n">
+        <x:f>ROUND(D252-E252,1)</x:f>
+        <x:v>39960</x:v>
+      </x:c>
+      <x:c r="J252" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K252" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B253" s="22" t="str">
+        <x:v>1月26日-1月30日</x:v>
+      </x:c>
+      <x:c r="C253" s="23" t="n">
+        <x:v>187000</x:v>
+      </x:c>
+      <x:c r="D253" s="23" t="n">
+        <x:v>190600</x:v>
+      </x:c>
+      <x:c r="E253" s="23" t="n">
+        <x:v>148560</x:v>
+      </x:c>
+      <x:c r="F253" s="23" t="n">
+        <x:v>148560</x:v>
+      </x:c>
+      <x:c r="G253" s="28" t="n">
+        <x:f>ROUND(F253-F252,1)</x:f>
+        <x:v>-34820</x:v>
+      </x:c>
+      <x:c r="H253" s="24" t="n">
+        <x:f>IFERROR(F253/F252-1,"")</x:f>
+        <x:v>-0.18987893990620575</x:v>
+      </x:c>
+      <x:c r="I253" s="26" t="n">
+        <x:f>ROUND(D253-E253,1)</x:f>
+        <x:v>42040</x:v>
+      </x:c>
+      <x:c r="J253" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K253" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B254" s="22" t="str">
+        <x:v>2月2日-2月6日</x:v>
+      </x:c>
+      <x:c r="C254" s="23" t="n">
+        <x:v>148040</x:v>
+      </x:c>
+      <x:c r="D254" s="23" t="n">
+        <x:v>153200</x:v>
+      </x:c>
+      <x:c r="E254" s="23" t="n">
+        <x:v>124480</x:v>
+      </x:c>
+      <x:c r="F254" s="23" t="n">
+        <x:v>133500</x:v>
+      </x:c>
+      <x:c r="G254" s="28" t="n">
+        <x:f>ROUND(F254-F253,1)</x:f>
+        <x:v>-15060</x:v>
+      </x:c>
+      <x:c r="H254" s="24" t="n">
+        <x:f>IFERROR(F254/F253-1,"")</x:f>
+        <x:v>-0.10137318255250405</x:v>
+      </x:c>
+      <x:c r="I254" s="26" t="n">
+        <x:f>ROUND(D254-E254,1)</x:f>
+        <x:v>28720</x:v>
+      </x:c>
+      <x:c r="J254" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K254" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B255" s="22" t="str">
+        <x:v>2月9日-2月13日</x:v>
+      </x:c>
+      <x:c r="C255" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="D255" s="23" t="n">
+        <x:v>153700</x:v>
+      </x:c>
+      <x:c r="E255" s="23" t="n">
+        <x:v>133500</x:v>
+      </x:c>
+      <x:c r="F255" s="23" t="n">
+        <x:v>153500</x:v>
+      </x:c>
+      <x:c r="G255" s="28" t="n">
+        <x:f>ROUND(F255-F254,1)</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="H255" s="24" t="n">
+        <x:f>IFERROR(F255/F254-1,"")</x:f>
+        <x:v>0.14981273408239693</x:v>
+      </x:c>
+      <x:c r="I255" s="26" t="n">
+        <x:f>ROUND(D255-E255,1)</x:f>
+        <x:v>20200</x:v>
+      </x:c>
+      <x:c r="J255" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K255" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B256" s="22" t="str">
+        <x:v>2月24日-2月27日</x:v>
+      </x:c>
+      <x:c r="C256" s="23" t="n">
+        <x:v>158340</x:v>
+      </x:c>
+      <x:c r="D256" s="23" t="n">
+        <x:v>186900</x:v>
+      </x:c>
+      <x:c r="E256" s="23" t="n">
+        <x:v>158340</x:v>
+      </x:c>
+      <x:c r="F256" s="23" t="n">
+        <x:v>177200</x:v>
+      </x:c>
+      <x:c r="G256" s="28" t="n">
+        <x:f>ROUND(F256-F255,1)</x:f>
+        <x:v>23700</x:v>
+      </x:c>
+      <x:c r="H256" s="24" t="n">
+        <x:f>IFERROR(F256/F255-1,"")</x:f>
+        <x:v>0.15439739413680775</x:v>
+      </x:c>
+      <x:c r="I256" s="26" t="n">
+        <x:f>ROUND(D256-E256,1)</x:f>
+        <x:v>28560</x:v>
+      </x:c>
+      <x:c r="J256" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K256" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B257" s="22" t="str">
+        <x:v>3月2日-3月6日</x:v>
+      </x:c>
+      <x:c r="C257" s="23" t="n">
+        <x:v>180000</x:v>
+      </x:c>
+      <x:c r="D257" s="23" t="n">
+        <x:v>180060</x:v>
+      </x:c>
+      <x:c r="E257" s="23" t="n">
+        <x:v>146040</x:v>
+      </x:c>
+      <x:c r="F257" s="23" t="n">
+        <x:v>156700</x:v>
+      </x:c>
+      <x:c r="G257" s="28" t="n">
+        <x:f>ROUND(F257-F256,1)</x:f>
+        <x:v>-20500</x:v>
+      </x:c>
+      <x:c r="H257" s="24" t="n">
+        <x:f>IFERROR(F257/F256-1,"")</x:f>
+        <x:v>-0.11568848758465011</x:v>
+      </x:c>
+      <x:c r="I257" s="26" t="n">
+        <x:f>ROUND(D257-E257,1)</x:f>
+        <x:v>34020</x:v>
+      </x:c>
+      <x:c r="J257" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K257" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B258" s="22" t="str">
+        <x:v>3月9日-3月13日</x:v>
+      </x:c>
+      <x:c r="C258" s="23" t="n">
+        <x:v>149000</x:v>
+      </x:c>
+      <x:c r="D258" s="23" t="n">
+        <x:v>167400</x:v>
+      </x:c>
+      <x:c r="E258" s="23" t="n">
+        <x:v>142600</x:v>
+      </x:c>
+      <x:c r="F258" s="23" t="n">
+        <x:v>152100</x:v>
+      </x:c>
+      <x:c r="G258" s="28" t="n">
+        <x:f>ROUND(F258-F257,1)</x:f>
+        <x:v>-4600</x:v>
+      </x:c>
+      <x:c r="H258" s="24" t="n">
+        <x:f>IFERROR(F258/F257-1,"")</x:f>
+        <x:v>-0.02935545628589664</x:v>
+      </x:c>
+      <x:c r="I258" s="26" t="n">
+        <x:f>ROUND(D258-E258,1)</x:f>
+        <x:v>24800</x:v>
+      </x:c>
+      <x:c r="J258" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K258" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B259" s="22" t="str">
+        <x:v>3月16日-3月20日</x:v>
+      </x:c>
+      <x:c r="C259" s="23" t="n">
+        <x:v>150880</x:v>
+      </x:c>
+      <x:c r="D259" s="23" t="n">
+        <x:v>160800</x:v>
+      </x:c>
+      <x:c r="E259" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="F259" s="23" t="n">
+        <x:v>143520</x:v>
+      </x:c>
+      <x:c r="G259" s="28" t="n">
+        <x:f>ROUND(F259-F258,1)</x:f>
+        <x:v>-8580</x:v>
+      </x:c>
+      <x:c r="H259" s="24" t="n">
+        <x:f>IFERROR(F259/F258-1,"")</x:f>
+        <x:v>-0.05641025641025643</x:v>
+      </x:c>
+      <x:c r="I259" s="26" t="n">
+        <x:f>ROUND(D259-E259,1)</x:f>
+        <x:v>20800</x:v>
+      </x:c>
+      <x:c r="J259" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K259" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B260" s="22" t="str">
+        <x:v>3月23日-3月27日</x:v>
+      </x:c>
+      <x:c r="C260" s="23" t="n">
+        <x:v>141220</x:v>
+      </x:c>
+      <x:c r="D260" s="23" t="n">
+        <x:v>172220</x:v>
+      </x:c>
+      <x:c r="E260" s="23" t="n">
+        <x:v>140020</x:v>
+      </x:c>
+      <x:c r="F260" s="23" t="n">
+        <x:v>169400</x:v>
+      </x:c>
+      <x:c r="G260" s="28" t="n">
+        <x:f>ROUND(F260-F259,1)</x:f>
+        <x:v>25880</x:v>
+      </x:c>
+      <x:c r="H260" s="24" t="n">
+        <x:f>IFERROR(F260/F259-1,"")</x:f>
+        <x:v>0.18032329988851736</x:v>
+      </x:c>
+      <x:c r="I260" s="26" t="n">
+        <x:f>ROUND(D260-E260,1)</x:f>
+        <x:v>32200</x:v>
+      </x:c>
+      <x:c r="J260" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K260" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B261" s="22" t="str">
+        <x:v>3月30日-4月3日</x:v>
+      </x:c>
+      <x:c r="C261" s="23" t="n">
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="D261" s="23" t="n">
+        <x:v>175000</x:v>
+      </x:c>
+      <x:c r="E261" s="23" t="n">
+        <x:v>154560</x:v>
+      </x:c>
+      <x:c r="F261" s="23" t="n">
+        <x:v>157860</x:v>
+      </x:c>
+      <x:c r="G261" s="28" t="n">
+        <x:f>ROUND(F261-F260,1)</x:f>
+        <x:v>-11540</x:v>
+      </x:c>
+      <x:c r="H261" s="24" t="n">
+        <x:f>IFERROR(F261/F260-1,"")</x:f>
+        <x:v>-0.06812278630460444</x:v>
+      </x:c>
+      <x:c r="I261" s="26" t="n">
+        <x:f>ROUND(D261-E261,1)</x:f>
+        <x:v>20440</x:v>
+      </x:c>
+      <x:c r="J261" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K261" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B262" s="22" t="str">
+        <x:v>4月7日-4月10日</x:v>
+      </x:c>
+      <x:c r="C262" s="23" t="n">
+        <x:v>158440</x:v>
+      </x:c>
+      <x:c r="D262" s="23" t="n">
+        <x:v>165500</x:v>
+      </x:c>
+      <x:c r="E262" s="23" t="n">
+        <x:v>152500</x:v>
+      </x:c>
+      <x:c r="F262" s="23" t="n">
+        <x:v>157600</x:v>
+      </x:c>
+      <x:c r="G262" s="28" t="n">
+        <x:f>ROUND(F262-F261,1)</x:f>
+        <x:v>-260</x:v>
+      </x:c>
+      <x:c r="H262" s="24" t="n">
+        <x:f>IFERROR(F262/F261-1,"")</x:f>
+        <x:v>-0.0016470290130495835</x:v>
+      </x:c>
+      <x:c r="I262" s="26" t="n">
+        <x:f>ROUND(D262-E262,1)</x:f>
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="J262" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K262" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B263" s="22" t="str">
+        <x:v>4月13日-4月17日</x:v>
+      </x:c>
+      <x:c r="C263" s="23" t="n">
+        <x:v>155020</x:v>
+      </x:c>
+      <x:c r="D263" s="23" t="n">
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="E263" s="23" t="n">
+        <x:v>154780</x:v>
+      </x:c>
+      <x:c r="F263" s="23" t="n">
+        <x:v>177560</x:v>
+      </x:c>
+      <x:c r="G263" s="28" t="n">
+        <x:f>ROUND(F263-F262,1)</x:f>
+        <x:v>19960</x:v>
+      </x:c>
+      <x:c r="H263" s="24" t="n">
+        <x:f>IFERROR(F263/F262-1,"")</x:f>
+        <x:v>0.1266497461928935</x:v>
+      </x:c>
+      <x:c r="I263" s="26" t="n">
+        <x:f>ROUND(D263-E263,1)</x:f>
+        <x:v>23220</x:v>
+      </x:c>
+      <x:c r="J263" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K263" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B264" s="22" t="str">
+        <x:v>4月20日-4月24日</x:v>
+      </x:c>
+      <x:c r="C264" s="23" t="n">
+        <x:v>177000</x:v>
+      </x:c>
+      <x:c r="D264" s="23" t="n">
+        <x:v>181440</x:v>
+      </x:c>
+      <x:c r="E264" s="23" t="n">
+        <x:v>169500</x:v>
+      </x:c>
+      <x:c r="F264" s="23" t="n">
+        <x:v>177900</x:v>
+      </x:c>
+      <x:c r="G264" s="28" t="n">
+        <x:f>ROUND(F264-F263,1)</x:f>
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="H264" s="24" t="n">
+        <x:f>IFERROR(F264/F263-1,"")</x:f>
+        <x:v>0.0019148456859652274</x:v>
+      </x:c>
+      <x:c r="I264" s="26" t="n">
+        <x:f>ROUND(D264-E264,1)</x:f>
+        <x:v>11940</x:v>
+      </x:c>
+      <x:c r="J264" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K264" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B265" s="22" t="str">
+        <x:v>4月27日-4月30日</x:v>
+      </x:c>
+      <x:c r="C265" s="23" t="n">
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="D265" s="23" t="n">
+        <x:v>189500</x:v>
+      </x:c>
+      <x:c r="E265" s="23" t="n">
+        <x:v>173400</x:v>
+      </x:c>
+      <x:c r="F265" s="23" t="n">
+        <x:v>189080</x:v>
+      </x:c>
+      <x:c r="G265" s="28" t="n">
+        <x:f>ROUND(F265-F264,1)</x:f>
+        <x:v>11180</x:v>
+      </x:c>
+      <x:c r="H265" s="24" t="n">
+        <x:f>IFERROR(F265/F264-1,"")</x:f>
+        <x:v>0.06284429454749851</x:v>
+      </x:c>
+      <x:c r="I265" s="26" t="n">
+        <x:f>ROUND(D265-E265,1)</x:f>
+        <x:v>16100</x:v>
+      </x:c>
+      <x:c r="J265" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K265" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B266" s="22" t="str">
+        <x:v>5月6日-5月8日</x:v>
+      </x:c>
+      <x:c r="C266" s="23" t="n">
+        <x:v>191500</x:v>
+      </x:c>
+      <x:c r="D266" s="23" t="n">
+        <x:v>201480</x:v>
+      </x:c>
+      <x:c r="E266" s="23" t="n">
+        <x:v>191040</x:v>
+      </x:c>
+      <x:c r="F266" s="23" t="n">
+        <x:v>196560</x:v>
+      </x:c>
+      <x:c r="G266" s="28" t="n">
+        <x:f>ROUND(F266-F265,1)</x:f>
+        <x:v>7480</x:v>
+      </x:c>
+      <x:c r="H266" s="24" t="n">
+        <x:f>IFERROR(F266/F265-1,"")</x:f>
+        <x:v>0.039559974613920135</x:v>
+      </x:c>
+      <x:c r="I266" s="26" t="n">
+        <x:f>ROUND(D266-E266,1)</x:f>
+        <x:v>10440</x:v>
+      </x:c>
+      <x:c r="J266" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K266" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B267" s="22" t="str">
+        <x:v>5月11日-5月15日</x:v>
+      </x:c>
+      <x:c r="C267" s="23" t="n">
+        <x:v>196560</x:v>
+      </x:c>
+      <x:c r="D267" s="23" t="n">
+        <x:v>209880</x:v>
+      </x:c>
+      <x:c r="E267" s="23" t="n">
+        <x:v>186800</x:v>
+      </x:c>
+      <x:c r="F267" s="23" t="n">
+        <x:v>188800</x:v>
+      </x:c>
+      <x:c r="G267" s="28" t="n">
+        <x:f>ROUND(F267-F266,1)</x:f>
+        <x:v>-7760</x:v>
+      </x:c>
+      <x:c r="H267" s="24" t="n">
+        <x:f>IFERROR(F267/F266-1,"")</x:f>
+        <x:v>-0.039479039479039524</x:v>
+      </x:c>
+      <x:c r="I267" s="26" t="n">
+        <x:f>ROUND(D267-E267,1)</x:f>
+        <x:v>23080</x:v>
+      </x:c>
+      <x:c r="J267" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K267" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B268" s="22" t="str">
+        <x:v>5月18日-5月22日</x:v>
+      </x:c>
+      <x:c r="C268" s="23" t="n">
+        <x:v>189000</x:v>
+      </x:c>
+      <x:c r="D268" s="23" t="n">
+        <x:v>193900</x:v>
+      </x:c>
+      <x:c r="E268" s="23" t="n">
+        <x:v>175200</x:v>
+      </x:c>
+      <x:c r="F268" s="23" t="n">
+        <x:v>184460</x:v>
+      </x:c>
+      <x:c r="G268" s="28" t="n">
+        <x:f>ROUND(F268-F267,1)</x:f>
+        <x:v>-4340</x:v>
+      </x:c>
+      <x:c r="H268" s="24" t="n">
+        <x:f>IFERROR(F268/F267-1,"")</x:f>
+        <x:v>-0.022987288135593253</x:v>
+      </x:c>
+      <x:c r="I268" s="26" t="n">
+        <x:f>ROUND(D268-E268,1)</x:f>
+        <x:v>18700</x:v>
+      </x:c>
+      <x:c r="J268" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K268" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B269" s="22" t="str">
+        <x:v>5月25日-5月29日</x:v>
+      </x:c>
+      <x:c r="C269" s="23" t="n">
+        <x:v>185500</x:v>
+      </x:c>
+      <x:c r="D269" s="23" t="n">
+        <x:v>187900</x:v>
+      </x:c>
+      <x:c r="E269" s="23" t="n">
+        <x:v>172080</x:v>
+      </x:c>
+      <x:c r="F269" s="23" t="n">
+        <x:v>179740</x:v>
+      </x:c>
+      <x:c r="G269" s="28" t="n">
+        <x:f>ROUND(F269-F268,1)</x:f>
+        <x:v>-4720</x:v>
+      </x:c>
+      <x:c r="H269" s="24" t="n">
+        <x:f>IFERROR(F269/F268-1,"")</x:f>
+        <x:v>-0.02558820340453216</x:v>
+      </x:c>
+      <x:c r="I269" s="26" t="n">
+        <x:f>ROUND(D269-E269,1)</x:f>
+        <x:v>15820</x:v>
+      </x:c>
+      <x:c r="J269" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K269" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B270" s="22" t="str">
+        <x:v>6月1日-6月5日</x:v>
+      </x:c>
+      <x:c r="C270" s="23" t="n">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="D270" s="23" t="n">
+        <x:v>182100</x:v>
+      </x:c>
+      <x:c r="E270" s="23" t="n">
+        <x:v>157180</x:v>
+      </x:c>
+      <x:c r="F270" s="23" t="n">
+        <x:v>164360</x:v>
+      </x:c>
+      <x:c r="G270" s="28" t="n">
+        <x:f>ROUND(F270-F269,1)</x:f>
+        <x:v>-15380</x:v>
+      </x:c>
+      <x:c r="H270" s="24" t="n">
+        <x:f>IFERROR(F270/F269-1,"")</x:f>
+        <x:v>-0.08556804272838547</x:v>
+      </x:c>
+      <x:c r="I270" s="26" t="n">
+        <x:f>ROUND(D270-E270,1)</x:f>
+        <x:v>24920</x:v>
+      </x:c>
+      <x:c r="J270" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K270" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="22" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B271" s="22" t="str">
+        <x:v>6月8日-6月12日</x:v>
+      </x:c>
+      <x:c r="C271" s="23" t="n">
+        <x:v>161500</x:v>
+      </x:c>
+      <x:c r="D271" s="23" t="n">
+        <x:v>178740</x:v>
+      </x:c>
+      <x:c r="E271" s="23" t="n">
+        <x:v>160260</x:v>
+      </x:c>
+      <x:c r="F271" s="23" t="n">
+        <x:v>175300</x:v>
+      </x:c>
+      <x:c r="G271" s="28" t="n">
+        <x:f>ROUND(F271-F270,1)</x:f>
+        <x:v>10940</x:v>
+      </x:c>
+      <x:c r="H271" s="24" t="n">
+        <x:f>IFERROR(F271/F270-1,"")</x:f>
+        <x:v>0.06656120710635194</x:v>
+      </x:c>
+      <x:c r="I271" s="26" t="n">
+        <x:f>ROUND(D271-E271,1)</x:f>
+        <x:v>18480</x:v>
+      </x:c>
+      <x:c r="J271" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K271" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="22" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B272" s="22" t="str">
+        <x:v>6月15日-6月18日</x:v>
+      </x:c>
+      <x:c r="C272" s="23" t="n">
+        <x:v>177600</x:v>
+      </x:c>
+      <x:c r="D272" s="23" t="n">
+        <x:v>177920</x:v>
+      </x:c>
+      <x:c r="E272" s="23" t="n">
+        <x:v>160100</x:v>
+      </x:c>
+      <x:c r="F272" s="23" t="n">
+        <x:v>160500</x:v>
+      </x:c>
+      <x:c r="G272" s="28" t="n">
+        <x:f>ROUND(F272-F271,1)</x:f>
+        <x:v>-14800</x:v>
+      </x:c>
+      <x:c r="H272" s="24" t="n">
+        <x:f>IFERROR(F272/F271-1,"")</x:f>
+        <x:v>-0.08442669709070161</x:v>
+      </x:c>
+      <x:c r="I272" s="26" t="n">
+        <x:f>ROUND(D272-E272,1)</x:f>
+        <x:v>17820</x:v>
+      </x:c>
+      <x:c r="J272" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K272" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="22" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B273" s="22" t="str">
+        <x:v>6月22日-6月26日</x:v>
+      </x:c>
+      <x:c r="C273" s="23" t="n">
+        <x:v>157220</x:v>
+      </x:c>
+      <x:c r="D273" s="23" t="n">
+        <x:v>163940</x:v>
+      </x:c>
+      <x:c r="E273" s="23" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="F273" s="23" t="n">
+        <x:v>150220</x:v>
+      </x:c>
+      <x:c r="G273" s="28" t="n">
+        <x:f>ROUND(F273-F272,1)</x:f>
+        <x:v>-10280</x:v>
+      </x:c>
+      <x:c r="H273" s="24" t="n">
+        <x:f>IFERROR(F273/F272-1,"")</x:f>
+        <x:v>-0.06404984423676008</x:v>
+      </x:c>
+      <x:c r="I273" s="26" t="n">
+        <x:f>ROUND(D273-E273,1)</x:f>
+        <x:v>18940</x:v>
+      </x:c>
+      <x:c r="J273" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K273" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="22" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B274" s="22" t="str">
+        <x:v>6月29日-7月3日</x:v>
+      </x:c>
+      <x:c r="C274" s="23" t="n">
+        <x:v>148000</x:v>
+      </x:c>
+      <x:c r="D274" s="23" t="n">
+        <x:v>172000</x:v>
+      </x:c>
+      <x:c r="E274" s="23" t="n">
+        <x:v>145300</x:v>
+      </x:c>
+      <x:c r="F274" s="23" t="n">
+        <x:v>168780</x:v>
+      </x:c>
+      <x:c r="G274" s="28" t="n">
+        <x:f>ROUND(F274-F273,1)</x:f>
+        <x:v>18560</x:v>
+      </x:c>
+      <x:c r="H274" s="24" t="n">
+        <x:f>IFERROR(F274/F273-1,"")</x:f>
+        <x:v>0.12355212355212353</x:v>
+      </x:c>
+      <x:c r="I274" s="26" t="n">
+        <x:f>ROUND(D274-E274,1)</x:f>
+        <x:v>26700</x:v>
+      </x:c>
+      <x:c r="J274" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K274" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="22" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B275" s="22" t="str">
+        <x:v>7月6日-7月10日</x:v>
+      </x:c>
+      <x:c r="C275" s="23" t="n">
+        <x:v>166980</x:v>
+      </x:c>
+      <x:c r="D275" s="23" t="n">
+        <x:v>168720</x:v>
+      </x:c>
+      <x:c r="E275" s="23" t="n">
+        <x:v>150260</x:v>
+      </x:c>
+      <x:c r="F275" s="23" t="n">
+        <x:v>151600</x:v>
+      </x:c>
+      <x:c r="G275" s="28" t="n">
+        <x:f>ROUND(F275-F274,1)</x:f>
+        <x:v>-17180</x:v>
+      </x:c>
+      <x:c r="H275" s="24" t="n">
+        <x:f>IFERROR(F275/F274-1,"")</x:f>
+        <x:v>-0.10178931152980208</x:v>
+      </x:c>
+      <x:c r="I275" s="26" t="n">
+        <x:f>ROUND(D275-E275,1)</x:f>
+        <x:v>18460</x:v>
+      </x:c>
+      <x:c r="J275" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K275" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="22" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B276" s="22" t="str">
+        <x:v>7月13日-7月17日</x:v>
+      </x:c>
+      <x:c r="C276" s="23" t="n">
+        <x:v>150500</x:v>
+      </x:c>
+      <x:c r="D276" s="23" t="n">
+        <x:v>156500</x:v>
+      </x:c>
+      <x:c r="E276" s="23" t="n">
+        <x:v>145860</x:v>
+      </x:c>
+      <x:c r="F276" s="23" t="n">
+        <x:v>150140</x:v>
+      </x:c>
+      <x:c r="G276" s="28" t="n">
+        <x:f>ROUND(F276-F275,1)</x:f>
+        <x:v>-1460</x:v>
+      </x:c>
+      <x:c r="H276" s="24" t="n">
+        <x:f>IFERROR(F276/F275-1,"")</x:f>
+        <x:v>-0.009630606860158264</x:v>
+      </x:c>
+      <x:c r="I276" s="26" t="n">
+        <x:f>ROUND(D276-E276,1)</x:f>
+        <x:v>10640</x:v>
+      </x:c>
+      <x:c r="J276" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K276" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="22" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B277" s="22" t="str">
+        <x:v>7月20日-7月24日</x:v>
+      </x:c>
+      <x:c r="C277" s="23" t="n">
+        <x:v>151500</x:v>
+      </x:c>
+      <x:c r="D277" s="23" t="n">
+        <x:v>154800</x:v>
+      </x:c>
+      <x:c r="E277" s="23" t="n">
+        <x:v>136800</x:v>
+      </x:c>
+      <x:c r="F277" s="23" t="n">
+        <x:v>144280</x:v>
+      </x:c>
+      <x:c r="G277" s="28" t="n">
+        <x:f>ROUND(F277-F276,1)</x:f>
+        <x:v>-5860</x:v>
+      </x:c>
+      <x:c r="H277" s="24" t="n">
+        <x:f>IFERROR(F277/F276-1,"")</x:f>
+        <x:v>-0.03903023844411879</x:v>
+      </x:c>
+      <x:c r="I277" s="26" t="n">
+        <x:f>ROUND(D277-E277,1)</x:f>
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J277" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K277" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="22" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B278" s="22" t="str">
+        <x:v>7月27日-7月31日</x:v>
+      </x:c>
+      <x:c r="C278" s="23" t="n">
+        <x:v>145780</x:v>
+      </x:c>
+      <x:c r="D278" s="23" t="n">
+        <x:v>149400</x:v>
+      </x:c>
+      <x:c r="E278" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="F278" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="G278" s="28" t="n">
+        <x:f>ROUND(F278-F277,1)</x:f>
+        <x:v>-6520</x:v>
+      </x:c>
+      <x:c r="H278" s="24" t="n">
+        <x:f>IFERROR(F278/F277-1,"")</x:f>
+        <x:v>-0.04518990851122817</x:v>
+      </x:c>
+      <x:c r="I278" s="26" t="n">
+        <x:f>ROUND(D278-E278,1)</x:f>
+        <x:v>11640</x:v>
+      </x:c>
+      <x:c r="J278" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K278" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B279" s="22" t="str">
+        <x:v>8月3日-8月5日</x:v>
+      </x:c>
+      <x:c r="C279" s="23" t="n">
+        <x:v>137500</x:v>
+      </x:c>
+      <x:c r="D279" s="23" t="n">
+        <x:v>144300</x:v>
+      </x:c>
+      <x:c r="E279" s="23" t="n">
+        <x:v>135560</x:v>
+      </x:c>
+      <x:c r="F279" s="23" t="n">
+        <x:v>143220</x:v>
+      </x:c>
+      <x:c r="G279" s="28" t="n">
+        <x:f>ROUND(F279-F278,1)</x:f>
+        <x:v>5460</x:v>
+      </x:c>
+      <x:c r="H279" s="24" t="n">
+        <x:f>IFERROR(F279/F278-1,"")</x:f>
+        <x:v>0.03963414634146334</x:v>
+      </x:c>
+      <x:c r="I279" s="26" t="n">
+        <x:f>ROUND(D279-E279,1)</x:f>
+        <x:v>8740</x:v>
+      </x:c>
+      <x:c r="J279" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K279" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B280" s="30" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C280" s="30"/>
+      <x:c r="D280" s="30"/>
+      <x:c r="E280" s="30"/>
+      <x:c r="F280" s="30"/>
+      <x:c r="G280" s="30"/>
+      <x:c r="H280" s="30"/>
+      <x:c r="I280" s="32" t="n">
+        <x:f>ROUND(SUM(I250:I279),1)</x:f>
+        <x:v>652360</x:v>
+      </x:c>
+      <x:c r="J280" s="30"/>
+      <x:c r="K280" s="30"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B281" s="30"/>
+      <x:c r="C281" s="30"/>
+      <x:c r="D281" s="30"/>
+      <x:c r="E281" s="30"/>
+      <x:c r="F281" s="30"/>
+      <x:c r="G281" s="30"/>
+      <x:c r="H281" s="30"/>
+      <x:c r="I281" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I250:I279),0),1)</x:f>
+        <x:v>21745.3</x:v>
+      </x:c>
+      <x:c r="J281" s="30"/>
+      <x:c r="K281" s="30"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -9422,6 +16542,7 @@
     <x:mergeCell ref="A143:K143"/>
     <x:mergeCell ref="A178:K178"/>
     <x:mergeCell ref="A213:K213"/>
+    <x:mergeCell ref="A248:K248"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R94808877259a4d70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1191204875974f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rccedb6b844b04239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5b279d49d7ce4fa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re9fc810039e24de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2f8a12e6b9434460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re6a9ac296ec94ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R748f7826e3af47ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf251281633ca41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R68df033dab174b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R83c190e6470841eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re4a525c098294532"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4d819a048ad14bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf75147ecb0d34a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rde1d8d72e58348f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re3696817747649a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R72bf0f643cf8455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3c52e7e8f0c34e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R16549c73ebaa4906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Ra19383398438402e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7523.5</x:v>
+        <x:v>7564.69</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7253.22</x:v>
+        <x:v>7434.49</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>270.3</x:v>
+        <x:v>130.2</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>25666.1</x:v>
+        <x:v>25796.3</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.7</x:v>
+        <x:v>180.4</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7845.39</x:v>
+        <x:v>7868.85</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7567.96</x:v>
+        <x:v>7722.57</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>277.4</x:v>
+        <x:v>146.3</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>25870.2</x:v>
+        <x:v>26016.5</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>182.2</x:v>
+        <x:v>181.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3884.4</x:v>
+        <x:v>3902.05</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3815.12</x:v>
+        <x:v>3864.27</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>69.3</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7107</x:v>
+        <x:v>7144.8</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>50</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7775.6</x:v>
+        <x:v>7768</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7501</x:v>
+        <x:v>7640</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>274.6</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>28758.4</x:v>
+        <x:v>28886.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>202.5</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>144300</x:v>
+        <x:v>143860</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>138320</x:v>
+        <x:v>139240</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>5980</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1266600</x:v>
+        <x:v>1271220</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8919.7</x:v>
+        <x:v>8889.7</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6681,30 +6681,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>15280</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>143200</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>143860</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>139240</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>141460</x:v>
+      </x:c>
+      <x:c r="H182" s="28" t="n">
+        <x:v>-1760</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>-0.01228878648233489</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>4620</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -6712,11 +6730,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>5093.3</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>19900</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>4975</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7907,37 +7943,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
         <x:v>7055.27</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7523.5</x:v>
+        <x:v>7564.69</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
         <x:v>7042.89</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7493.05</x:v>
+        <x:v>7530.43</x:v>
       </x:c>
       <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
-        <x:v>417.5</x:v>
+        <x:v>454.9</x:v>
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.0590120005483703</x:v>
+        <x:v>0.06429501194966858</x:v>
       </x:c>
       <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
-        <x:v>480.6</x:v>
+        <x:v>521.8</x:v>
       </x:c>
       <x:c r="J34" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K34" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -7955,7 +7991,7 @@
       <x:c r="H35" s="30"/>
       <x:c r="I35" s="32" t="n">
         <x:f>ROUND(SUM(I5:I34),1)</x:f>
-        <x:v>12549.8</x:v>
+        <x:v>12591</x:v>
       </x:c>
       <x:c r="J35" s="30"/>
       <x:c r="K35" s="30"/>
@@ -7973,7 +8009,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I34),0),1)</x:f>
-        <x:v>418.3</x:v>
+        <x:v>419.7</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -9129,37 +9165,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C69" s="23" t="n">
         <x:v>7457.12</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7845.39</x:v>
+        <x:v>7868.85</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
         <x:v>7397.94</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7809.21</x:v>
+        <x:v>7829.36</x:v>
       </x:c>
       <x:c r="G69" s="28" t="n">
         <x:f>ROUND(F69-F68,1)</x:f>
-        <x:v>315.2</x:v>
+        <x:v>335.4</x:v>
       </x:c>
       <x:c r="H69" s="24" t="n">
         <x:f>IFERROR(F69/F68-1,"")</x:f>
-        <x:v>0.04206303984926585</x:v>
+        <x:v>0.04475186115807461</x:v>
       </x:c>
       <x:c r="I69" s="26" t="n">
         <x:f>ROUND(D69-E69,1)</x:f>
-        <x:v>447.5</x:v>
+        <x:v>470.9</x:v>
       </x:c>
       <x:c r="J69" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K69" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -9177,7 +9213,7 @@
       <x:c r="H70" s="30"/>
       <x:c r="I70" s="32" t="n">
         <x:f>ROUND(SUM(I40:I69),1)</x:f>
-        <x:v>12742.6</x:v>
+        <x:v>12766</x:v>
       </x:c>
       <x:c r="J70" s="30"/>
       <x:c r="K70" s="30"/>
@@ -9195,7 +9231,7 @@
       <x:c r="H71" s="30"/>
       <x:c r="I71" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I40:I69),0),1)</x:f>
-        <x:v>424.8</x:v>
+        <x:v>425.5</x:v>
       </x:c>
       <x:c r="J71" s="30"/>
       <x:c r="K71" s="30"/>
@@ -10351,37 +10387,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B104" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C104" s="23" t="n">
         <x:v>3812.61</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>3884.4</x:v>
+        <x:v>3902.05</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
         <x:v>3797.64</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>3878.43</x:v>
+        <x:v>3900.35</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
         <x:f>ROUND(F104-F103,1)</x:f>
-        <x:v>46.2</x:v>
+        <x:v>68.1</x:v>
       </x:c>
       <x:c r="H104" s="24" t="n">
         <x:f>IFERROR(F104/F103-1,"")</x:f>
-        <x:v>0.012047721188019445</x:v>
+        <x:v>0.017767583619065386</x:v>
       </x:c>
       <x:c r="I104" s="26" t="n">
         <x:f>ROUND(D104-E104,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="J104" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K104" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -10399,7 +10435,7 @@
       <x:c r="H105" s="30"/>
       <x:c r="I105" s="32" t="n">
         <x:f>ROUND(SUM(I75:I104),1)</x:f>
-        <x:v>3322.7</x:v>
+        <x:v>3340.3</x:v>
       </x:c>
       <x:c r="J105" s="30"/>
       <x:c r="K105" s="30"/>
@@ -10417,7 +10453,7 @@
       <x:c r="H106" s="30"/>
       <x:c r="I106" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I75:I104),0),1)</x:f>
-        <x:v>110.8</x:v>
+        <x:v>111.3</x:v>
       </x:c>
       <x:c r="J106" s="30"/>
       <x:c r="K106" s="30"/>
@@ -12795,7 +12831,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
         <x:v>7391</x:v>
@@ -12807,15 +12843,15 @@
         <x:v>7335</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>7744.4</x:v>
+        <x:v>7730</x:v>
       </x:c>
       <x:c r="G174" s="28" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>349.4</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>0.047248140635564484</x:v>
+        <x:v>0.045300878972278635</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
@@ -12825,7 +12861,7 @@
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -16461,7 +16497,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>137500</x:v>
@@ -16473,15 +16509,15 @@
         <x:v>135560</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>143220</x:v>
+        <x:v>141460</x:v>
       </x:c>
       <x:c r="G279" s="28" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>5460</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>0.03963414634146334</x:v>
+        <x:v>0.026858304297328717</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
@@ -16491,7 +16527,7 @@
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -22349,30 +22385,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>550.2</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>7440.01</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>7564.69</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>7434.49</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>7530.43</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>37.4</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>0.004988622790452535</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>130.2</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -22380,11 +22434,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>183.4</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>680.4</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>170.1</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -28203,30 +28275,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>574.2</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>7737.59</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>7868.85</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>7722.57</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>7829.36</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>20.1</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>0.0025802866102973</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>146.3</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -28234,11 +28324,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>191.4</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>720.5</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>180.1</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34057,30 +34165,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>131.7</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>3864.27</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>3902.05</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>3864.27</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>3900.35</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>21.9</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>0.005651771464226574</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>37.8</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -34088,11 +34214,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>43.9</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>169.5</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>42.4</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -45765,30 +45909,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>585.8</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>7680</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>7768</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>7640</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>7730</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>-14.4</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>-0.0018594080884251074</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -45796,11 +45958,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>195.3</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>713.8</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>178.5</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R83c190e6470841eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re4a525c098294532"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4d819a048ad14bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf75147ecb0d34a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rde1d8d72e58348f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re3696817747649a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R72bf0f643cf8455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3c52e7e8f0c34e10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R16549c73ebaa4906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Ra19383398438402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc7e23ba750954837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9a97f7680b204352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4657322fd0564082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R9339521d9ccb4a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R50838a75b6df423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R67340aeed0454059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rdc3280fe143f4aee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R73695da6f41641b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3f5ee8413a79492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R51a2ca1e926142d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7466</x:v>
+        <x:v>7477</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7201.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>264.4</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>27392.4</x:v>
+        <x:v>27517.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>192.9</x:v>
+        <x:v>192.4</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4641.2</x:v>
+        <x:v>4626</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4520</x:v>
+        <x:v>4570.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>121.2</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10781.2</x:v>
+        <x:v>10836.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.9</x:v>
+        <x:v>75.8</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2907.6</x:v>
+        <x:v>2897.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2855</x:v>
+        <x:v>2879.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>52.6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6000</x:v>
+        <x:v>6018</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.3</x:v>
+        <x:v>42.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -11609,37 +11609,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B139" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C139" s="23" t="n">
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D139" s="23" t="n">
-        <x:v>7466</x:v>
+        <x:v>7477</x:v>
       </x:c>
       <x:c r="E139" s="23" t="n">
         <x:v>6976</x:v>
       </x:c>
       <x:c r="F139" s="23" t="n">
-        <x:v>7433.8</x:v>
+        <x:v>7451.8</x:v>
       </x:c>
       <x:c r="G139" s="28" t="n">
         <x:f>ROUND(F139-F138,1)</x:f>
-        <x:v>446</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="H139" s="24" t="n">
         <x:f>IFERROR(F139/F138-1,"")</x:f>
-        <x:v>0.06382552448553191</x:v>
+        <x:v>0.06640144251409597</x:v>
       </x:c>
       <x:c r="I139" s="26" t="n">
         <x:f>ROUND(D139-E139,1)</x:f>
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="J139" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K139" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -11657,7 +11657,7 @@
       <x:c r="H140" s="30"/>
       <x:c r="I140" s="32" t="n">
         <x:f>ROUND(SUM(I110:I139),1)</x:f>
-        <x:v>13220</x:v>
+        <x:v>13231</x:v>
       </x:c>
       <x:c r="J140" s="30"/>
       <x:c r="K140" s="30"/>
@@ -11675,7 +11675,7 @@
       <x:c r="H141" s="30"/>
       <x:c r="I141" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I110:I139),0),1)</x:f>
-        <x:v>440.7</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="J141" s="30"/>
       <x:c r="K141" s="30"/>
@@ -14053,7 +14053,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>4526.4</x:v>
@@ -14065,15 +14065,15 @@
         <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4621</x:v>
+        <x:v>4612</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>0.018289995592772224</x:v>
+        <x:v>0.016306743058616124</x:v>
       </x:c>
       <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
@@ -14083,7 +14083,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -15275,7 +15275,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>8月3日-8月5日</x:v>
+        <x:v>8月3日-8月6日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
         <x:v>2882.4</x:v>
@@ -15287,15 +15287,15 @@
         <x:v>2845.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2893.4</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>1.6</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>0.00055328860917081</x:v>
+        <x:v>0.0018673490559510952</x:v>
       </x:c>
       <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
@@ -15305,7 +15305,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -40055,30 +40055,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>564.6</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>7377</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>7477</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>7352</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>7451.8</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>0.002421372649250797</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -40086,11 +40104,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>188.2</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>689.6</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>172.4</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -51799,30 +51835,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>221.6</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>4585.2</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>4626</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>4570.8</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>4612</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>-9</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>-0.001947630383034027</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -51830,11 +51884,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>73.9</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>276.8</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>69.2</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -57653,30 +57725,48 @@
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B182" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="30"/>
-      <x:c r="D182" s="30"/>
-      <x:c r="E182" s="30"/>
-      <x:c r="F182" s="30"/>
-      <x:c r="G182" s="30"/>
-      <x:c r="H182" s="30"/>
-      <x:c r="I182" s="30"/>
-      <x:c r="J182" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J181),1)</x:f>
-        <x:v>122.2</x:v>
-      </x:c>
-      <x:c r="K182" s="30"/>
+      <x:c r="A182" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B182" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C182" s="22" t="str">
+        <x:v>8月6日</x:v>
+      </x:c>
+      <x:c r="D182" s="23" t="n">
+        <x:v>2885</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
+        <x:v>2897.8</x:v>
+      </x:c>
+      <x:c r="F182" s="23" t="n">
+        <x:v>2879.8</x:v>
+      </x:c>
+      <x:c r="G182" s="23" t="n">
+        <x:v>2897.2</x:v>
+      </x:c>
+      <x:c r="H182" s="23" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="I182" s="24" t="n">
+        <x:v>0.001313333794152216</x:v>
+      </x:c>
+      <x:c r="J182" s="23" t="n">
+        <x:f>ROUND(E182-F182,1)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K182" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B183" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B183" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C183" s="30"/>
       <x:c r="D183" s="30"/>
       <x:c r="E183" s="30"/>
@@ -57684,11 +57774,29 @@
       <x:c r="G183" s="30"/>
       <x:c r="H183" s="30"/>
       <x:c r="I183" s="30"/>
-      <x:c r="J183" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J181),0),1)</x:f>
-        <x:v>40.7</x:v>
+      <x:c r="J183" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J182),1)</x:f>
+        <x:v>140.2</x:v>
       </x:c>
       <x:c r="K183" s="30"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B184" s="30"/>
+      <x:c r="C184" s="30"/>
+      <x:c r="D184" s="30"/>
+      <x:c r="E184" s="30"/>
+      <x:c r="F184" s="30"/>
+      <x:c r="G184" s="30"/>
+      <x:c r="H184" s="30"/>
+      <x:c r="I184" s="30"/>
+      <x:c r="J184" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
+        <x:v>35.1</x:v>
+      </x:c>
+      <x:c r="K184" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc7e23ba750954837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9a97f7680b204352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4657322fd0564082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R9339521d9ccb4a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R50838a75b6df423c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R67340aeed0454059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rdc3280fe143f4aee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R73695da6f41641b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3f5ee8413a79492b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R51a2ca1e926142d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra026991cf01a4fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R10c728fee76140dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb5b7606d3dd5498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R43333f68ca694be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8d618d8f7e004627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R9fb3fc1cb8e24e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8f1c9d9be81f4158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R91749dfd3d984c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R69ee2570e9be44ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rbcd2b0c0dd9f4af0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7564.69</x:v>
+        <x:v>7685.57</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7434.49</x:v>
+        <x:v>7448.46</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>130.2</x:v>
+        <x:v>237.1</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>25796.3</x:v>
+        <x:v>26033.4</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.4</x:v>
+        <x:v>180.8</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7868.85</x:v>
+        <x:v>7983.17</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7722.57</x:v>
+        <x:v>7763.53</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>146.3</x:v>
+        <x:v>219.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>26016.5</x:v>
+        <x:v>26236.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>181.9</x:v>
+        <x:v>182.2</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3902.05</x:v>
+        <x:v>3940.93</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3864.27</x:v>
+        <x:v>3885.62</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>37.8</x:v>
+        <x:v>55.3</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7144.8</x:v>
+        <x:v>7200.1</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7477</x:v>
+        <x:v>7594.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7352</x:v>
+        <x:v>7369</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>125</x:v>
+        <x:v>225.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>27517.4</x:v>
+        <x:v>27742.6</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>192.4</x:v>
+        <x:v>192.7</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2897.8</x:v>
+        <x:v>2930.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2879.8</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>18</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6018</x:v>
+        <x:v>6064.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>42.1</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>143860</x:v>
+        <x:v>144800</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139240</x:v>
+        <x:v>139600</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4620</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1271220</x:v>
+        <x:v>1276420</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8889.7</x:v>
+        <x:v>8864</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6717,30 +6717,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>19900</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>142920</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>144800</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>139600</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="H183" s="28" t="n">
+        <x:v>-1460</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>-0.01032093878128093</x:v>
+      </x:c>
+      <x:c r="J183" s="23" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>5200</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -6748,11 +6766,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>4975</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>25100</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>5020</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7943,37 +7979,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
         <x:v>7055.27</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7564.69</x:v>
+        <x:v>7685.57</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
         <x:v>7042.89</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7530.43</x:v>
+        <x:v>7679.53</x:v>
       </x:c>
       <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
-        <x:v>454.9</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.06429501194966858</x:v>
+        <x:v>0.08536769787619547</x:v>
       </x:c>
       <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
-        <x:v>521.8</x:v>
+        <x:v>642.7</x:v>
       </x:c>
       <x:c r="J34" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K34" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -7991,7 +8027,7 @@
       <x:c r="H35" s="30"/>
       <x:c r="I35" s="32" t="n">
         <x:f>ROUND(SUM(I5:I34),1)</x:f>
-        <x:v>12591</x:v>
+        <x:v>12711.9</x:v>
       </x:c>
       <x:c r="J35" s="30"/>
       <x:c r="K35" s="30"/>
@@ -8009,7 +8045,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I34),0),1)</x:f>
-        <x:v>419.7</x:v>
+        <x:v>423.7</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -9165,37 +9201,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C69" s="23" t="n">
         <x:v>7457.12</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7868.85</x:v>
+        <x:v>7983.17</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
         <x:v>7397.94</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7829.36</x:v>
+        <x:v>7980.12</x:v>
       </x:c>
       <x:c r="G69" s="28" t="n">
         <x:f>ROUND(F69-F68,1)</x:f>
-        <x:v>335.4</x:v>
+        <x:v>486.1</x:v>
       </x:c>
       <x:c r="H69" s="24" t="n">
         <x:f>IFERROR(F69/F68-1,"")</x:f>
-        <x:v>0.04475186115807461</x:v>
+        <x:v>0.06486931527797601</x:v>
       </x:c>
       <x:c r="I69" s="26" t="n">
         <x:f>ROUND(D69-E69,1)</x:f>
-        <x:v>470.9</x:v>
+        <x:v>585.2</x:v>
       </x:c>
       <x:c r="J69" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K69" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -9213,7 +9249,7 @@
       <x:c r="H70" s="30"/>
       <x:c r="I70" s="32" t="n">
         <x:f>ROUND(SUM(I40:I69),1)</x:f>
-        <x:v>12766</x:v>
+        <x:v>12880.3</x:v>
       </x:c>
       <x:c r="J70" s="30"/>
       <x:c r="K70" s="30"/>
@@ -9231,7 +9267,7 @@
       <x:c r="H71" s="30"/>
       <x:c r="I71" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I40:I69),0),1)</x:f>
-        <x:v>425.5</x:v>
+        <x:v>429.3</x:v>
       </x:c>
       <x:c r="J71" s="30"/>
       <x:c r="K71" s="30"/>
@@ -10387,37 +10423,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B104" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C104" s="23" t="n">
         <x:v>3812.61</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>3902.05</x:v>
+        <x:v>3940.93</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
         <x:v>3797.64</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>3900.35</x:v>
+        <x:v>3940.04</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
         <x:f>ROUND(F104-F103,1)</x:f>
-        <x:v>68.1</x:v>
+        <x:v>107.8</x:v>
       </x:c>
       <x:c r="H104" s="24" t="n">
         <x:f>IFERROR(F104/F103-1,"")</x:f>
-        <x:v>0.017767583619065386</x:v>
+        <x:v>0.028124396570170074</x:v>
       </x:c>
       <x:c r="I104" s="26" t="n">
         <x:f>ROUND(D104-E104,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>143.3</x:v>
       </x:c>
       <x:c r="J104" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K104" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -10435,7 +10471,7 @@
       <x:c r="H105" s="30"/>
       <x:c r="I105" s="32" t="n">
         <x:f>ROUND(SUM(I75:I104),1)</x:f>
-        <x:v>3340.3</x:v>
+        <x:v>3379.2</x:v>
       </x:c>
       <x:c r="J105" s="30"/>
       <x:c r="K105" s="30"/>
@@ -10453,7 +10489,7 @@
       <x:c r="H106" s="30"/>
       <x:c r="I106" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I75:I104),0),1)</x:f>
-        <x:v>111.3</x:v>
+        <x:v>112.6</x:v>
       </x:c>
       <x:c r="J106" s="30"/>
       <x:c r="K106" s="30"/>
@@ -11609,37 +11645,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B139" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C139" s="23" t="n">
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D139" s="23" t="n">
-        <x:v>7477</x:v>
+        <x:v>7594.2</x:v>
       </x:c>
       <x:c r="E139" s="23" t="n">
         <x:v>6976</x:v>
       </x:c>
       <x:c r="F139" s="23" t="n">
-        <x:v>7451.8</x:v>
+        <x:v>7590.6</x:v>
       </x:c>
       <x:c r="G139" s="28" t="n">
         <x:f>ROUND(F139-F138,1)</x:f>
-        <x:v>464</x:v>
+        <x:v>602.8</x:v>
       </x:c>
       <x:c r="H139" s="24" t="n">
         <x:f>IFERROR(F139/F138-1,"")</x:f>
-        <x:v>0.06640144251409597</x:v>
+        <x:v>0.08626463264546791</x:v>
       </x:c>
       <x:c r="I139" s="26" t="n">
         <x:f>ROUND(D139-E139,1)</x:f>
-        <x:v>501</x:v>
+        <x:v>618.2</x:v>
       </x:c>
       <x:c r="J139" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K139" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -11657,7 +11693,7 @@
       <x:c r="H140" s="30"/>
       <x:c r="I140" s="32" t="n">
         <x:f>ROUND(SUM(I110:I139),1)</x:f>
-        <x:v>13231</x:v>
+        <x:v>13348.2</x:v>
       </x:c>
       <x:c r="J140" s="30"/>
       <x:c r="K140" s="30"/>
@@ -11675,7 +11711,7 @@
       <x:c r="H141" s="30"/>
       <x:c r="I141" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I110:I139),0),1)</x:f>
-        <x:v>441</x:v>
+        <x:v>444.9</x:v>
       </x:c>
       <x:c r="J141" s="30"/>
       <x:c r="K141" s="30"/>
@@ -15275,37 +15311,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
         <x:v>2882.4</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>2907.6</x:v>
+        <x:v>2930.6</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
         <x:v>2845.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>5.4</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>0.0018673490559510952</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>61.8</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -15323,7 +15359,7 @@
       <x:c r="H245" s="30"/>
       <x:c r="I245" s="32" t="n">
         <x:f>ROUND(SUM(I215:I244),1)</x:f>
-        <x:v>2794.6</x:v>
+        <x:v>2817.6</x:v>
       </x:c>
       <x:c r="J245" s="30"/>
       <x:c r="K245" s="30"/>
@@ -15341,7 +15377,7 @@
       <x:c r="H246" s="30"/>
       <x:c r="I246" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I215:I244),0),1)</x:f>
-        <x:v>93.2</x:v>
+        <x:v>93.9</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
@@ -16497,37 +16533,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>137500</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>144300</x:v>
+        <x:v>144800</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
         <x:v>135560</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>141460</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="G279" s="28" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>3700</x:v>
+        <x:v>2240</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>0.026858304297328717</x:v>
+        <x:v>0.016260162601626105</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>8740</x:v>
+        <x:v>9240</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -16545,7 +16581,7 @@
       <x:c r="H280" s="30"/>
       <x:c r="I280" s="32" t="n">
         <x:f>ROUND(SUM(I250:I279),1)</x:f>
-        <x:v>652360</x:v>
+        <x:v>652860</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
@@ -16563,7 +16599,7 @@
       <x:c r="H281" s="30"/>
       <x:c r="I281" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I250:I279),0),1)</x:f>
-        <x:v>21745.3</x:v>
+        <x:v>21762</x:v>
       </x:c>
       <x:c r="J281" s="30"/>
       <x:c r="K281" s="30"/>
@@ -22421,30 +22457,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>680.4</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>7534.24</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>7685.57</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>7448.46</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>7679.53</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>149.1</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.019799666154522333</x:v>
+      </x:c>
+      <x:c r="J183" s="26" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>237.1</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -22452,11 +22506,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>170.1</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>917.5</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>183.5</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -28311,30 +28383,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>720.5</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>7828.79</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>7983.17</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>7763.53</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>7980.12</x:v>
+      </x:c>
+      <x:c r="H183" s="28" t="n">
+        <x:v>150.8</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.019255724605842683</x:v>
+      </x:c>
+      <x:c r="J183" s="26" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>219.6</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -28342,11 +28432,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>180.1</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>940.1</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34201,30 +34309,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>169.5</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>3896.49</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>3940.93</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>3885.62</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>3940.04</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.01017600984527034</x:v>
+      </x:c>
+      <x:c r="J183" s="26" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>55.3</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -34232,11 +34358,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>42.4</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>224.8</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40091,30 +40235,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>689.6</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>7450</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>7594.2</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>7369</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>7590.6</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>138.8</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.018626372151694826</x:v>
+      </x:c>
+      <x:c r="J183" s="26" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>225.2</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -40122,11 +40284,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>172.4</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>914.8</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -57761,30 +57941,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>140.2</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>2892.2</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>32.8</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.011321275714482937</x:v>
+      </x:c>
+      <x:c r="J183" s="23" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>46.6</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -57792,11 +57990,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>35.1</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>186.8</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>37.4</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra026991cf01a4fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R10c728fee76140dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb5b7606d3dd5498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R43333f68ca694be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8d618d8f7e004627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R9fb3fc1cb8e24e02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8f1c9d9be81f4158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R91749dfd3d984c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R69ee2570e9be44ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rbcd2b0c0dd9f4af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R11e584b9468548d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rbeff0f686b4a4ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R98771d6c0df54c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5b23b4b8f3154765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rf69bd5740de6482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Red8fd047933d4f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R26ccc39d707c478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd55a43a76bde47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R98c2bc1146a24e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R6054d48f1f814a0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7768</x:v>
+        <x:v>7882.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7640</x:v>
+        <x:v>7667.4</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>128</x:v>
+        <x:v>215.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>28886.4</x:v>
+        <x:v>29101.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>202</x:v>
+        <x:v>202.1</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4626</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4570.8</x:v>
+        <x:v>4604.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>55.2</x:v>
+        <x:v>51.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10836.4</x:v>
+        <x:v>10888</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.8</x:v>
+        <x:v>75.6</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -12867,37 +12867,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
         <x:v>7391</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>7775.6</x:v>
+        <x:v>7882.6</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
         <x:v>7335</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>7730</x:v>
+        <x:v>7877.8</x:v>
       </x:c>
       <x:c r="G174" s="28" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>335</x:v>
+        <x:v>482.8</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>0.045300878972278635</x:v>
+        <x:v>0.06528735632183902</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>440.6</x:v>
+        <x:v>547.6</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -12915,7 +12915,7 @@
       <x:c r="H175" s="30"/>
       <x:c r="I175" s="32" t="n">
         <x:f>ROUND(SUM(I145:I174),1)</x:f>
-        <x:v>13889.6</x:v>
+        <x:v>13996.6</x:v>
       </x:c>
       <x:c r="J175" s="30"/>
       <x:c r="K175" s="30"/>
@@ -12933,7 +12933,7 @@
       <x:c r="H176" s="30"/>
       <x:c r="I176" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I145:I174),0),1)</x:f>
-        <x:v>463</x:v>
+        <x:v>466.6</x:v>
       </x:c>
       <x:c r="J176" s="30"/>
       <x:c r="K176" s="30"/>
@@ -14089,37 +14089,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>8月3日-8月6日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4641.2</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
         <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4612</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>74</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>0.016306743058616124</x:v>
+        <x:v>0.02371088585279857</x:v>
       </x:c>
       <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>147</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -14137,7 +14137,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I180:I209),1)</x:f>
-        <x:v>4952.2</x:v>
+        <x:v>4967.2</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -14155,7 +14155,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I180:I209),0),1)</x:f>
-        <x:v>165.1</x:v>
+        <x:v>165.6</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -46161,30 +46161,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>713.8</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>7725</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>7882.6</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>7667.4</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>7877.8</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>147.8</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.01912031047865459</x:v>
+      </x:c>
+      <x:c r="J183" s="26" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>215.2</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -46192,11 +46210,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>178.5</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>185.8</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -52051,30 +52087,48 @@
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B183" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="30"/>
-      <x:c r="D183" s="30"/>
-      <x:c r="E183" s="30"/>
-      <x:c r="F183" s="30"/>
-      <x:c r="G183" s="30"/>
-      <x:c r="H183" s="30"/>
-      <x:c r="I183" s="30"/>
-      <x:c r="J183" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J182),1)</x:f>
-        <x:v>276.8</x:v>
-      </x:c>
-      <x:c r="K183" s="30"/>
+      <x:c r="A183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B183" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C183" s="22" t="str">
+        <x:v>8月7日</x:v>
+      </x:c>
+      <x:c r="D183" s="23" t="n">
+        <x:v>4620</x:v>
+      </x:c>
+      <x:c r="E183" s="23" t="n">
+        <x:v>4656.2</x:v>
+      </x:c>
+      <x:c r="F183" s="23" t="n">
+        <x:v>4604.6</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
+        <x:v>4645.6</x:v>
+      </x:c>
+      <x:c r="H183" s="23" t="n">
+        <x:v>33.6</x:v>
+      </x:c>
+      <x:c r="I183" s="24" t="n">
+        <x:v>0.007285342584562038</x:v>
+      </x:c>
+      <x:c r="J183" s="23" t="n">
+        <x:f>ROUND(E183-F183,1)</x:f>
+        <x:v>51.6</x:v>
+      </x:c>
+      <x:c r="K183" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B184" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B184" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C184" s="30"/>
       <x:c r="D184" s="30"/>
       <x:c r="E184" s="30"/>
@@ -52082,11 +52136,29 @@
       <x:c r="G184" s="30"/>
       <x:c r="H184" s="30"/>
       <x:c r="I184" s="30"/>
-      <x:c r="J184" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J182),0),1)</x:f>
-        <x:v>69.2</x:v>
+      <x:c r="J184" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J183),1)</x:f>
+        <x:v>328.4</x:v>
       </x:c>
       <x:c r="K184" s="30"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B185" s="30"/>
+      <x:c r="C185" s="30"/>
+      <x:c r="D185" s="30"/>
+      <x:c r="E185" s="30"/>
+      <x:c r="F185" s="30"/>
+      <x:c r="G185" s="30"/>
+      <x:c r="H185" s="30"/>
+      <x:c r="I185" s="30"/>
+      <x:c r="J185" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
+        <x:v>65.7</x:v>
+      </x:c>
+      <x:c r="K185" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4772307dfd814045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R6d74d64fb8fa4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R18a822a91bf24838"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc48145a8ae024aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rfbd6d7ca6ab841b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R7d6a6c217ddf45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rc5456563b9f3494f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R0d3129bd219641f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R341d29c21df1490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rd7c45a0618f74435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7bdff34cff644087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf553da57e5694f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rf5cf2d6576314cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R2d906c315a624bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7ac75112fa8940b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdf45d599a3c7436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R36617edb23dd47e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R1a0aeacabe9a4137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra82508df8ba74f7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7104df33b7c94321"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7882.6</x:v>
+        <x:v>7918</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7667.4</x:v>
+        <x:v>7795.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>215.2</x:v>
+        <x:v>122.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29101.6</x:v>
+        <x:v>29223.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>202.1</x:v>
+        <x:v>201.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4663</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4604.6</x:v>
+        <x:v>4611</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>51.6</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10888</x:v>
+        <x:v>10940</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.6</x:v>
+        <x:v>75.4</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2884</x:v>
+        <x:v>2927.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>46.6</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6064.6</x:v>
+        <x:v>6086.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42.1</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>144800</x:v>
+        <x:v>146380</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139600</x:v>
+        <x:v>139280</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>5200</x:v>
+        <x:v>7100</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1276420</x:v>
+        <x:v>1283520</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8864</x:v>
+        <x:v>8851.9</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -6753,30 +6753,48 @@
       </x:c>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B184" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C184" s="30"/>
-      <x:c r="D184" s="30"/>
-      <x:c r="E184" s="30"/>
-      <x:c r="F184" s="30"/>
-      <x:c r="G184" s="30"/>
-      <x:c r="H184" s="30"/>
-      <x:c r="I184" s="30"/>
-      <x:c r="J184" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J183),1)</x:f>
-        <x:v>25100</x:v>
-      </x:c>
-      <x:c r="K184" s="30"/>
+      <x:c r="A184" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B184" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C184" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="D184" s="23" t="n">
+        <x:v>140500</x:v>
+      </x:c>
+      <x:c r="E184" s="23" t="n">
+        <x:v>146380</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="n">
+        <x:v>139280</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="n">
+        <x:v>146360</x:v>
+      </x:c>
+      <x:c r="H184" s="28" t="n">
+        <x:v>6360</x:v>
+      </x:c>
+      <x:c r="I184" s="24" t="n">
+        <x:v>0.045428571428571374</x:v>
+      </x:c>
+      <x:c r="J184" s="26" t="n">
+        <x:f>ROUND(E184-F184,1)</x:f>
+        <x:v>7100</x:v>
+      </x:c>
+      <x:c r="K184" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B185" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B185" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C185" s="30"/>
       <x:c r="D185" s="30"/>
       <x:c r="E185" s="30"/>
@@ -6784,11 +6802,29 @@
       <x:c r="G185" s="30"/>
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="30"/>
-      <x:c r="J185" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
-        <x:v>5020</x:v>
+      <x:c r="J185" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J184),1)</x:f>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="K185" s="30"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B186" s="30"/>
+      <x:c r="C186" s="30"/>
+      <x:c r="D186" s="30"/>
+      <x:c r="E186" s="30"/>
+      <x:c r="F186" s="30"/>
+      <x:c r="G186" s="30"/>
+      <x:c r="H186" s="30"/>
+      <x:c r="I186" s="30"/>
+      <x:c r="J186" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
+        <x:v>5366.7</x:v>
+      </x:c>
+      <x:c r="K186" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13053,155 +13089,155 @@
       </x:c>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B179" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C179" s="30"/>
-      <x:c r="D179" s="30"/>
-      <x:c r="E179" s="30"/>
-      <x:c r="F179" s="30"/>
-      <x:c r="G179" s="30"/>
-      <x:c r="H179" s="30"/>
-      <x:c r="I179" s="32" t="n">
-        <x:f>ROUND(SUM(I149:I178),1)</x:f>
-        <x:v>13996.6</x:v>
-      </x:c>
-      <x:c r="J179" s="30"/>
-      <x:c r="K179" s="30"/>
+      <x:c r="A179" s="22" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B179" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="C179" s="23" t="n">
+        <x:v>7888</x:v>
+      </x:c>
+      <x:c r="D179" s="23" t="n">
+        <x:v>7918</x:v>
+      </x:c>
+      <x:c r="E179" s="23" t="n">
+        <x:v>7795.8</x:v>
+      </x:c>
+      <x:c r="F179" s="23" t="n">
+        <x:v>7881.4</x:v>
+      </x:c>
+      <x:c r="G179" s="23" t="n">
+        <x:f>ROUND(F179-F178,1)</x:f>
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="H179" s="24" t="n">
+        <x:f>IFERROR(F179/F178-1,"")</x:f>
+        <x:v>0.0004569803752316748</x:v>
+      </x:c>
+      <x:c r="I179" s="23" t="n">
+        <x:f>ROUND(D179-E179,1)</x:f>
+        <x:v>122.2</x:v>
+      </x:c>
+      <x:c r="J179" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K179" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B180" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B180" s="30" t="n">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="C180" s="30"/>
       <x:c r="D180" s="30"/>
       <x:c r="E180" s="30"/>
       <x:c r="F180" s="30"/>
       <x:c r="G180" s="30"/>
       <x:c r="H180" s="30"/>
-      <x:c r="I180" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I149:I178),0),1)</x:f>
-        <x:v>466.6</x:v>
+      <x:c r="I180" s="32" t="n">
+        <x:f>ROUND(SUM(I149:I179),1)</x:f>
+        <x:v>14118.8</x:v>
       </x:c>
       <x:c r="J180" s="30"/>
       <x:c r="K180" s="30"/>
     </x:row>
-    <x:row r="182">
-      <x:c r="A182" s="17" t="str">
+    <x:row r="181">
+      <x:c r="A181" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B181" s="30"/>
+      <x:c r="C181" s="30"/>
+      <x:c r="D181" s="30"/>
+      <x:c r="E181" s="30"/>
+      <x:c r="F181" s="30"/>
+      <x:c r="G181" s="30"/>
+      <x:c r="H181" s="30"/>
+      <x:c r="I181" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I149:I179),0),1)</x:f>
+        <x:v>455.4</x:v>
+      </x:c>
+      <x:c r="J181" s="30"/>
+      <x:c r="K181" s="30"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B182" s="17"/>
-      <x:c r="C182" s="17"/>
-      <x:c r="D182" s="17"/>
-      <x:c r="E182" s="17"/>
-      <x:c r="F182" s="17"/>
-      <x:c r="G182" s="17"/>
-      <x:c r="H182" s="17"/>
-      <x:c r="I182" s="17"/>
-      <x:c r="J182" s="17"/>
-      <x:c r="K182" s="17"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="20" t="str">
+      <x:c r="B183" s="17"/>
+      <x:c r="C183" s="17"/>
+      <x:c r="D183" s="17"/>
+      <x:c r="E183" s="17"/>
+      <x:c r="F183" s="17"/>
+      <x:c r="G183" s="17"/>
+      <x:c r="H183" s="17"/>
+      <x:c r="I183" s="17"/>
+      <x:c r="J183" s="17"/>
+      <x:c r="K183" s="17"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B183" s="20" t="str">
+      <x:c r="B184" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C183" s="20" t="str">
+      <x:c r="C184" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D183" s="20" t="str">
+      <x:c r="D184" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E183" s="20" t="str">
+      <x:c r="E184" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F183" s="20" t="str">
+      <x:c r="F184" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G183" s="20" t="str">
+      <x:c r="G184" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H183" s="20" t="str">
+      <x:c r="H184" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I183" s="20" t="str">
+      <x:c r="I184" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J183" s="20" t="str">
+      <x:c r="J184" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K183" s="20" t="str">
+      <x:c r="K184" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B184" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C184" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D184" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E184" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F184" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G184" s="23"/>
-      <x:c r="H184" s="24"/>
-      <x:c r="I184" s="26" t="n">
-        <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J184" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K184" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B185" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C185" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G185" s="23" t="n">
-        <x:f>ROUND(F185-F184,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H185" s="24" t="n">
-        <x:f>IFERROR(F185/F184-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G185" s="23"/>
+      <x:c r="H185" s="24"/>
       <x:c r="I185" s="26" t="n">
         <x:f>ROUND(D185-E185,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J185" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13212,34 +13248,34 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B186" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C186" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G186" s="23" t="n">
         <x:f>ROUND(F186-F185,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H186" s="24" t="n">
         <x:f>IFERROR(F186/F185-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I186" s="26" t="n">
         <x:f>ROUND(D186-E186,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J186" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13250,34 +13286,34 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B187" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C187" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
         <x:f>ROUND(F187-F186,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H187" s="24" t="n">
         <x:f>IFERROR(F187/F186-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I187" s="26" t="n">
         <x:f>ROUND(D187-E187,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J187" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13288,34 +13324,34 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B188" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C188" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G188" s="23" t="n">
         <x:f>ROUND(F188-F187,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H188" s="24" t="n">
         <x:f>IFERROR(F188/F187-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I188" s="26" t="n">
         <x:f>ROUND(D188-E188,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J188" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13326,34 +13362,34 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B189" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C189" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G189" s="23" t="n">
         <x:f>ROUND(F189-F188,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H189" s="24" t="n">
         <x:f>IFERROR(F189/F188-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I189" s="26" t="n">
         <x:f>ROUND(D189-E189,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J189" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13364,110 +13400,110 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B190" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C190" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G190" s="23" t="n">
         <x:f>ROUND(F190-F189,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H190" s="24" t="n">
         <x:f>IFERROR(F190/F189-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I190" s="26" t="n">
         <x:f>ROUND(D190-E190,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J190" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K190" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B191" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C191" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G191" s="23" t="n">
         <x:f>ROUND(F191-F190,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H191" s="24" t="n">
         <x:f>IFERROR(F191/F190-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I191" s="26" t="n">
         <x:f>ROUND(D191-E191,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J191" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K191" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B192" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C192" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G192" s="23" t="n">
         <x:f>ROUND(F192-F191,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H192" s="24" t="n">
         <x:f>IFERROR(F192/F191-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I192" s="26" t="n">
         <x:f>ROUND(D192-E192,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J192" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13478,34 +13514,34 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B193" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C193" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D193" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E193" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F193" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G193" s="23" t="n">
         <x:f>ROUND(F193-F192,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H193" s="24" t="n">
         <x:f>IFERROR(F193/F192-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I193" s="26" t="n">
         <x:f>ROUND(D193-E193,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J193" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13516,37 +13552,37 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B194" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C194" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G194" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G194" s="23" t="n">
         <x:f>ROUND(F194-F193,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H194" s="24" t="n">
         <x:f>IFERROR(F194/F193-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I194" s="26" t="n">
         <x:f>ROUND(D194-E194,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J194" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K194" s="22" t="n">
         <x:v>5</x:v>
@@ -13554,34 +13590,34 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B195" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C195" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G195" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G195" s="28" t="n">
         <x:f>ROUND(F195-F194,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H195" s="24" t="n">
         <x:f>IFERROR(F195/F194-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I195" s="26" t="n">
         <x:f>ROUND(D195-E195,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J195" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13592,110 +13628,110 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B196" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C196" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G196" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G196" s="23" t="n">
         <x:f>ROUND(F196-F195,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H196" s="24" t="n">
         <x:f>IFERROR(F196/F195-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I196" s="26" t="n">
         <x:f>ROUND(D196-E196,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J196" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K196" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B197" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C197" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G197" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G197" s="28" t="n">
         <x:f>ROUND(F197-F196,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H197" s="24" t="n">
         <x:f>IFERROR(F197/F196-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I197" s="26" t="n">
         <x:f>ROUND(D197-E197,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J197" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K197" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B198" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C198" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G198" s="23" t="n">
         <x:f>ROUND(F198-F197,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H198" s="24" t="n">
         <x:f>IFERROR(F198/F197-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I198" s="26" t="n">
         <x:f>ROUND(D198-E198,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J198" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13706,148 +13742,148 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I199" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B200" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C200" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D200" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E200" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F200" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G200" s="23" t="n">
         <x:f>ROUND(F200-F199,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H200" s="24" t="n">
         <x:f>IFERROR(F200/F199-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I200" s="23" t="n">
         <x:f>ROUND(D200-E200,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J200" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K200" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B201" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C201" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D201" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E201" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F201" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G201" s="23" t="n">
         <x:f>ROUND(F201-F200,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H201" s="24" t="n">
         <x:f>IFERROR(F201/F200-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I201" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I201" s="23" t="n">
         <x:f>ROUND(D201-E201,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J201" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K201" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B202" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C202" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D202" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E202" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F202" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G202" s="23" t="n">
         <x:f>ROUND(F202-F201,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H202" s="24" t="n">
         <x:f>IFERROR(F202/F201-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I202" s="26" t="n">
         <x:f>ROUND(D202-E202,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J202" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13858,34 +13894,34 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B203" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C203" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D203" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E203" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F203" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G203" s="23" t="n">
         <x:f>ROUND(F203-F202,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H203" s="24" t="n">
         <x:f>IFERROR(F203/F202-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I203" s="26" t="n">
         <x:f>ROUND(D203-E203,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J203" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13896,34 +13932,34 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13934,34 +13970,34 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B205" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C205" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G205" s="23" t="n">
         <x:f>ROUND(F205-F204,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H205" s="24" t="n">
         <x:f>IFERROR(F205/F204-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I205" s="26" t="n">
         <x:f>ROUND(D205-E205,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J205" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13972,113 +14008,113 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B206" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C206" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G206" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G206" s="23" t="n">
         <x:f>ROUND(F206-F205,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H206" s="24" t="n">
         <x:f>IFERROR(F206/F205-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I206" s="26" t="n">
         <x:f>ROUND(D206-E206,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J206" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K206" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B207" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C207" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G207" s="28" t="n">
         <x:f>ROUND(F207-F206,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H207" s="24" t="n">
         <x:f>IFERROR(F207/F206-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I207" s="26" t="n">
         <x:f>ROUND(D207-E207,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J207" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K207" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B208" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C208" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D208" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E208" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F208" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G208" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G208" s="28" t="n">
         <x:f>ROUND(F208-F207,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H208" s="24" t="n">
         <x:f>IFERROR(F208/F207-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I208" s="26" t="n">
         <x:f>ROUND(D208-E208,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J208" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K208" s="22" t="n">
         <x:v>5</x:v>
@@ -14086,34 +14122,34 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14124,34 +14160,34 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B210" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C210" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D210" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E210" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F210" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G210" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
         <x:f>ROUND(F210-F209,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H210" s="24" t="n">
         <x:f>IFERROR(F210/F209-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I210" s="26" t="n">
         <x:f>ROUND(D210-E210,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J210" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14162,34 +14198,34 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B211" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C211" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D211" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E211" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F211" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G211" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G211" s="28" t="n">
         <x:f>ROUND(F211-F210,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H211" s="24" t="n">
         <x:f>IFERROR(F211/F210-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I211" s="26" t="n">
         <x:f>ROUND(D211-E211,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J211" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14200,34 +14236,34 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B212" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C212" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D212" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E212" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F212" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G212" s="23" t="n">
         <x:f>ROUND(F212-F211,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H212" s="24" t="n">
         <x:f>IFERROR(F212/F211-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I212" s="26" t="n">
         <x:f>ROUND(D212-E212,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J212" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14238,34 +14274,34 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B213" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C213" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D213" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E213" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F213" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G213" s="23" t="n">
         <x:f>ROUND(F213-F212,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H213" s="24" t="n">
         <x:f>IFERROR(F213/F212-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>-0.008780743523655543</x:v>
       </x:c>
       <x:c r="I213" s="26" t="n">
         <x:f>ROUND(D213-E213,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J213" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14275,193 +14311,193 @@
       </x:c>
     </x:row>
     <x:row r="214">
-      <x:c r="A214" s="31" t="str">
+      <x:c r="A214" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B214" s="22" t="str">
+        <x:v>8月3日-8月7日</x:v>
+      </x:c>
+      <x:c r="C214" s="23" t="n">
+        <x:v>4526.4</x:v>
+      </x:c>
+      <x:c r="D214" s="23" t="n">
+        <x:v>4656.2</x:v>
+      </x:c>
+      <x:c r="E214" s="23" t="n">
+        <x:v>4494.2</x:v>
+      </x:c>
+      <x:c r="F214" s="23" t="n">
+        <x:v>4645.6</x:v>
+      </x:c>
+      <x:c r="G214" s="23" t="n">
+        <x:f>ROUND(F214-F213,1)</x:f>
+        <x:v>107.6</x:v>
+      </x:c>
+      <x:c r="H214" s="24" t="n">
+        <x:f>IFERROR(F214/F213-1,"")</x:f>
+        <x:v>0.02371088585279857</x:v>
+      </x:c>
+      <x:c r="I214" s="26" t="n">
+        <x:f>ROUND(D214-E214,1)</x:f>
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J214" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K214" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="22" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="C215" s="23" t="n">
+        <x:v>4656.8</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>4663</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>4611</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>4644.6</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:f>ROUND(F215-F214,1)</x:f>
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="H215" s="24" t="n">
+        <x:f>IFERROR(F215/F214-1,"")</x:f>
+        <x:v>-0.00021525744790773516</x:v>
+      </x:c>
+      <x:c r="I215" s="23" t="n">
+        <x:f>ROUND(D215-E215,1)</x:f>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J215" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B214" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C214" s="30"/>
-      <x:c r="D214" s="30"/>
-      <x:c r="E214" s="30"/>
-      <x:c r="F214" s="30"/>
-      <x:c r="G214" s="30"/>
-      <x:c r="H214" s="30"/>
-      <x:c r="I214" s="32" t="n">
-        <x:f>ROUND(SUM(I184:I213),1)</x:f>
-        <x:v>4967.2</x:v>
-      </x:c>
-      <x:c r="J214" s="30"/>
-      <x:c r="K214" s="30"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A215" s="31" t="str">
+      <x:c r="B216" s="30" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C216" s="30"/>
+      <x:c r="D216" s="30"/>
+      <x:c r="E216" s="30"/>
+      <x:c r="F216" s="30"/>
+      <x:c r="G216" s="30"/>
+      <x:c r="H216" s="30"/>
+      <x:c r="I216" s="32" t="n">
+        <x:f>ROUND(SUM(I185:I215),1)</x:f>
+        <x:v>5019.2</x:v>
+      </x:c>
+      <x:c r="J216" s="30"/>
+      <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B215" s="30"/>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I184:I213),0),1)</x:f>
-        <x:v>165.6</x:v>
-      </x:c>
-      <x:c r="J215" s="30"/>
-      <x:c r="K215" s="30"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A217" s="17" t="str">
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I185:I215),0),1)</x:f>
+        <x:v>161.9</x:v>
+      </x:c>
+      <x:c r="J217" s="30"/>
+      <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B217" s="17"/>
-      <x:c r="C217" s="17"/>
-      <x:c r="D217" s="17"/>
-      <x:c r="E217" s="17"/>
-      <x:c r="F217" s="17"/>
-      <x:c r="G217" s="17"/>
-      <x:c r="H217" s="17"/>
-      <x:c r="I217" s="17"/>
-      <x:c r="J217" s="17"/>
-      <x:c r="K217" s="17"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="A218" s="20" t="str">
+      <x:c r="B219" s="17"/>
+      <x:c r="C219" s="17"/>
+      <x:c r="D219" s="17"/>
+      <x:c r="E219" s="17"/>
+      <x:c r="F219" s="17"/>
+      <x:c r="G219" s="17"/>
+      <x:c r="H219" s="17"/>
+      <x:c r="I219" s="17"/>
+      <x:c r="J219" s="17"/>
+      <x:c r="K219" s="17"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B218" s="20" t="str">
+      <x:c r="B220" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C218" s="20" t="str">
+      <x:c r="C220" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D218" s="20" t="str">
+      <x:c r="D220" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E218" s="20" t="str">
+      <x:c r="E220" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F218" s="20" t="str">
+      <x:c r="F220" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G218" s="20" t="str">
+      <x:c r="G220" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H218" s="20" t="str">
+      <x:c r="H220" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I218" s="20" t="str">
+      <x:c r="I220" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J218" s="20" t="str">
+      <x:c r="J220" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K218" s="20" t="str">
+      <x:c r="K220" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A219" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B219" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C219" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D219" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E219" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F219" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G219" s="23"/>
-      <x:c r="H219" s="24"/>
-      <x:c r="I219" s="26" t="n">
-        <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J219" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K219" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A220" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B220" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C220" s="23" t="n">
-        <x:v>3148.4</x:v>
-      </x:c>
-      <x:c r="D220" s="23" t="n">
-        <x:v>3181.2</x:v>
-      </x:c>
-      <x:c r="E220" s="23" t="n">
-        <x:v>3074.4</x:v>
-      </x:c>
-      <x:c r="F220" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G220" s="23" t="n">
-        <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H220" s="24" t="n">
-        <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
-      <x:c r="I220" s="26" t="n">
-        <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>106.8</x:v>
-      </x:c>
-      <x:c r="J220" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K220" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D221" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>3037.8</x:v>
-      </x:c>
-      <x:c r="G221" s="23" t="n">
-        <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>-46.6</x:v>
-      </x:c>
-      <x:c r="H221" s="24" t="n">
-        <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G221" s="23"/>
+      <x:c r="H221" s="24"/>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14472,34 +14508,34 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B222" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C222" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D222" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E222" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F222" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G222" s="23" t="n">
         <x:f>ROUND(F222-F221,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H222" s="24" t="n">
         <x:f>IFERROR(F222/F221-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I222" s="26" t="n">
         <x:f>ROUND(D222-E222,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J222" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14510,34 +14546,34 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B223" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C223" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D223" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E223" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F223" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G223" s="23" t="n">
         <x:f>ROUND(F223-F222,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H223" s="24" t="n">
         <x:f>IFERROR(F223/F222-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I223" s="26" t="n">
         <x:f>ROUND(D223-E223,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J223" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14548,34 +14584,34 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D224" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14586,72 +14622,72 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B225" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C225" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D225" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E225" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F225" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G225" s="23" t="n">
         <x:f>ROUND(F225-F224,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H225" s="24" t="n">
         <x:f>IFERROR(F225/F224-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I225" s="26" t="n">
         <x:f>ROUND(D225-E225,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J225" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K225" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B226" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C226" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D226" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E226" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F226" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G226" s="23" t="n">
         <x:f>ROUND(F226-F225,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H226" s="24" t="n">
         <x:f>IFERROR(F226/F225-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I226" s="26" t="n">
         <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J226" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14662,72 +14698,72 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G227" s="23" t="n">
         <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H227" s="24" t="n">
         <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K227" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G228" s="23" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14738,37 +14774,37 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I229" s="26" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K229" s="22" t="n">
         <x:v>5</x:v>
@@ -14776,37 +14812,37 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I230" s="26" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K230" s="22" t="n">
         <x:v>5</x:v>
@@ -14814,72 +14850,72 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I231" s="26" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K231" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -14890,224 +14926,224 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I233" s="23" t="n">
+        <x:v>0.02453287690771644</x:v>
+      </x:c>
+      <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K233" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
-      </x:c>
-      <x:c r="I234" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K234" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I235" s="23" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K235" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I236" s="26" t="n">
+        <x:v>0.013588255377261937</x:v>
+      </x:c>
+      <x:c r="I236" s="23" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K236" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
-      </x:c>
-      <x:c r="I237" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I237" s="23" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K237" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15118,34 +15154,34 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15156,34 +15192,34 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G240" s="23" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I240" s="26" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15194,75 +15230,75 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G241" s="23" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I241" s="23" t="n">
+        <x:v>-0.019513204164655518</x:v>
+      </x:c>
+      <x:c r="I241" s="26" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K241" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G242" s="23" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
+        <x:v>0.01870604781997187</x:v>
       </x:c>
       <x:c r="I242" s="26" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K242" s="22" t="n">
         <x:v>5</x:v>
@@ -15270,75 +15306,75 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
-      </x:c>
-      <x:c r="I243" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I243" s="23" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K243" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
         <x:v>5</x:v>
@@ -15346,34 +15382,34 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D245" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I245" s="26" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15384,34 +15420,34 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B246" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C246" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D246" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E246" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F246" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G246" s="23" t="n">
         <x:f>ROUND(F246-F245,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H246" s="24" t="n">
         <x:f>IFERROR(F246/F245-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I246" s="26" t="n">
         <x:f>ROUND(D246-E246,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J246" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15422,34 +15458,34 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B247" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C247" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D247" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E247" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F247" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G247" s="23" t="n">
         <x:f>ROUND(F247-F246,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H247" s="24" t="n">
         <x:f>IFERROR(F247/F246-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I247" s="26" t="n">
         <x:f>ROUND(D247-E247,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J247" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15460,34 +15496,34 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B248" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C248" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D248" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E248" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F248" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G248" s="23" t="n">
         <x:f>ROUND(F248-F247,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H248" s="24" t="n">
         <x:f>IFERROR(F248/F247-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I248" s="26" t="n">
         <x:f>ROUND(D248-E248,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J248" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15497,231 +15533,231 @@
       </x:c>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="31" t="str">
+      <x:c r="A249" s="22" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B249" s="22" t="str">
+        <x:v>7月27日-7月31日</x:v>
+      </x:c>
+      <x:c r="C249" s="23" t="n">
+        <x:v>2929.6</x:v>
+      </x:c>
+      <x:c r="D249" s="23" t="n">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="E249" s="23" t="n">
+        <x:v>2847.2</x:v>
+      </x:c>
+      <x:c r="F249" s="23" t="n">
+        <x:v>2891.8</x:v>
+      </x:c>
+      <x:c r="G249" s="23" t="n">
+        <x:f>ROUND(F249-F248,1)</x:f>
+        <x:v>-18.2</x:v>
+      </x:c>
+      <x:c r="H249" s="24" t="n">
+        <x:f>IFERROR(F249/F248-1,"")</x:f>
+        <x:v>-0.006254295532646004</x:v>
+      </x:c>
+      <x:c r="I249" s="26" t="n">
+        <x:f>ROUND(D249-E249,1)</x:f>
+        <x:v>82.8</x:v>
+      </x:c>
+      <x:c r="J249" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K249" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B250" s="22" t="str">
+        <x:v>8月3日-8月7日</x:v>
+      </x:c>
+      <x:c r="C250" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D250" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E250" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F250" s="23" t="n">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="G250" s="23" t="n">
+        <x:f>ROUND(F250-F249,1)</x:f>
+        <x:v>38.2</x:v>
+      </x:c>
+      <x:c r="H250" s="24" t="n">
+        <x:f>IFERROR(F250/F249-1,"")</x:f>
+        <x:v>0.013209765543951812</x:v>
+      </x:c>
+      <x:c r="I250" s="26" t="n">
+        <x:f>ROUND(D250-E250,1)</x:f>
+        <x:v>84.8</x:v>
+      </x:c>
+      <x:c r="J250" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K250" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="22" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B251" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="C251" s="23" t="n">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="D251" s="23" t="n">
+        <x:v>2949.6</x:v>
+      </x:c>
+      <x:c r="E251" s="23" t="n">
+        <x:v>2927.8</x:v>
+      </x:c>
+      <x:c r="F251" s="23" t="n">
+        <x:v>2936</x:v>
+      </x:c>
+      <x:c r="G251" s="23" t="n">
+        <x:f>ROUND(F251-F250,1)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H251" s="24" t="n">
+        <x:f>IFERROR(F251/F250-1,"")</x:f>
+        <x:v>0.0020477815699657675</x:v>
+      </x:c>
+      <x:c r="I251" s="23" t="n">
+        <x:f>ROUND(D251-E251,1)</x:f>
+        <x:v>21.8</x:v>
+      </x:c>
+      <x:c r="J251" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K251" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B249" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C249" s="30"/>
-      <x:c r="D249" s="30"/>
-      <x:c r="E249" s="30"/>
-      <x:c r="F249" s="30"/>
-      <x:c r="G249" s="30"/>
-      <x:c r="H249" s="30"/>
-      <x:c r="I249" s="32" t="n">
-        <x:f>ROUND(SUM(I219:I248),1)</x:f>
-        <x:v>2817.6</x:v>
-      </x:c>
-      <x:c r="J249" s="30"/>
-      <x:c r="K249" s="30"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250" s="31" t="str">
+      <x:c r="B252" s="30" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C252" s="30"/>
+      <x:c r="D252" s="30"/>
+      <x:c r="E252" s="30"/>
+      <x:c r="F252" s="30"/>
+      <x:c r="G252" s="30"/>
+      <x:c r="H252" s="30"/>
+      <x:c r="I252" s="32" t="n">
+        <x:f>ROUND(SUM(I221:I251),1)</x:f>
+        <x:v>2839.4</x:v>
+      </x:c>
+      <x:c r="J252" s="30"/>
+      <x:c r="K252" s="30"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B250" s="30"/>
-      <x:c r="C250" s="30"/>
-      <x:c r="D250" s="30"/>
-      <x:c r="E250" s="30"/>
-      <x:c r="F250" s="30"/>
-      <x:c r="G250" s="30"/>
-      <x:c r="H250" s="30"/>
-      <x:c r="I250" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I219:I248),0),1)</x:f>
-        <x:v>93.9</x:v>
-      </x:c>
-      <x:c r="J250" s="30"/>
-      <x:c r="K250" s="30"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252" s="17" t="str">
+      <x:c r="B253" s="30"/>
+      <x:c r="C253" s="30"/>
+      <x:c r="D253" s="30"/>
+      <x:c r="E253" s="30"/>
+      <x:c r="F253" s="30"/>
+      <x:c r="G253" s="30"/>
+      <x:c r="H253" s="30"/>
+      <x:c r="I253" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I221:I251),0),1)</x:f>
+        <x:v>91.6</x:v>
+      </x:c>
+      <x:c r="J253" s="30"/>
+      <x:c r="K253" s="30"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="17" t="str">
         <x:v>碳酸锂2609</x:v>
       </x:c>
-      <x:c r="B252" s="17"/>
-      <x:c r="C252" s="17"/>
-      <x:c r="D252" s="17"/>
-      <x:c r="E252" s="17"/>
-      <x:c r="F252" s="17"/>
-      <x:c r="G252" s="17"/>
-      <x:c r="H252" s="17"/>
-      <x:c r="I252" s="17"/>
-      <x:c r="J252" s="17"/>
-      <x:c r="K252" s="17"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253" s="20" t="str">
+      <x:c r="B255" s="17"/>
+      <x:c r="C255" s="17"/>
+      <x:c r="D255" s="17"/>
+      <x:c r="E255" s="17"/>
+      <x:c r="F255" s="17"/>
+      <x:c r="G255" s="17"/>
+      <x:c r="H255" s="17"/>
+      <x:c r="I255" s="17"/>
+      <x:c r="J255" s="17"/>
+      <x:c r="K255" s="17"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B253" s="20" t="str">
+      <x:c r="B256" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C253" s="20" t="str">
+      <x:c r="C256" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D253" s="20" t="str">
+      <x:c r="D256" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E253" s="20" t="str">
+      <x:c r="E256" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F253" s="20" t="str">
+      <x:c r="F256" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G253" s="20" t="str">
+      <x:c r="G256" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H253" s="20" t="str">
+      <x:c r="H256" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I253" s="20" t="str">
+      <x:c r="I256" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J253" s="20" t="str">
+      <x:c r="J256" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K253" s="20" t="str">
+      <x:c r="K256" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B254" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C254" s="23" t="n">
-        <x:v>126360</x:v>
-      </x:c>
-      <x:c r="D254" s="23" t="n">
-        <x:v>150760</x:v>
-      </x:c>
-      <x:c r="E254" s="23" t="n">
-        <x:v>125160</x:v>
-      </x:c>
-      <x:c r="F254" s="23" t="n">
-        <x:v>145380</x:v>
-      </x:c>
-      <x:c r="G254" s="23"/>
-      <x:c r="H254" s="24"/>
-      <x:c r="I254" s="26" t="n">
-        <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>25600</x:v>
-      </x:c>
-      <x:c r="J254" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K254" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B255" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C255" s="23" t="n">
-        <x:v>153000</x:v>
-      </x:c>
-      <x:c r="D255" s="23" t="n">
-        <x:v>176120</x:v>
-      </x:c>
-      <x:c r="E255" s="23" t="n">
-        <x:v>147740</x:v>
-      </x:c>
-      <x:c r="F255" s="23" t="n">
-        <x:v>147740</x:v>
-      </x:c>
-      <x:c r="G255" s="28" t="n">
-        <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>2360</x:v>
-      </x:c>
-      <x:c r="H255" s="24" t="n">
-        <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>0.016233319576282934</x:v>
-      </x:c>
-      <x:c r="I255" s="26" t="n">
-        <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>28380</x:v>
-      </x:c>
-      <x:c r="J255" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K255" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B256" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
-      </x:c>
-      <x:c r="C256" s="23" t="n">
-        <x:v>150720</x:v>
-      </x:c>
-      <x:c r="D256" s="23" t="n">
-        <x:v>183780</x:v>
-      </x:c>
-      <x:c r="E256" s="23" t="n">
-        <x:v>143820</x:v>
-      </x:c>
-      <x:c r="F256" s="23" t="n">
-        <x:v>183380</x:v>
-      </x:c>
-      <x:c r="G256" s="28" t="n">
-        <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>35640</x:v>
-      </x:c>
-      <x:c r="H256" s="24" t="n">
-        <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>0.24123460132665486</x:v>
-      </x:c>
-      <x:c r="I256" s="26" t="n">
-        <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>39960</x:v>
-      </x:c>
-      <x:c r="J256" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K256" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>126360</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>150760</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>125160</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>148560</x:v>
-      </x:c>
-      <x:c r="G257" s="28" t="n">
-        <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>-34820</x:v>
-      </x:c>
-      <x:c r="H257" s="24" t="n">
-        <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>-0.18987893990620575</x:v>
-      </x:c>
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="G257" s="23"/>
+      <x:c r="H257" s="24"/>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>42040</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15732,34 +15768,34 @@
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D258" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>176120</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="G258" s="28" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>-15060</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>-0.10137318255250405</x:v>
+        <x:v>0.016233319576282934</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>28720</x:v>
+        <x:v>28380</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15770,34 +15806,34 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B259" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C259" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>150720</x:v>
       </x:c>
       <x:c r="D259" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>183780</x:v>
       </x:c>
       <x:c r="E259" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>143820</x:v>
       </x:c>
       <x:c r="F259" s="23" t="n">
-        <x:v>153500</x:v>
+        <x:v>183380</x:v>
       </x:c>
       <x:c r="G259" s="28" t="n">
         <x:f>ROUND(F259-F258,1)</x:f>
-        <x:v>20000</x:v>
+        <x:v>35640</x:v>
       </x:c>
       <x:c r="H259" s="24" t="n">
         <x:f>IFERROR(F259/F258-1,"")</x:f>
-        <x:v>0.14981273408239693</x:v>
+        <x:v>0.24123460132665486</x:v>
       </x:c>
       <x:c r="I259" s="26" t="n">
         <x:f>ROUND(D259-E259,1)</x:f>
-        <x:v>20200</x:v>
+        <x:v>39960</x:v>
       </x:c>
       <x:c r="J259" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15808,72 +15844,72 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B260" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C260" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>187000</x:v>
       </x:c>
       <x:c r="D260" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>190600</x:v>
       </x:c>
       <x:c r="E260" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="F260" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="G260" s="28" t="n">
         <x:f>ROUND(F260-F259,1)</x:f>
-        <x:v>23700</x:v>
+        <x:v>-34820</x:v>
       </x:c>
       <x:c r="H260" s="24" t="n">
         <x:f>IFERROR(F260/F259-1,"")</x:f>
-        <x:v>0.15439739413680775</x:v>
+        <x:v>-0.18987893990620575</x:v>
       </x:c>
       <x:c r="I260" s="26" t="n">
         <x:f>ROUND(D260-E260,1)</x:f>
-        <x:v>28560</x:v>
+        <x:v>42040</x:v>
       </x:c>
       <x:c r="J260" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K260" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B261" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C261" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>148040</x:v>
       </x:c>
       <x:c r="D261" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>153200</x:v>
       </x:c>
       <x:c r="E261" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>124480</x:v>
       </x:c>
       <x:c r="F261" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>133500</x:v>
       </x:c>
       <x:c r="G261" s="28" t="n">
         <x:f>ROUND(F261-F260,1)</x:f>
-        <x:v>-20500</x:v>
+        <x:v>-15060</x:v>
       </x:c>
       <x:c r="H261" s="24" t="n">
         <x:f>IFERROR(F261/F260-1,"")</x:f>
-        <x:v>-0.11568848758465011</x:v>
+        <x:v>-0.10137318255250405</x:v>
       </x:c>
       <x:c r="I261" s="26" t="n">
         <x:f>ROUND(D261-E261,1)</x:f>
-        <x:v>34020</x:v>
+        <x:v>28720</x:v>
       </x:c>
       <x:c r="J261" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15884,34 +15920,34 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B262" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C262" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D262" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>153700</x:v>
       </x:c>
       <x:c r="E262" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>133500</x:v>
       </x:c>
       <x:c r="F262" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>153500</x:v>
       </x:c>
       <x:c r="G262" s="28" t="n">
         <x:f>ROUND(F262-F261,1)</x:f>
-        <x:v>-4600</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="H262" s="24" t="n">
         <x:f>IFERROR(F262/F261-1,"")</x:f>
-        <x:v>-0.02935545628589664</x:v>
+        <x:v>0.14981273408239693</x:v>
       </x:c>
       <x:c r="I262" s="26" t="n">
         <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>20200</x:v>
       </x:c>
       <x:c r="J262" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15922,72 +15958,72 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>186900</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>143520</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="G263" s="28" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>-8580</x:v>
+        <x:v>23700</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>-0.05641025641025643</x:v>
+        <x:v>0.15439739413680775</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>20800</x:v>
+        <x:v>28560</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K263" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>180000</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>180060</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>146040</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>156700</x:v>
       </x:c>
       <x:c r="G264" s="28" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>25880</x:v>
+        <x:v>-20500</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>0.18032329988851736</x:v>
+        <x:v>-0.11568848758465011</x:v>
       </x:c>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>32200</x:v>
+        <x:v>34020</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -15998,34 +16034,34 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>149000</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>167400</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>142600</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>152100</x:v>
       </x:c>
       <x:c r="G265" s="28" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>-11540</x:v>
+        <x:v>-4600</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>-0.06812278630460444</x:v>
+        <x:v>-0.02935545628589664</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>20440</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16036,72 +16072,72 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>160800</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>143520</x:v>
       </x:c>
       <x:c r="G266" s="28" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>-260</x:v>
+        <x:v>-8580</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>-0.0016470290130495835</x:v>
+        <x:v>-0.05641025641025643</x:v>
       </x:c>
       <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>20800</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K266" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>141220</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>172220</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>140020</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>177560</x:v>
+        <x:v>169400</x:v>
       </x:c>
       <x:c r="G267" s="28" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>19960</x:v>
+        <x:v>25880</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>0.1266497461928935</x:v>
+        <x:v>0.18032329988851736</x:v>
       </x:c>
       <x:c r="I267" s="26" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>23220</x:v>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16112,34 +16148,34 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>170000</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>175000</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="G268" s="28" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>-11540</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>0.0019148456859652274</x:v>
+        <x:v>-0.06812278630460444</x:v>
       </x:c>
       <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>20440</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16150,34 +16186,34 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>158440</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>165500</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>157600</x:v>
       </x:c>
       <x:c r="G269" s="28" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>11180</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>0.06284429454749851</x:v>
+        <x:v>-0.0016470290130495835</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>16100</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16188,72 +16224,72 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>155020</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>178000</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>154780</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>177560</x:v>
       </x:c>
       <x:c r="G270" s="28" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>19960</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>0.039559974613920135</x:v>
+        <x:v>0.1266497461928935</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>10440</x:v>
+        <x:v>23220</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K270" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>177000</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>209880</x:v>
+        <x:v>181440</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>186800</x:v>
+        <x:v>169500</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>188800</x:v>
+        <x:v>177900</x:v>
       </x:c>
       <x:c r="G271" s="28" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>-7760</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>-0.039479039479039524</x:v>
+        <x:v>0.0019148456859652274</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>23080</x:v>
+        <x:v>11940</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16264,110 +16300,110 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>182000</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>189500</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>173400</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>189080</x:v>
       </x:c>
       <x:c r="G272" s="28" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-4340</x:v>
+        <x:v>11180</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.022987288135593253</x:v>
+        <x:v>0.06284429454749851</x:v>
       </x:c>
       <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>18700</x:v>
+        <x:v>16100</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K272" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>191500</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>201480</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>191040</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>196560</x:v>
       </x:c>
       <x:c r="G273" s="28" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>-4720</x:v>
+        <x:v>7480</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>-0.02558820340453216</x:v>
+        <x:v>0.039559974613920135</x:v>
       </x:c>
       <x:c r="I273" s="26" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>10440</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K273" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>196560</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>209880</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>186800</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>188800</x:v>
       </x:c>
       <x:c r="G274" s="28" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>-15380</x:v>
+        <x:v>-7760</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>-0.08556804272838547</x:v>
+        <x:v>-0.039479039479039524</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>24920</x:v>
+        <x:v>23080</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16378,34 +16414,34 @@
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>189000</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>193900</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>175200</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>184460</x:v>
       </x:c>
       <x:c r="G275" s="28" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>-4340</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>0.06656120710635194</x:v>
+        <x:v>-0.022987288135593253</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>18480</x:v>
+        <x:v>18700</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16416,72 +16452,72 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>185500</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>187900</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>172080</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>179740</x:v>
       </x:c>
       <x:c r="G276" s="28" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>-14800</x:v>
+        <x:v>-4720</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>-0.08442669709070161</x:v>
+        <x:v>-0.02558820340453216</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>17820</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K276" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>181000</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>182100</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>157180</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>164360</x:v>
       </x:c>
       <x:c r="G277" s="28" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>-10280</x:v>
+        <x:v>-15380</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>-0.06404984423676008</x:v>
+        <x:v>-0.08556804272838547</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>18940</x:v>
+        <x:v>24920</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16492,34 +16528,34 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>161500</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>178740</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>160260</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>175300</x:v>
       </x:c>
       <x:c r="G278" s="28" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>18560</x:v>
+        <x:v>10940</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>0.12355212355212353</x:v>
+        <x:v>0.06656120710635194</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>26700</x:v>
+        <x:v>18480</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16530,72 +16566,72 @@
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>177600</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>177920</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>160100</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="G279" s="28" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-17180</x:v>
+        <x:v>-14800</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.10178931152980208</x:v>
+        <x:v>-0.08442669709070161</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>18460</x:v>
+        <x:v>17820</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>157220</x:v>
       </x:c>
       <x:c r="D280" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>163940</x:v>
       </x:c>
       <x:c r="E280" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>145000</x:v>
       </x:c>
       <x:c r="F280" s="23" t="n">
-        <x:v>150140</x:v>
+        <x:v>150220</x:v>
       </x:c>
       <x:c r="G280" s="28" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>-1460</x:v>
+        <x:v>-10280</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>-0.009630606860158264</x:v>
+        <x:v>-0.06404984423676008</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>10640</x:v>
+        <x:v>18940</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16606,34 +16642,34 @@
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>148000</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>145300</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>144280</x:v>
+        <x:v>168780</x:v>
       </x:c>
       <x:c r="G281" s="28" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>-5860</x:v>
+        <x:v>18560</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>-0.03903023844411879</x:v>
+        <x:v>0.12355212355212353</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>26700</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16644,34 +16680,34 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>166980</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>168720</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>150260</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G282" s="28" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>-6520</x:v>
+        <x:v>-17180</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>-0.04518990851122817</x:v>
+        <x:v>-0.10178931152980208</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>18460</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16682,34 +16718,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>145860</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>150140</x:v>
       </x:c>
       <x:c r="G283" s="28" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>2240</x:v>
+        <x:v>-1460</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>0.016260162601626105</x:v>
+        <x:v>-0.009630606860158264</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>9240</x:v>
+        <x:v>10640</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16719,42 +16755,194 @@
       </x:c>
     </x:row>
     <x:row r="284">
-      <x:c r="A284" s="31" t="str">
+      <x:c r="A284" s="22" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B284" s="22" t="str">
+        <x:v>7月20日-7月24日</x:v>
+      </x:c>
+      <x:c r="C284" s="23" t="n">
+        <x:v>151500</x:v>
+      </x:c>
+      <x:c r="D284" s="23" t="n">
+        <x:v>154800</x:v>
+      </x:c>
+      <x:c r="E284" s="23" t="n">
+        <x:v>136800</x:v>
+      </x:c>
+      <x:c r="F284" s="23" t="n">
+        <x:v>144280</x:v>
+      </x:c>
+      <x:c r="G284" s="28" t="n">
+        <x:f>ROUND(F284-F283,1)</x:f>
+        <x:v>-5860</x:v>
+      </x:c>
+      <x:c r="H284" s="24" t="n">
+        <x:f>IFERROR(F284/F283-1,"")</x:f>
+        <x:v>-0.03903023844411879</x:v>
+      </x:c>
+      <x:c r="I284" s="26" t="n">
+        <x:f>ROUND(D284-E284,1)</x:f>
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J284" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K284" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="22" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B285" s="22" t="str">
+        <x:v>7月27日-7月31日</x:v>
+      </x:c>
+      <x:c r="C285" s="23" t="n">
+        <x:v>145780</x:v>
+      </x:c>
+      <x:c r="D285" s="23" t="n">
+        <x:v>149400</x:v>
+      </x:c>
+      <x:c r="E285" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="F285" s="23" t="n">
+        <x:v>137760</x:v>
+      </x:c>
+      <x:c r="G285" s="28" t="n">
+        <x:f>ROUND(F285-F284,1)</x:f>
+        <x:v>-6520</x:v>
+      </x:c>
+      <x:c r="H285" s="24" t="n">
+        <x:f>IFERROR(F285/F284-1,"")</x:f>
+        <x:v>-0.04518990851122817</x:v>
+      </x:c>
+      <x:c r="I285" s="26" t="n">
+        <x:f>ROUND(D285-E285,1)</x:f>
+        <x:v>11640</x:v>
+      </x:c>
+      <x:c r="J285" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K285" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="22" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B286" s="22" t="str">
+        <x:v>8月3日-8月7日</x:v>
+      </x:c>
+      <x:c r="C286" s="23" t="n">
+        <x:v>137500</x:v>
+      </x:c>
+      <x:c r="D286" s="23" t="n">
+        <x:v>144800</x:v>
+      </x:c>
+      <x:c r="E286" s="23" t="n">
+        <x:v>135560</x:v>
+      </x:c>
+      <x:c r="F286" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="G286" s="28" t="n">
+        <x:f>ROUND(F286-F285,1)</x:f>
+        <x:v>2240</x:v>
+      </x:c>
+      <x:c r="H286" s="24" t="n">
+        <x:f>IFERROR(F286/F285-1,"")</x:f>
+        <x:v>0.016260162601626105</x:v>
+      </x:c>
+      <x:c r="I286" s="26" t="n">
+        <x:f>ROUND(D286-E286,1)</x:f>
+        <x:v>9240</x:v>
+      </x:c>
+      <x:c r="J286" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K286" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="22" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B287" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="C287" s="23" t="n">
+        <x:v>140500</x:v>
+      </x:c>
+      <x:c r="D287" s="23" t="n">
+        <x:v>146380</x:v>
+      </x:c>
+      <x:c r="E287" s="23" t="n">
+        <x:v>139280</x:v>
+      </x:c>
+      <x:c r="F287" s="23" t="n">
+        <x:v>146360</x:v>
+      </x:c>
+      <x:c r="G287" s="28" t="n">
+        <x:f>ROUND(F287-F286,1)</x:f>
+        <x:v>6360</x:v>
+      </x:c>
+      <x:c r="H287" s="24" t="n">
+        <x:f>IFERROR(F287/F286-1,"")</x:f>
+        <x:v>0.045428571428571374</x:v>
+      </x:c>
+      <x:c r="I287" s="26" t="n">
+        <x:f>ROUND(D287-E287,1)</x:f>
+        <x:v>7100</x:v>
+      </x:c>
+      <x:c r="J287" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K287" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B284" s="30" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C284" s="30"/>
-      <x:c r="D284" s="30"/>
-      <x:c r="E284" s="30"/>
-      <x:c r="F284" s="30"/>
-      <x:c r="G284" s="30"/>
-      <x:c r="H284" s="30"/>
-      <x:c r="I284" s="32" t="n">
-        <x:f>ROUND(SUM(I254:I283),1)</x:f>
-        <x:v>652860</x:v>
-      </x:c>
-      <x:c r="J284" s="30"/>
-      <x:c r="K284" s="30"/>
-    </x:row>
-    <x:row r="285">
-      <x:c r="A285" s="31" t="str">
+      <x:c r="B288" s="30" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C288" s="30"/>
+      <x:c r="D288" s="30"/>
+      <x:c r="E288" s="30"/>
+      <x:c r="F288" s="30"/>
+      <x:c r="G288" s="30"/>
+      <x:c r="H288" s="30"/>
+      <x:c r="I288" s="32" t="n">
+        <x:f>ROUND(SUM(I257:I287),1)</x:f>
+        <x:v>659960</x:v>
+      </x:c>
+      <x:c r="J288" s="30"/>
+      <x:c r="K288" s="30"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B285" s="30"/>
-      <x:c r="C285" s="30"/>
-      <x:c r="D285" s="30"/>
-      <x:c r="E285" s="30"/>
-      <x:c r="F285" s="30"/>
-      <x:c r="G285" s="30"/>
-      <x:c r="H285" s="30"/>
-      <x:c r="I285" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I254:I283),0),1)</x:f>
-        <x:v>21762</x:v>
-      </x:c>
-      <x:c r="J285" s="30"/>
-      <x:c r="K285" s="30"/>
+      <x:c r="B289" s="30"/>
+      <x:c r="C289" s="30"/>
+      <x:c r="D289" s="30"/>
+      <x:c r="E289" s="30"/>
+      <x:c r="F289" s="30"/>
+      <x:c r="G289" s="30"/>
+      <x:c r="H289" s="30"/>
+      <x:c r="I289" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I257:I287),0),1)</x:f>
+        <x:v>21289</x:v>
+      </x:c>
+      <x:c r="J289" s="30"/>
+      <x:c r="K289" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16764,9 +16952,9 @@
     <x:mergeCell ref="A75:K75"/>
     <x:mergeCell ref="A111:K111"/>
     <x:mergeCell ref="A147:K147"/>
-    <x:mergeCell ref="A182:K182"/>
-    <x:mergeCell ref="A217:K217"/>
-    <x:mergeCell ref="A252:K252"/>
+    <x:mergeCell ref="A183:K183"/>
+    <x:mergeCell ref="A219:K219"/>
+    <x:mergeCell ref="A255:K255"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -46493,30 +46681,48 @@
       </x:c>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B184" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C184" s="30"/>
-      <x:c r="D184" s="30"/>
-      <x:c r="E184" s="30"/>
-      <x:c r="F184" s="30"/>
-      <x:c r="G184" s="30"/>
-      <x:c r="H184" s="30"/>
-      <x:c r="I184" s="30"/>
-      <x:c r="J184" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J183),1)</x:f>
-        <x:v>929</x:v>
-      </x:c>
-      <x:c r="K184" s="30"/>
+      <x:c r="A184" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B184" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C184" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="D184" s="23" t="n">
+        <x:v>7888</x:v>
+      </x:c>
+      <x:c r="E184" s="23" t="n">
+        <x:v>7918</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="n">
+        <x:v>7795.8</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="n">
+        <x:v>7881.4</x:v>
+      </x:c>
+      <x:c r="H184" s="23" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="I184" s="24" t="n">
+        <x:v>0.0004569803752316748</x:v>
+      </x:c>
+      <x:c r="J184" s="23" t="n">
+        <x:f>ROUND(E184-F184,1)</x:f>
+        <x:v>122.2</x:v>
+      </x:c>
+      <x:c r="K184" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B185" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B185" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C185" s="30"/>
       <x:c r="D185" s="30"/>
       <x:c r="E185" s="30"/>
@@ -46524,11 +46730,29 @@
       <x:c r="G185" s="30"/>
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="30"/>
-      <x:c r="J185" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
-        <x:v>185.8</x:v>
+      <x:c r="J185" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J184),1)</x:f>
+        <x:v>1051.2</x:v>
       </x:c>
       <x:c r="K185" s="30"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B186" s="30"/>
+      <x:c r="C186" s="30"/>
+      <x:c r="D186" s="30"/>
+      <x:c r="E186" s="30"/>
+      <x:c r="F186" s="30"/>
+      <x:c r="G186" s="30"/>
+      <x:c r="H186" s="30"/>
+      <x:c r="I186" s="30"/>
+      <x:c r="J186" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
+        <x:v>175.2</x:v>
+      </x:c>
+      <x:c r="K186" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -52419,30 +52643,48 @@
       </x:c>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B184" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C184" s="30"/>
-      <x:c r="D184" s="30"/>
-      <x:c r="E184" s="30"/>
-      <x:c r="F184" s="30"/>
-      <x:c r="G184" s="30"/>
-      <x:c r="H184" s="30"/>
-      <x:c r="I184" s="30"/>
-      <x:c r="J184" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J183),1)</x:f>
-        <x:v>328.4</x:v>
-      </x:c>
-      <x:c r="K184" s="30"/>
+      <x:c r="A184" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B184" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C184" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="D184" s="23" t="n">
+        <x:v>4656.8</x:v>
+      </x:c>
+      <x:c r="E184" s="23" t="n">
+        <x:v>4663</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="n">
+        <x:v>4611</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="n">
+        <x:v>4644.6</x:v>
+      </x:c>
+      <x:c r="H184" s="23" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I184" s="24" t="n">
+        <x:v>-0.00021525744790773516</x:v>
+      </x:c>
+      <x:c r="J184" s="23" t="n">
+        <x:f>ROUND(E184-F184,1)</x:f>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K184" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B185" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B185" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C185" s="30"/>
       <x:c r="D185" s="30"/>
       <x:c r="E185" s="30"/>
@@ -52450,11 +52692,29 @@
       <x:c r="G185" s="30"/>
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="30"/>
-      <x:c r="J185" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
-        <x:v>65.7</x:v>
+      <x:c r="J185" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J184),1)</x:f>
+        <x:v>380.4</x:v>
       </x:c>
       <x:c r="K185" s="30"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B186" s="30"/>
+      <x:c r="C186" s="30"/>
+      <x:c r="D186" s="30"/>
+      <x:c r="E186" s="30"/>
+      <x:c r="F186" s="30"/>
+      <x:c r="G186" s="30"/>
+      <x:c r="H186" s="30"/>
+      <x:c r="I186" s="30"/>
+      <x:c r="J186" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
+        <x:v>63.4</x:v>
+      </x:c>
+      <x:c r="K186" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -58345,30 +58605,48 @@
       </x:c>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B184" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C184" s="30"/>
-      <x:c r="D184" s="30"/>
-      <x:c r="E184" s="30"/>
-      <x:c r="F184" s="30"/>
-      <x:c r="G184" s="30"/>
-      <x:c r="H184" s="30"/>
-      <x:c r="I184" s="30"/>
-      <x:c r="J184" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J183),1)</x:f>
-        <x:v>186.8</x:v>
-      </x:c>
-      <x:c r="K184" s="30"/>
+      <x:c r="A184" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B184" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C184" s="22" t="str">
+        <x:v>8月10日</x:v>
+      </x:c>
+      <x:c r="D184" s="23" t="n">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="E184" s="23" t="n">
+        <x:v>2949.6</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="n">
+        <x:v>2927.8</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="n">
+        <x:v>2936</x:v>
+      </x:c>
+      <x:c r="H184" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I184" s="24" t="n">
+        <x:v>0.0020477815699657675</x:v>
+      </x:c>
+      <x:c r="J184" s="23" t="n">
+        <x:f>ROUND(E184-F184,1)</x:f>
+        <x:v>21.8</x:v>
+      </x:c>
+      <x:c r="K184" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B185" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B185" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C185" s="30"/>
       <x:c r="D185" s="30"/>
       <x:c r="E185" s="30"/>
@@ -58376,11 +58654,29 @@
       <x:c r="G185" s="30"/>
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="30"/>
-      <x:c r="J185" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J183),0),1)</x:f>
-        <x:v>37.4</x:v>
+      <x:c r="J185" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J184),1)</x:f>
+        <x:v>208.6</x:v>
       </x:c>
       <x:c r="K185" s="30"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B186" s="30"/>
+      <x:c r="C186" s="30"/>
+      <x:c r="D186" s="30"/>
+      <x:c r="E186" s="30"/>
+      <x:c r="F186" s="30"/>
+      <x:c r="G186" s="30"/>
+      <x:c r="H186" s="30"/>
+      <x:c r="I186" s="30"/>
+      <x:c r="J186" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
+        <x:v>34.8</x:v>
+      </x:c>
+      <x:c r="K186" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7bdff34cff644087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf553da57e5694f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rf5cf2d6576314cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R2d906c315a624bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7ac75112fa8940b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdf45d599a3c7436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R36617edb23dd47e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R1a0aeacabe9a4137"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra82508df8ba74f7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7104df33b7c94321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra4d49b8a457b44c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R69891bfb8e1d48a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rbf478be00e9249bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Recf8f442d2184be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbb2ac3eb24134823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3e2e7633bf424fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R39fe5e046cfe422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ref1f2cdbec864bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcfc539cf86c8491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rdfba0e6ac5b24bb8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7736.1</x:v>
+        <x:v>7789.21</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7621.65</x:v>
+        <x:v>7642.44</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>114.5</x:v>
+        <x:v>146.8</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>26147.9</x:v>
+        <x:v>26294.7</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.3</x:v>
+        <x:v>180.1</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8031.16</x:v>
+        <x:v>8078.36</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7910.84</x:v>
+        <x:v>7947.67</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>120.3</x:v>
+        <x:v>130.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>26356.4</x:v>
+        <x:v>26487.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>181.8</x:v>
+        <x:v>181.4</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3967.59</x:v>
+        <x:v>3966.39</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3938.63</x:v>
+        <x:v>3930.64</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>29</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7229.1</x:v>
+        <x:v>7264.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.9</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>146380</x:v>
+        <x:v>146680</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139280</x:v>
+        <x:v>143500</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>7100</x:v>
+        <x:v>3180</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1283520</x:v>
+        <x:v>1286700</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8851.9</x:v>
+        <x:v>8813</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6789,30 +6789,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>32200</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>146500</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>146680</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>143500</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>145860</x:v>
+      </x:c>
+      <x:c r="H185" s="28" t="n">
+        <x:v>-500</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.0034162339437004974</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>3180</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -6820,11 +6838,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>5366.7</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>35380</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>5054.3</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8053,37 +8089,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C35" s="23" t="n">
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>7736.1</x:v>
+        <x:v>7789.21</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
         <x:v>7621.65</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>7733.9</x:v>
+        <x:v>7698.05</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
         <x:f>ROUND(F35-F34,1)</x:f>
-        <x:v>54.4</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.00707986035603736</x:v>
+        <x:v>0.002411605918591464</x:v>
       </x:c>
       <x:c r="I35" s="23" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
-        <x:v>114.5</x:v>
+        <x:v>167.6</x:v>
       </x:c>
       <x:c r="J35" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K35" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -8101,7 +8137,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="32" t="n">
         <x:f>ROUND(SUM(I5:I35),1)</x:f>
-        <x:v>12826.4</x:v>
+        <x:v>12879.5</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -8119,7 +8155,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I35),0),1)</x:f>
-        <x:v>413.8</x:v>
+        <x:v>415.5</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -9313,37 +9349,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C71" s="23" t="n">
         <x:v>8003.92</x:v>
       </x:c>
       <x:c r="D71" s="23" t="n">
-        <x:v>8031.16</x:v>
+        <x:v>8078.36</x:v>
       </x:c>
       <x:c r="E71" s="23" t="n">
         <x:v>7910.84</x:v>
       </x:c>
       <x:c r="F71" s="23" t="n">
-        <x:v>8030.95</x:v>
+        <x:v>7967.54</x:v>
       </x:c>
       <x:c r="G71" s="23" t="n">
         <x:f>ROUND(F71-F70,1)</x:f>
-        <x:v>50.8</x:v>
+        <x:v>-12.6</x:v>
       </x:c>
       <x:c r="H71" s="24" t="n">
         <x:f>IFERROR(F71/F70-1,"")</x:f>
-        <x:v>0.0063695784023298785</x:v>
-      </x:c>
-      <x:c r="I71" s="23" t="n">
+        <x:v>-0.0015764173972321327</x:v>
+      </x:c>
+      <x:c r="I71" s="26" t="n">
         <x:f>ROUND(D71-E71,1)</x:f>
-        <x:v>120.3</x:v>
+        <x:v>167.5</x:v>
       </x:c>
       <x:c r="J71" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K71" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -9361,7 +9397,7 @@
       <x:c r="H72" s="30"/>
       <x:c r="I72" s="32" t="n">
         <x:f>ROUND(SUM(I41:I71),1)</x:f>
-        <x:v>13000.6</x:v>
+        <x:v>13047.8</x:v>
       </x:c>
       <x:c r="J72" s="30"/>
       <x:c r="K72" s="30"/>
@@ -9379,7 +9415,7 @@
       <x:c r="H73" s="30"/>
       <x:c r="I73" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I41:I71),0),1)</x:f>
-        <x:v>419.4</x:v>
+        <x:v>420.9</x:v>
       </x:c>
       <x:c r="J73" s="30"/>
       <x:c r="K73" s="30"/>
@@ -10573,7 +10609,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B107" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C107" s="23" t="n">
         <x:v>3943.82</x:v>
@@ -10582,28 +10618,28 @@
         <x:v>3967.59</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>3938.63</x:v>
+        <x:v>3930.64</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>3966.59</x:v>
+        <x:v>3934.09</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
         <x:f>ROUND(F107-F106,1)</x:f>
-        <x:v>26.6</x:v>
+        <x:v>-5.9</x:v>
       </x:c>
       <x:c r="H107" s="24" t="n">
         <x:f>IFERROR(F107/F106-1,"")</x:f>
-        <x:v>0.0067385102689312415</x:v>
+        <x:v>-0.0015101369529242348</x:v>
       </x:c>
       <x:c r="I107" s="23" t="n">
         <x:f>ROUND(D107-E107,1)</x:f>
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J107" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K107" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10621,7 +10657,7 @@
       <x:c r="H108" s="30"/>
       <x:c r="I108" s="32" t="n">
         <x:f>ROUND(SUM(I77:I107),1)</x:f>
-        <x:v>3408.2</x:v>
+        <x:v>3416.2</x:v>
       </x:c>
       <x:c r="J108" s="30"/>
       <x:c r="K108" s="30"/>
@@ -10639,7 +10675,7 @@
       <x:c r="H109" s="30"/>
       <x:c r="I109" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I77:I107),0),1)</x:f>
-        <x:v>109.9</x:v>
+        <x:v>110.2</x:v>
       </x:c>
       <x:c r="J109" s="30"/>
       <x:c r="K109" s="30"/>
@@ -16873,37 +16909,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
         <x:v>140500</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>146380</x:v>
+        <x:v>146680</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
         <x:v>139280</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>146360</x:v>
+        <x:v>145860</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>6360</x:v>
+        <x:v>5860</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.045428571428571374</x:v>
+        <x:v>0.041857142857142815</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>7100</x:v>
+        <x:v>7400</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K287" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -16921,7 +16957,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="32" t="n">
         <x:f>ROUND(SUM(I257:I287),1)</x:f>
-        <x:v>659960</x:v>
+        <x:v>660260</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -16939,7 +16975,7 @@
       <x:c r="H289" s="30"/>
       <x:c r="I289" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I287),0),1)</x:f>
-        <x:v>21289</x:v>
+        <x:v>21298.7</x:v>
       </x:c>
       <x:c r="J289" s="30"/>
       <x:c r="K289" s="30"/>
@@ -22869,30 +22905,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>1032</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>7686.04</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>7789.21</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>7642.44</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>7698.05</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-35.8</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.004635436196485543</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>146.8</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -22900,11 +22954,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>172</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>1178.8</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>168.4</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -28831,30 +28903,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>1060.4</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>7979.28</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>8078.36</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>7947.67</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>7967.54</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-63.4</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.007895703497095563</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>130.7</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -28862,11 +28952,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>176.7</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>1191.1</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>170.2</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34793,30 +34901,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>253.8</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>3950.71</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>3966.39</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>3930.64</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>3934.09</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-32.5</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.008193435671445704</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>35.8</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -34824,11 +34950,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>42.3</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>289.6</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>41.4</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra4d49b8a457b44c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R69891bfb8e1d48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rbf478be00e9249bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Recf8f442d2184be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbb2ac3eb24134823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3e2e7633bf424fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R39fe5e046cfe422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ref1f2cdbec864bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcfc539cf86c8491a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rdfba0e6ac5b24bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb285e14b1ec4445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rdcd825c43b814f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb422a9c899cb44db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R00d02abc353045fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R03f6f280be524b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra8775c8d851f4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8b1cb2c01bee4dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3db5759e6f0b48c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4be49efcf05e41c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rc8c5707cd4234bfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7631.2</x:v>
+        <x:v>7692</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7525</x:v>
+        <x:v>7547.2</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>106.2</x:v>
+        <x:v>144.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>27848.8</x:v>
+        <x:v>27993.6</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>192.1</x:v>
+        <x:v>191.7</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7918</x:v>
+        <x:v>7963.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7795.8</x:v>
+        <x:v>7830</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>122.2</x:v>
+        <x:v>133.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29223.8</x:v>
+        <x:v>29357.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>201.5</x:v>
+        <x:v>201.1</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4663</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4611</x:v>
+        <x:v>4617.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>52</x:v>
+        <x:v>47.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10940</x:v>
+        <x:v>10987.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.4</x:v>
+        <x:v>75.3</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2949.6</x:v>
+        <x:v>2942.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2927.8</x:v>
+        <x:v>2904.6</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>21.8</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6086.4</x:v>
+        <x:v>6124.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>42</x:v>
+        <x:v>41.9</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -11869,37 +11869,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B143" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C143" s="23" t="n">
         <x:v>7628.8</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>7631.2</x:v>
+        <x:v>7692</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
         <x:v>7525</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>7607.2</x:v>
+        <x:v>7613.2</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
         <x:f>ROUND(F143-F142,1)</x:f>
-        <x:v>16.6</x:v>
+        <x:v>22.6</x:v>
       </x:c>
       <x:c r="H143" s="24" t="n">
         <x:f>IFERROR(F143/F142-1,"")</x:f>
-        <x:v>0.002186915395357314</x:v>
+        <x:v>0.0029773667430768036</x:v>
       </x:c>
       <x:c r="I143" s="23" t="n">
         <x:f>ROUND(D143-E143,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="J143" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K143" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -11917,7 +11917,7 @@
       <x:c r="H144" s="30"/>
       <x:c r="I144" s="32" t="n">
         <x:f>ROUND(SUM(I113:I143),1)</x:f>
-        <x:v>13454.4</x:v>
+        <x:v>13515.2</x:v>
       </x:c>
       <x:c r="J144" s="30"/>
       <x:c r="K144" s="30"/>
@@ -11935,7 +11935,7 @@
       <x:c r="H145" s="30"/>
       <x:c r="I145" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I113:I143),0),1)</x:f>
-        <x:v>434</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="J145" s="30"/>
       <x:c r="K145" s="30"/>
@@ -13129,37 +13129,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7888</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7918</x:v>
+        <x:v>7963.8</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
         <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7881.4</x:v>
+        <x:v>7872</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>3.6</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>0.0004569803752316748</x:v>
-      </x:c>
-      <x:c r="I179" s="23" t="n">
+        <x:v>-0.0007362461600954884</x:v>
+      </x:c>
+      <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>122.2</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -13177,7 +13177,7 @@
       <x:c r="H180" s="30"/>
       <x:c r="I180" s="32" t="n">
         <x:f>ROUND(SUM(I149:I179),1)</x:f>
-        <x:v>14118.8</x:v>
+        <x:v>14164.6</x:v>
       </x:c>
       <x:c r="J180" s="30"/>
       <x:c r="K180" s="30"/>
@@ -13195,7 +13195,7 @@
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I149:I179),0),1)</x:f>
-        <x:v>455.4</x:v>
+        <x:v>456.9</x:v>
       </x:c>
       <x:c r="J181" s="30"/>
       <x:c r="K181" s="30"/>
@@ -14389,37 +14389,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
         <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4663</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
         <x:v>4611</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4644.6</x:v>
+        <x:v>4625</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-1</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.00021525744790773516</x:v>
+        <x:v>-0.004434303426898656</x:v>
       </x:c>
       <x:c r="I215" s="23" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K215" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -14437,7 +14437,7 @@
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="32" t="n">
         <x:f>ROUND(SUM(I185:I215),1)</x:f>
-        <x:v>5019.2</x:v>
+        <x:v>5021.2</x:v>
       </x:c>
       <x:c r="J216" s="30"/>
       <x:c r="K216" s="30"/>
@@ -14455,7 +14455,7 @@
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I185:I215),0),1)</x:f>
-        <x:v>161.9</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J217" s="30"/>
       <x:c r="K217" s="30"/>
@@ -15649,7 +15649,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>8月10日</x:v>
+        <x:v>8月10日-8月11日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>2930</x:v>
@@ -15658,28 +15658,28 @@
         <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2927.8</x:v>
+        <x:v>2904.6</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2909</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>6</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>0.0020477815699657675</x:v>
+        <x:v>-0.0071672354948805195</x:v>
       </x:c>
       <x:c r="I251" s="23" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>21.8</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -15697,7 +15697,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I221:I251),1)</x:f>
-        <x:v>2839.4</x:v>
+        <x:v>2862.6</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -15715,7 +15715,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I221:I251),0),1)</x:f>
-        <x:v>91.6</x:v>
+        <x:v>92.3</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -40899,30 +40899,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>7588</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>7692</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>7547.2</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>7613.2</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>1021</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="I185" s="24" t="n">
+        <x:v>0.000788726469660217</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>144.8</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -40930,11 +40948,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>170.2</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>1165.8</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>166.5</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -46861,30 +46897,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>1051.2</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>7864.2</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>7963.8</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>7830</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>7872</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.0011926815032862192</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>133.8</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -46892,11 +46946,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>175.2</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>169.3</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -52823,30 +52895,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>380.4</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>4642.8</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>4665</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>4617.2</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>4625</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-19.6</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.004219954355595856</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>47.8</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -52854,11 +52944,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>63.4</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>428.2</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>61.2</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -58785,30 +58893,48 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B185" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C185" s="30"/>
-      <x:c r="D185" s="30"/>
-      <x:c r="E185" s="30"/>
-      <x:c r="F185" s="30"/>
-      <x:c r="G185" s="30"/>
-      <x:c r="H185" s="30"/>
-      <x:c r="I185" s="30"/>
-      <x:c r="J185" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J184),1)</x:f>
-        <x:v>208.6</x:v>
-      </x:c>
-      <x:c r="K185" s="30"/>
+      <x:c r="A185" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B185" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C185" s="22" t="str">
+        <x:v>8月11日</x:v>
+      </x:c>
+      <x:c r="D185" s="23" t="n">
+        <x:v>2931.8</x:v>
+      </x:c>
+      <x:c r="E185" s="23" t="n">
+        <x:v>2942.8</x:v>
+      </x:c>
+      <x:c r="F185" s="23" t="n">
+        <x:v>2904.6</x:v>
+      </x:c>
+      <x:c r="G185" s="23" t="n">
+        <x:v>2909</x:v>
+      </x:c>
+      <x:c r="H185" s="23" t="n">
+        <x:v>-27</x:v>
+      </x:c>
+      <x:c r="I185" s="24" t="n">
+        <x:v>-0.009196185286103553</x:v>
+      </x:c>
+      <x:c r="J185" s="23" t="n">
+        <x:f>ROUND(E185-F185,1)</x:f>
+        <x:v>38.2</x:v>
+      </x:c>
+      <x:c r="K185" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B186" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B186" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C186" s="30"/>
       <x:c r="D186" s="30"/>
       <x:c r="E186" s="30"/>
@@ -58816,11 +58942,29 @@
       <x:c r="G186" s="30"/>
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="30"/>
-      <x:c r="J186" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J184),0),1)</x:f>
-        <x:v>34.8</x:v>
+      <x:c r="J186" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J185),1)</x:f>
+        <x:v>246.8</x:v>
       </x:c>
       <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B187" s="30"/>
+      <x:c r="C187" s="30"/>
+      <x:c r="D187" s="30"/>
+      <x:c r="E187" s="30"/>
+      <x:c r="F187" s="30"/>
+      <x:c r="G187" s="30"/>
+      <x:c r="H187" s="30"/>
+      <x:c r="I187" s="30"/>
+      <x:c r="J187" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
+        <x:v>35.3</x:v>
+      </x:c>
+      <x:c r="K187" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb285e14b1ec4445f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rdcd825c43b814f10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb422a9c899cb44db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R00d02abc353045fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R03f6f280be524b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra8775c8d851f4dca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8b1cb2c01bee4dfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3db5759e6f0b48c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4be49efcf05e41c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rc8c5707cd4234bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd611034b1d21464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R21377fbe01354795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R986d9281d74342a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re0bcd187e05b4037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9428f0a6cd1c414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc0149c5450314b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rc37c1e0e9bf247e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R5b9742fe3b1c442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R648244f45e464552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Ref8107d6facb4095"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7789.21</x:v>
+        <x:v>7805.27</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7642.44</x:v>
+        <x:v>7692.44</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>146.8</x:v>
+        <x:v>112.8</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>26294.7</x:v>
+        <x:v>26407.5</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.1</x:v>
+        <x:v>179.6</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8078.36</x:v>
+        <x:v>8067.53</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7947.67</x:v>
+        <x:v>7961.83</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>130.7</x:v>
+        <x:v>105.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>26487.1</x:v>
+        <x:v>26592.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>181.4</x:v>
+        <x:v>180.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3966.39</x:v>
+        <x:v>3950.62</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3930.64</x:v>
+        <x:v>3927.55</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>35.8</x:v>
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7264.9</x:v>
+        <x:v>7288</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.8</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7692</x:v>
+        <x:v>7712.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7547.2</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>144.8</x:v>
+        <x:v>112.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>27993.6</x:v>
+        <x:v>28106.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>191.7</x:v>
+        <x:v>191.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8089,37 +8089,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C35" s="23" t="n">
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>7789.21</x:v>
+        <x:v>7805.27</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
         <x:v>7621.65</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>7698.05</x:v>
+        <x:v>7793.72</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
         <x:f>ROUND(F35-F34,1)</x:f>
-        <x:v>18.5</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.002411605918591464</x:v>
-      </x:c>
-      <x:c r="I35" s="23" t="n">
+        <x:v>0.014869399559608532</x:v>
+      </x:c>
+      <x:c r="I35" s="26" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
-        <x:v>167.6</x:v>
+        <x:v>183.6</x:v>
       </x:c>
       <x:c r="J35" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K35" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -8137,7 +8137,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="32" t="n">
         <x:f>ROUND(SUM(I5:I35),1)</x:f>
-        <x:v>12879.5</x:v>
+        <x:v>12895.5</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -8155,7 +8155,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I35),0),1)</x:f>
-        <x:v>415.5</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -9349,7 +9349,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C71" s="23" t="n">
         <x:v>8003.92</x:v>
@@ -9361,15 +9361,15 @@
         <x:v>7910.84</x:v>
       </x:c>
       <x:c r="F71" s="23" t="n">
-        <x:v>7967.54</x:v>
+        <x:v>8045.31</x:v>
       </x:c>
       <x:c r="G71" s="23" t="n">
         <x:f>ROUND(F71-F70,1)</x:f>
-        <x:v>-12.6</x:v>
+        <x:v>65.2</x:v>
       </x:c>
       <x:c r="H71" s="24" t="n">
         <x:f>IFERROR(F71/F70-1,"")</x:f>
-        <x:v>-0.0015764173972321327</x:v>
+        <x:v>0.00816905008947244</x:v>
       </x:c>
       <x:c r="I71" s="26" t="n">
         <x:f>ROUND(D71-E71,1)</x:f>
@@ -9379,7 +9379,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K71" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -10609,7 +10609,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B107" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C107" s="23" t="n">
         <x:v>3943.82</x:v>
@@ -10618,28 +10618,28 @@
         <x:v>3967.59</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>3930.64</x:v>
+        <x:v>3927.55</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>3934.09</x:v>
+        <x:v>3946.68</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
         <x:f>ROUND(F107-F106,1)</x:f>
-        <x:v>-5.9</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="H107" s="24" t="n">
         <x:f>IFERROR(F107/F106-1,"")</x:f>
-        <x:v>-0.0015101369529242348</x:v>
+        <x:v>0.001685262078557459</x:v>
       </x:c>
       <x:c r="I107" s="23" t="n">
         <x:f>ROUND(D107-E107,1)</x:f>
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J107" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K107" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10657,7 +10657,7 @@
       <x:c r="H108" s="30"/>
       <x:c r="I108" s="32" t="n">
         <x:f>ROUND(SUM(I77:I107),1)</x:f>
-        <x:v>3416.2</x:v>
+        <x:v>3419.2</x:v>
       </x:c>
       <x:c r="J108" s="30"/>
       <x:c r="K108" s="30"/>
@@ -10675,7 +10675,7 @@
       <x:c r="H109" s="30"/>
       <x:c r="I109" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I77:I107),0),1)</x:f>
-        <x:v>110.2</x:v>
+        <x:v>110.3</x:v>
       </x:c>
       <x:c r="J109" s="30"/>
       <x:c r="K109" s="30"/>
@@ -11869,37 +11869,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B143" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C143" s="23" t="n">
         <x:v>7628.8</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>7692</x:v>
+        <x:v>7712.8</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
         <x:v>7525</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>7613.2</x:v>
+        <x:v>7677.4</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
         <x:f>ROUND(F143-F142,1)</x:f>
-        <x:v>22.6</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H143" s="24" t="n">
         <x:f>IFERROR(F143/F142-1,"")</x:f>
-        <x:v>0.0029773667430768036</x:v>
+        <x:v>0.011435196163676054</x:v>
       </x:c>
       <x:c r="I143" s="23" t="n">
         <x:f>ROUND(D143-E143,1)</x:f>
-        <x:v>167</x:v>
+        <x:v>187.8</x:v>
       </x:c>
       <x:c r="J143" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K143" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -11917,7 +11917,7 @@
       <x:c r="H144" s="30"/>
       <x:c r="I144" s="32" t="n">
         <x:f>ROUND(SUM(I113:I143),1)</x:f>
-        <x:v>13515.2</x:v>
+        <x:v>13536</x:v>
       </x:c>
       <x:c r="J144" s="30"/>
       <x:c r="K144" s="30"/>
@@ -11935,7 +11935,7 @@
       <x:c r="H145" s="30"/>
       <x:c r="I145" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I113:I143),0),1)</x:f>
-        <x:v>436</x:v>
+        <x:v>436.6</x:v>
       </x:c>
       <x:c r="J145" s="30"/>
       <x:c r="K145" s="30"/>
@@ -22941,30 +22941,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>1178.8</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>7704.96</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>7805.27</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>7692.44</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>7793.72</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>95.7</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.012427822630406427</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>112.8</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -22972,11 +22990,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>168.4</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>1291.6</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>161.5</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -28939,30 +28975,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>1191.1</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>7978.04</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>8067.53</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>7961.83</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>8045.31</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>77.8</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.009760854667814733</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>105.7</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -28970,11 +29024,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>170.2</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>1296.8</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>162.1</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34937,30 +35009,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>289.6</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>3933.55</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>3950.62</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>3927.55</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>3946.68</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>12.6</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.0032002318198107726</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>23.1</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -34968,11 +35058,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>41.4</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>312.7</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>39.1</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40935,30 +41043,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>1165.8</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>7633.2</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>7712.8</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>7600</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>7677.4</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>64.2</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.008432722114222635</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>112.8</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -40966,11 +41092,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>166.5</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>1278.6</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>159.8</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd611034b1d21464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R21377fbe01354795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R986d9281d74342a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re0bcd187e05b4037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9428f0a6cd1c414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc0149c5450314b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rc37c1e0e9bf247e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R5b9742fe3b1c442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R648244f45e464552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Ref8107d6facb4095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5c5c6ee3489245b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd2e6d80560f14424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R754262708577473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc869301f7b4f40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4c67b9f40d3d4c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2b0b607e3e79453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R9d78544e4fdb4655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd30cdfcde11b4ae1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R0c7ccb41be8347bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R311b4386d5a948e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7963.8</x:v>
+        <x:v>7971.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7830</x:v>
+        <x:v>7859</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>133.8</x:v>
+        <x:v>112.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29357.6</x:v>
+        <x:v>29470.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>201.1</x:v>
+        <x:v>200.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4665</x:v>
+        <x:v>4657.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4617.2</x:v>
+        <x:v>4616.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>47.8</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>10987.8</x:v>
+        <x:v>11028.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75.3</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2942.8</x:v>
+        <x:v>2917.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2904.6</x:v>
+        <x:v>2902</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>38.2</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6124.6</x:v>
+        <x:v>6140.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.9</x:v>
+        <x:v>41.8</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>146680</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>143500</x:v>
+        <x:v>146060</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>3180</x:v>
+        <x:v>4820</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1286700</x:v>
+        <x:v>1291520</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8813</x:v>
+        <x:v>8785.9</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -6825,30 +6825,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>35380</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>146200</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>150880</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>146060</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>149700</x:v>
+      </x:c>
+      <x:c r="H186" s="28" t="n">
+        <x:v>3840</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.026326614561908768</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>4820</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -6856,11 +6874,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>5054.3</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>40200</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>5025</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13129,37 +13165,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7888</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7963.8</x:v>
+        <x:v>7971.8</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
         <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7872</x:v>
+        <x:v>7914.2</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>-5.8</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>-0.0007362461600954884</x:v>
+        <x:v>0.004620579349564613</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>168</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -13177,7 +13213,7 @@
       <x:c r="H180" s="30"/>
       <x:c r="I180" s="32" t="n">
         <x:f>ROUND(SUM(I149:I179),1)</x:f>
-        <x:v>14164.6</x:v>
+        <x:v>14172.6</x:v>
       </x:c>
       <x:c r="J180" s="30"/>
       <x:c r="K180" s="30"/>
@@ -13195,7 +13231,7 @@
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I149:I179),0),1)</x:f>
-        <x:v>456.9</x:v>
+        <x:v>457.2</x:v>
       </x:c>
       <x:c r="J181" s="30"/>
       <x:c r="K181" s="30"/>
@@ -14389,7 +14425,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
         <x:v>4656.8</x:v>
@@ -14401,15 +14437,15 @@
         <x:v>4611</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4625</x:v>
+        <x:v>4641</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-20.6</x:v>
+        <x:v>-4.6</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.004434303426898656</x:v>
+        <x:v>-0.0009901842603754485</x:v>
       </x:c>
       <x:c r="I215" s="23" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
@@ -14419,7 +14455,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K215" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -15649,7 +15685,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>2930</x:v>
@@ -15658,28 +15694,28 @@
         <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2904.6</x:v>
+        <x:v>2902</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2909</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-21</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.0071672354948805195</x:v>
+        <x:v>-0.0068259385665528916</x:v>
       </x:c>
       <x:c r="I251" s="23" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>45</x:v>
+        <x:v>47.6</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -15697,7 +15733,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I221:I251),1)</x:f>
-        <x:v>2862.6</x:v>
+        <x:v>2865.2</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -15715,7 +15751,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I221:I251),0),1)</x:f>
-        <x:v>92.3</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -16909,37 +16945,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>8月10日-8月11日</x:v>
+        <x:v>8月10日-8月12日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
         <x:v>140500</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>146680</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
         <x:v>139280</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>149700</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>5860</x:v>
+        <x:v>9700</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.041857142857142815</x:v>
+        <x:v>0.0692857142857144</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>7400</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K287" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -16957,7 +16993,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="32" t="n">
         <x:f>ROUND(SUM(I257:I287),1)</x:f>
-        <x:v>660260</x:v>
+        <x:v>664460</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -16975,7 +17011,7 @@
       <x:c r="H289" s="30"/>
       <x:c r="I289" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I287),0),1)</x:f>
-        <x:v>21298.7</x:v>
+        <x:v>21434.2</x:v>
       </x:c>
       <x:c r="J289" s="30"/>
       <x:c r="K289" s="30"/>
@@ -47077,30 +47113,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>1185</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>7890</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>7971.8</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>7859</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>7914.2</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>42.2</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.005360772357723587</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>112.8</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -47108,11 +47162,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>169.3</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>1297.8</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>162.2</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -53075,30 +53147,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>428.2</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>4627</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>4657.2</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>4616.8</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>4641</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.0034594594594594685</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>40.4</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -53106,11 +53196,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>61.2</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>468.6</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>58.6</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59073,30 +59181,48 @@
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B186" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C186" s="30"/>
-      <x:c r="D186" s="30"/>
-      <x:c r="E186" s="30"/>
-      <x:c r="F186" s="30"/>
-      <x:c r="G186" s="30"/>
-      <x:c r="H186" s="30"/>
-      <x:c r="I186" s="30"/>
-      <x:c r="J186" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J185),1)</x:f>
-        <x:v>246.8</x:v>
-      </x:c>
-      <x:c r="K186" s="30"/>
+      <x:c r="A186" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B186" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C186" s="22" t="str">
+        <x:v>8月12日</x:v>
+      </x:c>
+      <x:c r="D186" s="23" t="n">
+        <x:v>2911.2</x:v>
+      </x:c>
+      <x:c r="E186" s="23" t="n">
+        <x:v>2917.8</x:v>
+      </x:c>
+      <x:c r="F186" s="23" t="n">
+        <x:v>2902</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
+        <x:v>2910</x:v>
+      </x:c>
+      <x:c r="H186" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I186" s="24" t="n">
+        <x:v>0.00034376074252318034</x:v>
+      </x:c>
+      <x:c r="J186" s="23" t="n">
+        <x:f>ROUND(E186-F186,1)</x:f>
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="K186" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B187" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B187" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C187" s="30"/>
       <x:c r="D187" s="30"/>
       <x:c r="E187" s="30"/>
@@ -59104,11 +59230,29 @@
       <x:c r="G187" s="30"/>
       <x:c r="H187" s="30"/>
       <x:c r="I187" s="30"/>
-      <x:c r="J187" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J185),0),1)</x:f>
-        <x:v>35.3</x:v>
+      <x:c r="J187" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J186),1)</x:f>
+        <x:v>262.6</x:v>
       </x:c>
       <x:c r="K187" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B188" s="30"/>
+      <x:c r="C188" s="30"/>
+      <x:c r="D188" s="30"/>
+      <x:c r="E188" s="30"/>
+      <x:c r="F188" s="30"/>
+      <x:c r="G188" s="30"/>
+      <x:c r="H188" s="30"/>
+      <x:c r="I188" s="30"/>
+      <x:c r="J188" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+        <x:v>32.8</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5c5c6ee3489245b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd2e6d80560f14424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R754262708577473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc869301f7b4f40f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4c67b9f40d3d4c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2b0b607e3e79453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R9d78544e4fdb4655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd30cdfcde11b4ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R0c7ccb41be8347bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R311b4386d5a948e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3c6364c069e84c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1b1899a7377446e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0ae0fcb87535496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf276232ccbb84b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcef5c25a288043ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R49b0e217198d48a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R01fefb088c0e4609"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R46f4254cb98b41c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rc2e5a74ecf864c93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb5b308309ff14594"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,22 +519,22 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7805.27</x:v>
+        <x:v>7880.22</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7692.44</x:v>
+        <x:v>7714.37</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>112.8</x:v>
+        <x:v>165.9</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>26407.5</x:v>
+        <x:v>26573.4</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
         <x:v>179.6</x:v>
@@ -548,22 +548,22 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8067.53</x:v>
+        <x:v>8142.33</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7961.83</x:v>
+        <x:v>7966.87</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>105.7</x:v>
+        <x:v>175.5</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>26592.8</x:v>
+        <x:v>26768.3</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
         <x:v>180.9</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3950.62</x:v>
+        <x:v>3968.48</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3927.55</x:v>
+        <x:v>3924.64</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>23.1</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7288</x:v>
+        <x:v>7331.8</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.6</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>150880</x:v>
+        <x:v>152440</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>146060</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4820</x:v>
+        <x:v>5340</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1291520</x:v>
+        <x:v>1296860</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8785.9</x:v>
+        <x:v>8762.6</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6861,30 +6861,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>40200</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>150100</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>152440</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>147100</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>151420</x:v>
+      </x:c>
+      <x:c r="H187" s="28" t="n">
+        <x:v>1720</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>0.011489645958583816</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>5340</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -6892,11 +6910,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>5025</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>45540</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>5060</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8125,37 +8161,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C35" s="23" t="n">
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>7805.27</x:v>
+        <x:v>7880.22</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
         <x:v>7621.65</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>7793.72</x:v>
+        <x:v>7715.89</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
         <x:f>ROUND(F35-F34,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.014869399559608532</x:v>
+        <x:v>0.0047346647516191</x:v>
       </x:c>
       <x:c r="I35" s="26" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
-        <x:v>183.6</x:v>
+        <x:v>258.6</x:v>
       </x:c>
       <x:c r="J35" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K35" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -8173,7 +8209,7 @@
       <x:c r="H36" s="30"/>
       <x:c r="I36" s="32" t="n">
         <x:f>ROUND(SUM(I5:I35),1)</x:f>
-        <x:v>12895.5</x:v>
+        <x:v>12970.5</x:v>
       </x:c>
       <x:c r="J36" s="30"/>
       <x:c r="K36" s="30"/>
@@ -8191,7 +8227,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I35),0),1)</x:f>
-        <x:v>416</x:v>
+        <x:v>418.4</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -9385,37 +9421,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C71" s="23" t="n">
         <x:v>8003.92</x:v>
       </x:c>
       <x:c r="D71" s="23" t="n">
-        <x:v>8078.36</x:v>
+        <x:v>8142.33</x:v>
       </x:c>
       <x:c r="E71" s="23" t="n">
         <x:v>7910.84</x:v>
       </x:c>
       <x:c r="F71" s="23" t="n">
-        <x:v>8045.31</x:v>
+        <x:v>7968.38</x:v>
       </x:c>
       <x:c r="G71" s="23" t="n">
         <x:f>ROUND(F71-F70,1)</x:f>
-        <x:v>65.2</x:v>
+        <x:v>-11.7</x:v>
       </x:c>
       <x:c r="H71" s="24" t="n">
         <x:f>IFERROR(F71/F70-1,"")</x:f>
-        <x:v>0.00816905008947244</x:v>
+        <x:v>-0.0014711558222182397</x:v>
       </x:c>
       <x:c r="I71" s="26" t="n">
         <x:f>ROUND(D71-E71,1)</x:f>
-        <x:v>167.5</x:v>
+        <x:v>231.5</x:v>
       </x:c>
       <x:c r="J71" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K71" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -9433,7 +9469,7 @@
       <x:c r="H72" s="30"/>
       <x:c r="I72" s="32" t="n">
         <x:f>ROUND(SUM(I41:I71),1)</x:f>
-        <x:v>13047.8</x:v>
+        <x:v>13111.8</x:v>
       </x:c>
       <x:c r="J72" s="30"/>
       <x:c r="K72" s="30"/>
@@ -9451,7 +9487,7 @@
       <x:c r="H73" s="30"/>
       <x:c r="I73" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I41:I71),0),1)</x:f>
-        <x:v>420.9</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="J73" s="30"/>
       <x:c r="K73" s="30"/>
@@ -10645,37 +10681,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B107" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C107" s="23" t="n">
         <x:v>3943.82</x:v>
       </x:c>
       <x:c r="D107" s="23" t="n">
-        <x:v>3967.59</x:v>
+        <x:v>3968.48</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>3927.55</x:v>
+        <x:v>3924.64</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>3946.68</x:v>
+        <x:v>3926.96</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
         <x:f>ROUND(F107-F106,1)</x:f>
-        <x:v>6.6</x:v>
+        <x:v>-13.1</x:v>
       </x:c>
       <x:c r="H107" s="24" t="n">
         <x:f>IFERROR(F107/F106-1,"")</x:f>
-        <x:v>0.001685262078557459</x:v>
+        <x:v>-0.0033197632511344777</x:v>
       </x:c>
       <x:c r="I107" s="23" t="n">
         <x:f>ROUND(D107-E107,1)</x:f>
-        <x:v>40</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J107" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K107" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10693,7 +10729,7 @@
       <x:c r="H108" s="30"/>
       <x:c r="I108" s="32" t="n">
         <x:f>ROUND(SUM(I77:I107),1)</x:f>
-        <x:v>3419.2</x:v>
+        <x:v>3423</x:v>
       </x:c>
       <x:c r="J108" s="30"/>
       <x:c r="K108" s="30"/>
@@ -10711,7 +10747,7 @@
       <x:c r="H109" s="30"/>
       <x:c r="I109" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I77:I107),0),1)</x:f>
-        <x:v>110.3</x:v>
+        <x:v>110.4</x:v>
       </x:c>
       <x:c r="J109" s="30"/>
       <x:c r="K109" s="30"/>
@@ -16945,37 +16981,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
         <x:v>140500</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>152440</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
         <x:v>139280</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>149700</x:v>
+        <x:v>151420</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>9700</x:v>
+        <x:v>11420</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.0692857142857144</x:v>
+        <x:v>0.08157142857142863</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>11600</x:v>
+        <x:v>13160</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K287" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -16993,7 +17029,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="32" t="n">
         <x:f>ROUND(SUM(I257:I287),1)</x:f>
-        <x:v>664460</x:v>
+        <x:v>666020</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -17011,7 +17047,7 @@
       <x:c r="H289" s="30"/>
       <x:c r="I289" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I287),0),1)</x:f>
-        <x:v>21434.2</x:v>
+        <x:v>21484.5</x:v>
       </x:c>
       <x:c r="J289" s="30"/>
       <x:c r="K289" s="30"/>
@@ -23013,30 +23049,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>1291.6</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>7847.24</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>7880.22</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>7714.37</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>7715.89</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-77.8</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.009986245335988464</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>165.9</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -23044,11 +23098,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>161.5</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>1457.5</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>161.9</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29047,30 +29119,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>1296.8</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>8096.85</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>8142.33</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>7966.87</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>7968.38</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-76.9</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.009562092697484648</x:v>
+      </x:c>
+      <x:c r="J187" s="26" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>175.5</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -29078,11 +29168,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>162.1</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>1472.3</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>163.6</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35081,30 +35189,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>312.7</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>3957.16</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>3968.48</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>3924.64</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>3926.96</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-19.7</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.004996604741200117</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>43.8</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -35112,11 +35238,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>39.1</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>356.5</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>39.6</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3c6364c069e84c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1b1899a7377446e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0ae0fcb87535496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf276232ccbb84b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcef5c25a288043ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R49b0e217198d48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R01fefb088c0e4609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R46f4254cb98b41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rc2e5a74ecf864c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb5b308309ff14594"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra0ca5ec7c98f496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R0c11bc70eb56492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rf6a2ba028117428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R08bb2a3eaa5a4ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4459ebdc933b4e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re9fc0955169d4632"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R927173a7576d4775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R421c5e674af0492c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rb5e2f2ec828c4a44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7d24ad0e07ac4a58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7712.8</x:v>
+        <x:v>7776</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7600</x:v>
+        <x:v>7627</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>112.8</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>28106.4</x:v>
+        <x:v>28255.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>191.2</x:v>
+        <x:v>190.9</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7971.8</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7859</x:v>
+        <x:v>7860.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>112.8</x:v>
+        <x:v>163.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29470.4</x:v>
+        <x:v>29633.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>200.5</x:v>
+        <x:v>200.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4657.2</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4616.8</x:v>
+        <x:v>4621.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>40.4</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11028.2</x:v>
+        <x:v>11087.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>75</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2917.8</x:v>
+        <x:v>2933.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2902</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>15.8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6140.4</x:v>
+        <x:v>6173.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.8</x:v>
+        <x:v>41.7</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -11941,37 +11941,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B143" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C143" s="23" t="n">
         <x:v>7628.8</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>7712.8</x:v>
+        <x:v>7776</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
         <x:v>7525</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>7677.4</x:v>
+        <x:v>7634.2</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
         <x:f>ROUND(F143-F142,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="H143" s="24" t="n">
         <x:f>IFERROR(F143/F142-1,"")</x:f>
-        <x:v>0.011435196163676054</x:v>
-      </x:c>
-      <x:c r="I143" s="23" t="n">
+        <x:v>0.0057439464600952395</x:v>
+      </x:c>
+      <x:c r="I143" s="26" t="n">
         <x:f>ROUND(D143-E143,1)</x:f>
-        <x:v>187.8</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="J143" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K143" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -11989,7 +11989,7 @@
       <x:c r="H144" s="30"/>
       <x:c r="I144" s="32" t="n">
         <x:f>ROUND(SUM(I113:I143),1)</x:f>
-        <x:v>13536</x:v>
+        <x:v>13599.2</x:v>
       </x:c>
       <x:c r="J144" s="30"/>
       <x:c r="K144" s="30"/>
@@ -12007,7 +12007,7 @@
       <x:c r="H145" s="30"/>
       <x:c r="I145" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I113:I143),0),1)</x:f>
-        <x:v>436.6</x:v>
+        <x:v>438.7</x:v>
       </x:c>
       <x:c r="J145" s="30"/>
       <x:c r="K145" s="30"/>
@@ -13201,37 +13201,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7888</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7971.8</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
         <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7914.2</x:v>
+        <x:v>7866.2</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>36.4</x:v>
+        <x:v>-11.6</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>0.004620579349564613</x:v>
+        <x:v>-0.0014724923201909768</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>176</x:v>
+        <x:v>228.2</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -13249,7 +13249,7 @@
       <x:c r="H180" s="30"/>
       <x:c r="I180" s="32" t="n">
         <x:f>ROUND(SUM(I149:I179),1)</x:f>
-        <x:v>14172.6</x:v>
+        <x:v>14224.8</x:v>
       </x:c>
       <x:c r="J180" s="30"/>
       <x:c r="K180" s="30"/>
@@ -13267,7 +13267,7 @@
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I149:I179),0),1)</x:f>
-        <x:v>457.2</x:v>
+        <x:v>458.9</x:v>
       </x:c>
       <x:c r="J181" s="30"/>
       <x:c r="K181" s="30"/>
@@ -14461,37 +14461,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
         <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
         <x:v>4611</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4641</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-4.6</x:v>
+        <x:v>-21.6</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.0009901842603754485</x:v>
+        <x:v>-0.004649560874806391</x:v>
       </x:c>
       <x:c r="I215" s="23" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K215" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -14509,7 +14509,7 @@
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="32" t="n">
         <x:f>ROUND(SUM(I185:I215),1)</x:f>
-        <x:v>5021.2</x:v>
+        <x:v>5037.2</x:v>
       </x:c>
       <x:c r="J216" s="30"/>
       <x:c r="K216" s="30"/>
@@ -14527,7 +14527,7 @@
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I185:I215),0),1)</x:f>
-        <x:v>162</x:v>
+        <x:v>162.5</x:v>
       </x:c>
       <x:c r="J217" s="30"/>
       <x:c r="K217" s="30"/>
@@ -15721,7 +15721,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>8月10日-8月12日</x:v>
+        <x:v>8月10日-8月13日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>2930</x:v>
@@ -15730,28 +15730,28 @@
         <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2902</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-20</x:v>
+        <x:v>-27.4</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.0068259385665528916</x:v>
+        <x:v>-0.009351535836177538</x:v>
       </x:c>
       <x:c r="I251" s="23" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>47.6</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -15769,7 +15769,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I221:I251),1)</x:f>
-        <x:v>2865.2</x:v>
+        <x:v>2866.6</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -15787,7 +15787,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I221:I251),0),1)</x:f>
-        <x:v>92.4</x:v>
+        <x:v>92.5</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -41259,30 +41259,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>1278.6</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>7723</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>7776</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>7627</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>7634.2</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-43.2</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.005626904941777089</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -41290,11 +41308,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>159.8</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>1427.6</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>158.6</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -47293,30 +47329,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>1297.8</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>7971</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>8024</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>7860.8</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>7866.2</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.006065047635894993</x:v>
+      </x:c>
+      <x:c r="J187" s="26" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>163.2</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -47324,11 +47378,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>162.2</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>162.3</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -53327,30 +53399,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>468.6</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>4657.8</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>4681</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>4621.4</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>4624</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-17</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.00366300366300365</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>59.6</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -53358,11 +53448,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
-        <x:v>58.6</x:v>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>528.2</x:v>
       </x:c>
       <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
+        <x:v>58.7</x:v>
+      </x:c>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59361,30 +59469,48 @@
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B187" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C187" s="30"/>
-      <x:c r="D187" s="30"/>
-      <x:c r="E187" s="30"/>
-      <x:c r="F187" s="30"/>
-      <x:c r="G187" s="30"/>
-      <x:c r="H187" s="30"/>
-      <x:c r="I187" s="30"/>
-      <x:c r="J187" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J186),1)</x:f>
-        <x:v>262.6</x:v>
-      </x:c>
-      <x:c r="K187" s="30"/>
+      <x:c r="A187" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B187" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C187" s="22" t="str">
+        <x:v>8月13日</x:v>
+      </x:c>
+      <x:c r="D187" s="23" t="n">
+        <x:v>2915.2</x:v>
+      </x:c>
+      <x:c r="E187" s="23" t="n">
+        <x:v>2933.6</x:v>
+      </x:c>
+      <x:c r="F187" s="23" t="n">
+        <x:v>2900.6</x:v>
+      </x:c>
+      <x:c r="G187" s="23" t="n">
+        <x:v>2902.6</x:v>
+      </x:c>
+      <x:c r="H187" s="23" t="n">
+        <x:v>-7.4</x:v>
+      </x:c>
+      <x:c r="I187" s="24" t="n">
+        <x:v>-0.0025429553264605387</x:v>
+      </x:c>
+      <x:c r="J187" s="23" t="n">
+        <x:f>ROUND(E187-F187,1)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K187" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B188" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B188" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C188" s="30"/>
       <x:c r="D188" s="30"/>
       <x:c r="E188" s="30"/>
@@ -59392,11 +59518,29 @@
       <x:c r="G188" s="30"/>
       <x:c r="H188" s="30"/>
       <x:c r="I188" s="30"/>
-      <x:c r="J188" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J186),0),1)</x:f>
+      <x:c r="J188" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J187),1)</x:f>
+        <x:v>295.6</x:v>
+      </x:c>
+      <x:c r="K188" s="30"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B189" s="30"/>
+      <x:c r="C189" s="30"/>
+      <x:c r="D189" s="30"/>
+      <x:c r="E189" s="30"/>
+      <x:c r="F189" s="30"/>
+      <x:c r="G189" s="30"/>
+      <x:c r="H189" s="30"/>
+      <x:c r="I189" s="30"/>
+      <x:c r="J189" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
         <x:v>32.8</x:v>
       </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="K189" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra0ca5ec7c98f496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R0c11bc70eb56492f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rf6a2ba028117428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R08bb2a3eaa5a4ba4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4459ebdc933b4e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re9fc0955169d4632"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R927173a7576d4775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R421c5e674af0492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rb5e2f2ec828c4a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7d24ad0e07ac4a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf6fde38e9200485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R170ecf44ab3c4cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb3e6d4f610784545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R369c25a06ddb4119"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6ed6671e1e6b4c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc8d047512e904f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re2e678b35bfc4b4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb368b2051ca14e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5608fe2ec08240ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rf6a3c5e2b4ba4dc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7880.22</x:v>
+        <x:v>7784.38</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7714.37</x:v>
+        <x:v>7673.44</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>165.9</x:v>
+        <x:v>110.9</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>26573.4</x:v>
+        <x:v>26684.3</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.6</x:v>
+        <x:v>179.1</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8142.33</x:v>
+        <x:v>8005.15</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7966.87</x:v>
+        <x:v>7897.24</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>175.5</x:v>
+        <x:v>107.9</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>26768.3</x:v>
+        <x:v>26876.2</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.9</x:v>
+        <x:v>180.4</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3968.48</x:v>
+        <x:v>3932.64</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3924.64</x:v>
+        <x:v>3903.7</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>43.8</x:v>
+        <x:v>28.9</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7331.8</x:v>
+        <x:v>7360.7</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.5</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7776</x:v>
+        <x:v>7695</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7627</x:v>
+        <x:v>7597.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
+        <x:v>97.4</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="n">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="n">
-        <x:v>148</x:v>
-      </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>28255.4</x:v>
+        <x:v>28352.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.9</x:v>
+        <x:v>190.3</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8024</x:v>
+        <x:v>7914</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7860.8</x:v>
+        <x:v>7802</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>163.2</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29633.6</x:v>
+        <x:v>29745.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>200.2</x:v>
+        <x:v>199.6</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2933.6</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>33</x:v>
+        <x:v>33.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6173.4</x:v>
+        <x:v>6206.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>41.7</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8161,7 +8161,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C35" s="23" t="n">
         <x:v>7723.38</x:v>
@@ -8173,15 +8173,15 @@
         <x:v>7621.65</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>7715.89</x:v>
+        <x:v>7769.82</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
         <x:f>ROUND(F35-F34,1)</x:f>
-        <x:v>36.4</x:v>
+        <x:v>90.3</x:v>
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.0047346647516191</x:v>
+        <x:v>0.011757229934644453</x:v>
       </x:c>
       <x:c r="I35" s="26" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
@@ -8191,7 +8191,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K35" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -9421,7 +9421,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C71" s="23" t="n">
         <x:v>8003.92</x:v>
@@ -9430,28 +9430,28 @@
         <x:v>8142.33</x:v>
       </x:c>
       <x:c r="E71" s="23" t="n">
-        <x:v>7910.84</x:v>
+        <x:v>7897.24</x:v>
       </x:c>
       <x:c r="F71" s="23" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7990.33</x:v>
       </x:c>
       <x:c r="G71" s="23" t="n">
         <x:f>ROUND(F71-F70,1)</x:f>
-        <x:v>-11.7</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="H71" s="24" t="n">
         <x:f>IFERROR(F71/F70-1,"")</x:f>
-        <x:v>-0.0014711558222182397</x:v>
+        <x:v>0.0012794293820144187</x:v>
       </x:c>
       <x:c r="I71" s="26" t="n">
         <x:f>ROUND(D71-E71,1)</x:f>
-        <x:v>231.5</x:v>
+        <x:v>245.1</x:v>
       </x:c>
       <x:c r="J71" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K71" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -9469,7 +9469,7 @@
       <x:c r="H72" s="30"/>
       <x:c r="I72" s="32" t="n">
         <x:f>ROUND(SUM(I41:I71),1)</x:f>
-        <x:v>13111.8</x:v>
+        <x:v>13125.4</x:v>
       </x:c>
       <x:c r="J72" s="30"/>
       <x:c r="K72" s="30"/>
@@ -9487,7 +9487,7 @@
       <x:c r="H73" s="30"/>
       <x:c r="I73" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I41:I71),0),1)</x:f>
-        <x:v>423</x:v>
+        <x:v>423.4</x:v>
       </x:c>
       <x:c r="J73" s="30"/>
       <x:c r="K73" s="30"/>
@@ -10681,7 +10681,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B107" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C107" s="23" t="n">
         <x:v>3943.82</x:v>
@@ -10690,28 +10690,28 @@
         <x:v>3968.48</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>3924.64</x:v>
+        <x:v>3903.7</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>3926.96</x:v>
+        <x:v>3927.18</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
         <x:f>ROUND(F107-F106,1)</x:f>
-        <x:v>-13.1</x:v>
+        <x:v>-12.9</x:v>
       </x:c>
       <x:c r="H107" s="24" t="n">
         <x:f>IFERROR(F107/F106-1,"")</x:f>
-        <x:v>-0.0033197632511344777</x:v>
-      </x:c>
-      <x:c r="I107" s="23" t="n">
+        <x:v>-0.003263926254555849</x:v>
+      </x:c>
+      <x:c r="I107" s="26" t="n">
         <x:f>ROUND(D107-E107,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>64.8</x:v>
       </x:c>
       <x:c r="J107" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K107" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10729,7 +10729,7 @@
       <x:c r="H108" s="30"/>
       <x:c r="I108" s="32" t="n">
         <x:f>ROUND(SUM(I77:I107),1)</x:f>
-        <x:v>3423</x:v>
+        <x:v>3444</x:v>
       </x:c>
       <x:c r="J108" s="30"/>
       <x:c r="K108" s="30"/>
@@ -10747,7 +10747,7 @@
       <x:c r="H109" s="30"/>
       <x:c r="I109" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I77:I107),0),1)</x:f>
-        <x:v>110.4</x:v>
+        <x:v>111.1</x:v>
       </x:c>
       <x:c r="J109" s="30"/>
       <x:c r="K109" s="30"/>
@@ -11941,7 +11941,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B143" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C143" s="23" t="n">
         <x:v>7628.8</x:v>
@@ -11953,15 +11953,15 @@
         <x:v>7525</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>7634.2</x:v>
+        <x:v>7650.2</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
         <x:f>ROUND(F143-F142,1)</x:f>
-        <x:v>43.6</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H143" s="24" t="n">
         <x:f>IFERROR(F143/F142-1,"")</x:f>
-        <x:v>0.0057439464600952395</x:v>
+        <x:v>0.007851816720680693</x:v>
       </x:c>
       <x:c r="I143" s="26" t="n">
         <x:f>ROUND(D143-E143,1)</x:f>
@@ -11971,7 +11971,7 @@
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K143" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -13201,7 +13201,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7888</x:v>
@@ -13213,15 +13213,15 @@
         <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7866.2</x:v>
+        <x:v>7861.2</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>-11.6</x:v>
+        <x:v>-16.6</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>-0.0014724923201909768</x:v>
+        <x:v>-0.0021071872857905127</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
@@ -13231,7 +13231,7 @@
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -15721,7 +15721,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>2930</x:v>
@@ -15730,28 +15730,28 @@
         <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-27.4</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.009351535836177538</x:v>
-      </x:c>
-      <x:c r="I251" s="23" t="n">
+        <x:v>-0.013651877133105783</x:v>
+      </x:c>
+      <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>49</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -15769,7 +15769,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I221:I251),1)</x:f>
-        <x:v>2866.6</x:v>
+        <x:v>2890.2</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -15787,7 +15787,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I221:I251),0),1)</x:f>
-        <x:v>92.5</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -23085,30 +23085,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>1457.5</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>7750.99</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>7784.38</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>7673.44</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>7769.82</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>53.9</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>0.0069894723745413945</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>110.9</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -23116,11 +23134,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>161.9</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>1568.4</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>156.8</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29155,30 +29191,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>1472.3</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>7989.65</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>8005.15</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>7897.24</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>7990.33</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>21.9</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>0.0027546377055311932</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>107.9</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -29186,11 +29240,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>163.6</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>1580.2</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35225,30 +35297,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>356.5</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>3930.02</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>3932.64</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>3903.7</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>3927.18</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>0.00005602297960760616</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>28.9</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -35256,11 +35346,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>39.6</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>385.4</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -41295,30 +41403,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>1427.6</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>7670</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>7695</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>7597.6</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>7650.2</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>0.0020958319142805326</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>97.4</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -41326,11 +41452,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>158.6</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>152.5</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -47365,30 +47509,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>1461</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>7905</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>7914</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>7802</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>7861.2</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>-0.0006356309272583793</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -47396,11 +47558,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>162.3</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>157.3</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59505,30 +59685,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>295.6</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>2905.6</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>2910.2</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>2877</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>2890</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>-12.6</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>-0.004340935712809135</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>33.2</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -59536,11 +59734,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>32.8</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>328.8</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>32.9</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf6fde38e9200485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R170ecf44ab3c4cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb3e6d4f610784545"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R369c25a06ddb4119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6ed6671e1e6b4c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc8d047512e904f53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re2e678b35bfc4b4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb368b2051ca14e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5608fe2ec08240ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rf6a3c5e2b4ba4dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R479f879d16b042ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb0e9b23962994488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R486b5916323841f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R226a08d5efe24dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rf7b4182585e9460c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R7570f4ea542b4b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R9e73713f5bce4e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R66e1210b8f2049ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R810973de5b7549b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7dd5a732fe9845de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4681</x:v>
+        <x:v>4639.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4621.4</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>59.6</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11087.8</x:v>
+        <x:v>11129.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.9</x:v>
+        <x:v>74.7</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>152440</x:v>
+        <x:v>154500</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>147100</x:v>
+        <x:v>149700</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>5340</x:v>
+        <x:v>4800</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1296860</x:v>
+        <x:v>1301660</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8762.6</x:v>
+        <x:v>8736</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -6897,30 +6897,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>45540</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>149700</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>154500</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>149700</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>153940</x:v>
+      </x:c>
+      <x:c r="H188" s="28" t="n">
+        <x:v>2520</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>0.016642451459516483</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -6928,11 +6946,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>5060</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>50340</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>5034</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14461,7 +14497,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
         <x:v>4656.8</x:v>
@@ -14470,28 +14506,28 @@
         <x:v>4681</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4611</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-21.6</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.004649560874806391</x:v>
+        <x:v>-0.005424487687274104</x:v>
       </x:c>
       <x:c r="I215" s="23" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K215" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -14509,7 +14545,7 @@
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="32" t="n">
         <x:f>ROUND(SUM(I185:I215),1)</x:f>
-        <x:v>5037.2</x:v>
+        <x:v>5050.2</x:v>
       </x:c>
       <x:c r="J216" s="30"/>
       <x:c r="K216" s="30"/>
@@ -14527,7 +14563,7 @@
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I185:I215),0),1)</x:f>
-        <x:v>162.5</x:v>
+        <x:v>162.9</x:v>
       </x:c>
       <x:c r="J217" s="30"/>
       <x:c r="K217" s="30"/>
@@ -16981,37 +17017,37 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>8月10日-8月13日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
         <x:v>140500</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>152440</x:v>
+        <x:v>154500</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
         <x:v>139280</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>151420</x:v>
+        <x:v>153940</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>11420</x:v>
+        <x:v>13940</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.08157142857142863</x:v>
+        <x:v>0.09957142857142864</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>13160</x:v>
+        <x:v>15220</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K287" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -17029,7 +17065,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="32" t="n">
         <x:f>ROUND(SUM(I257:I287),1)</x:f>
-        <x:v>666020</x:v>
+        <x:v>668080</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -17047,7 +17083,7 @@
       <x:c r="H289" s="30"/>
       <x:c r="I289" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I287),0),1)</x:f>
-        <x:v>21484.5</x:v>
+        <x:v>21551</x:v>
       </x:c>
       <x:c r="J289" s="30"/>
       <x:c r="K289" s="30"/>
@@ -53615,30 +53651,48 @@
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B188" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C188" s="30"/>
-      <x:c r="D188" s="30"/>
-      <x:c r="E188" s="30"/>
-      <x:c r="F188" s="30"/>
-      <x:c r="G188" s="30"/>
-      <x:c r="H188" s="30"/>
-      <x:c r="I188" s="30"/>
-      <x:c r="J188" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J187),1)</x:f>
-        <x:v>528.2</x:v>
-      </x:c>
-      <x:c r="K188" s="30"/>
+      <x:c r="A188" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B188" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C188" s="22" t="str">
+        <x:v>8月14日</x:v>
+      </x:c>
+      <x:c r="D188" s="23" t="n">
+        <x:v>4635</x:v>
+      </x:c>
+      <x:c r="E188" s="23" t="n">
+        <x:v>4639.6</x:v>
+      </x:c>
+      <x:c r="F188" s="23" t="n">
+        <x:v>4598</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
+        <x:v>4620.4</x:v>
+      </x:c>
+      <x:c r="H188" s="23" t="n">
+        <x:v>-3.6</x:v>
+      </x:c>
+      <x:c r="I188" s="24" t="n">
+        <x:v>-0.0007785467128028634</x:v>
+      </x:c>
+      <x:c r="J188" s="23" t="n">
+        <x:f>ROUND(E188-F188,1)</x:f>
+        <x:v>41.6</x:v>
+      </x:c>
+      <x:c r="K188" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B189" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B189" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C189" s="30"/>
       <x:c r="D189" s="30"/>
       <x:c r="E189" s="30"/>
@@ -53646,11 +53700,29 @@
       <x:c r="G189" s="30"/>
       <x:c r="H189" s="30"/>
       <x:c r="I189" s="30"/>
-      <x:c r="J189" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J187),0),1)</x:f>
-        <x:v>58.7</x:v>
+      <x:c r="J189" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J188),1)</x:f>
+        <x:v>569.8</x:v>
       </x:c>
       <x:c r="K189" s="30"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B190" s="30"/>
+      <x:c r="C190" s="30"/>
+      <x:c r="D190" s="30"/>
+      <x:c r="E190" s="30"/>
+      <x:c r="F190" s="30"/>
+      <x:c r="G190" s="30"/>
+      <x:c r="H190" s="30"/>
+      <x:c r="I190" s="30"/>
+      <x:c r="J190" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K190" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re2b429a1d29d4ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R42e5052453704d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R65d039c74d15414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R17846cf47c724df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0113cdbb091f418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra0bf077b753a49d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd70fe17319994361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R0580a07ca7ad425a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8f072a1d4fbb4d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R1a3298c859314278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra5ece879ec1343b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R801fde32192f42f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3d9e9d711f694264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R76d79475a79d407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R732f4f6438d44346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc56ba59754464c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R300a78f70e4a4d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rbd48bc909a8342ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcad1364b037b4186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R2cd161e206de421a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7695</x:v>
+        <x:v>7875</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7597.6</x:v>
+        <x:v>7631.4</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>97.4</x:v>
+        <x:v>243.6</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>28352.8</x:v>
+        <x:v>28596.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.3</x:v>
+        <x:v>190.6</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>154500</x:v>
+        <x:v>155220</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>149700</x:v>
+        <x:v>150520</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4800</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1301660</x:v>
+        <x:v>1306360</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8736</x:v>
+        <x:v>8709.1</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -6933,30 +6933,48 @@
       </x:c>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B189" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C189" s="30"/>
-      <x:c r="D189" s="30"/>
-      <x:c r="E189" s="30"/>
-      <x:c r="F189" s="30"/>
-      <x:c r="G189" s="30"/>
-      <x:c r="H189" s="30"/>
-      <x:c r="I189" s="30"/>
-      <x:c r="J189" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J188),1)</x:f>
-        <x:v>50340</x:v>
-      </x:c>
-      <x:c r="K189" s="30"/>
+      <x:c r="A189" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B189" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C189" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="D189" s="23" t="n">
+        <x:v>154300</x:v>
+      </x:c>
+      <x:c r="E189" s="23" t="n">
+        <x:v>155220</x:v>
+      </x:c>
+      <x:c r="F189" s="23" t="n">
+        <x:v>150520</x:v>
+      </x:c>
+      <x:c r="G189" s="23" t="n">
+        <x:v>152860</x:v>
+      </x:c>
+      <x:c r="H189" s="28" t="n">
+        <x:v>-1080</x:v>
+      </x:c>
+      <x:c r="I189" s="24" t="n">
+        <x:v>-0.007015720410549542</x:v>
+      </x:c>
+      <x:c r="J189" s="23" t="n">
+        <x:f>ROUND(E189-F189,1)</x:f>
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="K189" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B190" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B190" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C190" s="30"/>
       <x:c r="D190" s="30"/>
       <x:c r="E190" s="30"/>
@@ -6964,11 +6982,29 @@
       <x:c r="G190" s="30"/>
       <x:c r="H190" s="30"/>
       <x:c r="I190" s="30"/>
-      <x:c r="J190" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
-        <x:v>5034</x:v>
+      <x:c r="J190" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J189),1)</x:f>
+        <x:v>55040</x:v>
       </x:c>
       <x:c r="K190" s="30"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B191" s="30"/>
+      <x:c r="C191" s="30"/>
+      <x:c r="D191" s="30"/>
+      <x:c r="E191" s="30"/>
+      <x:c r="F191" s="30"/>
+      <x:c r="G191" s="30"/>
+      <x:c r="H191" s="30"/>
+      <x:c r="I191" s="30"/>
+      <x:c r="J191" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
+        <x:v>5003.6</x:v>
+      </x:c>
+      <x:c r="K191" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -12125,155 +12161,155 @@
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B147" s="30" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C147" s="30"/>
-      <x:c r="D147" s="30"/>
-      <x:c r="E147" s="30"/>
-      <x:c r="F147" s="30"/>
-      <x:c r="G147" s="30"/>
-      <x:c r="H147" s="30"/>
-      <x:c r="I147" s="32" t="n">
-        <x:f>ROUND(SUM(I116:I146),1)</x:f>
-        <x:v>13599.2</x:v>
-      </x:c>
-      <x:c r="J147" s="30"/>
-      <x:c r="K147" s="30"/>
+      <x:c r="A147" s="22" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B147" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="C147" s="23" t="n">
+        <x:v>7675</x:v>
+      </x:c>
+      <x:c r="D147" s="23" t="n">
+        <x:v>7875</x:v>
+      </x:c>
+      <x:c r="E147" s="23" t="n">
+        <x:v>7631.4</x:v>
+      </x:c>
+      <x:c r="F147" s="23" t="n">
+        <x:v>7875</x:v>
+      </x:c>
+      <x:c r="G147" s="28" t="n">
+        <x:f>ROUND(F147-F146,1)</x:f>
+        <x:v>224.8</x:v>
+      </x:c>
+      <x:c r="H147" s="24" t="n">
+        <x:f>IFERROR(F147/F146-1,"")</x:f>
+        <x:v>0.029384852683590035</x:v>
+      </x:c>
+      <x:c r="I147" s="26" t="n">
+        <x:f>ROUND(D147-E147,1)</x:f>
+        <x:v>243.6</x:v>
+      </x:c>
+      <x:c r="J147" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+      <x:c r="K147" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B148" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B148" s="30" t="n">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="C148" s="30"/>
       <x:c r="D148" s="30"/>
       <x:c r="E148" s="30"/>
       <x:c r="F148" s="30"/>
       <x:c r="G148" s="30"/>
       <x:c r="H148" s="30"/>
-      <x:c r="I148" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I116:I146),0),1)</x:f>
-        <x:v>438.7</x:v>
+      <x:c r="I148" s="32" t="n">
+        <x:f>ROUND(SUM(I116:I147),1)</x:f>
+        <x:v>13842.8</x:v>
       </x:c>
       <x:c r="J148" s="30"/>
       <x:c r="K148" s="30"/>
     </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="17" t="str">
+    <x:row r="149">
+      <x:c r="A149" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B149" s="30"/>
+      <x:c r="C149" s="30"/>
+      <x:c r="D149" s="30"/>
+      <x:c r="E149" s="30"/>
+      <x:c r="F149" s="30"/>
+      <x:c r="G149" s="30"/>
+      <x:c r="H149" s="30"/>
+      <x:c r="I149" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I116:I147),0),1)</x:f>
+        <x:v>432.6</x:v>
+      </x:c>
+      <x:c r="J149" s="30"/>
+      <x:c r="K149" s="30"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="17" t="str">
         <x:v>IC主力</x:v>
       </x:c>
-      <x:c r="B150" s="17"/>
-      <x:c r="C150" s="17"/>
-      <x:c r="D150" s="17"/>
-      <x:c r="E150" s="17"/>
-      <x:c r="F150" s="17"/>
-      <x:c r="G150" s="17"/>
-      <x:c r="H150" s="17"/>
-      <x:c r="I150" s="17"/>
-      <x:c r="J150" s="17"/>
-      <x:c r="K150" s="17"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="20" t="str">
+      <x:c r="B151" s="17"/>
+      <x:c r="C151" s="17"/>
+      <x:c r="D151" s="17"/>
+      <x:c r="E151" s="17"/>
+      <x:c r="F151" s="17"/>
+      <x:c r="G151" s="17"/>
+      <x:c r="H151" s="17"/>
+      <x:c r="I151" s="17"/>
+      <x:c r="J151" s="17"/>
+      <x:c r="K151" s="17"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B151" s="20" t="str">
+      <x:c r="B152" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C151" s="20" t="str">
+      <x:c r="C152" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D151" s="20" t="str">
+      <x:c r="D152" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E151" s="20" t="str">
+      <x:c r="E152" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F151" s="20" t="str">
+      <x:c r="F152" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G151" s="20" t="str">
+      <x:c r="G152" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H151" s="20" t="str">
+      <x:c r="H152" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I151" s="20" t="str">
+      <x:c r="I152" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J151" s="20" t="str">
+      <x:c r="J152" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K151" s="20" t="str">
+      <x:c r="K152" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B152" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C152" s="23" t="n">
-        <x:v>7424.4</x:v>
-      </x:c>
-      <x:c r="D152" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="E152" s="23" t="n">
-        <x:v>7422</x:v>
-      </x:c>
-      <x:c r="F152" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="G152" s="23"/>
-      <x:c r="H152" s="24"/>
-      <x:c r="I152" s="26" t="n">
-        <x:f>ROUND(D152-E152,1)</x:f>
-        <x:v>615.8</x:v>
-      </x:c>
-      <x:c r="J152" s="22" t="str">
-        <x:v>IC2603</x:v>
-      </x:c>
-      <x:c r="K152" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B153" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C153" s="23" t="n">
-        <x:v>8099</x:v>
+        <x:v>7424.4</x:v>
       </x:c>
       <x:c r="D153" s="23" t="n">
-        <x:v>8388.6</x:v>
+        <x:v>8037.8</x:v>
       </x:c>
       <x:c r="E153" s="23" t="n">
-        <x:v>8044</x:v>
+        <x:v>7422</x:v>
       </x:c>
       <x:c r="F153" s="23" t="n">
-        <x:v>8210.4</x:v>
-      </x:c>
-      <x:c r="G153" s="28" t="n">
-        <x:f>ROUND(F153-F152,1)</x:f>
-        <x:v>172.6</x:v>
-      </x:c>
-      <x:c r="H153" s="24" t="n">
-        <x:f>IFERROR(F153/F152-1,"")</x:f>
-        <x:v>0.02147353753514647</x:v>
-      </x:c>
+        <x:v>8037.8</x:v>
+      </x:c>
+      <x:c r="G153" s="23"/>
+      <x:c r="H153" s="24"/>
       <x:c r="I153" s="26" t="n">
         <x:f>ROUND(D153-E153,1)</x:f>
-        <x:v>344.6</x:v>
+        <x:v>615.8</x:v>
       </x:c>
       <x:c r="J153" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12284,34 +12320,34 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B154" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C154" s="23" t="n">
-        <x:v>8182.6</x:v>
+        <x:v>8099</x:v>
       </x:c>
       <x:c r="D154" s="23" t="n">
-        <x:v>8660</x:v>
+        <x:v>8388.6</x:v>
       </x:c>
       <x:c r="E154" s="23" t="n">
-        <x:v>8112</x:v>
+        <x:v>8044</x:v>
       </x:c>
       <x:c r="F154" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8210.4</x:v>
       </x:c>
       <x:c r="G154" s="28" t="n">
         <x:f>ROUND(F154-F153,1)</x:f>
-        <x:v>447.8</x:v>
+        <x:v>172.6</x:v>
       </x:c>
       <x:c r="H154" s="24" t="n">
         <x:f>IFERROR(F154/F153-1,"")</x:f>
-        <x:v>0.05454058267563111</x:v>
+        <x:v>0.02147353753514647</x:v>
       </x:c>
       <x:c r="I154" s="26" t="n">
         <x:f>ROUND(D154-E154,1)</x:f>
-        <x:v>548</x:v>
+        <x:v>344.6</x:v>
       </x:c>
       <x:c r="J154" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12322,34 +12358,34 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B155" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C155" s="23" t="n">
-        <x:v>8695</x:v>
+        <x:v>8182.6</x:v>
       </x:c>
       <x:c r="D155" s="23" t="n">
-        <x:v>8728.2</x:v>
+        <x:v>8660</x:v>
       </x:c>
       <x:c r="E155" s="23" t="n">
-        <x:v>8135</x:v>
+        <x:v>8112</x:v>
       </x:c>
       <x:c r="F155" s="23" t="n">
-        <x:v>8362.4</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="G155" s="28" t="n">
         <x:f>ROUND(F155-F154,1)</x:f>
-        <x:v>-295.8</x:v>
+        <x:v>447.8</x:v>
       </x:c>
       <x:c r="H155" s="24" t="n">
         <x:f>IFERROR(F155/F154-1,"")</x:f>
-        <x:v>-0.03416414497239628</x:v>
+        <x:v>0.05454058267563111</x:v>
       </x:c>
       <x:c r="I155" s="26" t="n">
         <x:f>ROUND(D155-E155,1)</x:f>
-        <x:v>593.2</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J155" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12360,34 +12396,34 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B156" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C156" s="23" t="n">
-        <x:v>8262.2</x:v>
+        <x:v>8695</x:v>
       </x:c>
       <x:c r="D156" s="23" t="n">
-        <x:v>8334.4</x:v>
+        <x:v>8728.2</x:v>
       </x:c>
       <x:c r="E156" s="23" t="n">
-        <x:v>7832</x:v>
+        <x:v>8135</x:v>
       </x:c>
       <x:c r="F156" s="23" t="n">
-        <x:v>8117.4</x:v>
+        <x:v>8362.4</x:v>
       </x:c>
       <x:c r="G156" s="28" t="n">
         <x:f>ROUND(F156-F155,1)</x:f>
-        <x:v>-245</x:v>
+        <x:v>-295.8</x:v>
       </x:c>
       <x:c r="H156" s="24" t="n">
         <x:f>IFERROR(F156/F155-1,"")</x:f>
-        <x:v>-0.029297809241366157</x:v>
+        <x:v>-0.03416414497239628</x:v>
       </x:c>
       <x:c r="I156" s="26" t="n">
         <x:f>ROUND(D156-E156,1)</x:f>
-        <x:v>502.4</x:v>
+        <x:v>593.2</x:v>
       </x:c>
       <x:c r="J156" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12398,34 +12434,34 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B157" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C157" s="23" t="n">
-        <x:v>8260</x:v>
+        <x:v>8262.2</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>8458.8</x:v>
+        <x:v>8334.4</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>8220</x:v>
+        <x:v>7832</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>8274.8</x:v>
+        <x:v>8117.4</x:v>
       </x:c>
       <x:c r="G157" s="28" t="n">
         <x:f>ROUND(F157-F156,1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>-245</x:v>
       </x:c>
       <x:c r="H157" s="24" t="n">
         <x:f>IFERROR(F157/F156-1,"")</x:f>
-        <x:v>0.019390445216448615</x:v>
+        <x:v>-0.029297809241366157</x:v>
       </x:c>
       <x:c r="I157" s="26" t="n">
         <x:f>ROUND(D157-E157,1)</x:f>
-        <x:v>238.8</x:v>
+        <x:v>502.4</x:v>
       </x:c>
       <x:c r="J157" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12436,110 +12472,110 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B158" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C158" s="23" t="n">
-        <x:v>8360</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>8650</x:v>
+        <x:v>8458.8</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>8314</x:v>
+        <x:v>8220</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>8645.4</x:v>
+        <x:v>8274.8</x:v>
       </x:c>
       <x:c r="G158" s="28" t="n">
         <x:f>ROUND(F158-F157,1)</x:f>
-        <x:v>370.6</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="H158" s="24" t="n">
         <x:f>IFERROR(F158/F157-1,"")</x:f>
-        <x:v>0.04478658094455468</x:v>
+        <x:v>0.019390445216448615</x:v>
       </x:c>
       <x:c r="I158" s="26" t="n">
         <x:f>ROUND(D158-E158,1)</x:f>
-        <x:v>336</x:v>
+        <x:v>238.8</x:v>
       </x:c>
       <x:c r="J158" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K158" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
-        <x:v>8600</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>8686</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>8180.6</x:v>
+        <x:v>8314</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>8322.6</x:v>
+        <x:v>8645.4</x:v>
       </x:c>
       <x:c r="G159" s="28" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>-322.8</x:v>
+        <x:v>370.6</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>-0.03733777500173496</x:v>
+        <x:v>0.04478658094455468</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="J159" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B160" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C160" s="23" t="n">
-        <x:v>8201.8</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>8434.4</x:v>
+        <x:v>8686</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>8180.6</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>8213.8</x:v>
-      </x:c>
-      <x:c r="G160" s="23" t="n">
+        <x:v>8322.6</x:v>
+      </x:c>
+      <x:c r="G160" s="28" t="n">
         <x:f>ROUND(F160-F159,1)</x:f>
-        <x:v>-108.8</x:v>
+        <x:v>-322.8</x:v>
       </x:c>
       <x:c r="H160" s="24" t="n">
         <x:f>IFERROR(F160/F159-1,"")</x:f>
-        <x:v>-0.013072837815106042</x:v>
+        <x:v>-0.03733777500173496</x:v>
       </x:c>
       <x:c r="I160" s="26" t="n">
         <x:f>ROUND(D160-E160,1)</x:f>
-        <x:v>724.4</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J160" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12550,34 +12586,34 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B161" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C161" s="23" t="n">
-        <x:v>8225.2</x:v>
+        <x:v>8201.8</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>8229.6</x:v>
+        <x:v>8434.4</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>7827.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>7844.4</x:v>
-      </x:c>
-      <x:c r="G161" s="28" t="n">
+        <x:v>8213.8</x:v>
+      </x:c>
+      <x:c r="G161" s="23" t="n">
         <x:f>ROUND(F161-F160,1)</x:f>
-        <x:v>-369.4</x:v>
+        <x:v>-108.8</x:v>
       </x:c>
       <x:c r="H161" s="24" t="n">
         <x:f>IFERROR(F161/F160-1,"")</x:f>
-        <x:v>-0.04497309406121397</x:v>
+        <x:v>-0.013072837815106042</x:v>
       </x:c>
       <x:c r="I161" s="26" t="n">
         <x:f>ROUND(D161-E161,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>724.4</x:v>
       </x:c>
       <x:c r="J161" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12588,37 +12624,37 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B162" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C162" s="23" t="n">
-        <x:v>7460</x:v>
+        <x:v>8225.2</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>7652</x:v>
+        <x:v>8229.6</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
-        <x:v>7171</x:v>
+        <x:v>7827.8</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>7559.2</x:v>
+        <x:v>7844.4</x:v>
       </x:c>
       <x:c r="G162" s="28" t="n">
         <x:f>ROUND(F162-F161,1)</x:f>
-        <x:v>-285.2</x:v>
+        <x:v>-369.4</x:v>
       </x:c>
       <x:c r="H162" s="24" t="n">
         <x:f>IFERROR(F162/F161-1,"")</x:f>
-        <x:v>-0.03635714649941357</x:v>
+        <x:v>-0.04497309406121397</x:v>
       </x:c>
       <x:c r="I162" s="26" t="n">
         <x:f>ROUND(D162-E162,1)</x:f>
-        <x:v>481</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J162" s="22" t="str">
-        <x:v>IC2606</x:v>
+        <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K162" s="22" t="n">
         <x:v>5</x:v>
@@ -12626,34 +12662,34 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
-        <x:v>7470.8</x:v>
+        <x:v>7460</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>7619</x:v>
+        <x:v>7652</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
-        <x:v>7325.2</x:v>
+        <x:v>7171</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>7352</x:v>
+        <x:v>7559.2</x:v>
       </x:c>
       <x:c r="G163" s="28" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>-207.2</x:v>
+        <x:v>-285.2</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>-0.02741030796909727</x:v>
+        <x:v>-0.03635714649941357</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -12664,110 +12700,110 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B164" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C164" s="23" t="n">
-        <x:v>7380</x:v>
+        <x:v>7470.8</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>7945.4</x:v>
+        <x:v>7619</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>7355.6</x:v>
+        <x:v>7325.2</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>7828.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="G164" s="28" t="n">
         <x:f>ROUND(F164-F163,1)</x:f>
-        <x:v>476.6</x:v>
+        <x:v>-207.2</x:v>
       </x:c>
       <x:c r="H164" s="24" t="n">
         <x:f>IFERROR(F164/F163-1,"")</x:f>
-        <x:v>0.06482589771490765</x:v>
+        <x:v>-0.02741030796909727</x:v>
       </x:c>
       <x:c r="I164" s="26" t="n">
         <x:f>ROUND(D164-E164,1)</x:f>
-        <x:v>589.8</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J164" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K164" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B165" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C165" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>8119.6</x:v>
+        <x:v>7945.4</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7355.6</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>8098.8</x:v>
+        <x:v>7828.6</x:v>
       </x:c>
       <x:c r="G165" s="28" t="n">
         <x:f>ROUND(F165-F164,1)</x:f>
-        <x:v>270.2</x:v>
+        <x:v>476.6</x:v>
       </x:c>
       <x:c r="H165" s="24" t="n">
         <x:f>IFERROR(F165/F164-1,"")</x:f>
-        <x:v>0.034514472574917576</x:v>
+        <x:v>0.06482589771490765</x:v>
       </x:c>
       <x:c r="I165" s="26" t="n">
         <x:f>ROUND(D165-E165,1)</x:f>
-        <x:v>327.6</x:v>
+        <x:v>589.8</x:v>
       </x:c>
       <x:c r="J165" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K165" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B166" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C166" s="23" t="n">
-        <x:v>8076.4</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>8288.2</x:v>
+        <x:v>8119.6</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>8042</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
-        <x:v>8132.8</x:v>
-      </x:c>
-      <x:c r="G166" s="23" t="n">
+        <x:v>8098.8</x:v>
+      </x:c>
+      <x:c r="G166" s="28" t="n">
         <x:f>ROUND(F166-F165,1)</x:f>
-        <x:v>34</x:v>
+        <x:v>270.2</x:v>
       </x:c>
       <x:c r="H166" s="24" t="n">
         <x:f>IFERROR(F166/F165-1,"")</x:f>
-        <x:v>0.004198152812762368</x:v>
+        <x:v>0.034514472574917576</x:v>
       </x:c>
       <x:c r="I166" s="26" t="n">
         <x:f>ROUND(D166-E166,1)</x:f>
-        <x:v>246.2</x:v>
+        <x:v>327.6</x:v>
       </x:c>
       <x:c r="J166" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -12778,148 +12814,148 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
-        <x:v>8145.2</x:v>
+        <x:v>8076.4</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>8287.8</x:v>
+        <x:v>8288.2</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>8056.2</x:v>
+        <x:v>8042</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>8270</x:v>
+        <x:v>8132.8</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>137.2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>0.016869958685815423</x:v>
+        <x:v>0.004198152812762368</x:v>
       </x:c>
       <x:c r="I167" s="26" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>231.6</x:v>
+        <x:v>246.2</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K167" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B168" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C168" s="23" t="n">
-        <x:v>8377.6</x:v>
+        <x:v>8145.2</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>8648</x:v>
+        <x:v>8287.8</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>8375.4</x:v>
+        <x:v>8056.2</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>8620.8</x:v>
-      </x:c>
-      <x:c r="G168" s="28" t="n">
+        <x:v>8270</x:v>
+      </x:c>
+      <x:c r="G168" s="23" t="n">
         <x:f>ROUND(F168-F167,1)</x:f>
-        <x:v>350.8</x:v>
+        <x:v>137.2</x:v>
       </x:c>
       <x:c r="H168" s="24" t="n">
         <x:f>IFERROR(F168/F167-1,"")</x:f>
-        <x:v>0.042418379685610574</x:v>
+        <x:v>0.016869958685815423</x:v>
       </x:c>
       <x:c r="I168" s="26" t="n">
         <x:f>ROUND(D168-E168,1)</x:f>
-        <x:v>272.6</x:v>
+        <x:v>231.6</x:v>
       </x:c>
       <x:c r="J168" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K168" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B169" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C169" s="23" t="n">
-        <x:v>8691</x:v>
+        <x:v>8377.6</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>8886.8</x:v>
+        <x:v>8648</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>8378.2</x:v>
+        <x:v>8375.4</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>8448.8</x:v>
+        <x:v>8620.8</x:v>
       </x:c>
       <x:c r="G169" s="28" t="n">
         <x:f>ROUND(F169-F168,1)</x:f>
-        <x:v>-172</x:v>
+        <x:v>350.8</x:v>
       </x:c>
       <x:c r="H169" s="24" t="n">
         <x:f>IFERROR(F169/F168-1,"")</x:f>
-        <x:v>-0.01995174461766891</x:v>
+        <x:v>0.042418379685610574</x:v>
       </x:c>
       <x:c r="I169" s="26" t="n">
         <x:f>ROUND(D169-E169,1)</x:f>
-        <x:v>508.6</x:v>
+        <x:v>272.6</x:v>
       </x:c>
       <x:c r="J169" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K169" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B170" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C170" s="23" t="n">
-        <x:v>8418.4</x:v>
+        <x:v>8691</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>8728</x:v>
+        <x:v>8886.8</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>8310</x:v>
+        <x:v>8378.2</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>8469.2</x:v>
-      </x:c>
-      <x:c r="G170" s="23" t="n">
+        <x:v>8448.8</x:v>
+      </x:c>
+      <x:c r="G170" s="28" t="n">
         <x:f>ROUND(F170-F169,1)</x:f>
-        <x:v>20.4</x:v>
+        <x:v>-172</x:v>
       </x:c>
       <x:c r="H170" s="24" t="n">
         <x:f>IFERROR(F170/F169-1,"")</x:f>
-        <x:v>0.0024145440772656013</x:v>
+        <x:v>-0.01995174461766891</x:v>
       </x:c>
       <x:c r="I170" s="26" t="n">
         <x:f>ROUND(D170-E170,1)</x:f>
-        <x:v>418</x:v>
+        <x:v>508.6</x:v>
       </x:c>
       <x:c r="J170" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -12930,34 +12966,34 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B171" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C171" s="23" t="n">
-        <x:v>8543</x:v>
+        <x:v>8418.4</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8728</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>8218.2</x:v>
+        <x:v>8310</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>8274.6</x:v>
-      </x:c>
-      <x:c r="G171" s="28" t="n">
+        <x:v>8469.2</x:v>
+      </x:c>
+      <x:c r="G171" s="23" t="n">
         <x:f>ROUND(F171-F170,1)</x:f>
-        <x:v>-194.6</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="H171" s="24" t="n">
         <x:f>IFERROR(F171/F170-1,"")</x:f>
-        <x:v>-0.022977376847872377</x:v>
+        <x:v>0.0024145440772656013</x:v>
       </x:c>
       <x:c r="I171" s="26" t="n">
         <x:f>ROUND(D171-E171,1)</x:f>
-        <x:v>440</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J171" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -12968,34 +13004,34 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B172" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C172" s="23" t="n">
-        <x:v>8298</x:v>
+        <x:v>8543</x:v>
       </x:c>
       <x:c r="D172" s="23" t="n">
-        <x:v>8425</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>8101.6</x:v>
+        <x:v>8218.2</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>8190.6</x:v>
-      </x:c>
-      <x:c r="G172" s="23" t="n">
+        <x:v>8274.6</x:v>
+      </x:c>
+      <x:c r="G172" s="28" t="n">
         <x:f>ROUND(F172-F171,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-194.6</x:v>
       </x:c>
       <x:c r="H172" s="24" t="n">
         <x:f>IFERROR(F172/F171-1,"")</x:f>
-        <x:v>-0.010151548111086983</x:v>
+        <x:v>-0.022977376847872377</x:v>
       </x:c>
       <x:c r="I172" s="26" t="n">
         <x:f>ROUND(D172-E172,1)</x:f>
-        <x:v>323.4</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="J172" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -13006,34 +13042,34 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B173" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C173" s="23" t="n">
-        <x:v>8050</x:v>
+        <x:v>8298</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>8237.6</x:v>
+        <x:v>8425</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>7838</x:v>
+        <x:v>8101.6</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>8117.2</x:v>
+        <x:v>8190.6</x:v>
       </x:c>
       <x:c r="G173" s="23" t="n">
         <x:f>ROUND(F173-F172,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H173" s="24" t="n">
         <x:f>IFERROR(F173/F172-1,"")</x:f>
-        <x:v>-0.008961492442556174</x:v>
+        <x:v>-0.010151548111086983</x:v>
       </x:c>
       <x:c r="I173" s="26" t="n">
         <x:f>ROUND(D173-E173,1)</x:f>
-        <x:v>399.6</x:v>
+        <x:v>323.4</x:v>
       </x:c>
       <x:c r="J173" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -13044,113 +13080,113 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>8718</x:v>
+        <x:v>8237.6</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>7838</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>8682.8</x:v>
-      </x:c>
-      <x:c r="G174" s="28" t="n">
+        <x:v>8117.2</x:v>
+      </x:c>
+      <x:c r="G174" s="23" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>565.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>0.06967919972404268</x:v>
+        <x:v>-0.008961492442556174</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>536.8</x:v>
+        <x:v>399.6</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B175" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C175" s="23" t="n">
-        <x:v>8692.8</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="D175" s="23" t="n">
-        <x:v>8778.8</x:v>
+        <x:v>8718</x:v>
       </x:c>
       <x:c r="E175" s="23" t="n">
-        <x:v>8377</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="F175" s="23" t="n">
-        <x:v>8447</x:v>
+        <x:v>8682.8</x:v>
       </x:c>
       <x:c r="G175" s="28" t="n">
         <x:f>ROUND(F175-F174,1)</x:f>
-        <x:v>-235.8</x:v>
+        <x:v>565.6</x:v>
       </x:c>
       <x:c r="H175" s="24" t="n">
         <x:f>IFERROR(F175/F174-1,"")</x:f>
-        <x:v>-0.027157138250333945</x:v>
+        <x:v>0.06967919972404268</x:v>
       </x:c>
       <x:c r="I175" s="26" t="n">
         <x:f>ROUND(D175-E175,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>536.8</x:v>
       </x:c>
       <x:c r="J175" s="22" t="str">
-        <x:v>IC2606/IC2609</x:v>
+        <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K175" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B176" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C176" s="23" t="n">
-        <x:v>8463.8</x:v>
+        <x:v>8692.8</x:v>
       </x:c>
       <x:c r="D176" s="23" t="n">
-        <x:v>8873.8</x:v>
+        <x:v>8778.8</x:v>
       </x:c>
       <x:c r="E176" s="23" t="n">
-        <x:v>8350.4</x:v>
+        <x:v>8377</x:v>
       </x:c>
       <x:c r="F176" s="23" t="n">
-        <x:v>8538</x:v>
-      </x:c>
-      <x:c r="G176" s="23" t="n">
+        <x:v>8447</x:v>
+      </x:c>
+      <x:c r="G176" s="28" t="n">
         <x:f>ROUND(F176-F175,1)</x:f>
-        <x:v>91</x:v>
+        <x:v>-235.8</x:v>
       </x:c>
       <x:c r="H176" s="24" t="n">
         <x:f>IFERROR(F176/F175-1,"")</x:f>
-        <x:v>0.010773055522670827</x:v>
+        <x:v>-0.027157138250333945</x:v>
       </x:c>
       <x:c r="I176" s="26" t="n">
         <x:f>ROUND(D176-E176,1)</x:f>
-        <x:v>523.4</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J176" s="22" t="str">
-        <x:v>IC2609</x:v>
+        <x:v>IC2606/IC2609</x:v>
       </x:c>
       <x:c r="K176" s="22" t="n">
         <x:v>5</x:v>
@@ -13158,34 +13194,34 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B177" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C177" s="23" t="n">
-        <x:v>8574.4</x:v>
+        <x:v>8463.8</x:v>
       </x:c>
       <x:c r="D177" s="23" t="n">
-        <x:v>8618</x:v>
+        <x:v>8873.8</x:v>
       </x:c>
       <x:c r="E177" s="23" t="n">
-        <x:v>8173</x:v>
+        <x:v>8350.4</x:v>
       </x:c>
       <x:c r="F177" s="23" t="n">
-        <x:v>8333</x:v>
-      </x:c>
-      <x:c r="G177" s="28" t="n">
+        <x:v>8538</x:v>
+      </x:c>
+      <x:c r="G177" s="23" t="n">
         <x:f>ROUND(F177-F176,1)</x:f>
-        <x:v>-205</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H177" s="24" t="n">
         <x:f>IFERROR(F177/F176-1,"")</x:f>
-        <x:v>-0.024010306863434083</x:v>
+        <x:v>0.010773055522670827</x:v>
       </x:c>
       <x:c r="I177" s="26" t="n">
         <x:f>ROUND(D177-E177,1)</x:f>
-        <x:v>445</x:v>
+        <x:v>523.4</x:v>
       </x:c>
       <x:c r="J177" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13196,34 +13232,34 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B178" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C178" s="23" t="n">
-        <x:v>8303</x:v>
+        <x:v>8574.4</x:v>
       </x:c>
       <x:c r="D178" s="23" t="n">
-        <x:v>8328</x:v>
+        <x:v>8618</x:v>
       </x:c>
       <x:c r="E178" s="23" t="n">
-        <x:v>7362.8</x:v>
+        <x:v>8173</x:v>
       </x:c>
       <x:c r="F178" s="23" t="n">
-        <x:v>7389</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="G178" s="28" t="n">
         <x:f>ROUND(F178-F177,1)</x:f>
-        <x:v>-944</x:v>
+        <x:v>-205</x:v>
       </x:c>
       <x:c r="H178" s="24" t="n">
         <x:f>IFERROR(F178/F177-1,"")</x:f>
-        <x:v>-0.11328453138125527</x:v>
+        <x:v>-0.024010306863434083</x:v>
       </x:c>
       <x:c r="I178" s="26" t="n">
         <x:f>ROUND(D178-E178,1)</x:f>
-        <x:v>965.2</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="J178" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13234,34 +13270,34 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
-        <x:v>7490</x:v>
+        <x:v>8303</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7765.6</x:v>
+        <x:v>8328</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>7092</x:v>
+        <x:v>7362.8</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7416</x:v>
-      </x:c>
-      <x:c r="G179" s="23" t="n">
+        <x:v>7389</x:v>
+      </x:c>
+      <x:c r="G179" s="28" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>27</x:v>
+        <x:v>-944</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>0.0036540803897686658</x:v>
+        <x:v>-0.11328453138125527</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>673.6</x:v>
+        <x:v>965.2</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13272,34 +13308,34 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B180" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C180" s="23" t="n">
-        <x:v>7447</x:v>
+        <x:v>7490</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>7666.6</x:v>
+        <x:v>7765.6</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>7106</x:v>
+        <x:v>7092</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
-        <x:v>7395</x:v>
+        <x:v>7416</x:v>
       </x:c>
       <x:c r="G180" s="23" t="n">
         <x:f>ROUND(F180-F179,1)</x:f>
-        <x:v>-21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H180" s="24" t="n">
         <x:f>IFERROR(F180/F179-1,"")</x:f>
-        <x:v>-0.0028317152103559673</x:v>
+        <x:v>0.0036540803897686658</x:v>
       </x:c>
       <x:c r="I180" s="26" t="n">
         <x:f>ROUND(D180-E180,1)</x:f>
-        <x:v>560.6</x:v>
+        <x:v>673.6</x:v>
       </x:c>
       <x:c r="J180" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13310,34 +13346,34 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B181" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C181" s="23" t="n">
-        <x:v>7391</x:v>
+        <x:v>7447</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>7882.6</x:v>
+        <x:v>7666.6</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>7335</x:v>
+        <x:v>7106</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>7877.8</x:v>
-      </x:c>
-      <x:c r="G181" s="28" t="n">
+        <x:v>7395</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
         <x:f>ROUND(F181-F180,1)</x:f>
-        <x:v>482.8</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="H181" s="24" t="n">
         <x:f>IFERROR(F181/F180-1,"")</x:f>
-        <x:v>0.06528735632183902</x:v>
+        <x:v>-0.0028317152103559673</x:v>
       </x:c>
       <x:c r="I181" s="26" t="n">
         <x:f>ROUND(D181-E181,1)</x:f>
-        <x:v>547.6</x:v>
+        <x:v>560.6</x:v>
       </x:c>
       <x:c r="J181" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13348,34 +13384,34 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B182" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C182" s="23" t="n">
-        <x:v>7888</x:v>
+        <x:v>7391</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>8024</x:v>
+        <x:v>7882.6</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>7795.8</x:v>
+        <x:v>7335</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>7861.2</x:v>
-      </x:c>
-      <x:c r="G182" s="23" t="n">
+        <x:v>7877.8</x:v>
+      </x:c>
+      <x:c r="G182" s="28" t="n">
         <x:f>ROUND(F182-F181,1)</x:f>
-        <x:v>-16.6</x:v>
+        <x:v>482.8</x:v>
       </x:c>
       <x:c r="H182" s="24" t="n">
         <x:f>IFERROR(F182/F181-1,"")</x:f>
-        <x:v>-0.0021071872857905127</x:v>
+        <x:v>0.06528735632183902</x:v>
       </x:c>
       <x:c r="I182" s="26" t="n">
         <x:f>ROUND(D182-E182,1)</x:f>
-        <x:v>228.2</x:v>
+        <x:v>547.6</x:v>
       </x:c>
       <x:c r="J182" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -13386,192 +13422,192 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B183" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C183" s="23" t="n">
-        <x:v>7885</x:v>
+        <x:v>7888</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>8086</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
-        <x:v>7869</x:v>
+        <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>8082</x:v>
-      </x:c>
-      <x:c r="G183" s="28" t="n">
+        <x:v>7861.2</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
         <x:f>ROUND(F183-F182,1)</x:f>
-        <x:v>220.8</x:v>
+        <x:v>-16.6</x:v>
       </x:c>
       <x:c r="H183" s="24" t="n">
         <x:f>IFERROR(F183/F182-1,"")</x:f>
-        <x:v>0.028087314913753714</x:v>
+        <x:v>-0.0021071872857905127</x:v>
       </x:c>
       <x:c r="I183" s="26" t="n">
         <x:f>ROUND(D183-E183,1)</x:f>
-        <x:v>217</x:v>
+        <x:v>228.2</x:v>
       </x:c>
       <x:c r="J183" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K183" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="22" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B184" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="C184" s="23" t="n">
+        <x:v>7885</x:v>
+      </x:c>
+      <x:c r="D184" s="23" t="n">
+        <x:v>8086</x:v>
+      </x:c>
+      <x:c r="E184" s="23" t="n">
+        <x:v>7869</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="n">
+        <x:v>8082</x:v>
+      </x:c>
+      <x:c r="G184" s="28" t="n">
+        <x:f>ROUND(F184-F183,1)</x:f>
+        <x:v>220.8</x:v>
+      </x:c>
+      <x:c r="H184" s="24" t="n">
+        <x:f>IFERROR(F184/F183-1,"")</x:f>
+        <x:v>0.028087314913753714</x:v>
+      </x:c>
+      <x:c r="I184" s="26" t="n">
+        <x:f>ROUND(D184-E184,1)</x:f>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="J184" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K184" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B184" s="30" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C184" s="30"/>
-      <x:c r="D184" s="30"/>
-      <x:c r="E184" s="30"/>
-      <x:c r="F184" s="30"/>
-      <x:c r="G184" s="30"/>
-      <x:c r="H184" s="30"/>
-      <x:c r="I184" s="32" t="n">
-        <x:f>ROUND(SUM(I152:I183),1)</x:f>
-        <x:v>14441.8</x:v>
-      </x:c>
-      <x:c r="J184" s="30"/>
-      <x:c r="K184" s="30"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B185" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B185" s="30" t="n">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="C185" s="30"/>
       <x:c r="D185" s="30"/>
       <x:c r="E185" s="30"/>
       <x:c r="F185" s="30"/>
       <x:c r="G185" s="30"/>
       <x:c r="H185" s="30"/>
-      <x:c r="I185" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I152:I183),0),1)</x:f>
-        <x:v>451.3</x:v>
+      <x:c r="I185" s="32" t="n">
+        <x:f>ROUND(SUM(I153:I184),1)</x:f>
+        <x:v>14441.8</x:v>
       </x:c>
       <x:c r="J185" s="30"/>
       <x:c r="K185" s="30"/>
     </x:row>
-    <x:row r="187">
-      <x:c r="A187" s="17" t="str">
+    <x:row r="186">
+      <x:c r="A186" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B186" s="30"/>
+      <x:c r="C186" s="30"/>
+      <x:c r="D186" s="30"/>
+      <x:c r="E186" s="30"/>
+      <x:c r="F186" s="30"/>
+      <x:c r="G186" s="30"/>
+      <x:c r="H186" s="30"/>
+      <x:c r="I186" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I153:I184),0),1)</x:f>
+        <x:v>451.3</x:v>
+      </x:c>
+      <x:c r="J186" s="30"/>
+      <x:c r="K186" s="30"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B187" s="17"/>
-      <x:c r="C187" s="17"/>
-      <x:c r="D187" s="17"/>
-      <x:c r="E187" s="17"/>
-      <x:c r="F187" s="17"/>
-      <x:c r="G187" s="17"/>
-      <x:c r="H187" s="17"/>
-      <x:c r="I187" s="17"/>
-      <x:c r="J187" s="17"/>
-      <x:c r="K187" s="17"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" s="20" t="str">
+      <x:c r="B188" s="17"/>
+      <x:c r="C188" s="17"/>
+      <x:c r="D188" s="17"/>
+      <x:c r="E188" s="17"/>
+      <x:c r="F188" s="17"/>
+      <x:c r="G188" s="17"/>
+      <x:c r="H188" s="17"/>
+      <x:c r="I188" s="17"/>
+      <x:c r="J188" s="17"/>
+      <x:c r="K188" s="17"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B188" s="20" t="str">
+      <x:c r="B189" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C188" s="20" t="str">
+      <x:c r="C189" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D188" s="20" t="str">
+      <x:c r="D189" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E188" s="20" t="str">
+      <x:c r="E189" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F188" s="20" t="str">
+      <x:c r="F189" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G188" s="20" t="str">
+      <x:c r="G189" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H188" s="20" t="str">
+      <x:c r="H189" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I188" s="20" t="str">
+      <x:c r="I189" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J188" s="20" t="str">
+      <x:c r="J189" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K188" s="20" t="str">
+      <x:c r="K189" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B189" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C189" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D189" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E189" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F189" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G189" s="23"/>
-      <x:c r="H189" s="24"/>
-      <x:c r="I189" s="26" t="n">
-        <x:f>ROUND(D189-E189,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J189" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K189" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B190" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C190" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G190" s="23" t="n">
-        <x:f>ROUND(F190-F189,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H190" s="24" t="n">
-        <x:f>IFERROR(F190/F189-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G190" s="23"/>
+      <x:c r="H190" s="24"/>
       <x:c r="I190" s="26" t="n">
         <x:f>ROUND(D190-E190,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J190" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13582,34 +13618,34 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B191" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C191" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G191" s="23" t="n">
         <x:f>ROUND(F191-F190,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H191" s="24" t="n">
         <x:f>IFERROR(F191/F190-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I191" s="26" t="n">
         <x:f>ROUND(D191-E191,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J191" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13620,34 +13656,34 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B192" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C192" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G192" s="23" t="n">
         <x:f>ROUND(F192-F191,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H192" s="24" t="n">
         <x:f>IFERROR(F192/F191-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I192" s="26" t="n">
         <x:f>ROUND(D192-E192,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J192" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13658,34 +13694,34 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B193" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C193" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D193" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E193" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F193" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G193" s="23" t="n">
         <x:f>ROUND(F193-F192,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H193" s="24" t="n">
         <x:f>IFERROR(F193/F192-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I193" s="26" t="n">
         <x:f>ROUND(D193-E193,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J193" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13696,34 +13732,34 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B194" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C194" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G194" s="23" t="n">
         <x:f>ROUND(F194-F193,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H194" s="24" t="n">
         <x:f>IFERROR(F194/F193-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I194" s="26" t="n">
         <x:f>ROUND(D194-E194,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J194" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13734,110 +13770,110 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B195" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C195" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G195" s="23" t="n">
         <x:f>ROUND(F195-F194,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H195" s="24" t="n">
         <x:f>IFERROR(F195/F194-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I195" s="26" t="n">
         <x:f>ROUND(D195-E195,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J195" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K195" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B196" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C196" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G196" s="23" t="n">
         <x:f>ROUND(F196-F195,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H196" s="24" t="n">
         <x:f>IFERROR(F196/F195-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I196" s="26" t="n">
         <x:f>ROUND(D196-E196,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J196" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K196" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B197" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C197" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G197" s="23" t="n">
         <x:f>ROUND(F197-F196,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H197" s="24" t="n">
         <x:f>IFERROR(F197/F196-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I197" s="26" t="n">
         <x:f>ROUND(D197-E197,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J197" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13848,34 +13884,34 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B198" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C198" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G198" s="23" t="n">
         <x:f>ROUND(F198-F197,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H198" s="24" t="n">
         <x:f>IFERROR(F198/F197-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I198" s="26" t="n">
         <x:f>ROUND(D198-E198,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J198" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -13886,37 +13922,37 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G199" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
         <x:v>5</x:v>
@@ -13924,34 +13960,34 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B200" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C200" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D200" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E200" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F200" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G200" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G200" s="28" t="n">
         <x:f>ROUND(F200-F199,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H200" s="24" t="n">
         <x:f>IFERROR(F200/F199-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I200" s="26" t="n">
         <x:f>ROUND(D200-E200,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J200" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -13962,110 +13998,110 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B201" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C201" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D201" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E201" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F201" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G201" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G201" s="23" t="n">
         <x:f>ROUND(F201-F200,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H201" s="24" t="n">
         <x:f>IFERROR(F201/F200-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I201" s="26" t="n">
         <x:f>ROUND(D201-E201,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J201" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K201" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B202" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C202" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D202" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E202" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F202" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G202" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G202" s="28" t="n">
         <x:f>ROUND(F202-F201,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H202" s="24" t="n">
         <x:f>IFERROR(F202/F201-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I202" s="26" t="n">
         <x:f>ROUND(D202-E202,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J202" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K202" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B203" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C203" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D203" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E203" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F203" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G203" s="23" t="n">
         <x:f>ROUND(F203-F202,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H203" s="24" t="n">
         <x:f>IFERROR(F203/F202-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I203" s="26" t="n">
         <x:f>ROUND(D203-E203,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J203" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -14076,148 +14112,148 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I204" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K204" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B205" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C205" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G205" s="23" t="n">
         <x:f>ROUND(F205-F204,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H205" s="24" t="n">
         <x:f>IFERROR(F205/F204-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I205" s="23" t="n">
         <x:f>ROUND(D205-E205,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J205" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K205" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B206" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C206" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G206" s="23" t="n">
         <x:f>ROUND(F206-F205,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H206" s="24" t="n">
         <x:f>IFERROR(F206/F205-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I206" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I206" s="23" t="n">
         <x:f>ROUND(D206-E206,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J206" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K206" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B207" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C207" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G207" s="23" t="n">
         <x:f>ROUND(F207-F206,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H207" s="24" t="n">
         <x:f>IFERROR(F207/F206-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I207" s="26" t="n">
         <x:f>ROUND(D207-E207,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J207" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -14228,34 +14264,34 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B208" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C208" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D208" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E208" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F208" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G208" s="23" t="n">
         <x:f>ROUND(F208-F207,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H208" s="24" t="n">
         <x:f>IFERROR(F208/F207-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I208" s="26" t="n">
         <x:f>ROUND(D208-E208,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J208" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -14266,34 +14302,34 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -14304,34 +14340,34 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B210" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C210" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D210" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E210" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F210" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G210" s="23" t="n">
         <x:f>ROUND(F210-F209,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H210" s="24" t="n">
         <x:f>IFERROR(F210/F209-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I210" s="26" t="n">
         <x:f>ROUND(D210-E210,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J210" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -14342,113 +14378,113 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B211" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C211" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D211" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E211" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F211" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G211" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
         <x:f>ROUND(F211-F210,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H211" s="24" t="n">
         <x:f>IFERROR(F211/F210-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I211" s="26" t="n">
         <x:f>ROUND(D211-E211,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J211" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K211" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B212" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C212" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D212" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E212" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F212" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G212" s="28" t="n">
         <x:f>ROUND(F212-F211,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H212" s="24" t="n">
         <x:f>IFERROR(F212/F211-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I212" s="26" t="n">
         <x:f>ROUND(D212-E212,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J212" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K212" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B213" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C213" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D213" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E213" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F213" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G213" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G213" s="28" t="n">
         <x:f>ROUND(F213-F212,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H213" s="24" t="n">
         <x:f>IFERROR(F213/F212-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I213" s="26" t="n">
         <x:f>ROUND(D213-E213,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J213" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K213" s="22" t="n">
         <x:v>5</x:v>
@@ -14456,34 +14492,34 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B214" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C214" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D214" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E214" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G214" s="23" t="n">
         <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H214" s="24" t="n">
         <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I214" s="26" t="n">
         <x:f>ROUND(D214-E214,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J214" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14494,34 +14530,34 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G215" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I215" s="26" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14532,34 +14568,34 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B216" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C216" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D216" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E216" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F216" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G216" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G216" s="28" t="n">
         <x:f>ROUND(F216-F215,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H216" s="24" t="n">
         <x:f>IFERROR(F216/F215-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I216" s="26" t="n">
         <x:f>ROUND(D216-E216,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J216" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14570,34 +14606,34 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B217" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C217" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D217" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E217" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F217" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G217" s="23" t="n">
         <x:f>ROUND(F217-F216,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H217" s="24" t="n">
         <x:f>IFERROR(F217/F216-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I217" s="26" t="n">
         <x:f>ROUND(D217-E217,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J217" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14608,34 +14644,34 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B218" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C218" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D218" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E218" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F218" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G218" s="23" t="n">
         <x:f>ROUND(F218-F217,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H218" s="24" t="n">
         <x:f>IFERROR(F218/F217-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>-0.008780743523655543</x:v>
       </x:c>
       <x:c r="I218" s="26" t="n">
         <x:f>ROUND(D218-E218,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J218" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14646,34 +14682,34 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D219" s="23" t="n">
-        <x:v>4681</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>4598</x:v>
+        <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>4620.4</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G219" s="23" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>-25.2</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>-0.005424487687274104</x:v>
-      </x:c>
-      <x:c r="I219" s="23" t="n">
+        <x:v>0.02371088585279857</x:v>
+      </x:c>
+      <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -14684,192 +14720,192 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B220" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C220" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D220" s="23" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E220" s="23" t="n">
-        <x:v>4619.8</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F220" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G220" s="23" t="n">
         <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>78.6</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H220" s="24" t="n">
         <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>0.017011514154618768</x:v>
+        <x:v>-0.005424487687274104</x:v>
       </x:c>
       <x:c r="I220" s="23" t="n">
         <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J220" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K220" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="22" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="C221" s="23" t="n">
+        <x:v>4624</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>4700.6</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>4619.8</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>4699</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:f>ROUND(F221-F220,1)</x:f>
+        <x:v>78.6</x:v>
+      </x:c>
+      <x:c r="H221" s="24" t="n">
+        <x:f>IFERROR(F221/F220-1,"")</x:f>
+        <x:v>0.017011514154618768</x:v>
+      </x:c>
+      <x:c r="I221" s="23" t="n">
+        <x:f>ROUND(D221-E221,1)</x:f>
+        <x:v>80.8</x:v>
+      </x:c>
+      <x:c r="J221" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="32" t="n">
-        <x:f>ROUND(SUM(I189:I220),1)</x:f>
-        <x:v>5131</x:v>
-      </x:c>
-      <x:c r="J221" s="30"/>
-      <x:c r="K221" s="30"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
       <x:c r="F222" s="30"/>
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
-      <x:c r="I222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I189:I220),0),1)</x:f>
-        <x:v>160.3</x:v>
+      <x:c r="I222" s="32" t="n">
+        <x:f>ROUND(SUM(I190:I221),1)</x:f>
+        <x:v>5131</x:v>
       </x:c>
       <x:c r="J222" s="30"/>
       <x:c r="K222" s="30"/>
     </x:row>
-    <x:row r="224">
-      <x:c r="A224" s="17" t="str">
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I190:I221),0),1)</x:f>
+        <x:v>160.3</x:v>
+      </x:c>
+      <x:c r="J223" s="30"/>
+      <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B224" s="17"/>
-      <x:c r="C224" s="17"/>
-      <x:c r="D224" s="17"/>
-      <x:c r="E224" s="17"/>
-      <x:c r="F224" s="17"/>
-      <x:c r="G224" s="17"/>
-      <x:c r="H224" s="17"/>
-      <x:c r="I224" s="17"/>
-      <x:c r="J224" s="17"/>
-      <x:c r="K224" s="17"/>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A225" s="20" t="str">
+      <x:c r="B225" s="17"/>
+      <x:c r="C225" s="17"/>
+      <x:c r="D225" s="17"/>
+      <x:c r="E225" s="17"/>
+      <x:c r="F225" s="17"/>
+      <x:c r="G225" s="17"/>
+      <x:c r="H225" s="17"/>
+      <x:c r="I225" s="17"/>
+      <x:c r="J225" s="17"/>
+      <x:c r="K225" s="17"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B225" s="20" t="str">
+      <x:c r="B226" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C225" s="20" t="str">
+      <x:c r="C226" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D225" s="20" t="str">
+      <x:c r="D226" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E225" s="20" t="str">
+      <x:c r="E226" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F225" s="20" t="str">
+      <x:c r="F226" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G225" s="20" t="str">
+      <x:c r="G226" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H225" s="20" t="str">
+      <x:c r="H226" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I225" s="20" t="str">
+      <x:c r="I226" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J225" s="20" t="str">
+      <x:c r="J226" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K225" s="20" t="str">
+      <x:c r="K226" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A226" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B226" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C226" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D226" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E226" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F226" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G226" s="23"/>
-      <x:c r="H226" s="24"/>
-      <x:c r="I226" s="26" t="n">
-        <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J226" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K226" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G227" s="23" t="n">
-        <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H227" s="24" t="n">
-        <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G227" s="23"/>
+      <x:c r="H227" s="24"/>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14880,34 +14916,34 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G228" s="23" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14918,34 +14954,34 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I229" s="26" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14956,34 +14992,34 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I230" s="26" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -14994,34 +15030,34 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I231" s="26" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -15032,110 +15068,110 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K232" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K233" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -15146,34 +15182,34 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I235" s="26" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -15184,37 +15220,37 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K236" s="22" t="n">
         <x:v>5</x:v>
@@ -15222,34 +15258,34 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I237" s="26" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15260,110 +15296,110 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K238" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G240" s="23" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I240" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I240" s="26" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15374,148 +15410,148 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G241" s="23" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I241" s="23" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K241" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G242" s="23" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I242" s="23" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K242" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I243" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I243" s="23" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K243" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15526,34 +15562,34 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D245" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I245" s="26" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15564,34 +15600,34 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B246" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C246" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D246" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E246" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F246" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G246" s="23" t="n">
         <x:f>ROUND(F246-F245,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H246" s="24" t="n">
         <x:f>IFERROR(F246/F245-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I246" s="26" t="n">
         <x:f>ROUND(D246-E246,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J246" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15602,34 +15638,34 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B247" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C247" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D247" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E247" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F247" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G247" s="23" t="n">
         <x:f>ROUND(F247-F246,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H247" s="24" t="n">
         <x:f>IFERROR(F247/F246-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I247" s="26" t="n">
         <x:f>ROUND(D247-E247,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J247" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -15640,113 +15676,113 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B248" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C248" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D248" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E248" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F248" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G248" s="23" t="n">
         <x:f>ROUND(F248-F247,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H248" s="24" t="n">
         <x:f>IFERROR(F248/F247-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I248" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I248" s="26" t="n">
         <x:f>ROUND(D248-E248,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J248" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K248" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B249" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C249" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D249" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E249" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F249" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G249" s="23" t="n">
         <x:f>ROUND(F249-F248,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H249" s="24" t="n">
         <x:f>IFERROR(F249/F248-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I249" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I249" s="23" t="n">
         <x:f>ROUND(D249-E249,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J249" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K249" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B250" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C250" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D250" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E250" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F250" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G250" s="23" t="n">
         <x:f>ROUND(F250-F249,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H250" s="24" t="n">
         <x:f>IFERROR(F250/F249-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I250" s="26" t="n">
         <x:f>ROUND(D250-E250,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J250" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K250" s="22" t="n">
         <x:v>5</x:v>
@@ -15754,34 +15790,34 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D251" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15792,34 +15828,34 @@
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B252" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C252" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D252" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E252" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F252" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G252" s="23" t="n">
         <x:f>ROUND(F252-F251,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H252" s="24" t="n">
         <x:f>IFERROR(F252/F251-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I252" s="26" t="n">
         <x:f>ROUND(D252-E252,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J252" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15830,34 +15866,34 @@
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B253" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C253" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D253" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E253" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F253" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G253" s="23" t="n">
         <x:f>ROUND(F253-F252,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H253" s="24" t="n">
         <x:f>IFERROR(F253/F252-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I253" s="26" t="n">
         <x:f>ROUND(D253-E253,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J253" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15868,34 +15904,34 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B254" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C254" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D254" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E254" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F254" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G254" s="23" t="n">
         <x:f>ROUND(F254-F253,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H254" s="24" t="n">
         <x:f>IFERROR(F254/F253-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I254" s="26" t="n">
         <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J254" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15906,34 +15942,34 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B255" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C255" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D255" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E255" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F255" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G255" s="23" t="n">
         <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H255" s="24" t="n">
         <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I255" s="26" t="n">
         <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J255" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15944,34 +15980,34 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B256" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C256" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D256" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E256" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F256" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D256" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E256" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F256" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G256" s="23" t="n">
         <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H256" s="24" t="n">
         <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I256" s="26" t="n">
         <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J256" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -15982,192 +16018,192 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>2883.4</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>2919.2</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>29.2</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>0.01010380622837359</x:v>
-      </x:c>
-      <x:c r="I257" s="23" t="n">
+        <x:v>-0.013651877133105783</x:v>
+      </x:c>
+      <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>37.8</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K257" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="22" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B258" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="C258" s="23" t="n">
+        <x:v>2886</x:v>
+      </x:c>
+      <x:c r="D258" s="23" t="n">
+        <x:v>2921.2</x:v>
+      </x:c>
+      <x:c r="E258" s="23" t="n">
+        <x:v>2883.4</x:v>
+      </x:c>
+      <x:c r="F258" s="23" t="n">
+        <x:v>2919.2</x:v>
+      </x:c>
+      <x:c r="G258" s="23" t="n">
+        <x:f>ROUND(F258-F257,1)</x:f>
+        <x:v>29.2</x:v>
+      </x:c>
+      <x:c r="H258" s="24" t="n">
+        <x:f>IFERROR(F258/F257-1,"")</x:f>
+        <x:v>0.01010380622837359</x:v>
+      </x:c>
+      <x:c r="I258" s="23" t="n">
+        <x:f>ROUND(D258-E258,1)</x:f>
+        <x:v>37.8</x:v>
+      </x:c>
+      <x:c r="J258" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K258" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A258" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B258" s="30" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C258" s="30"/>
-      <x:c r="D258" s="30"/>
-      <x:c r="E258" s="30"/>
-      <x:c r="F258" s="30"/>
-      <x:c r="G258" s="30"/>
-      <x:c r="H258" s="30"/>
-      <x:c r="I258" s="32" t="n">
-        <x:f>ROUND(SUM(I226:I257),1)</x:f>
-        <x:v>2928</x:v>
-      </x:c>
-      <x:c r="J258" s="30"/>
-      <x:c r="K258" s="30"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B259" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B259" s="30" t="n">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="C259" s="30"/>
       <x:c r="D259" s="30"/>
       <x:c r="E259" s="30"/>
       <x:c r="F259" s="30"/>
       <x:c r="G259" s="30"/>
       <x:c r="H259" s="30"/>
-      <x:c r="I259" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I226:I257),0),1)</x:f>
-        <x:v>91.5</x:v>
+      <x:c r="I259" s="32" t="n">
+        <x:f>ROUND(SUM(I227:I258),1)</x:f>
+        <x:v>2928</x:v>
       </x:c>
       <x:c r="J259" s="30"/>
       <x:c r="K259" s="30"/>
     </x:row>
-    <x:row r="261">
-      <x:c r="A261" s="17" t="str">
+    <x:row r="260">
+      <x:c r="A260" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B260" s="30"/>
+      <x:c r="C260" s="30"/>
+      <x:c r="D260" s="30"/>
+      <x:c r="E260" s="30"/>
+      <x:c r="F260" s="30"/>
+      <x:c r="G260" s="30"/>
+      <x:c r="H260" s="30"/>
+      <x:c r="I260" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I227:I258),0),1)</x:f>
+        <x:v>91.5</x:v>
+      </x:c>
+      <x:c r="J260" s="30"/>
+      <x:c r="K260" s="30"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="17" t="str">
         <x:v>碳酸锂2609</x:v>
       </x:c>
-      <x:c r="B261" s="17"/>
-      <x:c r="C261" s="17"/>
-      <x:c r="D261" s="17"/>
-      <x:c r="E261" s="17"/>
-      <x:c r="F261" s="17"/>
-      <x:c r="G261" s="17"/>
-      <x:c r="H261" s="17"/>
-      <x:c r="I261" s="17"/>
-      <x:c r="J261" s="17"/>
-      <x:c r="K261" s="17"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262" s="20" t="str">
+      <x:c r="B262" s="17"/>
+      <x:c r="C262" s="17"/>
+      <x:c r="D262" s="17"/>
+      <x:c r="E262" s="17"/>
+      <x:c r="F262" s="17"/>
+      <x:c r="G262" s="17"/>
+      <x:c r="H262" s="17"/>
+      <x:c r="I262" s="17"/>
+      <x:c r="J262" s="17"/>
+      <x:c r="K262" s="17"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B262" s="20" t="str">
+      <x:c r="B263" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C262" s="20" t="str">
+      <x:c r="C263" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D262" s="20" t="str">
+      <x:c r="D263" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E262" s="20" t="str">
+      <x:c r="E263" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F262" s="20" t="str">
+      <x:c r="F263" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G262" s="20" t="str">
+      <x:c r="G263" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H262" s="20" t="str">
+      <x:c r="H263" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I262" s="20" t="str">
+      <x:c r="I263" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J262" s="20" t="str">
+      <x:c r="J263" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K262" s="20" t="str">
+      <x:c r="K263" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A263" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B263" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C263" s="23" t="n">
-        <x:v>126360</x:v>
-      </x:c>
-      <x:c r="D263" s="23" t="n">
-        <x:v>150760</x:v>
-      </x:c>
-      <x:c r="E263" s="23" t="n">
-        <x:v>125160</x:v>
-      </x:c>
-      <x:c r="F263" s="23" t="n">
-        <x:v>145380</x:v>
-      </x:c>
-      <x:c r="G263" s="23"/>
-      <x:c r="H263" s="24"/>
-      <x:c r="I263" s="26" t="n">
-        <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>25600</x:v>
-      </x:c>
-      <x:c r="J263" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K263" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>126360</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>176120</x:v>
+        <x:v>150760</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>147740</x:v>
+        <x:v>125160</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>147740</x:v>
-      </x:c>
-      <x:c r="G264" s="28" t="n">
-        <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>2360</x:v>
-      </x:c>
-      <x:c r="H264" s="24" t="n">
-        <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>0.016233319576282934</x:v>
-      </x:c>
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="G264" s="23"/>
+      <x:c r="H264" s="24"/>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>28380</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16178,34 +16214,34 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>183780</x:v>
+        <x:v>176120</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>143820</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>183380</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="G265" s="28" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>35640</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>0.24123460132665486</x:v>
+        <x:v>0.016233319576282934</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>39960</x:v>
+        <x:v>28380</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16216,34 +16252,34 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>150720</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>183780</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>143820</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>183380</x:v>
       </x:c>
       <x:c r="G266" s="28" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>-34820</x:v>
+        <x:v>35640</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>-0.18987893990620575</x:v>
+        <x:v>0.24123460132665486</x:v>
       </x:c>
       <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>42040</x:v>
+        <x:v>39960</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16254,34 +16290,34 @@
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>187000</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>190600</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="G267" s="28" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>-15060</x:v>
+        <x:v>-34820</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>-0.10137318255250405</x:v>
+        <x:v>-0.18987893990620575</x:v>
       </x:c>
       <x:c r="I267" s="26" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>28720</x:v>
+        <x:v>42040</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16292,34 +16328,34 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>148040</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>153200</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
+        <x:v>124480</x:v>
+      </x:c>
+      <x:c r="F268" s="23" t="n">
         <x:v>133500</x:v>
-      </x:c>
-      <x:c r="F268" s="23" t="n">
-        <x:v>153500</x:v>
       </x:c>
       <x:c r="G268" s="28" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>20000</x:v>
+        <x:v>-15060</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>0.14981273408239693</x:v>
+        <x:v>-0.10137318255250405</x:v>
       </x:c>
       <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>20200</x:v>
+        <x:v>28720</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16330,110 +16366,110 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>153700</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>133500</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>153500</x:v>
       </x:c>
       <x:c r="G269" s="28" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>23700</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>0.15439739413680775</x:v>
+        <x:v>0.14981273408239693</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>28560</x:v>
+        <x:v>20200</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K269" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>186900</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="G270" s="28" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>-20500</x:v>
+        <x:v>23700</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>-0.11568848758465011</x:v>
+        <x:v>0.15439739413680775</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>34020</x:v>
+        <x:v>28560</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K270" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>180000</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>180060</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>146040</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>156700</x:v>
       </x:c>
       <x:c r="G271" s="28" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>-4600</x:v>
+        <x:v>-20500</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>-0.02935545628589664</x:v>
+        <x:v>-0.11568848758465011</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>34020</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16444,34 +16480,34 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>149000</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>167400</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>142600</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>143520</x:v>
+        <x:v>152100</x:v>
       </x:c>
       <x:c r="G272" s="28" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-8580</x:v>
+        <x:v>-4600</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.05641025641025643</x:v>
+        <x:v>-0.02935545628589664</x:v>
       </x:c>
       <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>20800</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16482,34 +16518,34 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>160800</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>143520</x:v>
       </x:c>
       <x:c r="G273" s="28" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>25880</x:v>
+        <x:v>-8580</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>0.18032329988851736</x:v>
+        <x:v>-0.05641025641025643</x:v>
       </x:c>
       <x:c r="I273" s="26" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>32200</x:v>
+        <x:v>20800</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16520,34 +16556,34 @@
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>141220</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>172220</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>140020</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>169400</x:v>
       </x:c>
       <x:c r="G274" s="28" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>-11540</x:v>
+        <x:v>25880</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>-0.06812278630460444</x:v>
+        <x:v>0.18032329988851736</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>20440</x:v>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16558,110 +16594,110 @@
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>170000</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>175000</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="G275" s="28" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>-260</x:v>
+        <x:v>-11540</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>-0.0016470290130495835</x:v>
+        <x:v>-0.06812278630460444</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>20440</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K275" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>158440</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>165500</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>177560</x:v>
+        <x:v>157600</x:v>
       </x:c>
       <x:c r="G276" s="28" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>19960</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>0.1266497461928935</x:v>
+        <x:v>-0.0016470290130495835</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>23220</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K276" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>155020</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>178000</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>154780</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>177560</x:v>
       </x:c>
       <x:c r="G277" s="28" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>19960</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>0.0019148456859652274</x:v>
+        <x:v>0.1266497461928935</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>23220</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16672,148 +16708,148 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>177000</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>181440</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>169500</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>177900</x:v>
       </x:c>
       <x:c r="G278" s="28" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>11180</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>0.06284429454749851</x:v>
+        <x:v>0.0019148456859652274</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>16100</x:v>
+        <x:v>11940</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K278" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>182000</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>189500</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>173400</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>189080</x:v>
       </x:c>
       <x:c r="G279" s="28" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>11180</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>0.039559974613920135</x:v>
+        <x:v>0.06284429454749851</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>10440</x:v>
+        <x:v>16100</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
+        <x:v>191500</x:v>
+      </x:c>
+      <x:c r="D280" s="23" t="n">
+        <x:v>201480</x:v>
+      </x:c>
+      <x:c r="E280" s="23" t="n">
+        <x:v>191040</x:v>
+      </x:c>
+      <x:c r="F280" s="23" t="n">
         <x:v>196560</x:v>
-      </x:c>
-      <x:c r="D280" s="23" t="n">
-        <x:v>209880</x:v>
-      </x:c>
-      <x:c r="E280" s="23" t="n">
-        <x:v>186800</x:v>
-      </x:c>
-      <x:c r="F280" s="23" t="n">
-        <x:v>188800</x:v>
       </x:c>
       <x:c r="G280" s="28" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>-7760</x:v>
+        <x:v>7480</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>-0.039479039479039524</x:v>
+        <x:v>0.039559974613920135</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>23080</x:v>
+        <x:v>10440</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K280" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>196560</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>209880</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>186800</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>188800</x:v>
       </x:c>
       <x:c r="G281" s="28" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>-4340</x:v>
+        <x:v>-7760</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>-0.022987288135593253</x:v>
+        <x:v>-0.039479039479039524</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>18700</x:v>
+        <x:v>23080</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16824,34 +16860,34 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>189000</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>193900</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>175200</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>184460</x:v>
       </x:c>
       <x:c r="G282" s="28" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>-4720</x:v>
+        <x:v>-4340</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>-0.02558820340453216</x:v>
+        <x:v>-0.022987288135593253</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>18700</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16862,34 +16898,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>185500</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>187900</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>172080</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>179740</x:v>
       </x:c>
       <x:c r="G283" s="28" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>-15380</x:v>
+        <x:v>-4720</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>-0.08556804272838547</x:v>
+        <x:v>-0.02558820340453216</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>24920</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16900,34 +16936,34 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>181000</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>182100</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>157180</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>164360</x:v>
       </x:c>
       <x:c r="G284" s="28" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>-15380</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>0.06656120710635194</x:v>
+        <x:v>-0.08556804272838547</x:v>
       </x:c>
       <x:c r="I284" s="26" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>18480</x:v>
+        <x:v>24920</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -16938,110 +16974,110 @@
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>161500</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>178740</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>160260</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>175300</x:v>
       </x:c>
       <x:c r="G285" s="28" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-14800</x:v>
+        <x:v>10940</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.08442669709070161</x:v>
+        <x:v>0.06656120710635194</x:v>
       </x:c>
       <x:c r="I285" s="26" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>17820</x:v>
+        <x:v>18480</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K285" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>177600</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>177920</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>160100</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="G286" s="28" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>-10280</x:v>
+        <x:v>-14800</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>-0.06404984423676008</x:v>
+        <x:v>-0.08442669709070161</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>18940</x:v>
+        <x:v>17820</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>157220</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>163940</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>145000</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>150220</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>18560</x:v>
+        <x:v>-10280</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.12355212355212353</x:v>
+        <x:v>-0.06404984423676008</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>26700</x:v>
+        <x:v>18940</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17052,34 +17088,34 @@
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>148000</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>145300</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>168780</x:v>
       </x:c>
       <x:c r="G288" s="28" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>-17180</x:v>
+        <x:v>18560</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>-0.10178931152980208</x:v>
+        <x:v>0.12355212355212353</x:v>
       </x:c>
       <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>18460</x:v>
+        <x:v>26700</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17090,34 +17126,34 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>166980</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>168720</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>150260</x:v>
       </x:c>
       <x:c r="F289" s="23" t="n">
-        <x:v>150140</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G289" s="28" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>-1460</x:v>
+        <x:v>-17180</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>-0.009630606860158264</x:v>
+        <x:v>-0.10178931152980208</x:v>
       </x:c>
       <x:c r="I289" s="26" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>10640</x:v>
+        <x:v>18460</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17128,34 +17164,34 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B290" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C290" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="D290" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="E290" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>145860</x:v>
       </x:c>
       <x:c r="F290" s="23" t="n">
-        <x:v>144280</x:v>
+        <x:v>150140</x:v>
       </x:c>
       <x:c r="G290" s="28" t="n">
         <x:f>ROUND(F290-F289,1)</x:f>
-        <x:v>-5860</x:v>
+        <x:v>-1460</x:v>
       </x:c>
       <x:c r="H290" s="24" t="n">
         <x:f>IFERROR(F290/F289-1,"")</x:f>
-        <x:v>-0.03903023844411879</x:v>
+        <x:v>-0.009630606860158264</x:v>
       </x:c>
       <x:c r="I290" s="26" t="n">
         <x:f>ROUND(D290-E290,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>10640</x:v>
       </x:c>
       <x:c r="J290" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17166,34 +17202,34 @@
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B291" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C291" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>151500</x:v>
       </x:c>
       <x:c r="D291" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>154800</x:v>
       </x:c>
       <x:c r="E291" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>136800</x:v>
       </x:c>
       <x:c r="F291" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>144280</x:v>
       </x:c>
       <x:c r="G291" s="28" t="n">
         <x:f>ROUND(F291-F290,1)</x:f>
-        <x:v>-6520</x:v>
+        <x:v>-5860</x:v>
       </x:c>
       <x:c r="H291" s="24" t="n">
         <x:f>IFERROR(F291/F290-1,"")</x:f>
-        <x:v>-0.04518990851122817</x:v>
+        <x:v>-0.03903023844411879</x:v>
       </x:c>
       <x:c r="I291" s="26" t="n">
         <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J291" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17204,34 +17240,34 @@
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>145780</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>149400</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="G292" s="28" t="n">
         <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>2240</x:v>
+        <x:v>-6520</x:v>
       </x:c>
       <x:c r="H292" s="24" t="n">
         <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>0.016260162601626105</x:v>
+        <x:v>-0.04518990851122817</x:v>
       </x:c>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>9240</x:v>
+        <x:v>11640</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17242,34 +17278,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>137500</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>144800</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>139280</x:v>
+        <x:v>135560</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="G293" s="28" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>13940</x:v>
+        <x:v>2240</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.09957142857142864</x:v>
+        <x:v>0.016260162601626105</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>15220</x:v>
+        <x:v>9240</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17279,42 +17315,118 @@
       </x:c>
     </x:row>
     <x:row r="294">
-      <x:c r="A294" s="31" t="str">
+      <x:c r="A294" s="22" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B294" s="22" t="str">
+        <x:v>8月10日-8月14日</x:v>
+      </x:c>
+      <x:c r="C294" s="23" t="n">
+        <x:v>140500</x:v>
+      </x:c>
+      <x:c r="D294" s="23" t="n">
+        <x:v>154500</x:v>
+      </x:c>
+      <x:c r="E294" s="23" t="n">
+        <x:v>139280</x:v>
+      </x:c>
+      <x:c r="F294" s="23" t="n">
+        <x:v>153940</x:v>
+      </x:c>
+      <x:c r="G294" s="28" t="n">
+        <x:f>ROUND(F294-F293,1)</x:f>
+        <x:v>13940</x:v>
+      </x:c>
+      <x:c r="H294" s="24" t="n">
+        <x:f>IFERROR(F294/F293-1,"")</x:f>
+        <x:v>0.09957142857142864</x:v>
+      </x:c>
+      <x:c r="I294" s="26" t="n">
+        <x:f>ROUND(D294-E294,1)</x:f>
+        <x:v>15220</x:v>
+      </x:c>
+      <x:c r="J294" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K294" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="22" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B295" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="C295" s="23" t="n">
+        <x:v>154300</x:v>
+      </x:c>
+      <x:c r="D295" s="23" t="n">
+        <x:v>155220</x:v>
+      </x:c>
+      <x:c r="E295" s="23" t="n">
+        <x:v>150520</x:v>
+      </x:c>
+      <x:c r="F295" s="23" t="n">
+        <x:v>152860</x:v>
+      </x:c>
+      <x:c r="G295" s="28" t="n">
+        <x:f>ROUND(F295-F294,1)</x:f>
+        <x:v>-1080</x:v>
+      </x:c>
+      <x:c r="H295" s="24" t="n">
+        <x:f>IFERROR(F295/F294-1,"")</x:f>
+        <x:v>-0.007015720410549542</x:v>
+      </x:c>
+      <x:c r="I295" s="23" t="n">
+        <x:f>ROUND(D295-E295,1)</x:f>
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="J295" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K295" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B294" s="30" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C294" s="30"/>
-      <x:c r="D294" s="30"/>
-      <x:c r="E294" s="30"/>
-      <x:c r="F294" s="30"/>
-      <x:c r="G294" s="30"/>
-      <x:c r="H294" s="30"/>
-      <x:c r="I294" s="32" t="n">
-        <x:f>ROUND(SUM(I263:I293),1)</x:f>
-        <x:v>668080</x:v>
-      </x:c>
-      <x:c r="J294" s="30"/>
-      <x:c r="K294" s="30"/>
-    </x:row>
-    <x:row r="295">
-      <x:c r="A295" s="31" t="str">
+      <x:c r="B296" s="30" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C296" s="30"/>
+      <x:c r="D296" s="30"/>
+      <x:c r="E296" s="30"/>
+      <x:c r="F296" s="30"/>
+      <x:c r="G296" s="30"/>
+      <x:c r="H296" s="30"/>
+      <x:c r="I296" s="32" t="n">
+        <x:f>ROUND(SUM(I264:I295),1)</x:f>
+        <x:v>672780</x:v>
+      </x:c>
+      <x:c r="J296" s="30"/>
+      <x:c r="K296" s="30"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B295" s="30"/>
-      <x:c r="C295" s="30"/>
-      <x:c r="D295" s="30"/>
-      <x:c r="E295" s="30"/>
-      <x:c r="F295" s="30"/>
-      <x:c r="G295" s="30"/>
-      <x:c r="H295" s="30"/>
-      <x:c r="I295" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I263:I293),0),1)</x:f>
-        <x:v>21551</x:v>
-      </x:c>
-      <x:c r="J295" s="30"/>
-      <x:c r="K295" s="30"/>
+      <x:c r="B297" s="30"/>
+      <x:c r="C297" s="30"/>
+      <x:c r="D297" s="30"/>
+      <x:c r="E297" s="30"/>
+      <x:c r="F297" s="30"/>
+      <x:c r="G297" s="30"/>
+      <x:c r="H297" s="30"/>
+      <x:c r="I297" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I264:I295),0),1)</x:f>
+        <x:v>21024.4</x:v>
+      </x:c>
+      <x:c r="J297" s="30"/>
+      <x:c r="K297" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -17323,10 +17435,10 @@
     <x:mergeCell ref="A40:K40"/>
     <x:mergeCell ref="A77:K77"/>
     <x:mergeCell ref="A114:K114"/>
-    <x:mergeCell ref="A150:K150"/>
-    <x:mergeCell ref="A187:K187"/>
-    <x:mergeCell ref="A224:K224"/>
-    <x:mergeCell ref="A261:K261"/>
+    <x:mergeCell ref="A151:K151"/>
+    <x:mergeCell ref="A188:K188"/>
+    <x:mergeCell ref="A225:K225"/>
+    <x:mergeCell ref="A262:K262"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -41811,30 +41923,48 @@
       </x:c>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B189" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C189" s="30"/>
-      <x:c r="D189" s="30"/>
-      <x:c r="E189" s="30"/>
-      <x:c r="F189" s="30"/>
-      <x:c r="G189" s="30"/>
-      <x:c r="H189" s="30"/>
-      <x:c r="I189" s="30"/>
-      <x:c r="J189" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J188),1)</x:f>
-        <x:v>1525</x:v>
-      </x:c>
-      <x:c r="K189" s="30"/>
+      <x:c r="A189" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B189" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C189" s="22" t="str">
+        <x:v>8月17日</x:v>
+      </x:c>
+      <x:c r="D189" s="23" t="n">
+        <x:v>7675</x:v>
+      </x:c>
+      <x:c r="E189" s="23" t="n">
+        <x:v>7875</x:v>
+      </x:c>
+      <x:c r="F189" s="23" t="n">
+        <x:v>7631.4</x:v>
+      </x:c>
+      <x:c r="G189" s="23" t="n">
+        <x:v>7875</x:v>
+      </x:c>
+      <x:c r="H189" s="28" t="n">
+        <x:v>224.8</x:v>
+      </x:c>
+      <x:c r="I189" s="24" t="n">
+        <x:v>0.029384852683590035</x:v>
+      </x:c>
+      <x:c r="J189" s="26" t="n">
+        <x:f>ROUND(E189-F189,1)</x:f>
+        <x:v>243.6</x:v>
+      </x:c>
+      <x:c r="K189" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B190" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B190" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C190" s="30"/>
       <x:c r="D190" s="30"/>
       <x:c r="E190" s="30"/>
@@ -41842,11 +41972,29 @@
       <x:c r="G190" s="30"/>
       <x:c r="H190" s="30"/>
       <x:c r="I190" s="30"/>
-      <x:c r="J190" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J188),0),1)</x:f>
-        <x:v>152.5</x:v>
+      <x:c r="J190" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J189),1)</x:f>
+        <x:v>1768.6</x:v>
       </x:c>
       <x:c r="K190" s="30"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B191" s="30"/>
+      <x:c r="C191" s="30"/>
+      <x:c r="D191" s="30"/>
+      <x:c r="E191" s="30"/>
+      <x:c r="F191" s="30"/>
+      <x:c r="G191" s="30"/>
+      <x:c r="H191" s="30"/>
+      <x:c r="I191" s="30"/>
+      <x:c r="J191" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
+        <x:v>160.8</x:v>
+      </x:c>
+      <x:c r="K191" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra5ece879ec1343b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R801fde32192f42f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3d9e9d711f694264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R76d79475a79d407d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R732f4f6438d44346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc56ba59754464c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R300a78f70e4a4d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rbd48bc909a8342ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcad1364b037b4186"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R2cd161e206de421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R60dabca3c77f4dad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rceef5dd15f3b46d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R32b1e57807394393"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Recd0478ed64c4557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R13ad6402daf14d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1ed8ddee17314905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf30fba1fd49b4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rf1f7416989c44a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R958156bc7ed84863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R6262fe1cd7a6488a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7995.5</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7750.43</x:v>
+        <x:v>7842.25</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>217.9</x:v>
+        <x:v>153.3</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>26902.2</x:v>
+        <x:v>27055.5</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.3</x:v>
+        <x:v>179.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8184.64</x:v>
+        <x:v>8211.31</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7992.36</x:v>
+        <x:v>8069.82</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>192.3</x:v>
+        <x:v>141.5</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>27068.5</x:v>
+        <x:v>27210</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.5</x:v>
+        <x:v>180.2</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3983.51</x:v>
+        <x:v>3994.18</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3924.47</x:v>
+        <x:v>3955.6</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>59</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7419.7</x:v>
+        <x:v>7458.3</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.5</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8086</x:v>
+        <x:v>8091.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7869</x:v>
+        <x:v>7932.4</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>217</x:v>
+        <x:v>159.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>29962.6</x:v>
+        <x:v>30122</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>199.8</x:v>
+        <x:v>199.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>155220</x:v>
+        <x:v>155980</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>150520</x:v>
+        <x:v>151520</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4700</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1306360</x:v>
+        <x:v>1310820</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8709.1</x:v>
+        <x:v>8680.9</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -6969,30 +6969,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>55040</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>153500</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>155980</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>151520</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>153940</x:v>
+      </x:c>
+      <x:c r="H190" s="28" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>0.007065288499280342</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>4460</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -7000,11 +7018,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>5003.6</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>59500</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>4958.3</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8271,37 +8307,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
         <x:v>7797.18</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7995.5</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
         <x:v>7750.43</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7945.96</x:v>
       </x:c>
       <x:c r="G36" s="28" t="n">
         <x:f>ROUND(F36-F35,1)</x:f>
-        <x:v>198.6</x:v>
+        <x:v>176.1</x:v>
       </x:c>
       <x:c r="H36" s="24" t="n">
         <x:f>IFERROR(F36/F35-1,"")</x:f>
-        <x:v>0.02555528956912778</x:v>
+        <x:v>0.022669765837561195</x:v>
       </x:c>
       <x:c r="I36" s="26" t="n">
         <x:f>ROUND(D36-E36,1)</x:f>
-        <x:v>217.9</x:v>
+        <x:v>245.1</x:v>
       </x:c>
       <x:c r="J36" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K36" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8319,7 +8355,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="32" t="n">
         <x:f>ROUND(SUM(I5:I36),1)</x:f>
-        <x:v>13188.4</x:v>
+        <x:v>13215.6</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -8337,7 +8373,7 @@
       <x:c r="H38" s="30"/>
       <x:c r="I38" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I36),0),1)</x:f>
-        <x:v>412.1</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="J38" s="30"/>
       <x:c r="K38" s="30"/>
@@ -9569,37 +9605,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C73" s="23" t="n">
         <x:v>8007.87</x:v>
       </x:c>
       <x:c r="D73" s="23" t="n">
-        <x:v>8184.64</x:v>
+        <x:v>8211.31</x:v>
       </x:c>
       <x:c r="E73" s="23" t="n">
         <x:v>7992.36</x:v>
       </x:c>
       <x:c r="F73" s="23" t="n">
-        <x:v>8184.64</x:v>
+        <x:v>8177.18</x:v>
       </x:c>
       <x:c r="G73" s="28" t="n">
         <x:f>ROUND(F73-F72,1)</x:f>
-        <x:v>194.3</x:v>
+        <x:v>186.9</x:v>
       </x:c>
       <x:c r="H73" s="24" t="n">
         <x:f>IFERROR(F73/F72-1,"")</x:f>
-        <x:v>0.02431814455723358</x:v>
+        <x:v>0.023384516033755798</x:v>
       </x:c>
       <x:c r="I73" s="26" t="n">
         <x:f>ROUND(D73-E73,1)</x:f>
-        <x:v>192.3</x:v>
+        <x:v>218.9</x:v>
       </x:c>
       <x:c r="J73" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K73" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -9617,7 +9653,7 @@
       <x:c r="H74" s="30"/>
       <x:c r="I74" s="32" t="n">
         <x:f>ROUND(SUM(I42:I73),1)</x:f>
-        <x:v>13317.7</x:v>
+        <x:v>13344.3</x:v>
       </x:c>
       <x:c r="J74" s="30"/>
       <x:c r="K74" s="30"/>
@@ -9635,7 +9671,7 @@
       <x:c r="H75" s="30"/>
       <x:c r="I75" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I42:I73),0),1)</x:f>
-        <x:v>416.2</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="J75" s="30"/>
       <x:c r="K75" s="30"/>
@@ -10867,37 +10903,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B110" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C110" s="23" t="n">
         <x:v>3930.1</x:v>
       </x:c>
       <x:c r="D110" s="23" t="n">
-        <x:v>3983.51</x:v>
+        <x:v>3994.18</x:v>
       </x:c>
       <x:c r="E110" s="23" t="n">
         <x:v>3924.47</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>3982.65</x:v>
+        <x:v>3990.3</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
         <x:f>ROUND(F110-F109,1)</x:f>
-        <x:v>55.5</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="H110" s="24" t="n">
         <x:f>IFERROR(F110/F109-1,"")</x:f>
-        <x:v>0.014124639053977761</x:v>
+        <x:v>0.016072601714207213</x:v>
       </x:c>
       <x:c r="I110" s="26" t="n">
         <x:f>ROUND(D110-E110,1)</x:f>
-        <x:v>59</x:v>
+        <x:v>69.7</x:v>
       </x:c>
       <x:c r="J110" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K110" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -10915,7 +10951,7 @@
       <x:c r="H111" s="30"/>
       <x:c r="I111" s="32" t="n">
         <x:f>ROUND(SUM(I79:I110),1)</x:f>
-        <x:v>3503</x:v>
+        <x:v>3513.7</x:v>
       </x:c>
       <x:c r="J111" s="30"/>
       <x:c r="K111" s="30"/>
@@ -10933,7 +10969,7 @@
       <x:c r="H112" s="30"/>
       <x:c r="I112" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I79:I110),0),1)</x:f>
-        <x:v>109.5</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J112" s="30"/>
       <x:c r="K112" s="30"/>
@@ -13463,37 +13499,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
         <x:v>7885</x:v>
       </x:c>
       <x:c r="D184" s="23" t="n">
-        <x:v>8086</x:v>
+        <x:v>8091.8</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
         <x:v>7869</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>8082</x:v>
+        <x:v>8022.6</x:v>
       </x:c>
       <x:c r="G184" s="28" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>220.8</x:v>
+        <x:v>161.4</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>0.028087314913753714</x:v>
+        <x:v>0.020531216608151492</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>217</x:v>
+        <x:v>222.8</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K184" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -13511,7 +13547,7 @@
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="32" t="n">
         <x:f>ROUND(SUM(I153:I184),1)</x:f>
-        <x:v>14441.8</x:v>
+        <x:v>14447.6</x:v>
       </x:c>
       <x:c r="J185" s="30"/>
       <x:c r="K185" s="30"/>
@@ -13529,7 +13565,7 @@
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I153:I184),0),1)</x:f>
-        <x:v>451.3</x:v>
+        <x:v>451.5</x:v>
       </x:c>
       <x:c r="J186" s="30"/>
       <x:c r="K186" s="30"/>
@@ -17357,37 +17393,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
         <x:v>154300</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>155220</x:v>
+        <x:v>155980</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
         <x:v>150520</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>152860</x:v>
-      </x:c>
-      <x:c r="G295" s="28" t="n">
+        <x:v>153940</x:v>
+      </x:c>
+      <x:c r="G295" s="23" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-1080</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.007015720410549542</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I295" s="23" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>4700</x:v>
+        <x:v>5460</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K295" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -17405,7 +17441,7 @@
       <x:c r="H296" s="30"/>
       <x:c r="I296" s="32" t="n">
         <x:f>ROUND(SUM(I264:I295),1)</x:f>
-        <x:v>672780</x:v>
+        <x:v>673540</x:v>
       </x:c>
       <x:c r="J296" s="30"/>
       <x:c r="K296" s="30"/>
@@ -17423,7 +17459,7 @@
       <x:c r="H297" s="30"/>
       <x:c r="I297" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I264:I295),0),1)</x:f>
-        <x:v>21024.4</x:v>
+        <x:v>21048.1</x:v>
       </x:c>
       <x:c r="J297" s="30"/>
       <x:c r="K297" s="30"/>
@@ -23533,30 +23569,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>1786.3</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>7969.37</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>7995.5</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>7842.25</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>7945.96</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-22.4</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.0028136208363557236</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>153.3</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -23564,11 +23618,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>162.4</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>1939.6</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>161.6</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29675,30 +29747,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>1772.5</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>8178.84</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>8211.31</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>8069.82</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>8177.18</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-7.5</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.0009114634241701447</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>141.5</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -29706,11 +29796,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>161.1</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>159.5</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35817,30 +35925,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>444.4</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>3979.49</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>3994.18</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>3955.6</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>3990.3</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>0.0019208316070957743</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>38.6</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -35848,11 +35974,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>40.4</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>40.3</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -48101,30 +48245,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>1790</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>8078</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>8091.8</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>7932.4</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>8022.6</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-59.4</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.007349665924276105</x:v>
+      </x:c>
+      <x:c r="J190" s="26" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>159.4</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -48132,11 +48294,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>162.7</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>1949.4</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>162.5</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R60dabca3c77f4dad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rceef5dd15f3b46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R32b1e57807394393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Recd0478ed64c4557"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R13ad6402daf14d76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1ed8ddee17314905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf30fba1fd49b4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rf1f7416989c44a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R958156bc7ed84863"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R6262fe1cd7a6488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8549f45f12d84a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R09d0e0f4c0ce4039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd2c6d0f1a72a418a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R82057985ee244c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb7674133ed5f40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb4f84784a3b2490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rb2c1e87fa2654f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R5e92753c6d1442d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re8ed87a061394b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rae2e912ea9d24136"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7875</x:v>
+        <x:v>7882.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7631.4</x:v>
+        <x:v>7725</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>243.6</x:v>
+        <x:v>157.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>28596.4</x:v>
+        <x:v>28754.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.6</x:v>
+        <x:v>190.4</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,22 +664,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4698.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4619.8</x:v>
+        <x:v>4633.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>80.8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11210.2</x:v>
+        <x:v>11275.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>74.7</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2883.4</x:v>
+        <x:v>2886.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>37.8</x:v>
+        <x:v>33.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6244.4</x:v>
+        <x:v>6278</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>41.6</x:v>
@@ -12201,37 +12201,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B147" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C147" s="23" t="n">
         <x:v>7675</x:v>
       </x:c>
       <x:c r="D147" s="23" t="n">
-        <x:v>7875</x:v>
+        <x:v>7882.8</x:v>
       </x:c>
       <x:c r="E147" s="23" t="n">
         <x:v>7631.4</x:v>
       </x:c>
       <x:c r="F147" s="23" t="n">
-        <x:v>7875</x:v>
+        <x:v>7807</x:v>
       </x:c>
       <x:c r="G147" s="28" t="n">
         <x:f>ROUND(F147-F146,1)</x:f>
-        <x:v>224.8</x:v>
+        <x:v>156.8</x:v>
       </x:c>
       <x:c r="H147" s="24" t="n">
         <x:f>IFERROR(F147/F146-1,"")</x:f>
-        <x:v>0.029384852683590035</x:v>
+        <x:v>0.02049619617787779</x:v>
       </x:c>
       <x:c r="I147" s="26" t="n">
         <x:f>ROUND(D147-E147,1)</x:f>
-        <x:v>243.6</x:v>
+        <x:v>251.4</x:v>
       </x:c>
       <x:c r="J147" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K147" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -12249,7 +12249,7 @@
       <x:c r="H148" s="30"/>
       <x:c r="I148" s="32" t="n">
         <x:f>ROUND(SUM(I116:I147),1)</x:f>
-        <x:v>13842.8</x:v>
+        <x:v>13850.6</x:v>
       </x:c>
       <x:c r="J148" s="30"/>
       <x:c r="K148" s="30"/>
@@ -12267,7 +12267,7 @@
       <x:c r="H149" s="30"/>
       <x:c r="I149" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I116:I147),0),1)</x:f>
-        <x:v>432.6</x:v>
+        <x:v>432.8</x:v>
       </x:c>
       <x:c r="J149" s="30"/>
       <x:c r="K149" s="30"/>
@@ -14797,7 +14797,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
         <x:v>4624</x:v>
@@ -14809,15 +14809,15 @@
         <x:v>4619.8</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4670.2</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>78.6</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>0.017011514154618768</x:v>
+        <x:v>0.010778287594147784</x:v>
       </x:c>
       <x:c r="I221" s="23" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
@@ -14827,7 +14827,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -16095,7 +16095,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>8月17日</x:v>
+        <x:v>8月17日-8月18日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
         <x:v>2886</x:v>
@@ -16107,15 +16107,15 @@
         <x:v>2883.4</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2919.2</x:v>
+        <x:v>2911.6</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>29.2</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>0.01010380622837359</x:v>
+        <x:v>0.007474048442906556</x:v>
       </x:c>
       <x:c r="I258" s="23" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
@@ -16125,7 +16125,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K258" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -42103,30 +42103,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>1768.6</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>7861</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>7882.8</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>7725</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>7807</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-68</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.008634920634920662</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>157.8</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -42134,11 +42152,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>160.8</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>1926.4</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>160.5</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54423,30 +54459,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>650.6</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>4688.2</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>4698.2</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>4633.2</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>4670.2</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-28.8</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.006128963609278615</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -54454,11 +54508,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>59.1</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>715.6</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>59.6</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -60565,30 +60637,48 @@
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B190" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C190" s="30"/>
-      <x:c r="D190" s="30"/>
-      <x:c r="E190" s="30"/>
-      <x:c r="F190" s="30"/>
-      <x:c r="G190" s="30"/>
-      <x:c r="H190" s="30"/>
-      <x:c r="I190" s="30"/>
-      <x:c r="J190" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J189),1)</x:f>
-        <x:v>366.6</x:v>
-      </x:c>
-      <x:c r="K190" s="30"/>
+      <x:c r="A190" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B190" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C190" s="22" t="str">
+        <x:v>8月18日</x:v>
+      </x:c>
+      <x:c r="D190" s="23" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="E190" s="23" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="F190" s="23" t="n">
+        <x:v>2886.4</x:v>
+      </x:c>
+      <x:c r="G190" s="23" t="n">
+        <x:v>2911.6</x:v>
+      </x:c>
+      <x:c r="H190" s="23" t="n">
+        <x:v>-7.6</x:v>
+      </x:c>
+      <x:c r="I190" s="24" t="n">
+        <x:v>-0.002603453000822098</x:v>
+      </x:c>
+      <x:c r="J190" s="23" t="n">
+        <x:f>ROUND(E190-F190,1)</x:f>
+        <x:v>33.6</x:v>
+      </x:c>
+      <x:c r="K190" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B191" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B191" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C191" s="30"/>
       <x:c r="D191" s="30"/>
       <x:c r="E191" s="30"/>
@@ -60596,11 +60686,29 @@
       <x:c r="G191" s="30"/>
       <x:c r="H191" s="30"/>
       <x:c r="I191" s="30"/>
-      <x:c r="J191" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J189),0),1)</x:f>
-        <x:v>33.3</x:v>
+      <x:c r="J191" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J190),1)</x:f>
+        <x:v>400.2</x:v>
       </x:c>
       <x:c r="K191" s="30"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B192" s="30"/>
+      <x:c r="C192" s="30"/>
+      <x:c r="D192" s="30"/>
+      <x:c r="E192" s="30"/>
+      <x:c r="F192" s="30"/>
+      <x:c r="G192" s="30"/>
+      <x:c r="H192" s="30"/>
+      <x:c r="I192" s="30"/>
+      <x:c r="J192" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
+        <x:v>33.4</x:v>
+      </x:c>
+      <x:c r="K192" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8549f45f12d84a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R09d0e0f4c0ce4039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd2c6d0f1a72a418a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R82057985ee244c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb7674133ed5f40da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb4f84784a3b2490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rb2c1e87fa2654f79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R5e92753c6d1442d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re8ed87a061394b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rae2e912ea9d24136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8886668be3214521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb1cf11f26bb74829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rcfeee34c52b6406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Ra43da6bd7aee4e7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0141bac180e54f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R5530e4c06f5a489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R90efc97f4ac549f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a65468688be49e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rdebd96fc5d944693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rdc93af55a37646e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7995.5</x:v>
+        <x:v>7821.18</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7842.25</x:v>
+        <x:v>7490.21</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>153.3</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>27055.5</x:v>
+        <x:v>27386.5</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.2</x:v>
+        <x:v>180.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8211.31</x:v>
+        <x:v>8050.08</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>8069.82</x:v>
+        <x:v>7762.29</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>141.5</x:v>
+        <x:v>287.8</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>27210</x:v>
+        <x:v>27497.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.2</x:v>
+        <x:v>180.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3994.18</x:v>
+        <x:v>3961.14</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3955.6</x:v>
+        <x:v>3879.58</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>38.6</x:v>
+        <x:v>81.6</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7458.3</x:v>
+        <x:v>7539.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.4</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7882.8</x:v>
+        <x:v>7734.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7725</x:v>
+        <x:v>7430</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>157.8</x:v>
+        <x:v>304.6</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>28754.2</x:v>
+        <x:v>29058.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.4</x:v>
+        <x:v>191.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4698.2</x:v>
+        <x:v>4624.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4633.2</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>65</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11275.2</x:v>
+        <x:v>11367.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.7</x:v>
+        <x:v>74.8</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8307,7 +8307,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
         <x:v>7797.18</x:v>
@@ -8316,28 +8316,28 @@
         <x:v>7995.5</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>7750.43</x:v>
+        <x:v>7490.21</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>7945.96</x:v>
+        <x:v>7517.77</x:v>
       </x:c>
       <x:c r="G36" s="28" t="n">
         <x:f>ROUND(F36-F35,1)</x:f>
-        <x:v>176.1</x:v>
+        <x:v>-252</x:v>
       </x:c>
       <x:c r="H36" s="24" t="n">
         <x:f>IFERROR(F36/F35-1,"")</x:f>
-        <x:v>0.022669765837561195</x:v>
+        <x:v>-0.03243961893583114</x:v>
       </x:c>
       <x:c r="I36" s="26" t="n">
         <x:f>ROUND(D36-E36,1)</x:f>
-        <x:v>245.1</x:v>
+        <x:v>505.3</x:v>
       </x:c>
       <x:c r="J36" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K36" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8355,7 +8355,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="32" t="n">
         <x:f>ROUND(SUM(I5:I36),1)</x:f>
-        <x:v>13215.6</x:v>
+        <x:v>13475.8</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -8373,7 +8373,7 @@
       <x:c r="H38" s="30"/>
       <x:c r="I38" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I36),0),1)</x:f>
-        <x:v>413</x:v>
+        <x:v>421.1</x:v>
       </x:c>
       <x:c r="J38" s="30"/>
       <x:c r="K38" s="30"/>
@@ -9605,7 +9605,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C73" s="23" t="n">
         <x:v>8007.87</x:v>
@@ -9614,28 +9614,28 @@
         <x:v>8211.31</x:v>
       </x:c>
       <x:c r="E73" s="23" t="n">
-        <x:v>7992.36</x:v>
+        <x:v>7762.29</x:v>
       </x:c>
       <x:c r="F73" s="23" t="n">
-        <x:v>8177.18</x:v>
+        <x:v>7783.46</x:v>
       </x:c>
       <x:c r="G73" s="28" t="n">
         <x:f>ROUND(F73-F72,1)</x:f>
-        <x:v>186.9</x:v>
+        <x:v>-206.9</x:v>
       </x:c>
       <x:c r="H73" s="24" t="n">
         <x:f>IFERROR(F73/F72-1,"")</x:f>
-        <x:v>0.023384516033755798</x:v>
+        <x:v>-0.025890044591399874</x:v>
       </x:c>
       <x:c r="I73" s="26" t="n">
         <x:f>ROUND(D73-E73,1)</x:f>
-        <x:v>218.9</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="J73" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K73" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -9653,7 +9653,7 @@
       <x:c r="H74" s="30"/>
       <x:c r="I74" s="32" t="n">
         <x:f>ROUND(SUM(I42:I73),1)</x:f>
-        <x:v>13344.3</x:v>
+        <x:v>13574.4</x:v>
       </x:c>
       <x:c r="J74" s="30"/>
       <x:c r="K74" s="30"/>
@@ -9671,7 +9671,7 @@
       <x:c r="H75" s="30"/>
       <x:c r="I75" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I42:I73),0),1)</x:f>
-        <x:v>417</x:v>
+        <x:v>424.2</x:v>
       </x:c>
       <x:c r="J75" s="30"/>
       <x:c r="K75" s="30"/>
@@ -10903,7 +10903,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B110" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C110" s="23" t="n">
         <x:v>3930.1</x:v>
@@ -10912,28 +10912,28 @@
         <x:v>3994.18</x:v>
       </x:c>
       <x:c r="E110" s="23" t="n">
-        <x:v>3924.47</x:v>
+        <x:v>3879.58</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>3990.3</x:v>
+        <x:v>3894.42</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
         <x:f>ROUND(F110-F109,1)</x:f>
-        <x:v>63.1</x:v>
+        <x:v>-32.8</x:v>
       </x:c>
       <x:c r="H110" s="24" t="n">
         <x:f>IFERROR(F110/F109-1,"")</x:f>
-        <x:v>0.016072601714207213</x:v>
+        <x:v>-0.008341863627335577</x:v>
       </x:c>
       <x:c r="I110" s="26" t="n">
         <x:f>ROUND(D110-E110,1)</x:f>
-        <x:v>69.7</x:v>
+        <x:v>114.6</x:v>
       </x:c>
       <x:c r="J110" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K110" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -10951,7 +10951,7 @@
       <x:c r="H111" s="30"/>
       <x:c r="I111" s="32" t="n">
         <x:f>ROUND(SUM(I79:I110),1)</x:f>
-        <x:v>3513.7</x:v>
+        <x:v>3558.6</x:v>
       </x:c>
       <x:c r="J111" s="30"/>
       <x:c r="K111" s="30"/>
@@ -10969,7 +10969,7 @@
       <x:c r="H112" s="30"/>
       <x:c r="I112" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I79:I110),0),1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>111.2</x:v>
       </x:c>
       <x:c r="J112" s="30"/>
       <x:c r="K112" s="30"/>
@@ -12201,7 +12201,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B147" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C147" s="23" t="n">
         <x:v>7675</x:v>
@@ -12210,28 +12210,28 @@
         <x:v>7882.8</x:v>
       </x:c>
       <x:c r="E147" s="23" t="n">
-        <x:v>7631.4</x:v>
+        <x:v>7430</x:v>
       </x:c>
       <x:c r="F147" s="23" t="n">
-        <x:v>7807</x:v>
+        <x:v>7468.8</x:v>
       </x:c>
       <x:c r="G147" s="28" t="n">
         <x:f>ROUND(F147-F146,1)</x:f>
-        <x:v>156.8</x:v>
+        <x:v>-181.4</x:v>
       </x:c>
       <x:c r="H147" s="24" t="n">
         <x:f>IFERROR(F147/F146-1,"")</x:f>
-        <x:v>0.02049619617787779</x:v>
+        <x:v>-0.023711798384355887</x:v>
       </x:c>
       <x:c r="I147" s="26" t="n">
         <x:f>ROUND(D147-E147,1)</x:f>
-        <x:v>251.4</x:v>
+        <x:v>452.8</x:v>
       </x:c>
       <x:c r="J147" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K147" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -12249,7 +12249,7 @@
       <x:c r="H148" s="30"/>
       <x:c r="I148" s="32" t="n">
         <x:f>ROUND(SUM(I116:I147),1)</x:f>
-        <x:v>13850.6</x:v>
+        <x:v>14052</x:v>
       </x:c>
       <x:c r="J148" s="30"/>
       <x:c r="K148" s="30"/>
@@ -12267,7 +12267,7 @@
       <x:c r="H149" s="30"/>
       <x:c r="I149" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I116:I147),0),1)</x:f>
-        <x:v>432.8</x:v>
+        <x:v>439.1</x:v>
       </x:c>
       <x:c r="J149" s="30"/>
       <x:c r="K149" s="30"/>
@@ -14797,7 +14797,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
         <x:v>4624</x:v>
@@ -14806,28 +14806,28 @@
         <x:v>4700.6</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>4619.8</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4670.2</x:v>
+        <x:v>4554.2</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>-66.2</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>0.010778287594147784</x:v>
-      </x:c>
-      <x:c r="I221" s="23" t="n">
+        <x:v>-0.014327763829971363</x:v>
+      </x:c>
+      <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>168.8</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -14845,7 +14845,7 @@
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="32" t="n">
         <x:f>ROUND(SUM(I190:I221),1)</x:f>
-        <x:v>5131</x:v>
+        <x:v>5219</x:v>
       </x:c>
       <x:c r="J222" s="30"/>
       <x:c r="K222" s="30"/>
@@ -14863,7 +14863,7 @@
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I190:I221),0),1)</x:f>
-        <x:v>160.3</x:v>
+        <x:v>163.1</x:v>
       </x:c>
       <x:c r="J223" s="30"/>
       <x:c r="K223" s="30"/>
@@ -23605,30 +23605,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>1939.6</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>7795.26</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>7821.18</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>7490.21</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>7517.77</x:v>
+      </x:c>
+      <x:c r="H191" s="28" t="n">
+        <x:v>-428.2</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.0538877618311695</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -23636,11 +23654,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>161.6</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>2270.6</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>174.7</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29783,30 +29819,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>1914</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>8029.52</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>8050.08</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>7762.29</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>7783.46</x:v>
+      </x:c>
+      <x:c r="H191" s="28" t="n">
+        <x:v>-393.7</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.04814862825570676</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>287.8</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -29814,11 +29868,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>159.5</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>2201.8</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>169.4</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35961,30 +36033,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>483</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>3952.12</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>3961.14</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>3879.58</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>3894.42</x:v>
+      </x:c>
+      <x:c r="H191" s="23" t="n">
+        <x:v>-95.9</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.024028268551236742</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>81.6</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -35992,11 +36082,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>40.3</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>564.6</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>43.4</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -42139,30 +42247,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>1926.4</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>7711</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>7734.6</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>7430</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>7468.8</x:v>
+      </x:c>
+      <x:c r="H191" s="28" t="n">
+        <x:v>-338.2</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.04332009734853337</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>304.6</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -42170,11 +42296,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>160.5</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>2231</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>171.6</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54495,30 +54639,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>715.6</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>4605.2</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>4624.2</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>4531.8</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>4554.2</x:v>
+      </x:c>
+      <x:c r="H191" s="23" t="n">
+        <x:v>-116</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.024838336687936224</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -54526,11 +54688,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>59.6</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>62.2</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8886668be3214521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb1cf11f26bb74829"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rcfeee34c52b6406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Ra43da6bd7aee4e7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0141bac180e54f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R5530e4c06f5a489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R90efc97f4ac549f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a65468688be49e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rdebd96fc5d944693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rdc93af55a37646e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re6a16cfa49fd4716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rc71cd848c13b4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R12ba8364187a43fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rae60081141b14f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7fdb02014cc84d48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdd7b1cf67f014b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rabc756f410754d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R6c51a023cbfd4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R30a6c641a9344047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R51042800ba044ca9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>8091.8</x:v>
+        <x:v>7939.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7932.4</x:v>
+        <x:v>7680.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>159.4</x:v>
+        <x:v>259.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>30122</x:v>
+        <x:v>30381.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>199.5</x:v>
+        <x:v>199.9</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2920</x:v>
+        <x:v>2892.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2886.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>33.6</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6278</x:v>
+        <x:v>6327.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>41.6</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>155980</x:v>
+        <x:v>153220</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>151520</x:v>
+        <x:v>148400</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4460</x:v>
+        <x:v>4820</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1310820</x:v>
+        <x:v>1315640</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8680.9</x:v>
+        <x:v>8655.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -7005,30 +7005,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>59500</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>152260</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>153220</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>148400</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>149480</x:v>
+      </x:c>
+      <x:c r="H191" s="28" t="n">
+        <x:v>-4460</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.028972326880602806</x:v>
+      </x:c>
+      <x:c r="J191" s="23" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>4820</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -7036,11 +7054,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>4958.3</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>64320</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>4947.7</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13499,7 +13535,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
         <x:v>7885</x:v>
@@ -13508,28 +13544,28 @@
         <x:v>8091.8</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>7869</x:v>
+        <x:v>7680.2</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>8022.6</x:v>
-      </x:c>
-      <x:c r="G184" s="28" t="n">
+        <x:v>7712</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>161.4</x:v>
+        <x:v>-149.2</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>0.020531216608151492</x:v>
+        <x:v>-0.01897929069353277</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>222.8</x:v>
+        <x:v>411.6</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K184" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -13547,7 +13583,7 @@
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="32" t="n">
         <x:f>ROUND(SUM(I153:I184),1)</x:f>
-        <x:v>14447.6</x:v>
+        <x:v>14636.4</x:v>
       </x:c>
       <x:c r="J185" s="30"/>
       <x:c r="K185" s="30"/>
@@ -13565,7 +13601,7 @@
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I153:I184),0),1)</x:f>
-        <x:v>451.5</x:v>
+        <x:v>457.4</x:v>
       </x:c>
       <x:c r="J186" s="30"/>
       <x:c r="K186" s="30"/>
@@ -16095,7 +16131,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
         <x:v>2886</x:v>
@@ -16104,28 +16140,28 @@
         <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>2883.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2911.6</x:v>
+        <x:v>2865</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>21.6</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>0.007474048442906556</x:v>
-      </x:c>
-      <x:c r="I258" s="23" t="n">
+        <x:v>-0.00865051903114189</x:v>
+      </x:c>
+      <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>37.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K258" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -16143,7 +16179,7 @@
       <x:c r="H259" s="30"/>
       <x:c r="I259" s="32" t="n">
         <x:f>ROUND(SUM(I227:I258),1)</x:f>
-        <x:v>2928</x:v>
+        <x:v>2968.4</x:v>
       </x:c>
       <x:c r="J259" s="30"/>
       <x:c r="K259" s="30"/>
@@ -16161,7 +16197,7 @@
       <x:c r="H260" s="30"/>
       <x:c r="I260" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I227:I258),0),1)</x:f>
-        <x:v>91.5</x:v>
+        <x:v>92.8</x:v>
       </x:c>
       <x:c r="J260" s="30"/>
       <x:c r="K260" s="30"/>
@@ -17393,7 +17429,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>8月17日-8月18日</x:v>
+        <x:v>8月17日-8月19日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
         <x:v>154300</x:v>
@@ -17402,28 +17438,28 @@
         <x:v>155980</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>150520</x:v>
+        <x:v>148400</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>153940</x:v>
-      </x:c>
-      <x:c r="G295" s="23" t="n">
+        <x:v>149480</x:v>
+      </x:c>
+      <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>0</x:v>
+        <x:v>-4460</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I295" s="23" t="n">
+        <x:v>-0.028972326880602806</x:v>
+      </x:c>
+      <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>5460</x:v>
+        <x:v>7580</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K295" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -17441,7 +17477,7 @@
       <x:c r="H296" s="30"/>
       <x:c r="I296" s="32" t="n">
         <x:f>ROUND(SUM(I264:I295),1)</x:f>
-        <x:v>673540</x:v>
+        <x:v>675660</x:v>
       </x:c>
       <x:c r="J296" s="30"/>
       <x:c r="K296" s="30"/>
@@ -17459,7 +17495,7 @@
       <x:c r="H297" s="30"/>
       <x:c r="I297" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I264:I295),0),1)</x:f>
-        <x:v>21048.1</x:v>
+        <x:v>21114.4</x:v>
       </x:c>
       <x:c r="J297" s="30"/>
       <x:c r="K297" s="30"/>
@@ -48461,30 +48497,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>1949.4</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>7927.8</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>7939.8</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>7680.2</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>7712</x:v>
+      </x:c>
+      <x:c r="H191" s="28" t="n">
+        <x:v>-310.6</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.03871562834991149</x:v>
+      </x:c>
+      <x:c r="J191" s="26" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>259.6</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -48492,11 +48546,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>162.5</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>2209</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>169.9</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -60853,30 +60925,48 @@
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B191" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C191" s="30"/>
-      <x:c r="D191" s="30"/>
-      <x:c r="E191" s="30"/>
-      <x:c r="F191" s="30"/>
-      <x:c r="G191" s="30"/>
-      <x:c r="H191" s="30"/>
-      <x:c r="I191" s="30"/>
-      <x:c r="J191" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J190),1)</x:f>
-        <x:v>400.2</x:v>
-      </x:c>
-      <x:c r="K191" s="30"/>
+      <x:c r="A191" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B191" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C191" s="22" t="str">
+        <x:v>8月19日</x:v>
+      </x:c>
+      <x:c r="D191" s="23" t="n">
+        <x:v>2885</x:v>
+      </x:c>
+      <x:c r="E191" s="23" t="n">
+        <x:v>2892.8</x:v>
+      </x:c>
+      <x:c r="F191" s="23" t="n">
+        <x:v>2843</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
+        <x:v>2865</x:v>
+      </x:c>
+      <x:c r="H191" s="23" t="n">
+        <x:v>-46.6</x:v>
+      </x:c>
+      <x:c r="I191" s="24" t="n">
+        <x:v>-0.01600494573430411</x:v>
+      </x:c>
+      <x:c r="J191" s="23" t="n">
+        <x:f>ROUND(E191-F191,1)</x:f>
+        <x:v>49.8</x:v>
+      </x:c>
+      <x:c r="K191" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B192" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B192" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C192" s="30"/>
       <x:c r="D192" s="30"/>
       <x:c r="E192" s="30"/>
@@ -60884,11 +60974,29 @@
       <x:c r="G192" s="30"/>
       <x:c r="H192" s="30"/>
       <x:c r="I192" s="30"/>
-      <x:c r="J192" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J190),0),1)</x:f>
-        <x:v>33.4</x:v>
+      <x:c r="J192" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J191),1)</x:f>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="K192" s="30"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B193" s="30"/>
+      <x:c r="C193" s="30"/>
+      <x:c r="D193" s="30"/>
+      <x:c r="E193" s="30"/>
+      <x:c r="F193" s="30"/>
+      <x:c r="G193" s="30"/>
+      <x:c r="H193" s="30"/>
+      <x:c r="I193" s="30"/>
+      <x:c r="J193" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
+        <x:v>34.6</x:v>
+      </x:c>
+      <x:c r="K193" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re6a16cfa49fd4716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rc71cd848c13b4aa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R12ba8364187a43fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rae60081141b14f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7fdb02014cc84d48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdd7b1cf67f014b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rabc756f410754d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R6c51a023cbfd4887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R30a6c641a9344047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R51042800ba044ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R453ae6db5d9c474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rfff1164978ad4755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3bb890d3f6034c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdd2bb07706d0440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2c971c54c05e49a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R75f4bfc9f17446c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd06e71e757444154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ra596548056304159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9ff1160e75a2442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R88b36b1b4837430c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7821.18</x:v>
+        <x:v>7656.613</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7490.21</x:v>
+        <x:v>7541.475</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>331</x:v>
+        <x:v>115.1</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>27386.5</x:v>
+        <x:v>27501.3</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>180.2</x:v>
+        <x:v>179.7</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>8050.08</x:v>
+        <x:v>7923.91</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7762.29</x:v>
+        <x:v>7796.28</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>287.8</x:v>
+        <x:v>127.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>27497.8</x:v>
+        <x:v>27625.4</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.9</x:v>
+        <x:v>180.6</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3961.14</x:v>
+        <x:v>3925.06</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3879.58</x:v>
+        <x:v>3888.1</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>81.6</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7539.9</x:v>
+        <x:v>7576.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.6</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7939.8</x:v>
+        <x:v>7811</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7680.2</x:v>
+        <x:v>7713</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>259.6</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>30381.6</x:v>
+        <x:v>30479.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>199.9</x:v>
+        <x:v>199.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4624.2</x:v>
+        <x:v>4585</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4531.8</x:v>
+        <x:v>4532.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>92.4</x:v>
+        <x:v>52.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11367.6</x:v>
+        <x:v>11420.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.8</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>153220</x:v>
+        <x:v>152600</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>148400</x:v>
+        <x:v>149800</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4820</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1315640</x:v>
+        <x:v>1318440</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8655.5</x:v>
+        <x:v>8617.3</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7041,30 +7041,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>64320</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>150800</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>152600</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>149800</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>151500</x:v>
+      </x:c>
+      <x:c r="H192" s="28" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.013513513513513598</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -7072,11 +7090,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>4947.7</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>67120</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>4794.3</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7174,16 +7210,16 @@
         <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C5" s="23" t="n">
-        <x:v>7639.54</x:v>
+        <x:v>7639.538</x:v>
       </x:c>
       <x:c r="D5" s="23" t="n">
-        <x:v>8131.49</x:v>
+        <x:v>8131.491</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
-        <x:v>7623.75</x:v>
+        <x:v>7623.749</x:v>
       </x:c>
       <x:c r="F5" s="23" t="n">
-        <x:v>8129.18</x:v>
+        <x:v>8129.183</x:v>
       </x:c>
       <x:c r="G5" s="23"/>
       <x:c r="H5" s="24"/>
@@ -7206,16 +7242,16 @@
         <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C6" s="23" t="n">
-        <x:v>8196.08</x:v>
+        <x:v>8196.085</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
-        <x:v>8415.1</x:v>
+        <x:v>8415.098</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
-        <x:v>8151.11</x:v>
+        <x:v>8151.107</x:v>
       </x:c>
       <x:c r="F6" s="23" t="n">
-        <x:v>8232.73</x:v>
+        <x:v>8232.729</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
         <x:f>ROUND(F6-F5,1)</x:f>
@@ -7223,7 +7259,7 @@
       </x:c>
       <x:c r="H6" s="24" t="n">
         <x:f>IFERROR(F6/F5-1,"")</x:f>
-        <x:v>0.012738062141568918</x:v>
+        <x:v>0.01273756538633708</x:v>
       </x:c>
       <x:c r="I6" s="26" t="n">
         <x:f>ROUND(D6-E6,1)</x:f>
@@ -7244,16 +7280,16 @@
         <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C7" s="23" t="n">
-        <x:v>8204.63</x:v>
+        <x:v>8204.627</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
-        <x:v>8478.56</x:v>
+        <x:v>8478.556</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
-        <x:v>8104.92</x:v>
+        <x:v>8104.918</x:v>
       </x:c>
       <x:c r="F7" s="23" t="n">
-        <x:v>8470.74</x:v>
+        <x:v>8470.744</x:v>
       </x:c>
       <x:c r="G7" s="28" t="n">
         <x:f>ROUND(F7-F6,1)</x:f>
@@ -7261,7 +7297,7 @@
       </x:c>
       <x:c r="H7" s="24" t="n">
         <x:f>IFERROR(F7/F6-1,"")</x:f>
-        <x:v>0.028910215687870222</x:v>
+        <x:v>0.02891082653151833</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
         <x:f>ROUND(D7-E7,1)</x:f>
@@ -7282,10 +7318,10 @@
         <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C8" s="23" t="n">
-        <x:v>8513.22</x:v>
+        <x:v>8513.222</x:v>
       </x:c>
       <x:c r="D8" s="23" t="n">
-        <x:v>8530.42</x:v>
+        <x:v>8530.417</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
         <x:v>8083.97</x:v>
@@ -7299,7 +7335,7 @@
       </x:c>
       <x:c r="H8" s="24" t="n">
         <x:f>IFERROR(F8/F7-1,"")</x:f>
-        <x:v>-0.025485376720333686</x:v>
+        <x:v>-0.025485836899332592</x:v>
       </x:c>
       <x:c r="I8" s="26" t="n">
         <x:f>ROUND(D8-E8,1)</x:f>
@@ -7320,16 +7356,16 @@
         <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C9" s="23" t="n">
-        <x:v>8166.74</x:v>
+        <x:v>8166.736</x:v>
       </x:c>
       <x:c r="D9" s="23" t="n">
-        <x:v>8221.58</x:v>
+        <x:v>8221.582</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
         <x:v>7950.01</x:v>
       </x:c>
       <x:c r="F9" s="23" t="n">
-        <x:v>8051.57</x:v>
+        <x:v>8051.574</x:v>
       </x:c>
       <x:c r="G9" s="28" t="n">
         <x:f>ROUND(F9-F8,1)</x:f>
@@ -7337,7 +7373,7 @@
       </x:c>
       <x:c r="H9" s="24" t="n">
         <x:f>IFERROR(F9/F8-1,"")</x:f>
-        <x:v>-0.024626704753321182</x:v>
+        <x:v>-0.02462622019028804</x:v>
       </x:c>
       <x:c r="I9" s="26" t="n">
         <x:f>ROUND(D9-E9,1)</x:f>
@@ -7358,16 +7394,16 @@
         <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C10" s="23" t="n">
-        <x:v>8177.29</x:v>
+        <x:v>8177.291</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
-        <x:v>8337.37</x:v>
+        <x:v>8337.371</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
-        <x:v>8149.65</x:v>
+        <x:v>8149.646</x:v>
       </x:c>
       <x:c r="F10" s="23" t="n">
-        <x:v>8204.83</x:v>
+        <x:v>8204.829</x:v>
       </x:c>
       <x:c r="G10" s="28" t="n">
         <x:f>ROUND(F10-F9,1)</x:f>
@@ -7375,7 +7411,7 @@
       </x:c>
       <x:c r="H10" s="24" t="n">
         <x:f>IFERROR(F10/F9-1,"")</x:f>
-        <x:v>0.01903479694022403</x:v>
+        <x:v>0.01903416648719869</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
         <x:f>ROUND(D10-E10,1)</x:f>
@@ -7396,16 +7432,16 @@
         <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C11" s="23" t="n">
-        <x:v>8319.69</x:v>
+        <x:v>8319.691</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
-        <x:v>8561.3</x:v>
+        <x:v>8561.295</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
-        <x:v>8236.71</x:v>
+        <x:v>8236.707</x:v>
       </x:c>
       <x:c r="F11" s="23" t="n">
-        <x:v>8560.84</x:v>
+        <x:v>8560.843</x:v>
       </x:c>
       <x:c r="G11" s="28" t="n">
         <x:f>ROUND(F11-F10,1)</x:f>
@@ -7413,7 +7449,7 @@
       </x:c>
       <x:c r="H11" s="24" t="n">
         <x:f>IFERROR(F11/F10-1,"")</x:f>
-        <x:v>0.0433902957160599</x:v>
+        <x:v>0.04339078852222289</x:v>
       </x:c>
       <x:c r="I11" s="26" t="n">
         <x:f>ROUND(D11-E11,1)</x:f>
@@ -7434,16 +7470,16 @@
         <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C12" s="23" t="n">
-        <x:v>8464.27</x:v>
+        <x:v>8464.273</x:v>
       </x:c>
       <x:c r="D12" s="23" t="n">
-        <x:v>8535.81</x:v>
+        <x:v>8535.807</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
-        <x:v>8039.59</x:v>
+        <x:v>8039.593</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
-        <x:v>8248.86</x:v>
+        <x:v>8248.857</x:v>
       </x:c>
       <x:c r="G12" s="28" t="n">
         <x:f>ROUND(F12-F11,1)</x:f>
@@ -7451,7 +7487,7 @@
       </x:c>
       <x:c r="H12" s="24" t="n">
         <x:f>IFERROR(F12/F11-1,"")</x:f>
-        <x:v>-0.036442685530859054</x:v>
+        <x:v>-0.03644337362570493</x:v>
       </x:c>
       <x:c r="I12" s="26" t="n">
         <x:f>ROUND(D12-E12,1)</x:f>
@@ -7472,16 +7508,16 @@
         <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C13" s="23" t="n">
-        <x:v>8131.74</x:v>
+        <x:v>8131.742</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
-        <x:v>8394.12</x:v>
+        <x:v>8394.122</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
-        <x:v>7983.57</x:v>
+        <x:v>7983.569</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
-        <x:v>8214.29</x:v>
+        <x:v>8214.293</x:v>
       </x:c>
       <x:c r="G13" s="23" t="n">
         <x:f>ROUND(F13-F12,1)</x:f>
@@ -7489,7 +7525,7 @@
       </x:c>
       <x:c r="H13" s="24" t="n">
         <x:f>IFERROR(F13/F12-1,"")</x:f>
-        <x:v>-0.004190882134016083</x:v>
+        <x:v>-0.004190156284682889</x:v>
       </x:c>
       <x:c r="I13" s="26" t="n">
         <x:f>ROUND(D13-E13,1)</x:f>
@@ -7510,16 +7546,16 @@
         <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C14" s="23" t="n">
-        <x:v>8212.27</x:v>
+        <x:v>8212.267</x:v>
       </x:c>
       <x:c r="D14" s="23" t="n">
-        <x:v>8226.03</x:v>
+        <x:v>8226.032</x:v>
       </x:c>
       <x:c r="E14" s="23" t="n">
-        <x:v>7781.58</x:v>
+        <x:v>7781.579</x:v>
       </x:c>
       <x:c r="F14" s="23" t="n">
-        <x:v>7783.43</x:v>
+        <x:v>7783.435</x:v>
       </x:c>
       <x:c r="G14" s="28" t="n">
         <x:f>ROUND(F14-F13,1)</x:f>
@@ -7527,7 +7563,7 @@
       </x:c>
       <x:c r="H14" s="24" t="n">
         <x:f>IFERROR(F14/F13-1,"")</x:f>
-        <x:v>-0.05245249437261168</x:v>
+        <x:v>-0.052452231738020494</x:v>
       </x:c>
       <x:c r="I14" s="26" t="n">
         <x:f>ROUND(D14-E14,1)</x:f>
@@ -7548,16 +7584,16 @@
         <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C15" s="23" t="n">
-        <x:v>7632.97</x:v>
+        <x:v>7632.972</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>7784.55</x:v>
+        <x:v>7784.547</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
-        <x:v>7357.7</x:v>
+        <x:v>7357.696</x:v>
       </x:c>
       <x:c r="F15" s="23" t="n">
-        <x:v>7746.31</x:v>
+        <x:v>7746.313</x:v>
       </x:c>
       <x:c r="G15" s="23" t="n">
         <x:f>ROUND(F15-F14,1)</x:f>
@@ -7565,7 +7601,7 @@
       </x:c>
       <x:c r="H15" s="24" t="n">
         <x:f>IFERROR(F15/F14-1,"")</x:f>
-        <x:v>-0.004769105651364458</x:v>
+        <x:v>-0.0047693595436976155</x:v>
       </x:c>
       <x:c r="I15" s="26" t="n">
         <x:f>ROUND(D15-E15,1)</x:f>
@@ -7586,13 +7622,13 @@
         <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C16" s="23" t="n">
-        <x:v>7664.64</x:v>
+        <x:v>7664.636</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
-        <x:v>7789.24</x:v>
+        <x:v>7789.239</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
-        <x:v>7521.94</x:v>
+        <x:v>7521.944</x:v>
       </x:c>
       <x:c r="F16" s="23" t="n">
         <x:v>7536.6</x:v>
@@ -7603,7 +7639,7 @@
       </x:c>
       <x:c r="H16" s="24" t="n">
         <x:f>IFERROR(F16/F15-1,"")</x:f>
-        <x:v>-0.027072244720389493</x:v>
+        <x:v>-0.027072621516842865</x:v>
       </x:c>
       <x:c r="I16" s="26" t="n">
         <x:f>ROUND(D16-E16,1)</x:f>
@@ -7624,16 +7660,16 @@
         <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C17" s="23" t="n">
-        <x:v>7556.28</x:v>
+        <x:v>7556.277</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>8059.76</x:v>
+        <x:v>8059.755</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
-        <x:v>7554.41</x:v>
+        <x:v>7554.408</x:v>
       </x:c>
       <x:c r="F17" s="23" t="n">
-        <x:v>7998.23</x:v>
+        <x:v>7998.232</x:v>
       </x:c>
       <x:c r="G17" s="28" t="n">
         <x:f>ROUND(F17-F16,1)</x:f>
@@ -7641,11 +7677,11 @@
       </x:c>
       <x:c r="H17" s="24" t="n">
         <x:f>IFERROR(F17/F16-1,"")</x:f>
-        <x:v>0.06125175808720096</x:v>
+        <x:v>0.061252023458854055</x:v>
       </x:c>
       <x:c r="I17" s="26" t="n">
         <x:f>ROUND(D17-E17,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>505.3</x:v>
       </x:c>
       <x:c r="J17" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -7662,16 +7698,16 @@
         <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C18" s="23" t="n">
-        <x:v>7947.22</x:v>
+        <x:v>7947.222</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
-        <x:v>8333.22</x:v>
+        <x:v>8333.222</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
-        <x:v>7947.22</x:v>
+        <x:v>7947.222</x:v>
       </x:c>
       <x:c r="F18" s="23" t="n">
-        <x:v>8307.44</x:v>
+        <x:v>8307.436</x:v>
       </x:c>
       <x:c r="G18" s="28" t="n">
         <x:f>ROUND(F18-F17,1)</x:f>
@@ -7679,7 +7715,7 @@
       </x:c>
       <x:c r="H18" s="24" t="n">
         <x:f>IFERROR(F18/F17-1,"")</x:f>
-        <x:v>0.03865980348152043</x:v>
+        <x:v>0.03865904364864625</x:v>
       </x:c>
       <x:c r="I18" s="26" t="n">
         <x:f>ROUND(D18-E18,1)</x:f>
@@ -7700,16 +7736,16 @@
         <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C19" s="23" t="n">
-        <x:v>8308.06</x:v>
+        <x:v>8308.055</x:v>
       </x:c>
       <x:c r="D19" s="23" t="n">
-        <x:v>8500.44</x:v>
+        <x:v>8500.438</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
-        <x:v>8254.43</x:v>
+        <x:v>8254.431</x:v>
       </x:c>
       <x:c r="F19" s="23" t="n">
-        <x:v>8304.14</x:v>
+        <x:v>8304.141</x:v>
       </x:c>
       <x:c r="G19" s="23" t="n">
         <x:f>ROUND(F19-F18,1)</x:f>
@@ -7717,7 +7753,7 @@
       </x:c>
       <x:c r="H19" s="24" t="n">
         <x:f>IFERROR(F19/F18-1,"")</x:f>
-        <x:v>-0.0003972342863747258</x:v>
+        <x:v>-0.00039663260722078153</x:v>
       </x:c>
       <x:c r="I19" s="26" t="n">
         <x:f>ROUND(D19-E19,1)</x:f>
@@ -7738,16 +7774,16 @@
         <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C20" s="23" t="n">
-        <x:v>8292.81</x:v>
+        <x:v>8292.811</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
-        <x:v>8402.36</x:v>
+        <x:v>8402.356</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
-        <x:v>8163.35</x:v>
+        <x:v>8163.348</x:v>
       </x:c>
       <x:c r="F20" s="23" t="n">
-        <x:v>8381.95</x:v>
+        <x:v>8381.947</x:v>
       </x:c>
       <x:c r="G20" s="23" t="n">
         <x:f>ROUND(F20-F19,1)</x:f>
@@ -7755,7 +7791,7 @@
       </x:c>
       <x:c r="H20" s="24" t="n">
         <x:f>IFERROR(F20/F19-1,"")</x:f>
-        <x:v>0.009370025071831822</x:v>
+        <x:v>0.009369542256086438</x:v>
       </x:c>
       <x:c r="I20" s="26" t="n">
         <x:f>ROUND(D20-E20,1)</x:f>
@@ -7776,16 +7812,16 @@
         <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C21" s="23" t="n">
-        <x:v>8462.02</x:v>
+        <x:v>8462.023</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:v>8760.19</x:v>
+        <x:v>8760.194</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
-        <x:v>8462.02</x:v>
+        <x:v>8462.023</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
-        <x:v>8741.15</x:v>
+        <x:v>8741.151</x:v>
       </x:c>
       <x:c r="G21" s="28" t="n">
         <x:f>ROUND(F21-F20,1)</x:f>
@@ -7793,7 +7829,7 @@
       </x:c>
       <x:c r="H21" s="24" t="n">
         <x:f>IFERROR(F21/F20-1,"")</x:f>
-        <x:v>0.04285398982337041</x:v>
+        <x:v>0.04285448237742373</x:v>
       </x:c>
       <x:c r="I21" s="26" t="n">
         <x:f>ROUND(D21-E21,1)</x:f>
@@ -7814,7 +7850,7 @@
         <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C22" s="23" t="n">
-        <x:v>8807.91</x:v>
+        <x:v>8807.905</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
         <x:v>8991.85</x:v>
@@ -7823,7 +7859,7 @@
         <x:v>8616.06</x:v>
       </x:c>
       <x:c r="F22" s="23" t="n">
-        <x:v>8682.65</x:v>
+        <x:v>8682.654</x:v>
       </x:c>
       <x:c r="G22" s="23" t="n">
         <x:f>ROUND(F22-F21,1)</x:f>
@@ -7831,7 +7867,7 @@
       </x:c>
       <x:c r="H22" s="24" t="n">
         <x:f>IFERROR(F22/F21-1,"")</x:f>
-        <x:v>-0.006692483254491677</x:v>
+        <x:v>-0.0066921392846318595</x:v>
       </x:c>
       <x:c r="I22" s="26" t="n">
         <x:f>ROUND(D22-E22,1)</x:f>
@@ -7852,7 +7888,7 @@
         <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C23" s="23" t="n">
-        <x:v>8645.76</x:v>
+        <x:v>8645.763</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
         <x:v>8896.6</x:v>
@@ -7861,7 +7897,7 @@
         <x:v>8500.92</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
-        <x:v>8692.67</x:v>
+        <x:v>8692.666</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
         <x:f>ROUND(F23-F22,1)</x:f>
@@ -7869,7 +7905,7 @@
       </x:c>
       <x:c r="H23" s="24" t="n">
         <x:f>IFERROR(F23/F22-1,"")</x:f>
-        <x:v>0.0011540255567137336</x:v>
+        <x:v>0.0011531036478016343</x:v>
       </x:c>
       <x:c r="I23" s="26" t="n">
         <x:f>ROUND(D23-E23,1)</x:f>
@@ -7890,16 +7926,16 @@
         <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C24" s="23" t="n">
-        <x:v>8756.46</x:v>
+        <x:v>8756.458</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
-        <x:v>8802.95</x:v>
+        <x:v>8802.946</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
-        <x:v>8357.8</x:v>
+        <x:v>8357.801</x:v>
       </x:c>
       <x:c r="F24" s="23" t="n">
-        <x:v>8408.74</x:v>
+        <x:v>8408.736</x:v>
       </x:c>
       <x:c r="G24" s="28" t="n">
         <x:f>ROUND(F24-F23,1)</x:f>
@@ -7907,11 +7943,11 @@
       </x:c>
       <x:c r="H24" s="24" t="n">
         <x:f>IFERROR(F24/F23-1,"")</x:f>
-        <x:v>-0.03266315182791946</x:v>
+        <x:v>-0.03266316685813053</x:v>
       </x:c>
       <x:c r="I24" s="26" t="n">
         <x:f>ROUND(D24-E24,1)</x:f>
-        <x:v>445.2</x:v>
+        <x:v>445.1</x:v>
       </x:c>
       <x:c r="J24" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -7928,16 +7964,16 @@
         <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C25" s="23" t="n">
-        <x:v>8393.52</x:v>
+        <x:v>8393.518</x:v>
       </x:c>
       <x:c r="D25" s="23" t="n">
-        <x:v>8549.25</x:v>
+        <x:v>8549.249</x:v>
       </x:c>
       <x:c r="E25" s="23" t="n">
-        <x:v>8219.15</x:v>
+        <x:v>8219.153</x:v>
       </x:c>
       <x:c r="F25" s="23" t="n">
-        <x:v>8340.96</x:v>
+        <x:v>8340.963</x:v>
       </x:c>
       <x:c r="G25" s="23" t="n">
         <x:f>ROUND(F25-F24,1)</x:f>
@@ -7945,7 +7981,7 @@
       </x:c>
       <x:c r="H25" s="24" t="n">
         <x:f>IFERROR(F25/F24-1,"")</x:f>
-        <x:v>-0.00806066069351663</x:v>
+        <x:v>-0.008059832060371641</x:v>
       </x:c>
       <x:c r="I25" s="26" t="n">
         <x:f>ROUND(D25-E25,1)</x:f>
@@ -7966,16 +8002,16 @@
         <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C26" s="23" t="n">
-        <x:v>8069.48</x:v>
+        <x:v>8069.482</x:v>
       </x:c>
       <x:c r="D26" s="23" t="n">
-        <x:v>8348.79</x:v>
+        <x:v>8348.786</x:v>
       </x:c>
       <x:c r="E26" s="23" t="n">
-        <x:v>7987.4</x:v>
+        <x:v>7987.396</x:v>
       </x:c>
       <x:c r="F26" s="23" t="n">
-        <x:v>8202.8</x:v>
+        <x:v>8202.799</x:v>
       </x:c>
       <x:c r="G26" s="23" t="n">
         <x:f>ROUND(F26-F25,1)</x:f>
@@ -7983,7 +8019,7 @@
       </x:c>
       <x:c r="H26" s="24" t="n">
         <x:f>IFERROR(F26/F25-1,"")</x:f>
-        <x:v>-0.01656404059005201</x:v>
+        <x:v>-0.016564514193385005</x:v>
       </x:c>
       <x:c r="I26" s="26" t="n">
         <x:f>ROUND(D26-E26,1)</x:f>
@@ -8004,16 +8040,16 @@
         <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C27" s="23" t="n">
-        <x:v>8269.4</x:v>
+        <x:v>8269.397</x:v>
       </x:c>
       <x:c r="D27" s="23" t="n">
-        <x:v>8796.48</x:v>
+        <x:v>8796.485</x:v>
       </x:c>
       <x:c r="E27" s="23" t="n">
-        <x:v>8269.4</x:v>
+        <x:v>8269.397</x:v>
       </x:c>
       <x:c r="F27" s="23" t="n">
-        <x:v>8771.02</x:v>
+        <x:v>8771.024</x:v>
       </x:c>
       <x:c r="G27" s="28" t="n">
         <x:f>ROUND(F27-F26,1)</x:f>
@@ -8021,7 +8057,7 @@
       </x:c>
       <x:c r="H27" s="24" t="n">
         <x:f>IFERROR(F27/F26-1,"")</x:f>
-        <x:v>0.06927146827912445</x:v>
+        <x:v>0.06927208627201509</x:v>
       </x:c>
       <x:c r="I27" s="26" t="n">
         <x:f>ROUND(D27-E27,1)</x:f>
@@ -8042,16 +8078,16 @@
         <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C28" s="23" t="n">
-        <x:v>8813.72</x:v>
+        <x:v>8813.725</x:v>
       </x:c>
       <x:c r="D28" s="23" t="n">
-        <x:v>8872.12</x:v>
+        <x:v>8872.123</x:v>
       </x:c>
       <x:c r="E28" s="23" t="n">
-        <x:v>8563.7</x:v>
+        <x:v>8563.695</x:v>
       </x:c>
       <x:c r="F28" s="23" t="n">
-        <x:v>8601.41</x:v>
+        <x:v>8601.408</x:v>
       </x:c>
       <x:c r="G28" s="28" t="n">
         <x:f>ROUND(F28-F27,1)</x:f>
@@ -8059,7 +8095,7 @@
       </x:c>
       <x:c r="H28" s="24" t="n">
         <x:f>IFERROR(F28/F27-1,"")</x:f>
-        <x:v>-0.019337545690239044</x:v>
+        <x:v>-0.0193382209420474</x:v>
       </x:c>
       <x:c r="I28" s="26" t="n">
         <x:f>ROUND(D28-E28,1)</x:f>
@@ -8080,16 +8116,16 @@
         <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C29" s="23" t="n">
-        <x:v>8616.42</x:v>
+        <x:v>8616.424</x:v>
       </x:c>
       <x:c r="D29" s="23" t="n">
-        <x:v>8944.19</x:v>
+        <x:v>8944.195</x:v>
       </x:c>
       <x:c r="E29" s="23" t="n">
-        <x:v>8413.86</x:v>
+        <x:v>8413.864</x:v>
       </x:c>
       <x:c r="F29" s="23" t="n">
-        <x:v>8620.79</x:v>
+        <x:v>8620.789</x:v>
       </x:c>
       <x:c r="G29" s="23" t="n">
         <x:f>ROUND(F29-F28,1)</x:f>
@@ -8097,7 +8133,7 @@
       </x:c>
       <x:c r="H29" s="24" t="n">
         <x:f>IFERROR(F29/F28-1,"")</x:f>
-        <x:v>0.002253118965378942</x:v>
+        <x:v>0.002253235749309912</x:v>
       </x:c>
       <x:c r="I29" s="26" t="n">
         <x:f>ROUND(D29-E29,1)</x:f>
@@ -8118,16 +8154,16 @@
         <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C30" s="23" t="n">
-        <x:v>8669.12</x:v>
+        <x:v>8669.123</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
-        <x:v>8694.8</x:v>
+        <x:v>8694.805</x:v>
       </x:c>
       <x:c r="E30" s="23" t="n">
-        <x:v>7978.81</x:v>
+        <x:v>7978.806</x:v>
       </x:c>
       <x:c r="F30" s="23" t="n">
-        <x:v>8198.31</x:v>
+        <x:v>8198.308</x:v>
       </x:c>
       <x:c r="G30" s="28" t="n">
         <x:f>ROUND(F30-F29,1)</x:f>
@@ -8135,7 +8171,7 @@
       </x:c>
       <x:c r="H30" s="24" t="n">
         <x:f>IFERROR(F30/F29-1,"")</x:f>
-        <x:v>-0.049007109557244855</x:v>
+        <x:v>-0.04900723124066719</x:v>
       </x:c>
       <x:c r="I30" s="26" t="n">
         <x:f>ROUND(D30-E30,1)</x:f>
@@ -8156,16 +8192,16 @@
         <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C31" s="23" t="n">
-        <x:v>8124.36</x:v>
+        <x:v>8124.363</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
-        <x:v>8171.5</x:v>
+        <x:v>8171.504</x:v>
       </x:c>
       <x:c r="E31" s="23" t="n">
-        <x:v>7163.31</x:v>
+        <x:v>7163.309</x:v>
       </x:c>
       <x:c r="F31" s="23" t="n">
-        <x:v>7168</x:v>
+        <x:v>7167.996</x:v>
       </x:c>
       <x:c r="G31" s="28" t="n">
         <x:f>ROUND(F31-F30,1)</x:f>
@@ -8173,7 +8209,7 @@
       </x:c>
       <x:c r="H31" s="24" t="n">
         <x:f>IFERROR(F31/F30-1,"")</x:f>
-        <x:v>-0.12567346196960105</x:v>
+        <x:v>-0.12567373658076775</x:v>
       </x:c>
       <x:c r="I31" s="26" t="n">
         <x:f>ROUND(D31-E31,1)</x:f>
@@ -8194,16 +8230,16 @@
         <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C32" s="23" t="n">
-        <x:v>7256.27</x:v>
+        <x:v>7256.267</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
-        <x:v>7302.45</x:v>
+        <x:v>7302.454</x:v>
       </x:c>
       <x:c r="E32" s="23" t="n">
-        <x:v>6714.19</x:v>
+        <x:v>6714.187</x:v>
       </x:c>
       <x:c r="F32" s="23" t="n">
-        <x:v>6995.69</x:v>
+        <x:v>6995.693</x:v>
       </x:c>
       <x:c r="G32" s="28" t="n">
         <x:f>ROUND(F32-F31,1)</x:f>
@@ -8211,7 +8247,7 @@
       </x:c>
       <x:c r="H32" s="24" t="n">
         <x:f>IFERROR(F32/F31-1,"")</x:f>
-        <x:v>-0.024038783482142945</x:v>
+        <x:v>-0.02403782033360513</x:v>
       </x:c>
       <x:c r="I32" s="26" t="n">
         <x:f>ROUND(D32-E32,1)</x:f>
@@ -8232,16 +8268,16 @@
         <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C33" s="23" t="n">
-        <x:v>6981.16</x:v>
+        <x:v>6981.165</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
-        <x:v>7228.78</x:v>
+        <x:v>7228.785</x:v>
       </x:c>
       <x:c r="E33" s="23" t="n">
-        <x:v>6841.75</x:v>
+        <x:v>6841.751</x:v>
       </x:c>
       <x:c r="F33" s="23" t="n">
-        <x:v>7075.51</x:v>
+        <x:v>7075.507</x:v>
       </x:c>
       <x:c r="G33" s="23" t="n">
         <x:f>ROUND(F33-F32,1)</x:f>
@@ -8249,7 +8285,7 @@
       </x:c>
       <x:c r="H33" s="24" t="n">
         <x:f>IFERROR(F33/F32-1,"")</x:f>
-        <x:v>0.011409882370430946</x:v>
+        <x:v>0.01140901980690101</x:v>
       </x:c>
       <x:c r="I33" s="26" t="n">
         <x:f>ROUND(D33-E33,1)</x:f>
@@ -8270,16 +8306,16 @@
         <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
-        <x:v>7055.27</x:v>
+        <x:v>7055.271</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
         <x:v>7685.57</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
-        <x:v>7042.89</x:v>
+        <x:v>7042.889</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7679.53</x:v>
+        <x:v>7679.529</x:v>
       </x:c>
       <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
@@ -8287,7 +8323,7 @@
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.08536769787619547</x:v>
+        <x:v>0.08536801673717531</x:v>
       </x:c>
       <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
@@ -8311,7 +8347,7 @@
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>7880.22</x:v>
+        <x:v>7880.217</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
         <x:v>7621.65</x:v>
@@ -8325,7 +8361,7 @@
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.011757229934644453</x:v>
+        <x:v>0.011757361681946854</x:v>
       </x:c>
       <x:c r="I35" s="26" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
@@ -8343,27 +8379,27 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
-        <x:v>7797.18</x:v>
+        <x:v>7797.184</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>7995.5</x:v>
+        <x:v>7995.501</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>7490.21</x:v>
+        <x:v>7490.212</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>7517.77</x:v>
+        <x:v>7589.779</x:v>
       </x:c>
       <x:c r="G36" s="28" t="n">
         <x:f>ROUND(F36-F35,1)</x:f>
-        <x:v>-252</x:v>
+        <x:v>-180</x:v>
       </x:c>
       <x:c r="H36" s="24" t="n">
         <x:f>IFERROR(F36/F35-1,"")</x:f>
-        <x:v>-0.03243961893583114</x:v>
+        <x:v>-0.02317183667060485</x:v>
       </x:c>
       <x:c r="I36" s="26" t="n">
         <x:f>ROUND(D36-E36,1)</x:f>
@@ -8373,7 +8409,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K36" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8391,7 +8427,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="32" t="n">
         <x:f>ROUND(SUM(I5:I36),1)</x:f>
-        <x:v>13475.8</x:v>
+        <x:v>13475.6</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -9641,7 +9677,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C73" s="23" t="n">
         <x:v>8007.87</x:v>
@@ -9653,15 +9689,15 @@
         <x:v>7762.29</x:v>
       </x:c>
       <x:c r="F73" s="23" t="n">
-        <x:v>7783.46</x:v>
-      </x:c>
-      <x:c r="G73" s="28" t="n">
+        <x:v>7850.4</x:v>
+      </x:c>
+      <x:c r="G73" s="23" t="n">
         <x:f>ROUND(F73-F72,1)</x:f>
-        <x:v>-206.9</x:v>
+        <x:v>-139.9</x:v>
       </x:c>
       <x:c r="H73" s="24" t="n">
         <x:f>IFERROR(F73/F72-1,"")</x:f>
-        <x:v>-0.025890044591399874</x:v>
+        <x:v>-0.01751241813542126</x:v>
       </x:c>
       <x:c r="I73" s="26" t="n">
         <x:f>ROUND(D73-E73,1)</x:f>
@@ -9671,7 +9707,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K73" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -10939,7 +10975,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B110" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C110" s="23" t="n">
         <x:v>3930.1</x:v>
@@ -10951,15 +10987,15 @@
         <x:v>3879.58</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>3894.42</x:v>
+        <x:v>3903.72</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
         <x:f>ROUND(F110-F109,1)</x:f>
-        <x:v>-32.8</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="H110" s="24" t="n">
         <x:f>IFERROR(F110/F109-1,"")</x:f>
-        <x:v>-0.008341863627335577</x:v>
+        <x:v>-0.005973752158037082</x:v>
       </x:c>
       <x:c r="I110" s="26" t="n">
         <x:f>ROUND(D110-E110,1)</x:f>
@@ -10969,7 +11005,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K110" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -13535,7 +13571,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
         <x:v>7885</x:v>
@@ -13547,15 +13583,15 @@
         <x:v>7680.2</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>7712</x:v>
+        <x:v>7761</x:v>
       </x:c>
       <x:c r="G184" s="23" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>-149.2</x:v>
+        <x:v>-100.2</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>-0.01897929069353277</x:v>
+        <x:v>-0.012746145626621908</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
@@ -13565,7 +13601,7 @@
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K184" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -14833,7 +14869,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
         <x:v>4624</x:v>
@@ -14845,15 +14881,15 @@
         <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4554.2</x:v>
+        <x:v>4554</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>-66.2</x:v>
+        <x:v>-66.4</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>-0.014327763829971363</x:v>
+        <x:v>-0.014371050125530194</x:v>
       </x:c>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
@@ -14863,7 +14899,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -17429,7 +17465,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
         <x:v>154300</x:v>
@@ -17441,15 +17477,15 @@
         <x:v>148400</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>149480</x:v>
+        <x:v>151500</x:v>
       </x:c>
       <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-4460</x:v>
+        <x:v>-2440</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.028972326880602806</x:v>
+        <x:v>-0.01585033129790825</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
@@ -17459,7 +17495,7 @@
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K295" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -17599,13 +17635,13 @@
         <x:v>1月5日</x:v>
       </x:c>
       <x:c r="D5" s="23" t="n">
-        <x:v>7639.54</x:v>
+        <x:v>7639.538</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
-        <x:v>7753.96</x:v>
+        <x:v>7753.959</x:v>
       </x:c>
       <x:c r="F5" s="23" t="n">
-        <x:v>7623.75</x:v>
+        <x:v>7623.749</x:v>
       </x:c>
       <x:c r="G5" s="23" t="n">
         <x:v>7753.88</x:v>
@@ -17614,7 +17650,7 @@
         <x:v>158.6</x:v>
       </x:c>
       <x:c r="I5" s="24" t="n">
-        <x:v>0.020881389494528335</x:v>
+        <x:v>0.020880717445099117</x:v>
       </x:c>
       <x:c r="J5" s="23" t="n">
         <x:f>ROUND(E5-F5,1)</x:f>
@@ -17635,22 +17671,22 @@
         <x:v>1月6日</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
-        <x:v>7756.16</x:v>
+        <x:v>7756.158</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
-        <x:v>7864.9</x:v>
+        <x:v>7864.903</x:v>
       </x:c>
       <x:c r="F6" s="23" t="n">
-        <x:v>7755.07</x:v>
+        <x:v>7755.072</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
-        <x:v>7864.9</x:v>
+        <x:v>7864.903</x:v>
       </x:c>
       <x:c r="H6" s="23" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="I6" s="24" t="n">
-        <x:v>0.014317993056379485</x:v>
+        <x:v>0.01431837995945262</x:v>
       </x:c>
       <x:c r="J6" s="23" t="n">
         <x:f>ROUND(E6-F6,1)</x:f>
@@ -17671,13 +17707,13 @@
         <x:v>1月7日</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
-        <x:v>7881.84</x:v>
+        <x:v>7881.836</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
-        <x:v>7939.75</x:v>
+        <x:v>7939.752</x:v>
       </x:c>
       <x:c r="F7" s="23" t="n">
-        <x:v>7864.14</x:v>
+        <x:v>7864.139</x:v>
       </x:c>
       <x:c r="G7" s="23" t="n">
         <x:v>7906.42</x:v>
@@ -17686,7 +17722,7 @@
         <x:v>41.5</x:v>
       </x:c>
       <x:c r="I7" s="24" t="n">
-        <x:v>0.005279151673892812</x:v>
+        <x:v>0.005278768218756058</x:v>
       </x:c>
       <x:c r="J7" s="23" t="n">
         <x:f>ROUND(E7-F7,1)</x:f>
@@ -17710,19 +17746,19 @@
         <x:v>7886.81</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
-        <x:v>7993.63</x:v>
+        <x:v>7993.631</x:v>
       </x:c>
       <x:c r="F8" s="23" t="n">
-        <x:v>7886.63</x:v>
+        <x:v>7886.629</x:v>
       </x:c>
       <x:c r="G8" s="23" t="n">
-        <x:v>7971.59</x:v>
+        <x:v>7971.589</x:v>
       </x:c>
       <x:c r="H8" s="23" t="n">
         <x:v>65.2</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>0.008242668616137205</x:v>
+        <x:v>0.008242542136643438</x:v>
       </x:c>
       <x:c r="J8" s="23" t="n">
         <x:f>ROUND(E8-F8,1)</x:f>
@@ -17746,19 +17782,19 @@
         <x:v>7969.19</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
-        <x:v>8131.49</x:v>
+        <x:v>8131.491</x:v>
       </x:c>
       <x:c r="F9" s="23" t="n">
         <x:v>7969.19</x:v>
       </x:c>
       <x:c r="G9" s="23" t="n">
-        <x:v>8129.18</x:v>
+        <x:v>8129.183</x:v>
       </x:c>
       <x:c r="H9" s="28" t="n">
         <x:v>157.6</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>0.01976895449966687</x:v>
+        <x:v>0.019769458761609515</x:v>
       </x:c>
       <x:c r="J9" s="23" t="n">
         <x:f>ROUND(E9-F9,1)</x:f>
@@ -17779,22 +17815,22 @@
         <x:v>1月12日</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
-        <x:v>8196.08</x:v>
+        <x:v>8196.085</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
-        <x:v>8371.75</x:v>
+        <x:v>8371.749</x:v>
       </x:c>
       <x:c r="F10" s="23" t="n">
-        <x:v>8171.11</x:v>
+        <x:v>8171.105</x:v>
       </x:c>
       <x:c r="G10" s="23" t="n">
-        <x:v>8357.01</x:v>
+        <x:v>8357.011</x:v>
       </x:c>
       <x:c r="H10" s="28" t="n">
         <x:v>227.8</x:v>
       </x:c>
       <x:c r="I10" s="24" t="n">
-        <x:v>0.028026196984197727</x:v>
+        <x:v>0.028025940614204492</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
         <x:f>ROUND(E10-F10,1)</x:f>
@@ -17815,22 +17851,22 @@
         <x:v>1月13日</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
-        <x:v>8381.04</x:v>
+        <x:v>8381.042</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
-        <x:v>8381.04</x:v>
+        <x:v>8381.042</x:v>
       </x:c>
       <x:c r="F11" s="23" t="n">
-        <x:v>8177.63</x:v>
+        <x:v>8177.629</x:v>
       </x:c>
       <x:c r="G11" s="23" t="n">
-        <x:v>8203.13</x:v>
+        <x:v>8203.133</x:v>
       </x:c>
       <x:c r="H11" s="28" t="n">
         <x:v>-153.9</x:v>
       </x:c>
       <x:c r="I11" s="24" t="n">
-        <x:v>-0.018413284176996392</x:v>
+        <x:v>-0.018413042653647405</x:v>
       </x:c>
       <x:c r="J11" s="26" t="n">
         <x:f>ROUND(E11-F11,1)</x:f>
@@ -17854,19 +17890,19 @@
         <x:v>8204.28</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
-        <x:v>8415.1</x:v>
+        <x:v>8415.098</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
-        <x:v>8154.24</x:v>
+        <x:v>8154.241</x:v>
       </x:c>
       <x:c r="G12" s="23" t="n">
-        <x:v>8257.17</x:v>
+        <x:v>8257.172</x:v>
       </x:c>
       <x:c r="H12" s="23" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="I12" s="24" t="n">
-        <x:v>0.006587729317955482</x:v>
+        <x:v>0.00658760500408806</x:v>
       </x:c>
       <x:c r="J12" s="26" t="n">
         <x:f>ROUND(E12-F12,1)</x:f>
@@ -17887,22 +17923,22 @@
         <x:v>1月15日</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
-        <x:v>8197.06</x:v>
+        <x:v>8197.061</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
-        <x:v>8267.81</x:v>
+        <x:v>8267.813</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
-        <x:v>8151.11</x:v>
+        <x:v>8151.107</x:v>
       </x:c>
       <x:c r="G13" s="23" t="n">
-        <x:v>8240.78</x:v>
+        <x:v>8240.775</x:v>
       </x:c>
       <x:c r="H13" s="23" t="n">
         <x:v>-16.4</x:v>
       </x:c>
       <x:c r="I13" s="24" t="n">
-        <x:v>-0.00198494157199125</x:v>
+        <x:v>-0.0019857888390845124</x:v>
       </x:c>
       <x:c r="J13" s="23" t="n">
         <x:f>ROUND(E13-F13,1)</x:f>
@@ -17923,22 +17959,22 @@
         <x:v>1月16日</x:v>
       </x:c>
       <x:c r="D14" s="42" t="n">
-        <x:v>8276.61</x:v>
+        <x:v>8276.608</x:v>
       </x:c>
       <x:c r="E14" s="42" t="n">
-        <x:v>8304.4</x:v>
+        <x:v>8304.399</x:v>
       </x:c>
       <x:c r="F14" s="42" t="n">
-        <x:v>8180.12</x:v>
+        <x:v>8180.117</x:v>
       </x:c>
       <x:c r="G14" s="42" t="n">
-        <x:v>8232.73</x:v>
+        <x:v>8232.729</x:v>
       </x:c>
       <x:c r="H14" s="42" t="n">
-        <x:v>-8.1</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="I14" s="43" t="n">
-        <x:v>-0.0009768492788305716</x:v>
+        <x:v>-0.0009763644802824878</x:v>
       </x:c>
       <x:c r="J14" s="42" t="n">
         <x:f>ROUND(E14-F14,1)</x:f>
@@ -17959,22 +17995,22 @@
         <x:v>1月19日</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>8204.63</x:v>
+        <x:v>8204.627</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
         <x:v>8298.48</x:v>
       </x:c>
       <x:c r="F15" s="23" t="n">
-        <x:v>8187.94</x:v>
+        <x:v>8187.938</x:v>
       </x:c>
       <x:c r="G15" s="23" t="n">
-        <x:v>8265.65</x:v>
+        <x:v>8265.646</x:v>
       </x:c>
       <x:c r="H15" s="23" t="n">
         <x:v>32.9</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
-        <x:v>0.003998673587011892</x:v>
+        <x:v>0.003998309673499678</x:v>
       </x:c>
       <x:c r="J15" s="23" t="n">
         <x:f>ROUND(E15-F15,1)</x:f>
@@ -17995,22 +18031,22 @@
         <x:v>1月20日</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
-        <x:v>8271.78</x:v>
+        <x:v>8271.779</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
         <x:v>8300.05</x:v>
       </x:c>
       <x:c r="F16" s="23" t="n">
-        <x:v>8104.92</x:v>
+        <x:v>8104.918</x:v>
       </x:c>
       <x:c r="G16" s="23" t="n">
-        <x:v>8182.75</x:v>
+        <x:v>8182.752</x:v>
       </x:c>
       <x:c r="H16" s="23" t="n">
         <x:v>-82.9</x:v>
       </x:c>
       <x:c r="I16" s="24" t="n">
-        <x:v>-0.01002945926817611</x:v>
+        <x:v>-0.010028738225663192</x:v>
       </x:c>
       <x:c r="J16" s="26" t="n">
         <x:f>ROUND(E16-F16,1)</x:f>
@@ -18031,13 +18067,13 @@
         <x:v>1月21日</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>8138.68</x:v>
+        <x:v>8138.682</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
-        <x:v>8289.13</x:v>
+        <x:v>8289.134</x:v>
       </x:c>
       <x:c r="F17" s="23" t="n">
-        <x:v>8136.92</x:v>
+        <x:v>8136.918</x:v>
       </x:c>
       <x:c r="G17" s="23" t="n">
         <x:v>8247.68</x:v>
@@ -18046,7 +18082,7 @@
         <x:v>64.9</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>0.007934985182243226</x:v>
+        <x:v>0.007934738826252952</x:v>
       </x:c>
       <x:c r="J17" s="23" t="n">
         <x:f>ROUND(E17-F17,1)</x:f>
@@ -18067,22 +18103,22 @@
         <x:v>1月22日</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
-        <x:v>8272.47</x:v>
+        <x:v>8272.468</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
-        <x:v>8314.22</x:v>
+        <x:v>8314.216</x:v>
       </x:c>
       <x:c r="F18" s="23" t="n">
-        <x:v>8252.74</x:v>
+        <x:v>8252.745</x:v>
       </x:c>
       <x:c r="G18" s="23" t="n">
-        <x:v>8309.35</x:v>
+        <x:v>8309.346</x:v>
       </x:c>
       <x:c r="H18" s="23" t="n">
         <x:v>61.7</x:v>
       </x:c>
       <x:c r="I18" s="24" t="n">
-        <x:v>0.0074772542096686045</x:v>
+        <x:v>0.007476769224800117</x:v>
       </x:c>
       <x:c r="J18" s="23" t="n">
         <x:f>ROUND(E18-F18,1)</x:f>
@@ -18106,19 +18142,19 @@
         <x:v>8331.77</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
-        <x:v>8478.56</x:v>
+        <x:v>8478.556</x:v>
       </x:c>
       <x:c r="F19" s="23" t="n">
-        <x:v>8323.35</x:v>
+        <x:v>8323.349</x:v>
       </x:c>
       <x:c r="G19" s="23" t="n">
-        <x:v>8470.74</x:v>
+        <x:v>8470.744</x:v>
       </x:c>
       <x:c r="H19" s="28" t="n">
         <x:v>161.4</x:v>
       </x:c>
       <x:c r="I19" s="24" t="n">
-        <x:v>0.019422698526358806</x:v>
+        <x:v>0.019423670647485514</x:v>
       </x:c>
       <x:c r="J19" s="23" t="n">
         <x:f>ROUND(E19-F19,1)</x:f>
@@ -18139,22 +18175,22 @@
         <x:v>1月26日</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
-        <x:v>8513.22</x:v>
+        <x:v>8513.222</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
-        <x:v>8530.42</x:v>
+        <x:v>8530.417</x:v>
       </x:c>
       <x:c r="F20" s="23" t="n">
-        <x:v>8302.1</x:v>
+        <x:v>8302.099</x:v>
       </x:c>
       <x:c r="G20" s="23" t="n">
-        <x:v>8365.43</x:v>
+        <x:v>8365.435</x:v>
       </x:c>
       <x:c r="H20" s="23" t="n">
         <x:v>-105.3</x:v>
       </x:c>
       <x:c r="I20" s="24" t="n">
-        <x:v>-0.012432207811832185</x:v>
+        <x:v>-0.012432083887790824</x:v>
       </x:c>
       <x:c r="J20" s="26" t="n">
         <x:f>ROUND(E20-F20,1)</x:f>
@@ -18175,22 +18211,22 @@
         <x:v>1月27日</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:v>8325.43</x:v>
+        <x:v>8325.433</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
-        <x:v>8406.1</x:v>
+        <x:v>8406.099</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
-        <x:v>8186.24</x:v>
+        <x:v>8186.244</x:v>
       </x:c>
       <x:c r="G21" s="23" t="n">
-        <x:v>8382.15</x:v>
+        <x:v>8382.153</x:v>
       </x:c>
       <x:c r="H21" s="23" t="n">
         <x:v>16.7</x:v>
       </x:c>
       <x:c r="I21" s="24" t="n">
-        <x:v>0.001998701800146385</x:v>
+        <x:v>0.001998461526507622</x:v>
       </x:c>
       <x:c r="J21" s="26" t="n">
         <x:f>ROUND(E21-F21,1)</x:f>
@@ -18211,22 +18247,22 @@
         <x:v>1月28日</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
-        <x:v>8392.75</x:v>
+        <x:v>8392.753</x:v>
       </x:c>
       <x:c r="E22" s="23" t="n">
         <x:v>8432.62</x:v>
       </x:c>
       <x:c r="F22" s="23" t="n">
-        <x:v>8334.68</x:v>
+        <x:v>8334.683</x:v>
       </x:c>
       <x:c r="G22" s="23" t="n">
-        <x:v>8399.79</x:v>
+        <x:v>8399.794</x:v>
       </x:c>
       <x:c r="H22" s="23" t="n">
         <x:v>17.6</x:v>
       </x:c>
       <x:c r="I22" s="24" t="n">
-        <x:v>0.0021044720030065633</x:v>
+        <x:v>0.002104590550900287</x:v>
       </x:c>
       <x:c r="J22" s="23" t="n">
         <x:f>ROUND(E22-F22,1)</x:f>
@@ -18247,22 +18283,22 @@
         <x:v>1月29日</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
-        <x:v>8380.61</x:v>
+        <x:v>8380.605</x:v>
       </x:c>
       <x:c r="E23" s="23" t="n">
-        <x:v>8463.12</x:v>
+        <x:v>8463.125</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
-        <x:v>8308.82</x:v>
+        <x:v>8308.825</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
-        <x:v>8332.21</x:v>
+        <x:v>8332.207</x:v>
       </x:c>
       <x:c r="H23" s="23" t="n">
         <x:v>-67.6</x:v>
       </x:c>
       <x:c r="I23" s="24" t="n">
-        <x:v>-0.008045439231219031</x:v>
+        <x:v>-0.00804626875373371</x:v>
       </x:c>
       <x:c r="J23" s="23" t="n">
         <x:f>ROUND(E23-F23,1)</x:f>
@@ -18283,10 +18319,10 @@
         <x:v>1月30日</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
-        <x:v>8255.33</x:v>
+        <x:v>8255.335</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
-        <x:v>8313.23</x:v>
+        <x:v>8313.227</x:v>
       </x:c>
       <x:c r="F24" s="23" t="n">
         <x:v>8083.97</x:v>
@@ -18298,7 +18334,7 @@
         <x:v>-77.3</x:v>
       </x:c>
       <x:c r="I24" s="24" t="n">
-        <x:v>-0.00928325138228614</x:v>
+        <x:v>-0.009282894676044373</x:v>
       </x:c>
       <x:c r="J24" s="26" t="n">
         <x:f>ROUND(E24-F24,1)</x:f>
@@ -18407,22 +18443,22 @@
         <x:v>2月2日</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
-        <x:v>8166.74</x:v>
+        <x:v>8166.736</x:v>
       </x:c>
       <x:c r="E30" s="23" t="n">
-        <x:v>8221.58</x:v>
+        <x:v>8221.582</x:v>
       </x:c>
       <x:c r="F30" s="23" t="n">
-        <x:v>7974.6</x:v>
+        <x:v>7974.599</x:v>
       </x:c>
       <x:c r="G30" s="23" t="n">
-        <x:v>7975.43</x:v>
+        <x:v>7975.428</x:v>
       </x:c>
       <x:c r="H30" s="28" t="n">
         <x:v>-279.4</x:v>
       </x:c>
       <x:c r="I30" s="24" t="n">
-        <x:v>-0.03385036208972658</x:v>
+        <x:v>-0.03385060437124321</x:v>
       </x:c>
       <x:c r="J30" s="26" t="n">
         <x:f>ROUND(E30-F30,1)</x:f>
@@ -18443,22 +18479,22 @@
         <x:v>2月3日</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
-        <x:v>8058.76</x:v>
+        <x:v>8058.763</x:v>
       </x:c>
       <x:c r="E31" s="23" t="n">
-        <x:v>8210.05</x:v>
+        <x:v>8210.047</x:v>
       </x:c>
       <x:c r="F31" s="23" t="n">
-        <x:v>8023.24</x:v>
+        <x:v>8023.238</x:v>
       </x:c>
       <x:c r="G31" s="23" t="n">
-        <x:v>8209.1</x:v>
+        <x:v>8209.101</x:v>
       </x:c>
       <x:c r="H31" s="28" t="n">
         <x:v>233.7</x:v>
       </x:c>
       <x:c r="I31" s="24" t="n">
-        <x:v>0.029298733735986682</x:v>
+        <x:v>0.02929911723859835</x:v>
       </x:c>
       <x:c r="J31" s="26" t="n">
         <x:f>ROUND(E31-F31,1)</x:f>
@@ -18479,10 +18515,10 @@
         <x:v>2月4日</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
-        <x:v>8184.2</x:v>
+        <x:v>8184.205</x:v>
       </x:c>
       <x:c r="E32" s="23" t="n">
-        <x:v>8216.2</x:v>
+        <x:v>8216.204</x:v>
       </x:c>
       <x:c r="F32" s="23" t="n">
         <x:v>8101.2</x:v>
@@ -18494,7 +18530,7 @@
         <x:v>-2</x:v>
       </x:c>
       <x:c r="I32" s="24" t="n">
-        <x:v>-0.00024119574618408635</x:v>
+        <x:v>-0.00024131753282119472</x:v>
       </x:c>
       <x:c r="J32" s="23" t="n">
         <x:f>ROUND(E32-F32,1)</x:f>
@@ -18515,22 +18551,22 @@
         <x:v>2月5日</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
-        <x:v>8121.51</x:v>
+        <x:v>8121.511</x:v>
       </x:c>
       <x:c r="E33" s="23" t="n">
-        <x:v>8154.56</x:v>
+        <x:v>8154.558</x:v>
       </x:c>
       <x:c r="F33" s="23" t="n">
-        <x:v>8027.62</x:v>
+        <x:v>8027.623</x:v>
       </x:c>
       <x:c r="G33" s="23" t="n">
-        <x:v>8068.08</x:v>
+        <x:v>8068.077</x:v>
       </x:c>
       <x:c r="H33" s="23" t="n">
         <x:v>-139</x:v>
       </x:c>
       <x:c r="I33" s="24" t="n">
-        <x:v>-0.01694138747818974</x:v>
+        <x:v>-0.016941753014455774</x:v>
       </x:c>
       <x:c r="J33" s="23" t="n">
         <x:f>ROUND(E33-F33,1)</x:f>
@@ -18551,22 +18587,22 @@
         <x:v>2月6日</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7980.47</x:v>
+        <x:v>7980.466</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
-        <x:v>8152.32</x:v>
+        <x:v>8152.322</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
         <x:v>7950.01</x:v>
       </x:c>
       <x:c r="G34" s="23" t="n">
-        <x:v>8051.57</x:v>
+        <x:v>8051.574</x:v>
       </x:c>
       <x:c r="H34" s="23" t="n">
         <x:v>-16.5</x:v>
       </x:c>
       <x:c r="I34" s="24" t="n">
-        <x:v>-0.002046335683334899</x:v>
+        <x:v>-0.0020454688273302546</x:v>
       </x:c>
       <x:c r="J34" s="26" t="n">
         <x:f>ROUND(E34-F34,1)</x:f>
@@ -18587,22 +18623,22 @@
         <x:v>2月9日</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>8177.29</x:v>
+        <x:v>8177.291</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
-        <x:v>8235.15</x:v>
+        <x:v>8235.155</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>8149.65</x:v>
+        <x:v>8149.646</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
-        <x:v>8233.78</x:v>
+        <x:v>8233.778</x:v>
       </x:c>
       <x:c r="H35" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I35" s="24" t="n">
-        <x:v>0.022630368983937332</x:v>
+        <x:v>0.022629612545323585</x:v>
       </x:c>
       <x:c r="J35" s="23" t="n">
         <x:f>ROUND(E35-F35,1)</x:f>
@@ -18623,13 +18659,13 @@
         <x:v>2月10日</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>8246.22</x:v>
+        <x:v>8246.218</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>8274.14</x:v>
+        <x:v>8274.143</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>8199.51</x:v>
+        <x:v>8199.511</x:v>
       </x:c>
       <x:c r="G36" s="23" t="n">
         <x:v>8250.3</x:v>
@@ -18638,7 +18674,7 @@
         <x:v>16.5</x:v>
       </x:c>
       <x:c r="I36" s="24" t="n">
-        <x:v>0.00200636888525052</x:v>
+        <x:v>0.002006612274462416</x:v>
       </x:c>
       <x:c r="J36" s="23" t="n">
         <x:f>ROUND(E36-F36,1)</x:f>
@@ -18662,19 +18698,19 @@
         <x:v>8239.17</x:v>
       </x:c>
       <x:c r="E37" s="23" t="n">
-        <x:v>8304.13</x:v>
+        <x:v>8304.125</x:v>
       </x:c>
       <x:c r="F37" s="23" t="n">
-        <x:v>8236.96</x:v>
+        <x:v>8236.957</x:v>
       </x:c>
       <x:c r="G37" s="23" t="n">
-        <x:v>8239.51</x:v>
+        <x:v>8239.513</x:v>
       </x:c>
       <x:c r="H37" s="23" t="n">
         <x:v>-10.8</x:v>
       </x:c>
       <x:c r="I37" s="24" t="n">
-        <x:v>-0.0013078312303793638</x:v>
+        <x:v>-0.0013074676072383218</x:v>
       </x:c>
       <x:c r="J37" s="23" t="n">
         <x:f>ROUND(E37-F37,1)</x:f>
@@ -18695,22 +18731,22 @@
         <x:v>2月12日</x:v>
       </x:c>
       <x:c r="D38" s="23" t="n">
-        <x:v>8252.19</x:v>
+        <x:v>8252.185</x:v>
       </x:c>
       <x:c r="E38" s="23" t="n">
-        <x:v>8337.37</x:v>
+        <x:v>8337.371</x:v>
       </x:c>
       <x:c r="F38" s="23" t="n">
-        <x:v>8227.6</x:v>
+        <x:v>8227.604</x:v>
       </x:c>
       <x:c r="G38" s="23" t="n">
-        <x:v>8314.83</x:v>
+        <x:v>8314.832</x:v>
       </x:c>
       <x:c r="H38" s="23" t="n">
         <x:v>75.3</x:v>
       </x:c>
       <x:c r="I38" s="24" t="n">
-        <x:v>0.009141320296959465</x:v>
+        <x:v>0.009141195602215824</x:v>
       </x:c>
       <x:c r="J38" s="23" t="n">
         <x:f>ROUND(E38-F38,1)</x:f>
@@ -18731,22 +18767,22 @@
         <x:v>2月13日</x:v>
       </x:c>
       <x:c r="D39" s="23" t="n">
-        <x:v>8272.88</x:v>
+        <x:v>8272.876</x:v>
       </x:c>
       <x:c r="E39" s="23" t="n">
-        <x:v>8323.72</x:v>
+        <x:v>8323.715</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>8200.15</x:v>
+        <x:v>8200.148</x:v>
       </x:c>
       <x:c r="G39" s="23" t="n">
-        <x:v>8204.83</x:v>
+        <x:v>8204.829</x:v>
       </x:c>
       <x:c r="H39" s="23" t="n">
         <x:v>-110</x:v>
       </x:c>
       <x:c r="I39" s="24" t="n">
-        <x:v>-0.013229374503146762</x:v>
+        <x:v>-0.013229732122068238</x:v>
       </x:c>
       <x:c r="J39" s="23" t="n">
         <x:f>ROUND(E39-F39,1)</x:f>
@@ -18767,22 +18803,22 @@
         <x:v>2月24日</x:v>
       </x:c>
       <x:c r="D40" s="42" t="n">
-        <x:v>8319.69</x:v>
+        <x:v>8319.691</x:v>
       </x:c>
       <x:c r="E40" s="42" t="n">
-        <x:v>8356.91</x:v>
+        <x:v>8356.914</x:v>
       </x:c>
       <x:c r="F40" s="42" t="n">
-        <x:v>8236.71</x:v>
+        <x:v>8236.707</x:v>
       </x:c>
       <x:c r="G40" s="42" t="n">
-        <x:v>8299.77</x:v>
+        <x:v>8299.771</x:v>
       </x:c>
       <x:c r="H40" s="42" t="n">
         <x:v>94.9</x:v>
       </x:c>
       <x:c r="I40" s="43" t="n">
-        <x:v>0.011571233042001028</x:v>
+        <x:v>0.011571478211185315</x:v>
       </x:c>
       <x:c r="J40" s="42" t="n">
         <x:f>ROUND(E40-F40,1)</x:f>
@@ -18803,22 +18839,22 @@
         <x:v>2月25日</x:v>
       </x:c>
       <x:c r="D41" s="23" t="n">
-        <x:v>8320.61</x:v>
+        <x:v>8320.612</x:v>
       </x:c>
       <x:c r="E41" s="23" t="n">
-        <x:v>8449.76</x:v>
+        <x:v>8449.763</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>8310.33</x:v>
+        <x:v>8310.325</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
-        <x:v>8426.33</x:v>
+        <x:v>8426.331</x:v>
       </x:c>
       <x:c r="H41" s="23" t="n">
         <x:v>126.6</x:v>
       </x:c>
       <x:c r="I41" s="24" t="n">
-        <x:v>0.015248615323075088</x:v>
+        <x:v>0.015248613485841833</x:v>
       </x:c>
       <x:c r="J41" s="23" t="n">
         <x:f>ROUND(E41-F41,1)</x:f>
@@ -18839,22 +18875,22 @@
         <x:v>2月26日</x:v>
       </x:c>
       <x:c r="D42" s="23" t="n">
-        <x:v>8447.78</x:v>
+        <x:v>8447.783</x:v>
       </x:c>
       <x:c r="E42" s="23" t="n">
-        <x:v>8496.75</x:v>
+        <x:v>8496.748</x:v>
       </x:c>
       <x:c r="F42" s="23" t="n">
-        <x:v>8398.07</x:v>
+        <x:v>8398.066</x:v>
       </x:c>
       <x:c r="G42" s="23" t="n">
-        <x:v>8490.62</x:v>
+        <x:v>8490.617</x:v>
       </x:c>
       <x:c r="H42" s="23" t="n">
         <x:v>64.3</x:v>
       </x:c>
       <x:c r="I42" s="24" t="n">
-        <x:v>0.007629656089899184</x:v>
+        <x:v>0.00762918048199146</x:v>
       </x:c>
       <x:c r="J42" s="23" t="n">
         <x:f>ROUND(E42-F42,1)</x:f>
@@ -18875,22 +18911,22 @@
         <x:v>2月27日</x:v>
       </x:c>
       <x:c r="D43" s="23" t="n">
-        <x:v>8434.1</x:v>
+        <x:v>8434.096</x:v>
       </x:c>
       <x:c r="E43" s="23" t="n">
-        <x:v>8561.3</x:v>
+        <x:v>8561.295</x:v>
       </x:c>
       <x:c r="F43" s="23" t="n">
-        <x:v>8433.72</x:v>
+        <x:v>8433.717</x:v>
       </x:c>
       <x:c r="G43" s="23" t="n">
-        <x:v>8560.84</x:v>
+        <x:v>8560.843</x:v>
       </x:c>
       <x:c r="H43" s="23" t="n">
         <x:v>70.2</x:v>
       </x:c>
       <x:c r="I43" s="24" t="n">
-        <x:v>0.00827030299318543</x:v>
+        <x:v>0.008271012577766745</x:v>
       </x:c>
       <x:c r="J43" s="23" t="n">
         <x:f>ROUND(E43-F43,1)</x:f>
@@ -18999,22 +19035,22 @@
         <x:v>3月2日</x:v>
       </x:c>
       <x:c r="D49" s="23" t="n">
-        <x:v>8464.27</x:v>
+        <x:v>8464.273</x:v>
       </x:c>
       <x:c r="E49" s="23" t="n">
-        <x:v>8535.81</x:v>
+        <x:v>8535.807</x:v>
       </x:c>
       <x:c r="F49" s="23" t="n">
-        <x:v>8393.93</x:v>
+        <x:v>8393.927</x:v>
       </x:c>
       <x:c r="G49" s="23" t="n">
-        <x:v>8476.97</x:v>
+        <x:v>8476.965</x:v>
       </x:c>
       <x:c r="H49" s="23" t="n">
         <x:v>-83.9</x:v>
       </x:c>
       <x:c r="I49" s="24" t="n">
-        <x:v>-0.009796935814709862</x:v>
+        <x:v>-0.009797866868952121</x:v>
       </x:c>
       <x:c r="J49" s="23" t="n">
         <x:f>ROUND(E49-F49,1)</x:f>
@@ -19035,26 +19071,26 @@
         <x:v>3月3日</x:v>
       </x:c>
       <x:c r="D50" s="23" t="n">
-        <x:v>8495.95</x:v>
+        <x:v>8495.954</x:v>
       </x:c>
       <x:c r="E50" s="23" t="n">
-        <x:v>8510.85</x:v>
+        <x:v>8510.854</x:v>
       </x:c>
       <x:c r="F50" s="23" t="n">
-        <x:v>8128.3</x:v>
+        <x:v>8128.305</x:v>
       </x:c>
       <x:c r="G50" s="23" t="n">
-        <x:v>8142.45</x:v>
+        <x:v>8142.454</x:v>
       </x:c>
       <x:c r="H50" s="28" t="n">
         <x:v>-334.5</x:v>
       </x:c>
       <x:c r="I50" s="24" t="n">
-        <x:v>-0.039462213503173804</x:v>
+        <x:v>-0.0394611750785806</x:v>
       </x:c>
       <x:c r="J50" s="26" t="n">
         <x:f>ROUND(E50-F50,1)</x:f>
-        <x:v>382.6</x:v>
+        <x:v>382.5</x:v>
       </x:c>
       <x:c r="K50" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -19071,22 +19107,22 @@
         <x:v>3月4日</x:v>
       </x:c>
       <x:c r="D51" s="23" t="n">
-        <x:v>8039.59</x:v>
+        <x:v>8039.593</x:v>
       </x:c>
       <x:c r="E51" s="23" t="n">
-        <x:v>8228.9</x:v>
+        <x:v>8228.895</x:v>
       </x:c>
       <x:c r="F51" s="23" t="n">
-        <x:v>8039.59</x:v>
+        <x:v>8039.593</x:v>
       </x:c>
       <x:c r="G51" s="23" t="n">
-        <x:v>8094.52</x:v>
+        <x:v>8094.518</x:v>
       </x:c>
       <x:c r="H51" s="23" t="n">
         <x:v>-47.9</x:v>
       </x:c>
       <x:c r="I51" s="24" t="n">
-        <x:v>-0.005886434672610741</x:v>
+        <x:v>-0.005887168659472919</x:v>
       </x:c>
       <x:c r="J51" s="26" t="n">
         <x:f>ROUND(E51-F51,1)</x:f>
@@ -19107,22 +19143,22 @@
         <x:v>3月5日</x:v>
       </x:c>
       <x:c r="D52" s="23" t="n">
-        <x:v>8235.37</x:v>
+        <x:v>8235.374</x:v>
       </x:c>
       <x:c r="E52" s="23" t="n">
-        <x:v>8243.83</x:v>
+        <x:v>8243.829</x:v>
       </x:c>
       <x:c r="F52" s="23" t="n">
-        <x:v>8121.38</x:v>
+        <x:v>8121.382</x:v>
       </x:c>
       <x:c r="G52" s="23" t="n">
-        <x:v>8171.12</x:v>
+        <x:v>8171.119</x:v>
       </x:c>
       <x:c r="H52" s="23" t="n">
         <x:v>76.6</x:v>
       </x:c>
       <x:c r="I52" s="24" t="n">
-        <x:v>0.009463192382006547</x:v>
+        <x:v>0.009463318260580778</x:v>
       </x:c>
       <x:c r="J52" s="23" t="n">
         <x:f>ROUND(E52-F52,1)</x:f>
@@ -19143,22 +19179,22 @@
         <x:v>3月6日</x:v>
       </x:c>
       <x:c r="D53" s="23" t="n">
-        <x:v>8120.49</x:v>
+        <x:v>8120.495</x:v>
       </x:c>
       <x:c r="E53" s="23" t="n">
         <x:v>8273.68</x:v>
       </x:c>
       <x:c r="F53" s="23" t="n">
-        <x:v>8115.48</x:v>
+        <x:v>8115.479</x:v>
       </x:c>
       <x:c r="G53" s="23" t="n">
-        <x:v>8248.86</x:v>
+        <x:v>8248.857</x:v>
       </x:c>
       <x:c r="H53" s="23" t="n">
         <x:v>77.7</x:v>
       </x:c>
       <x:c r="I53" s="24" t="n">
-        <x:v>0.009513995633401606</x:v>
+        <x:v>0.00951375203322824</x:v>
       </x:c>
       <x:c r="J53" s="23" t="n">
         <x:f>ROUND(E53-F53,1)</x:f>
@@ -19179,22 +19215,22 @@
         <x:v>3月9日</x:v>
       </x:c>
       <x:c r="D54" s="23" t="n">
-        <x:v>8131.74</x:v>
+        <x:v>8131.742</x:v>
       </x:c>
       <x:c r="E54" s="23" t="n">
-        <x:v>8230.66</x:v>
+        <x:v>8230.656</x:v>
       </x:c>
       <x:c r="F54" s="23" t="n">
-        <x:v>7983.57</x:v>
+        <x:v>7983.569</x:v>
       </x:c>
       <x:c r="G54" s="23" t="n">
-        <x:v>8203.87</x:v>
+        <x:v>8203.869</x:v>
       </x:c>
       <x:c r="H54" s="23" t="n">
         <x:v>-45</x:v>
       </x:c>
       <x:c r="I54" s="24" t="n">
-        <x:v>-0.00545408698898997</x:v>
+        <x:v>-0.005453846514735239</x:v>
       </x:c>
       <x:c r="J54" s="26" t="n">
         <x:f>ROUND(E54-F54,1)</x:f>
@@ -19215,13 +19251,13 @@
         <x:v>3月10日</x:v>
       </x:c>
       <x:c r="D55" s="23" t="n">
-        <x:v>8272.94</x:v>
+        <x:v>8272.941</x:v>
       </x:c>
       <x:c r="E55" s="23" t="n">
-        <x:v>8351.67</x:v>
+        <x:v>8351.666</x:v>
       </x:c>
       <x:c r="F55" s="23" t="n">
-        <x:v>8271.49</x:v>
+        <x:v>8271.493</x:v>
       </x:c>
       <x:c r="G55" s="23" t="n">
         <x:v>8350.09</x:v>
@@ -19230,7 +19266,7 @@
         <x:v>146.2</x:v>
       </x:c>
       <x:c r="I55" s="24" t="n">
-        <x:v>0.017823295590983168</x:v>
+        <x:v>0.017823419657237327</x:v>
       </x:c>
       <x:c r="J55" s="23" t="n">
         <x:f>ROUND(E55-F55,1)</x:f>
@@ -19254,19 +19290,19 @@
         <x:v>8356.09</x:v>
       </x:c>
       <x:c r="E56" s="23" t="n">
-        <x:v>8394.12</x:v>
+        <x:v>8394.122</x:v>
       </x:c>
       <x:c r="F56" s="23" t="n">
-        <x:v>8334.33</x:v>
+        <x:v>8334.328</x:v>
       </x:c>
       <x:c r="G56" s="23" t="n">
-        <x:v>8363.53</x:v>
+        <x:v>8363.526</x:v>
       </x:c>
       <x:c r="H56" s="23" t="n">
         <x:v>13.4</x:v>
       </x:c>
       <x:c r="I56" s="24" t="n">
-        <x:v>0.0016095634897348443</x:v>
+        <x:v>0.0016090844529819126</x:v>
       </x:c>
       <x:c r="J56" s="23" t="n">
         <x:f>ROUND(E56-F56,1)</x:f>
@@ -19287,22 +19323,22 @@
         <x:v>3月12日</x:v>
       </x:c>
       <x:c r="D57" s="23" t="n">
-        <x:v>8357.35</x:v>
+        <x:v>8357.351</x:v>
       </x:c>
       <x:c r="E57" s="23" t="n">
-        <x:v>8388.63</x:v>
+        <x:v>8388.633</x:v>
       </x:c>
       <x:c r="F57" s="23" t="n">
         <x:v>8267.39</x:v>
       </x:c>
       <x:c r="G57" s="23" t="n">
-        <x:v>8335.91</x:v>
+        <x:v>8335.908</x:v>
       </x:c>
       <x:c r="H57" s="23" t="n">
         <x:v>-27.6</x:v>
       </x:c>
       <x:c r="I57" s="24" t="n">
-        <x:v>-0.0033024333026845376</x:v>
+        <x:v>-0.003302195748539627</x:v>
       </x:c>
       <x:c r="J57" s="23" t="n">
         <x:f>ROUND(E57-F57,1)</x:f>
@@ -19323,22 +19359,22 @@
         <x:v>3月13日</x:v>
       </x:c>
       <x:c r="D58" s="23" t="n">
-        <x:v>8297.91</x:v>
+        <x:v>8297.913</x:v>
       </x:c>
       <x:c r="E58" s="23" t="n">
-        <x:v>8350.92</x:v>
+        <x:v>8350.917</x:v>
       </x:c>
       <x:c r="F58" s="23" t="n">
-        <x:v>8196.37</x:v>
+        <x:v>8196.374</x:v>
       </x:c>
       <x:c r="G58" s="23" t="n">
-        <x:v>8214.29</x:v>
+        <x:v>8214.293</x:v>
       </x:c>
       <x:c r="H58" s="23" t="n">
         <x:v>-121.6</x:v>
       </x:c>
       <x:c r="I58" s="24" t="n">
-        <x:v>-0.014589888806380902</x:v>
+        <x:v>-0.014589292492191541</x:v>
       </x:c>
       <x:c r="J58" s="23" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
@@ -19359,22 +19395,22 @@
         <x:v>3月16日</x:v>
       </x:c>
       <x:c r="D59" s="23" t="n">
-        <x:v>8212.27</x:v>
+        <x:v>8212.267</x:v>
       </x:c>
       <x:c r="E59" s="23" t="n">
-        <x:v>8226.03</x:v>
+        <x:v>8226.032</x:v>
       </x:c>
       <x:c r="F59" s="23" t="n">
-        <x:v>8089.49</x:v>
+        <x:v>8089.488</x:v>
       </x:c>
       <x:c r="G59" s="23" t="n">
-        <x:v>8211.35</x:v>
+        <x:v>8211.352</x:v>
       </x:c>
       <x:c r="H59" s="23" t="n">
         <x:v>-2.9</x:v>
       </x:c>
       <x:c r="I59" s="24" t="n">
-        <x:v>-0.00035791285674113826</x:v>
+        <x:v>-0.0003580344650475631</x:v>
       </x:c>
       <x:c r="J59" s="23" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
@@ -19398,19 +19434,19 @@
         <x:v>8219.5</x:v>
       </x:c>
       <x:c r="E60" s="23" t="n">
-        <x:v>8223.99</x:v>
+        <x:v>8223.989</x:v>
       </x:c>
       <x:c r="F60" s="23" t="n">
-        <x:v>8019.08</x:v>
+        <x:v>8019.075</x:v>
       </x:c>
       <x:c r="G60" s="23" t="n">
-        <x:v>8019.86</x:v>
+        <x:v>8019.857</x:v>
       </x:c>
       <x:c r="H60" s="28" t="n">
         <x:v>-191.5</x:v>
       </x:c>
       <x:c r="I60" s="24" t="n">
-        <x:v>-0.023320160509538668</x:v>
+        <x:v>-0.023320763742682216</x:v>
       </x:c>
       <x:c r="J60" s="26" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
@@ -19431,22 +19467,22 @@
         <x:v>3月18日</x:v>
       </x:c>
       <x:c r="D61" s="23" t="n">
-        <x:v>8050.71</x:v>
+        <x:v>8050.714</x:v>
       </x:c>
       <x:c r="E61" s="23" t="n">
-        <x:v>8105.81</x:v>
+        <x:v>8105.806</x:v>
       </x:c>
       <x:c r="F61" s="23" t="n">
-        <x:v>7970.19</x:v>
+        <x:v>7970.189</x:v>
       </x:c>
       <x:c r="G61" s="23" t="n">
-        <x:v>8096.59</x:v>
+        <x:v>8096.595</x:v>
       </x:c>
       <x:c r="H61" s="23" t="n">
         <x:v>76.7</x:v>
       </x:c>
       <x:c r="I61" s="24" t="n">
-        <x:v>0.009567498684515785</x:v>
+        <x:v>0.00956849978746499</x:v>
       </x:c>
       <x:c r="J61" s="23" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -19467,22 +19503,22 @@
         <x:v>3月19日</x:v>
       </x:c>
       <x:c r="D62" s="23" t="n">
-        <x:v>7988.87</x:v>
+        <x:v>7988.873</x:v>
       </x:c>
       <x:c r="E62" s="23" t="n">
-        <x:v>8008.39</x:v>
+        <x:v>8008.389</x:v>
       </x:c>
       <x:c r="F62" s="23" t="n">
-        <x:v>7874.26</x:v>
+        <x:v>7874.262</x:v>
       </x:c>
       <x:c r="G62" s="23" t="n">
-        <x:v>7909.23</x:v>
+        <x:v>7909.234</x:v>
       </x:c>
       <x:c r="H62" s="28" t="n">
         <x:v>-187.4</x:v>
       </x:c>
       <x:c r="I62" s="24" t="n">
-        <x:v>-0.023140606107015516</x:v>
+        <x:v>-0.02314071532539297</x:v>
       </x:c>
       <x:c r="J62" s="23" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -19503,22 +19539,22 @@
         <x:v>3月20日</x:v>
       </x:c>
       <x:c r="D63" s="42" t="n">
-        <x:v>7943.41</x:v>
+        <x:v>7943.413</x:v>
       </x:c>
       <x:c r="E63" s="42" t="n">
-        <x:v>7996.16</x:v>
+        <x:v>7996.164</x:v>
       </x:c>
       <x:c r="F63" s="42" t="n">
-        <x:v>7781.58</x:v>
+        <x:v>7781.579</x:v>
       </x:c>
       <x:c r="G63" s="42" t="n">
-        <x:v>7783.43</x:v>
+        <x:v>7783.435</x:v>
       </x:c>
       <x:c r="H63" s="42" t="n">
         <x:v>-125.8</x:v>
       </x:c>
       <x:c r="I63" s="43" t="n">
-        <x:v>-0.015905467409596086</x:v>
+        <x:v>-0.015905332931103078</x:v>
       </x:c>
       <x:c r="J63" s="26" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -19539,22 +19575,22 @@
         <x:v>3月23日</x:v>
       </x:c>
       <x:c r="D64" s="23" t="n">
-        <x:v>7632.97</x:v>
+        <x:v>7632.972</x:v>
       </x:c>
       <x:c r="E64" s="23" t="n">
         <x:v>7712.04</x:v>
       </x:c>
       <x:c r="F64" s="23" t="n">
-        <x:v>7357.7</x:v>
+        <x:v>7357.696</x:v>
       </x:c>
       <x:c r="G64" s="23" t="n">
-        <x:v>7409.11</x:v>
+        <x:v>7409.107</x:v>
       </x:c>
       <x:c r="H64" s="28" t="n">
         <x:v>-374.3</x:v>
       </x:c>
       <x:c r="I64" s="24" t="n">
-        <x:v>-0.0480919080662382</x:v>
+        <x:v>-0.04809290499631591</x:v>
       </x:c>
       <x:c r="J64" s="26" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -19575,22 +19611,22 @@
         <x:v>3月24日</x:v>
       </x:c>
       <x:c r="D65" s="23" t="n">
-        <x:v>7538.7</x:v>
+        <x:v>7538.697</x:v>
       </x:c>
       <x:c r="E65" s="23" t="n">
-        <x:v>7601.88</x:v>
+        <x:v>7601.883</x:v>
       </x:c>
       <x:c r="F65" s="23" t="n">
-        <x:v>7361.79</x:v>
+        <x:v>7361.793</x:v>
       </x:c>
       <x:c r="G65" s="23" t="n">
-        <x:v>7600.86</x:v>
+        <x:v>7600.857</x:v>
       </x:c>
       <x:c r="H65" s="28" t="n">
         <x:v>191.8</x:v>
       </x:c>
       <x:c r="I65" s="24" t="n">
-        <x:v>0.02588030141272024</x:v>
+        <x:v>0.025880311891838037</x:v>
       </x:c>
       <x:c r="J65" s="26" t="n">
         <x:f>ROUND(E65-F65,1)</x:f>
@@ -19611,22 +19647,22 @@
         <x:v>3月25日</x:v>
       </x:c>
       <x:c r="D66" s="23" t="n">
-        <x:v>7654.78</x:v>
+        <x:v>7654.784</x:v>
       </x:c>
       <x:c r="E66" s="23" t="n">
-        <x:v>7781.2</x:v>
+        <x:v>7781.197</x:v>
       </x:c>
       <x:c r="F66" s="23" t="n">
-        <x:v>7654.78</x:v>
+        <x:v>7654.784</x:v>
       </x:c>
       <x:c r="G66" s="23" t="n">
-        <x:v>7751.18</x:v>
+        <x:v>7751.181</x:v>
       </x:c>
       <x:c r="H66" s="28" t="n">
         <x:v>150.3</x:v>
       </x:c>
       <x:c r="I66" s="24" t="n">
-        <x:v>0.019776709477611787</x:v>
+        <x:v>0.019777243539774503</x:v>
       </x:c>
       <x:c r="J66" s="23" t="n">
         <x:f>ROUND(E66-F66,1)</x:f>
@@ -19647,22 +19683,22 @@
         <x:v>3月26日</x:v>
       </x:c>
       <x:c r="D67" s="23" t="n">
-        <x:v>7733.7</x:v>
+        <x:v>7733.702</x:v>
       </x:c>
       <x:c r="E67" s="23" t="n">
-        <x:v>7775.89</x:v>
+        <x:v>7775.893</x:v>
       </x:c>
       <x:c r="F67" s="23" t="n">
-        <x:v>7614.89</x:v>
+        <x:v>7614.889</x:v>
       </x:c>
       <x:c r="G67" s="23" t="n">
-        <x:v>7639.38</x:v>
+        <x:v>7639.376</x:v>
       </x:c>
       <x:c r="H67" s="23" t="n">
         <x:v>-111.8</x:v>
       </x:c>
       <x:c r="I67" s="24" t="n">
-        <x:v>-0.01442361034061912</x:v>
+        <x:v>-0.01442425354278265</x:v>
       </x:c>
       <x:c r="J67" s="23" t="n">
         <x:f>ROUND(E67-F67,1)</x:f>
@@ -19683,22 +19719,22 @@
         <x:v>3月27日</x:v>
       </x:c>
       <x:c r="D68" s="23" t="n">
-        <x:v>7526.59</x:v>
+        <x:v>7526.586</x:v>
       </x:c>
       <x:c r="E68" s="23" t="n">
-        <x:v>7784.55</x:v>
+        <x:v>7784.547</x:v>
       </x:c>
       <x:c r="F68" s="23" t="n">
-        <x:v>7526.59</x:v>
+        <x:v>7526.586</x:v>
       </x:c>
       <x:c r="G68" s="23" t="n">
-        <x:v>7746.31</x:v>
+        <x:v>7746.313</x:v>
       </x:c>
       <x:c r="H68" s="23" t="n">
         <x:v>106.9</x:v>
       </x:c>
       <x:c r="I68" s="24" t="n">
-        <x:v>0.013997209197605054</x:v>
+        <x:v>0.013998132831791521</x:v>
       </x:c>
       <x:c r="J68" s="26" t="n">
         <x:f>ROUND(E68-F68,1)</x:f>
@@ -19719,13 +19755,13 @@
         <x:v>3月30日</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7664.64</x:v>
+        <x:v>7664.636</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
-        <x:v>7774.85</x:v>
+        <x:v>7774.851</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7618.96</x:v>
+        <x:v>7618.961</x:v>
       </x:c>
       <x:c r="G69" s="23" t="n">
         <x:v>7767.93</x:v>
@@ -19734,7 +19770,7 @@
         <x:v>21.6</x:v>
       </x:c>
       <x:c r="I69" s="24" t="n">
-        <x:v>0.0027910062984828343</x:v>
+        <x:v>0.0027906179365591033</x:v>
       </x:c>
       <x:c r="J69" s="23" t="n">
         <x:f>ROUND(E69-F69,1)</x:f>
@@ -19755,13 +19791,13 @@
         <x:v>3月31日</x:v>
       </x:c>
       <x:c r="D70" s="23" t="n">
-        <x:v>7741.96</x:v>
+        <x:v>7741.959</x:v>
       </x:c>
       <x:c r="E70" s="23" t="n">
-        <x:v>7789.24</x:v>
+        <x:v>7789.239</x:v>
       </x:c>
       <x:c r="F70" s="23" t="n">
-        <x:v>7618.19</x:v>
+        <x:v>7618.187</x:v>
       </x:c>
       <x:c r="G70" s="23" t="n">
         <x:v>7619.85</x:v>
@@ -19796,7 +19832,7 @@
       <x:c r="I71" s="30"/>
       <x:c r="J71" s="32" t="n">
         <x:f>ROUND(SUM(J49:J70),1)</x:f>
-        <x:v>3949.7</x:v>
+        <x:v>3949.6</x:v>
       </x:c>
       <x:c r="K71" s="30"/>
     </x:row>
@@ -19879,26 +19915,26 @@
         <x:v>4月1日</x:v>
       </x:c>
       <x:c r="D76" s="23" t="n">
-        <x:v>7767.88</x:v>
+        <x:v>7767.883</x:v>
       </x:c>
       <x:c r="E76" s="23" t="n">
-        <x:v>7786.76</x:v>
+        <x:v>7786.759</x:v>
       </x:c>
       <x:c r="F76" s="23" t="n">
         <x:v>7692.01</x:v>
       </x:c>
       <x:c r="G76" s="23" t="n">
-        <x:v>7764.15</x:v>
+        <x:v>7764.153</x:v>
       </x:c>
       <x:c r="H76" s="23" t="n">
         <x:v>144.3</x:v>
       </x:c>
       <x:c r="I76" s="24" t="n">
-        <x:v>0.01893738065709938</x:v>
+        <x:v>0.01893777436563715</x:v>
       </x:c>
       <x:c r="J76" s="23" t="n">
         <x:f>ROUND(E76-F76,1)</x:f>
-        <x:v>94.8</x:v>
+        <x:v>94.7</x:v>
       </x:c>
       <x:c r="K76" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -19915,22 +19951,22 @@
         <x:v>4月2日</x:v>
       </x:c>
       <x:c r="D77" s="23" t="n">
-        <x:v>7733.75</x:v>
+        <x:v>7733.747</x:v>
       </x:c>
       <x:c r="E77" s="23" t="n">
-        <x:v>7764.03</x:v>
+        <x:v>7764.027</x:v>
       </x:c>
       <x:c r="F77" s="23" t="n">
-        <x:v>7581.39</x:v>
+        <x:v>7581.392</x:v>
       </x:c>
       <x:c r="G77" s="23" t="n">
-        <x:v>7623.42</x:v>
+        <x:v>7623.417</x:v>
       </x:c>
       <x:c r="H77" s="23" t="n">
         <x:v>-140.7</x:v>
       </x:c>
       <x:c r="I77" s="24" t="n">
-        <x:v>-0.018125615811131923</x:v>
+        <x:v>-0.01812638158985269</x:v>
       </x:c>
       <x:c r="J77" s="26" t="n">
         <x:f>ROUND(E77-F77,1)</x:f>
@@ -19951,13 +19987,13 @@
         <x:v>4月3日</x:v>
       </x:c>
       <x:c r="D78" s="23" t="n">
-        <x:v>7658.82</x:v>
+        <x:v>7658.821</x:v>
       </x:c>
       <x:c r="E78" s="23" t="n">
-        <x:v>7664.76</x:v>
+        <x:v>7664.756</x:v>
       </x:c>
       <x:c r="F78" s="23" t="n">
-        <x:v>7521.94</x:v>
+        <x:v>7521.944</x:v>
       </x:c>
       <x:c r="G78" s="23" t="n">
         <x:v>7536.6</x:v>
@@ -19966,7 +20002,7 @@
         <x:v>-86.8</x:v>
       </x:c>
       <x:c r="I78" s="24" t="n">
-        <x:v>-0.011388589373273361</x:v>
+        <x:v>-0.011388200330639142</x:v>
       </x:c>
       <x:c r="J78" s="23" t="n">
         <x:f>ROUND(E78-F78,1)</x:f>
@@ -19987,22 +20023,22 @@
         <x:v>4月7日</x:v>
       </x:c>
       <x:c r="D79" s="23" t="n">
-        <x:v>7556.28</x:v>
+        <x:v>7556.277</x:v>
       </x:c>
       <x:c r="E79" s="23" t="n">
-        <x:v>7640.51</x:v>
+        <x:v>7640.505</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7554.41</x:v>
+        <x:v>7554.408</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
-        <x:v>7606.02</x:v>
+        <x:v>7606.017</x:v>
       </x:c>
       <x:c r="H79" s="23" t="n">
         <x:v>69.4</x:v>
       </x:c>
       <x:c r="I79" s="24" t="n">
-        <x:v>0.009211050075630833</x:v>
+        <x:v>0.00921065201815141</x:v>
       </x:c>
       <x:c r="J79" s="23" t="n">
         <x:f>ROUND(E79-F79,1)</x:f>
@@ -20026,19 +20062,19 @@
         <x:v>7765.55</x:v>
       </x:c>
       <x:c r="E80" s="23" t="n">
-        <x:v>7955.77</x:v>
+        <x:v>7955.768</x:v>
       </x:c>
       <x:c r="F80" s="23" t="n">
-        <x:v>7765.2</x:v>
+        <x:v>7765.197</x:v>
       </x:c>
       <x:c r="G80" s="23" t="n">
-        <x:v>7955.77</x:v>
+        <x:v>7955.768</x:v>
       </x:c>
       <x:c r="H80" s="28" t="n">
         <x:v>349.8</x:v>
       </x:c>
       <x:c r="I80" s="24" t="n">
-        <x:v>0.045983313217688115</x:v>
+        <x:v>0.04598346282949417</x:v>
       </x:c>
       <x:c r="J80" s="26" t="n">
         <x:f>ROUND(E80-F80,1)</x:f>
@@ -20059,22 +20095,22 @@
         <x:v>4月9日</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7881.8</x:v>
+        <x:v>7881.803</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
-        <x:v>7959.07</x:v>
+        <x:v>7959.067</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7872.47</x:v>
+        <x:v>7872.475</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
-        <x:v>7921.45</x:v>
+        <x:v>7921.447</x:v>
       </x:c>
       <x:c r="H81" s="23" t="n">
         <x:v>-34.3</x:v>
       </x:c>
       <x:c r="I81" s="24" t="n">
-        <x:v>-0.004313850199289426</x:v>
+        <x:v>-0.004313976978715273</x:v>
       </x:c>
       <x:c r="J81" s="23" t="n">
         <x:f>ROUND(E81-F81,1)</x:f>
@@ -20095,22 +20131,22 @@
         <x:v>4月10日</x:v>
       </x:c>
       <x:c r="D82" s="23" t="n">
-        <x:v>7981.62</x:v>
+        <x:v>7981.622</x:v>
       </x:c>
       <x:c r="E82" s="23" t="n">
-        <x:v>8059.76</x:v>
+        <x:v>8059.755</x:v>
       </x:c>
       <x:c r="F82" s="23" t="n">
-        <x:v>7981.62</x:v>
+        <x:v>7981.622</x:v>
       </x:c>
       <x:c r="G82" s="23" t="n">
-        <x:v>7998.23</x:v>
+        <x:v>7998.232</x:v>
       </x:c>
       <x:c r="H82" s="23" t="n">
         <x:v>76.8</x:v>
       </x:c>
       <x:c r="I82" s="24" t="n">
-        <x:v>0.009692669902606088</x:v>
+        <x:v>0.009693304771211553</x:v>
       </x:c>
       <x:c r="J82" s="23" t="n">
         <x:f>ROUND(E82-F82,1)</x:f>
@@ -20131,22 +20167,22 @@
         <x:v>4月13日</x:v>
       </x:c>
       <x:c r="D83" s="23" t="n">
-        <x:v>7947.22</x:v>
+        <x:v>7947.222</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>8040.03</x:v>
+        <x:v>8040.026</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>7947.22</x:v>
+        <x:v>7947.222</x:v>
       </x:c>
       <x:c r="G83" s="23" t="n">
-        <x:v>8025.57</x:v>
+        <x:v>8025.572</x:v>
       </x:c>
       <x:c r="H83" s="23" t="n">
         <x:v>27.3</x:v>
       </x:c>
       <x:c r="I83" s="24" t="n">
-        <x:v>0.0034182562892040025</x:v>
+        <x:v>0.0034182554344510674</x:v>
       </x:c>
       <x:c r="J83" s="23" t="n">
         <x:f>ROUND(E83-F83,1)</x:f>
@@ -20170,19 +20206,19 @@
         <x:v>8088.05</x:v>
       </x:c>
       <x:c r="E84" s="23" t="n">
-        <x:v>8144.76</x:v>
+        <x:v>8144.762</x:v>
       </x:c>
       <x:c r="F84" s="23" t="n">
         <x:v>8059.38</x:v>
       </x:c>
       <x:c r="G84" s="23" t="n">
-        <x:v>8144.76</x:v>
+        <x:v>8144.762</x:v>
       </x:c>
       <x:c r="H84" s="23" t="n">
         <x:v>119.2</x:v>
       </x:c>
       <x:c r="I84" s="24" t="n">
-        <x:v>0.014851281591214072</x:v>
+        <x:v>0.01485127789022389</x:v>
       </x:c>
       <x:c r="J84" s="23" t="n">
         <x:f>ROUND(E84-F84,1)</x:f>
@@ -20203,22 +20239,22 @@
         <x:v>4月15日</x:v>
       </x:c>
       <x:c r="D85" s="23" t="n">
-        <x:v>8186.07</x:v>
+        <x:v>8186.074</x:v>
       </x:c>
       <x:c r="E85" s="23" t="n">
-        <x:v>8193.3</x:v>
+        <x:v>8193.296</x:v>
       </x:c>
       <x:c r="F85" s="23" t="n">
-        <x:v>8083.27</x:v>
+        <x:v>8083.265</x:v>
       </x:c>
       <x:c r="G85" s="23" t="n">
-        <x:v>8106.16</x:v>
+        <x:v>8106.165</x:v>
       </x:c>
       <x:c r="H85" s="23" t="n">
         <x:v>-38.6</x:v>
       </x:c>
       <x:c r="I85" s="24" t="n">
-        <x:v>-0.004739243390842751</x:v>
+        <x:v>-0.004738873892202067</x:v>
       </x:c>
       <x:c r="J85" s="23" t="n">
         <x:f>ROUND(E85-F85,1)</x:f>
@@ -20239,22 +20275,22 @@
         <x:v>4月16日</x:v>
       </x:c>
       <x:c r="D86" s="23" t="n">
-        <x:v>8120.36</x:v>
+        <x:v>8120.358</x:v>
       </x:c>
       <x:c r="E86" s="23" t="n">
-        <x:v>8239.01</x:v>
+        <x:v>8239.008</x:v>
       </x:c>
       <x:c r="F86" s="23" t="n">
-        <x:v>8100.49</x:v>
+        <x:v>8100.489</x:v>
       </x:c>
       <x:c r="G86" s="23" t="n">
-        <x:v>8232.98</x:v>
+        <x:v>8232.983</x:v>
       </x:c>
       <x:c r="H86" s="23" t="n">
         <x:v>126.8</x:v>
       </x:c>
       <x:c r="I86" s="24" t="n">
-        <x:v>0.01564489227945165</x:v>
+        <x:v>0.015644635903661053</x:v>
       </x:c>
       <x:c r="J86" s="23" t="n">
         <x:f>ROUND(E86-F86,1)</x:f>
@@ -20275,22 +20311,22 @@
         <x:v>4月17日</x:v>
       </x:c>
       <x:c r="D87" s="42" t="n">
-        <x:v>8225.73</x:v>
+        <x:v>8225.729</x:v>
       </x:c>
       <x:c r="E87" s="42" t="n">
-        <x:v>8333.22</x:v>
+        <x:v>8333.222</x:v>
       </x:c>
       <x:c r="F87" s="42" t="n">
-        <x:v>8223.71</x:v>
+        <x:v>8223.706</x:v>
       </x:c>
       <x:c r="G87" s="42" t="n">
-        <x:v>8307.44</x:v>
+        <x:v>8307.436</x:v>
       </x:c>
       <x:c r="H87" s="42" t="n">
         <x:v>74.5</x:v>
       </x:c>
       <x:c r="I87" s="43" t="n">
-        <x:v>0.009044112824275086</x:v>
+        <x:v>0.009043259290101746</x:v>
       </x:c>
       <x:c r="J87" s="42" t="n">
         <x:f>ROUND(E87-F87,1)</x:f>
@@ -20311,22 +20347,22 @@
         <x:v>4月20日</x:v>
       </x:c>
       <x:c r="D88" s="23" t="n">
-        <x:v>8308.06</x:v>
+        <x:v>8308.055</x:v>
       </x:c>
       <x:c r="E88" s="23" t="n">
-        <x:v>8374.81</x:v>
+        <x:v>8374.812</x:v>
       </x:c>
       <x:c r="F88" s="23" t="n">
-        <x:v>8308.06</x:v>
+        <x:v>8308.055</x:v>
       </x:c>
       <x:c r="G88" s="23" t="n">
-        <x:v>8357.81</x:v>
+        <x:v>8357.814</x:v>
       </x:c>
       <x:c r="H88" s="23" t="n">
         <x:v>50.4</x:v>
       </x:c>
       <x:c r="I88" s="24" t="n">
-        <x:v>0.006063239698390621</x:v>
+        <x:v>0.006064205610491591</x:v>
       </x:c>
       <x:c r="J88" s="23" t="n">
         <x:f>ROUND(E88-F88,1)</x:f>
@@ -20347,22 +20383,22 @@
         <x:v>4月21日</x:v>
       </x:c>
       <x:c r="D89" s="23" t="n">
-        <x:v>8331.59</x:v>
+        <x:v>8331.592</x:v>
       </x:c>
       <x:c r="E89" s="23" t="n">
-        <x:v>8358.12</x:v>
+        <x:v>8358.124</x:v>
       </x:c>
       <x:c r="F89" s="23" t="n">
-        <x:v>8270.16</x:v>
+        <x:v>8270.161</x:v>
       </x:c>
       <x:c r="G89" s="23" t="n">
-        <x:v>8351.16</x:v>
+        <x:v>8351.156</x:v>
       </x:c>
       <x:c r="H89" s="23" t="n">
-        <x:v>-6.6</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="I89" s="24" t="n">
-        <x:v>-0.00079566297869893</x:v>
+        <x:v>-0.0007966197859869961</x:v>
       </x:c>
       <x:c r="J89" s="23" t="n">
         <x:f>ROUND(E89-F89,1)</x:f>
@@ -20383,13 +20419,13 @@
         <x:v>4月22日</x:v>
       </x:c>
       <x:c r="D90" s="23" t="n">
-        <x:v>8317.28</x:v>
+        <x:v>8317.278</x:v>
       </x:c>
       <x:c r="E90" s="23" t="n">
-        <x:v>8482.15</x:v>
+        <x:v>8482.153</x:v>
       </x:c>
       <x:c r="F90" s="23" t="n">
-        <x:v>8317.28</x:v>
+        <x:v>8317.278</x:v>
       </x:c>
       <x:c r="G90" s="23" t="n">
         <x:v>8481.24</x:v>
@@ -20398,7 +20434,7 @@
         <x:v>130.1</x:v>
       </x:c>
       <x:c r="I90" s="24" t="n">
-        <x:v>0.015576279223485034</x:v>
+        <x:v>0.015576765659748082</x:v>
       </x:c>
       <x:c r="J90" s="23" t="n">
         <x:f>ROUND(E90-F90,1)</x:f>
@@ -20419,13 +20455,13 @@
         <x:v>4月23日</x:v>
       </x:c>
       <x:c r="D91" s="23" t="n">
-        <x:v>8489</x:v>
+        <x:v>8488.996</x:v>
       </x:c>
       <x:c r="E91" s="23" t="n">
-        <x:v>8500.44</x:v>
+        <x:v>8500.438</x:v>
       </x:c>
       <x:c r="F91" s="23" t="n">
-        <x:v>8302.85</x:v>
+        <x:v>8302.849</x:v>
       </x:c>
       <x:c r="G91" s="23" t="n">
         <x:v>8362.74</x:v>
@@ -20455,22 +20491,22 @@
         <x:v>4月24日</x:v>
       </x:c>
       <x:c r="D92" s="23" t="n">
-        <x:v>8318.6</x:v>
+        <x:v>8318.597</x:v>
       </x:c>
       <x:c r="E92" s="23" t="n">
         <x:v>8360.79</x:v>
       </x:c>
       <x:c r="F92" s="23" t="n">
-        <x:v>8254.43</x:v>
+        <x:v>8254.431</x:v>
       </x:c>
       <x:c r="G92" s="23" t="n">
-        <x:v>8304.14</x:v>
+        <x:v>8304.141</x:v>
       </x:c>
       <x:c r="H92" s="23" t="n">
         <x:v>-58.6</x:v>
       </x:c>
       <x:c r="I92" s="24" t="n">
-        <x:v>-0.00700727273596935</x:v>
+        <x:v>-0.007007153157936319</x:v>
       </x:c>
       <x:c r="J92" s="23" t="n">
         <x:f>ROUND(E92-F92,1)</x:f>
@@ -20491,22 +20527,22 @@
         <x:v>4月27日</x:v>
       </x:c>
       <x:c r="D93" s="23" t="n">
-        <x:v>8292.81</x:v>
+        <x:v>8292.811</x:v>
       </x:c>
       <x:c r="E93" s="23" t="n">
-        <x:v>8366.31</x:v>
+        <x:v>8366.312</x:v>
       </x:c>
       <x:c r="F93" s="23" t="n">
-        <x:v>8249.94</x:v>
+        <x:v>8249.944</x:v>
       </x:c>
       <x:c r="G93" s="23" t="n">
-        <x:v>8338.73</x:v>
+        <x:v>8338.726</x:v>
       </x:c>
       <x:c r="H93" s="23" t="n">
         <x:v>34.6</x:v>
       </x:c>
       <x:c r="I93" s="24" t="n">
-        <x:v>0.004165392201961993</x:v>
+        <x:v>0.004164789591120988</x:v>
       </x:c>
       <x:c r="J93" s="23" t="n">
         <x:f>ROUND(E93-F93,1)</x:f>
@@ -20527,22 +20563,22 @@
         <x:v>4月28日</x:v>
       </x:c>
       <x:c r="D94" s="23" t="n">
-        <x:v>8307.69</x:v>
+        <x:v>8307.692</x:v>
       </x:c>
       <x:c r="E94" s="23" t="n">
-        <x:v>8316.27</x:v>
+        <x:v>8316.267</x:v>
       </x:c>
       <x:c r="F94" s="23" t="n">
-        <x:v>8187.24</x:v>
+        <x:v>8187.239</x:v>
       </x:c>
       <x:c r="G94" s="23" t="n">
-        <x:v>8226.69</x:v>
+        <x:v>8226.692</x:v>
       </x:c>
       <x:c r="H94" s="23" t="n">
         <x:v>-112</x:v>
       </x:c>
       <x:c r="I94" s="24" t="n">
-        <x:v>-0.013436098782428352</x:v>
+        <x:v>-0.013435385693210344</x:v>
       </x:c>
       <x:c r="J94" s="23" t="n">
         <x:f>ROUND(E94-F94,1)</x:f>
@@ -20563,22 +20599,22 @@
         <x:v>4月29日</x:v>
       </x:c>
       <x:c r="D95" s="23" t="n">
-        <x:v>8163.35</x:v>
+        <x:v>8163.348</x:v>
       </x:c>
       <x:c r="E95" s="23" t="n">
-        <x:v>8361.49</x:v>
+        <x:v>8361.487</x:v>
       </x:c>
       <x:c r="F95" s="23" t="n">
-        <x:v>8163.35</x:v>
+        <x:v>8163.348</x:v>
       </x:c>
       <x:c r="G95" s="23" t="n">
-        <x:v>8343.07</x:v>
+        <x:v>8343.065</x:v>
       </x:c>
       <x:c r="H95" s="23" t="n">
         <x:v>116.4</x:v>
       </x:c>
       <x:c r="I95" s="24" t="n">
-        <x:v>0.014146637347462798</x:v>
+        <x:v>0.014145783019468894</x:v>
       </x:c>
       <x:c r="J95" s="26" t="n">
         <x:f>ROUND(E95-F95,1)</x:f>
@@ -20599,22 +20635,22 @@
         <x:v>4月30日</x:v>
       </x:c>
       <x:c r="D96" s="23" t="n">
-        <x:v>8345.25</x:v>
+        <x:v>8345.247</x:v>
       </x:c>
       <x:c r="E96" s="23" t="n">
-        <x:v>8402.36</x:v>
+        <x:v>8402.356</x:v>
       </x:c>
       <x:c r="F96" s="23" t="n">
-        <x:v>8324.29</x:v>
+        <x:v>8324.294</x:v>
       </x:c>
       <x:c r="G96" s="23" t="n">
-        <x:v>8381.95</x:v>
+        <x:v>8381.947</x:v>
       </x:c>
       <x:c r="H96" s="23" t="n">
         <x:v>38.9</x:v>
       </x:c>
       <x:c r="I96" s="24" t="n">
-        <x:v>0.004660155074810657</x:v>
+        <x:v>0.004660397587697096</x:v>
       </x:c>
       <x:c r="J96" s="23" t="n">
         <x:f>ROUND(E96-F96,1)</x:f>
@@ -20640,7 +20676,7 @@
       <x:c r="I97" s="30"/>
       <x:c r="J97" s="32" t="n">
         <x:f>ROUND(SUM(J76:J96),1)</x:f>
-        <x:v>2543.1</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="K97" s="30"/>
     </x:row>
@@ -20723,22 +20759,22 @@
         <x:v>5月6日</x:v>
       </x:c>
       <x:c r="D102" s="23" t="n">
-        <x:v>8462.02</x:v>
+        <x:v>8462.023</x:v>
       </x:c>
       <x:c r="E102" s="23" t="n">
-        <x:v>8610.88</x:v>
+        <x:v>8610.881</x:v>
       </x:c>
       <x:c r="F102" s="23" t="n">
-        <x:v>8462.02</x:v>
+        <x:v>8462.023</x:v>
       </x:c>
       <x:c r="G102" s="23" t="n">
-        <x:v>8574.56</x:v>
+        <x:v>8574.556</x:v>
       </x:c>
       <x:c r="H102" s="28" t="n">
         <x:v>192.6</x:v>
       </x:c>
       <x:c r="I102" s="24" t="n">
-        <x:v>0.02297913969899601</x:v>
+        <x:v>0.0229790286194842</x:v>
       </x:c>
       <x:c r="J102" s="23" t="n">
         <x:f>ROUND(E102-F102,1)</x:f>
@@ -20759,13 +20795,13 @@
         <x:v>5月7日</x:v>
       </x:c>
       <x:c r="D103" s="23" t="n">
-        <x:v>8602.15</x:v>
+        <x:v>8602.146</x:v>
       </x:c>
       <x:c r="E103" s="23" t="n">
-        <x:v>8716.86</x:v>
+        <x:v>8716.861</x:v>
       </x:c>
       <x:c r="F103" s="23" t="n">
-        <x:v>8573.3</x:v>
+        <x:v>8573.295</x:v>
       </x:c>
       <x:c r="G103" s="23" t="n">
         <x:v>8714.51</x:v>
@@ -20774,7 +20810,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="I103" s="24" t="n">
-        <x:v>0.01632153719841023</x:v>
+        <x:v>0.01632201130880717</x:v>
       </x:c>
       <x:c r="J103" s="23" t="n">
         <x:f>ROUND(E103-F103,1)</x:f>
@@ -20795,22 +20831,22 @@
         <x:v>5月8日</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>8655.13</x:v>
+        <x:v>8655.127</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
-        <x:v>8760.19</x:v>
+        <x:v>8760.194</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>8651.06</x:v>
+        <x:v>8651.059</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
-        <x:v>8741.15</x:v>
+        <x:v>8741.151</x:v>
       </x:c>
       <x:c r="H104" s="23" t="n">
         <x:v>26.6</x:v>
       </x:c>
       <x:c r="I104" s="24" t="n">
-        <x:v>0.0030569705009231285</x:v>
+        <x:v>0.003057085252068159</x:v>
       </x:c>
       <x:c r="J104" s="23" t="n">
         <x:f>ROUND(E104-F104,1)</x:f>
@@ -20831,22 +20867,22 @@
         <x:v>5月11日</x:v>
       </x:c>
       <x:c r="D105" s="23" t="n">
-        <x:v>8807.91</x:v>
+        <x:v>8807.905</x:v>
       </x:c>
       <x:c r="E105" s="23" t="n">
-        <x:v>8888.87</x:v>
+        <x:v>8888.873</x:v>
       </x:c>
       <x:c r="F105" s="23" t="n">
-        <x:v>8760.71</x:v>
+        <x:v>8760.714</x:v>
       </x:c>
       <x:c r="G105" s="23" t="n">
-        <x:v>8866.78</x:v>
+        <x:v>8866.779</x:v>
       </x:c>
       <x:c r="H105" s="23" t="n">
         <x:v>125.6</x:v>
       </x:c>
       <x:c r="I105" s="24" t="n">
-        <x:v>0.014372250790799956</x:v>
+        <x:v>0.01437202034377405</x:v>
       </x:c>
       <x:c r="J105" s="23" t="n">
         <x:f>ROUND(E105-F105,1)</x:f>
@@ -20867,22 +20903,22 @@
         <x:v>5月12日</x:v>
       </x:c>
       <x:c r="D106" s="23" t="n">
-        <x:v>8880.41</x:v>
+        <x:v>8880.415</x:v>
       </x:c>
       <x:c r="E106" s="23" t="n">
-        <x:v>8881.9</x:v>
+        <x:v>8881.902</x:v>
       </x:c>
       <x:c r="F106" s="23" t="n">
-        <x:v>8749.72</x:v>
+        <x:v>8749.722</x:v>
       </x:c>
       <x:c r="G106" s="23" t="n">
-        <x:v>8821.89</x:v>
+        <x:v>8821.887</x:v>
       </x:c>
       <x:c r="H106" s="23" t="n">
         <x:v>-44.9</x:v>
       </x:c>
       <x:c r="I106" s="24" t="n">
-        <x:v>-0.0050627172434639656</x:v>
+        <x:v>-0.005062943375491846</x:v>
       </x:c>
       <x:c r="J106" s="23" t="n">
         <x:f>ROUND(E106-F106,1)</x:f>
@@ -20903,22 +20939,22 @@
         <x:v>5月13日</x:v>
       </x:c>
       <x:c r="D107" s="23" t="n">
-        <x:v>8764.02</x:v>
+        <x:v>8764.023</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>8958.46</x:v>
+        <x:v>8958.456</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>8764.02</x:v>
+        <x:v>8764.023</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
-        <x:v>8955.45</x:v>
+        <x:v>8955.447</x:v>
       </x:c>
       <x:c r="H107" s="23" t="n">
         <x:v>133.6</x:v>
       </x:c>
       <x:c r="I107" s="24" t="n">
-        <x:v>0.01513961294008448</x:v>
+        <x:v>0.015139618088510831</x:v>
       </x:c>
       <x:c r="J107" s="26" t="n">
         <x:f>ROUND(E107-F107,1)</x:f>
@@ -20939,22 +20975,22 @@
         <x:v>5月14日</x:v>
       </x:c>
       <x:c r="D108" s="23" t="n">
-        <x:v>8989.49</x:v>
+        <x:v>8989.487</x:v>
       </x:c>
       <x:c r="E108" s="23" t="n">
         <x:v>8991.85</x:v>
       </x:c>
       <x:c r="F108" s="23" t="n">
-        <x:v>8778.71</x:v>
+        <x:v>8778.709</x:v>
       </x:c>
       <x:c r="G108" s="23" t="n">
-        <x:v>8778.71</x:v>
+        <x:v>8778.709</x:v>
       </x:c>
       <x:c r="H108" s="28" t="n">
         <x:v>-176.7</x:v>
       </x:c>
       <x:c r="I108" s="24" t="n">
-        <x:v>-0.01973546834609108</x:v>
+        <x:v>-0.01973525162953893</x:v>
       </x:c>
       <x:c r="J108" s="26" t="n">
         <x:f>ROUND(E108-F108,1)</x:f>
@@ -20975,22 +21011,22 @@
         <x:v>5月15日</x:v>
       </x:c>
       <x:c r="D109" s="42" t="n">
-        <x:v>8786.38</x:v>
+        <x:v>8786.382</x:v>
       </x:c>
       <x:c r="E109" s="42" t="n">
-        <x:v>8846.52</x:v>
+        <x:v>8846.515</x:v>
       </x:c>
       <x:c r="F109" s="42" t="n">
         <x:v>8616.06</x:v>
       </x:c>
       <x:c r="G109" s="42" t="n">
-        <x:v>8682.65</x:v>
+        <x:v>8682.654</x:v>
       </x:c>
       <x:c r="H109" s="42" t="n">
         <x:v>-96.1</x:v>
       </x:c>
       <x:c r="I109" s="43" t="n">
-        <x:v>-0.010942382195106015</x:v>
+        <x:v>-0.010941813881745088</x:v>
       </x:c>
       <x:c r="J109" s="26" t="n">
         <x:f>ROUND(E109-F109,1)</x:f>
@@ -21011,22 +21047,22 @@
         <x:v>5月18日</x:v>
       </x:c>
       <x:c r="D110" s="23" t="n">
-        <x:v>8645.76</x:v>
+        <x:v>8645.763</x:v>
       </x:c>
       <x:c r="E110" s="23" t="n">
-        <x:v>8766.31</x:v>
+        <x:v>8766.306</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>8610.74</x:v>
+        <x:v>8610.742</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
-        <x:v>8720.21</x:v>
+        <x:v>8720.213</x:v>
       </x:c>
       <x:c r="H110" s="23" t="n">
         <x:v>37.6</x:v>
       </x:c>
       <x:c r="I110" s="24" t="n">
-        <x:v>0.004325868254507537</x:v>
+        <x:v>0.004325751089470975</x:v>
       </x:c>
       <x:c r="J110" s="23" t="n">
         <x:f>ROUND(E110-F110,1)</x:f>
@@ -21047,22 +21083,22 @@
         <x:v>5月19日</x:v>
       </x:c>
       <x:c r="D111" s="23" t="n">
-        <x:v>8691.38</x:v>
+        <x:v>8691.384</x:v>
       </x:c>
       <x:c r="E111" s="23" t="n">
-        <x:v>8812.03</x:v>
+        <x:v>8812.031</x:v>
       </x:c>
       <x:c r="F111" s="23" t="n">
-        <x:v>8602.05</x:v>
+        <x:v>8602.046</x:v>
       </x:c>
       <x:c r="G111" s="23" t="n">
-        <x:v>8808.64</x:v>
+        <x:v>8808.645</x:v>
       </x:c>
       <x:c r="H111" s="23" t="n">
         <x:v>88.4</x:v>
       </x:c>
       <x:c r="I111" s="24" t="n">
-        <x:v>0.010140810829097013</x:v>
+        <x:v>0.010141036692567162</x:v>
       </x:c>
       <x:c r="J111" s="26" t="n">
         <x:f>ROUND(E111-F111,1)</x:f>
@@ -21083,10 +21119,10 @@
         <x:v>5月20日</x:v>
       </x:c>
       <x:c r="D112" s="23" t="n">
-        <x:v>8769.1</x:v>
+        <x:v>8769.097</x:v>
       </x:c>
       <x:c r="E112" s="23" t="n">
-        <x:v>8823.68</x:v>
+        <x:v>8823.684</x:v>
       </x:c>
       <x:c r="F112" s="23" t="n">
         <x:v>8697.4</x:v>
@@ -21098,7 +21134,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="24" t="n">
-        <x:v>0.00003065172376226499</x:v>
+        <x:v>0.00003008408217142211</x:v>
       </x:c>
       <x:c r="J112" s="23" t="n">
         <x:f>ROUND(E112-F112,1)</x:f>
@@ -21119,7 +21155,7 @@
         <x:v>5月21日</x:v>
       </x:c>
       <x:c r="D113" s="23" t="n">
-        <x:v>8852.43</x:v>
+        <x:v>8852.434</x:v>
       </x:c>
       <x:c r="E113" s="23" t="n">
         <x:v>8896.6</x:v>
@@ -21128,13 +21164,13 @@
         <x:v>8500.92</x:v>
       </x:c>
       <x:c r="G113" s="23" t="n">
-        <x:v>8510.5</x:v>
+        <x:v>8510.496</x:v>
       </x:c>
       <x:c r="H113" s="28" t="n">
         <x:v>-298.4</x:v>
       </x:c>
       <x:c r="I113" s="24" t="n">
-        <x:v>-0.033875927895732794</x:v>
+        <x:v>-0.03387638198142573</x:v>
       </x:c>
       <x:c r="J113" s="26" t="n">
         <x:f>ROUND(E113-F113,1)</x:f>
@@ -21158,19 +21194,19 @@
         <x:v>8578.9</x:v>
       </x:c>
       <x:c r="E114" s="23" t="n">
-        <x:v>8719.39</x:v>
+        <x:v>8719.387</x:v>
       </x:c>
       <x:c r="F114" s="23" t="n">
-        <x:v>8521.7</x:v>
+        <x:v>8521.695</x:v>
       </x:c>
       <x:c r="G114" s="23" t="n">
-        <x:v>8692.67</x:v>
+        <x:v>8692.666</x:v>
       </x:c>
       <x:c r="H114" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I114" s="24" t="n">
-        <x:v>0.0214053228364961</x:v>
+        <x:v>0.021405332897165952</x:v>
       </x:c>
       <x:c r="J114" s="26" t="n">
         <x:f>ROUND(E114-F114,1)</x:f>
@@ -21191,22 +21227,22 @@
         <x:v>5月25日</x:v>
       </x:c>
       <x:c r="D115" s="23" t="n">
-        <x:v>8756.46</x:v>
+        <x:v>8756.458</x:v>
       </x:c>
       <x:c r="E115" s="23" t="n">
-        <x:v>8802.95</x:v>
+        <x:v>8802.946</x:v>
       </x:c>
       <x:c r="F115" s="23" t="n">
-        <x:v>8670.72</x:v>
+        <x:v>8670.716</x:v>
       </x:c>
       <x:c r="G115" s="23" t="n">
-        <x:v>8799.31</x:v>
+        <x:v>8799.312</x:v>
       </x:c>
       <x:c r="H115" s="23" t="n">
         <x:v>106.6</x:v>
       </x:c>
       <x:c r="I115" s="24" t="n">
-        <x:v>0.012267807244494389</x:v>
+        <x:v>0.012268503126658725</x:v>
       </x:c>
       <x:c r="J115" s="23" t="n">
         <x:f>ROUND(E115-F115,1)</x:f>
@@ -21227,22 +21263,22 @@
         <x:v>5月26日</x:v>
       </x:c>
       <x:c r="D116" s="23" t="n">
-        <x:v>8755.91</x:v>
+        <x:v>8755.908</x:v>
       </x:c>
       <x:c r="E116" s="23" t="n">
-        <x:v>8756.46</x:v>
+        <x:v>8756.463</x:v>
       </x:c>
       <x:c r="F116" s="23" t="n">
-        <x:v>8560.8</x:v>
+        <x:v>8560.804</x:v>
       </x:c>
       <x:c r="G116" s="23" t="n">
-        <x:v>8687.25</x:v>
+        <x:v>8687.253</x:v>
       </x:c>
       <x:c r="H116" s="23" t="n">
         <x:v>-112.1</x:v>
       </x:c>
       <x:c r="I116" s="24" t="n">
-        <x:v>-0.012735089455877757</x:v>
+        <x:v>-0.012734972916064291</x:v>
       </x:c>
       <x:c r="J116" s="26" t="n">
         <x:f>ROUND(E116-F116,1)</x:f>
@@ -21263,22 +21299,22 @@
         <x:v>5月27日</x:v>
       </x:c>
       <x:c r="D117" s="23" t="n">
-        <x:v>8679.54</x:v>
+        <x:v>8679.536</x:v>
       </x:c>
       <x:c r="E117" s="23" t="n">
-        <x:v>8737.05</x:v>
+        <x:v>8737.055</x:v>
       </x:c>
       <x:c r="F117" s="23" t="n">
-        <x:v>8495.72</x:v>
+        <x:v>8495.723</x:v>
       </x:c>
       <x:c r="G117" s="23" t="n">
-        <x:v>8546.51</x:v>
+        <x:v>8546.514</x:v>
       </x:c>
       <x:c r="H117" s="23" t="n">
         <x:v>-140.7</x:v>
       </x:c>
       <x:c r="I117" s="24" t="n">
-        <x:v>-0.016200753978531712</x:v>
+        <x:v>-0.016200633272681397</x:v>
       </x:c>
       <x:c r="J117" s="26" t="n">
         <x:f>ROUND(E117-F117,1)</x:f>
@@ -21299,22 +21335,22 @@
         <x:v>5月28日</x:v>
       </x:c>
       <x:c r="D118" s="23" t="n">
-        <x:v>8527.91</x:v>
+        <x:v>8527.909</x:v>
       </x:c>
       <x:c r="E118" s="23" t="n">
         <x:v>8659.61</x:v>
       </x:c>
       <x:c r="F118" s="23" t="n">
-        <x:v>8459.95</x:v>
+        <x:v>8459.949</x:v>
       </x:c>
       <x:c r="G118" s="23" t="n">
-        <x:v>8637.74</x:v>
+        <x:v>8637.743</x:v>
       </x:c>
       <x:c r="H118" s="23" t="n">
         <x:v>91.2</x:v>
       </x:c>
       <x:c r="I118" s="24" t="n">
-        <x:v>0.010674532645489121</x:v>
+        <x:v>0.010674410642748766</x:v>
       </x:c>
       <x:c r="J118" s="26" t="n">
         <x:f>ROUND(E118-F118,1)</x:f>
@@ -21335,22 +21371,22 @@
         <x:v>5月29日</x:v>
       </x:c>
       <x:c r="D119" s="23" t="n">
-        <x:v>8673.8</x:v>
+        <x:v>8673.798</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
-        <x:v>8680.27</x:v>
+        <x:v>8680.266</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>8357.8</x:v>
+        <x:v>8357.801</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
-        <x:v>8408.74</x:v>
+        <x:v>8408.736</x:v>
       </x:c>
       <x:c r="H119" s="28" t="n">
         <x:v>-229</x:v>
       </x:c>
       <x:c r="I119" s="24" t="n">
-        <x:v>-0.026511564367531326</x:v>
+        <x:v>-0.0265123655566043</x:v>
       </x:c>
       <x:c r="J119" s="26" t="n">
         <x:f>ROUND(E119-F119,1)</x:f>
@@ -21459,22 +21495,22 @@
         <x:v>6月1日</x:v>
       </x:c>
       <x:c r="D125" s="23" t="n">
-        <x:v>8393.52</x:v>
+        <x:v>8393.518</x:v>
       </x:c>
       <x:c r="E125" s="23" t="n">
-        <x:v>8504.98</x:v>
+        <x:v>8504.983</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>8339.35</x:v>
+        <x:v>8339.353</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
-        <x:v>8345.13</x:v>
+        <x:v>8345.129</x:v>
       </x:c>
       <x:c r="H125" s="23" t="n">
         <x:v>-63.6</x:v>
       </x:c>
       <x:c r="I125" s="24" t="n">
-        <x:v>-0.007564748107326547</x:v>
+        <x:v>-0.007564394934030494</x:v>
       </x:c>
       <x:c r="J125" s="23" t="n">
         <x:f>ROUND(E125-F125,1)</x:f>
@@ -21495,22 +21531,22 @@
         <x:v>6月2日</x:v>
       </x:c>
       <x:c r="D126" s="23" t="n">
-        <x:v>8360.81</x:v>
+        <x:v>8360.807</x:v>
       </x:c>
       <x:c r="E126" s="23" t="n">
-        <x:v>8440.23</x:v>
+        <x:v>8440.232</x:v>
       </x:c>
       <x:c r="F126" s="23" t="n">
-        <x:v>8219.15</x:v>
+        <x:v>8219.153</x:v>
       </x:c>
       <x:c r="G126" s="23" t="n">
-        <x:v>8384.78</x:v>
+        <x:v>8384.781</x:v>
       </x:c>
       <x:c r="H126" s="23" t="n">
         <x:v>39.7</x:v>
       </x:c>
       <x:c r="I126" s="24" t="n">
-        <x:v>0.004751274096389313</x:v>
+        <x:v>0.004751514326501116</x:v>
       </x:c>
       <x:c r="J126" s="26" t="n">
         <x:f>ROUND(E126-F126,1)</x:f>
@@ -21531,22 +21567,22 @@
         <x:v>6月3日</x:v>
       </x:c>
       <x:c r="D127" s="23" t="n">
-        <x:v>8386.86</x:v>
+        <x:v>8386.858</x:v>
       </x:c>
       <x:c r="E127" s="23" t="n">
-        <x:v>8549.25</x:v>
+        <x:v>8549.249</x:v>
       </x:c>
       <x:c r="F127" s="23" t="n">
-        <x:v>8357.46</x:v>
+        <x:v>8357.464</x:v>
       </x:c>
       <x:c r="G127" s="23" t="n">
-        <x:v>8432.68</x:v>
+        <x:v>8432.679</x:v>
       </x:c>
       <x:c r="H127" s="23" t="n">
         <x:v>47.9</x:v>
       </x:c>
       <x:c r="I127" s="24" t="n">
-        <x:v>0.005712731878475097</x:v>
+        <x:v>0.00571249266975471</x:v>
       </x:c>
       <x:c r="J127" s="26" t="n">
         <x:f>ROUND(E127-F127,1)</x:f>
@@ -21567,22 +21603,22 @@
         <x:v>6月4日</x:v>
       </x:c>
       <x:c r="D128" s="23" t="n">
-        <x:v>8338.85</x:v>
+        <x:v>8338.854</x:v>
       </x:c>
       <x:c r="E128" s="23" t="n">
-        <x:v>8456.02</x:v>
+        <x:v>8456.017</x:v>
       </x:c>
       <x:c r="F128" s="23" t="n">
-        <x:v>8338.85</x:v>
+        <x:v>8338.854</x:v>
       </x:c>
       <x:c r="G128" s="23" t="n">
-        <x:v>8420.09</x:v>
+        <x:v>8420.095</x:v>
       </x:c>
       <x:c r="H128" s="23" t="n">
         <x:v>-12.6</x:v>
       </x:c>
       <x:c r="I128" s="24" t="n">
-        <x:v>-0.0014930010388156667</x:v>
+        <x:v>-0.001492289698208693</x:v>
       </x:c>
       <x:c r="J128" s="23" t="n">
         <x:f>ROUND(E128-F128,1)</x:f>
@@ -21603,22 +21639,22 @@
         <x:v>6月5日</x:v>
       </x:c>
       <x:c r="D129" s="23" t="n">
-        <x:v>8380.85</x:v>
+        <x:v>8380.852</x:v>
       </x:c>
       <x:c r="E129" s="23" t="n">
         <x:v>8500.1</x:v>
       </x:c>
       <x:c r="F129" s="23" t="n">
-        <x:v>8305.4</x:v>
+        <x:v>8305.396</x:v>
       </x:c>
       <x:c r="G129" s="23" t="n">
-        <x:v>8340.96</x:v>
+        <x:v>8340.963</x:v>
       </x:c>
       <x:c r="H129" s="23" t="n">
         <x:v>-79.1</x:v>
       </x:c>
       <x:c r="I129" s="24" t="n">
-        <x:v>-0.009397761781643754</x:v>
+        <x:v>-0.009397993728099241</x:v>
       </x:c>
       <x:c r="J129" s="26" t="n">
         <x:f>ROUND(E129-F129,1)</x:f>
@@ -21639,22 +21675,22 @@
         <x:v>6月8日</x:v>
       </x:c>
       <x:c r="D130" s="23" t="n">
-        <x:v>8069.48</x:v>
+        <x:v>8069.482</x:v>
       </x:c>
       <x:c r="E130" s="23" t="n">
-        <x:v>8260.19</x:v>
+        <x:v>8260.192</x:v>
       </x:c>
       <x:c r="F130" s="23" t="n">
-        <x:v>7987.4</x:v>
+        <x:v>7987.396</x:v>
       </x:c>
       <x:c r="G130" s="23" t="n">
-        <x:v>8081.26</x:v>
+        <x:v>8081.261</x:v>
       </x:c>
       <x:c r="H130" s="28" t="n">
         <x:v>-259.7</x:v>
       </x:c>
       <x:c r="I130" s="24" t="n">
-        <x:v>-0.031135504786019674</x:v>
+        <x:v>-0.031135733367957497</x:v>
       </x:c>
       <x:c r="J130" s="26" t="n">
         <x:f>ROUND(E130-F130,1)</x:f>
@@ -21675,22 +21711,22 @@
         <x:v>6月9日</x:v>
       </x:c>
       <x:c r="D131" s="23" t="n">
-        <x:v>8178.82</x:v>
+        <x:v>8178.823</x:v>
       </x:c>
       <x:c r="E131" s="23" t="n">
-        <x:v>8322.11</x:v>
+        <x:v>8322.109</x:v>
       </x:c>
       <x:c r="F131" s="23" t="n">
-        <x:v>8096.58</x:v>
+        <x:v>8096.577</x:v>
       </x:c>
       <x:c r="G131" s="23" t="n">
-        <x:v>8318.7</x:v>
+        <x:v>8318.698</x:v>
       </x:c>
       <x:c r="H131" s="28" t="n">
         <x:v>237.4</x:v>
       </x:c>
       <x:c r="I131" s="24" t="n">
-        <x:v>0.029381556836433953</x:v>
+        <x:v>0.029381181971476877</x:v>
       </x:c>
       <x:c r="J131" s="26" t="n">
         <x:f>ROUND(E131-F131,1)</x:f>
@@ -21711,22 +21747,22 @@
         <x:v>6月10日</x:v>
       </x:c>
       <x:c r="D132" s="23" t="n">
-        <x:v>8232.02</x:v>
+        <x:v>8232.024</x:v>
       </x:c>
       <x:c r="E132" s="23" t="n">
-        <x:v>8285.29</x:v>
+        <x:v>8285.286</x:v>
       </x:c>
       <x:c r="F132" s="23" t="n">
         <x:v>8103.01</x:v>
       </x:c>
       <x:c r="G132" s="23" t="n">
-        <x:v>8198.72</x:v>
+        <x:v>8198.723</x:v>
       </x:c>
       <x:c r="H132" s="23" t="n">
         <x:v>-120</x:v>
       </x:c>
       <x:c r="I132" s="24" t="n">
-        <x:v>-0.014422926659213742</x:v>
+        <x:v>-0.014422329071208106</x:v>
       </x:c>
       <x:c r="J132" s="26" t="n">
         <x:f>ROUND(E132-F132,1)</x:f>
@@ -21750,19 +21786,19 @@
         <x:v>8158.46</x:v>
       </x:c>
       <x:c r="E133" s="23" t="n">
-        <x:v>8223.53</x:v>
+        <x:v>8223.527</x:v>
       </x:c>
       <x:c r="F133" s="23" t="n">
         <x:v>8084.9</x:v>
       </x:c>
       <x:c r="G133" s="23" t="n">
-        <x:v>8159.45</x:v>
+        <x:v>8159.455</x:v>
       </x:c>
       <x:c r="H133" s="23" t="n">
         <x:v>-39.3</x:v>
       </x:c>
       <x:c r="I133" s="24" t="n">
-        <x:v>-0.004789772061980391</x:v>
+        <x:v>-0.004789526368923602</x:v>
       </x:c>
       <x:c r="J133" s="23" t="n">
         <x:f>ROUND(E133-F133,1)</x:f>
@@ -21783,22 +21819,22 @@
         <x:v>6月12日</x:v>
       </x:c>
       <x:c r="D134" s="23" t="n">
-        <x:v>8294.9</x:v>
+        <x:v>8294.897</x:v>
       </x:c>
       <x:c r="E134" s="23" t="n">
-        <x:v>8348.79</x:v>
+        <x:v>8348.786</x:v>
       </x:c>
       <x:c r="F134" s="23" t="n">
-        <x:v>8181.42</x:v>
+        <x:v>8181.417</x:v>
       </x:c>
       <x:c r="G134" s="23" t="n">
-        <x:v>8202.8</x:v>
+        <x:v>8202.799</x:v>
       </x:c>
       <x:c r="H134" s="23" t="n">
         <x:v>43.3</x:v>
       </x:c>
       <x:c r="I134" s="24" t="n">
-        <x:v>0.005312858097052953</x:v>
+        <x:v>0.005312119498177337</x:v>
       </x:c>
       <x:c r="J134" s="23" t="n">
         <x:f>ROUND(E134-F134,1)</x:f>
@@ -21819,22 +21855,22 @@
         <x:v>6月15日</x:v>
       </x:c>
       <x:c r="D135" s="23" t="n">
-        <x:v>8269.4</x:v>
+        <x:v>8269.397</x:v>
       </x:c>
       <x:c r="E135" s="23" t="n">
-        <x:v>8521.23</x:v>
+        <x:v>8521.233</x:v>
       </x:c>
       <x:c r="F135" s="23" t="n">
-        <x:v>8269.4</x:v>
+        <x:v>8269.397</x:v>
       </x:c>
       <x:c r="G135" s="23" t="n">
-        <x:v>8521.23</x:v>
+        <x:v>8521.233</x:v>
       </x:c>
       <x:c r="H135" s="28" t="n">
         <x:v>318.4</x:v>
       </x:c>
       <x:c r="I135" s="24" t="n">
-        <x:v>0.03881967133174036</x:v>
+        <x:v>0.03882016370265795</x:v>
       </x:c>
       <x:c r="J135" s="26" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
@@ -21861,16 +21897,16 @@
         <x:v>8684.65</x:v>
       </x:c>
       <x:c r="F136" s="23" t="n">
-        <x:v>8508.91</x:v>
+        <x:v>8508.908</x:v>
       </x:c>
       <x:c r="G136" s="23" t="n">
-        <x:v>8646.4</x:v>
+        <x:v>8646.403</x:v>
       </x:c>
       <x:c r="H136" s="23" t="n">
         <x:v>125.2</x:v>
       </x:c>
       <x:c r="I136" s="24" t="n">
-        <x:v>0.01468919393092305</x:v>
+        <x:v>0.014689188759420047</x:v>
       </x:c>
       <x:c r="J136" s="23" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -21894,19 +21930,19 @@
         <x:v>8581.65</x:v>
       </x:c>
       <x:c r="E137" s="23" t="n">
-        <x:v>8705.4</x:v>
+        <x:v>8705.403</x:v>
       </x:c>
       <x:c r="F137" s="23" t="n">
         <x:v>8581.65</x:v>
       </x:c>
       <x:c r="G137" s="23" t="n">
-        <x:v>8704.47</x:v>
+        <x:v>8704.468</x:v>
       </x:c>
       <x:c r="H137" s="23" t="n">
         <x:v>58.1</x:v>
       </x:c>
       <x:c r="I137" s="24" t="n">
-        <x:v>0.006716089933382685</x:v>
+        <x:v>0.006715509327982927</x:v>
       </x:c>
       <x:c r="J137" s="23" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -21927,22 +21963,22 @@
         <x:v>6月18日</x:v>
       </x:c>
       <x:c r="D138" s="23" t="n">
-        <x:v>8666.64</x:v>
+        <x:v>8666.638</x:v>
       </x:c>
       <x:c r="E138" s="23" t="n">
-        <x:v>8796.48</x:v>
+        <x:v>8796.485</x:v>
       </x:c>
       <x:c r="F138" s="23" t="n">
-        <x:v>8664.28</x:v>
+        <x:v>8664.278</x:v>
       </x:c>
       <x:c r="G138" s="23" t="n">
-        <x:v>8771.02</x:v>
+        <x:v>8771.024</x:v>
       </x:c>
       <x:c r="H138" s="23" t="n">
         <x:v>66.6</x:v>
       </x:c>
       <x:c r="I138" s="24" t="n">
-        <x:v>0.00764549708368234</x:v>
+        <x:v>0.007646188141538168</x:v>
       </x:c>
       <x:c r="J138" s="23" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -21963,22 +21999,22 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="42" t="n">
-        <x:v>8813.72</x:v>
+        <x:v>8813.725</x:v>
       </x:c>
       <x:c r="E139" s="42" t="n">
-        <x:v>8865.81</x:v>
+        <x:v>8865.815</x:v>
       </x:c>
       <x:c r="F139" s="42" t="n">
-        <x:v>8609.61</x:v>
+        <x:v>8609.611</x:v>
       </x:c>
       <x:c r="G139" s="42" t="n">
-        <x:v>8865.68</x:v>
+        <x:v>8865.676</x:v>
       </x:c>
       <x:c r="H139" s="42" t="n">
         <x:v>94.7</x:v>
       </x:c>
       <x:c r="I139" s="43" t="n">
-        <x:v>0.010792359383515304</x:v>
+        <x:v>0.010791442367504622</x:v>
       </x:c>
       <x:c r="J139" s="26" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -21999,22 +22035,22 @@
         <x:v>6月23日</x:v>
       </x:c>
       <x:c r="D140" s="23" t="n">
-        <x:v>8838.76</x:v>
+        <x:v>8838.763</x:v>
       </x:c>
       <x:c r="E140" s="23" t="n">
-        <x:v>8862.72</x:v>
+        <x:v>8862.719</x:v>
       </x:c>
       <x:c r="F140" s="23" t="n">
-        <x:v>8626.1</x:v>
+        <x:v>8626.101</x:v>
       </x:c>
       <x:c r="G140" s="23" t="n">
-        <x:v>8680.04</x:v>
+        <x:v>8680.039</x:v>
       </x:c>
       <x:c r="H140" s="28" t="n">
         <x:v>-185.6</x:v>
       </x:c>
       <x:c r="I140" s="24" t="n">
-        <x:v>-0.02093917217855812</x:v>
+        <x:v>-0.020938843242184646</x:v>
       </x:c>
       <x:c r="J140" s="26" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -22035,22 +22071,22 @@
         <x:v>6月24日</x:v>
       </x:c>
       <x:c r="D141" s="23" t="n">
-        <x:v>8650.82</x:v>
+        <x:v>8650.816</x:v>
       </x:c>
       <x:c r="E141" s="23" t="n">
-        <x:v>8803.5</x:v>
+        <x:v>8803.501</x:v>
       </x:c>
       <x:c r="F141" s="23" t="n">
-        <x:v>8581.75</x:v>
+        <x:v>8581.751</x:v>
       </x:c>
       <x:c r="G141" s="23" t="n">
-        <x:v>8793.49</x:v>
+        <x:v>8793.487</x:v>
       </x:c>
       <x:c r="H141" s="23" t="n">
         <x:v>113.4</x:v>
       </x:c>
       <x:c r="I141" s="24" t="n">
-        <x:v>0.013070216266284351</x:v>
+        <x:v>0.01306998735835152</x:v>
       </x:c>
       <x:c r="J141" s="26" t="n">
         <x:f>ROUND(E141-F141,1)</x:f>
@@ -22071,13 +22107,13 @@
         <x:v>6月25日</x:v>
       </x:c>
       <x:c r="D142" s="23" t="n">
-        <x:v>8806.07</x:v>
+        <x:v>8806.071</x:v>
       </x:c>
       <x:c r="E142" s="23" t="n">
-        <x:v>8872.12</x:v>
+        <x:v>8872.123</x:v>
       </x:c>
       <x:c r="F142" s="23" t="n">
-        <x:v>8743.25</x:v>
+        <x:v>8743.249</x:v>
       </x:c>
       <x:c r="G142" s="23" t="n">
         <x:v>8825.92</x:v>
@@ -22086,7 +22122,7 @@
         <x:v>32.4</x:v>
       </x:c>
       <x:c r="I142" s="24" t="n">
-        <x:v>0.003687955521641584</x:v>
+        <x:v>0.0036882979414196715</x:v>
       </x:c>
       <x:c r="J142" s="23" t="n">
         <x:f>ROUND(E142-F142,1)</x:f>
@@ -22107,22 +22143,22 @@
         <x:v>6月26日</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>8771.6</x:v>
+        <x:v>8771.598</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
-        <x:v>8797.28</x:v>
+        <x:v>8797.282</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>8563.7</x:v>
+        <x:v>8563.695</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
-        <x:v>8601.41</x:v>
+        <x:v>8601.408</x:v>
       </x:c>
       <x:c r="H143" s="28" t="n">
         <x:v>-224.5</x:v>
       </x:c>
       <x:c r="I143" s="24" t="n">
-        <x:v>-0.025437574779739736</x:v>
+        <x:v>-0.025437801385011505</x:v>
       </x:c>
       <x:c r="J143" s="26" t="n">
         <x:f>ROUND(E143-F143,1)</x:f>
@@ -22143,22 +22179,22 @@
         <x:v>6月29日</x:v>
       </x:c>
       <x:c r="D144" s="23" t="n">
-        <x:v>8616.42</x:v>
+        <x:v>8616.424</x:v>
       </x:c>
       <x:c r="E144" s="23" t="n">
         <x:v>8677.63</x:v>
       </x:c>
       <x:c r="F144" s="23" t="n">
-        <x:v>8413.86</x:v>
+        <x:v>8413.864</x:v>
       </x:c>
       <x:c r="G144" s="23" t="n">
-        <x:v>8597.89</x:v>
+        <x:v>8597.893</x:v>
       </x:c>
       <x:c r="H144" s="23" t="n">
         <x:v>-3.5</x:v>
       </x:c>
       <x:c r="I144" s="24" t="n">
-        <x:v>-0.0004092352300378854</x:v>
+        <x:v>-0.00040865402501533143</x:v>
       </x:c>
       <x:c r="J144" s="26" t="n">
         <x:f>ROUND(E144-F144,1)</x:f>
@@ -22182,19 +22218,19 @@
         <x:v>8574.25</x:v>
       </x:c>
       <x:c r="E145" s="23" t="n">
-        <x:v>8815.11</x:v>
+        <x:v>8815.108</x:v>
       </x:c>
       <x:c r="F145" s="23" t="n">
-        <x:v>8547.31</x:v>
+        <x:v>8547.312</x:v>
       </x:c>
       <x:c r="G145" s="23" t="n">
-        <x:v>8809.79</x:v>
+        <x:v>8809.786</x:v>
       </x:c>
       <x:c r="H145" s="28" t="n">
         <x:v>211.9</x:v>
       </x:c>
       <x:c r="I145" s="24" t="n">
-        <x:v>0.02464558164852093</x:v>
+        <x:v>0.024644758896162022</x:v>
       </x:c>
       <x:c r="J145" s="26" t="n">
         <x:f>ROUND(E145-F145,1)</x:f>
@@ -22306,10 +22342,10 @@
         <x:v>8827.47</x:v>
       </x:c>
       <x:c r="E151" s="23" t="n">
-        <x:v>8944.19</x:v>
+        <x:v>8944.195</x:v>
       </x:c>
       <x:c r="F151" s="23" t="n">
-        <x:v>8806.65</x:v>
+        <x:v>8806.646</x:v>
       </x:c>
       <x:c r="G151" s="23" t="n">
         <x:v>8876.63</x:v>
@@ -22318,7 +22354,7 @@
         <x:v>66.8</x:v>
       </x:c>
       <x:c r="I151" s="24" t="n">
-        <x:v>0.007587013992387925</x:v>
+        <x:v>0.007587471477740637</x:v>
       </x:c>
       <x:c r="J151" s="23" t="n">
         <x:f>ROUND(E151-F151,1)</x:f>
@@ -22339,22 +22375,22 @@
         <x:v>7月2日</x:v>
       </x:c>
       <x:c r="D152" s="23" t="n">
-        <x:v>8688.29</x:v>
+        <x:v>8688.291</x:v>
       </x:c>
       <x:c r="E152" s="23" t="n">
-        <x:v>8865.97</x:v>
+        <x:v>8865.966</x:v>
       </x:c>
       <x:c r="F152" s="23" t="n">
-        <x:v>8598.87</x:v>
+        <x:v>8598.869</x:v>
       </x:c>
       <x:c r="G152" s="23" t="n">
-        <x:v>8625.33</x:v>
+        <x:v>8625.334</x:v>
       </x:c>
       <x:c r="H152" s="28" t="n">
         <x:v>-251.3</x:v>
       </x:c>
       <x:c r="I152" s="24" t="n">
-        <x:v>-0.028310293433431277</x:v>
+        <x:v>-0.02830984281196791</x:v>
       </x:c>
       <x:c r="J152" s="26" t="n">
         <x:f>ROUND(E152-F152,1)</x:f>
@@ -22375,22 +22411,22 @@
         <x:v>7月3日</x:v>
       </x:c>
       <x:c r="D153" s="23" t="n">
-        <x:v>8627.38</x:v>
+        <x:v>8627.382</x:v>
       </x:c>
       <x:c r="E153" s="23" t="n">
-        <x:v>8740.67</x:v>
+        <x:v>8740.668</x:v>
       </x:c>
       <x:c r="F153" s="23" t="n">
-        <x:v>8559.28</x:v>
+        <x:v>8559.285</x:v>
       </x:c>
       <x:c r="G153" s="23" t="n">
-        <x:v>8620.79</x:v>
+        <x:v>8620.789</x:v>
       </x:c>
       <x:c r="H153" s="23" t="n">
         <x:v>-4.5</x:v>
       </x:c>
       <x:c r="I153" s="24" t="n">
-        <x:v>-0.0005263566727300439</x:v>
+        <x:v>-0.0005269361163289243</x:v>
       </x:c>
       <x:c r="J153" s="26" t="n">
         <x:f>ROUND(E153-F153,1)</x:f>
@@ -22411,22 +22447,22 @@
         <x:v>7月6日</x:v>
       </x:c>
       <x:c r="D154" s="23" t="n">
-        <x:v>8669.12</x:v>
+        <x:v>8669.123</x:v>
       </x:c>
       <x:c r="E154" s="23" t="n">
-        <x:v>8694.8</x:v>
+        <x:v>8694.805</x:v>
       </x:c>
       <x:c r="F154" s="23" t="n">
-        <x:v>8432.9</x:v>
+        <x:v>8432.897</x:v>
       </x:c>
       <x:c r="G154" s="23" t="n">
-        <x:v>8472.6</x:v>
+        <x:v>8472.603</x:v>
       </x:c>
       <x:c r="H154" s="23" t="n">
         <x:v>-148.2</x:v>
       </x:c>
       <x:c r="I154" s="24" t="n">
-        <x:v>-0.01718983991026346</x:v>
+        <x:v>-0.01718937790960917</x:v>
       </x:c>
       <x:c r="J154" s="26" t="n">
         <x:f>ROUND(E154-F154,1)</x:f>
@@ -22447,22 +22483,22 @@
         <x:v>7月7日</x:v>
       </x:c>
       <x:c r="D155" s="23" t="n">
-        <x:v>8436.39</x:v>
+        <x:v>8436.389</x:v>
       </x:c>
       <x:c r="E155" s="23" t="n">
-        <x:v>8489.48</x:v>
+        <x:v>8489.476</x:v>
       </x:c>
       <x:c r="F155" s="23" t="n">
-        <x:v>8261.4</x:v>
+        <x:v>8261.398</x:v>
       </x:c>
       <x:c r="G155" s="23" t="n">
-        <x:v>8301.8</x:v>
+        <x:v>8301.804</x:v>
       </x:c>
       <x:c r="H155" s="28" t="n">
         <x:v>-170.8</x:v>
       </x:c>
       <x:c r="I155" s="24" t="n">
-        <x:v>-0.020159101102377175</x:v>
+        <x:v>-0.02015897593691085</x:v>
       </x:c>
       <x:c r="J155" s="26" t="n">
         <x:f>ROUND(E155-F155,1)</x:f>
@@ -22483,22 +22519,22 @@
         <x:v>7月8日</x:v>
       </x:c>
       <x:c r="D156" s="23" t="n">
-        <x:v>8315.96</x:v>
+        <x:v>8315.962</x:v>
       </x:c>
       <x:c r="E156" s="23" t="n">
-        <x:v>8328.96</x:v>
+        <x:v>8328.965</x:v>
       </x:c>
       <x:c r="F156" s="23" t="n">
-        <x:v>8117.86</x:v>
+        <x:v>8117.861</x:v>
       </x:c>
       <x:c r="G156" s="23" t="n">
-        <x:v>8117.86</x:v>
+        <x:v>8117.861</x:v>
       </x:c>
       <x:c r="H156" s="28" t="n">
         <x:v>-183.9</x:v>
       </x:c>
       <x:c r="I156" s="24" t="n">
-        <x:v>-0.02215664072851664</x:v>
+        <x:v>-0.02215699142017813</x:v>
       </x:c>
       <x:c r="J156" s="26" t="n">
         <x:f>ROUND(E156-F156,1)</x:f>
@@ -22519,22 +22555,22 @@
         <x:v>7月9日</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>8161.86</x:v>
+        <x:v>8161.859</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>8312.62</x:v>
+        <x:v>8312.621</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>7978.81</x:v>
+        <x:v>7978.806</x:v>
       </x:c>
       <x:c r="G157" s="23" t="n">
-        <x:v>8300.08</x:v>
+        <x:v>8300.077</x:v>
       </x:c>
       <x:c r="H157" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I157" s="24" t="n">
-        <x:v>0.022446802482427586</x:v>
+        <x:v>0.0224463069766776</x:v>
       </x:c>
       <x:c r="J157" s="26" t="n">
         <x:f>ROUND(E157-F157,1)</x:f>
@@ -22555,22 +22591,22 @@
         <x:v>7月10日</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>8312.49</x:v>
+        <x:v>8312.492</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>8438.19</x:v>
+        <x:v>8438.194</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>8198.31</x:v>
+        <x:v>8198.308</x:v>
       </x:c>
       <x:c r="G158" s="23" t="n">
-        <x:v>8198.31</x:v>
+        <x:v>8198.308</x:v>
       </x:c>
       <x:c r="H158" s="23" t="n">
         <x:v>-101.8</x:v>
       </x:c>
       <x:c r="I158" s="24" t="n">
-        <x:v>-0.012261327601661764</x:v>
+        <x:v>-0.012261211552615503</x:v>
       </x:c>
       <x:c r="J158" s="26" t="n">
         <x:f>ROUND(E158-F158,1)</x:f>
@@ -22591,22 +22627,22 @@
         <x:v>7月13日</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>8124.36</x:v>
+        <x:v>8124.363</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>8171.5</x:v>
+        <x:v>8171.504</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7769.29</x:v>
+        <x:v>7769.292</x:v>
       </x:c>
       <x:c r="G159" s="23" t="n">
-        <x:v>7787.85</x:v>
+        <x:v>7787.853</x:v>
       </x:c>
       <x:c r="H159" s="28" t="n">
         <x:v>-410.5</x:v>
       </x:c>
       <x:c r="I159" s="24" t="n">
-        <x:v>-0.050066416127226065</x:v>
+        <x:v>-0.050065818459126055</x:v>
       </x:c>
       <x:c r="J159" s="26" t="n">
         <x:f>ROUND(E159-F159,1)</x:f>
@@ -22627,22 +22663,22 @@
         <x:v>7月14日</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>7799.81</x:v>
+        <x:v>7799.813</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>7934.1</x:v>
+        <x:v>7934.103</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>7657.67</x:v>
+        <x:v>7657.671</x:v>
       </x:c>
       <x:c r="G160" s="23" t="n">
-        <x:v>7925.12</x:v>
+        <x:v>7925.123</x:v>
       </x:c>
       <x:c r="H160" s="23" t="n">
         <x:v>137.3</x:v>
       </x:c>
       <x:c r="I160" s="24" t="n">
-        <x:v>0.017626174104534487</x:v>
+        <x:v>0.017626167314662933</x:v>
       </x:c>
       <x:c r="J160" s="26" t="n">
         <x:f>ROUND(E160-F160,1)</x:f>
@@ -22663,22 +22699,22 @@
         <x:v>7月15日</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>7959.37</x:v>
+        <x:v>7959.374</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>7979.08</x:v>
+        <x:v>7979.077</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>7783.22</x:v>
+        <x:v>7783.219</x:v>
       </x:c>
       <x:c r="G161" s="23" t="n">
-        <x:v>7817.83</x:v>
+        <x:v>7817.831</x:v>
       </x:c>
       <x:c r="H161" s="23" t="n">
         <x:v>-107.3</x:v>
       </x:c>
       <x:c r="I161" s="24" t="n">
-        <x:v>-0.013537965355729598</x:v>
+        <x:v>-0.01353821259304111</x:v>
       </x:c>
       <x:c r="J161" s="26" t="n">
         <x:f>ROUND(E161-F161,1)</x:f>
@@ -22699,22 +22735,22 @@
         <x:v>7月16日</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>7713.14</x:v>
+        <x:v>7713.135</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
         <x:v>7836.39</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>7591.42</x:v>
+        <x:v>7591.421</x:v>
       </x:c>
       <x:c r="G162" s="23" t="n">
-        <x:v>7631.76</x:v>
+        <x:v>7631.762</x:v>
       </x:c>
       <x:c r="H162" s="28" t="n">
         <x:v>-186.1</x:v>
       </x:c>
       <x:c r="I162" s="24" t="n">
-        <x:v>-0.023800722195289503</x:v>
+        <x:v>-0.02380059123815803</x:v>
       </x:c>
       <x:c r="J162" s="26" t="n">
         <x:f>ROUND(E162-F162,1)</x:f>
@@ -22735,22 +22771,22 @@
         <x:v>7月17日</x:v>
       </x:c>
       <x:c r="D163" s="42" t="n">
-        <x:v>7599.39</x:v>
+        <x:v>7599.388</x:v>
       </x:c>
       <x:c r="E163" s="42" t="n">
-        <x:v>7605.61</x:v>
+        <x:v>7605.613</x:v>
       </x:c>
       <x:c r="F163" s="42" t="n">
-        <x:v>7163.31</x:v>
+        <x:v>7163.309</x:v>
       </x:c>
       <x:c r="G163" s="42" t="n">
-        <x:v>7168</x:v>
+        <x:v>7167.996</x:v>
       </x:c>
       <x:c r="H163" s="28" t="n">
         <x:v>-463.8</x:v>
       </x:c>
       <x:c r="I163" s="43" t="n">
-        <x:v>-0.06076711007683677</x:v>
+        <x:v>-0.06076788034008396</x:v>
       </x:c>
       <x:c r="J163" s="26" t="n">
         <x:f>ROUND(E163-F163,1)</x:f>
@@ -22771,22 +22807,22 @@
         <x:v>7月20日</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>7256.27</x:v>
+        <x:v>7256.267</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>7298.12</x:v>
+        <x:v>7298.122</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>6824.14</x:v>
+        <x:v>6824.145</x:v>
       </x:c>
       <x:c r="G164" s="23" t="n">
-        <x:v>6965.38</x:v>
+        <x:v>6965.376</x:v>
       </x:c>
       <x:c r="H164" s="28" t="n">
         <x:v>-202.6</x:v>
       </x:c>
       <x:c r="I164" s="24" t="n">
-        <x:v>-0.028267299107142874</x:v>
+        <x:v>-0.028267314881314065</x:v>
       </x:c>
       <x:c r="J164" s="26" t="n">
         <x:f>ROUND(E164-F164,1)</x:f>
@@ -22807,22 +22843,22 @@
         <x:v>7月21日</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>6975.89</x:v>
+        <x:v>6975.893</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>7264.34</x:v>
+        <x:v>7264.338</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>6714.19</x:v>
+        <x:v>6714.187</x:v>
       </x:c>
       <x:c r="G165" s="23" t="n">
-        <x:v>7259.86</x:v>
+        <x:v>7259.863</x:v>
       </x:c>
       <x:c r="H165" s="28" t="n">
         <x:v>294.5</x:v>
       </x:c>
       <x:c r="I165" s="24" t="n">
-        <x:v>0.042277664678739724</x:v>
+        <x:v>0.042278693928367916</x:v>
       </x:c>
       <x:c r="J165" s="26" t="n">
         <x:f>ROUND(E165-F165,1)</x:f>
@@ -22843,22 +22879,22 @@
         <x:v>7月22日</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>7196.86</x:v>
+        <x:v>7196.863</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>7302.45</x:v>
+        <x:v>7302.454</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
         <x:v>7118.66</x:v>
       </x:c>
       <x:c r="G166" s="23" t="n">
-        <x:v>7158.76</x:v>
+        <x:v>7158.762</x:v>
       </x:c>
       <x:c r="H166" s="23" t="n">
         <x:v>-101.1</x:v>
       </x:c>
       <x:c r="I166" s="24" t="n">
-        <x:v>-0.013925888378012674</x:v>
+        <x:v>-0.01392602036705104</x:v>
       </x:c>
       <x:c r="J166" s="26" t="n">
         <x:f>ROUND(E166-F166,1)</x:f>
@@ -22879,13 +22915,13 @@
         <x:v>7月23日</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>7169.54</x:v>
+        <x:v>7169.543</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>7247.14</x:v>
+        <x:v>7247.141</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7113.5</x:v>
+        <x:v>7113.498</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
         <x:v>7195.5</x:v>
@@ -22894,7 +22930,7 @@
         <x:v>36.7</x:v>
       </x:c>
       <x:c r="I167" s="24" t="n">
-        <x:v>0.005132173728411127</x:v>
+        <x:v>0.0051318929166803695</x:v>
       </x:c>
       <x:c r="J167" s="23" t="n">
         <x:f>ROUND(E167-F167,1)</x:f>
@@ -22915,22 +22951,22 @@
         <x:v>7月24日</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>7109.25</x:v>
+        <x:v>7109.248</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>7174.55</x:v>
+        <x:v>7174.552</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>6995.69</x:v>
+        <x:v>6995.693</x:v>
       </x:c>
       <x:c r="G168" s="23" t="n">
-        <x:v>6995.69</x:v>
+        <x:v>6995.693</x:v>
       </x:c>
       <x:c r="H168" s="28" t="n">
         <x:v>-199.8</x:v>
       </x:c>
       <x:c r="I168" s="24" t="n">
-        <x:v>-0.027768744354110253</x:v>
+        <x:v>-0.02776832742686397</x:v>
       </x:c>
       <x:c r="J168" s="23" t="n">
         <x:f>ROUND(E168-F168,1)</x:f>
@@ -22951,22 +22987,22 @@
         <x:v>7月27日</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>6981.16</x:v>
+        <x:v>6981.165</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>7228.78</x:v>
+        <x:v>7228.785</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>6972.28</x:v>
+        <x:v>6972.282</x:v>
       </x:c>
       <x:c r="G169" s="23" t="n">
-        <x:v>7228.78</x:v>
+        <x:v>7228.785</x:v>
       </x:c>
       <x:c r="H169" s="28" t="n">
         <x:v>233.1</x:v>
       </x:c>
       <x:c r="I169" s="24" t="n">
-        <x:v>0.03331908646609549</x:v>
+        <x:v>0.03331935806788544</x:v>
       </x:c>
       <x:c r="J169" s="26" t="n">
         <x:f>ROUND(E169-F169,1)</x:f>
@@ -22987,22 +23023,22 @@
         <x:v>7月28日</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>7135.73</x:v>
+        <x:v>7135.735</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>7189.18</x:v>
+        <x:v>7189.177</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>6992.94</x:v>
+        <x:v>6992.944</x:v>
       </x:c>
       <x:c r="G170" s="23" t="n">
-        <x:v>7026.28</x:v>
+        <x:v>7026.276</x:v>
       </x:c>
       <x:c r="H170" s="28" t="n">
         <x:v>-202.5</x:v>
       </x:c>
       <x:c r="I170" s="24" t="n">
-        <x:v>-0.028013025711115858</x:v>
+        <x:v>-0.02801425135759328</x:v>
       </x:c>
       <x:c r="J170" s="26" t="n">
         <x:f>ROUND(E170-F170,1)</x:f>
@@ -23023,22 +23059,22 @@
         <x:v>7月29日</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>7020.22</x:v>
+        <x:v>7020.223</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>7132.35</x:v>
+        <x:v>7132.352</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>6897.39</x:v>
+        <x:v>6897.392</x:v>
       </x:c>
       <x:c r="G171" s="23" t="n">
-        <x:v>7095.19</x:v>
+        <x:v>7095.186</x:v>
       </x:c>
       <x:c r="H171" s="23" t="n">
         <x:v>68.9</x:v>
       </x:c>
       <x:c r="I171" s="24" t="n">
-        <x:v>0.009807465685967465</x:v>
+        <x:v>0.009807471269275503</x:v>
       </x:c>
       <x:c r="J171" s="26" t="n">
         <x:f>ROUND(E171-F171,1)</x:f>
@@ -23062,19 +23098,19 @@
         <x:v>7053.09</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>7121.52</x:v>
+        <x:v>7121.523</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>6841.75</x:v>
+        <x:v>6841.751</x:v>
       </x:c>
       <x:c r="G172" s="23" t="n">
-        <x:v>6900.66</x:v>
+        <x:v>6900.658</x:v>
       </x:c>
       <x:c r="H172" s="28" t="n">
         <x:v>-194.5</x:v>
       </x:c>
       <x:c r="I172" s="24" t="n">
-        <x:v>-0.027417165713673586</x:v>
+        <x:v>-0.027416899289179897</x:v>
       </x:c>
       <x:c r="J172" s="26" t="n">
         <x:f>ROUND(E172-F172,1)</x:f>
@@ -23095,22 +23131,22 @@
         <x:v>7月31日</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>7082.75</x:v>
+        <x:v>7082.754</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>7218.06</x:v>
+        <x:v>7218.061</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>7071.05</x:v>
+        <x:v>7071.048</x:v>
       </x:c>
       <x:c r="G173" s="23" t="n">
-        <x:v>7075.51</x:v>
+        <x:v>7075.507</x:v>
       </x:c>
       <x:c r="H173" s="28" t="n">
-        <x:v>174.9</x:v>
+        <x:v>174.8</x:v>
       </x:c>
       <x:c r="I173" s="24" t="n">
-        <x:v>0.02533815606043488</x:v>
+        <x:v>0.02533801849041062</x:v>
       </x:c>
       <x:c r="J173" s="23" t="n">
         <x:f>ROUND(E173-F173,1)</x:f>
@@ -23219,22 +23255,22 @@
         <x:v>8月3日</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7055.27</x:v>
+        <x:v>7055.271</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>7118.1</x:v>
+        <x:v>7118.097</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7042.89</x:v>
+        <x:v>7042.889</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
-        <x:v>7079.78</x:v>
+        <x:v>7079.776</x:v>
       </x:c>
       <x:c r="H179" s="23" t="n">
         <x:v>4.3</x:v>
       </x:c>
       <x:c r="I179" s="24" t="n">
-        <x:v>0.0006034900664404486</x:v>
+        <x:v>0.0006033489896908328</x:v>
       </x:c>
       <x:c r="J179" s="23" t="n">
         <x:f>ROUND(E179-F179,1)</x:f>
@@ -23255,22 +23291,22 @@
         <x:v>8月4日</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>7128.49</x:v>
+        <x:v>7128.494</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>7307.17</x:v>
+        <x:v>7307.171</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
         <x:v>7102.46</x:v>
       </x:c>
       <x:c r="G180" s="23" t="n">
-        <x:v>7279.19</x:v>
+        <x:v>7279.193</x:v>
       </x:c>
       <x:c r="H180" s="28" t="n">
         <x:v>199.4</x:v>
       </x:c>
       <x:c r="I180" s="24" t="n">
-        <x:v>0.028166129456000055</x:v>
+        <x:v>0.028167134101418023</x:v>
       </x:c>
       <x:c r="J180" s="26" t="n">
         <x:f>ROUND(E180-F180,1)</x:f>
@@ -23291,22 +23327,22 @@
         <x:v>8月5日</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>7253.22</x:v>
+        <x:v>7253.225</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>7523.5</x:v>
+        <x:v>7523.498</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>7253.22</x:v>
+        <x:v>7253.225</x:v>
       </x:c>
       <x:c r="G181" s="23" t="n">
-        <x:v>7493.05</x:v>
+        <x:v>7493.048</x:v>
       </x:c>
       <x:c r="H181" s="28" t="n">
         <x:v>213.9</x:v>
       </x:c>
       <x:c r="I181" s="24" t="n">
-        <x:v>0.02937964251517</x:v>
+        <x:v>0.029378943517502476</x:v>
       </x:c>
       <x:c r="J181" s="26" t="n">
         <x:f>ROUND(E181-F181,1)</x:f>
@@ -23327,22 +23363,22 @@
         <x:v>8月6日</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>7440.01</x:v>
+        <x:v>7440.008</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>7564.69</x:v>
+        <x:v>7564.692</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>7434.49</x:v>
+        <x:v>7434.494</x:v>
       </x:c>
       <x:c r="G182" s="23" t="n">
-        <x:v>7530.43</x:v>
+        <x:v>7530.425</x:v>
       </x:c>
       <x:c r="H182" s="23" t="n">
         <x:v>37.4</x:v>
       </x:c>
       <x:c r="I182" s="24" t="n">
-        <x:v>0.004988622790452535</x:v>
+        <x:v>0.0049882237508689364</x:v>
       </x:c>
       <x:c r="J182" s="23" t="n">
         <x:f>ROUND(E182-F182,1)</x:f>
@@ -23363,22 +23399,22 @@
         <x:v>8月7日</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>7534.24</x:v>
+        <x:v>7534.242</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
         <x:v>7685.57</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>7448.46</x:v>
+        <x:v>7448.459</x:v>
       </x:c>
       <x:c r="G183" s="23" t="n">
-        <x:v>7679.53</x:v>
+        <x:v>7679.529</x:v>
       </x:c>
       <x:c r="H183" s="23" t="n">
         <x:v>149.1</x:v>
       </x:c>
       <x:c r="I183" s="24" t="n">
-        <x:v>0.019799666154522333</x:v>
+        <x:v>0.019800210479488323</x:v>
       </x:c>
       <x:c r="J183" s="26" t="n">
         <x:f>ROUND(E183-F183,1)</x:f>
@@ -23402,7 +23438,7 @@
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>7736.1</x:v>
+        <x:v>7736.102</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
         <x:v>7621.65</x:v>
@@ -23414,7 +23450,7 @@
         <x:v>54.4</x:v>
       </x:c>
       <x:c r="I184" s="24" t="n">
-        <x:v>0.00707986035603736</x:v>
+        <x:v>0.007079991494269855</x:v>
       </x:c>
       <x:c r="J184" s="23" t="n">
         <x:f>ROUND(E184-F184,1)</x:f>
@@ -23435,22 +23471,22 @@
         <x:v>8月11日</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>7686.04</x:v>
+        <x:v>7686.042</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
         <x:v>7789.21</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>7642.44</x:v>
+        <x:v>7642.437</x:v>
       </x:c>
       <x:c r="G185" s="23" t="n">
-        <x:v>7698.05</x:v>
+        <x:v>7698.048</x:v>
       </x:c>
       <x:c r="H185" s="23" t="n">
-        <x:v>-35.8</x:v>
+        <x:v>-35.9</x:v>
       </x:c>
       <x:c r="I185" s="24" t="n">
-        <x:v>-0.004635436196485543</x:v>
+        <x:v>-0.004635694798226009</x:v>
       </x:c>
       <x:c r="J185" s="23" t="n">
         <x:f>ROUND(E185-F185,1)</x:f>
@@ -23471,22 +23507,22 @@
         <x:v>8月12日</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>7704.96</x:v>
+        <x:v>7704.959</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>7805.27</x:v>
+        <x:v>7805.272</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>7692.44</x:v>
+        <x:v>7692.438</x:v>
       </x:c>
       <x:c r="G186" s="23" t="n">
-        <x:v>7793.72</x:v>
+        <x:v>7793.717</x:v>
       </x:c>
       <x:c r="H186" s="23" t="n">
         <x:v>95.7</x:v>
       </x:c>
       <x:c r="I186" s="24" t="n">
-        <x:v>0.012427822630406427</x:v>
+        <x:v>0.012427695956169549</x:v>
       </x:c>
       <x:c r="J186" s="23" t="n">
         <x:f>ROUND(E186-F186,1)</x:f>
@@ -23507,26 +23543,26 @@
         <x:v>8月13日</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>7847.24</x:v>
+        <x:v>7847.238</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>7880.22</x:v>
+        <x:v>7880.217</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>7714.37</x:v>
+        <x:v>7714.367</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
-        <x:v>7715.89</x:v>
+        <x:v>7715.895</x:v>
       </x:c>
       <x:c r="H187" s="23" t="n">
         <x:v>-77.8</x:v>
       </x:c>
       <x:c r="I187" s="24" t="n">
-        <x:v>-0.009986245335988464</x:v>
+        <x:v>-0.00998522271208968</x:v>
       </x:c>
       <x:c r="J187" s="23" t="n">
         <x:f>ROUND(E187-F187,1)</x:f>
-        <x:v>165.9</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="K187" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -23543,13 +23579,13 @@
         <x:v>8月14日</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>7750.99</x:v>
+        <x:v>7750.987</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>7784.38</x:v>
+        <x:v>7784.377</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>7673.44</x:v>
+        <x:v>7673.441</x:v>
       </x:c>
       <x:c r="G188" s="23" t="n">
         <x:v>7769.82</x:v>
@@ -23558,7 +23594,7 @@
         <x:v>53.9</x:v>
       </x:c>
       <x:c r="I188" s="24" t="n">
-        <x:v>0.0069894723745413945</x:v>
+        <x:v>0.006988819832307147</x:v>
       </x:c>
       <x:c r="J188" s="23" t="n">
         <x:f>ROUND(E188-F188,1)</x:f>
@@ -23579,22 +23615,22 @@
         <x:v>8月17日</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>7797.18</x:v>
+        <x:v>7797.184</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7968.383</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>7750.43</x:v>
+        <x:v>7750.433</x:v>
       </x:c>
       <x:c r="G189" s="23" t="n">
-        <x:v>7968.38</x:v>
+        <x:v>7968.383</x:v>
       </x:c>
       <x:c r="H189" s="28" t="n">
         <x:v>198.6</x:v>
       </x:c>
       <x:c r="I189" s="24" t="n">
-        <x:v>0.02555528956912778</x:v>
+        <x:v>0.02555567567845851</x:v>
       </x:c>
       <x:c r="J189" s="26" t="n">
         <x:f>ROUND(E189-F189,1)</x:f>
@@ -23615,22 +23651,22 @@
         <x:v>8月18日</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>7969.37</x:v>
+        <x:v>7969.374</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>7995.5</x:v>
+        <x:v>7995.501</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>7842.25</x:v>
+        <x:v>7842.246</x:v>
       </x:c>
       <x:c r="G190" s="23" t="n">
-        <x:v>7945.96</x:v>
+        <x:v>7945.964</x:v>
       </x:c>
       <x:c r="H190" s="23" t="n">
         <x:v>-22.4</x:v>
       </x:c>
       <x:c r="I190" s="24" t="n">
-        <x:v>-0.0028136208363557236</x:v>
+        <x:v>-0.002813494281085571</x:v>
       </x:c>
       <x:c r="J190" s="23" t="n">
         <x:f>ROUND(E190-F190,1)</x:f>
@@ -23651,22 +23687,22 @@
         <x:v>8月19日</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>7795.26</x:v>
+        <x:v>7795.259</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>7821.18</x:v>
+        <x:v>7821.177</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>7490.21</x:v>
+        <x:v>7490.212</x:v>
       </x:c>
       <x:c r="G191" s="23" t="n">
-        <x:v>7517.77</x:v>
+        <x:v>7517.768</x:v>
       </x:c>
       <x:c r="H191" s="28" t="n">
         <x:v>-428.2</x:v>
       </x:c>
       <x:c r="I191" s="24" t="n">
-        <x:v>-0.0538877618311695</x:v>
+        <x:v>-0.053888489804383655</x:v>
       </x:c>
       <x:c r="J191" s="26" t="n">
         <x:f>ROUND(E191-F191,1)</x:f>
@@ -23677,30 +23713,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>2270.6</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>7602.498</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>7656.613</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>7541.475</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>7589.779</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.009578773912682692</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>115.1</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -23708,11 +23762,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>174.7</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>2385.6</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>170.4</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29891,30 +29963,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>2201.8</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>7864.68</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>7923.91</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>7796.28</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>7850.4</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>66.9</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.008600288303659331</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>127.6</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -29922,11 +30012,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>169.4</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>2329.4</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>166.4</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -36105,30 +36213,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>564.6</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>3907.21</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>3925.06</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>3888.1</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>3903.72</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.002388032107476734</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -36136,11 +36262,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>43.4</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>601.6</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -48533,30 +48677,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>2209</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>7789.6</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>7811</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>7713</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>7761</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.006353734439834113</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -48564,11 +48726,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>169.9</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>164.8</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54747,30 +54927,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>808</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>4580</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>4585</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>4532.4</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>4554</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>-0.2</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>-0.000043915506565350704</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>52.6</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -54778,11 +54976,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>62.2</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>860.6</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>61.5</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R453ae6db5d9c474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rfff1164978ad4755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3bb890d3f6034c8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdd2bb07706d0440b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2c971c54c05e49a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R75f4bfc9f17446c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd06e71e757444154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ra596548056304159"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9ff1160e75a2442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R88b36b1b4837430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re21a1a73109549ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf3f900f1630749dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R65a30dc9cf2f4153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rda1ba70c062c48af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra2a9afdcc8fe40d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R21f1c60e17b348be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R76ed75ac8aa04045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R0be543999a5240ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6ed532afffb44ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R474fd0be94ef4339"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -522,10 +522,10 @@
         <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7656.613</x:v>
+        <x:v>7656.61</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7541.475</x:v>
+        <x:v>7541.48</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
         <x:v>115.1</x:v>
@@ -534,7 +534,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>27501.3</x:v>
+        <x:v>27501.6</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
         <x:v>179.7</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7734.6</x:v>
+        <x:v>7582.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7430</x:v>
+        <x:v>7482.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>304.6</x:v>
+        <x:v>99.4</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>29058.8</x:v>
+        <x:v>29158.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>191.2</x:v>
+        <x:v>190.6</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2892.8</x:v>
+        <x:v>2880.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2843</x:v>
+        <x:v>2848</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>49.8</x:v>
+        <x:v>32.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6327.8</x:v>
+        <x:v>6360.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>41.6</x:v>
@@ -7210,16 +7210,16 @@
         <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C5" s="23" t="n">
-        <x:v>7639.538</x:v>
+        <x:v>7639.54</x:v>
       </x:c>
       <x:c r="D5" s="23" t="n">
-        <x:v>8131.491</x:v>
+        <x:v>8131.49</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
-        <x:v>7623.749</x:v>
+        <x:v>7623.75</x:v>
       </x:c>
       <x:c r="F5" s="23" t="n">
-        <x:v>8129.183</x:v>
+        <x:v>8129.18</x:v>
       </x:c>
       <x:c r="G5" s="23"/>
       <x:c r="H5" s="24"/>
@@ -7242,16 +7242,16 @@
         <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C6" s="23" t="n">
-        <x:v>8196.085</x:v>
+        <x:v>8196.08</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
-        <x:v>8415.098</x:v>
+        <x:v>8415.1</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
-        <x:v>8151.107</x:v>
+        <x:v>8151.11</x:v>
       </x:c>
       <x:c r="F6" s="23" t="n">
-        <x:v>8232.729</x:v>
+        <x:v>8232.73</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
         <x:f>ROUND(F6-F5,1)</x:f>
@@ -7259,7 +7259,7 @@
       </x:c>
       <x:c r="H6" s="24" t="n">
         <x:f>IFERROR(F6/F5-1,"")</x:f>
-        <x:v>0.01273756538633708</x:v>
+        <x:v>0.012738062141568918</x:v>
       </x:c>
       <x:c r="I6" s="26" t="n">
         <x:f>ROUND(D6-E6,1)</x:f>
@@ -7280,16 +7280,16 @@
         <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C7" s="23" t="n">
-        <x:v>8204.627</x:v>
+        <x:v>8204.63</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
-        <x:v>8478.556</x:v>
+        <x:v>8478.56</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
-        <x:v>8104.918</x:v>
+        <x:v>8104.92</x:v>
       </x:c>
       <x:c r="F7" s="23" t="n">
-        <x:v>8470.744</x:v>
+        <x:v>8470.74</x:v>
       </x:c>
       <x:c r="G7" s="28" t="n">
         <x:f>ROUND(F7-F6,1)</x:f>
@@ -7297,7 +7297,7 @@
       </x:c>
       <x:c r="H7" s="24" t="n">
         <x:f>IFERROR(F7/F6-1,"")</x:f>
-        <x:v>0.02891082653151833</x:v>
+        <x:v>0.028910215687870222</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
         <x:f>ROUND(D7-E7,1)</x:f>
@@ -7318,10 +7318,10 @@
         <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C8" s="23" t="n">
-        <x:v>8513.222</x:v>
+        <x:v>8513.22</x:v>
       </x:c>
       <x:c r="D8" s="23" t="n">
-        <x:v>8530.417</x:v>
+        <x:v>8530.42</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
         <x:v>8083.97</x:v>
@@ -7335,7 +7335,7 @@
       </x:c>
       <x:c r="H8" s="24" t="n">
         <x:f>IFERROR(F8/F7-1,"")</x:f>
-        <x:v>-0.025485836899332592</x:v>
+        <x:v>-0.025485376720333686</x:v>
       </x:c>
       <x:c r="I8" s="26" t="n">
         <x:f>ROUND(D8-E8,1)</x:f>
@@ -7356,16 +7356,16 @@
         <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C9" s="23" t="n">
-        <x:v>8166.736</x:v>
+        <x:v>8166.74</x:v>
       </x:c>
       <x:c r="D9" s="23" t="n">
-        <x:v>8221.582</x:v>
+        <x:v>8221.58</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
         <x:v>7950.01</x:v>
       </x:c>
       <x:c r="F9" s="23" t="n">
-        <x:v>8051.574</x:v>
+        <x:v>8051.57</x:v>
       </x:c>
       <x:c r="G9" s="28" t="n">
         <x:f>ROUND(F9-F8,1)</x:f>
@@ -7373,7 +7373,7 @@
       </x:c>
       <x:c r="H9" s="24" t="n">
         <x:f>IFERROR(F9/F8-1,"")</x:f>
-        <x:v>-0.02462622019028804</x:v>
+        <x:v>-0.024626704753321182</x:v>
       </x:c>
       <x:c r="I9" s="26" t="n">
         <x:f>ROUND(D9-E9,1)</x:f>
@@ -7394,16 +7394,16 @@
         <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C10" s="23" t="n">
-        <x:v>8177.291</x:v>
+        <x:v>8177.29</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
-        <x:v>8337.371</x:v>
+        <x:v>8337.37</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
-        <x:v>8149.646</x:v>
+        <x:v>8149.65</x:v>
       </x:c>
       <x:c r="F10" s="23" t="n">
-        <x:v>8204.829</x:v>
+        <x:v>8204.83</x:v>
       </x:c>
       <x:c r="G10" s="28" t="n">
         <x:f>ROUND(F10-F9,1)</x:f>
@@ -7411,7 +7411,7 @@
       </x:c>
       <x:c r="H10" s="24" t="n">
         <x:f>IFERROR(F10/F9-1,"")</x:f>
-        <x:v>0.01903416648719869</x:v>
+        <x:v>0.01903479694022403</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
         <x:f>ROUND(D10-E10,1)</x:f>
@@ -7432,16 +7432,16 @@
         <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C11" s="23" t="n">
-        <x:v>8319.691</x:v>
+        <x:v>8319.69</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
-        <x:v>8561.295</x:v>
+        <x:v>8561.3</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
-        <x:v>8236.707</x:v>
+        <x:v>8236.71</x:v>
       </x:c>
       <x:c r="F11" s="23" t="n">
-        <x:v>8560.843</x:v>
+        <x:v>8560.84</x:v>
       </x:c>
       <x:c r="G11" s="28" t="n">
         <x:f>ROUND(F11-F10,1)</x:f>
@@ -7449,7 +7449,7 @@
       </x:c>
       <x:c r="H11" s="24" t="n">
         <x:f>IFERROR(F11/F10-1,"")</x:f>
-        <x:v>0.04339078852222289</x:v>
+        <x:v>0.0433902957160599</x:v>
       </x:c>
       <x:c r="I11" s="26" t="n">
         <x:f>ROUND(D11-E11,1)</x:f>
@@ -7470,16 +7470,16 @@
         <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C12" s="23" t="n">
-        <x:v>8464.273</x:v>
+        <x:v>8464.27</x:v>
       </x:c>
       <x:c r="D12" s="23" t="n">
-        <x:v>8535.807</x:v>
+        <x:v>8535.81</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
-        <x:v>8039.593</x:v>
+        <x:v>8039.59</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
-        <x:v>8248.857</x:v>
+        <x:v>8248.86</x:v>
       </x:c>
       <x:c r="G12" s="28" t="n">
         <x:f>ROUND(F12-F11,1)</x:f>
@@ -7487,7 +7487,7 @@
       </x:c>
       <x:c r="H12" s="24" t="n">
         <x:f>IFERROR(F12/F11-1,"")</x:f>
-        <x:v>-0.03644337362570493</x:v>
+        <x:v>-0.036442685530859054</x:v>
       </x:c>
       <x:c r="I12" s="26" t="n">
         <x:f>ROUND(D12-E12,1)</x:f>
@@ -7508,16 +7508,16 @@
         <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C13" s="23" t="n">
-        <x:v>8131.742</x:v>
+        <x:v>8131.74</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
-        <x:v>8394.122</x:v>
+        <x:v>8394.12</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
-        <x:v>7983.569</x:v>
+        <x:v>7983.57</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
-        <x:v>8214.293</x:v>
+        <x:v>8214.29</x:v>
       </x:c>
       <x:c r="G13" s="23" t="n">
         <x:f>ROUND(F13-F12,1)</x:f>
@@ -7525,7 +7525,7 @@
       </x:c>
       <x:c r="H13" s="24" t="n">
         <x:f>IFERROR(F13/F12-1,"")</x:f>
-        <x:v>-0.004190156284682889</x:v>
+        <x:v>-0.004190882134016083</x:v>
       </x:c>
       <x:c r="I13" s="26" t="n">
         <x:f>ROUND(D13-E13,1)</x:f>
@@ -7546,16 +7546,16 @@
         <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C14" s="23" t="n">
-        <x:v>8212.267</x:v>
+        <x:v>8212.27</x:v>
       </x:c>
       <x:c r="D14" s="23" t="n">
-        <x:v>8226.032</x:v>
+        <x:v>8226.03</x:v>
       </x:c>
       <x:c r="E14" s="23" t="n">
-        <x:v>7781.579</x:v>
+        <x:v>7781.58</x:v>
       </x:c>
       <x:c r="F14" s="23" t="n">
-        <x:v>7783.435</x:v>
+        <x:v>7783.43</x:v>
       </x:c>
       <x:c r="G14" s="28" t="n">
         <x:f>ROUND(F14-F13,1)</x:f>
@@ -7563,7 +7563,7 @@
       </x:c>
       <x:c r="H14" s="24" t="n">
         <x:f>IFERROR(F14/F13-1,"")</x:f>
-        <x:v>-0.052452231738020494</x:v>
+        <x:v>-0.05245249437261168</x:v>
       </x:c>
       <x:c r="I14" s="26" t="n">
         <x:f>ROUND(D14-E14,1)</x:f>
@@ -7584,16 +7584,16 @@
         <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C15" s="23" t="n">
-        <x:v>7632.972</x:v>
+        <x:v>7632.97</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>7784.547</x:v>
+        <x:v>7784.55</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
-        <x:v>7357.696</x:v>
+        <x:v>7357.7</x:v>
       </x:c>
       <x:c r="F15" s="23" t="n">
-        <x:v>7746.313</x:v>
+        <x:v>7746.31</x:v>
       </x:c>
       <x:c r="G15" s="23" t="n">
         <x:f>ROUND(F15-F14,1)</x:f>
@@ -7601,7 +7601,7 @@
       </x:c>
       <x:c r="H15" s="24" t="n">
         <x:f>IFERROR(F15/F14-1,"")</x:f>
-        <x:v>-0.0047693595436976155</x:v>
+        <x:v>-0.004769105651364458</x:v>
       </x:c>
       <x:c r="I15" s="26" t="n">
         <x:f>ROUND(D15-E15,1)</x:f>
@@ -7622,13 +7622,13 @@
         <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C16" s="23" t="n">
-        <x:v>7664.636</x:v>
+        <x:v>7664.64</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
-        <x:v>7789.239</x:v>
+        <x:v>7789.24</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
-        <x:v>7521.944</x:v>
+        <x:v>7521.94</x:v>
       </x:c>
       <x:c r="F16" s="23" t="n">
         <x:v>7536.6</x:v>
@@ -7639,7 +7639,7 @@
       </x:c>
       <x:c r="H16" s="24" t="n">
         <x:f>IFERROR(F16/F15-1,"")</x:f>
-        <x:v>-0.027072621516842865</x:v>
+        <x:v>-0.027072244720389493</x:v>
       </x:c>
       <x:c r="I16" s="26" t="n">
         <x:f>ROUND(D16-E16,1)</x:f>
@@ -7660,16 +7660,16 @@
         <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C17" s="23" t="n">
-        <x:v>7556.277</x:v>
+        <x:v>7556.28</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>8059.755</x:v>
+        <x:v>8059.76</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
-        <x:v>7554.408</x:v>
+        <x:v>7554.41</x:v>
       </x:c>
       <x:c r="F17" s="23" t="n">
-        <x:v>7998.232</x:v>
+        <x:v>7998.23</x:v>
       </x:c>
       <x:c r="G17" s="28" t="n">
         <x:f>ROUND(F17-F16,1)</x:f>
@@ -7677,11 +7677,11 @@
       </x:c>
       <x:c r="H17" s="24" t="n">
         <x:f>IFERROR(F17/F16-1,"")</x:f>
-        <x:v>0.061252023458854055</x:v>
+        <x:v>0.06125175808720096</x:v>
       </x:c>
       <x:c r="I17" s="26" t="n">
         <x:f>ROUND(D17-E17,1)</x:f>
-        <x:v>505.3</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J17" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -7698,16 +7698,16 @@
         <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C18" s="23" t="n">
-        <x:v>7947.222</x:v>
+        <x:v>7947.22</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
-        <x:v>8333.222</x:v>
+        <x:v>8333.22</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
-        <x:v>7947.222</x:v>
+        <x:v>7947.22</x:v>
       </x:c>
       <x:c r="F18" s="23" t="n">
-        <x:v>8307.436</x:v>
+        <x:v>8307.44</x:v>
       </x:c>
       <x:c r="G18" s="28" t="n">
         <x:f>ROUND(F18-F17,1)</x:f>
@@ -7715,7 +7715,7 @@
       </x:c>
       <x:c r="H18" s="24" t="n">
         <x:f>IFERROR(F18/F17-1,"")</x:f>
-        <x:v>0.03865904364864625</x:v>
+        <x:v>0.03865980348152043</x:v>
       </x:c>
       <x:c r="I18" s="26" t="n">
         <x:f>ROUND(D18-E18,1)</x:f>
@@ -7736,16 +7736,16 @@
         <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C19" s="23" t="n">
-        <x:v>8308.055</x:v>
+        <x:v>8308.06</x:v>
       </x:c>
       <x:c r="D19" s="23" t="n">
-        <x:v>8500.438</x:v>
+        <x:v>8500.44</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
-        <x:v>8254.431</x:v>
+        <x:v>8254.43</x:v>
       </x:c>
       <x:c r="F19" s="23" t="n">
-        <x:v>8304.141</x:v>
+        <x:v>8304.14</x:v>
       </x:c>
       <x:c r="G19" s="23" t="n">
         <x:f>ROUND(F19-F18,1)</x:f>
@@ -7753,7 +7753,7 @@
       </x:c>
       <x:c r="H19" s="24" t="n">
         <x:f>IFERROR(F19/F18-1,"")</x:f>
-        <x:v>-0.00039663260722078153</x:v>
+        <x:v>-0.0003972342863747258</x:v>
       </x:c>
       <x:c r="I19" s="26" t="n">
         <x:f>ROUND(D19-E19,1)</x:f>
@@ -7774,16 +7774,16 @@
         <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C20" s="23" t="n">
-        <x:v>8292.811</x:v>
+        <x:v>8292.81</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
-        <x:v>8402.356</x:v>
+        <x:v>8402.36</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
-        <x:v>8163.348</x:v>
+        <x:v>8163.35</x:v>
       </x:c>
       <x:c r="F20" s="23" t="n">
-        <x:v>8381.947</x:v>
+        <x:v>8381.95</x:v>
       </x:c>
       <x:c r="G20" s="23" t="n">
         <x:f>ROUND(F20-F19,1)</x:f>
@@ -7791,7 +7791,7 @@
       </x:c>
       <x:c r="H20" s="24" t="n">
         <x:f>IFERROR(F20/F19-1,"")</x:f>
-        <x:v>0.009369542256086438</x:v>
+        <x:v>0.009370025071831822</x:v>
       </x:c>
       <x:c r="I20" s="26" t="n">
         <x:f>ROUND(D20-E20,1)</x:f>
@@ -7812,16 +7812,16 @@
         <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C21" s="23" t="n">
-        <x:v>8462.023</x:v>
+        <x:v>8462.02</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:v>8760.194</x:v>
+        <x:v>8760.19</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
-        <x:v>8462.023</x:v>
+        <x:v>8462.02</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
-        <x:v>8741.151</x:v>
+        <x:v>8741.15</x:v>
       </x:c>
       <x:c r="G21" s="28" t="n">
         <x:f>ROUND(F21-F20,1)</x:f>
@@ -7829,7 +7829,7 @@
       </x:c>
       <x:c r="H21" s="24" t="n">
         <x:f>IFERROR(F21/F20-1,"")</x:f>
-        <x:v>0.04285448237742373</x:v>
+        <x:v>0.04285398982337041</x:v>
       </x:c>
       <x:c r="I21" s="26" t="n">
         <x:f>ROUND(D21-E21,1)</x:f>
@@ -7850,7 +7850,7 @@
         <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C22" s="23" t="n">
-        <x:v>8807.905</x:v>
+        <x:v>8807.91</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
         <x:v>8991.85</x:v>
@@ -7859,7 +7859,7 @@
         <x:v>8616.06</x:v>
       </x:c>
       <x:c r="F22" s="23" t="n">
-        <x:v>8682.654</x:v>
+        <x:v>8682.65</x:v>
       </x:c>
       <x:c r="G22" s="23" t="n">
         <x:f>ROUND(F22-F21,1)</x:f>
@@ -7867,7 +7867,7 @@
       </x:c>
       <x:c r="H22" s="24" t="n">
         <x:f>IFERROR(F22/F21-1,"")</x:f>
-        <x:v>-0.0066921392846318595</x:v>
+        <x:v>-0.006692483254491677</x:v>
       </x:c>
       <x:c r="I22" s="26" t="n">
         <x:f>ROUND(D22-E22,1)</x:f>
@@ -7888,7 +7888,7 @@
         <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C23" s="23" t="n">
-        <x:v>8645.763</x:v>
+        <x:v>8645.76</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
         <x:v>8896.6</x:v>
@@ -7897,7 +7897,7 @@
         <x:v>8500.92</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
-        <x:v>8692.666</x:v>
+        <x:v>8692.67</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
         <x:f>ROUND(F23-F22,1)</x:f>
@@ -7905,7 +7905,7 @@
       </x:c>
       <x:c r="H23" s="24" t="n">
         <x:f>IFERROR(F23/F22-1,"")</x:f>
-        <x:v>0.0011531036478016343</x:v>
+        <x:v>0.0011540255567137336</x:v>
       </x:c>
       <x:c r="I23" s="26" t="n">
         <x:f>ROUND(D23-E23,1)</x:f>
@@ -7926,16 +7926,16 @@
         <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C24" s="23" t="n">
-        <x:v>8756.458</x:v>
+        <x:v>8756.46</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
-        <x:v>8802.946</x:v>
+        <x:v>8802.95</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
-        <x:v>8357.801</x:v>
+        <x:v>8357.8</x:v>
       </x:c>
       <x:c r="F24" s="23" t="n">
-        <x:v>8408.736</x:v>
+        <x:v>8408.74</x:v>
       </x:c>
       <x:c r="G24" s="28" t="n">
         <x:f>ROUND(F24-F23,1)</x:f>
@@ -7943,11 +7943,11 @@
       </x:c>
       <x:c r="H24" s="24" t="n">
         <x:f>IFERROR(F24/F23-1,"")</x:f>
-        <x:v>-0.03266316685813053</x:v>
+        <x:v>-0.03266315182791946</x:v>
       </x:c>
       <x:c r="I24" s="26" t="n">
         <x:f>ROUND(D24-E24,1)</x:f>
-        <x:v>445.1</x:v>
+        <x:v>445.2</x:v>
       </x:c>
       <x:c r="J24" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -7964,16 +7964,16 @@
         <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C25" s="23" t="n">
-        <x:v>8393.518</x:v>
+        <x:v>8393.52</x:v>
       </x:c>
       <x:c r="D25" s="23" t="n">
-        <x:v>8549.249</x:v>
+        <x:v>8549.25</x:v>
       </x:c>
       <x:c r="E25" s="23" t="n">
-        <x:v>8219.153</x:v>
+        <x:v>8219.15</x:v>
       </x:c>
       <x:c r="F25" s="23" t="n">
-        <x:v>8340.963</x:v>
+        <x:v>8340.96</x:v>
       </x:c>
       <x:c r="G25" s="23" t="n">
         <x:f>ROUND(F25-F24,1)</x:f>
@@ -7981,7 +7981,7 @@
       </x:c>
       <x:c r="H25" s="24" t="n">
         <x:f>IFERROR(F25/F24-1,"")</x:f>
-        <x:v>-0.008059832060371641</x:v>
+        <x:v>-0.00806066069351663</x:v>
       </x:c>
       <x:c r="I25" s="26" t="n">
         <x:f>ROUND(D25-E25,1)</x:f>
@@ -8002,16 +8002,16 @@
         <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C26" s="23" t="n">
-        <x:v>8069.482</x:v>
+        <x:v>8069.48</x:v>
       </x:c>
       <x:c r="D26" s="23" t="n">
-        <x:v>8348.786</x:v>
+        <x:v>8348.79</x:v>
       </x:c>
       <x:c r="E26" s="23" t="n">
-        <x:v>7987.396</x:v>
+        <x:v>7987.4</x:v>
       </x:c>
       <x:c r="F26" s="23" t="n">
-        <x:v>8202.799</x:v>
+        <x:v>8202.8</x:v>
       </x:c>
       <x:c r="G26" s="23" t="n">
         <x:f>ROUND(F26-F25,1)</x:f>
@@ -8019,7 +8019,7 @@
       </x:c>
       <x:c r="H26" s="24" t="n">
         <x:f>IFERROR(F26/F25-1,"")</x:f>
-        <x:v>-0.016564514193385005</x:v>
+        <x:v>-0.01656404059005201</x:v>
       </x:c>
       <x:c r="I26" s="26" t="n">
         <x:f>ROUND(D26-E26,1)</x:f>
@@ -8040,16 +8040,16 @@
         <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C27" s="23" t="n">
-        <x:v>8269.397</x:v>
+        <x:v>8269.4</x:v>
       </x:c>
       <x:c r="D27" s="23" t="n">
-        <x:v>8796.485</x:v>
+        <x:v>8796.48</x:v>
       </x:c>
       <x:c r="E27" s="23" t="n">
-        <x:v>8269.397</x:v>
+        <x:v>8269.4</x:v>
       </x:c>
       <x:c r="F27" s="23" t="n">
-        <x:v>8771.024</x:v>
+        <x:v>8771.02</x:v>
       </x:c>
       <x:c r="G27" s="28" t="n">
         <x:f>ROUND(F27-F26,1)</x:f>
@@ -8057,7 +8057,7 @@
       </x:c>
       <x:c r="H27" s="24" t="n">
         <x:f>IFERROR(F27/F26-1,"")</x:f>
-        <x:v>0.06927208627201509</x:v>
+        <x:v>0.06927146827912445</x:v>
       </x:c>
       <x:c r="I27" s="26" t="n">
         <x:f>ROUND(D27-E27,1)</x:f>
@@ -8078,16 +8078,16 @@
         <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C28" s="23" t="n">
-        <x:v>8813.725</x:v>
+        <x:v>8813.72</x:v>
       </x:c>
       <x:c r="D28" s="23" t="n">
-        <x:v>8872.123</x:v>
+        <x:v>8872.12</x:v>
       </x:c>
       <x:c r="E28" s="23" t="n">
-        <x:v>8563.695</x:v>
+        <x:v>8563.7</x:v>
       </x:c>
       <x:c r="F28" s="23" t="n">
-        <x:v>8601.408</x:v>
+        <x:v>8601.41</x:v>
       </x:c>
       <x:c r="G28" s="28" t="n">
         <x:f>ROUND(F28-F27,1)</x:f>
@@ -8095,7 +8095,7 @@
       </x:c>
       <x:c r="H28" s="24" t="n">
         <x:f>IFERROR(F28/F27-1,"")</x:f>
-        <x:v>-0.0193382209420474</x:v>
+        <x:v>-0.019337545690239044</x:v>
       </x:c>
       <x:c r="I28" s="26" t="n">
         <x:f>ROUND(D28-E28,1)</x:f>
@@ -8116,16 +8116,16 @@
         <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C29" s="23" t="n">
-        <x:v>8616.424</x:v>
+        <x:v>8616.42</x:v>
       </x:c>
       <x:c r="D29" s="23" t="n">
-        <x:v>8944.195</x:v>
+        <x:v>8944.19</x:v>
       </x:c>
       <x:c r="E29" s="23" t="n">
-        <x:v>8413.864</x:v>
+        <x:v>8413.86</x:v>
       </x:c>
       <x:c r="F29" s="23" t="n">
-        <x:v>8620.789</x:v>
+        <x:v>8620.79</x:v>
       </x:c>
       <x:c r="G29" s="23" t="n">
         <x:f>ROUND(F29-F28,1)</x:f>
@@ -8133,7 +8133,7 @@
       </x:c>
       <x:c r="H29" s="24" t="n">
         <x:f>IFERROR(F29/F28-1,"")</x:f>
-        <x:v>0.002253235749309912</x:v>
+        <x:v>0.002253118965378942</x:v>
       </x:c>
       <x:c r="I29" s="26" t="n">
         <x:f>ROUND(D29-E29,1)</x:f>
@@ -8154,16 +8154,16 @@
         <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C30" s="23" t="n">
-        <x:v>8669.123</x:v>
+        <x:v>8669.12</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
-        <x:v>8694.805</x:v>
+        <x:v>8694.8</x:v>
       </x:c>
       <x:c r="E30" s="23" t="n">
-        <x:v>7978.806</x:v>
+        <x:v>7978.81</x:v>
       </x:c>
       <x:c r="F30" s="23" t="n">
-        <x:v>8198.308</x:v>
+        <x:v>8198.31</x:v>
       </x:c>
       <x:c r="G30" s="28" t="n">
         <x:f>ROUND(F30-F29,1)</x:f>
@@ -8171,7 +8171,7 @@
       </x:c>
       <x:c r="H30" s="24" t="n">
         <x:f>IFERROR(F30/F29-1,"")</x:f>
-        <x:v>-0.04900723124066719</x:v>
+        <x:v>-0.049007109557244855</x:v>
       </x:c>
       <x:c r="I30" s="26" t="n">
         <x:f>ROUND(D30-E30,1)</x:f>
@@ -8192,16 +8192,16 @@
         <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C31" s="23" t="n">
-        <x:v>8124.363</x:v>
+        <x:v>8124.36</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
-        <x:v>8171.504</x:v>
+        <x:v>8171.5</x:v>
       </x:c>
       <x:c r="E31" s="23" t="n">
-        <x:v>7163.309</x:v>
+        <x:v>7163.31</x:v>
       </x:c>
       <x:c r="F31" s="23" t="n">
-        <x:v>7167.996</x:v>
+        <x:v>7168</x:v>
       </x:c>
       <x:c r="G31" s="28" t="n">
         <x:f>ROUND(F31-F30,1)</x:f>
@@ -8209,7 +8209,7 @@
       </x:c>
       <x:c r="H31" s="24" t="n">
         <x:f>IFERROR(F31/F30-1,"")</x:f>
-        <x:v>-0.12567373658076775</x:v>
+        <x:v>-0.12567346196960105</x:v>
       </x:c>
       <x:c r="I31" s="26" t="n">
         <x:f>ROUND(D31-E31,1)</x:f>
@@ -8230,16 +8230,16 @@
         <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C32" s="23" t="n">
-        <x:v>7256.267</x:v>
+        <x:v>7256.27</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
-        <x:v>7302.454</x:v>
+        <x:v>7302.45</x:v>
       </x:c>
       <x:c r="E32" s="23" t="n">
-        <x:v>6714.187</x:v>
+        <x:v>6714.19</x:v>
       </x:c>
       <x:c r="F32" s="23" t="n">
-        <x:v>6995.693</x:v>
+        <x:v>6995.69</x:v>
       </x:c>
       <x:c r="G32" s="28" t="n">
         <x:f>ROUND(F32-F31,1)</x:f>
@@ -8247,7 +8247,7 @@
       </x:c>
       <x:c r="H32" s="24" t="n">
         <x:f>IFERROR(F32/F31-1,"")</x:f>
-        <x:v>-0.02403782033360513</x:v>
+        <x:v>-0.024038783482142945</x:v>
       </x:c>
       <x:c r="I32" s="26" t="n">
         <x:f>ROUND(D32-E32,1)</x:f>
@@ -8268,16 +8268,16 @@
         <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C33" s="23" t="n">
-        <x:v>6981.165</x:v>
+        <x:v>6981.16</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
-        <x:v>7228.785</x:v>
+        <x:v>7228.78</x:v>
       </x:c>
       <x:c r="E33" s="23" t="n">
-        <x:v>6841.751</x:v>
+        <x:v>6841.75</x:v>
       </x:c>
       <x:c r="F33" s="23" t="n">
-        <x:v>7075.507</x:v>
+        <x:v>7075.51</x:v>
       </x:c>
       <x:c r="G33" s="23" t="n">
         <x:f>ROUND(F33-F32,1)</x:f>
@@ -8285,7 +8285,7 @@
       </x:c>
       <x:c r="H33" s="24" t="n">
         <x:f>IFERROR(F33/F32-1,"")</x:f>
-        <x:v>0.01140901980690101</x:v>
+        <x:v>0.011409882370430946</x:v>
       </x:c>
       <x:c r="I33" s="26" t="n">
         <x:f>ROUND(D33-E33,1)</x:f>
@@ -8306,16 +8306,16 @@
         <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C34" s="23" t="n">
-        <x:v>7055.271</x:v>
+        <x:v>7055.27</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
         <x:v>7685.57</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
-        <x:v>7042.889</x:v>
+        <x:v>7042.89</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>7679.529</x:v>
+        <x:v>7679.53</x:v>
       </x:c>
       <x:c r="G34" s="28" t="n">
         <x:f>ROUND(F34-F33,1)</x:f>
@@ -8323,7 +8323,7 @@
       </x:c>
       <x:c r="H34" s="24" t="n">
         <x:f>IFERROR(F34/F33-1,"")</x:f>
-        <x:v>0.08536801673717531</x:v>
+        <x:v>0.08536769787619547</x:v>
       </x:c>
       <x:c r="I34" s="26" t="n">
         <x:f>ROUND(D34-E34,1)</x:f>
@@ -8347,7 +8347,7 @@
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>7880.217</x:v>
+        <x:v>7880.22</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
         <x:v>7621.65</x:v>
@@ -8361,7 +8361,7 @@
       </x:c>
       <x:c r="H35" s="24" t="n">
         <x:f>IFERROR(F35/F34-1,"")</x:f>
-        <x:v>0.011757361681946854</x:v>
+        <x:v>0.011757229934644453</x:v>
       </x:c>
       <x:c r="I35" s="26" t="n">
         <x:f>ROUND(D35-E35,1)</x:f>
@@ -8382,16 +8382,16 @@
         <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
-        <x:v>7797.184</x:v>
+        <x:v>7797.18</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>7995.501</x:v>
+        <x:v>7995.5</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>7490.212</x:v>
+        <x:v>7490.21</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>7589.779</x:v>
+        <x:v>7589.78</x:v>
       </x:c>
       <x:c r="G36" s="28" t="n">
         <x:f>ROUND(F36-F35,1)</x:f>
@@ -8399,7 +8399,7 @@
       </x:c>
       <x:c r="H36" s="24" t="n">
         <x:f>IFERROR(F36/F35-1,"")</x:f>
-        <x:v>-0.02317183667060485</x:v>
+        <x:v>-0.023171707967494792</x:v>
       </x:c>
       <x:c r="I36" s="26" t="n">
         <x:f>ROUND(D36-E36,1)</x:f>
@@ -8427,7 +8427,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="32" t="n">
         <x:f>ROUND(SUM(I5:I36),1)</x:f>
-        <x:v>13475.6</x:v>
+        <x:v>13475.8</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -12273,7 +12273,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B147" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C147" s="23" t="n">
         <x:v>7675</x:v>
@@ -12285,15 +12285,15 @@
         <x:v>7430</x:v>
       </x:c>
       <x:c r="F147" s="23" t="n">
-        <x:v>7468.8</x:v>
-      </x:c>
-      <x:c r="G147" s="28" t="n">
+        <x:v>7516.2</x:v>
+      </x:c>
+      <x:c r="G147" s="23" t="n">
         <x:f>ROUND(F147-F146,1)</x:f>
-        <x:v>-181.4</x:v>
+        <x:v>-134</x:v>
       </x:c>
       <x:c r="H147" s="24" t="n">
         <x:f>IFERROR(F147/F146-1,"")</x:f>
-        <x:v>-0.023711798384355887</x:v>
+        <x:v>-0.01751588193772713</x:v>
       </x:c>
       <x:c r="I147" s="26" t="n">
         <x:f>ROUND(D147-E147,1)</x:f>
@@ -12303,7 +12303,7 @@
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K147" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -16167,7 +16167,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>8月17日-8月19日</x:v>
+        <x:v>8月17日-8月20日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
         <x:v>2886</x:v>
@@ -16179,15 +16179,15 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2865</x:v>
+        <x:v>2858.8</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>-25</x:v>
+        <x:v>-31.2</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>-0.00865051903114189</x:v>
+        <x:v>-0.01079584775086495</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
@@ -16197,7 +16197,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K258" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -17635,13 +17635,13 @@
         <x:v>1月5日</x:v>
       </x:c>
       <x:c r="D5" s="23" t="n">
-        <x:v>7639.538</x:v>
+        <x:v>7639.54</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
-        <x:v>7753.959</x:v>
+        <x:v>7753.96</x:v>
       </x:c>
       <x:c r="F5" s="23" t="n">
-        <x:v>7623.749</x:v>
+        <x:v>7623.75</x:v>
       </x:c>
       <x:c r="G5" s="23" t="n">
         <x:v>7753.88</x:v>
@@ -17650,7 +17650,7 @@
         <x:v>158.6</x:v>
       </x:c>
       <x:c r="I5" s="24" t="n">
-        <x:v>0.020880717445099117</x:v>
+        <x:v>0.020881389494528335</x:v>
       </x:c>
       <x:c r="J5" s="23" t="n">
         <x:f>ROUND(E5-F5,1)</x:f>
@@ -17671,22 +17671,22 @@
         <x:v>1月6日</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
-        <x:v>7756.158</x:v>
+        <x:v>7756.16</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
-        <x:v>7864.903</x:v>
+        <x:v>7864.9</x:v>
       </x:c>
       <x:c r="F6" s="23" t="n">
-        <x:v>7755.072</x:v>
+        <x:v>7755.07</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
-        <x:v>7864.903</x:v>
+        <x:v>7864.9</x:v>
       </x:c>
       <x:c r="H6" s="23" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="I6" s="24" t="n">
-        <x:v>0.01431837995945262</x:v>
+        <x:v>0.014317993056379485</x:v>
       </x:c>
       <x:c r="J6" s="23" t="n">
         <x:f>ROUND(E6-F6,1)</x:f>
@@ -17707,13 +17707,13 @@
         <x:v>1月7日</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
-        <x:v>7881.836</x:v>
+        <x:v>7881.84</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
-        <x:v>7939.752</x:v>
+        <x:v>7939.75</x:v>
       </x:c>
       <x:c r="F7" s="23" t="n">
-        <x:v>7864.139</x:v>
+        <x:v>7864.14</x:v>
       </x:c>
       <x:c r="G7" s="23" t="n">
         <x:v>7906.42</x:v>
@@ -17722,7 +17722,7 @@
         <x:v>41.5</x:v>
       </x:c>
       <x:c r="I7" s="24" t="n">
-        <x:v>0.005278768218756058</x:v>
+        <x:v>0.005279151673892812</x:v>
       </x:c>
       <x:c r="J7" s="23" t="n">
         <x:f>ROUND(E7-F7,1)</x:f>
@@ -17746,19 +17746,19 @@
         <x:v>7886.81</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
-        <x:v>7993.631</x:v>
+        <x:v>7993.63</x:v>
       </x:c>
       <x:c r="F8" s="23" t="n">
-        <x:v>7886.629</x:v>
+        <x:v>7886.63</x:v>
       </x:c>
       <x:c r="G8" s="23" t="n">
-        <x:v>7971.589</x:v>
+        <x:v>7971.59</x:v>
       </x:c>
       <x:c r="H8" s="23" t="n">
         <x:v>65.2</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>0.008242542136643438</x:v>
+        <x:v>0.008242668616137205</x:v>
       </x:c>
       <x:c r="J8" s="23" t="n">
         <x:f>ROUND(E8-F8,1)</x:f>
@@ -17782,19 +17782,19 @@
         <x:v>7969.19</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
-        <x:v>8131.491</x:v>
+        <x:v>8131.49</x:v>
       </x:c>
       <x:c r="F9" s="23" t="n">
         <x:v>7969.19</x:v>
       </x:c>
       <x:c r="G9" s="23" t="n">
-        <x:v>8129.183</x:v>
+        <x:v>8129.18</x:v>
       </x:c>
       <x:c r="H9" s="28" t="n">
         <x:v>157.6</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>0.019769458761609515</x:v>
+        <x:v>0.01976895449966687</x:v>
       </x:c>
       <x:c r="J9" s="23" t="n">
         <x:f>ROUND(E9-F9,1)</x:f>
@@ -17815,22 +17815,22 @@
         <x:v>1月12日</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
-        <x:v>8196.085</x:v>
+        <x:v>8196.08</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
-        <x:v>8371.749</x:v>
+        <x:v>8371.75</x:v>
       </x:c>
       <x:c r="F10" s="23" t="n">
-        <x:v>8171.105</x:v>
+        <x:v>8171.11</x:v>
       </x:c>
       <x:c r="G10" s="23" t="n">
-        <x:v>8357.011</x:v>
+        <x:v>8357.01</x:v>
       </x:c>
       <x:c r="H10" s="28" t="n">
         <x:v>227.8</x:v>
       </x:c>
       <x:c r="I10" s="24" t="n">
-        <x:v>0.028025940614204492</x:v>
+        <x:v>0.028026196984197727</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
         <x:f>ROUND(E10-F10,1)</x:f>
@@ -17851,22 +17851,22 @@
         <x:v>1月13日</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
-        <x:v>8381.042</x:v>
+        <x:v>8381.04</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
-        <x:v>8381.042</x:v>
+        <x:v>8381.04</x:v>
       </x:c>
       <x:c r="F11" s="23" t="n">
-        <x:v>8177.629</x:v>
+        <x:v>8177.63</x:v>
       </x:c>
       <x:c r="G11" s="23" t="n">
-        <x:v>8203.133</x:v>
+        <x:v>8203.13</x:v>
       </x:c>
       <x:c r="H11" s="28" t="n">
         <x:v>-153.9</x:v>
       </x:c>
       <x:c r="I11" s="24" t="n">
-        <x:v>-0.018413042653647405</x:v>
+        <x:v>-0.018413284176996392</x:v>
       </x:c>
       <x:c r="J11" s="26" t="n">
         <x:f>ROUND(E11-F11,1)</x:f>
@@ -17890,19 +17890,19 @@
         <x:v>8204.28</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
-        <x:v>8415.098</x:v>
+        <x:v>8415.1</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
-        <x:v>8154.241</x:v>
+        <x:v>8154.24</x:v>
       </x:c>
       <x:c r="G12" s="23" t="n">
-        <x:v>8257.172</x:v>
+        <x:v>8257.17</x:v>
       </x:c>
       <x:c r="H12" s="23" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="I12" s="24" t="n">
-        <x:v>0.00658760500408806</x:v>
+        <x:v>0.006587729317955482</x:v>
       </x:c>
       <x:c r="J12" s="26" t="n">
         <x:f>ROUND(E12-F12,1)</x:f>
@@ -17923,22 +17923,22 @@
         <x:v>1月15日</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
-        <x:v>8197.061</x:v>
+        <x:v>8197.06</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
-        <x:v>8267.813</x:v>
+        <x:v>8267.81</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
-        <x:v>8151.107</x:v>
+        <x:v>8151.11</x:v>
       </x:c>
       <x:c r="G13" s="23" t="n">
-        <x:v>8240.775</x:v>
+        <x:v>8240.78</x:v>
       </x:c>
       <x:c r="H13" s="23" t="n">
         <x:v>-16.4</x:v>
       </x:c>
       <x:c r="I13" s="24" t="n">
-        <x:v>-0.0019857888390845124</x:v>
+        <x:v>-0.00198494157199125</x:v>
       </x:c>
       <x:c r="J13" s="23" t="n">
         <x:f>ROUND(E13-F13,1)</x:f>
@@ -17959,22 +17959,22 @@
         <x:v>1月16日</x:v>
       </x:c>
       <x:c r="D14" s="42" t="n">
-        <x:v>8276.608</x:v>
+        <x:v>8276.61</x:v>
       </x:c>
       <x:c r="E14" s="42" t="n">
-        <x:v>8304.399</x:v>
+        <x:v>8304.4</x:v>
       </x:c>
       <x:c r="F14" s="42" t="n">
-        <x:v>8180.117</x:v>
+        <x:v>8180.12</x:v>
       </x:c>
       <x:c r="G14" s="42" t="n">
-        <x:v>8232.729</x:v>
+        <x:v>8232.73</x:v>
       </x:c>
       <x:c r="H14" s="42" t="n">
-        <x:v>-8</x:v>
+        <x:v>-8.1</x:v>
       </x:c>
       <x:c r="I14" s="43" t="n">
-        <x:v>-0.0009763644802824878</x:v>
+        <x:v>-0.0009768492788305716</x:v>
       </x:c>
       <x:c r="J14" s="42" t="n">
         <x:f>ROUND(E14-F14,1)</x:f>
@@ -17995,22 +17995,22 @@
         <x:v>1月19日</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>8204.627</x:v>
+        <x:v>8204.63</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
         <x:v>8298.48</x:v>
       </x:c>
       <x:c r="F15" s="23" t="n">
-        <x:v>8187.938</x:v>
+        <x:v>8187.94</x:v>
       </x:c>
       <x:c r="G15" s="23" t="n">
-        <x:v>8265.646</x:v>
+        <x:v>8265.65</x:v>
       </x:c>
       <x:c r="H15" s="23" t="n">
         <x:v>32.9</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
-        <x:v>0.003998309673499678</x:v>
+        <x:v>0.003998673587011892</x:v>
       </x:c>
       <x:c r="J15" s="23" t="n">
         <x:f>ROUND(E15-F15,1)</x:f>
@@ -18031,22 +18031,22 @@
         <x:v>1月20日</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
-        <x:v>8271.779</x:v>
+        <x:v>8271.78</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
         <x:v>8300.05</x:v>
       </x:c>
       <x:c r="F16" s="23" t="n">
-        <x:v>8104.918</x:v>
+        <x:v>8104.92</x:v>
       </x:c>
       <x:c r="G16" s="23" t="n">
-        <x:v>8182.752</x:v>
+        <x:v>8182.75</x:v>
       </x:c>
       <x:c r="H16" s="23" t="n">
         <x:v>-82.9</x:v>
       </x:c>
       <x:c r="I16" s="24" t="n">
-        <x:v>-0.010028738225663192</x:v>
+        <x:v>-0.01002945926817611</x:v>
       </x:c>
       <x:c r="J16" s="26" t="n">
         <x:f>ROUND(E16-F16,1)</x:f>
@@ -18067,13 +18067,13 @@
         <x:v>1月21日</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>8138.682</x:v>
+        <x:v>8138.68</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
-        <x:v>8289.134</x:v>
+        <x:v>8289.13</x:v>
       </x:c>
       <x:c r="F17" s="23" t="n">
-        <x:v>8136.918</x:v>
+        <x:v>8136.92</x:v>
       </x:c>
       <x:c r="G17" s="23" t="n">
         <x:v>8247.68</x:v>
@@ -18082,7 +18082,7 @@
         <x:v>64.9</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>0.007934738826252952</x:v>
+        <x:v>0.007934985182243226</x:v>
       </x:c>
       <x:c r="J17" s="23" t="n">
         <x:f>ROUND(E17-F17,1)</x:f>
@@ -18103,22 +18103,22 @@
         <x:v>1月22日</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
-        <x:v>8272.468</x:v>
+        <x:v>8272.47</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
-        <x:v>8314.216</x:v>
+        <x:v>8314.22</x:v>
       </x:c>
       <x:c r="F18" s="23" t="n">
-        <x:v>8252.745</x:v>
+        <x:v>8252.74</x:v>
       </x:c>
       <x:c r="G18" s="23" t="n">
-        <x:v>8309.346</x:v>
+        <x:v>8309.35</x:v>
       </x:c>
       <x:c r="H18" s="23" t="n">
         <x:v>61.7</x:v>
       </x:c>
       <x:c r="I18" s="24" t="n">
-        <x:v>0.007476769224800117</x:v>
+        <x:v>0.0074772542096686045</x:v>
       </x:c>
       <x:c r="J18" s="23" t="n">
         <x:f>ROUND(E18-F18,1)</x:f>
@@ -18142,19 +18142,19 @@
         <x:v>8331.77</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
-        <x:v>8478.556</x:v>
+        <x:v>8478.56</x:v>
       </x:c>
       <x:c r="F19" s="23" t="n">
-        <x:v>8323.349</x:v>
+        <x:v>8323.35</x:v>
       </x:c>
       <x:c r="G19" s="23" t="n">
-        <x:v>8470.744</x:v>
+        <x:v>8470.74</x:v>
       </x:c>
       <x:c r="H19" s="28" t="n">
         <x:v>161.4</x:v>
       </x:c>
       <x:c r="I19" s="24" t="n">
-        <x:v>0.019423670647485514</x:v>
+        <x:v>0.019422698526358806</x:v>
       </x:c>
       <x:c r="J19" s="23" t="n">
         <x:f>ROUND(E19-F19,1)</x:f>
@@ -18175,22 +18175,22 @@
         <x:v>1月26日</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
-        <x:v>8513.222</x:v>
+        <x:v>8513.22</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
-        <x:v>8530.417</x:v>
+        <x:v>8530.42</x:v>
       </x:c>
       <x:c r="F20" s="23" t="n">
-        <x:v>8302.099</x:v>
+        <x:v>8302.1</x:v>
       </x:c>
       <x:c r="G20" s="23" t="n">
-        <x:v>8365.435</x:v>
+        <x:v>8365.43</x:v>
       </x:c>
       <x:c r="H20" s="23" t="n">
         <x:v>-105.3</x:v>
       </x:c>
       <x:c r="I20" s="24" t="n">
-        <x:v>-0.012432083887790824</x:v>
+        <x:v>-0.012432207811832185</x:v>
       </x:c>
       <x:c r="J20" s="26" t="n">
         <x:f>ROUND(E20-F20,1)</x:f>
@@ -18211,22 +18211,22 @@
         <x:v>1月27日</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:v>8325.433</x:v>
+        <x:v>8325.43</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
-        <x:v>8406.099</x:v>
+        <x:v>8406.1</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
-        <x:v>8186.244</x:v>
+        <x:v>8186.24</x:v>
       </x:c>
       <x:c r="G21" s="23" t="n">
-        <x:v>8382.153</x:v>
+        <x:v>8382.15</x:v>
       </x:c>
       <x:c r="H21" s="23" t="n">
         <x:v>16.7</x:v>
       </x:c>
       <x:c r="I21" s="24" t="n">
-        <x:v>0.001998461526507622</x:v>
+        <x:v>0.001998701800146385</x:v>
       </x:c>
       <x:c r="J21" s="26" t="n">
         <x:f>ROUND(E21-F21,1)</x:f>
@@ -18247,22 +18247,22 @@
         <x:v>1月28日</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
-        <x:v>8392.753</x:v>
+        <x:v>8392.75</x:v>
       </x:c>
       <x:c r="E22" s="23" t="n">
         <x:v>8432.62</x:v>
       </x:c>
       <x:c r="F22" s="23" t="n">
-        <x:v>8334.683</x:v>
+        <x:v>8334.68</x:v>
       </x:c>
       <x:c r="G22" s="23" t="n">
-        <x:v>8399.794</x:v>
+        <x:v>8399.79</x:v>
       </x:c>
       <x:c r="H22" s="23" t="n">
         <x:v>17.6</x:v>
       </x:c>
       <x:c r="I22" s="24" t="n">
-        <x:v>0.002104590550900287</x:v>
+        <x:v>0.0021044720030065633</x:v>
       </x:c>
       <x:c r="J22" s="23" t="n">
         <x:f>ROUND(E22-F22,1)</x:f>
@@ -18283,22 +18283,22 @@
         <x:v>1月29日</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
-        <x:v>8380.605</x:v>
+        <x:v>8380.61</x:v>
       </x:c>
       <x:c r="E23" s="23" t="n">
-        <x:v>8463.125</x:v>
+        <x:v>8463.12</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
-        <x:v>8308.825</x:v>
+        <x:v>8308.82</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
-        <x:v>8332.207</x:v>
+        <x:v>8332.21</x:v>
       </x:c>
       <x:c r="H23" s="23" t="n">
         <x:v>-67.6</x:v>
       </x:c>
       <x:c r="I23" s="24" t="n">
-        <x:v>-0.00804626875373371</x:v>
+        <x:v>-0.008045439231219031</x:v>
       </x:c>
       <x:c r="J23" s="23" t="n">
         <x:f>ROUND(E23-F23,1)</x:f>
@@ -18319,10 +18319,10 @@
         <x:v>1月30日</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
-        <x:v>8255.335</x:v>
+        <x:v>8255.33</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
-        <x:v>8313.227</x:v>
+        <x:v>8313.23</x:v>
       </x:c>
       <x:c r="F24" s="23" t="n">
         <x:v>8083.97</x:v>
@@ -18334,7 +18334,7 @@
         <x:v>-77.3</x:v>
       </x:c>
       <x:c r="I24" s="24" t="n">
-        <x:v>-0.009282894676044373</x:v>
+        <x:v>-0.00928325138228614</x:v>
       </x:c>
       <x:c r="J24" s="26" t="n">
         <x:f>ROUND(E24-F24,1)</x:f>
@@ -18443,22 +18443,22 @@
         <x:v>2月2日</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
-        <x:v>8166.736</x:v>
+        <x:v>8166.74</x:v>
       </x:c>
       <x:c r="E30" s="23" t="n">
-        <x:v>8221.582</x:v>
+        <x:v>8221.58</x:v>
       </x:c>
       <x:c r="F30" s="23" t="n">
-        <x:v>7974.599</x:v>
+        <x:v>7974.6</x:v>
       </x:c>
       <x:c r="G30" s="23" t="n">
-        <x:v>7975.428</x:v>
+        <x:v>7975.43</x:v>
       </x:c>
       <x:c r="H30" s="28" t="n">
         <x:v>-279.4</x:v>
       </x:c>
       <x:c r="I30" s="24" t="n">
-        <x:v>-0.03385060437124321</x:v>
+        <x:v>-0.03385036208972658</x:v>
       </x:c>
       <x:c r="J30" s="26" t="n">
         <x:f>ROUND(E30-F30,1)</x:f>
@@ -18479,22 +18479,22 @@
         <x:v>2月3日</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
-        <x:v>8058.763</x:v>
+        <x:v>8058.76</x:v>
       </x:c>
       <x:c r="E31" s="23" t="n">
-        <x:v>8210.047</x:v>
+        <x:v>8210.05</x:v>
       </x:c>
       <x:c r="F31" s="23" t="n">
-        <x:v>8023.238</x:v>
+        <x:v>8023.24</x:v>
       </x:c>
       <x:c r="G31" s="23" t="n">
-        <x:v>8209.101</x:v>
+        <x:v>8209.1</x:v>
       </x:c>
       <x:c r="H31" s="28" t="n">
         <x:v>233.7</x:v>
       </x:c>
       <x:c r="I31" s="24" t="n">
-        <x:v>0.02929911723859835</x:v>
+        <x:v>0.029298733735986682</x:v>
       </x:c>
       <x:c r="J31" s="26" t="n">
         <x:f>ROUND(E31-F31,1)</x:f>
@@ -18515,10 +18515,10 @@
         <x:v>2月4日</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
-        <x:v>8184.205</x:v>
+        <x:v>8184.2</x:v>
       </x:c>
       <x:c r="E32" s="23" t="n">
-        <x:v>8216.204</x:v>
+        <x:v>8216.2</x:v>
       </x:c>
       <x:c r="F32" s="23" t="n">
         <x:v>8101.2</x:v>
@@ -18530,7 +18530,7 @@
         <x:v>-2</x:v>
       </x:c>
       <x:c r="I32" s="24" t="n">
-        <x:v>-0.00024131753282119472</x:v>
+        <x:v>-0.00024119574618408635</x:v>
       </x:c>
       <x:c r="J32" s="23" t="n">
         <x:f>ROUND(E32-F32,1)</x:f>
@@ -18551,22 +18551,22 @@
         <x:v>2月5日</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
-        <x:v>8121.511</x:v>
+        <x:v>8121.51</x:v>
       </x:c>
       <x:c r="E33" s="23" t="n">
-        <x:v>8154.558</x:v>
+        <x:v>8154.56</x:v>
       </x:c>
       <x:c r="F33" s="23" t="n">
-        <x:v>8027.623</x:v>
+        <x:v>8027.62</x:v>
       </x:c>
       <x:c r="G33" s="23" t="n">
-        <x:v>8068.077</x:v>
+        <x:v>8068.08</x:v>
       </x:c>
       <x:c r="H33" s="23" t="n">
         <x:v>-139</x:v>
       </x:c>
       <x:c r="I33" s="24" t="n">
-        <x:v>-0.016941753014455774</x:v>
+        <x:v>-0.01694138747818974</x:v>
       </x:c>
       <x:c r="J33" s="23" t="n">
         <x:f>ROUND(E33-F33,1)</x:f>
@@ -18587,22 +18587,22 @@
         <x:v>2月6日</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>7980.466</x:v>
+        <x:v>7980.47</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
-        <x:v>8152.322</x:v>
+        <x:v>8152.32</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
         <x:v>7950.01</x:v>
       </x:c>
       <x:c r="G34" s="23" t="n">
-        <x:v>8051.574</x:v>
+        <x:v>8051.57</x:v>
       </x:c>
       <x:c r="H34" s="23" t="n">
         <x:v>-16.5</x:v>
       </x:c>
       <x:c r="I34" s="24" t="n">
-        <x:v>-0.0020454688273302546</x:v>
+        <x:v>-0.002046335683334899</x:v>
       </x:c>
       <x:c r="J34" s="26" t="n">
         <x:f>ROUND(E34-F34,1)</x:f>
@@ -18623,22 +18623,22 @@
         <x:v>2月9日</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>8177.291</x:v>
+        <x:v>8177.29</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
-        <x:v>8235.155</x:v>
+        <x:v>8235.15</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>8149.646</x:v>
+        <x:v>8149.65</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
-        <x:v>8233.778</x:v>
+        <x:v>8233.78</x:v>
       </x:c>
       <x:c r="H35" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I35" s="24" t="n">
-        <x:v>0.022629612545323585</x:v>
+        <x:v>0.022630368983937332</x:v>
       </x:c>
       <x:c r="J35" s="23" t="n">
         <x:f>ROUND(E35-F35,1)</x:f>
@@ -18659,13 +18659,13 @@
         <x:v>2月10日</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>8246.218</x:v>
+        <x:v>8246.22</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>8274.143</x:v>
+        <x:v>8274.14</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>8199.511</x:v>
+        <x:v>8199.51</x:v>
       </x:c>
       <x:c r="G36" s="23" t="n">
         <x:v>8250.3</x:v>
@@ -18674,7 +18674,7 @@
         <x:v>16.5</x:v>
       </x:c>
       <x:c r="I36" s="24" t="n">
-        <x:v>0.002006612274462416</x:v>
+        <x:v>0.00200636888525052</x:v>
       </x:c>
       <x:c r="J36" s="23" t="n">
         <x:f>ROUND(E36-F36,1)</x:f>
@@ -18698,19 +18698,19 @@
         <x:v>8239.17</x:v>
       </x:c>
       <x:c r="E37" s="23" t="n">
-        <x:v>8304.125</x:v>
+        <x:v>8304.13</x:v>
       </x:c>
       <x:c r="F37" s="23" t="n">
-        <x:v>8236.957</x:v>
+        <x:v>8236.96</x:v>
       </x:c>
       <x:c r="G37" s="23" t="n">
-        <x:v>8239.513</x:v>
+        <x:v>8239.51</x:v>
       </x:c>
       <x:c r="H37" s="23" t="n">
         <x:v>-10.8</x:v>
       </x:c>
       <x:c r="I37" s="24" t="n">
-        <x:v>-0.0013074676072383218</x:v>
+        <x:v>-0.0013078312303793638</x:v>
       </x:c>
       <x:c r="J37" s="23" t="n">
         <x:f>ROUND(E37-F37,1)</x:f>
@@ -18731,22 +18731,22 @@
         <x:v>2月12日</x:v>
       </x:c>
       <x:c r="D38" s="23" t="n">
-        <x:v>8252.185</x:v>
+        <x:v>8252.19</x:v>
       </x:c>
       <x:c r="E38" s="23" t="n">
-        <x:v>8337.371</x:v>
+        <x:v>8337.37</x:v>
       </x:c>
       <x:c r="F38" s="23" t="n">
-        <x:v>8227.604</x:v>
+        <x:v>8227.6</x:v>
       </x:c>
       <x:c r="G38" s="23" t="n">
-        <x:v>8314.832</x:v>
+        <x:v>8314.83</x:v>
       </x:c>
       <x:c r="H38" s="23" t="n">
         <x:v>75.3</x:v>
       </x:c>
       <x:c r="I38" s="24" t="n">
-        <x:v>0.009141195602215824</x:v>
+        <x:v>0.009141320296959465</x:v>
       </x:c>
       <x:c r="J38" s="23" t="n">
         <x:f>ROUND(E38-F38,1)</x:f>
@@ -18767,22 +18767,22 @@
         <x:v>2月13日</x:v>
       </x:c>
       <x:c r="D39" s="23" t="n">
-        <x:v>8272.876</x:v>
+        <x:v>8272.88</x:v>
       </x:c>
       <x:c r="E39" s="23" t="n">
-        <x:v>8323.715</x:v>
+        <x:v>8323.72</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>8200.148</x:v>
+        <x:v>8200.15</x:v>
       </x:c>
       <x:c r="G39" s="23" t="n">
-        <x:v>8204.829</x:v>
+        <x:v>8204.83</x:v>
       </x:c>
       <x:c r="H39" s="23" t="n">
         <x:v>-110</x:v>
       </x:c>
       <x:c r="I39" s="24" t="n">
-        <x:v>-0.013229732122068238</x:v>
+        <x:v>-0.013229374503146762</x:v>
       </x:c>
       <x:c r="J39" s="23" t="n">
         <x:f>ROUND(E39-F39,1)</x:f>
@@ -18803,22 +18803,22 @@
         <x:v>2月24日</x:v>
       </x:c>
       <x:c r="D40" s="42" t="n">
-        <x:v>8319.691</x:v>
+        <x:v>8319.69</x:v>
       </x:c>
       <x:c r="E40" s="42" t="n">
-        <x:v>8356.914</x:v>
+        <x:v>8356.91</x:v>
       </x:c>
       <x:c r="F40" s="42" t="n">
-        <x:v>8236.707</x:v>
+        <x:v>8236.71</x:v>
       </x:c>
       <x:c r="G40" s="42" t="n">
-        <x:v>8299.771</x:v>
+        <x:v>8299.77</x:v>
       </x:c>
       <x:c r="H40" s="42" t="n">
         <x:v>94.9</x:v>
       </x:c>
       <x:c r="I40" s="43" t="n">
-        <x:v>0.011571478211185315</x:v>
+        <x:v>0.011571233042001028</x:v>
       </x:c>
       <x:c r="J40" s="42" t="n">
         <x:f>ROUND(E40-F40,1)</x:f>
@@ -18839,22 +18839,22 @@
         <x:v>2月25日</x:v>
       </x:c>
       <x:c r="D41" s="23" t="n">
-        <x:v>8320.612</x:v>
+        <x:v>8320.61</x:v>
       </x:c>
       <x:c r="E41" s="23" t="n">
-        <x:v>8449.763</x:v>
+        <x:v>8449.76</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>8310.325</x:v>
+        <x:v>8310.33</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
-        <x:v>8426.331</x:v>
+        <x:v>8426.33</x:v>
       </x:c>
       <x:c r="H41" s="23" t="n">
         <x:v>126.6</x:v>
       </x:c>
       <x:c r="I41" s="24" t="n">
-        <x:v>0.015248613485841833</x:v>
+        <x:v>0.015248615323075088</x:v>
       </x:c>
       <x:c r="J41" s="23" t="n">
         <x:f>ROUND(E41-F41,1)</x:f>
@@ -18875,22 +18875,22 @@
         <x:v>2月26日</x:v>
       </x:c>
       <x:c r="D42" s="23" t="n">
-        <x:v>8447.783</x:v>
+        <x:v>8447.78</x:v>
       </x:c>
       <x:c r="E42" s="23" t="n">
-        <x:v>8496.748</x:v>
+        <x:v>8496.75</x:v>
       </x:c>
       <x:c r="F42" s="23" t="n">
-        <x:v>8398.066</x:v>
+        <x:v>8398.07</x:v>
       </x:c>
       <x:c r="G42" s="23" t="n">
-        <x:v>8490.617</x:v>
+        <x:v>8490.62</x:v>
       </x:c>
       <x:c r="H42" s="23" t="n">
         <x:v>64.3</x:v>
       </x:c>
       <x:c r="I42" s="24" t="n">
-        <x:v>0.00762918048199146</x:v>
+        <x:v>0.007629656089899184</x:v>
       </x:c>
       <x:c r="J42" s="23" t="n">
         <x:f>ROUND(E42-F42,1)</x:f>
@@ -18911,22 +18911,22 @@
         <x:v>2月27日</x:v>
       </x:c>
       <x:c r="D43" s="23" t="n">
-        <x:v>8434.096</x:v>
+        <x:v>8434.1</x:v>
       </x:c>
       <x:c r="E43" s="23" t="n">
-        <x:v>8561.295</x:v>
+        <x:v>8561.3</x:v>
       </x:c>
       <x:c r="F43" s="23" t="n">
-        <x:v>8433.717</x:v>
+        <x:v>8433.72</x:v>
       </x:c>
       <x:c r="G43" s="23" t="n">
-        <x:v>8560.843</x:v>
+        <x:v>8560.84</x:v>
       </x:c>
       <x:c r="H43" s="23" t="n">
         <x:v>70.2</x:v>
       </x:c>
       <x:c r="I43" s="24" t="n">
-        <x:v>0.008271012577766745</x:v>
+        <x:v>0.00827030299318543</x:v>
       </x:c>
       <x:c r="J43" s="23" t="n">
         <x:f>ROUND(E43-F43,1)</x:f>
@@ -19035,22 +19035,22 @@
         <x:v>3月2日</x:v>
       </x:c>
       <x:c r="D49" s="23" t="n">
-        <x:v>8464.273</x:v>
+        <x:v>8464.27</x:v>
       </x:c>
       <x:c r="E49" s="23" t="n">
-        <x:v>8535.807</x:v>
+        <x:v>8535.81</x:v>
       </x:c>
       <x:c r="F49" s="23" t="n">
-        <x:v>8393.927</x:v>
+        <x:v>8393.93</x:v>
       </x:c>
       <x:c r="G49" s="23" t="n">
-        <x:v>8476.965</x:v>
+        <x:v>8476.97</x:v>
       </x:c>
       <x:c r="H49" s="23" t="n">
         <x:v>-83.9</x:v>
       </x:c>
       <x:c r="I49" s="24" t="n">
-        <x:v>-0.009797866868952121</x:v>
+        <x:v>-0.009796935814709862</x:v>
       </x:c>
       <x:c r="J49" s="23" t="n">
         <x:f>ROUND(E49-F49,1)</x:f>
@@ -19071,26 +19071,26 @@
         <x:v>3月3日</x:v>
       </x:c>
       <x:c r="D50" s="23" t="n">
-        <x:v>8495.954</x:v>
+        <x:v>8495.95</x:v>
       </x:c>
       <x:c r="E50" s="23" t="n">
-        <x:v>8510.854</x:v>
+        <x:v>8510.85</x:v>
       </x:c>
       <x:c r="F50" s="23" t="n">
-        <x:v>8128.305</x:v>
+        <x:v>8128.3</x:v>
       </x:c>
       <x:c r="G50" s="23" t="n">
-        <x:v>8142.454</x:v>
+        <x:v>8142.45</x:v>
       </x:c>
       <x:c r="H50" s="28" t="n">
         <x:v>-334.5</x:v>
       </x:c>
       <x:c r="I50" s="24" t="n">
-        <x:v>-0.0394611750785806</x:v>
+        <x:v>-0.039462213503173804</x:v>
       </x:c>
       <x:c r="J50" s="26" t="n">
         <x:f>ROUND(E50-F50,1)</x:f>
-        <x:v>382.5</x:v>
+        <x:v>382.6</x:v>
       </x:c>
       <x:c r="K50" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -19107,22 +19107,22 @@
         <x:v>3月4日</x:v>
       </x:c>
       <x:c r="D51" s="23" t="n">
-        <x:v>8039.593</x:v>
+        <x:v>8039.59</x:v>
       </x:c>
       <x:c r="E51" s="23" t="n">
-        <x:v>8228.895</x:v>
+        <x:v>8228.9</x:v>
       </x:c>
       <x:c r="F51" s="23" t="n">
-        <x:v>8039.593</x:v>
+        <x:v>8039.59</x:v>
       </x:c>
       <x:c r="G51" s="23" t="n">
-        <x:v>8094.518</x:v>
+        <x:v>8094.52</x:v>
       </x:c>
       <x:c r="H51" s="23" t="n">
         <x:v>-47.9</x:v>
       </x:c>
       <x:c r="I51" s="24" t="n">
-        <x:v>-0.005887168659472919</x:v>
+        <x:v>-0.005886434672610741</x:v>
       </x:c>
       <x:c r="J51" s="26" t="n">
         <x:f>ROUND(E51-F51,1)</x:f>
@@ -19143,22 +19143,22 @@
         <x:v>3月5日</x:v>
       </x:c>
       <x:c r="D52" s="23" t="n">
-        <x:v>8235.374</x:v>
+        <x:v>8235.37</x:v>
       </x:c>
       <x:c r="E52" s="23" t="n">
-        <x:v>8243.829</x:v>
+        <x:v>8243.83</x:v>
       </x:c>
       <x:c r="F52" s="23" t="n">
-        <x:v>8121.382</x:v>
+        <x:v>8121.38</x:v>
       </x:c>
       <x:c r="G52" s="23" t="n">
-        <x:v>8171.119</x:v>
+        <x:v>8171.12</x:v>
       </x:c>
       <x:c r="H52" s="23" t="n">
         <x:v>76.6</x:v>
       </x:c>
       <x:c r="I52" s="24" t="n">
-        <x:v>0.009463318260580778</x:v>
+        <x:v>0.009463192382006547</x:v>
       </x:c>
       <x:c r="J52" s="23" t="n">
         <x:f>ROUND(E52-F52,1)</x:f>
@@ -19179,22 +19179,22 @@
         <x:v>3月6日</x:v>
       </x:c>
       <x:c r="D53" s="23" t="n">
-        <x:v>8120.495</x:v>
+        <x:v>8120.49</x:v>
       </x:c>
       <x:c r="E53" s="23" t="n">
         <x:v>8273.68</x:v>
       </x:c>
       <x:c r="F53" s="23" t="n">
-        <x:v>8115.479</x:v>
+        <x:v>8115.48</x:v>
       </x:c>
       <x:c r="G53" s="23" t="n">
-        <x:v>8248.857</x:v>
+        <x:v>8248.86</x:v>
       </x:c>
       <x:c r="H53" s="23" t="n">
         <x:v>77.7</x:v>
       </x:c>
       <x:c r="I53" s="24" t="n">
-        <x:v>0.00951375203322824</x:v>
+        <x:v>0.009513995633401606</x:v>
       </x:c>
       <x:c r="J53" s="23" t="n">
         <x:f>ROUND(E53-F53,1)</x:f>
@@ -19215,22 +19215,22 @@
         <x:v>3月9日</x:v>
       </x:c>
       <x:c r="D54" s="23" t="n">
-        <x:v>8131.742</x:v>
+        <x:v>8131.74</x:v>
       </x:c>
       <x:c r="E54" s="23" t="n">
-        <x:v>8230.656</x:v>
+        <x:v>8230.66</x:v>
       </x:c>
       <x:c r="F54" s="23" t="n">
-        <x:v>7983.569</x:v>
+        <x:v>7983.57</x:v>
       </x:c>
       <x:c r="G54" s="23" t="n">
-        <x:v>8203.869</x:v>
+        <x:v>8203.87</x:v>
       </x:c>
       <x:c r="H54" s="23" t="n">
         <x:v>-45</x:v>
       </x:c>
       <x:c r="I54" s="24" t="n">
-        <x:v>-0.005453846514735239</x:v>
+        <x:v>-0.00545408698898997</x:v>
       </x:c>
       <x:c r="J54" s="26" t="n">
         <x:f>ROUND(E54-F54,1)</x:f>
@@ -19251,13 +19251,13 @@
         <x:v>3月10日</x:v>
       </x:c>
       <x:c r="D55" s="23" t="n">
-        <x:v>8272.941</x:v>
+        <x:v>8272.94</x:v>
       </x:c>
       <x:c r="E55" s="23" t="n">
-        <x:v>8351.666</x:v>
+        <x:v>8351.67</x:v>
       </x:c>
       <x:c r="F55" s="23" t="n">
-        <x:v>8271.493</x:v>
+        <x:v>8271.49</x:v>
       </x:c>
       <x:c r="G55" s="23" t="n">
         <x:v>8350.09</x:v>
@@ -19266,7 +19266,7 @@
         <x:v>146.2</x:v>
       </x:c>
       <x:c r="I55" s="24" t="n">
-        <x:v>0.017823419657237327</x:v>
+        <x:v>0.017823295590983168</x:v>
       </x:c>
       <x:c r="J55" s="23" t="n">
         <x:f>ROUND(E55-F55,1)</x:f>
@@ -19290,19 +19290,19 @@
         <x:v>8356.09</x:v>
       </x:c>
       <x:c r="E56" s="23" t="n">
-        <x:v>8394.122</x:v>
+        <x:v>8394.12</x:v>
       </x:c>
       <x:c r="F56" s="23" t="n">
-        <x:v>8334.328</x:v>
+        <x:v>8334.33</x:v>
       </x:c>
       <x:c r="G56" s="23" t="n">
-        <x:v>8363.526</x:v>
+        <x:v>8363.53</x:v>
       </x:c>
       <x:c r="H56" s="23" t="n">
         <x:v>13.4</x:v>
       </x:c>
       <x:c r="I56" s="24" t="n">
-        <x:v>0.0016090844529819126</x:v>
+        <x:v>0.0016095634897348443</x:v>
       </x:c>
       <x:c r="J56" s="23" t="n">
         <x:f>ROUND(E56-F56,1)</x:f>
@@ -19323,22 +19323,22 @@
         <x:v>3月12日</x:v>
       </x:c>
       <x:c r="D57" s="23" t="n">
-        <x:v>8357.351</x:v>
+        <x:v>8357.35</x:v>
       </x:c>
       <x:c r="E57" s="23" t="n">
-        <x:v>8388.633</x:v>
+        <x:v>8388.63</x:v>
       </x:c>
       <x:c r="F57" s="23" t="n">
         <x:v>8267.39</x:v>
       </x:c>
       <x:c r="G57" s="23" t="n">
-        <x:v>8335.908</x:v>
+        <x:v>8335.91</x:v>
       </x:c>
       <x:c r="H57" s="23" t="n">
         <x:v>-27.6</x:v>
       </x:c>
       <x:c r="I57" s="24" t="n">
-        <x:v>-0.003302195748539627</x:v>
+        <x:v>-0.0033024333026845376</x:v>
       </x:c>
       <x:c r="J57" s="23" t="n">
         <x:f>ROUND(E57-F57,1)</x:f>
@@ -19359,22 +19359,22 @@
         <x:v>3月13日</x:v>
       </x:c>
       <x:c r="D58" s="23" t="n">
-        <x:v>8297.913</x:v>
+        <x:v>8297.91</x:v>
       </x:c>
       <x:c r="E58" s="23" t="n">
-        <x:v>8350.917</x:v>
+        <x:v>8350.92</x:v>
       </x:c>
       <x:c r="F58" s="23" t="n">
-        <x:v>8196.374</x:v>
+        <x:v>8196.37</x:v>
       </x:c>
       <x:c r="G58" s="23" t="n">
-        <x:v>8214.293</x:v>
+        <x:v>8214.29</x:v>
       </x:c>
       <x:c r="H58" s="23" t="n">
         <x:v>-121.6</x:v>
       </x:c>
       <x:c r="I58" s="24" t="n">
-        <x:v>-0.014589292492191541</x:v>
+        <x:v>-0.014589888806380902</x:v>
       </x:c>
       <x:c r="J58" s="23" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
@@ -19395,22 +19395,22 @@
         <x:v>3月16日</x:v>
       </x:c>
       <x:c r="D59" s="23" t="n">
-        <x:v>8212.267</x:v>
+        <x:v>8212.27</x:v>
       </x:c>
       <x:c r="E59" s="23" t="n">
-        <x:v>8226.032</x:v>
+        <x:v>8226.03</x:v>
       </x:c>
       <x:c r="F59" s="23" t="n">
-        <x:v>8089.488</x:v>
+        <x:v>8089.49</x:v>
       </x:c>
       <x:c r="G59" s="23" t="n">
-        <x:v>8211.352</x:v>
+        <x:v>8211.35</x:v>
       </x:c>
       <x:c r="H59" s="23" t="n">
         <x:v>-2.9</x:v>
       </x:c>
       <x:c r="I59" s="24" t="n">
-        <x:v>-0.0003580344650475631</x:v>
+        <x:v>-0.00035791285674113826</x:v>
       </x:c>
       <x:c r="J59" s="23" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
@@ -19434,19 +19434,19 @@
         <x:v>8219.5</x:v>
       </x:c>
       <x:c r="E60" s="23" t="n">
-        <x:v>8223.989</x:v>
+        <x:v>8223.99</x:v>
       </x:c>
       <x:c r="F60" s="23" t="n">
-        <x:v>8019.075</x:v>
+        <x:v>8019.08</x:v>
       </x:c>
       <x:c r="G60" s="23" t="n">
-        <x:v>8019.857</x:v>
+        <x:v>8019.86</x:v>
       </x:c>
       <x:c r="H60" s="28" t="n">
         <x:v>-191.5</x:v>
       </x:c>
       <x:c r="I60" s="24" t="n">
-        <x:v>-0.023320763742682216</x:v>
+        <x:v>-0.023320160509538668</x:v>
       </x:c>
       <x:c r="J60" s="26" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
@@ -19467,22 +19467,22 @@
         <x:v>3月18日</x:v>
       </x:c>
       <x:c r="D61" s="23" t="n">
-        <x:v>8050.714</x:v>
+        <x:v>8050.71</x:v>
       </x:c>
       <x:c r="E61" s="23" t="n">
-        <x:v>8105.806</x:v>
+        <x:v>8105.81</x:v>
       </x:c>
       <x:c r="F61" s="23" t="n">
-        <x:v>7970.189</x:v>
+        <x:v>7970.19</x:v>
       </x:c>
       <x:c r="G61" s="23" t="n">
-        <x:v>8096.595</x:v>
+        <x:v>8096.59</x:v>
       </x:c>
       <x:c r="H61" s="23" t="n">
         <x:v>76.7</x:v>
       </x:c>
       <x:c r="I61" s="24" t="n">
-        <x:v>0.00956849978746499</x:v>
+        <x:v>0.009567498684515785</x:v>
       </x:c>
       <x:c r="J61" s="23" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
@@ -19503,22 +19503,22 @@
         <x:v>3月19日</x:v>
       </x:c>
       <x:c r="D62" s="23" t="n">
-        <x:v>7988.873</x:v>
+        <x:v>7988.87</x:v>
       </x:c>
       <x:c r="E62" s="23" t="n">
-        <x:v>8008.389</x:v>
+        <x:v>8008.39</x:v>
       </x:c>
       <x:c r="F62" s="23" t="n">
-        <x:v>7874.262</x:v>
+        <x:v>7874.26</x:v>
       </x:c>
       <x:c r="G62" s="23" t="n">
-        <x:v>7909.234</x:v>
+        <x:v>7909.23</x:v>
       </x:c>
       <x:c r="H62" s="28" t="n">
         <x:v>-187.4</x:v>
       </x:c>
       <x:c r="I62" s="24" t="n">
-        <x:v>-0.02314071532539297</x:v>
+        <x:v>-0.023140606107015516</x:v>
       </x:c>
       <x:c r="J62" s="23" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
@@ -19539,22 +19539,22 @@
         <x:v>3月20日</x:v>
       </x:c>
       <x:c r="D63" s="42" t="n">
-        <x:v>7943.413</x:v>
+        <x:v>7943.41</x:v>
       </x:c>
       <x:c r="E63" s="42" t="n">
-        <x:v>7996.164</x:v>
+        <x:v>7996.16</x:v>
       </x:c>
       <x:c r="F63" s="42" t="n">
-        <x:v>7781.579</x:v>
+        <x:v>7781.58</x:v>
       </x:c>
       <x:c r="G63" s="42" t="n">
-        <x:v>7783.435</x:v>
+        <x:v>7783.43</x:v>
       </x:c>
       <x:c r="H63" s="42" t="n">
         <x:v>-125.8</x:v>
       </x:c>
       <x:c r="I63" s="43" t="n">
-        <x:v>-0.015905332931103078</x:v>
+        <x:v>-0.015905467409596086</x:v>
       </x:c>
       <x:c r="J63" s="26" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
@@ -19575,22 +19575,22 @@
         <x:v>3月23日</x:v>
       </x:c>
       <x:c r="D64" s="23" t="n">
-        <x:v>7632.972</x:v>
+        <x:v>7632.97</x:v>
       </x:c>
       <x:c r="E64" s="23" t="n">
         <x:v>7712.04</x:v>
       </x:c>
       <x:c r="F64" s="23" t="n">
-        <x:v>7357.696</x:v>
+        <x:v>7357.7</x:v>
       </x:c>
       <x:c r="G64" s="23" t="n">
-        <x:v>7409.107</x:v>
+        <x:v>7409.11</x:v>
       </x:c>
       <x:c r="H64" s="28" t="n">
         <x:v>-374.3</x:v>
       </x:c>
       <x:c r="I64" s="24" t="n">
-        <x:v>-0.04809290499631591</x:v>
+        <x:v>-0.0480919080662382</x:v>
       </x:c>
       <x:c r="J64" s="26" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
@@ -19611,22 +19611,22 @@
         <x:v>3月24日</x:v>
       </x:c>
       <x:c r="D65" s="23" t="n">
-        <x:v>7538.697</x:v>
+        <x:v>7538.7</x:v>
       </x:c>
       <x:c r="E65" s="23" t="n">
-        <x:v>7601.883</x:v>
+        <x:v>7601.88</x:v>
       </x:c>
       <x:c r="F65" s="23" t="n">
-        <x:v>7361.793</x:v>
+        <x:v>7361.79</x:v>
       </x:c>
       <x:c r="G65" s="23" t="n">
-        <x:v>7600.857</x:v>
+        <x:v>7600.86</x:v>
       </x:c>
       <x:c r="H65" s="28" t="n">
         <x:v>191.8</x:v>
       </x:c>
       <x:c r="I65" s="24" t="n">
-        <x:v>0.025880311891838037</x:v>
+        <x:v>0.02588030141272024</x:v>
       </x:c>
       <x:c r="J65" s="26" t="n">
         <x:f>ROUND(E65-F65,1)</x:f>
@@ -19647,22 +19647,22 @@
         <x:v>3月25日</x:v>
       </x:c>
       <x:c r="D66" s="23" t="n">
-        <x:v>7654.784</x:v>
+        <x:v>7654.78</x:v>
       </x:c>
       <x:c r="E66" s="23" t="n">
-        <x:v>7781.197</x:v>
+        <x:v>7781.2</x:v>
       </x:c>
       <x:c r="F66" s="23" t="n">
-        <x:v>7654.784</x:v>
+        <x:v>7654.78</x:v>
       </x:c>
       <x:c r="G66" s="23" t="n">
-        <x:v>7751.181</x:v>
+        <x:v>7751.18</x:v>
       </x:c>
       <x:c r="H66" s="28" t="n">
         <x:v>150.3</x:v>
       </x:c>
       <x:c r="I66" s="24" t="n">
-        <x:v>0.019777243539774503</x:v>
+        <x:v>0.019776709477611787</x:v>
       </x:c>
       <x:c r="J66" s="23" t="n">
         <x:f>ROUND(E66-F66,1)</x:f>
@@ -19683,22 +19683,22 @@
         <x:v>3月26日</x:v>
       </x:c>
       <x:c r="D67" s="23" t="n">
-        <x:v>7733.702</x:v>
+        <x:v>7733.7</x:v>
       </x:c>
       <x:c r="E67" s="23" t="n">
-        <x:v>7775.893</x:v>
+        <x:v>7775.89</x:v>
       </x:c>
       <x:c r="F67" s="23" t="n">
-        <x:v>7614.889</x:v>
+        <x:v>7614.89</x:v>
       </x:c>
       <x:c r="G67" s="23" t="n">
-        <x:v>7639.376</x:v>
+        <x:v>7639.38</x:v>
       </x:c>
       <x:c r="H67" s="23" t="n">
         <x:v>-111.8</x:v>
       </x:c>
       <x:c r="I67" s="24" t="n">
-        <x:v>-0.01442425354278265</x:v>
+        <x:v>-0.01442361034061912</x:v>
       </x:c>
       <x:c r="J67" s="23" t="n">
         <x:f>ROUND(E67-F67,1)</x:f>
@@ -19719,22 +19719,22 @@
         <x:v>3月27日</x:v>
       </x:c>
       <x:c r="D68" s="23" t="n">
-        <x:v>7526.586</x:v>
+        <x:v>7526.59</x:v>
       </x:c>
       <x:c r="E68" s="23" t="n">
-        <x:v>7784.547</x:v>
+        <x:v>7784.55</x:v>
       </x:c>
       <x:c r="F68" s="23" t="n">
-        <x:v>7526.586</x:v>
+        <x:v>7526.59</x:v>
       </x:c>
       <x:c r="G68" s="23" t="n">
-        <x:v>7746.313</x:v>
+        <x:v>7746.31</x:v>
       </x:c>
       <x:c r="H68" s="23" t="n">
         <x:v>106.9</x:v>
       </x:c>
       <x:c r="I68" s="24" t="n">
-        <x:v>0.013998132831791521</x:v>
+        <x:v>0.013997209197605054</x:v>
       </x:c>
       <x:c r="J68" s="26" t="n">
         <x:f>ROUND(E68-F68,1)</x:f>
@@ -19755,13 +19755,13 @@
         <x:v>3月30日</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>7664.636</x:v>
+        <x:v>7664.64</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
-        <x:v>7774.851</x:v>
+        <x:v>7774.85</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>7618.961</x:v>
+        <x:v>7618.96</x:v>
       </x:c>
       <x:c r="G69" s="23" t="n">
         <x:v>7767.93</x:v>
@@ -19770,7 +19770,7 @@
         <x:v>21.6</x:v>
       </x:c>
       <x:c r="I69" s="24" t="n">
-        <x:v>0.0027906179365591033</x:v>
+        <x:v>0.0027910062984828343</x:v>
       </x:c>
       <x:c r="J69" s="23" t="n">
         <x:f>ROUND(E69-F69,1)</x:f>
@@ -19791,13 +19791,13 @@
         <x:v>3月31日</x:v>
       </x:c>
       <x:c r="D70" s="23" t="n">
-        <x:v>7741.959</x:v>
+        <x:v>7741.96</x:v>
       </x:c>
       <x:c r="E70" s="23" t="n">
-        <x:v>7789.239</x:v>
+        <x:v>7789.24</x:v>
       </x:c>
       <x:c r="F70" s="23" t="n">
-        <x:v>7618.187</x:v>
+        <x:v>7618.19</x:v>
       </x:c>
       <x:c r="G70" s="23" t="n">
         <x:v>7619.85</x:v>
@@ -19832,7 +19832,7 @@
       <x:c r="I71" s="30"/>
       <x:c r="J71" s="32" t="n">
         <x:f>ROUND(SUM(J49:J70),1)</x:f>
-        <x:v>3949.6</x:v>
+        <x:v>3949.7</x:v>
       </x:c>
       <x:c r="K71" s="30"/>
     </x:row>
@@ -19915,26 +19915,26 @@
         <x:v>4月1日</x:v>
       </x:c>
       <x:c r="D76" s="23" t="n">
-        <x:v>7767.883</x:v>
+        <x:v>7767.88</x:v>
       </x:c>
       <x:c r="E76" s="23" t="n">
-        <x:v>7786.759</x:v>
+        <x:v>7786.76</x:v>
       </x:c>
       <x:c r="F76" s="23" t="n">
         <x:v>7692.01</x:v>
       </x:c>
       <x:c r="G76" s="23" t="n">
-        <x:v>7764.153</x:v>
+        <x:v>7764.15</x:v>
       </x:c>
       <x:c r="H76" s="23" t="n">
         <x:v>144.3</x:v>
       </x:c>
       <x:c r="I76" s="24" t="n">
-        <x:v>0.01893777436563715</x:v>
+        <x:v>0.01893738065709938</x:v>
       </x:c>
       <x:c r="J76" s="23" t="n">
         <x:f>ROUND(E76-F76,1)</x:f>
-        <x:v>94.7</x:v>
+        <x:v>94.8</x:v>
       </x:c>
       <x:c r="K76" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -19951,22 +19951,22 @@
         <x:v>4月2日</x:v>
       </x:c>
       <x:c r="D77" s="23" t="n">
-        <x:v>7733.747</x:v>
+        <x:v>7733.75</x:v>
       </x:c>
       <x:c r="E77" s="23" t="n">
-        <x:v>7764.027</x:v>
+        <x:v>7764.03</x:v>
       </x:c>
       <x:c r="F77" s="23" t="n">
-        <x:v>7581.392</x:v>
+        <x:v>7581.39</x:v>
       </x:c>
       <x:c r="G77" s="23" t="n">
-        <x:v>7623.417</x:v>
+        <x:v>7623.42</x:v>
       </x:c>
       <x:c r="H77" s="23" t="n">
         <x:v>-140.7</x:v>
       </x:c>
       <x:c r="I77" s="24" t="n">
-        <x:v>-0.01812638158985269</x:v>
+        <x:v>-0.018125615811131923</x:v>
       </x:c>
       <x:c r="J77" s="26" t="n">
         <x:f>ROUND(E77-F77,1)</x:f>
@@ -19987,13 +19987,13 @@
         <x:v>4月3日</x:v>
       </x:c>
       <x:c r="D78" s="23" t="n">
-        <x:v>7658.821</x:v>
+        <x:v>7658.82</x:v>
       </x:c>
       <x:c r="E78" s="23" t="n">
-        <x:v>7664.756</x:v>
+        <x:v>7664.76</x:v>
       </x:c>
       <x:c r="F78" s="23" t="n">
-        <x:v>7521.944</x:v>
+        <x:v>7521.94</x:v>
       </x:c>
       <x:c r="G78" s="23" t="n">
         <x:v>7536.6</x:v>
@@ -20002,7 +20002,7 @@
         <x:v>-86.8</x:v>
       </x:c>
       <x:c r="I78" s="24" t="n">
-        <x:v>-0.011388200330639142</x:v>
+        <x:v>-0.011388589373273361</x:v>
       </x:c>
       <x:c r="J78" s="23" t="n">
         <x:f>ROUND(E78-F78,1)</x:f>
@@ -20023,22 +20023,22 @@
         <x:v>4月7日</x:v>
       </x:c>
       <x:c r="D79" s="23" t="n">
-        <x:v>7556.277</x:v>
+        <x:v>7556.28</x:v>
       </x:c>
       <x:c r="E79" s="23" t="n">
-        <x:v>7640.505</x:v>
+        <x:v>7640.51</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7554.408</x:v>
+        <x:v>7554.41</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
-        <x:v>7606.017</x:v>
+        <x:v>7606.02</x:v>
       </x:c>
       <x:c r="H79" s="23" t="n">
         <x:v>69.4</x:v>
       </x:c>
       <x:c r="I79" s="24" t="n">
-        <x:v>0.00921065201815141</x:v>
+        <x:v>0.009211050075630833</x:v>
       </x:c>
       <x:c r="J79" s="23" t="n">
         <x:f>ROUND(E79-F79,1)</x:f>
@@ -20062,19 +20062,19 @@
         <x:v>7765.55</x:v>
       </x:c>
       <x:c r="E80" s="23" t="n">
-        <x:v>7955.768</x:v>
+        <x:v>7955.77</x:v>
       </x:c>
       <x:c r="F80" s="23" t="n">
-        <x:v>7765.197</x:v>
+        <x:v>7765.2</x:v>
       </x:c>
       <x:c r="G80" s="23" t="n">
-        <x:v>7955.768</x:v>
+        <x:v>7955.77</x:v>
       </x:c>
       <x:c r="H80" s="28" t="n">
         <x:v>349.8</x:v>
       </x:c>
       <x:c r="I80" s="24" t="n">
-        <x:v>0.04598346282949417</x:v>
+        <x:v>0.045983313217688115</x:v>
       </x:c>
       <x:c r="J80" s="26" t="n">
         <x:f>ROUND(E80-F80,1)</x:f>
@@ -20095,22 +20095,22 @@
         <x:v>4月9日</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7881.803</x:v>
+        <x:v>7881.8</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
-        <x:v>7959.067</x:v>
+        <x:v>7959.07</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7872.475</x:v>
+        <x:v>7872.47</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
-        <x:v>7921.447</x:v>
+        <x:v>7921.45</x:v>
       </x:c>
       <x:c r="H81" s="23" t="n">
         <x:v>-34.3</x:v>
       </x:c>
       <x:c r="I81" s="24" t="n">
-        <x:v>-0.004313976978715273</x:v>
+        <x:v>-0.004313850199289426</x:v>
       </x:c>
       <x:c r="J81" s="23" t="n">
         <x:f>ROUND(E81-F81,1)</x:f>
@@ -20131,22 +20131,22 @@
         <x:v>4月10日</x:v>
       </x:c>
       <x:c r="D82" s="23" t="n">
-        <x:v>7981.622</x:v>
+        <x:v>7981.62</x:v>
       </x:c>
       <x:c r="E82" s="23" t="n">
-        <x:v>8059.755</x:v>
+        <x:v>8059.76</x:v>
       </x:c>
       <x:c r="F82" s="23" t="n">
-        <x:v>7981.622</x:v>
+        <x:v>7981.62</x:v>
       </x:c>
       <x:c r="G82" s="23" t="n">
-        <x:v>7998.232</x:v>
+        <x:v>7998.23</x:v>
       </x:c>
       <x:c r="H82" s="23" t="n">
         <x:v>76.8</x:v>
       </x:c>
       <x:c r="I82" s="24" t="n">
-        <x:v>0.009693304771211553</x:v>
+        <x:v>0.009692669902606088</x:v>
       </x:c>
       <x:c r="J82" s="23" t="n">
         <x:f>ROUND(E82-F82,1)</x:f>
@@ -20167,22 +20167,22 @@
         <x:v>4月13日</x:v>
       </x:c>
       <x:c r="D83" s="23" t="n">
-        <x:v>7947.222</x:v>
+        <x:v>7947.22</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>8040.026</x:v>
+        <x:v>8040.03</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>7947.222</x:v>
+        <x:v>7947.22</x:v>
       </x:c>
       <x:c r="G83" s="23" t="n">
-        <x:v>8025.572</x:v>
+        <x:v>8025.57</x:v>
       </x:c>
       <x:c r="H83" s="23" t="n">
         <x:v>27.3</x:v>
       </x:c>
       <x:c r="I83" s="24" t="n">
-        <x:v>0.0034182554344510674</x:v>
+        <x:v>0.0034182562892040025</x:v>
       </x:c>
       <x:c r="J83" s="23" t="n">
         <x:f>ROUND(E83-F83,1)</x:f>
@@ -20206,19 +20206,19 @@
         <x:v>8088.05</x:v>
       </x:c>
       <x:c r="E84" s="23" t="n">
-        <x:v>8144.762</x:v>
+        <x:v>8144.76</x:v>
       </x:c>
       <x:c r="F84" s="23" t="n">
         <x:v>8059.38</x:v>
       </x:c>
       <x:c r="G84" s="23" t="n">
-        <x:v>8144.762</x:v>
+        <x:v>8144.76</x:v>
       </x:c>
       <x:c r="H84" s="23" t="n">
         <x:v>119.2</x:v>
       </x:c>
       <x:c r="I84" s="24" t="n">
-        <x:v>0.01485127789022389</x:v>
+        <x:v>0.014851281591214072</x:v>
       </x:c>
       <x:c r="J84" s="23" t="n">
         <x:f>ROUND(E84-F84,1)</x:f>
@@ -20239,22 +20239,22 @@
         <x:v>4月15日</x:v>
       </x:c>
       <x:c r="D85" s="23" t="n">
-        <x:v>8186.074</x:v>
+        <x:v>8186.07</x:v>
       </x:c>
       <x:c r="E85" s="23" t="n">
-        <x:v>8193.296</x:v>
+        <x:v>8193.3</x:v>
       </x:c>
       <x:c r="F85" s="23" t="n">
-        <x:v>8083.265</x:v>
+        <x:v>8083.27</x:v>
       </x:c>
       <x:c r="G85" s="23" t="n">
-        <x:v>8106.165</x:v>
+        <x:v>8106.16</x:v>
       </x:c>
       <x:c r="H85" s="23" t="n">
         <x:v>-38.6</x:v>
       </x:c>
       <x:c r="I85" s="24" t="n">
-        <x:v>-0.004738873892202067</x:v>
+        <x:v>-0.004739243390842751</x:v>
       </x:c>
       <x:c r="J85" s="23" t="n">
         <x:f>ROUND(E85-F85,1)</x:f>
@@ -20275,22 +20275,22 @@
         <x:v>4月16日</x:v>
       </x:c>
       <x:c r="D86" s="23" t="n">
-        <x:v>8120.358</x:v>
+        <x:v>8120.36</x:v>
       </x:c>
       <x:c r="E86" s="23" t="n">
-        <x:v>8239.008</x:v>
+        <x:v>8239.01</x:v>
       </x:c>
       <x:c r="F86" s="23" t="n">
-        <x:v>8100.489</x:v>
+        <x:v>8100.49</x:v>
       </x:c>
       <x:c r="G86" s="23" t="n">
-        <x:v>8232.983</x:v>
+        <x:v>8232.98</x:v>
       </x:c>
       <x:c r="H86" s="23" t="n">
         <x:v>126.8</x:v>
       </x:c>
       <x:c r="I86" s="24" t="n">
-        <x:v>0.015644635903661053</x:v>
+        <x:v>0.01564489227945165</x:v>
       </x:c>
       <x:c r="J86" s="23" t="n">
         <x:f>ROUND(E86-F86,1)</x:f>
@@ -20311,22 +20311,22 @@
         <x:v>4月17日</x:v>
       </x:c>
       <x:c r="D87" s="42" t="n">
-        <x:v>8225.729</x:v>
+        <x:v>8225.73</x:v>
       </x:c>
       <x:c r="E87" s="42" t="n">
-        <x:v>8333.222</x:v>
+        <x:v>8333.22</x:v>
       </x:c>
       <x:c r="F87" s="42" t="n">
-        <x:v>8223.706</x:v>
+        <x:v>8223.71</x:v>
       </x:c>
       <x:c r="G87" s="42" t="n">
-        <x:v>8307.436</x:v>
+        <x:v>8307.44</x:v>
       </x:c>
       <x:c r="H87" s="42" t="n">
         <x:v>74.5</x:v>
       </x:c>
       <x:c r="I87" s="43" t="n">
-        <x:v>0.009043259290101746</x:v>
+        <x:v>0.009044112824275086</x:v>
       </x:c>
       <x:c r="J87" s="42" t="n">
         <x:f>ROUND(E87-F87,1)</x:f>
@@ -20347,22 +20347,22 @@
         <x:v>4月20日</x:v>
       </x:c>
       <x:c r="D88" s="23" t="n">
-        <x:v>8308.055</x:v>
+        <x:v>8308.06</x:v>
       </x:c>
       <x:c r="E88" s="23" t="n">
-        <x:v>8374.812</x:v>
+        <x:v>8374.81</x:v>
       </x:c>
       <x:c r="F88" s="23" t="n">
-        <x:v>8308.055</x:v>
+        <x:v>8308.06</x:v>
       </x:c>
       <x:c r="G88" s="23" t="n">
-        <x:v>8357.814</x:v>
+        <x:v>8357.81</x:v>
       </x:c>
       <x:c r="H88" s="23" t="n">
         <x:v>50.4</x:v>
       </x:c>
       <x:c r="I88" s="24" t="n">
-        <x:v>0.006064205610491591</x:v>
+        <x:v>0.006063239698390621</x:v>
       </x:c>
       <x:c r="J88" s="23" t="n">
         <x:f>ROUND(E88-F88,1)</x:f>
@@ -20383,22 +20383,22 @@
         <x:v>4月21日</x:v>
       </x:c>
       <x:c r="D89" s="23" t="n">
-        <x:v>8331.592</x:v>
+        <x:v>8331.59</x:v>
       </x:c>
       <x:c r="E89" s="23" t="n">
-        <x:v>8358.124</x:v>
+        <x:v>8358.12</x:v>
       </x:c>
       <x:c r="F89" s="23" t="n">
-        <x:v>8270.161</x:v>
+        <x:v>8270.16</x:v>
       </x:c>
       <x:c r="G89" s="23" t="n">
-        <x:v>8351.156</x:v>
+        <x:v>8351.16</x:v>
       </x:c>
       <x:c r="H89" s="23" t="n">
-        <x:v>-6.7</x:v>
+        <x:v>-6.6</x:v>
       </x:c>
       <x:c r="I89" s="24" t="n">
-        <x:v>-0.0007966197859869961</x:v>
+        <x:v>-0.00079566297869893</x:v>
       </x:c>
       <x:c r="J89" s="23" t="n">
         <x:f>ROUND(E89-F89,1)</x:f>
@@ -20419,13 +20419,13 @@
         <x:v>4月22日</x:v>
       </x:c>
       <x:c r="D90" s="23" t="n">
-        <x:v>8317.278</x:v>
+        <x:v>8317.28</x:v>
       </x:c>
       <x:c r="E90" s="23" t="n">
-        <x:v>8482.153</x:v>
+        <x:v>8482.15</x:v>
       </x:c>
       <x:c r="F90" s="23" t="n">
-        <x:v>8317.278</x:v>
+        <x:v>8317.28</x:v>
       </x:c>
       <x:c r="G90" s="23" t="n">
         <x:v>8481.24</x:v>
@@ -20434,7 +20434,7 @@
         <x:v>130.1</x:v>
       </x:c>
       <x:c r="I90" s="24" t="n">
-        <x:v>0.015576765659748082</x:v>
+        <x:v>0.015576279223485034</x:v>
       </x:c>
       <x:c r="J90" s="23" t="n">
         <x:f>ROUND(E90-F90,1)</x:f>
@@ -20455,13 +20455,13 @@
         <x:v>4月23日</x:v>
       </x:c>
       <x:c r="D91" s="23" t="n">
-        <x:v>8488.996</x:v>
+        <x:v>8489</x:v>
       </x:c>
       <x:c r="E91" s="23" t="n">
-        <x:v>8500.438</x:v>
+        <x:v>8500.44</x:v>
       </x:c>
       <x:c r="F91" s="23" t="n">
-        <x:v>8302.849</x:v>
+        <x:v>8302.85</x:v>
       </x:c>
       <x:c r="G91" s="23" t="n">
         <x:v>8362.74</x:v>
@@ -20491,22 +20491,22 @@
         <x:v>4月24日</x:v>
       </x:c>
       <x:c r="D92" s="23" t="n">
-        <x:v>8318.597</x:v>
+        <x:v>8318.6</x:v>
       </x:c>
       <x:c r="E92" s="23" t="n">
         <x:v>8360.79</x:v>
       </x:c>
       <x:c r="F92" s="23" t="n">
-        <x:v>8254.431</x:v>
+        <x:v>8254.43</x:v>
       </x:c>
       <x:c r="G92" s="23" t="n">
-        <x:v>8304.141</x:v>
+        <x:v>8304.14</x:v>
       </x:c>
       <x:c r="H92" s="23" t="n">
         <x:v>-58.6</x:v>
       </x:c>
       <x:c r="I92" s="24" t="n">
-        <x:v>-0.007007153157936319</x:v>
+        <x:v>-0.00700727273596935</x:v>
       </x:c>
       <x:c r="J92" s="23" t="n">
         <x:f>ROUND(E92-F92,1)</x:f>
@@ -20527,22 +20527,22 @@
         <x:v>4月27日</x:v>
       </x:c>
       <x:c r="D93" s="23" t="n">
-        <x:v>8292.811</x:v>
+        <x:v>8292.81</x:v>
       </x:c>
       <x:c r="E93" s="23" t="n">
-        <x:v>8366.312</x:v>
+        <x:v>8366.31</x:v>
       </x:c>
       <x:c r="F93" s="23" t="n">
-        <x:v>8249.944</x:v>
+        <x:v>8249.94</x:v>
       </x:c>
       <x:c r="G93" s="23" t="n">
-        <x:v>8338.726</x:v>
+        <x:v>8338.73</x:v>
       </x:c>
       <x:c r="H93" s="23" t="n">
         <x:v>34.6</x:v>
       </x:c>
       <x:c r="I93" s="24" t="n">
-        <x:v>0.004164789591120988</x:v>
+        <x:v>0.004165392201961993</x:v>
       </x:c>
       <x:c r="J93" s="23" t="n">
         <x:f>ROUND(E93-F93,1)</x:f>
@@ -20563,22 +20563,22 @@
         <x:v>4月28日</x:v>
       </x:c>
       <x:c r="D94" s="23" t="n">
-        <x:v>8307.692</x:v>
+        <x:v>8307.69</x:v>
       </x:c>
       <x:c r="E94" s="23" t="n">
-        <x:v>8316.267</x:v>
+        <x:v>8316.27</x:v>
       </x:c>
       <x:c r="F94" s="23" t="n">
-        <x:v>8187.239</x:v>
+        <x:v>8187.24</x:v>
       </x:c>
       <x:c r="G94" s="23" t="n">
-        <x:v>8226.692</x:v>
+        <x:v>8226.69</x:v>
       </x:c>
       <x:c r="H94" s="23" t="n">
         <x:v>-112</x:v>
       </x:c>
       <x:c r="I94" s="24" t="n">
-        <x:v>-0.013435385693210344</x:v>
+        <x:v>-0.013436098782428352</x:v>
       </x:c>
       <x:c r="J94" s="23" t="n">
         <x:f>ROUND(E94-F94,1)</x:f>
@@ -20599,22 +20599,22 @@
         <x:v>4月29日</x:v>
       </x:c>
       <x:c r="D95" s="23" t="n">
-        <x:v>8163.348</x:v>
+        <x:v>8163.35</x:v>
       </x:c>
       <x:c r="E95" s="23" t="n">
-        <x:v>8361.487</x:v>
+        <x:v>8361.49</x:v>
       </x:c>
       <x:c r="F95" s="23" t="n">
-        <x:v>8163.348</x:v>
+        <x:v>8163.35</x:v>
       </x:c>
       <x:c r="G95" s="23" t="n">
-        <x:v>8343.065</x:v>
+        <x:v>8343.07</x:v>
       </x:c>
       <x:c r="H95" s="23" t="n">
         <x:v>116.4</x:v>
       </x:c>
       <x:c r="I95" s="24" t="n">
-        <x:v>0.014145783019468894</x:v>
+        <x:v>0.014146637347462798</x:v>
       </x:c>
       <x:c r="J95" s="26" t="n">
         <x:f>ROUND(E95-F95,1)</x:f>
@@ -20635,22 +20635,22 @@
         <x:v>4月30日</x:v>
       </x:c>
       <x:c r="D96" s="23" t="n">
-        <x:v>8345.247</x:v>
+        <x:v>8345.25</x:v>
       </x:c>
       <x:c r="E96" s="23" t="n">
-        <x:v>8402.356</x:v>
+        <x:v>8402.36</x:v>
       </x:c>
       <x:c r="F96" s="23" t="n">
-        <x:v>8324.294</x:v>
+        <x:v>8324.29</x:v>
       </x:c>
       <x:c r="G96" s="23" t="n">
-        <x:v>8381.947</x:v>
+        <x:v>8381.95</x:v>
       </x:c>
       <x:c r="H96" s="23" t="n">
         <x:v>38.9</x:v>
       </x:c>
       <x:c r="I96" s="24" t="n">
-        <x:v>0.004660397587697096</x:v>
+        <x:v>0.004660155074810657</x:v>
       </x:c>
       <x:c r="J96" s="23" t="n">
         <x:f>ROUND(E96-F96,1)</x:f>
@@ -20676,7 +20676,7 @@
       <x:c r="I97" s="30"/>
       <x:c r="J97" s="32" t="n">
         <x:f>ROUND(SUM(J76:J96),1)</x:f>
-        <x:v>2543</x:v>
+        <x:v>2543.1</x:v>
       </x:c>
       <x:c r="K97" s="30"/>
     </x:row>
@@ -20759,22 +20759,22 @@
         <x:v>5月6日</x:v>
       </x:c>
       <x:c r="D102" s="23" t="n">
-        <x:v>8462.023</x:v>
+        <x:v>8462.02</x:v>
       </x:c>
       <x:c r="E102" s="23" t="n">
-        <x:v>8610.881</x:v>
+        <x:v>8610.88</x:v>
       </x:c>
       <x:c r="F102" s="23" t="n">
-        <x:v>8462.023</x:v>
+        <x:v>8462.02</x:v>
       </x:c>
       <x:c r="G102" s="23" t="n">
-        <x:v>8574.556</x:v>
+        <x:v>8574.56</x:v>
       </x:c>
       <x:c r="H102" s="28" t="n">
         <x:v>192.6</x:v>
       </x:c>
       <x:c r="I102" s="24" t="n">
-        <x:v>0.0229790286194842</x:v>
+        <x:v>0.02297913969899601</x:v>
       </x:c>
       <x:c r="J102" s="23" t="n">
         <x:f>ROUND(E102-F102,1)</x:f>
@@ -20795,13 +20795,13 @@
         <x:v>5月7日</x:v>
       </x:c>
       <x:c r="D103" s="23" t="n">
-        <x:v>8602.146</x:v>
+        <x:v>8602.15</x:v>
       </x:c>
       <x:c r="E103" s="23" t="n">
-        <x:v>8716.861</x:v>
+        <x:v>8716.86</x:v>
       </x:c>
       <x:c r="F103" s="23" t="n">
-        <x:v>8573.295</x:v>
+        <x:v>8573.3</x:v>
       </x:c>
       <x:c r="G103" s="23" t="n">
         <x:v>8714.51</x:v>
@@ -20810,7 +20810,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="I103" s="24" t="n">
-        <x:v>0.01632201130880717</x:v>
+        <x:v>0.01632153719841023</x:v>
       </x:c>
       <x:c r="J103" s="23" t="n">
         <x:f>ROUND(E103-F103,1)</x:f>
@@ -20831,22 +20831,22 @@
         <x:v>5月8日</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>8655.127</x:v>
+        <x:v>8655.13</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
-        <x:v>8760.194</x:v>
+        <x:v>8760.19</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>8651.059</x:v>
+        <x:v>8651.06</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
-        <x:v>8741.151</x:v>
+        <x:v>8741.15</x:v>
       </x:c>
       <x:c r="H104" s="23" t="n">
         <x:v>26.6</x:v>
       </x:c>
       <x:c r="I104" s="24" t="n">
-        <x:v>0.003057085252068159</x:v>
+        <x:v>0.0030569705009231285</x:v>
       </x:c>
       <x:c r="J104" s="23" t="n">
         <x:f>ROUND(E104-F104,1)</x:f>
@@ -20867,22 +20867,22 @@
         <x:v>5月11日</x:v>
       </x:c>
       <x:c r="D105" s="23" t="n">
-        <x:v>8807.905</x:v>
+        <x:v>8807.91</x:v>
       </x:c>
       <x:c r="E105" s="23" t="n">
-        <x:v>8888.873</x:v>
+        <x:v>8888.87</x:v>
       </x:c>
       <x:c r="F105" s="23" t="n">
-        <x:v>8760.714</x:v>
+        <x:v>8760.71</x:v>
       </x:c>
       <x:c r="G105" s="23" t="n">
-        <x:v>8866.779</x:v>
+        <x:v>8866.78</x:v>
       </x:c>
       <x:c r="H105" s="23" t="n">
         <x:v>125.6</x:v>
       </x:c>
       <x:c r="I105" s="24" t="n">
-        <x:v>0.01437202034377405</x:v>
+        <x:v>0.014372250790799956</x:v>
       </x:c>
       <x:c r="J105" s="23" t="n">
         <x:f>ROUND(E105-F105,1)</x:f>
@@ -20903,22 +20903,22 @@
         <x:v>5月12日</x:v>
       </x:c>
       <x:c r="D106" s="23" t="n">
-        <x:v>8880.415</x:v>
+        <x:v>8880.41</x:v>
       </x:c>
       <x:c r="E106" s="23" t="n">
-        <x:v>8881.902</x:v>
+        <x:v>8881.9</x:v>
       </x:c>
       <x:c r="F106" s="23" t="n">
-        <x:v>8749.722</x:v>
+        <x:v>8749.72</x:v>
       </x:c>
       <x:c r="G106" s="23" t="n">
-        <x:v>8821.887</x:v>
+        <x:v>8821.89</x:v>
       </x:c>
       <x:c r="H106" s="23" t="n">
         <x:v>-44.9</x:v>
       </x:c>
       <x:c r="I106" s="24" t="n">
-        <x:v>-0.005062943375491846</x:v>
+        <x:v>-0.0050627172434639656</x:v>
       </x:c>
       <x:c r="J106" s="23" t="n">
         <x:f>ROUND(E106-F106,1)</x:f>
@@ -20939,22 +20939,22 @@
         <x:v>5月13日</x:v>
       </x:c>
       <x:c r="D107" s="23" t="n">
-        <x:v>8764.023</x:v>
+        <x:v>8764.02</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>8958.456</x:v>
+        <x:v>8958.46</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>8764.023</x:v>
+        <x:v>8764.02</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
-        <x:v>8955.447</x:v>
+        <x:v>8955.45</x:v>
       </x:c>
       <x:c r="H107" s="23" t="n">
         <x:v>133.6</x:v>
       </x:c>
       <x:c r="I107" s="24" t="n">
-        <x:v>0.015139618088510831</x:v>
+        <x:v>0.01513961294008448</x:v>
       </x:c>
       <x:c r="J107" s="26" t="n">
         <x:f>ROUND(E107-F107,1)</x:f>
@@ -20975,22 +20975,22 @@
         <x:v>5月14日</x:v>
       </x:c>
       <x:c r="D108" s="23" t="n">
-        <x:v>8989.487</x:v>
+        <x:v>8989.49</x:v>
       </x:c>
       <x:c r="E108" s="23" t="n">
         <x:v>8991.85</x:v>
       </x:c>
       <x:c r="F108" s="23" t="n">
-        <x:v>8778.709</x:v>
+        <x:v>8778.71</x:v>
       </x:c>
       <x:c r="G108" s="23" t="n">
-        <x:v>8778.709</x:v>
+        <x:v>8778.71</x:v>
       </x:c>
       <x:c r="H108" s="28" t="n">
         <x:v>-176.7</x:v>
       </x:c>
       <x:c r="I108" s="24" t="n">
-        <x:v>-0.01973525162953893</x:v>
+        <x:v>-0.01973546834609108</x:v>
       </x:c>
       <x:c r="J108" s="26" t="n">
         <x:f>ROUND(E108-F108,1)</x:f>
@@ -21011,22 +21011,22 @@
         <x:v>5月15日</x:v>
       </x:c>
       <x:c r="D109" s="42" t="n">
-        <x:v>8786.382</x:v>
+        <x:v>8786.38</x:v>
       </x:c>
       <x:c r="E109" s="42" t="n">
-        <x:v>8846.515</x:v>
+        <x:v>8846.52</x:v>
       </x:c>
       <x:c r="F109" s="42" t="n">
         <x:v>8616.06</x:v>
       </x:c>
       <x:c r="G109" s="42" t="n">
-        <x:v>8682.654</x:v>
+        <x:v>8682.65</x:v>
       </x:c>
       <x:c r="H109" s="42" t="n">
         <x:v>-96.1</x:v>
       </x:c>
       <x:c r="I109" s="43" t="n">
-        <x:v>-0.010941813881745088</x:v>
+        <x:v>-0.010942382195106015</x:v>
       </x:c>
       <x:c r="J109" s="26" t="n">
         <x:f>ROUND(E109-F109,1)</x:f>
@@ -21047,22 +21047,22 @@
         <x:v>5月18日</x:v>
       </x:c>
       <x:c r="D110" s="23" t="n">
-        <x:v>8645.763</x:v>
+        <x:v>8645.76</x:v>
       </x:c>
       <x:c r="E110" s="23" t="n">
-        <x:v>8766.306</x:v>
+        <x:v>8766.31</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>8610.742</x:v>
+        <x:v>8610.74</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
-        <x:v>8720.213</x:v>
+        <x:v>8720.21</x:v>
       </x:c>
       <x:c r="H110" s="23" t="n">
         <x:v>37.6</x:v>
       </x:c>
       <x:c r="I110" s="24" t="n">
-        <x:v>0.004325751089470975</x:v>
+        <x:v>0.004325868254507537</x:v>
       </x:c>
       <x:c r="J110" s="23" t="n">
         <x:f>ROUND(E110-F110,1)</x:f>
@@ -21083,22 +21083,22 @@
         <x:v>5月19日</x:v>
       </x:c>
       <x:c r="D111" s="23" t="n">
-        <x:v>8691.384</x:v>
+        <x:v>8691.38</x:v>
       </x:c>
       <x:c r="E111" s="23" t="n">
-        <x:v>8812.031</x:v>
+        <x:v>8812.03</x:v>
       </x:c>
       <x:c r="F111" s="23" t="n">
-        <x:v>8602.046</x:v>
+        <x:v>8602.05</x:v>
       </x:c>
       <x:c r="G111" s="23" t="n">
-        <x:v>8808.645</x:v>
+        <x:v>8808.64</x:v>
       </x:c>
       <x:c r="H111" s="23" t="n">
         <x:v>88.4</x:v>
       </x:c>
       <x:c r="I111" s="24" t="n">
-        <x:v>0.010141036692567162</x:v>
+        <x:v>0.010140810829097013</x:v>
       </x:c>
       <x:c r="J111" s="26" t="n">
         <x:f>ROUND(E111-F111,1)</x:f>
@@ -21119,10 +21119,10 @@
         <x:v>5月20日</x:v>
       </x:c>
       <x:c r="D112" s="23" t="n">
-        <x:v>8769.097</x:v>
+        <x:v>8769.1</x:v>
       </x:c>
       <x:c r="E112" s="23" t="n">
-        <x:v>8823.684</x:v>
+        <x:v>8823.68</x:v>
       </x:c>
       <x:c r="F112" s="23" t="n">
         <x:v>8697.4</x:v>
@@ -21134,7 +21134,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="24" t="n">
-        <x:v>0.00003008408217142211</x:v>
+        <x:v>0.00003065172376226499</x:v>
       </x:c>
       <x:c r="J112" s="23" t="n">
         <x:f>ROUND(E112-F112,1)</x:f>
@@ -21155,7 +21155,7 @@
         <x:v>5月21日</x:v>
       </x:c>
       <x:c r="D113" s="23" t="n">
-        <x:v>8852.434</x:v>
+        <x:v>8852.43</x:v>
       </x:c>
       <x:c r="E113" s="23" t="n">
         <x:v>8896.6</x:v>
@@ -21164,13 +21164,13 @@
         <x:v>8500.92</x:v>
       </x:c>
       <x:c r="G113" s="23" t="n">
-        <x:v>8510.496</x:v>
+        <x:v>8510.5</x:v>
       </x:c>
       <x:c r="H113" s="28" t="n">
         <x:v>-298.4</x:v>
       </x:c>
       <x:c r="I113" s="24" t="n">
-        <x:v>-0.03387638198142573</x:v>
+        <x:v>-0.033875927895732794</x:v>
       </x:c>
       <x:c r="J113" s="26" t="n">
         <x:f>ROUND(E113-F113,1)</x:f>
@@ -21194,19 +21194,19 @@
         <x:v>8578.9</x:v>
       </x:c>
       <x:c r="E114" s="23" t="n">
-        <x:v>8719.387</x:v>
+        <x:v>8719.39</x:v>
       </x:c>
       <x:c r="F114" s="23" t="n">
-        <x:v>8521.695</x:v>
+        <x:v>8521.7</x:v>
       </x:c>
       <x:c r="G114" s="23" t="n">
-        <x:v>8692.666</x:v>
+        <x:v>8692.67</x:v>
       </x:c>
       <x:c r="H114" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I114" s="24" t="n">
-        <x:v>0.021405332897165952</x:v>
+        <x:v>0.0214053228364961</x:v>
       </x:c>
       <x:c r="J114" s="26" t="n">
         <x:f>ROUND(E114-F114,1)</x:f>
@@ -21227,22 +21227,22 @@
         <x:v>5月25日</x:v>
       </x:c>
       <x:c r="D115" s="23" t="n">
-        <x:v>8756.458</x:v>
+        <x:v>8756.46</x:v>
       </x:c>
       <x:c r="E115" s="23" t="n">
-        <x:v>8802.946</x:v>
+        <x:v>8802.95</x:v>
       </x:c>
       <x:c r="F115" s="23" t="n">
-        <x:v>8670.716</x:v>
+        <x:v>8670.72</x:v>
       </x:c>
       <x:c r="G115" s="23" t="n">
-        <x:v>8799.312</x:v>
+        <x:v>8799.31</x:v>
       </x:c>
       <x:c r="H115" s="23" t="n">
         <x:v>106.6</x:v>
       </x:c>
       <x:c r="I115" s="24" t="n">
-        <x:v>0.012268503126658725</x:v>
+        <x:v>0.012267807244494389</x:v>
       </x:c>
       <x:c r="J115" s="23" t="n">
         <x:f>ROUND(E115-F115,1)</x:f>
@@ -21263,22 +21263,22 @@
         <x:v>5月26日</x:v>
       </x:c>
       <x:c r="D116" s="23" t="n">
-        <x:v>8755.908</x:v>
+        <x:v>8755.91</x:v>
       </x:c>
       <x:c r="E116" s="23" t="n">
-        <x:v>8756.463</x:v>
+        <x:v>8756.46</x:v>
       </x:c>
       <x:c r="F116" s="23" t="n">
-        <x:v>8560.804</x:v>
+        <x:v>8560.8</x:v>
       </x:c>
       <x:c r="G116" s="23" t="n">
-        <x:v>8687.253</x:v>
+        <x:v>8687.25</x:v>
       </x:c>
       <x:c r="H116" s="23" t="n">
         <x:v>-112.1</x:v>
       </x:c>
       <x:c r="I116" s="24" t="n">
-        <x:v>-0.012734972916064291</x:v>
+        <x:v>-0.012735089455877757</x:v>
       </x:c>
       <x:c r="J116" s="26" t="n">
         <x:f>ROUND(E116-F116,1)</x:f>
@@ -21299,22 +21299,22 @@
         <x:v>5月27日</x:v>
       </x:c>
       <x:c r="D117" s="23" t="n">
-        <x:v>8679.536</x:v>
+        <x:v>8679.54</x:v>
       </x:c>
       <x:c r="E117" s="23" t="n">
-        <x:v>8737.055</x:v>
+        <x:v>8737.05</x:v>
       </x:c>
       <x:c r="F117" s="23" t="n">
-        <x:v>8495.723</x:v>
+        <x:v>8495.72</x:v>
       </x:c>
       <x:c r="G117" s="23" t="n">
-        <x:v>8546.514</x:v>
+        <x:v>8546.51</x:v>
       </x:c>
       <x:c r="H117" s="23" t="n">
         <x:v>-140.7</x:v>
       </x:c>
       <x:c r="I117" s="24" t="n">
-        <x:v>-0.016200633272681397</x:v>
+        <x:v>-0.016200753978531712</x:v>
       </x:c>
       <x:c r="J117" s="26" t="n">
         <x:f>ROUND(E117-F117,1)</x:f>
@@ -21335,22 +21335,22 @@
         <x:v>5月28日</x:v>
       </x:c>
       <x:c r="D118" s="23" t="n">
-        <x:v>8527.909</x:v>
+        <x:v>8527.91</x:v>
       </x:c>
       <x:c r="E118" s="23" t="n">
         <x:v>8659.61</x:v>
       </x:c>
       <x:c r="F118" s="23" t="n">
-        <x:v>8459.949</x:v>
+        <x:v>8459.95</x:v>
       </x:c>
       <x:c r="G118" s="23" t="n">
-        <x:v>8637.743</x:v>
+        <x:v>8637.74</x:v>
       </x:c>
       <x:c r="H118" s="23" t="n">
         <x:v>91.2</x:v>
       </x:c>
       <x:c r="I118" s="24" t="n">
-        <x:v>0.010674410642748766</x:v>
+        <x:v>0.010674532645489121</x:v>
       </x:c>
       <x:c r="J118" s="26" t="n">
         <x:f>ROUND(E118-F118,1)</x:f>
@@ -21371,22 +21371,22 @@
         <x:v>5月29日</x:v>
       </x:c>
       <x:c r="D119" s="23" t="n">
-        <x:v>8673.798</x:v>
+        <x:v>8673.8</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
-        <x:v>8680.266</x:v>
+        <x:v>8680.27</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>8357.801</x:v>
+        <x:v>8357.8</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
-        <x:v>8408.736</x:v>
+        <x:v>8408.74</x:v>
       </x:c>
       <x:c r="H119" s="28" t="n">
         <x:v>-229</x:v>
       </x:c>
       <x:c r="I119" s="24" t="n">
-        <x:v>-0.0265123655566043</x:v>
+        <x:v>-0.026511564367531326</x:v>
       </x:c>
       <x:c r="J119" s="26" t="n">
         <x:f>ROUND(E119-F119,1)</x:f>
@@ -21495,22 +21495,22 @@
         <x:v>6月1日</x:v>
       </x:c>
       <x:c r="D125" s="23" t="n">
-        <x:v>8393.518</x:v>
+        <x:v>8393.52</x:v>
       </x:c>
       <x:c r="E125" s="23" t="n">
-        <x:v>8504.983</x:v>
+        <x:v>8504.98</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>8339.353</x:v>
+        <x:v>8339.35</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
-        <x:v>8345.129</x:v>
+        <x:v>8345.13</x:v>
       </x:c>
       <x:c r="H125" s="23" t="n">
         <x:v>-63.6</x:v>
       </x:c>
       <x:c r="I125" s="24" t="n">
-        <x:v>-0.007564394934030494</x:v>
+        <x:v>-0.007564748107326547</x:v>
       </x:c>
       <x:c r="J125" s="23" t="n">
         <x:f>ROUND(E125-F125,1)</x:f>
@@ -21531,22 +21531,22 @@
         <x:v>6月2日</x:v>
       </x:c>
       <x:c r="D126" s="23" t="n">
-        <x:v>8360.807</x:v>
+        <x:v>8360.81</x:v>
       </x:c>
       <x:c r="E126" s="23" t="n">
-        <x:v>8440.232</x:v>
+        <x:v>8440.23</x:v>
       </x:c>
       <x:c r="F126" s="23" t="n">
-        <x:v>8219.153</x:v>
+        <x:v>8219.15</x:v>
       </x:c>
       <x:c r="G126" s="23" t="n">
-        <x:v>8384.781</x:v>
+        <x:v>8384.78</x:v>
       </x:c>
       <x:c r="H126" s="23" t="n">
         <x:v>39.7</x:v>
       </x:c>
       <x:c r="I126" s="24" t="n">
-        <x:v>0.004751514326501116</x:v>
+        <x:v>0.004751274096389313</x:v>
       </x:c>
       <x:c r="J126" s="26" t="n">
         <x:f>ROUND(E126-F126,1)</x:f>
@@ -21567,22 +21567,22 @@
         <x:v>6月3日</x:v>
       </x:c>
       <x:c r="D127" s="23" t="n">
-        <x:v>8386.858</x:v>
+        <x:v>8386.86</x:v>
       </x:c>
       <x:c r="E127" s="23" t="n">
-        <x:v>8549.249</x:v>
+        <x:v>8549.25</x:v>
       </x:c>
       <x:c r="F127" s="23" t="n">
-        <x:v>8357.464</x:v>
+        <x:v>8357.46</x:v>
       </x:c>
       <x:c r="G127" s="23" t="n">
-        <x:v>8432.679</x:v>
+        <x:v>8432.68</x:v>
       </x:c>
       <x:c r="H127" s="23" t="n">
         <x:v>47.9</x:v>
       </x:c>
       <x:c r="I127" s="24" t="n">
-        <x:v>0.00571249266975471</x:v>
+        <x:v>0.005712731878475097</x:v>
       </x:c>
       <x:c r="J127" s="26" t="n">
         <x:f>ROUND(E127-F127,1)</x:f>
@@ -21603,22 +21603,22 @@
         <x:v>6月4日</x:v>
       </x:c>
       <x:c r="D128" s="23" t="n">
-        <x:v>8338.854</x:v>
+        <x:v>8338.85</x:v>
       </x:c>
       <x:c r="E128" s="23" t="n">
-        <x:v>8456.017</x:v>
+        <x:v>8456.02</x:v>
       </x:c>
       <x:c r="F128" s="23" t="n">
-        <x:v>8338.854</x:v>
+        <x:v>8338.85</x:v>
       </x:c>
       <x:c r="G128" s="23" t="n">
-        <x:v>8420.095</x:v>
+        <x:v>8420.09</x:v>
       </x:c>
       <x:c r="H128" s="23" t="n">
         <x:v>-12.6</x:v>
       </x:c>
       <x:c r="I128" s="24" t="n">
-        <x:v>-0.001492289698208693</x:v>
+        <x:v>-0.0014930010388156667</x:v>
       </x:c>
       <x:c r="J128" s="23" t="n">
         <x:f>ROUND(E128-F128,1)</x:f>
@@ -21639,22 +21639,22 @@
         <x:v>6月5日</x:v>
       </x:c>
       <x:c r="D129" s="23" t="n">
-        <x:v>8380.852</x:v>
+        <x:v>8380.85</x:v>
       </x:c>
       <x:c r="E129" s="23" t="n">
         <x:v>8500.1</x:v>
       </x:c>
       <x:c r="F129" s="23" t="n">
-        <x:v>8305.396</x:v>
+        <x:v>8305.4</x:v>
       </x:c>
       <x:c r="G129" s="23" t="n">
-        <x:v>8340.963</x:v>
+        <x:v>8340.96</x:v>
       </x:c>
       <x:c r="H129" s="23" t="n">
         <x:v>-79.1</x:v>
       </x:c>
       <x:c r="I129" s="24" t="n">
-        <x:v>-0.009397993728099241</x:v>
+        <x:v>-0.009397761781643754</x:v>
       </x:c>
       <x:c r="J129" s="26" t="n">
         <x:f>ROUND(E129-F129,1)</x:f>
@@ -21675,22 +21675,22 @@
         <x:v>6月8日</x:v>
       </x:c>
       <x:c r="D130" s="23" t="n">
-        <x:v>8069.482</x:v>
+        <x:v>8069.48</x:v>
       </x:c>
       <x:c r="E130" s="23" t="n">
-        <x:v>8260.192</x:v>
+        <x:v>8260.19</x:v>
       </x:c>
       <x:c r="F130" s="23" t="n">
-        <x:v>7987.396</x:v>
+        <x:v>7987.4</x:v>
       </x:c>
       <x:c r="G130" s="23" t="n">
-        <x:v>8081.261</x:v>
+        <x:v>8081.26</x:v>
       </x:c>
       <x:c r="H130" s="28" t="n">
         <x:v>-259.7</x:v>
       </x:c>
       <x:c r="I130" s="24" t="n">
-        <x:v>-0.031135733367957497</x:v>
+        <x:v>-0.031135504786019674</x:v>
       </x:c>
       <x:c r="J130" s="26" t="n">
         <x:f>ROUND(E130-F130,1)</x:f>
@@ -21711,22 +21711,22 @@
         <x:v>6月9日</x:v>
       </x:c>
       <x:c r="D131" s="23" t="n">
-        <x:v>8178.823</x:v>
+        <x:v>8178.82</x:v>
       </x:c>
       <x:c r="E131" s="23" t="n">
-        <x:v>8322.109</x:v>
+        <x:v>8322.11</x:v>
       </x:c>
       <x:c r="F131" s="23" t="n">
-        <x:v>8096.577</x:v>
+        <x:v>8096.58</x:v>
       </x:c>
       <x:c r="G131" s="23" t="n">
-        <x:v>8318.698</x:v>
+        <x:v>8318.7</x:v>
       </x:c>
       <x:c r="H131" s="28" t="n">
         <x:v>237.4</x:v>
       </x:c>
       <x:c r="I131" s="24" t="n">
-        <x:v>0.029381181971476877</x:v>
+        <x:v>0.029381556836433953</x:v>
       </x:c>
       <x:c r="J131" s="26" t="n">
         <x:f>ROUND(E131-F131,1)</x:f>
@@ -21747,22 +21747,22 @@
         <x:v>6月10日</x:v>
       </x:c>
       <x:c r="D132" s="23" t="n">
-        <x:v>8232.024</x:v>
+        <x:v>8232.02</x:v>
       </x:c>
       <x:c r="E132" s="23" t="n">
-        <x:v>8285.286</x:v>
+        <x:v>8285.29</x:v>
       </x:c>
       <x:c r="F132" s="23" t="n">
         <x:v>8103.01</x:v>
       </x:c>
       <x:c r="G132" s="23" t="n">
-        <x:v>8198.723</x:v>
+        <x:v>8198.72</x:v>
       </x:c>
       <x:c r="H132" s="23" t="n">
         <x:v>-120</x:v>
       </x:c>
       <x:c r="I132" s="24" t="n">
-        <x:v>-0.014422329071208106</x:v>
+        <x:v>-0.014422926659213742</x:v>
       </x:c>
       <x:c r="J132" s="26" t="n">
         <x:f>ROUND(E132-F132,1)</x:f>
@@ -21786,19 +21786,19 @@
         <x:v>8158.46</x:v>
       </x:c>
       <x:c r="E133" s="23" t="n">
-        <x:v>8223.527</x:v>
+        <x:v>8223.53</x:v>
       </x:c>
       <x:c r="F133" s="23" t="n">
         <x:v>8084.9</x:v>
       </x:c>
       <x:c r="G133" s="23" t="n">
-        <x:v>8159.455</x:v>
+        <x:v>8159.45</x:v>
       </x:c>
       <x:c r="H133" s="23" t="n">
         <x:v>-39.3</x:v>
       </x:c>
       <x:c r="I133" s="24" t="n">
-        <x:v>-0.004789526368923602</x:v>
+        <x:v>-0.004789772061980391</x:v>
       </x:c>
       <x:c r="J133" s="23" t="n">
         <x:f>ROUND(E133-F133,1)</x:f>
@@ -21819,22 +21819,22 @@
         <x:v>6月12日</x:v>
       </x:c>
       <x:c r="D134" s="23" t="n">
-        <x:v>8294.897</x:v>
+        <x:v>8294.9</x:v>
       </x:c>
       <x:c r="E134" s="23" t="n">
-        <x:v>8348.786</x:v>
+        <x:v>8348.79</x:v>
       </x:c>
       <x:c r="F134" s="23" t="n">
-        <x:v>8181.417</x:v>
+        <x:v>8181.42</x:v>
       </x:c>
       <x:c r="G134" s="23" t="n">
-        <x:v>8202.799</x:v>
+        <x:v>8202.8</x:v>
       </x:c>
       <x:c r="H134" s="23" t="n">
         <x:v>43.3</x:v>
       </x:c>
       <x:c r="I134" s="24" t="n">
-        <x:v>0.005312119498177337</x:v>
+        <x:v>0.005312858097052953</x:v>
       </x:c>
       <x:c r="J134" s="23" t="n">
         <x:f>ROUND(E134-F134,1)</x:f>
@@ -21855,22 +21855,22 @@
         <x:v>6月15日</x:v>
       </x:c>
       <x:c r="D135" s="23" t="n">
-        <x:v>8269.397</x:v>
+        <x:v>8269.4</x:v>
       </x:c>
       <x:c r="E135" s="23" t="n">
-        <x:v>8521.233</x:v>
+        <x:v>8521.23</x:v>
       </x:c>
       <x:c r="F135" s="23" t="n">
-        <x:v>8269.397</x:v>
+        <x:v>8269.4</x:v>
       </x:c>
       <x:c r="G135" s="23" t="n">
-        <x:v>8521.233</x:v>
+        <x:v>8521.23</x:v>
       </x:c>
       <x:c r="H135" s="28" t="n">
         <x:v>318.4</x:v>
       </x:c>
       <x:c r="I135" s="24" t="n">
-        <x:v>0.03882016370265795</x:v>
+        <x:v>0.03881967133174036</x:v>
       </x:c>
       <x:c r="J135" s="26" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
@@ -21897,16 +21897,16 @@
         <x:v>8684.65</x:v>
       </x:c>
       <x:c r="F136" s="23" t="n">
-        <x:v>8508.908</x:v>
+        <x:v>8508.91</x:v>
       </x:c>
       <x:c r="G136" s="23" t="n">
-        <x:v>8646.403</x:v>
+        <x:v>8646.4</x:v>
       </x:c>
       <x:c r="H136" s="23" t="n">
         <x:v>125.2</x:v>
       </x:c>
       <x:c r="I136" s="24" t="n">
-        <x:v>0.014689188759420047</x:v>
+        <x:v>0.01468919393092305</x:v>
       </x:c>
       <x:c r="J136" s="23" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
@@ -21930,19 +21930,19 @@
         <x:v>8581.65</x:v>
       </x:c>
       <x:c r="E137" s="23" t="n">
-        <x:v>8705.403</x:v>
+        <x:v>8705.4</x:v>
       </x:c>
       <x:c r="F137" s="23" t="n">
         <x:v>8581.65</x:v>
       </x:c>
       <x:c r="G137" s="23" t="n">
-        <x:v>8704.468</x:v>
+        <x:v>8704.47</x:v>
       </x:c>
       <x:c r="H137" s="23" t="n">
         <x:v>58.1</x:v>
       </x:c>
       <x:c r="I137" s="24" t="n">
-        <x:v>0.006715509327982927</x:v>
+        <x:v>0.006716089933382685</x:v>
       </x:c>
       <x:c r="J137" s="23" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
@@ -21963,22 +21963,22 @@
         <x:v>6月18日</x:v>
       </x:c>
       <x:c r="D138" s="23" t="n">
-        <x:v>8666.638</x:v>
+        <x:v>8666.64</x:v>
       </x:c>
       <x:c r="E138" s="23" t="n">
-        <x:v>8796.485</x:v>
+        <x:v>8796.48</x:v>
       </x:c>
       <x:c r="F138" s="23" t="n">
-        <x:v>8664.278</x:v>
+        <x:v>8664.28</x:v>
       </x:c>
       <x:c r="G138" s="23" t="n">
-        <x:v>8771.024</x:v>
+        <x:v>8771.02</x:v>
       </x:c>
       <x:c r="H138" s="23" t="n">
         <x:v>66.6</x:v>
       </x:c>
       <x:c r="I138" s="24" t="n">
-        <x:v>0.007646188141538168</x:v>
+        <x:v>0.00764549708368234</x:v>
       </x:c>
       <x:c r="J138" s="23" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
@@ -21999,22 +21999,22 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="42" t="n">
-        <x:v>8813.725</x:v>
+        <x:v>8813.72</x:v>
       </x:c>
       <x:c r="E139" s="42" t="n">
-        <x:v>8865.815</x:v>
+        <x:v>8865.81</x:v>
       </x:c>
       <x:c r="F139" s="42" t="n">
-        <x:v>8609.611</x:v>
+        <x:v>8609.61</x:v>
       </x:c>
       <x:c r="G139" s="42" t="n">
-        <x:v>8865.676</x:v>
+        <x:v>8865.68</x:v>
       </x:c>
       <x:c r="H139" s="42" t="n">
         <x:v>94.7</x:v>
       </x:c>
       <x:c r="I139" s="43" t="n">
-        <x:v>0.010791442367504622</x:v>
+        <x:v>0.010792359383515304</x:v>
       </x:c>
       <x:c r="J139" s="26" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
@@ -22035,22 +22035,22 @@
         <x:v>6月23日</x:v>
       </x:c>
       <x:c r="D140" s="23" t="n">
-        <x:v>8838.763</x:v>
+        <x:v>8838.76</x:v>
       </x:c>
       <x:c r="E140" s="23" t="n">
-        <x:v>8862.719</x:v>
+        <x:v>8862.72</x:v>
       </x:c>
       <x:c r="F140" s="23" t="n">
-        <x:v>8626.101</x:v>
+        <x:v>8626.1</x:v>
       </x:c>
       <x:c r="G140" s="23" t="n">
-        <x:v>8680.039</x:v>
+        <x:v>8680.04</x:v>
       </x:c>
       <x:c r="H140" s="28" t="n">
         <x:v>-185.6</x:v>
       </x:c>
       <x:c r="I140" s="24" t="n">
-        <x:v>-0.020938843242184646</x:v>
+        <x:v>-0.02093917217855812</x:v>
       </x:c>
       <x:c r="J140" s="26" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
@@ -22071,22 +22071,22 @@
         <x:v>6月24日</x:v>
       </x:c>
       <x:c r="D141" s="23" t="n">
-        <x:v>8650.816</x:v>
+        <x:v>8650.82</x:v>
       </x:c>
       <x:c r="E141" s="23" t="n">
-        <x:v>8803.501</x:v>
+        <x:v>8803.5</x:v>
       </x:c>
       <x:c r="F141" s="23" t="n">
-        <x:v>8581.751</x:v>
+        <x:v>8581.75</x:v>
       </x:c>
       <x:c r="G141" s="23" t="n">
-        <x:v>8793.487</x:v>
+        <x:v>8793.49</x:v>
       </x:c>
       <x:c r="H141" s="23" t="n">
         <x:v>113.4</x:v>
       </x:c>
       <x:c r="I141" s="24" t="n">
-        <x:v>0.01306998735835152</x:v>
+        <x:v>0.013070216266284351</x:v>
       </x:c>
       <x:c r="J141" s="26" t="n">
         <x:f>ROUND(E141-F141,1)</x:f>
@@ -22107,13 +22107,13 @@
         <x:v>6月25日</x:v>
       </x:c>
       <x:c r="D142" s="23" t="n">
-        <x:v>8806.071</x:v>
+        <x:v>8806.07</x:v>
       </x:c>
       <x:c r="E142" s="23" t="n">
-        <x:v>8872.123</x:v>
+        <x:v>8872.12</x:v>
       </x:c>
       <x:c r="F142" s="23" t="n">
-        <x:v>8743.249</x:v>
+        <x:v>8743.25</x:v>
       </x:c>
       <x:c r="G142" s="23" t="n">
         <x:v>8825.92</x:v>
@@ -22122,7 +22122,7 @@
         <x:v>32.4</x:v>
       </x:c>
       <x:c r="I142" s="24" t="n">
-        <x:v>0.0036882979414196715</x:v>
+        <x:v>0.003687955521641584</x:v>
       </x:c>
       <x:c r="J142" s="23" t="n">
         <x:f>ROUND(E142-F142,1)</x:f>
@@ -22143,22 +22143,22 @@
         <x:v>6月26日</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>8771.598</x:v>
+        <x:v>8771.6</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
-        <x:v>8797.282</x:v>
+        <x:v>8797.28</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>8563.695</x:v>
+        <x:v>8563.7</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
-        <x:v>8601.408</x:v>
+        <x:v>8601.41</x:v>
       </x:c>
       <x:c r="H143" s="28" t="n">
         <x:v>-224.5</x:v>
       </x:c>
       <x:c r="I143" s="24" t="n">
-        <x:v>-0.025437801385011505</x:v>
+        <x:v>-0.025437574779739736</x:v>
       </x:c>
       <x:c r="J143" s="26" t="n">
         <x:f>ROUND(E143-F143,1)</x:f>
@@ -22179,22 +22179,22 @@
         <x:v>6月29日</x:v>
       </x:c>
       <x:c r="D144" s="23" t="n">
-        <x:v>8616.424</x:v>
+        <x:v>8616.42</x:v>
       </x:c>
       <x:c r="E144" s="23" t="n">
         <x:v>8677.63</x:v>
       </x:c>
       <x:c r="F144" s="23" t="n">
-        <x:v>8413.864</x:v>
+        <x:v>8413.86</x:v>
       </x:c>
       <x:c r="G144" s="23" t="n">
-        <x:v>8597.893</x:v>
+        <x:v>8597.89</x:v>
       </x:c>
       <x:c r="H144" s="23" t="n">
         <x:v>-3.5</x:v>
       </x:c>
       <x:c r="I144" s="24" t="n">
-        <x:v>-0.00040865402501533143</x:v>
+        <x:v>-0.0004092352300378854</x:v>
       </x:c>
       <x:c r="J144" s="26" t="n">
         <x:f>ROUND(E144-F144,1)</x:f>
@@ -22218,19 +22218,19 @@
         <x:v>8574.25</x:v>
       </x:c>
       <x:c r="E145" s="23" t="n">
-        <x:v>8815.108</x:v>
+        <x:v>8815.11</x:v>
       </x:c>
       <x:c r="F145" s="23" t="n">
-        <x:v>8547.312</x:v>
+        <x:v>8547.31</x:v>
       </x:c>
       <x:c r="G145" s="23" t="n">
-        <x:v>8809.786</x:v>
+        <x:v>8809.79</x:v>
       </x:c>
       <x:c r="H145" s="28" t="n">
         <x:v>211.9</x:v>
       </x:c>
       <x:c r="I145" s="24" t="n">
-        <x:v>0.024644758896162022</x:v>
+        <x:v>0.02464558164852093</x:v>
       </x:c>
       <x:c r="J145" s="26" t="n">
         <x:f>ROUND(E145-F145,1)</x:f>
@@ -22342,10 +22342,10 @@
         <x:v>8827.47</x:v>
       </x:c>
       <x:c r="E151" s="23" t="n">
-        <x:v>8944.195</x:v>
+        <x:v>8944.19</x:v>
       </x:c>
       <x:c r="F151" s="23" t="n">
-        <x:v>8806.646</x:v>
+        <x:v>8806.65</x:v>
       </x:c>
       <x:c r="G151" s="23" t="n">
         <x:v>8876.63</x:v>
@@ -22354,7 +22354,7 @@
         <x:v>66.8</x:v>
       </x:c>
       <x:c r="I151" s="24" t="n">
-        <x:v>0.007587471477740637</x:v>
+        <x:v>0.007587013992387925</x:v>
       </x:c>
       <x:c r="J151" s="23" t="n">
         <x:f>ROUND(E151-F151,1)</x:f>
@@ -22375,22 +22375,22 @@
         <x:v>7月2日</x:v>
       </x:c>
       <x:c r="D152" s="23" t="n">
-        <x:v>8688.291</x:v>
+        <x:v>8688.29</x:v>
       </x:c>
       <x:c r="E152" s="23" t="n">
-        <x:v>8865.966</x:v>
+        <x:v>8865.97</x:v>
       </x:c>
       <x:c r="F152" s="23" t="n">
-        <x:v>8598.869</x:v>
+        <x:v>8598.87</x:v>
       </x:c>
       <x:c r="G152" s="23" t="n">
-        <x:v>8625.334</x:v>
+        <x:v>8625.33</x:v>
       </x:c>
       <x:c r="H152" s="28" t="n">
         <x:v>-251.3</x:v>
       </x:c>
       <x:c r="I152" s="24" t="n">
-        <x:v>-0.02830984281196791</x:v>
+        <x:v>-0.028310293433431277</x:v>
       </x:c>
       <x:c r="J152" s="26" t="n">
         <x:f>ROUND(E152-F152,1)</x:f>
@@ -22411,22 +22411,22 @@
         <x:v>7月3日</x:v>
       </x:c>
       <x:c r="D153" s="23" t="n">
-        <x:v>8627.382</x:v>
+        <x:v>8627.38</x:v>
       </x:c>
       <x:c r="E153" s="23" t="n">
-        <x:v>8740.668</x:v>
+        <x:v>8740.67</x:v>
       </x:c>
       <x:c r="F153" s="23" t="n">
-        <x:v>8559.285</x:v>
+        <x:v>8559.28</x:v>
       </x:c>
       <x:c r="G153" s="23" t="n">
-        <x:v>8620.789</x:v>
+        <x:v>8620.79</x:v>
       </x:c>
       <x:c r="H153" s="23" t="n">
         <x:v>-4.5</x:v>
       </x:c>
       <x:c r="I153" s="24" t="n">
-        <x:v>-0.0005269361163289243</x:v>
+        <x:v>-0.0005263566727300439</x:v>
       </x:c>
       <x:c r="J153" s="26" t="n">
         <x:f>ROUND(E153-F153,1)</x:f>
@@ -22447,22 +22447,22 @@
         <x:v>7月6日</x:v>
       </x:c>
       <x:c r="D154" s="23" t="n">
-        <x:v>8669.123</x:v>
+        <x:v>8669.12</x:v>
       </x:c>
       <x:c r="E154" s="23" t="n">
-        <x:v>8694.805</x:v>
+        <x:v>8694.8</x:v>
       </x:c>
       <x:c r="F154" s="23" t="n">
-        <x:v>8432.897</x:v>
+        <x:v>8432.9</x:v>
       </x:c>
       <x:c r="G154" s="23" t="n">
-        <x:v>8472.603</x:v>
+        <x:v>8472.6</x:v>
       </x:c>
       <x:c r="H154" s="23" t="n">
         <x:v>-148.2</x:v>
       </x:c>
       <x:c r="I154" s="24" t="n">
-        <x:v>-0.01718937790960917</x:v>
+        <x:v>-0.01718983991026346</x:v>
       </x:c>
       <x:c r="J154" s="26" t="n">
         <x:f>ROUND(E154-F154,1)</x:f>
@@ -22483,22 +22483,22 @@
         <x:v>7月7日</x:v>
       </x:c>
       <x:c r="D155" s="23" t="n">
-        <x:v>8436.389</x:v>
+        <x:v>8436.39</x:v>
       </x:c>
       <x:c r="E155" s="23" t="n">
-        <x:v>8489.476</x:v>
+        <x:v>8489.48</x:v>
       </x:c>
       <x:c r="F155" s="23" t="n">
-        <x:v>8261.398</x:v>
+        <x:v>8261.4</x:v>
       </x:c>
       <x:c r="G155" s="23" t="n">
-        <x:v>8301.804</x:v>
+        <x:v>8301.8</x:v>
       </x:c>
       <x:c r="H155" s="28" t="n">
         <x:v>-170.8</x:v>
       </x:c>
       <x:c r="I155" s="24" t="n">
-        <x:v>-0.02015897593691085</x:v>
+        <x:v>-0.020159101102377175</x:v>
       </x:c>
       <x:c r="J155" s="26" t="n">
         <x:f>ROUND(E155-F155,1)</x:f>
@@ -22519,22 +22519,22 @@
         <x:v>7月8日</x:v>
       </x:c>
       <x:c r="D156" s="23" t="n">
-        <x:v>8315.962</x:v>
+        <x:v>8315.96</x:v>
       </x:c>
       <x:c r="E156" s="23" t="n">
-        <x:v>8328.965</x:v>
+        <x:v>8328.96</x:v>
       </x:c>
       <x:c r="F156" s="23" t="n">
-        <x:v>8117.861</x:v>
+        <x:v>8117.86</x:v>
       </x:c>
       <x:c r="G156" s="23" t="n">
-        <x:v>8117.861</x:v>
+        <x:v>8117.86</x:v>
       </x:c>
       <x:c r="H156" s="28" t="n">
         <x:v>-183.9</x:v>
       </x:c>
       <x:c r="I156" s="24" t="n">
-        <x:v>-0.02215699142017813</x:v>
+        <x:v>-0.02215664072851664</x:v>
       </x:c>
       <x:c r="J156" s="26" t="n">
         <x:f>ROUND(E156-F156,1)</x:f>
@@ -22555,22 +22555,22 @@
         <x:v>7月9日</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>8161.859</x:v>
+        <x:v>8161.86</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>8312.621</x:v>
+        <x:v>8312.62</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>7978.806</x:v>
+        <x:v>7978.81</x:v>
       </x:c>
       <x:c r="G157" s="23" t="n">
-        <x:v>8300.077</x:v>
+        <x:v>8300.08</x:v>
       </x:c>
       <x:c r="H157" s="28" t="n">
         <x:v>182.2</x:v>
       </x:c>
       <x:c r="I157" s="24" t="n">
-        <x:v>0.0224463069766776</x:v>
+        <x:v>0.022446802482427586</x:v>
       </x:c>
       <x:c r="J157" s="26" t="n">
         <x:f>ROUND(E157-F157,1)</x:f>
@@ -22591,22 +22591,22 @@
         <x:v>7月10日</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>8312.492</x:v>
+        <x:v>8312.49</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>8438.194</x:v>
+        <x:v>8438.19</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>8198.308</x:v>
+        <x:v>8198.31</x:v>
       </x:c>
       <x:c r="G158" s="23" t="n">
-        <x:v>8198.308</x:v>
+        <x:v>8198.31</x:v>
       </x:c>
       <x:c r="H158" s="23" t="n">
         <x:v>-101.8</x:v>
       </x:c>
       <x:c r="I158" s="24" t="n">
-        <x:v>-0.012261211552615503</x:v>
+        <x:v>-0.012261327601661764</x:v>
       </x:c>
       <x:c r="J158" s="26" t="n">
         <x:f>ROUND(E158-F158,1)</x:f>
@@ -22627,22 +22627,22 @@
         <x:v>7月13日</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>8124.363</x:v>
+        <x:v>8124.36</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>8171.504</x:v>
+        <x:v>8171.5</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7769.292</x:v>
+        <x:v>7769.29</x:v>
       </x:c>
       <x:c r="G159" s="23" t="n">
-        <x:v>7787.853</x:v>
+        <x:v>7787.85</x:v>
       </x:c>
       <x:c r="H159" s="28" t="n">
         <x:v>-410.5</x:v>
       </x:c>
       <x:c r="I159" s="24" t="n">
-        <x:v>-0.050065818459126055</x:v>
+        <x:v>-0.050066416127226065</x:v>
       </x:c>
       <x:c r="J159" s="26" t="n">
         <x:f>ROUND(E159-F159,1)</x:f>
@@ -22663,22 +22663,22 @@
         <x:v>7月14日</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>7799.813</x:v>
+        <x:v>7799.81</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>7934.103</x:v>
+        <x:v>7934.1</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>7657.671</x:v>
+        <x:v>7657.67</x:v>
       </x:c>
       <x:c r="G160" s="23" t="n">
-        <x:v>7925.123</x:v>
+        <x:v>7925.12</x:v>
       </x:c>
       <x:c r="H160" s="23" t="n">
         <x:v>137.3</x:v>
       </x:c>
       <x:c r="I160" s="24" t="n">
-        <x:v>0.017626167314662933</x:v>
+        <x:v>0.017626174104534487</x:v>
       </x:c>
       <x:c r="J160" s="26" t="n">
         <x:f>ROUND(E160-F160,1)</x:f>
@@ -22699,22 +22699,22 @@
         <x:v>7月15日</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>7959.374</x:v>
+        <x:v>7959.37</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>7979.077</x:v>
+        <x:v>7979.08</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>7783.219</x:v>
+        <x:v>7783.22</x:v>
       </x:c>
       <x:c r="G161" s="23" t="n">
-        <x:v>7817.831</x:v>
+        <x:v>7817.83</x:v>
       </x:c>
       <x:c r="H161" s="23" t="n">
         <x:v>-107.3</x:v>
       </x:c>
       <x:c r="I161" s="24" t="n">
-        <x:v>-0.01353821259304111</x:v>
+        <x:v>-0.013537965355729598</x:v>
       </x:c>
       <x:c r="J161" s="26" t="n">
         <x:f>ROUND(E161-F161,1)</x:f>
@@ -22735,22 +22735,22 @@
         <x:v>7月16日</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>7713.135</x:v>
+        <x:v>7713.14</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
         <x:v>7836.39</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>7591.421</x:v>
+        <x:v>7591.42</x:v>
       </x:c>
       <x:c r="G162" s="23" t="n">
-        <x:v>7631.762</x:v>
+        <x:v>7631.76</x:v>
       </x:c>
       <x:c r="H162" s="28" t="n">
         <x:v>-186.1</x:v>
       </x:c>
       <x:c r="I162" s="24" t="n">
-        <x:v>-0.02380059123815803</x:v>
+        <x:v>-0.023800722195289503</x:v>
       </x:c>
       <x:c r="J162" s="26" t="n">
         <x:f>ROUND(E162-F162,1)</x:f>
@@ -22771,22 +22771,22 @@
         <x:v>7月17日</x:v>
       </x:c>
       <x:c r="D163" s="42" t="n">
-        <x:v>7599.388</x:v>
+        <x:v>7599.39</x:v>
       </x:c>
       <x:c r="E163" s="42" t="n">
-        <x:v>7605.613</x:v>
+        <x:v>7605.61</x:v>
       </x:c>
       <x:c r="F163" s="42" t="n">
-        <x:v>7163.309</x:v>
+        <x:v>7163.31</x:v>
       </x:c>
       <x:c r="G163" s="42" t="n">
-        <x:v>7167.996</x:v>
+        <x:v>7168</x:v>
       </x:c>
       <x:c r="H163" s="28" t="n">
         <x:v>-463.8</x:v>
       </x:c>
       <x:c r="I163" s="43" t="n">
-        <x:v>-0.06076788034008396</x:v>
+        <x:v>-0.06076711007683677</x:v>
       </x:c>
       <x:c r="J163" s="26" t="n">
         <x:f>ROUND(E163-F163,1)</x:f>
@@ -22807,22 +22807,22 @@
         <x:v>7月20日</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>7256.267</x:v>
+        <x:v>7256.27</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>7298.122</x:v>
+        <x:v>7298.12</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>6824.145</x:v>
+        <x:v>6824.14</x:v>
       </x:c>
       <x:c r="G164" s="23" t="n">
-        <x:v>6965.376</x:v>
+        <x:v>6965.38</x:v>
       </x:c>
       <x:c r="H164" s="28" t="n">
         <x:v>-202.6</x:v>
       </x:c>
       <x:c r="I164" s="24" t="n">
-        <x:v>-0.028267314881314065</x:v>
+        <x:v>-0.028267299107142874</x:v>
       </x:c>
       <x:c r="J164" s="26" t="n">
         <x:f>ROUND(E164-F164,1)</x:f>
@@ -22843,22 +22843,22 @@
         <x:v>7月21日</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>6975.893</x:v>
+        <x:v>6975.89</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>7264.338</x:v>
+        <x:v>7264.34</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>6714.187</x:v>
+        <x:v>6714.19</x:v>
       </x:c>
       <x:c r="G165" s="23" t="n">
-        <x:v>7259.863</x:v>
+        <x:v>7259.86</x:v>
       </x:c>
       <x:c r="H165" s="28" t="n">
         <x:v>294.5</x:v>
       </x:c>
       <x:c r="I165" s="24" t="n">
-        <x:v>0.042278693928367916</x:v>
+        <x:v>0.042277664678739724</x:v>
       </x:c>
       <x:c r="J165" s="26" t="n">
         <x:f>ROUND(E165-F165,1)</x:f>
@@ -22879,22 +22879,22 @@
         <x:v>7月22日</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>7196.863</x:v>
+        <x:v>7196.86</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>7302.454</x:v>
+        <x:v>7302.45</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
         <x:v>7118.66</x:v>
       </x:c>
       <x:c r="G166" s="23" t="n">
-        <x:v>7158.762</x:v>
+        <x:v>7158.76</x:v>
       </x:c>
       <x:c r="H166" s="23" t="n">
         <x:v>-101.1</x:v>
       </x:c>
       <x:c r="I166" s="24" t="n">
-        <x:v>-0.01392602036705104</x:v>
+        <x:v>-0.013925888378012674</x:v>
       </x:c>
       <x:c r="J166" s="26" t="n">
         <x:f>ROUND(E166-F166,1)</x:f>
@@ -22915,13 +22915,13 @@
         <x:v>7月23日</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>7169.543</x:v>
+        <x:v>7169.54</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>7247.141</x:v>
+        <x:v>7247.14</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7113.498</x:v>
+        <x:v>7113.5</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
         <x:v>7195.5</x:v>
@@ -22930,7 +22930,7 @@
         <x:v>36.7</x:v>
       </x:c>
       <x:c r="I167" s="24" t="n">
-        <x:v>0.0051318929166803695</x:v>
+        <x:v>0.005132173728411127</x:v>
       </x:c>
       <x:c r="J167" s="23" t="n">
         <x:f>ROUND(E167-F167,1)</x:f>
@@ -22951,22 +22951,22 @@
         <x:v>7月24日</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>7109.248</x:v>
+        <x:v>7109.25</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>7174.552</x:v>
+        <x:v>7174.55</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>6995.693</x:v>
+        <x:v>6995.69</x:v>
       </x:c>
       <x:c r="G168" s="23" t="n">
-        <x:v>6995.693</x:v>
+        <x:v>6995.69</x:v>
       </x:c>
       <x:c r="H168" s="28" t="n">
         <x:v>-199.8</x:v>
       </x:c>
       <x:c r="I168" s="24" t="n">
-        <x:v>-0.02776832742686397</x:v>
+        <x:v>-0.027768744354110253</x:v>
       </x:c>
       <x:c r="J168" s="23" t="n">
         <x:f>ROUND(E168-F168,1)</x:f>
@@ -22987,22 +22987,22 @@
         <x:v>7月27日</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>6981.165</x:v>
+        <x:v>6981.16</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>7228.785</x:v>
+        <x:v>7228.78</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>6972.282</x:v>
+        <x:v>6972.28</x:v>
       </x:c>
       <x:c r="G169" s="23" t="n">
-        <x:v>7228.785</x:v>
+        <x:v>7228.78</x:v>
       </x:c>
       <x:c r="H169" s="28" t="n">
         <x:v>233.1</x:v>
       </x:c>
       <x:c r="I169" s="24" t="n">
-        <x:v>0.03331935806788544</x:v>
+        <x:v>0.03331908646609549</x:v>
       </x:c>
       <x:c r="J169" s="26" t="n">
         <x:f>ROUND(E169-F169,1)</x:f>
@@ -23023,22 +23023,22 @@
         <x:v>7月28日</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>7135.735</x:v>
+        <x:v>7135.73</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>7189.177</x:v>
+        <x:v>7189.18</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>6992.944</x:v>
+        <x:v>6992.94</x:v>
       </x:c>
       <x:c r="G170" s="23" t="n">
-        <x:v>7026.276</x:v>
+        <x:v>7026.28</x:v>
       </x:c>
       <x:c r="H170" s="28" t="n">
         <x:v>-202.5</x:v>
       </x:c>
       <x:c r="I170" s="24" t="n">
-        <x:v>-0.02801425135759328</x:v>
+        <x:v>-0.028013025711115858</x:v>
       </x:c>
       <x:c r="J170" s="26" t="n">
         <x:f>ROUND(E170-F170,1)</x:f>
@@ -23059,22 +23059,22 @@
         <x:v>7月29日</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>7020.223</x:v>
+        <x:v>7020.22</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>7132.352</x:v>
+        <x:v>7132.35</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>6897.392</x:v>
+        <x:v>6897.39</x:v>
       </x:c>
       <x:c r="G171" s="23" t="n">
-        <x:v>7095.186</x:v>
+        <x:v>7095.19</x:v>
       </x:c>
       <x:c r="H171" s="23" t="n">
         <x:v>68.9</x:v>
       </x:c>
       <x:c r="I171" s="24" t="n">
-        <x:v>0.009807471269275503</x:v>
+        <x:v>0.009807465685967465</x:v>
       </x:c>
       <x:c r="J171" s="26" t="n">
         <x:f>ROUND(E171-F171,1)</x:f>
@@ -23098,19 +23098,19 @@
         <x:v>7053.09</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>7121.523</x:v>
+        <x:v>7121.52</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>6841.751</x:v>
+        <x:v>6841.75</x:v>
       </x:c>
       <x:c r="G172" s="23" t="n">
-        <x:v>6900.658</x:v>
+        <x:v>6900.66</x:v>
       </x:c>
       <x:c r="H172" s="28" t="n">
         <x:v>-194.5</x:v>
       </x:c>
       <x:c r="I172" s="24" t="n">
-        <x:v>-0.027416899289179897</x:v>
+        <x:v>-0.027417165713673586</x:v>
       </x:c>
       <x:c r="J172" s="26" t="n">
         <x:f>ROUND(E172-F172,1)</x:f>
@@ -23131,22 +23131,22 @@
         <x:v>7月31日</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>7082.754</x:v>
+        <x:v>7082.75</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>7218.061</x:v>
+        <x:v>7218.06</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>7071.048</x:v>
+        <x:v>7071.05</x:v>
       </x:c>
       <x:c r="G173" s="23" t="n">
-        <x:v>7075.507</x:v>
+        <x:v>7075.51</x:v>
       </x:c>
       <x:c r="H173" s="28" t="n">
-        <x:v>174.8</x:v>
+        <x:v>174.9</x:v>
       </x:c>
       <x:c r="I173" s="24" t="n">
-        <x:v>0.02533801849041062</x:v>
+        <x:v>0.02533815606043488</x:v>
       </x:c>
       <x:c r="J173" s="23" t="n">
         <x:f>ROUND(E173-F173,1)</x:f>
@@ -23255,22 +23255,22 @@
         <x:v>8月3日</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>7055.271</x:v>
+        <x:v>7055.27</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>7118.097</x:v>
+        <x:v>7118.1</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>7042.889</x:v>
+        <x:v>7042.89</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
-        <x:v>7079.776</x:v>
+        <x:v>7079.78</x:v>
       </x:c>
       <x:c r="H179" s="23" t="n">
         <x:v>4.3</x:v>
       </x:c>
       <x:c r="I179" s="24" t="n">
-        <x:v>0.0006033489896908328</x:v>
+        <x:v>0.0006034900664404486</x:v>
       </x:c>
       <x:c r="J179" s="23" t="n">
         <x:f>ROUND(E179-F179,1)</x:f>
@@ -23291,22 +23291,22 @@
         <x:v>8月4日</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>7128.494</x:v>
+        <x:v>7128.49</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>7307.171</x:v>
+        <x:v>7307.17</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
         <x:v>7102.46</x:v>
       </x:c>
       <x:c r="G180" s="23" t="n">
-        <x:v>7279.193</x:v>
+        <x:v>7279.19</x:v>
       </x:c>
       <x:c r="H180" s="28" t="n">
         <x:v>199.4</x:v>
       </x:c>
       <x:c r="I180" s="24" t="n">
-        <x:v>0.028167134101418023</x:v>
+        <x:v>0.028166129456000055</x:v>
       </x:c>
       <x:c r="J180" s="26" t="n">
         <x:f>ROUND(E180-F180,1)</x:f>
@@ -23327,22 +23327,22 @@
         <x:v>8月5日</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>7253.225</x:v>
+        <x:v>7253.22</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>7523.498</x:v>
+        <x:v>7523.5</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>7253.225</x:v>
+        <x:v>7253.22</x:v>
       </x:c>
       <x:c r="G181" s="23" t="n">
-        <x:v>7493.048</x:v>
+        <x:v>7493.05</x:v>
       </x:c>
       <x:c r="H181" s="28" t="n">
         <x:v>213.9</x:v>
       </x:c>
       <x:c r="I181" s="24" t="n">
-        <x:v>0.029378943517502476</x:v>
+        <x:v>0.02937964251517</x:v>
       </x:c>
       <x:c r="J181" s="26" t="n">
         <x:f>ROUND(E181-F181,1)</x:f>
@@ -23363,22 +23363,22 @@
         <x:v>8月6日</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>7440.008</x:v>
+        <x:v>7440.01</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>7564.692</x:v>
+        <x:v>7564.69</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>7434.494</x:v>
+        <x:v>7434.49</x:v>
       </x:c>
       <x:c r="G182" s="23" t="n">
-        <x:v>7530.425</x:v>
+        <x:v>7530.43</x:v>
       </x:c>
       <x:c r="H182" s="23" t="n">
         <x:v>37.4</x:v>
       </x:c>
       <x:c r="I182" s="24" t="n">
-        <x:v>0.0049882237508689364</x:v>
+        <x:v>0.004988622790452535</x:v>
       </x:c>
       <x:c r="J182" s="23" t="n">
         <x:f>ROUND(E182-F182,1)</x:f>
@@ -23399,22 +23399,22 @@
         <x:v>8月7日</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>7534.242</x:v>
+        <x:v>7534.24</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
         <x:v>7685.57</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>7448.459</x:v>
+        <x:v>7448.46</x:v>
       </x:c>
       <x:c r="G183" s="23" t="n">
-        <x:v>7679.529</x:v>
+        <x:v>7679.53</x:v>
       </x:c>
       <x:c r="H183" s="23" t="n">
         <x:v>149.1</x:v>
       </x:c>
       <x:c r="I183" s="24" t="n">
-        <x:v>0.019800210479488323</x:v>
+        <x:v>0.019799666154522333</x:v>
       </x:c>
       <x:c r="J183" s="26" t="n">
         <x:f>ROUND(E183-F183,1)</x:f>
@@ -23438,7 +23438,7 @@
         <x:v>7723.38</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>7736.102</x:v>
+        <x:v>7736.1</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
         <x:v>7621.65</x:v>
@@ -23450,7 +23450,7 @@
         <x:v>54.4</x:v>
       </x:c>
       <x:c r="I184" s="24" t="n">
-        <x:v>0.007079991494269855</x:v>
+        <x:v>0.00707986035603736</x:v>
       </x:c>
       <x:c r="J184" s="23" t="n">
         <x:f>ROUND(E184-F184,1)</x:f>
@@ -23471,22 +23471,22 @@
         <x:v>8月11日</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>7686.042</x:v>
+        <x:v>7686.04</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
         <x:v>7789.21</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>7642.437</x:v>
+        <x:v>7642.44</x:v>
       </x:c>
       <x:c r="G185" s="23" t="n">
-        <x:v>7698.048</x:v>
+        <x:v>7698.05</x:v>
       </x:c>
       <x:c r="H185" s="23" t="n">
-        <x:v>-35.9</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="I185" s="24" t="n">
-        <x:v>-0.004635694798226009</x:v>
+        <x:v>-0.004635436196485543</x:v>
       </x:c>
       <x:c r="J185" s="23" t="n">
         <x:f>ROUND(E185-F185,1)</x:f>
@@ -23507,22 +23507,22 @@
         <x:v>8月12日</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>7704.959</x:v>
+        <x:v>7704.96</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>7805.272</x:v>
+        <x:v>7805.27</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>7692.438</x:v>
+        <x:v>7692.44</x:v>
       </x:c>
       <x:c r="G186" s="23" t="n">
-        <x:v>7793.717</x:v>
+        <x:v>7793.72</x:v>
       </x:c>
       <x:c r="H186" s="23" t="n">
         <x:v>95.7</x:v>
       </x:c>
       <x:c r="I186" s="24" t="n">
-        <x:v>0.012427695956169549</x:v>
+        <x:v>0.012427822630406427</x:v>
       </x:c>
       <x:c r="J186" s="23" t="n">
         <x:f>ROUND(E186-F186,1)</x:f>
@@ -23543,26 +23543,26 @@
         <x:v>8月13日</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>7847.238</x:v>
+        <x:v>7847.24</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>7880.217</x:v>
+        <x:v>7880.22</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>7714.367</x:v>
+        <x:v>7714.37</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
-        <x:v>7715.895</x:v>
+        <x:v>7715.89</x:v>
       </x:c>
       <x:c r="H187" s="23" t="n">
         <x:v>-77.8</x:v>
       </x:c>
       <x:c r="I187" s="24" t="n">
-        <x:v>-0.00998522271208968</x:v>
+        <x:v>-0.009986245335988464</x:v>
       </x:c>
       <x:c r="J187" s="23" t="n">
         <x:f>ROUND(E187-F187,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>165.9</x:v>
       </x:c>
       <x:c r="K187" s="22" t="str">
         <x:v>中证1000</x:v>
@@ -23579,13 +23579,13 @@
         <x:v>8月14日</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>7750.987</x:v>
+        <x:v>7750.99</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>7784.377</x:v>
+        <x:v>7784.38</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>7673.441</x:v>
+        <x:v>7673.44</x:v>
       </x:c>
       <x:c r="G188" s="23" t="n">
         <x:v>7769.82</x:v>
@@ -23594,7 +23594,7 @@
         <x:v>53.9</x:v>
       </x:c>
       <x:c r="I188" s="24" t="n">
-        <x:v>0.006988819832307147</x:v>
+        <x:v>0.0069894723745413945</x:v>
       </x:c>
       <x:c r="J188" s="23" t="n">
         <x:f>ROUND(E188-F188,1)</x:f>
@@ -23615,22 +23615,22 @@
         <x:v>8月17日</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>7797.184</x:v>
+        <x:v>7797.18</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>7968.383</x:v>
+        <x:v>7968.38</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>7750.433</x:v>
+        <x:v>7750.43</x:v>
       </x:c>
       <x:c r="G189" s="23" t="n">
-        <x:v>7968.383</x:v>
+        <x:v>7968.38</x:v>
       </x:c>
       <x:c r="H189" s="28" t="n">
         <x:v>198.6</x:v>
       </x:c>
       <x:c r="I189" s="24" t="n">
-        <x:v>0.02555567567845851</x:v>
+        <x:v>0.02555528956912778</x:v>
       </x:c>
       <x:c r="J189" s="26" t="n">
         <x:f>ROUND(E189-F189,1)</x:f>
@@ -23651,22 +23651,22 @@
         <x:v>8月18日</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>7969.374</x:v>
+        <x:v>7969.37</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>7995.501</x:v>
+        <x:v>7995.5</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>7842.246</x:v>
+        <x:v>7842.25</x:v>
       </x:c>
       <x:c r="G190" s="23" t="n">
-        <x:v>7945.964</x:v>
+        <x:v>7945.96</x:v>
       </x:c>
       <x:c r="H190" s="23" t="n">
         <x:v>-22.4</x:v>
       </x:c>
       <x:c r="I190" s="24" t="n">
-        <x:v>-0.002813494281085571</x:v>
+        <x:v>-0.0028136208363557236</x:v>
       </x:c>
       <x:c r="J190" s="23" t="n">
         <x:f>ROUND(E190-F190,1)</x:f>
@@ -23687,22 +23687,22 @@
         <x:v>8月19日</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>7795.259</x:v>
+        <x:v>7795.26</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>7821.177</x:v>
+        <x:v>7821.18</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>7490.212</x:v>
+        <x:v>7490.21</x:v>
       </x:c>
       <x:c r="G191" s="23" t="n">
-        <x:v>7517.768</x:v>
+        <x:v>7517.77</x:v>
       </x:c>
       <x:c r="H191" s="28" t="n">
         <x:v>-428.2</x:v>
       </x:c>
       <x:c r="I191" s="24" t="n">
-        <x:v>-0.053888489804383655</x:v>
+        <x:v>-0.0538877618311695</x:v>
       </x:c>
       <x:c r="J191" s="26" t="n">
         <x:f>ROUND(E191-F191,1)</x:f>
@@ -23723,22 +23723,22 @@
         <x:v>8月20日</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>7602.498</x:v>
+        <x:v>7602.5</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>7656.613</x:v>
+        <x:v>7656.61</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>7541.475</x:v>
+        <x:v>7541.48</x:v>
       </x:c>
       <x:c r="G192" s="23" t="n">
-        <x:v>7589.779</x:v>
+        <x:v>7589.78</x:v>
       </x:c>
       <x:c r="H192" s="23" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="I192" s="24" t="n">
-        <x:v>0.009578773912682692</x:v>
+        <x:v>0.009578638346211532</x:v>
       </x:c>
       <x:c r="J192" s="23" t="n">
         <x:f>ROUND(E192-F192,1)</x:f>
@@ -23764,7 +23764,7 @@
       <x:c r="I193" s="30"/>
       <x:c r="J193" s="32" t="n">
         <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>2385.6</x:v>
+        <x:v>2385.7</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
     </x:row>
@@ -42463,30 +42463,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>2231</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>7550</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>7582.2</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>7482.8</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>7516.2</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>47.4</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>0.0063464010282776595</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>99.4</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -42494,11 +42512,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>171.6</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>2330.4</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>166.5</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -61177,30 +61213,48 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B192" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C192" s="30"/>
-      <x:c r="D192" s="30"/>
-      <x:c r="E192" s="30"/>
-      <x:c r="F192" s="30"/>
-      <x:c r="G192" s="30"/>
-      <x:c r="H192" s="30"/>
-      <x:c r="I192" s="30"/>
-      <x:c r="J192" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J191),1)</x:f>
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="K192" s="30"/>
+      <x:c r="A192" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B192" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C192" s="22" t="str">
+        <x:v>8月20日</x:v>
+      </x:c>
+      <x:c r="D192" s="23" t="n">
+        <x:v>2871.6</x:v>
+      </x:c>
+      <x:c r="E192" s="23" t="n">
+        <x:v>2880.8</x:v>
+      </x:c>
+      <x:c r="F192" s="23" t="n">
+        <x:v>2848</x:v>
+      </x:c>
+      <x:c r="G192" s="23" t="n">
+        <x:v>2858.8</x:v>
+      </x:c>
+      <x:c r="H192" s="23" t="n">
+        <x:v>-6.2</x:v>
+      </x:c>
+      <x:c r="I192" s="24" t="n">
+        <x:v>-0.0021640488656194945</x:v>
+      </x:c>
+      <x:c r="J192" s="23" t="n">
+        <x:f>ROUND(E192-F192,1)</x:f>
+        <x:v>32.8</x:v>
+      </x:c>
+      <x:c r="K192" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B193" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B193" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C193" s="30"/>
       <x:c r="D193" s="30"/>
       <x:c r="E193" s="30"/>
@@ -61208,11 +61262,29 @@
       <x:c r="G193" s="30"/>
       <x:c r="H193" s="30"/>
       <x:c r="I193" s="30"/>
-      <x:c r="J193" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J191),0),1)</x:f>
-        <x:v>34.6</x:v>
+      <x:c r="J193" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J192),1)</x:f>
+        <x:v>482.8</x:v>
       </x:c>
       <x:c r="K193" s="30"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B194" s="30"/>
+      <x:c r="C194" s="30"/>
+      <x:c r="D194" s="30"/>
+      <x:c r="E194" s="30"/>
+      <x:c r="F194" s="30"/>
+      <x:c r="G194" s="30"/>
+      <x:c r="H194" s="30"/>
+      <x:c r="I194" s="30"/>
+      <x:c r="J194" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
+        <x:v>34.5</x:v>
+      </x:c>
+      <x:c r="K194" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Re21a1a73109549ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf3f900f1630749dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R65a30dc9cf2f4153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rda1ba70c062c48af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra2a9afdcc8fe40d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R21f1c60e17b348be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R76ed75ac8aa04045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R0be543999a5240ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6ed532afffb44ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R474fd0be94ef4339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8e5e02039b324f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd55d72c8ec524da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8e3480f46661472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R3a36967479ef441e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rd5965369eb3745eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcdd086c483c64b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R4e8ae3574d994590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re1d3f324c68740f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9ce1b4bcbcdc48e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R2edaf9963bc24823"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7656.61</x:v>
+        <x:v>7634.08</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7541.48</x:v>
+        <x:v>7472.49</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>115.1</x:v>
+        <x:v>161.6</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>27501.6</x:v>
+        <x:v>27663.2</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>179.7</x:v>
+        <x:v>179.6</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7923.91</x:v>
+        <x:v>7877.34</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7796.28</x:v>
+        <x:v>7756.28</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>127.6</x:v>
+        <x:v>121.1</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>27625.4</x:v>
+        <x:v>27746.5</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>180.6</x:v>
+        <x:v>180.2</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3925.06</x:v>
+        <x:v>3912.13</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3888.1</x:v>
+        <x:v>3883.79</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>37</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>7576.9</x:v>
+        <x:v>7605.2</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>49.5</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7582.2</x:v>
+        <x:v>7575</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7482.8</x:v>
+        <x:v>7410</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>99.4</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>29158.2</x:v>
+        <x:v>29323.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.6</x:v>
+        <x:v>190.4</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>152600</x:v>
+        <x:v>157000</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>149800</x:v>
+        <x:v>150020</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>2800</x:v>
+        <x:v>6980</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1318440</x:v>
+        <x:v>1325420</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8617.3</x:v>
+        <x:v>8606.6</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7077,30 +7077,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>67120</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>151500</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>157000</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>150020</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>156140</x:v>
+      </x:c>
+      <x:c r="H193" s="28" t="n">
+        <x:v>4640</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.03062706270627058</x:v>
+      </x:c>
+      <x:c r="J193" s="26" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>6980</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -7108,11 +7126,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>4794.3</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>74100</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>4940</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8379,7 +8415,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
         <x:v>7797.18</x:v>
@@ -8388,28 +8424,28 @@
         <x:v>7995.5</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>7490.21</x:v>
+        <x:v>7472.49</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>7589.78</x:v>
+        <x:v>7601.8</x:v>
       </x:c>
       <x:c r="G36" s="28" t="n">
         <x:f>ROUND(F36-F35,1)</x:f>
-        <x:v>-180</x:v>
+        <x:v>-168</x:v>
       </x:c>
       <x:c r="H36" s="24" t="n">
         <x:f>IFERROR(F36/F35-1,"")</x:f>
-        <x:v>-0.023171707967494792</x:v>
+        <x:v>-0.021624696582417502</x:v>
       </x:c>
       <x:c r="I36" s="26" t="n">
         <x:f>ROUND(D36-E36,1)</x:f>
-        <x:v>505.3</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="J36" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K36" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8427,7 +8463,7 @@
       <x:c r="H37" s="30"/>
       <x:c r="I37" s="32" t="n">
         <x:f>ROUND(SUM(I5:I36),1)</x:f>
-        <x:v>13475.8</x:v>
+        <x:v>13493.5</x:v>
       </x:c>
       <x:c r="J37" s="30"/>
       <x:c r="K37" s="30"/>
@@ -8445,7 +8481,7 @@
       <x:c r="H38" s="30"/>
       <x:c r="I38" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I36),0),1)</x:f>
-        <x:v>421.1</x:v>
+        <x:v>421.7</x:v>
       </x:c>
       <x:c r="J38" s="30"/>
       <x:c r="K38" s="30"/>
@@ -9677,7 +9713,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C73" s="23" t="n">
         <x:v>8007.87</x:v>
@@ -9686,28 +9722,28 @@
         <x:v>8211.31</x:v>
       </x:c>
       <x:c r="E73" s="23" t="n">
-        <x:v>7762.29</x:v>
+        <x:v>7756.28</x:v>
       </x:c>
       <x:c r="F73" s="23" t="n">
-        <x:v>7850.4</x:v>
+        <x:v>7854.33</x:v>
       </x:c>
       <x:c r="G73" s="23" t="n">
         <x:f>ROUND(F73-F72,1)</x:f>
-        <x:v>-139.9</x:v>
+        <x:v>-136</x:v>
       </x:c>
       <x:c r="H73" s="24" t="n">
         <x:f>IFERROR(F73/F72-1,"")</x:f>
-        <x:v>-0.01751241813542126</x:v>
+        <x:v>-0.01702057361836118</x:v>
       </x:c>
       <x:c r="I73" s="26" t="n">
         <x:f>ROUND(D73-E73,1)</x:f>
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="J73" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K73" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -9725,7 +9761,7 @@
       <x:c r="H74" s="30"/>
       <x:c r="I74" s="32" t="n">
         <x:f>ROUND(SUM(I42:I73),1)</x:f>
-        <x:v>13574.4</x:v>
+        <x:v>13580.4</x:v>
       </x:c>
       <x:c r="J74" s="30"/>
       <x:c r="K74" s="30"/>
@@ -9743,7 +9779,7 @@
       <x:c r="H75" s="30"/>
       <x:c r="I75" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I42:I73),0),1)</x:f>
-        <x:v>424.2</x:v>
+        <x:v>424.4</x:v>
       </x:c>
       <x:c r="J75" s="30"/>
       <x:c r="K75" s="30"/>
@@ -10975,7 +11011,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B110" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C110" s="23" t="n">
         <x:v>3930.1</x:v>
@@ -10987,15 +11023,15 @@
         <x:v>3879.58</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>3903.72</x:v>
+        <x:v>3905.2</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
         <x:f>ROUND(F110-F109,1)</x:f>
-        <x:v>-23.5</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="H110" s="24" t="n">
         <x:f>IFERROR(F110/F109-1,"")</x:f>
-        <x:v>-0.005973752158037082</x:v>
+        <x:v>-0.00559689140808417</x:v>
       </x:c>
       <x:c r="I110" s="26" t="n">
         <x:f>ROUND(D110-E110,1)</x:f>
@@ -11005,7 +11041,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K110" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -12273,7 +12309,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B147" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C147" s="23" t="n">
         <x:v>7675</x:v>
@@ -12282,28 +12318,28 @@
         <x:v>7882.8</x:v>
       </x:c>
       <x:c r="E147" s="23" t="n">
-        <x:v>7430</x:v>
+        <x:v>7410</x:v>
       </x:c>
       <x:c r="F147" s="23" t="n">
-        <x:v>7516.2</x:v>
+        <x:v>7527</x:v>
       </x:c>
       <x:c r="G147" s="23" t="n">
         <x:f>ROUND(F147-F146,1)</x:f>
-        <x:v>-134</x:v>
+        <x:v>-123.2</x:v>
       </x:c>
       <x:c r="H147" s="24" t="n">
         <x:f>IFERROR(F147/F146-1,"")</x:f>
-        <x:v>-0.01751588193772713</x:v>
+        <x:v>-0.016104154139761073</x:v>
       </x:c>
       <x:c r="I147" s="26" t="n">
         <x:f>ROUND(D147-E147,1)</x:f>
-        <x:v>452.8</x:v>
+        <x:v>472.8</x:v>
       </x:c>
       <x:c r="J147" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K147" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -12321,7 +12357,7 @@
       <x:c r="H148" s="30"/>
       <x:c r="I148" s="32" t="n">
         <x:f>ROUND(SUM(I116:I147),1)</x:f>
-        <x:v>14052</x:v>
+        <x:v>14072</x:v>
       </x:c>
       <x:c r="J148" s="30"/>
       <x:c r="K148" s="30"/>
@@ -12339,7 +12375,7 @@
       <x:c r="H149" s="30"/>
       <x:c r="I149" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I116:I147),0),1)</x:f>
-        <x:v>439.1</x:v>
+        <x:v>439.8</x:v>
       </x:c>
       <x:c r="J149" s="30"/>
       <x:c r="K149" s="30"/>
@@ -17465,37 +17501,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
         <x:v>154300</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>155980</x:v>
+        <x:v>157000</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
         <x:v>148400</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>156140</x:v>
       </x:c>
       <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-2440</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.01585033129790825</x:v>
+        <x:v>0.014291282317786091</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>7580</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K295" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -17513,7 +17549,7 @@
       <x:c r="H296" s="30"/>
       <x:c r="I296" s="32" t="n">
         <x:f>ROUND(SUM(I264:I295),1)</x:f>
-        <x:v>675660</x:v>
+        <x:v>676680</x:v>
       </x:c>
       <x:c r="J296" s="30"/>
       <x:c r="K296" s="30"/>
@@ -17531,7 +17567,7 @@
       <x:c r="H297" s="30"/>
       <x:c r="I297" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I264:I295),0),1)</x:f>
-        <x:v>21114.4</x:v>
+        <x:v>21146.3</x:v>
       </x:c>
       <x:c r="J297" s="30"/>
       <x:c r="K297" s="30"/>
@@ -23749,30 +23785,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>2385.7</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>7555.55</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>7634.08</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>7472.49</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>7601.8</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.0015837086186951677</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>161.6</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -23780,11 +23834,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>170.4</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>2547.3</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>169.8</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -29999,30 +30071,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>2329.4</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>7812.26</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>7877.34</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>7756.28</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>7854.33</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.0005006114338124146</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>121.1</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -30030,11 +30120,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>166.4</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>2450.5</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>163.4</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -36249,30 +36357,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>601.6</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>3891.18</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>3912.13</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>3883.79</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>3905.2</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.0003791255520375625</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>28.3</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -36280,11 +36406,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>43</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>629.9</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -42499,30 +42643,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>2330.4</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>7575</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>7410</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>7527</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.0014368963039834703</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -42530,11 +42692,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>166.5</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>2495.4</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>166.4</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8e5e02039b324f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd55d72c8ec524da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8e3480f46661472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R3a36967479ef441e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rd5965369eb3745eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcdd086c483c64b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R4e8ae3574d994590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re1d3f324c68740f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9ce1b4bcbcdc48e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R2edaf9963bc24823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7ad68763f8bc40cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra35ad29e59554802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd86fdd2ffa8649b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R73ca806ec516410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcfc0e6b9c6614839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3f0a0eb5cc6b4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R22f90d37c1f34844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R49a5523920454040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9e9b8900080e4d7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R70ae6648aaa143b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7811</x:v>
+        <x:v>7797.2</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7713</x:v>
+        <x:v>7669.6</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>98</x:v>
+        <x:v>127.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>30479.6</x:v>
+        <x:v>30607.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>199.2</x:v>
+        <x:v>198.7</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4585</x:v>
+        <x:v>4595.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4532.4</x:v>
+        <x:v>4542.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>52.6</x:v>
+        <x:v>53.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>11420.2</x:v>
+        <x:v>11473.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>74.6</x:v>
+        <x:v>74.5</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2880.8</x:v>
+        <x:v>2873</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2848</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>32.8</x:v>
+        <x:v>25.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6360.6</x:v>
+        <x:v>6386.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>41.6</x:v>
+        <x:v>41.5</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -13607,7 +13607,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
         <x:v>7885</x:v>
@@ -13616,28 +13616,28 @@
         <x:v>8091.8</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>7680.2</x:v>
+        <x:v>7669.6</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>7761</x:v>
+        <x:v>7762</x:v>
       </x:c>
       <x:c r="G184" s="23" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>-100.2</x:v>
+        <x:v>-99.2</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>-0.012746145626621908</x:v>
+        <x:v>-0.012618938584439965</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>411.6</x:v>
+        <x:v>422.2</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K184" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -13655,7 +13655,7 @@
       <x:c r="H185" s="30"/>
       <x:c r="I185" s="32" t="n">
         <x:f>ROUND(SUM(I153:I184),1)</x:f>
-        <x:v>14636.4</x:v>
+        <x:v>14647</x:v>
       </x:c>
       <x:c r="J185" s="30"/>
       <x:c r="K185" s="30"/>
@@ -13673,7 +13673,7 @@
       <x:c r="H186" s="30"/>
       <x:c r="I186" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I153:I184),0),1)</x:f>
-        <x:v>457.4</x:v>
+        <x:v>457.7</x:v>
       </x:c>
       <x:c r="J186" s="30"/>
       <x:c r="K186" s="30"/>
@@ -14905,7 +14905,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
         <x:v>4624</x:v>
@@ -14917,15 +14917,15 @@
         <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4554</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>-66.4</x:v>
+        <x:v>-44.4</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>-0.014371050125530194</x:v>
+        <x:v>-0.00960955761405935</x:v>
       </x:c>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
@@ -14935,7 +14935,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -16203,7 +16203,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>8月17日-8月20日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
         <x:v>2886</x:v>
@@ -16215,15 +16215,15 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2858.8</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>-31.2</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>-0.01079584775086495</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
@@ -16233,7 +16233,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K258" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -48929,30 +48929,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>2307</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>7744</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>7797.2</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>7669.6</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>7762</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.00012884937508061967</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>127.6</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -48960,11 +48978,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>164.8</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>2434.6</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>162.3</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -55179,30 +55215,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>860.6</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>4556</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>4595.8</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>4542.4</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>4576</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.004830917874396157</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>53.4</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -55210,11 +55264,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>61.5</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>60.9</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -61429,30 +61501,48 @@
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B193" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C193" s="30"/>
-      <x:c r="D193" s="30"/>
-      <x:c r="E193" s="30"/>
-      <x:c r="F193" s="30"/>
-      <x:c r="G193" s="30"/>
-      <x:c r="H193" s="30"/>
-      <x:c r="I193" s="30"/>
-      <x:c r="J193" s="32" t="n">
-        <x:f>ROUND(SUM(J179:J192),1)</x:f>
-        <x:v>482.8</x:v>
-      </x:c>
-      <x:c r="K193" s="30"/>
+      <x:c r="A193" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B193" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C193" s="41" t="str">
+        <x:v>8月21日</x:v>
+      </x:c>
+      <x:c r="D193" s="42" t="n">
+        <x:v>2854</x:v>
+      </x:c>
+      <x:c r="E193" s="42" t="n">
+        <x:v>2873</x:v>
+      </x:c>
+      <x:c r="F193" s="42" t="n">
+        <x:v>2847.2</x:v>
+      </x:c>
+      <x:c r="G193" s="42" t="n">
+        <x:v>2861</x:v>
+      </x:c>
+      <x:c r="H193" s="42" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="I193" s="43" t="n">
+        <x:v>0.0007695536588778751</x:v>
+      </x:c>
+      <x:c r="J193" s="42" t="n">
+        <x:f>ROUND(E193-F193,1)</x:f>
+        <x:v>25.8</x:v>
+      </x:c>
+      <x:c r="K193" s="41" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B194" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B194" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C194" s="30"/>
       <x:c r="D194" s="30"/>
       <x:c r="E194" s="30"/>
@@ -61460,11 +61550,29 @@
       <x:c r="G194" s="30"/>
       <x:c r="H194" s="30"/>
       <x:c r="I194" s="30"/>
-      <x:c r="J194" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J179:J192),0),1)</x:f>
-        <x:v>34.5</x:v>
+      <x:c r="J194" s="32" t="n">
+        <x:f>ROUND(SUM(J179:J193),1)</x:f>
+        <x:v>508.6</x:v>
       </x:c>
       <x:c r="K194" s="30"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B195" s="30"/>
+      <x:c r="C195" s="30"/>
+      <x:c r="D195" s="30"/>
+      <x:c r="E195" s="30"/>
+      <x:c r="F195" s="30"/>
+      <x:c r="G195" s="30"/>
+      <x:c r="H195" s="30"/>
+      <x:c r="I195" s="30"/>
+      <x:c r="J195" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J179:J193),0),1)</x:f>
+        <x:v>33.9</x:v>
+      </x:c>
+      <x:c r="K195" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R4ba8a38f0e934e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R16714056187c48a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rec124e61ebe14ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rad8b523b66a445d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R882e166613394cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R5a77aec71af84f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R1f97e13ab776430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R24254bfe04bc4d2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rfb9e1f111bca45b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rfacb77491fc04184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rfbcc50c283064c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1cfc53c1f2be46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R74ca989657f94b8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R948c4b3a96354826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8a6f986add5f4891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re481092b1242468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R123c0731947c4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R383592c8c66d46e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R48d442b4ad224758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R657eb7601f8546e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7575</x:v>
+        <x:v>7549</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7410</x:v>
+        <x:v>7308.8</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>165</x:v>
+        <x:v>240.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>29323.2</x:v>
+        <x:v>29563.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>190.4</x:v>
+        <x:v>190.7</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -12493,155 +12493,155 @@
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B151" s="30" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C151" s="30"/>
-      <x:c r="D151" s="30"/>
-      <x:c r="E151" s="30"/>
-      <x:c r="F151" s="30"/>
-      <x:c r="G151" s="30"/>
-      <x:c r="H151" s="30"/>
-      <x:c r="I151" s="32" t="n">
-        <x:f>ROUND(SUM(I119:I150),1)</x:f>
-        <x:v>14072</x:v>
-      </x:c>
-      <x:c r="J151" s="30"/>
-      <x:c r="K151" s="30"/>
+      <x:c r="A151" s="22" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B151" s="22" t="str">
+        <x:v>8月24日</x:v>
+      </x:c>
+      <x:c r="C151" s="23" t="n">
+        <x:v>7534.8</x:v>
+      </x:c>
+      <x:c r="D151" s="23" t="n">
+        <x:v>7549</x:v>
+      </x:c>
+      <x:c r="E151" s="23" t="n">
+        <x:v>7308.8</x:v>
+      </x:c>
+      <x:c r="F151" s="23" t="n">
+        <x:v>7425.8</x:v>
+      </x:c>
+      <x:c r="G151" s="23" t="n">
+        <x:f>ROUND(F151-F150,1)</x:f>
+        <x:v>-101.2</x:v>
+      </x:c>
+      <x:c r="H151" s="24" t="n">
+        <x:f>IFERROR(F151/F150-1,"")</x:f>
+        <x:v>-0.013444931579646546</x:v>
+      </x:c>
+      <x:c r="I151" s="26" t="n">
+        <x:f>ROUND(D151-E151,1)</x:f>
+        <x:v>240.2</x:v>
+      </x:c>
+      <x:c r="J151" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+      <x:c r="K151" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B152" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B152" s="30" t="n">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="C152" s="30"/>
       <x:c r="D152" s="30"/>
       <x:c r="E152" s="30"/>
       <x:c r="F152" s="30"/>
       <x:c r="G152" s="30"/>
       <x:c r="H152" s="30"/>
-      <x:c r="I152" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I119:I150),0),1)</x:f>
-        <x:v>439.8</x:v>
+      <x:c r="I152" s="32" t="n">
+        <x:f>ROUND(SUM(I119:I151),1)</x:f>
+        <x:v>14312.2</x:v>
       </x:c>
       <x:c r="J152" s="30"/>
       <x:c r="K152" s="30"/>
     </x:row>
-    <x:row r="154">
-      <x:c r="A154" s="17" t="str">
+    <x:row r="153">
+      <x:c r="A153" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B153" s="30"/>
+      <x:c r="C153" s="30"/>
+      <x:c r="D153" s="30"/>
+      <x:c r="E153" s="30"/>
+      <x:c r="F153" s="30"/>
+      <x:c r="G153" s="30"/>
+      <x:c r="H153" s="30"/>
+      <x:c r="I153" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I119:I151),0),1)</x:f>
+        <x:v>433.7</x:v>
+      </x:c>
+      <x:c r="J153" s="30"/>
+      <x:c r="K153" s="30"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="17" t="str">
         <x:v>IC主力</x:v>
       </x:c>
-      <x:c r="B154" s="17"/>
-      <x:c r="C154" s="17"/>
-      <x:c r="D154" s="17"/>
-      <x:c r="E154" s="17"/>
-      <x:c r="F154" s="17"/>
-      <x:c r="G154" s="17"/>
-      <x:c r="H154" s="17"/>
-      <x:c r="I154" s="17"/>
-      <x:c r="J154" s="17"/>
-      <x:c r="K154" s="17"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="20" t="str">
+      <x:c r="B155" s="17"/>
+      <x:c r="C155" s="17"/>
+      <x:c r="D155" s="17"/>
+      <x:c r="E155" s="17"/>
+      <x:c r="F155" s="17"/>
+      <x:c r="G155" s="17"/>
+      <x:c r="H155" s="17"/>
+      <x:c r="I155" s="17"/>
+      <x:c r="J155" s="17"/>
+      <x:c r="K155" s="17"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B155" s="20" t="str">
+      <x:c r="B156" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C155" s="20" t="str">
+      <x:c r="C156" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D155" s="20" t="str">
+      <x:c r="D156" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E155" s="20" t="str">
+      <x:c r="E156" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F155" s="20" t="str">
+      <x:c r="F156" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G155" s="20" t="str">
+      <x:c r="G156" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H155" s="20" t="str">
+      <x:c r="H156" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I155" s="20" t="str">
+      <x:c r="I156" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J155" s="20" t="str">
+      <x:c r="J156" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K155" s="20" t="str">
+      <x:c r="K156" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B156" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C156" s="23" t="n">
-        <x:v>7424.4</x:v>
-      </x:c>
-      <x:c r="D156" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="E156" s="23" t="n">
-        <x:v>7422</x:v>
-      </x:c>
-      <x:c r="F156" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="G156" s="23"/>
-      <x:c r="H156" s="24"/>
-      <x:c r="I156" s="26" t="n">
-        <x:f>ROUND(D156-E156,1)</x:f>
-        <x:v>615.8</x:v>
-      </x:c>
-      <x:c r="J156" s="22" t="str">
-        <x:v>IC2603</x:v>
-      </x:c>
-      <x:c r="K156" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B157" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C157" s="23" t="n">
-        <x:v>8099</x:v>
+        <x:v>7424.4</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>8388.6</x:v>
+        <x:v>8037.8</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>8044</x:v>
+        <x:v>7422</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>8210.4</x:v>
-      </x:c>
-      <x:c r="G157" s="28" t="n">
-        <x:f>ROUND(F157-F156,1)</x:f>
-        <x:v>172.6</x:v>
-      </x:c>
-      <x:c r="H157" s="24" t="n">
-        <x:f>IFERROR(F157/F156-1,"")</x:f>
-        <x:v>0.02147353753514647</x:v>
-      </x:c>
+        <x:v>8037.8</x:v>
+      </x:c>
+      <x:c r="G157" s="23"/>
+      <x:c r="H157" s="24"/>
       <x:c r="I157" s="26" t="n">
         <x:f>ROUND(D157-E157,1)</x:f>
-        <x:v>344.6</x:v>
+        <x:v>615.8</x:v>
       </x:c>
       <x:c r="J157" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12652,34 +12652,34 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B158" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C158" s="23" t="n">
-        <x:v>8182.6</x:v>
+        <x:v>8099</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>8660</x:v>
+        <x:v>8388.6</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>8112</x:v>
+        <x:v>8044</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8210.4</x:v>
       </x:c>
       <x:c r="G158" s="28" t="n">
         <x:f>ROUND(F158-F157,1)</x:f>
-        <x:v>447.8</x:v>
+        <x:v>172.6</x:v>
       </x:c>
       <x:c r="H158" s="24" t="n">
         <x:f>IFERROR(F158/F157-1,"")</x:f>
-        <x:v>0.05454058267563111</x:v>
+        <x:v>0.02147353753514647</x:v>
       </x:c>
       <x:c r="I158" s="26" t="n">
         <x:f>ROUND(D158-E158,1)</x:f>
-        <x:v>548</x:v>
+        <x:v>344.6</x:v>
       </x:c>
       <x:c r="J158" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12690,34 +12690,34 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
-        <x:v>8695</x:v>
+        <x:v>8182.6</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>8728.2</x:v>
+        <x:v>8660</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>8135</x:v>
+        <x:v>8112</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>8362.4</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="G159" s="28" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>-295.8</x:v>
+        <x:v>447.8</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>-0.03416414497239628</x:v>
+        <x:v>0.05454058267563111</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
-        <x:v>593.2</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J159" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12728,34 +12728,34 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B160" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C160" s="23" t="n">
-        <x:v>8262.2</x:v>
+        <x:v>8695</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>8334.4</x:v>
+        <x:v>8728.2</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>7832</x:v>
+        <x:v>8135</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>8117.4</x:v>
+        <x:v>8362.4</x:v>
       </x:c>
       <x:c r="G160" s="28" t="n">
         <x:f>ROUND(F160-F159,1)</x:f>
-        <x:v>-245</x:v>
+        <x:v>-295.8</x:v>
       </x:c>
       <x:c r="H160" s="24" t="n">
         <x:f>IFERROR(F160/F159-1,"")</x:f>
-        <x:v>-0.029297809241366157</x:v>
+        <x:v>-0.03416414497239628</x:v>
       </x:c>
       <x:c r="I160" s="26" t="n">
         <x:f>ROUND(D160-E160,1)</x:f>
-        <x:v>502.4</x:v>
+        <x:v>593.2</x:v>
       </x:c>
       <x:c r="J160" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12766,34 +12766,34 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B161" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C161" s="23" t="n">
-        <x:v>8260</x:v>
+        <x:v>8262.2</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>8458.8</x:v>
+        <x:v>8334.4</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>8220</x:v>
+        <x:v>7832</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>8274.8</x:v>
+        <x:v>8117.4</x:v>
       </x:c>
       <x:c r="G161" s="28" t="n">
         <x:f>ROUND(F161-F160,1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>-245</x:v>
       </x:c>
       <x:c r="H161" s="24" t="n">
         <x:f>IFERROR(F161/F160-1,"")</x:f>
-        <x:v>0.019390445216448615</x:v>
+        <x:v>-0.029297809241366157</x:v>
       </x:c>
       <x:c r="I161" s="26" t="n">
         <x:f>ROUND(D161-E161,1)</x:f>
-        <x:v>238.8</x:v>
+        <x:v>502.4</x:v>
       </x:c>
       <x:c r="J161" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12804,110 +12804,110 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B162" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C162" s="23" t="n">
-        <x:v>8360</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>8650</x:v>
+        <x:v>8458.8</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
-        <x:v>8314</x:v>
+        <x:v>8220</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>8645.4</x:v>
+        <x:v>8274.8</x:v>
       </x:c>
       <x:c r="G162" s="28" t="n">
         <x:f>ROUND(F162-F161,1)</x:f>
-        <x:v>370.6</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="H162" s="24" t="n">
         <x:f>IFERROR(F162/F161-1,"")</x:f>
-        <x:v>0.04478658094455468</x:v>
+        <x:v>0.019390445216448615</x:v>
       </x:c>
       <x:c r="I162" s="26" t="n">
         <x:f>ROUND(D162-E162,1)</x:f>
-        <x:v>336</x:v>
+        <x:v>238.8</x:v>
       </x:c>
       <x:c r="J162" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K162" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
-        <x:v>8600</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>8686</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
-        <x:v>8180.6</x:v>
+        <x:v>8314</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>8322.6</x:v>
+        <x:v>8645.4</x:v>
       </x:c>
       <x:c r="G163" s="28" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>-322.8</x:v>
+        <x:v>370.6</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>-0.03733777500173496</x:v>
+        <x:v>0.04478658094455468</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K163" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B164" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C164" s="23" t="n">
-        <x:v>8201.8</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>8434.4</x:v>
+        <x:v>8686</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>8180.6</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>8213.8</x:v>
-      </x:c>
-      <x:c r="G164" s="23" t="n">
+        <x:v>8322.6</x:v>
+      </x:c>
+      <x:c r="G164" s="28" t="n">
         <x:f>ROUND(F164-F163,1)</x:f>
-        <x:v>-108.8</x:v>
+        <x:v>-322.8</x:v>
       </x:c>
       <x:c r="H164" s="24" t="n">
         <x:f>IFERROR(F164/F163-1,"")</x:f>
-        <x:v>-0.013072837815106042</x:v>
+        <x:v>-0.03733777500173496</x:v>
       </x:c>
       <x:c r="I164" s="26" t="n">
         <x:f>ROUND(D164-E164,1)</x:f>
-        <x:v>724.4</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J164" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12918,34 +12918,34 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B165" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C165" s="23" t="n">
-        <x:v>8225.2</x:v>
+        <x:v>8201.8</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>8229.6</x:v>
+        <x:v>8434.4</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>7827.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>7844.4</x:v>
-      </x:c>
-      <x:c r="G165" s="28" t="n">
+        <x:v>8213.8</x:v>
+      </x:c>
+      <x:c r="G165" s="23" t="n">
         <x:f>ROUND(F165-F164,1)</x:f>
-        <x:v>-369.4</x:v>
+        <x:v>-108.8</x:v>
       </x:c>
       <x:c r="H165" s="24" t="n">
         <x:f>IFERROR(F165/F164-1,"")</x:f>
-        <x:v>-0.04497309406121397</x:v>
+        <x:v>-0.013072837815106042</x:v>
       </x:c>
       <x:c r="I165" s="26" t="n">
         <x:f>ROUND(D165-E165,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>724.4</x:v>
       </x:c>
       <x:c r="J165" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -12956,37 +12956,37 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B166" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C166" s="23" t="n">
-        <x:v>7460</x:v>
+        <x:v>8225.2</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>7652</x:v>
+        <x:v>8229.6</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>7171</x:v>
+        <x:v>7827.8</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
-        <x:v>7559.2</x:v>
+        <x:v>7844.4</x:v>
       </x:c>
       <x:c r="G166" s="28" t="n">
         <x:f>ROUND(F166-F165,1)</x:f>
-        <x:v>-285.2</x:v>
+        <x:v>-369.4</x:v>
       </x:c>
       <x:c r="H166" s="24" t="n">
         <x:f>IFERROR(F166/F165-1,"")</x:f>
-        <x:v>-0.03635714649941357</x:v>
+        <x:v>-0.04497309406121397</x:v>
       </x:c>
       <x:c r="I166" s="26" t="n">
         <x:f>ROUND(D166-E166,1)</x:f>
-        <x:v>481</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J166" s="22" t="str">
-        <x:v>IC2606</x:v>
+        <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K166" s="22" t="n">
         <x:v>5</x:v>
@@ -12994,34 +12994,34 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
-        <x:v>7470.8</x:v>
+        <x:v>7460</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>7619</x:v>
+        <x:v>7652</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>7325.2</x:v>
+        <x:v>7171</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7352</x:v>
+        <x:v>7559.2</x:v>
       </x:c>
       <x:c r="G167" s="28" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-207.2</x:v>
+        <x:v>-285.2</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.02741030796909727</x:v>
+        <x:v>-0.03635714649941357</x:v>
       </x:c>
       <x:c r="I167" s="26" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -13032,110 +13032,110 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B168" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C168" s="23" t="n">
-        <x:v>7380</x:v>
+        <x:v>7470.8</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>7945.4</x:v>
+        <x:v>7619</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>7355.6</x:v>
+        <x:v>7325.2</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>7828.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="G168" s="28" t="n">
         <x:f>ROUND(F168-F167,1)</x:f>
-        <x:v>476.6</x:v>
+        <x:v>-207.2</x:v>
       </x:c>
       <x:c r="H168" s="24" t="n">
         <x:f>IFERROR(F168/F167-1,"")</x:f>
-        <x:v>0.06482589771490765</x:v>
+        <x:v>-0.02741030796909727</x:v>
       </x:c>
       <x:c r="I168" s="26" t="n">
         <x:f>ROUND(D168-E168,1)</x:f>
-        <x:v>589.8</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J168" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K168" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B169" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C169" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>8119.6</x:v>
+        <x:v>7945.4</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7355.6</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>8098.8</x:v>
+        <x:v>7828.6</x:v>
       </x:c>
       <x:c r="G169" s="28" t="n">
         <x:f>ROUND(F169-F168,1)</x:f>
-        <x:v>270.2</x:v>
+        <x:v>476.6</x:v>
       </x:c>
       <x:c r="H169" s="24" t="n">
         <x:f>IFERROR(F169/F168-1,"")</x:f>
-        <x:v>0.034514472574917576</x:v>
+        <x:v>0.06482589771490765</x:v>
       </x:c>
       <x:c r="I169" s="26" t="n">
         <x:f>ROUND(D169-E169,1)</x:f>
-        <x:v>327.6</x:v>
+        <x:v>589.8</x:v>
       </x:c>
       <x:c r="J169" s="22" t="str">
         <x:v